--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -6358,152 +6358,152 @@
       </c>
       <c r="B1" s="81" t="inlineStr">
         <is>
+          <t>240917</t>
+        </is>
+      </c>
+      <c r="C1" s="81" t="inlineStr">
+        <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>240823</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="T1" s="81" t="inlineStr">
         <is>
           <t>240822</t>
         </is>
       </c>
-      <c r="T1" s="81" t="inlineStr">
+      <c r="U1" s="81" t="inlineStr">
         <is>
           <t>240821</t>
         </is>
       </c>
-      <c r="U1" s="81" t="inlineStr">
+      <c r="V1" s="81" t="inlineStr">
         <is>
           <t>240820</t>
         </is>
       </c>
-      <c r="V1" s="81" t="inlineStr">
+      <c r="W1" s="81" t="inlineStr">
         <is>
           <t>240819</t>
         </is>
       </c>
-      <c r="W1" s="81" t="inlineStr">
+      <c r="X1" s="81" t="inlineStr">
         <is>
           <t>240816</t>
         </is>
       </c>
-      <c r="X1" s="81" t="inlineStr">
+      <c r="Y1" s="81" t="inlineStr">
         <is>
           <t>240815</t>
         </is>
       </c>
-      <c r="Y1" s="81" t="inlineStr">
+      <c r="Z1" s="81" t="inlineStr">
         <is>
           <t>240814</t>
         </is>
       </c>
-      <c r="Z1" s="81" t="inlineStr">
+      <c r="AA1" s="81" t="inlineStr">
         <is>
           <t>240813</t>
         </is>
       </c>
-      <c r="AA1" s="81" t="inlineStr">
+      <c r="AB1" s="81" t="inlineStr">
         <is>
           <t>240812</t>
         </is>
       </c>
-      <c r="AB1" s="81" t="inlineStr">
+      <c r="AC1" s="81" t="inlineStr">
         <is>
           <t>240809</t>
         </is>
       </c>
-      <c r="AC1" s="81" t="inlineStr">
+      <c r="AD1" s="81" t="inlineStr">
         <is>
           <t>240808</t>
         </is>
       </c>
-      <c r="AD1" s="81" t="inlineStr">
+      <c r="AE1" s="81" t="inlineStr">
         <is>
           <t>240807</t>
-        </is>
-      </c>
-      <c r="AE1" s="81" t="inlineStr">
-        <is>
-          <t>240806</t>
         </is>
       </c>
     </row>
@@ -6568,94 +6568,94 @@
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="97" t="inlineStr">
+      <c r="M2" s="96" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="96" t="inlineStr">
+      <c r="O2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="96" t="inlineStr">
+      <c r="P2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="96" t="inlineStr">
+      <c r="Q2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="97" t="inlineStr">
+      <c r="R2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="96" t="inlineStr">
+      <c r="S2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="96" t="inlineStr">
+      <c r="T2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="96" t="inlineStr">
+      <c r="U2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="96" t="inlineStr">
+      <c r="V2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="98" t="inlineStr">
+      <c r="W2" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W2" s="97" t="inlineStr">
+      <c r="X2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X2" s="97" t="inlineStr">
+      <c r="Y2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y2" s="96" t="inlineStr">
+      <c r="Z2" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="97" t="inlineStr">
+      <c r="AA2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA2" s="97" t="inlineStr">
+      <c r="AB2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB2" s="97" t="inlineStr">
+      <c r="AC2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC2" s="97" t="inlineStr">
+      <c r="AD2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD2" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE2" s="96" t="inlineStr">
@@ -6677,88 +6677,88 @@
         <v>-9.81</v>
       </c>
       <c r="D3" s="99" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="E3" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="E3" s="99" t="n">
+      <c r="F3" s="99" t="n">
         <v>-9.82</v>
       </c>
-      <c r="F3" s="99" t="n">
+      <c r="G3" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="G3" s="99" t="n">
+      <c r="H3" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="I3" s="99" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="I3" s="99" t="n">
+      <c r="J3" s="99" t="n">
         <v>-7.94</v>
       </c>
-      <c r="J3" s="99" t="n">
+      <c r="K3" s="99" t="n">
         <v>-8.34</v>
       </c>
-      <c r="K3" s="99" t="n">
+      <c r="L3" s="99" t="n">
         <v>-7.43</v>
       </c>
-      <c r="L3" s="99" t="n">
+      <c r="M3" s="99" t="n">
         <v>-7.87</v>
       </c>
-      <c r="M3" s="99" t="n">
+      <c r="N3" s="99" t="n">
         <v>-6.78</v>
       </c>
-      <c r="N3" s="99" t="n">
+      <c r="O3" s="99" t="n">
         <v>-7.9</v>
       </c>
-      <c r="O3" s="99" t="n">
+      <c r="P3" s="99" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="P3" s="99" t="n">
+      <c r="Q3" s="99" t="n">
         <v>-7.46</v>
       </c>
-      <c r="Q3" s="99" t="n">
+      <c r="R3" s="99" t="n">
         <v>-7.49</v>
       </c>
-      <c r="R3" s="99" t="n">
+      <c r="S3" s="99" t="n">
         <v>-7.68</v>
       </c>
-      <c r="S3" s="99" t="n">
+      <c r="T3" s="99" t="n">
         <v>-8.43</v>
       </c>
-      <c r="T3" s="99" t="n">
+      <c r="U3" s="99" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="U3" s="99" t="n">
+      <c r="V3" s="99" t="n">
         <v>-8.24</v>
       </c>
-      <c r="V3" s="99" t="n">
+      <c r="W3" s="99" t="n">
         <v>-6.32</v>
       </c>
-      <c r="W3" s="99" t="n">
+      <c r="X3" s="99" t="n">
         <v>-7.6</v>
       </c>
-      <c r="X3" s="99" t="n">
+      <c r="Y3" s="99" t="n">
         <v>-8.9</v>
       </c>
-      <c r="Y3" s="99" t="n">
+      <c r="Z3" s="99" t="n">
         <v>-9.73</v>
       </c>
-      <c r="Z3" s="99" t="n">
+      <c r="AA3" s="99" t="n">
         <v>-9.56</v>
       </c>
-      <c r="AA3" s="99" t="n">
+      <c r="AB3" s="99" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="AB3" s="99" t="n">
+      <c r="AC3" s="99" t="n">
         <v>-8.33</v>
       </c>
-      <c r="AC3" s="99" t="n">
+      <c r="AD3" s="99" t="n">
         <v>-8.01</v>
       </c>
-      <c r="AD3" s="99" t="n">
+      <c r="AE3" s="99" t="n">
         <v>-8.77</v>
-      </c>
-      <c r="AE3" s="99" t="n">
-        <v>-8.92</v>
       </c>
     </row>
     <row r="4">
@@ -6774,88 +6774,88 @@
         <v>-12.12</v>
       </c>
       <c r="D4" s="99" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="E4" s="99" t="n">
         <v>-11.77</v>
       </c>
-      <c r="E4" s="99" t="n">
+      <c r="F4" s="99" t="n">
         <v>-11.13</v>
       </c>
-      <c r="F4" s="99" t="n">
+      <c r="G4" s="99" t="n">
         <v>-11.05</v>
       </c>
-      <c r="G4" s="99" t="n">
+      <c r="H4" s="99" t="n">
         <v>-10.42</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="I4" s="99" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="I4" s="99" t="n">
+      <c r="J4" s="99" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="J4" s="99" t="n">
+      <c r="K4" s="99" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="K4" s="99" t="n">
+      <c r="L4" s="99" t="n">
         <v>-8.65</v>
       </c>
-      <c r="L4" s="99" t="n">
+      <c r="M4" s="99" t="n">
         <v>-7.71</v>
       </c>
-      <c r="M4" s="99" t="n">
+      <c r="N4" s="99" t="n">
         <v>-6.12</v>
       </c>
-      <c r="N4" s="99" t="n">
+      <c r="O4" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="O4" s="99" t="n">
+      <c r="P4" s="99" t="n">
         <v>-6.9</v>
       </c>
-      <c r="P4" s="99" t="n">
+      <c r="Q4" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="Q4" s="99" t="n">
+      <c r="R4" s="99" t="n">
         <v>-5.67</v>
       </c>
-      <c r="R4" s="99" t="n">
+      <c r="S4" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="S4" s="99" t="n">
+      <c r="T4" s="99" t="n">
         <v>-3.69</v>
       </c>
-      <c r="T4" s="99" t="n">
+      <c r="U4" s="99" t="n">
         <v>-5.27</v>
       </c>
-      <c r="U4" s="99" t="n">
+      <c r="V4" s="99" t="n">
         <v>-3.71</v>
       </c>
-      <c r="V4" s="99" t="n">
+      <c r="W4" s="99" t="n">
         <v>-3.7</v>
       </c>
-      <c r="W4" s="99" t="n">
+      <c r="X4" s="99" t="n">
         <v>-3.65</v>
       </c>
-      <c r="X4" s="99" t="n">
+      <c r="Y4" s="99" t="n">
         <v>-2.49</v>
       </c>
-      <c r="Y4" s="99" t="n">
+      <c r="Z4" s="99" t="n">
         <v>-2.47</v>
       </c>
-      <c r="Z4" s="99" t="n">
+      <c r="AA4" s="99" t="n">
         <v>-1.46</v>
       </c>
-      <c r="AA4" s="99" t="n">
+      <c r="AB4" s="99" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AB4" s="99" t="n">
+      <c r="AC4" s="99" t="n">
         <v>1.15</v>
       </c>
-      <c r="AC4" s="99" t="n">
+      <c r="AD4" s="99" t="n">
         <v>2.88</v>
       </c>
-      <c r="AD4" s="99" t="n">
+      <c r="AE4" s="99" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AE4" s="99" t="n">
-        <v>5.02</v>
       </c>
     </row>
     <row r="5">
@@ -6871,88 +6871,88 @@
         <v>18.87</v>
       </c>
       <c r="D5" s="99" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="E5" s="99" t="n">
         <v>20.56</v>
       </c>
-      <c r="E5" s="99" t="n">
+      <c r="F5" s="99" t="n">
         <v>21.18</v>
       </c>
-      <c r="F5" s="99" t="n">
+      <c r="G5" s="99" t="n">
         <v>24.39</v>
       </c>
-      <c r="G5" s="99" t="n">
+      <c r="H5" s="99" t="n">
         <v>20.64</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="I5" s="99" t="n">
         <v>24.91</v>
       </c>
-      <c r="I5" s="99" t="n">
+      <c r="J5" s="99" t="n">
         <v>29.13</v>
       </c>
-      <c r="J5" s="99" t="n">
+      <c r="K5" s="99" t="n">
         <v>27.12</v>
       </c>
-      <c r="K5" s="99" t="n">
+      <c r="L5" s="99" t="n">
         <v>30.8</v>
       </c>
-      <c r="L5" s="99" t="n">
+      <c r="M5" s="99" t="n">
         <v>32.53</v>
       </c>
-      <c r="M5" s="99" t="n">
+      <c r="N5" s="99" t="n">
         <v>40.52</v>
       </c>
-      <c r="N5" s="99" t="n">
+      <c r="O5" s="99" t="n">
         <v>31.09</v>
       </c>
-      <c r="O5" s="99" t="n">
+      <c r="P5" s="99" t="n">
         <v>34.85</v>
       </c>
-      <c r="P5" s="99" t="n">
+      <c r="Q5" s="99" t="n">
         <v>38.18</v>
       </c>
-      <c r="Q5" s="99" t="n">
+      <c r="R5" s="99" t="n">
         <v>40.27</v>
       </c>
-      <c r="R5" s="99" t="n">
+      <c r="S5" s="99" t="n">
         <v>39.76</v>
       </c>
-      <c r="S5" s="99" t="n">
+      <c r="T5" s="99" t="n">
         <v>37.4</v>
       </c>
-      <c r="T5" s="99" t="n">
+      <c r="U5" s="99" t="n">
         <v>39.36</v>
       </c>
-      <c r="U5" s="99" t="n">
+      <c r="V5" s="99" t="n">
         <v>41.93</v>
       </c>
-      <c r="V5" s="99" t="n">
+      <c r="W5" s="99" t="n">
         <v>49.88</v>
       </c>
-      <c r="W5" s="99" t="n">
+      <c r="X5" s="99" t="n">
         <v>44.87</v>
       </c>
-      <c r="X5" s="99" t="n">
+      <c r="Y5" s="99" t="n">
         <v>44.14</v>
       </c>
-      <c r="Y5" s="99" t="n">
+      <c r="Z5" s="99" t="n">
         <v>33.73</v>
       </c>
-      <c r="Z5" s="99" t="n">
+      <c r="AA5" s="99" t="n">
         <v>37.89</v>
       </c>
-      <c r="AA5" s="99" t="n">
+      <c r="AB5" s="99" t="n">
         <v>33.7</v>
       </c>
-      <c r="AB5" s="99" t="n">
+      <c r="AC5" s="99" t="n">
         <v>34.57</v>
       </c>
-      <c r="AC5" s="99" t="n">
+      <c r="AD5" s="99" t="n">
         <v>36.2</v>
       </c>
-      <c r="AD5" s="99" t="n">
+      <c r="AE5" s="99" t="n">
         <v>36.18</v>
-      </c>
-      <c r="AE5" s="99" t="n">
-        <v>35.34</v>
       </c>
     </row>
     <row r="6">
@@ -6968,88 +6968,88 @@
         <v>4.21</v>
       </c>
       <c r="D6" s="99" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E6" s="99" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="E6" s="99" t="n">
+      <c r="F6" s="99" t="n">
         <v>11.08</v>
       </c>
-      <c r="F6" s="99" t="n">
+      <c r="G6" s="99" t="n">
         <v>27.27</v>
       </c>
-      <c r="G6" s="99" t="n">
+      <c r="H6" s="99" t="n">
         <v>2.86</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="I6" s="99" t="n">
         <v>7.92</v>
       </c>
-      <c r="I6" s="99" t="n">
+      <c r="J6" s="99" t="n">
         <v>24.73</v>
       </c>
-      <c r="J6" s="99" t="n">
+      <c r="K6" s="99" t="n">
         <v>7.06</v>
       </c>
-      <c r="K6" s="99" t="n">
+      <c r="L6" s="99" t="n">
         <v>15.5</v>
       </c>
-      <c r="L6" s="99" t="n">
+      <c r="M6" s="99" t="n">
         <v>20.88</v>
       </c>
-      <c r="M6" s="99" t="n">
+      <c r="N6" s="99" t="n">
         <v>63.5</v>
       </c>
-      <c r="N6" s="99" t="n">
+      <c r="O6" s="99" t="n">
         <v>2.54</v>
       </c>
-      <c r="O6" s="99" t="n">
+      <c r="P6" s="99" t="n">
         <v>6.81</v>
       </c>
-      <c r="P6" s="99" t="n">
+      <c r="Q6" s="99" t="n">
         <v>20.06</v>
       </c>
-      <c r="Q6" s="99" t="n">
+      <c r="R6" s="99" t="n">
         <v>48.33</v>
       </c>
-      <c r="R6" s="99" t="n">
+      <c r="S6" s="99" t="n">
         <v>41.33</v>
       </c>
-      <c r="S6" s="99" t="n">
+      <c r="T6" s="99" t="n">
         <v>12.42</v>
       </c>
-      <c r="T6" s="99" t="n">
+      <c r="U6" s="99" t="n">
         <v>18.92</v>
       </c>
-      <c r="U6" s="99" t="n">
+      <c r="V6" s="99" t="n">
         <v>28.57</v>
       </c>
-      <c r="V6" s="99" t="n">
+      <c r="W6" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="W6" s="99" t="n">
+      <c r="X6" s="99" t="n">
         <v>77.2</v>
       </c>
-      <c r="X6" s="99" t="n">
+      <c r="Y6" s="99" t="n">
         <v>74.79000000000001</v>
       </c>
-      <c r="Y6" s="99" t="n">
+      <c r="Z6" s="99" t="n">
         <v>20.6</v>
       </c>
-      <c r="Z6" s="99" t="n">
+      <c r="AA6" s="99" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="AA6" s="99" t="n">
+      <c r="AB6" s="99" t="n">
         <v>9.16</v>
       </c>
-      <c r="AB6" s="99" t="n">
+      <c r="AC6" s="99" t="n">
         <v>14.59</v>
       </c>
-      <c r="AC6" s="99" t="n">
+      <c r="AD6" s="99" t="n">
         <v>34.08</v>
       </c>
-      <c r="AD6" s="99" t="n">
+      <c r="AE6" s="99" t="n">
         <v>33.68</v>
-      </c>
-      <c r="AE6" s="99" t="n">
-        <v>25.38</v>
       </c>
     </row>
     <row r="7">
@@ -7083,114 +7083,114 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G7" s="96" t="inlineStr">
+      <c r="G7" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H7" s="96" t="inlineStr">
+      <c r="I7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I7" s="97" t="inlineStr">
+      <c r="J7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J7" s="97" t="inlineStr">
+      <c r="K7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K7" s="97" t="inlineStr">
+      <c r="L7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L7" s="96" t="inlineStr">
+      <c r="M7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M7" s="98" t="inlineStr">
+      <c r="N7" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N7" s="97" t="inlineStr">
+      <c r="O7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="96" t="inlineStr">
+      <c r="P7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P7" s="96" t="inlineStr">
+      <c r="Q7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q7" s="96" t="inlineStr">
+      <c r="R7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R7" s="96" t="inlineStr">
+      <c r="S7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S7" s="96" t="inlineStr">
+      <c r="T7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T7" s="96" t="inlineStr">
+      <c r="U7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U7" s="96" t="inlineStr">
+      <c r="V7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V7" s="97" t="inlineStr">
+      <c r="W7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W7" s="97" t="inlineStr">
+      <c r="X7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X7" s="97" t="inlineStr">
+      <c r="Y7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y7" s="96" t="inlineStr">
+      <c r="Z7" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z7" s="97" t="inlineStr">
+      <c r="AA7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA7" s="97" t="inlineStr">
+      <c r="AB7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB7" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC7" s="96" t="inlineStr">
@@ -7222,88 +7222,88 @@
         <v>-13.62</v>
       </c>
       <c r="D8" s="99" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="E8" s="99" t="n">
         <v>-12.75</v>
       </c>
-      <c r="E8" s="99" t="n">
+      <c r="F8" s="99" t="n">
         <v>-11.62</v>
       </c>
-      <c r="F8" s="99" t="n">
+      <c r="G8" s="99" t="n">
         <v>-12.8</v>
       </c>
-      <c r="G8" s="99" t="n">
+      <c r="H8" s="99" t="n">
         <v>-13.49</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="I8" s="99" t="n">
         <v>-12.19</v>
       </c>
-      <c r="I8" s="99" t="n">
+      <c r="J8" s="99" t="n">
         <v>-11.56</v>
       </c>
-      <c r="J8" s="99" t="n">
+      <c r="K8" s="99" t="n">
         <v>-10.95</v>
       </c>
-      <c r="K8" s="99" t="n">
+      <c r="L8" s="99" t="n">
         <v>-10.7</v>
       </c>
-      <c r="L8" s="99" t="n">
+      <c r="M8" s="99" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="M8" s="99" t="n">
+      <c r="N8" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="N8" s="99" t="n">
+      <c r="O8" s="99" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="O8" s="99" t="n">
+      <c r="P8" s="99" t="n">
         <v>-10.94</v>
       </c>
-      <c r="P8" s="99" t="n">
+      <c r="Q8" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="Q8" s="99" t="n">
+      <c r="R8" s="99" t="n">
         <v>-8.17</v>
       </c>
-      <c r="R8" s="99" t="n">
+      <c r="S8" s="99" t="n">
         <v>-7.67</v>
       </c>
-      <c r="S8" s="99" t="n">
+      <c r="T8" s="99" t="n">
         <v>-6.65</v>
       </c>
-      <c r="T8" s="99" t="n">
+      <c r="U8" s="99" t="n">
         <v>-5.88</v>
       </c>
-      <c r="U8" s="99" t="n">
+      <c r="V8" s="99" t="n">
         <v>-6.11</v>
       </c>
-      <c r="V8" s="99" t="n">
+      <c r="W8" s="99" t="n">
         <v>-3.29</v>
       </c>
-      <c r="W8" s="99" t="n">
+      <c r="X8" s="99" t="n">
         <v>-5.01</v>
       </c>
-      <c r="X8" s="99" t="n">
+      <c r="Y8" s="99" t="n">
         <v>-6.28</v>
       </c>
-      <c r="Y8" s="99" t="n">
+      <c r="Z8" s="99" t="n">
         <v>-6.32</v>
       </c>
-      <c r="Z8" s="99" t="n">
+      <c r="AA8" s="99" t="n">
         <v>-5.68</v>
       </c>
-      <c r="AA8" s="99" t="n">
+      <c r="AB8" s="99" t="n">
         <v>-6.24</v>
       </c>
-      <c r="AB8" s="99" t="n">
+      <c r="AC8" s="99" t="n">
         <v>-5.48</v>
       </c>
-      <c r="AC8" s="99" t="n">
+      <c r="AD8" s="99" t="n">
         <v>-5.41</v>
       </c>
-      <c r="AD8" s="99" t="n">
+      <c r="AE8" s="99" t="n">
         <v>-6.93</v>
-      </c>
-      <c r="AE8" s="99" t="n">
-        <v>-6.52</v>
       </c>
     </row>
     <row r="9">
@@ -7319,88 +7319,88 @@
         <v>-18.74</v>
       </c>
       <c r="D9" s="99" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="E9" s="99" t="n">
         <v>-19.06</v>
       </c>
-      <c r="E9" s="99" t="n">
+      <c r="F9" s="99" t="n">
         <v>-18.16</v>
       </c>
-      <c r="F9" s="99" t="n">
+      <c r="G9" s="99" t="n">
         <v>-20.04</v>
       </c>
-      <c r="G9" s="99" t="n">
+      <c r="H9" s="99" t="n">
         <v>-19.01</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="I9" s="99" t="n">
         <v>-17.71</v>
       </c>
-      <c r="I9" s="99" t="n">
+      <c r="J9" s="99" t="n">
         <v>-17.63</v>
       </c>
-      <c r="J9" s="99" t="n">
+      <c r="K9" s="99" t="n">
         <v>-17.79</v>
       </c>
-      <c r="K9" s="99" t="n">
+      <c r="L9" s="99" t="n">
         <v>-17.53</v>
       </c>
-      <c r="L9" s="99" t="n">
+      <c r="M9" s="99" t="n">
         <v>-16.58</v>
       </c>
-      <c r="M9" s="99" t="n">
+      <c r="N9" s="99" t="n">
         <v>-12.6</v>
       </c>
-      <c r="N9" s="99" t="n">
+      <c r="O9" s="99" t="n">
         <v>-16.3</v>
       </c>
-      <c r="O9" s="99" t="n">
+      <c r="P9" s="99" t="n">
         <v>-17.92</v>
       </c>
-      <c r="P9" s="99" t="n">
+      <c r="Q9" s="99" t="n">
         <v>-17.61</v>
       </c>
-      <c r="Q9" s="99" t="n">
+      <c r="R9" s="99" t="n">
         <v>-16.31</v>
       </c>
-      <c r="R9" s="99" t="n">
+      <c r="S9" s="99" t="n">
         <v>-15.1</v>
       </c>
-      <c r="S9" s="99" t="n">
+      <c r="T9" s="99" t="n">
         <v>-11.15</v>
       </c>
-      <c r="T9" s="99" t="n">
+      <c r="U9" s="99" t="n">
         <v>-13.21</v>
       </c>
-      <c r="U9" s="99" t="n">
+      <c r="V9" s="99" t="n">
         <v>-9.76</v>
       </c>
-      <c r="V9" s="99" t="n">
+      <c r="W9" s="99" t="n">
         <v>-8</v>
       </c>
-      <c r="W9" s="99" t="n">
+      <c r="X9" s="99" t="n">
         <v>-7.5</v>
       </c>
-      <c r="X9" s="99" t="n">
+      <c r="Y9" s="99" t="n">
         <v>-6.3</v>
       </c>
-      <c r="Y9" s="99" t="n">
+      <c r="Z9" s="99" t="n">
         <v>-7.12</v>
       </c>
-      <c r="Z9" s="99" t="n">
+      <c r="AA9" s="99" t="n">
         <v>-6.89</v>
       </c>
-      <c r="AA9" s="99" t="n">
+      <c r="AB9" s="99" t="n">
         <v>-5.88</v>
       </c>
-      <c r="AB9" s="99" t="n">
+      <c r="AC9" s="99" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AC9" s="99" t="n">
+      <c r="AD9" s="99" t="n">
         <v>-1.65</v>
       </c>
-      <c r="AD9" s="99" t="n">
+      <c r="AE9" s="99" t="n">
         <v>4.55</v>
-      </c>
-      <c r="AE9" s="99" t="n">
-        <v>6.01</v>
       </c>
     </row>
     <row r="10">
@@ -7416,88 +7416,88 @@
         <v>33.41</v>
       </c>
       <c r="D10" s="99" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="E10" s="99" t="n">
         <v>35.55</v>
       </c>
-      <c r="E10" s="99" t="n">
+      <c r="F10" s="99" t="n">
         <v>38.79</v>
       </c>
-      <c r="F10" s="99" t="n">
+      <c r="G10" s="99" t="n">
         <v>34.56</v>
       </c>
-      <c r="G10" s="99" t="n">
+      <c r="H10" s="99" t="n">
         <v>29.42</v>
       </c>
-      <c r="H10" s="99" t="n">
+      <c r="I10" s="99" t="n">
         <v>32.81</v>
       </c>
-      <c r="I10" s="99" t="n">
+      <c r="J10" s="99" t="n">
         <v>37.49</v>
       </c>
-      <c r="J10" s="99" t="n">
+      <c r="K10" s="99" t="n">
         <v>38.05</v>
       </c>
-      <c r="K10" s="99" t="n">
+      <c r="L10" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="L10" s="99" t="n">
+      <c r="M10" s="99" t="n">
         <v>35.52</v>
       </c>
-      <c r="M10" s="99" t="n">
+      <c r="N10" s="99" t="n">
         <v>49.6</v>
       </c>
-      <c r="N10" s="99" t="n">
+      <c r="O10" s="99" t="n">
         <v>35.78</v>
       </c>
-      <c r="O10" s="99" t="n">
+      <c r="P10" s="99" t="n">
         <v>25.18</v>
       </c>
-      <c r="P10" s="99" t="n">
+      <c r="Q10" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="Q10" s="99" t="n">
+      <c r="R10" s="99" t="n">
         <v>30.93</v>
       </c>
-      <c r="R10" s="99" t="n">
+      <c r="S10" s="99" t="n">
         <v>32.82</v>
       </c>
-      <c r="S10" s="99" t="n">
+      <c r="T10" s="99" t="n">
         <v>32.56</v>
       </c>
-      <c r="T10" s="99" t="n">
+      <c r="U10" s="99" t="n">
         <v>35.9</v>
       </c>
-      <c r="U10" s="99" t="n">
+      <c r="V10" s="99" t="n">
         <v>36.95</v>
       </c>
-      <c r="V10" s="99" t="n">
+      <c r="W10" s="99" t="n">
         <v>42.83</v>
       </c>
-      <c r="W10" s="99" t="n">
+      <c r="X10" s="99" t="n">
         <v>44.05</v>
       </c>
-      <c r="X10" s="99" t="n">
+      <c r="Y10" s="99" t="n">
         <v>45.48</v>
       </c>
-      <c r="Y10" s="99" t="n">
+      <c r="Z10" s="99" t="n">
         <v>40.54</v>
       </c>
-      <c r="Z10" s="99" t="n">
+      <c r="AA10" s="99" t="n">
         <v>46.12</v>
       </c>
-      <c r="AA10" s="99" t="n">
+      <c r="AB10" s="99" t="n">
         <v>43.69</v>
       </c>
-      <c r="AB10" s="99" t="n">
+      <c r="AC10" s="99" t="n">
         <v>42.47</v>
       </c>
-      <c r="AC10" s="99" t="n">
+      <c r="AD10" s="99" t="n">
         <v>44.1</v>
       </c>
-      <c r="AD10" s="99" t="n">
+      <c r="AE10" s="99" t="n">
         <v>43.33</v>
-      </c>
-      <c r="AE10" s="99" t="n">
-        <v>46.02</v>
       </c>
     </row>
     <row r="11">
@@ -7513,88 +7513,88 @@
         <v>30.54</v>
       </c>
       <c r="D11" s="99" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="E11" s="99" t="n">
         <v>35.28</v>
       </c>
-      <c r="E11" s="99" t="n">
+      <c r="F11" s="99" t="n">
         <v>42.99</v>
       </c>
-      <c r="F11" s="99" t="n">
+      <c r="G11" s="99" t="n">
         <v>33.88</v>
       </c>
-      <c r="G11" s="99" t="n">
+      <c r="H11" s="99" t="n">
         <v>22.22</v>
       </c>
-      <c r="H11" s="99" t="n">
+      <c r="I11" s="99" t="n">
         <v>27.98</v>
       </c>
-      <c r="I11" s="99" t="n">
+      <c r="J11" s="99" t="n">
         <v>37.32</v>
       </c>
-      <c r="J11" s="99" t="n">
+      <c r="K11" s="99" t="n">
         <v>38.49</v>
       </c>
-      <c r="K11" s="99" t="n">
+      <c r="L11" s="99" t="n">
         <v>41.22</v>
       </c>
-      <c r="L11" s="99" t="n">
+      <c r="M11" s="99" t="n">
         <v>34.35</v>
       </c>
-      <c r="M11" s="99" t="n">
+      <c r="N11" s="99" t="n">
         <v>63.18</v>
       </c>
-      <c r="N11" s="99" t="n">
+      <c r="O11" s="99" t="n">
         <v>38.1</v>
       </c>
-      <c r="O11" s="99" t="n">
+      <c r="P11" s="99" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="P11" s="99" t="n">
+      <c r="Q11" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="Q11" s="99" t="n">
+      <c r="R11" s="99" t="n">
         <v>17.04</v>
       </c>
-      <c r="R11" s="99" t="n">
+      <c r="S11" s="99" t="n">
         <v>20.21</v>
       </c>
-      <c r="S11" s="99" t="n">
+      <c r="T11" s="99" t="n">
         <v>19.37</v>
       </c>
-      <c r="T11" s="99" t="n">
+      <c r="U11" s="99" t="n">
         <v>25.01</v>
       </c>
-      <c r="U11" s="99" t="n">
+      <c r="V11" s="99" t="n">
         <v>26.94</v>
       </c>
-      <c r="V11" s="99" t="n">
+      <c r="W11" s="99" t="n">
         <v>39.73</v>
       </c>
-      <c r="W11" s="99" t="n">
+      <c r="X11" s="99" t="n">
         <v>42.89</v>
       </c>
-      <c r="X11" s="99" t="n">
+      <c r="Y11" s="99" t="n">
         <v>46.52</v>
       </c>
-      <c r="Y11" s="99" t="n">
+      <c r="Z11" s="99" t="n">
         <v>33.79</v>
       </c>
-      <c r="Z11" s="99" t="n">
+      <c r="AA11" s="99" t="n">
         <v>47.1</v>
       </c>
-      <c r="AA11" s="99" t="n">
+      <c r="AB11" s="99" t="n">
         <v>40.57</v>
       </c>
-      <c r="AB11" s="99" t="n">
+      <c r="AC11" s="99" t="n">
         <v>37.36</v>
       </c>
-      <c r="AC11" s="99" t="n">
+      <c r="AD11" s="99" t="n">
         <v>40.69</v>
       </c>
-      <c r="AD11" s="99" t="n">
+      <c r="AE11" s="99" t="n">
         <v>38.97</v>
-      </c>
-      <c r="AE11" s="99" t="n">
-        <v>43.76</v>
       </c>
     </row>
     <row r="12">
@@ -7613,124 +7613,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D12" s="97" t="inlineStr">
+      <c r="D12" s="96" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E12" s="98" t="inlineStr">
+      <c r="F12" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F12" s="96" t="inlineStr">
+      <c r="G12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G12" s="96" t="inlineStr">
+      <c r="H12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H12" s="96" t="inlineStr">
+      <c r="I12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I12" s="98" t="inlineStr">
+      <c r="J12" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J12" s="97" t="inlineStr">
+      <c r="K12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K12" s="97" t="inlineStr">
+      <c r="L12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L12" s="96" t="inlineStr">
+      <c r="M12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="98" t="inlineStr">
+      <c r="N12" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N12" s="97" t="inlineStr">
+      <c r="O12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O12" s="97" t="inlineStr">
+      <c r="P12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P12" s="96" t="inlineStr">
+      <c r="Q12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q12" s="97" t="inlineStr">
+      <c r="R12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R12" s="96" t="inlineStr">
+      <c r="S12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S12" s="96" t="inlineStr">
+      <c r="T12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T12" s="96" t="inlineStr">
+      <c r="U12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U12" s="96" t="inlineStr">
+      <c r="V12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V12" s="97" t="inlineStr">
+      <c r="W12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W12" s="97" t="inlineStr">
+      <c r="X12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X12" s="97" t="inlineStr">
+      <c r="Y12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y12" s="96" t="inlineStr">
+      <c r="Z12" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z12" s="97" t="inlineStr">
+      <c r="AA12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AA12" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AB12" s="96" t="inlineStr">
@@ -7767,88 +7767,88 @@
         <v>-12.57</v>
       </c>
       <c r="D13" s="99" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="E13" s="99" t="n">
         <v>-11.96</v>
       </c>
-      <c r="E13" s="99" t="n">
+      <c r="F13" s="99" t="n">
         <v>-12.87</v>
       </c>
-      <c r="F13" s="99" t="n">
+      <c r="G13" s="99" t="n">
         <v>-14.98</v>
       </c>
-      <c r="G13" s="99" t="n">
+      <c r="H13" s="99" t="n">
         <v>-14.79</v>
       </c>
-      <c r="H13" s="99" t="n">
+      <c r="I13" s="99" t="n">
         <v>-14.14</v>
       </c>
-      <c r="I13" s="99" t="n">
+      <c r="J13" s="99" t="n">
         <v>-11.99</v>
       </c>
-      <c r="J13" s="99" t="n">
+      <c r="K13" s="99" t="n">
         <v>-12.63</v>
       </c>
-      <c r="K13" s="99" t="n">
+      <c r="L13" s="99" t="n">
         <v>-12.92</v>
       </c>
-      <c r="L13" s="99" t="n">
+      <c r="M13" s="99" t="n">
         <v>-13.71</v>
       </c>
-      <c r="M13" s="99" t="n">
+      <c r="N13" s="99" t="n">
         <v>-13.18</v>
       </c>
-      <c r="N13" s="99" t="n">
+      <c r="O13" s="99" t="n">
         <v>-15.93</v>
       </c>
-      <c r="O13" s="99" t="n">
+      <c r="P13" s="99" t="n">
         <v>-16.93</v>
       </c>
-      <c r="P13" s="99" t="n">
+      <c r="Q13" s="99" t="n">
         <v>-15.87</v>
       </c>
-      <c r="Q13" s="99" t="n">
+      <c r="R13" s="99" t="n">
         <v>-14.39</v>
       </c>
-      <c r="R13" s="99" t="n">
+      <c r="S13" s="99" t="n">
         <v>-14.68</v>
       </c>
-      <c r="S13" s="99" t="n">
+      <c r="T13" s="99" t="n">
         <v>-14.6</v>
       </c>
-      <c r="T13" s="99" t="n">
+      <c r="U13" s="99" t="n">
         <v>-13.72</v>
       </c>
-      <c r="U13" s="99" t="n">
+      <c r="V13" s="99" t="n">
         <v>-14.36</v>
       </c>
-      <c r="V13" s="99" t="n">
+      <c r="W13" s="99" t="n">
         <v>-12.61</v>
       </c>
-      <c r="W13" s="99" t="n">
+      <c r="X13" s="99" t="n">
         <v>-14.07</v>
       </c>
-      <c r="X13" s="99" t="n">
+      <c r="Y13" s="99" t="n">
         <v>-15.19</v>
       </c>
-      <c r="Y13" s="99" t="n">
+      <c r="Z13" s="99" t="n">
         <v>-14.89</v>
       </c>
-      <c r="Z13" s="99" t="n">
+      <c r="AA13" s="99" t="n">
         <v>-14.33</v>
       </c>
-      <c r="AA13" s="99" t="n">
+      <c r="AB13" s="99" t="n">
         <v>-14.61</v>
       </c>
-      <c r="AB13" s="99" t="n">
+      <c r="AC13" s="99" t="n">
         <v>-13.48</v>
       </c>
-      <c r="AC13" s="99" t="n">
+      <c r="AD13" s="99" t="n">
         <v>-12.37</v>
       </c>
-      <c r="AD13" s="99" t="n">
+      <c r="AE13" s="99" t="n">
         <v>-12.68</v>
-      </c>
-      <c r="AE13" s="99" t="n">
-        <v>-12.52</v>
       </c>
     </row>
     <row r="14">
@@ -7864,88 +7864,88 @@
         <v>-19.08</v>
       </c>
       <c r="D14" s="99" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="E14" s="99" t="n">
         <v>-18.72</v>
       </c>
-      <c r="E14" s="99" t="n">
+      <c r="F14" s="99" t="n">
         <v>-18.28</v>
       </c>
-      <c r="F14" s="99" t="n">
+      <c r="G14" s="99" t="n">
         <v>-20.06</v>
       </c>
-      <c r="G14" s="99" t="n">
+      <c r="H14" s="99" t="n">
         <v>-18.31</v>
       </c>
-      <c r="H14" s="99" t="n">
+      <c r="I14" s="99" t="n">
         <v>-18.32</v>
       </c>
-      <c r="I14" s="99" t="n">
+      <c r="J14" s="99" t="n">
         <v>-17.44</v>
       </c>
-      <c r="J14" s="99" t="n">
+      <c r="K14" s="99" t="n">
         <v>-18.44</v>
       </c>
-      <c r="K14" s="99" t="n">
+      <c r="L14" s="99" t="n">
         <v>-17.67</v>
       </c>
-      <c r="L14" s="99" t="n">
+      <c r="M14" s="99" t="n">
         <v>-14.96</v>
       </c>
-      <c r="M14" s="99" t="n">
+      <c r="N14" s="99" t="n">
         <v>-11.7</v>
       </c>
-      <c r="N14" s="99" t="n">
+      <c r="O14" s="99" t="n">
         <v>-15.89</v>
       </c>
-      <c r="O14" s="99" t="n">
+      <c r="P14" s="99" t="n">
         <v>-16.48</v>
       </c>
-      <c r="P14" s="99" t="n">
+      <c r="Q14" s="99" t="n">
         <v>-16.57</v>
       </c>
-      <c r="Q14" s="99" t="n">
+      <c r="R14" s="99" t="n">
         <v>-15.28</v>
       </c>
-      <c r="R14" s="99" t="n">
+      <c r="S14" s="99" t="n">
         <v>-14.4</v>
       </c>
-      <c r="S14" s="99" t="n">
+      <c r="T14" s="99" t="n">
         <v>-11.57</v>
       </c>
-      <c r="T14" s="99" t="n">
+      <c r="U14" s="99" t="n">
         <v>-13.13</v>
       </c>
-      <c r="U14" s="99" t="n">
+      <c r="V14" s="99" t="n">
         <v>-10.49</v>
       </c>
-      <c r="V14" s="99" t="n">
+      <c r="W14" s="99" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="W14" s="99" t="n">
+      <c r="X14" s="99" t="n">
         <v>-9.470000000000001</v>
       </c>
-      <c r="X14" s="99" t="n">
+      <c r="Y14" s="99" t="n">
         <v>-9.119999999999999</v>
       </c>
-      <c r="Y14" s="99" t="n">
+      <c r="Z14" s="99" t="n">
         <v>-9.27</v>
       </c>
-      <c r="Z14" s="99" t="n">
+      <c r="AA14" s="99" t="n">
         <v>-7.97</v>
       </c>
-      <c r="AA14" s="99" t="n">
+      <c r="AB14" s="99" t="n">
         <v>-7.79</v>
       </c>
-      <c r="AB14" s="99" t="n">
+      <c r="AC14" s="99" t="n">
         <v>-6.52</v>
       </c>
-      <c r="AC14" s="99" t="n">
+      <c r="AD14" s="99" t="n">
         <v>-3.35</v>
       </c>
-      <c r="AD14" s="99" t="n">
+      <c r="AE14" s="99" t="n">
         <v>3.69</v>
-      </c>
-      <c r="AE14" s="99" t="n">
-        <v>4.97</v>
       </c>
     </row>
     <row r="15">
@@ -7961,88 +7961,88 @@
         <v>40.59</v>
       </c>
       <c r="D15" s="99" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="E15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="E15" s="99" t="n">
+      <c r="F15" s="99" t="n">
         <v>48.89</v>
       </c>
-      <c r="F15" s="99" t="n">
+      <c r="G15" s="99" t="n">
         <v>40.91</v>
       </c>
-      <c r="G15" s="99" t="n">
+      <c r="H15" s="99" t="n">
         <v>40.48</v>
       </c>
-      <c r="H15" s="99" t="n">
+      <c r="I15" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="I15" s="99" t="n">
+      <c r="J15" s="99" t="n">
         <v>48.15</v>
       </c>
-      <c r="J15" s="99" t="n">
+      <c r="K15" s="99" t="n">
         <v>44.33</v>
       </c>
-      <c r="K15" s="99" t="n">
+      <c r="L15" s="99" t="n">
         <v>44.83</v>
       </c>
-      <c r="L15" s="99" t="n">
+      <c r="M15" s="99" t="n">
         <v>37.59</v>
       </c>
-      <c r="M15" s="99" t="n">
+      <c r="N15" s="99" t="n">
         <v>51.16</v>
       </c>
-      <c r="N15" s="99" t="n">
+      <c r="O15" s="99" t="n">
         <v>31.05</v>
       </c>
-      <c r="O15" s="99" t="n">
+      <c r="P15" s="99" t="n">
         <v>23.87</v>
       </c>
-      <c r="P15" s="99" t="n">
+      <c r="Q15" s="99" t="n">
         <v>23.35</v>
       </c>
-      <c r="Q15" s="99" t="n">
+      <c r="R15" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="R15" s="99" t="n">
+      <c r="S15" s="99" t="n">
         <v>27.05</v>
       </c>
-      <c r="S15" s="99" t="n">
+      <c r="T15" s="99" t="n">
         <v>26.89</v>
       </c>
-      <c r="T15" s="99" t="n">
+      <c r="U15" s="99" t="n">
         <v>29.42</v>
       </c>
-      <c r="U15" s="99" t="n">
+      <c r="V15" s="99" t="n">
         <v>31.54</v>
       </c>
-      <c r="V15" s="99" t="n">
+      <c r="W15" s="99" t="n">
         <v>36.95</v>
       </c>
-      <c r="W15" s="99" t="n">
+      <c r="X15" s="99" t="n">
         <v>37.54</v>
       </c>
-      <c r="X15" s="99" t="n">
+      <c r="Y15" s="99" t="n">
         <v>37.85</v>
       </c>
-      <c r="Y15" s="99" t="n">
+      <c r="Z15" s="99" t="n">
         <v>34.56</v>
       </c>
-      <c r="Z15" s="99" t="n">
+      <c r="AA15" s="99" t="n">
         <v>39.73</v>
       </c>
-      <c r="AA15" s="99" t="n">
+      <c r="AB15" s="99" t="n">
         <v>33.97</v>
       </c>
-      <c r="AB15" s="99" t="n">
+      <c r="AC15" s="99" t="n">
         <v>34.63</v>
       </c>
-      <c r="AC15" s="99" t="n">
+      <c r="AD15" s="99" t="n">
         <v>37.83</v>
       </c>
-      <c r="AD15" s="99" t="n">
+      <c r="AE15" s="99" t="n">
         <v>39.66</v>
-      </c>
-      <c r="AE15" s="99" t="n">
-        <v>41.08</v>
       </c>
     </row>
     <row r="16">
@@ -8058,88 +8058,88 @@
         <v>40.57</v>
       </c>
       <c r="D16" s="99" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="E16" s="99" t="n">
         <v>47.22</v>
       </c>
-      <c r="E16" s="99" t="n">
+      <c r="F16" s="99" t="n">
         <v>50.08</v>
       </c>
-      <c r="F16" s="99" t="n">
+      <c r="G16" s="99" t="n">
         <v>41.17</v>
       </c>
-      <c r="G16" s="99" t="n">
+      <c r="H16" s="99" t="n">
         <v>40.69</v>
       </c>
-      <c r="H16" s="99" t="n">
+      <c r="I16" s="99" t="n">
         <v>40.24</v>
       </c>
-      <c r="I16" s="99" t="n">
+      <c r="J16" s="99" t="n">
         <v>49.36</v>
       </c>
-      <c r="J16" s="99" t="n">
+      <c r="K16" s="99" t="n">
         <v>45.18</v>
       </c>
-      <c r="K16" s="99" t="n">
+      <c r="L16" s="99" t="n">
         <v>45.74</v>
       </c>
-      <c r="L16" s="99" t="n">
+      <c r="M16" s="99" t="n">
         <v>37.86</v>
       </c>
-      <c r="M16" s="99" t="n">
+      <c r="N16" s="99" t="n">
         <v>53.33</v>
       </c>
-      <c r="N16" s="99" t="n">
+      <c r="O16" s="99" t="n">
         <v>30.77</v>
       </c>
-      <c r="O16" s="99" t="n">
+      <c r="P16" s="99" t="n">
         <v>22.26</v>
       </c>
-      <c r="P16" s="99" t="n">
+      <c r="Q16" s="99" t="n">
         <v>21.65</v>
       </c>
-      <c r="Q16" s="99" t="n">
+      <c r="R16" s="99" t="n">
         <v>25.27</v>
       </c>
-      <c r="R16" s="99" t="n">
+      <c r="S16" s="99" t="n">
         <v>25.69</v>
       </c>
-      <c r="S16" s="99" t="n">
+      <c r="T16" s="99" t="n">
         <v>25.5</v>
       </c>
-      <c r="T16" s="99" t="n">
+      <c r="U16" s="99" t="n">
         <v>28.26</v>
       </c>
-      <c r="U16" s="99" t="n">
+      <c r="V16" s="99" t="n">
         <v>30.6</v>
       </c>
-      <c r="V16" s="99" t="n">
+      <c r="W16" s="99" t="n">
         <v>36.7</v>
       </c>
-      <c r="W16" s="99" t="n">
+      <c r="X16" s="99" t="n">
         <v>37.37</v>
       </c>
-      <c r="X16" s="99" t="n">
+      <c r="Y16" s="99" t="n">
         <v>37.73</v>
       </c>
-      <c r="Y16" s="99" t="n">
+      <c r="Z16" s="99" t="n">
         <v>34</v>
       </c>
-      <c r="Z16" s="99" t="n">
+      <c r="AA16" s="99" t="n">
         <v>39.78</v>
       </c>
-      <c r="AA16" s="99" t="n">
+      <c r="AB16" s="99" t="n">
         <v>33.25</v>
       </c>
-      <c r="AB16" s="99" t="n">
+      <c r="AC16" s="99" t="n">
         <v>33.97</v>
       </c>
-      <c r="AC16" s="99" t="n">
+      <c r="AD16" s="99" t="n">
         <v>37.48</v>
       </c>
-      <c r="AD16" s="99" t="n">
+      <c r="AE16" s="99" t="n">
         <v>39.5</v>
-      </c>
-      <c r="AE16" s="99" t="n">
-        <v>41.07</v>
       </c>
     </row>
     <row r="17">
@@ -8153,149 +8153,149 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D17" s="97" t="inlineStr">
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E17" s="96" t="inlineStr">
+      <c r="F17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F17" s="96" t="inlineStr">
+      <c r="G17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G17" s="96" t="inlineStr">
+      <c r="H17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H17" s="96" t="inlineStr">
+      <c r="I17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I17" s="96" t="inlineStr">
+      <c r="J17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J17" s="96" t="inlineStr">
+      <c r="K17" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K17" s="97" t="inlineStr">
+      <c r="L17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L17" s="97" t="inlineStr">
+      <c r="M17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M17" s="98" t="inlineStr">
+      <c r="N17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N17" s="97" t="inlineStr">
+      <c r="O17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="97" t="inlineStr">
+      <c r="P17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="98" t="inlineStr">
+      <c r="Q17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q17" s="98" t="inlineStr">
+      <c r="R17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R17" s="97" t="inlineStr">
+      <c r="S17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S17" s="98" t="inlineStr">
+      <c r="T17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T17" s="97" t="inlineStr">
+      <c r="U17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U17" s="98" t="inlineStr">
+      <c r="V17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V17" s="98" t="inlineStr">
+      <c r="W17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W17" s="98" t="inlineStr">
+      <c r="X17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X17" s="98" t="inlineStr">
+      <c r="Y17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y17" s="98" t="inlineStr">
+      <c r="Z17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z17" s="98" t="inlineStr">
+      <c r="AA17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA17" s="98" t="inlineStr">
+      <c r="AB17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB17" s="98" t="inlineStr">
+      <c r="AC17" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC17" s="97" t="inlineStr">
+      <c r="AD17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD17" s="97" t="inlineStr">
+      <c r="AE17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE17" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -8306,94 +8306,94 @@
         </is>
       </c>
       <c r="B18" s="99" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="C18" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="C18" s="99" t="n">
+      <c r="D18" s="99" t="n">
         <v>-5.76</v>
       </c>
-      <c r="D18" s="99" t="n">
+      <c r="E18" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="E18" s="99" t="n">
+      <c r="F18" s="99" t="n">
         <v>-4.61</v>
       </c>
-      <c r="F18" s="99" t="n">
+      <c r="G18" s="99" t="n">
         <v>-3.94</v>
       </c>
-      <c r="G18" s="99" t="n">
+      <c r="H18" s="99" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="H18" s="99" t="n">
-        <v>-2.75</v>
       </c>
       <c r="I18" s="99" t="n">
         <v>-2.75</v>
       </c>
       <c r="J18" s="99" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="K18" s="99" t="n">
         <v>-3.96</v>
       </c>
-      <c r="K18" s="99" t="n">
+      <c r="L18" s="99" t="n">
         <v>-3.9</v>
       </c>
-      <c r="L18" s="99" t="n">
+      <c r="M18" s="99" t="n">
         <v>-4.25</v>
       </c>
-      <c r="M18" s="99" t="n">
+      <c r="N18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="N18" s="99" t="n">
+      <c r="O18" s="99" t="n">
         <v>-3.57</v>
       </c>
-      <c r="O18" s="99" t="n">
+      <c r="P18" s="99" t="n">
         <v>-3.86</v>
       </c>
-      <c r="P18" s="99" t="n">
+      <c r="Q18" s="99" t="n">
         <v>-1.13</v>
       </c>
-      <c r="Q18" s="99" t="n">
+      <c r="R18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="R18" s="99" t="n">
+      <c r="S18" s="99" t="n">
         <v>-4.68</v>
       </c>
-      <c r="S18" s="99" t="n">
+      <c r="T18" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="T18" s="99" t="n">
+      <c r="U18" s="99" t="n">
         <v>-7.63</v>
       </c>
-      <c r="U18" s="99" t="n">
+      <c r="V18" s="99" t="n">
         <v>-5.9</v>
       </c>
-      <c r="V18" s="99" t="n">
+      <c r="W18" s="99" t="n">
         <v>-6.89</v>
       </c>
-      <c r="W18" s="99" t="n">
+      <c r="X18" s="99" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="X18" s="99" t="n">
+      <c r="Y18" s="99" t="n">
         <v>-10.99</v>
       </c>
-      <c r="Y18" s="99" t="n">
+      <c r="Z18" s="99" t="n">
         <v>-12.85</v>
       </c>
-      <c r="Z18" s="99" t="n">
+      <c r="AA18" s="99" t="n">
         <v>-12.17</v>
       </c>
-      <c r="AA18" s="99" t="n">
+      <c r="AB18" s="99" t="n">
         <v>-11.69</v>
       </c>
-      <c r="AB18" s="99" t="n">
+      <c r="AC18" s="99" t="n">
         <v>-10.4</v>
       </c>
-      <c r="AC18" s="99" t="n">
+      <c r="AD18" s="99" t="n">
         <v>-11.63</v>
       </c>
-      <c r="AD18" s="99" t="n">
+      <c r="AE18" s="99" t="n">
         <v>-11</v>
-      </c>
-      <c r="AE18" s="99" t="n">
-        <v>-10.2</v>
       </c>
     </row>
     <row r="19">
@@ -8403,94 +8403,94 @@
         </is>
       </c>
       <c r="B19" s="99" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="C19" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="C19" s="99" t="n">
+      <c r="D19" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="D19" s="99" t="n">
+      <c r="E19" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="E19" s="99" t="n">
+      <c r="F19" s="99" t="n">
         <v>2.32</v>
       </c>
-      <c r="F19" s="99" t="n">
+      <c r="G19" s="99" t="n">
         <v>1.61</v>
       </c>
-      <c r="G19" s="99" t="n">
+      <c r="H19" s="99" t="n">
         <v>0.67</v>
-      </c>
-      <c r="H19" s="99" t="n">
-        <v>2.05</v>
       </c>
       <c r="I19" s="99" t="n">
         <v>2.05</v>
       </c>
       <c r="J19" s="99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K19" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="K19" s="99" t="n">
+      <c r="L19" s="99" t="n">
         <v>7.94</v>
       </c>
-      <c r="L19" s="99" t="n">
+      <c r="M19" s="99" t="n">
         <v>9.01</v>
       </c>
-      <c r="M19" s="99" t="n">
+      <c r="N19" s="99" t="n">
         <v>9.44</v>
       </c>
-      <c r="N19" s="99" t="n">
+      <c r="O19" s="99" t="n">
         <v>10.05</v>
       </c>
-      <c r="O19" s="99" t="n">
+      <c r="P19" s="99" t="n">
         <v>6.61</v>
       </c>
-      <c r="P19" s="99" t="n">
+      <c r="Q19" s="99" t="n">
         <v>7.75</v>
       </c>
-      <c r="Q19" s="99" t="n">
+      <c r="R19" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="R19" s="99" t="n">
+      <c r="S19" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="S19" s="99" t="n">
+      <c r="T19" s="99" t="n">
         <v>5.06</v>
       </c>
-      <c r="T19" s="99" t="n">
+      <c r="U19" s="99" t="n">
         <v>4.55</v>
       </c>
-      <c r="U19" s="99" t="n">
+      <c r="V19" s="99" t="n">
         <v>4.69</v>
       </c>
-      <c r="V19" s="99" t="n">
+      <c r="W19" s="99" t="n">
         <v>4.94</v>
       </c>
-      <c r="W19" s="99" t="n">
+      <c r="X19" s="99" t="n">
         <v>5.62</v>
       </c>
-      <c r="X19" s="99" t="n">
+      <c r="Y19" s="99" t="n">
         <v>5.3</v>
       </c>
-      <c r="Y19" s="99" t="n">
+      <c r="Z19" s="99" t="n">
         <v>5.93</v>
       </c>
-      <c r="Z19" s="99" t="n">
+      <c r="AA19" s="99" t="n">
         <v>5.1</v>
       </c>
-      <c r="AA19" s="99" t="n">
+      <c r="AB19" s="99" t="n">
         <v>7.32</v>
       </c>
-      <c r="AB19" s="99" t="n">
+      <c r="AC19" s="99" t="n">
         <v>7.63</v>
       </c>
-      <c r="AC19" s="99" t="n">
+      <c r="AD19" s="99" t="n">
         <v>7.27</v>
       </c>
-      <c r="AD19" s="99" t="n">
+      <c r="AE19" s="99" t="n">
         <v>6.3</v>
-      </c>
-      <c r="AE19" s="99" t="n">
-        <v>3.52</v>
       </c>
     </row>
     <row r="20">
@@ -8500,94 +8500,94 @@
         </is>
       </c>
       <c r="B20" s="99" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="C20" s="99" t="n">
         <v>52.57</v>
       </c>
-      <c r="C20" s="99" t="n">
+      <c r="D20" s="99" t="n">
         <v>48.7</v>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="E20" s="99" t="n">
         <v>38.58</v>
       </c>
-      <c r="E20" s="99" t="n">
+      <c r="F20" s="99" t="n">
         <v>26.15</v>
       </c>
-      <c r="F20" s="99" t="n">
+      <c r="G20" s="99" t="n">
         <v>31.15</v>
       </c>
-      <c r="G20" s="99" t="n">
+      <c r="H20" s="99" t="n">
         <v>27.74</v>
-      </c>
-      <c r="H20" s="99" t="n">
-        <v>38.27</v>
       </c>
       <c r="I20" s="99" t="n">
         <v>38.27</v>
       </c>
       <c r="J20" s="99" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="K20" s="99" t="n">
         <v>38.92</v>
       </c>
-      <c r="K20" s="99" t="n">
+      <c r="L20" s="99" t="n">
         <v>49.28</v>
       </c>
-      <c r="L20" s="99" t="n">
+      <c r="M20" s="99" t="n">
         <v>51.67</v>
       </c>
-      <c r="M20" s="99" t="n">
+      <c r="N20" s="99" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="N20" s="99" t="n">
+      <c r="O20" s="99" t="n">
         <v>65.08</v>
       </c>
-      <c r="O20" s="99" t="n">
+      <c r="P20" s="99" t="n">
         <v>60.24</v>
       </c>
-      <c r="P20" s="99" t="n">
+      <c r="Q20" s="99" t="n">
         <v>77.66</v>
       </c>
-      <c r="Q20" s="99" t="n">
+      <c r="R20" s="99" t="n">
         <v>75.16</v>
       </c>
-      <c r="R20" s="99" t="n">
+      <c r="S20" s="99" t="n">
         <v>67.81</v>
       </c>
-      <c r="S20" s="99" t="n">
+      <c r="T20" s="99" t="n">
         <v>70.5</v>
       </c>
-      <c r="T20" s="99" t="n">
+      <c r="U20" s="99" t="n">
         <v>58.65</v>
       </c>
-      <c r="U20" s="99" t="n">
+      <c r="V20" s="99" t="n">
         <v>69.89</v>
       </c>
-      <c r="V20" s="99" t="n">
+      <c r="W20" s="99" t="n">
         <v>75.78</v>
       </c>
-      <c r="W20" s="99" t="n">
+      <c r="X20" s="99" t="n">
         <v>70.91</v>
       </c>
-      <c r="X20" s="99" t="n">
+      <c r="Y20" s="99" t="n">
         <v>52.62</v>
       </c>
-      <c r="Y20" s="99" t="n">
+      <c r="Z20" s="99" t="n">
         <v>52.99</v>
       </c>
-      <c r="Z20" s="99" t="n">
+      <c r="AA20" s="99" t="n">
         <v>57.79</v>
       </c>
-      <c r="AA20" s="99" t="n">
+      <c r="AB20" s="99" t="n">
         <v>54.24</v>
       </c>
-      <c r="AB20" s="99" t="n">
+      <c r="AC20" s="99" t="n">
         <v>53.11</v>
       </c>
-      <c r="AC20" s="99" t="n">
+      <c r="AD20" s="99" t="n">
         <v>42.07</v>
       </c>
-      <c r="AD20" s="99" t="n">
+      <c r="AE20" s="99" t="n">
         <v>41.26</v>
-      </c>
-      <c r="AE20" s="99" t="n">
-        <v>27.26</v>
       </c>
     </row>
     <row r="21">
@@ -8597,94 +8597,94 @@
         </is>
       </c>
       <c r="B21" s="99" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="C21" s="99" t="n">
         <v>49.33</v>
       </c>
-      <c r="C21" s="99" t="n">
+      <c r="D21" s="99" t="n">
         <v>48.3</v>
       </c>
-      <c r="D21" s="99" t="n">
+      <c r="E21" s="99" t="n">
         <v>45.75</v>
       </c>
-      <c r="E21" s="99" t="n">
+      <c r="F21" s="99" t="n">
         <v>43.02</v>
       </c>
-      <c r="F21" s="99" t="n">
+      <c r="G21" s="99" t="n">
         <v>45.06</v>
       </c>
-      <c r="G21" s="99" t="n">
+      <c r="H21" s="99" t="n">
         <v>44.32</v>
-      </c>
-      <c r="H21" s="99" t="n">
-        <v>48.45</v>
       </c>
       <c r="I21" s="99" t="n">
         <v>48.45</v>
       </c>
       <c r="J21" s="99" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="K21" s="99" t="n">
         <v>48.67</v>
       </c>
-      <c r="K21" s="99" t="n">
+      <c r="L21" s="99" t="n">
         <v>52.11</v>
       </c>
-      <c r="L21" s="99" t="n">
+      <c r="M21" s="99" t="n">
         <v>52.84</v>
       </c>
-      <c r="M21" s="99" t="n">
+      <c r="N21" s="99" t="n">
         <v>58.6</v>
       </c>
-      <c r="N21" s="99" t="n">
+      <c r="O21" s="99" t="n">
         <v>55.46</v>
       </c>
-      <c r="O21" s="99" t="n">
+      <c r="P21" s="99" t="n">
         <v>53.93</v>
       </c>
-      <c r="P21" s="99" t="n">
+      <c r="Q21" s="99" t="n">
         <v>57.57</v>
       </c>
-      <c r="Q21" s="99" t="n">
+      <c r="R21" s="99" t="n">
         <v>56.41</v>
       </c>
-      <c r="R21" s="99" t="n">
+      <c r="S21" s="99" t="n">
         <v>53.44</v>
       </c>
-      <c r="S21" s="99" t="n">
+      <c r="T21" s="99" t="n">
         <v>53.98</v>
       </c>
-      <c r="T21" s="99" t="n">
+      <c r="U21" s="99" t="n">
         <v>49.84</v>
       </c>
-      <c r="U21" s="99" t="n">
+      <c r="V21" s="99" t="n">
         <v>51.97</v>
       </c>
-      <c r="V21" s="99" t="n">
+      <c r="W21" s="99" t="n">
         <v>53.01</v>
       </c>
-      <c r="W21" s="99" t="n">
+      <c r="X21" s="99" t="n">
         <v>50.78</v>
       </c>
-      <c r="X21" s="99" t="n">
+      <c r="Y21" s="99" t="n">
         <v>45.07</v>
       </c>
-      <c r="Y21" s="99" t="n">
+      <c r="Z21" s="99" t="n">
         <v>45.13</v>
       </c>
-      <c r="Z21" s="99" t="n">
+      <c r="AA21" s="99" t="n">
         <v>46.04</v>
       </c>
-      <c r="AA21" s="99" t="n">
+      <c r="AB21" s="99" t="n">
         <v>44.96</v>
       </c>
-      <c r="AB21" s="99" t="n">
+      <c r="AC21" s="99" t="n">
         <v>44.6</v>
       </c>
-      <c r="AC21" s="99" t="n">
+      <c r="AD21" s="99" t="n">
         <v>41.23</v>
       </c>
-      <c r="AD21" s="99" t="n">
+      <c r="AE21" s="99" t="n">
         <v>40.99</v>
-      </c>
-      <c r="AE21" s="99" t="n">
-        <v>36.98</v>
       </c>
     </row>
     <row r="22">
@@ -8713,129 +8713,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="97" t="inlineStr">
+      <c r="F22" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G22" s="96" t="inlineStr">
+      <c r="H22" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H22" s="96" t="inlineStr">
+      <c r="I22" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I22" s="96" t="inlineStr">
+      <c r="J22" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J22" s="96" t="inlineStr">
+      <c r="K22" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K22" s="96" t="inlineStr">
+      <c r="L22" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L22" s="97" t="inlineStr">
+      <c r="M22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="97" t="inlineStr">
+      <c r="N22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="97" t="inlineStr">
+      <c r="O22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="97" t="inlineStr">
+      <c r="P22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="97" t="inlineStr">
+      <c r="Q22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="97" t="inlineStr">
+      <c r="R22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="97" t="inlineStr">
+      <c r="S22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="97" t="inlineStr">
+      <c r="T22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="98" t="inlineStr">
+      <c r="U22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U22" s="98" t="inlineStr">
+      <c r="V22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V22" s="98" t="inlineStr">
+      <c r="W22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W22" s="98" t="inlineStr">
+      <c r="X22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X22" s="98" t="inlineStr">
+      <c r="Y22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y22" s="98" t="inlineStr">
+      <c r="Z22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z22" s="98" t="inlineStr">
+      <c r="AA22" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA22" s="97" t="inlineStr">
+      <c r="AB22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="97" t="inlineStr">
+      <c r="AC22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="97" t="inlineStr">
+      <c r="AD22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE22" s="96" t="inlineStr">
@@ -8854,91 +8854,91 @@
         <v>2.92</v>
       </c>
       <c r="C23" s="99" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D23" s="99" t="n">
         <v>2.53</v>
       </c>
-      <c r="D23" s="99" t="n">
+      <c r="E23" s="99" t="n">
         <v>2.24</v>
       </c>
-      <c r="E23" s="99" t="n">
+      <c r="F23" s="99" t="n">
         <v>2.26</v>
       </c>
-      <c r="F23" s="99" t="n">
+      <c r="G23" s="99" t="n">
         <v>1.14</v>
       </c>
-      <c r="G23" s="99" t="n">
+      <c r="H23" s="99" t="n">
         <v>0.92</v>
       </c>
-      <c r="H23" s="99" t="n">
+      <c r="I23" s="99" t="n">
         <v>0.62</v>
       </c>
-      <c r="I23" s="99" t="n">
+      <c r="J23" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="J23" s="99" t="n">
+      <c r="K23" s="99" t="n">
         <v>3.24</v>
       </c>
-      <c r="K23" s="99" t="n">
+      <c r="L23" s="99" t="n">
         <v>3.29</v>
-      </c>
-      <c r="L23" s="99" t="n">
-        <v>5.5</v>
       </c>
       <c r="M23" s="99" t="n">
         <v>5.5</v>
       </c>
       <c r="N23" s="99" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O23" s="99" t="n">
         <v>5.68</v>
       </c>
-      <c r="O23" s="99" t="n">
+      <c r="P23" s="99" t="n">
         <v>5.84</v>
       </c>
-      <c r="P23" s="99" t="n">
+      <c r="Q23" s="99" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q23" s="99" t="n">
+      <c r="R23" s="99" t="n">
         <v>7.28</v>
       </c>
-      <c r="R23" s="99" t="n">
+      <c r="S23" s="99" t="n">
         <v>6.98</v>
       </c>
-      <c r="S23" s="99" t="n">
+      <c r="T23" s="99" t="n">
         <v>4.99</v>
       </c>
-      <c r="T23" s="99" t="n">
+      <c r="U23" s="99" t="n">
         <v>5.96</v>
       </c>
-      <c r="U23" s="99" t="n">
+      <c r="V23" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="V23" s="99" t="n">
+      <c r="W23" s="99" t="n">
         <v>5.68</v>
       </c>
-      <c r="W23" s="99" t="n">
+      <c r="X23" s="99" t="n">
         <v>4.38</v>
       </c>
-      <c r="X23" s="99" t="n">
+      <c r="Y23" s="99" t="n">
         <v>4.43</v>
       </c>
-      <c r="Y23" s="99" t="n">
+      <c r="Z23" s="99" t="n">
         <v>2.87</v>
       </c>
-      <c r="Z23" s="99" t="n">
+      <c r="AA23" s="99" t="n">
         <v>2.59</v>
       </c>
-      <c r="AA23" s="99" t="n">
+      <c r="AB23" s="99" t="n">
         <v>0.68</v>
       </c>
-      <c r="AB23" s="99" t="n">
+      <c r="AC23" s="99" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC23" s="99" t="n">
+      <c r="AD23" s="99" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD23" s="99" t="n">
+      <c r="AE23" s="99" t="n">
         <v>-0.44</v>
-      </c>
-      <c r="AE23" s="99" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -8951,91 +8951,91 @@
         <v>7.95</v>
       </c>
       <c r="C24" s="99" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="D24" s="99" t="n">
         <v>7.49</v>
       </c>
-      <c r="D24" s="99" t="n">
+      <c r="E24" s="99" t="n">
         <v>6.76</v>
       </c>
-      <c r="E24" s="99" t="n">
+      <c r="F24" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="F24" s="99" t="n">
+      <c r="G24" s="99" t="n">
         <v>6.12</v>
       </c>
-      <c r="G24" s="99" t="n">
+      <c r="H24" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="I24" s="99" t="n">
         <v>5.69</v>
       </c>
-      <c r="I24" s="99" t="n">
+      <c r="J24" s="99" t="n">
         <v>6.85</v>
       </c>
-      <c r="J24" s="99" t="n">
+      <c r="K24" s="99" t="n">
         <v>6.87</v>
       </c>
-      <c r="K24" s="99" t="n">
+      <c r="L24" s="99" t="n">
         <v>6.83</v>
-      </c>
-      <c r="L24" s="99" t="n">
-        <v>10.36</v>
       </c>
       <c r="M24" s="99" t="n">
         <v>10.36</v>
       </c>
       <c r="N24" s="99" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="O24" s="99" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="O24" s="99" t="n">
+      <c r="P24" s="99" t="n">
         <v>8.43</v>
       </c>
-      <c r="P24" s="99" t="n">
+      <c r="Q24" s="99" t="n">
         <v>10.21</v>
       </c>
-      <c r="Q24" s="99" t="n">
+      <c r="R24" s="99" t="n">
         <v>10.6</v>
       </c>
-      <c r="R24" s="99" t="n">
+      <c r="S24" s="99" t="n">
         <v>9.82</v>
       </c>
-      <c r="S24" s="99" t="n">
+      <c r="T24" s="99" t="n">
         <v>8.44</v>
       </c>
-      <c r="T24" s="99" t="n">
+      <c r="U24" s="99" t="n">
         <v>10.29</v>
       </c>
-      <c r="U24" s="99" t="n">
+      <c r="V24" s="99" t="n">
         <v>10.4</v>
       </c>
-      <c r="V24" s="99" t="n">
+      <c r="W24" s="99" t="n">
         <v>10.44</v>
       </c>
-      <c r="W24" s="99" t="n">
+      <c r="X24" s="99" t="n">
         <v>9.56</v>
       </c>
-      <c r="X24" s="99" t="n">
+      <c r="Y24" s="99" t="n">
         <v>8.93</v>
       </c>
-      <c r="Y24" s="99" t="n">
+      <c r="Z24" s="99" t="n">
         <v>7.24</v>
       </c>
-      <c r="Z24" s="99" t="n">
+      <c r="AA24" s="99" t="n">
         <v>9.09</v>
       </c>
-      <c r="AA24" s="99" t="n">
+      <c r="AB24" s="99" t="n">
         <v>7.41</v>
       </c>
-      <c r="AB24" s="99" t="n">
+      <c r="AC24" s="99" t="n">
         <v>6.76</v>
       </c>
-      <c r="AC24" s="99" t="n">
+      <c r="AD24" s="99" t="n">
         <v>5.76</v>
       </c>
-      <c r="AD24" s="99" t="n">
+      <c r="AE24" s="99" t="n">
         <v>3.98</v>
-      </c>
-      <c r="AE24" s="99" t="n">
-        <v>5.79</v>
       </c>
     </row>
     <row r="25">
@@ -9048,91 +9048,91 @@
         <v>95.83</v>
       </c>
       <c r="C25" s="99" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="D25" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="D25" s="99" t="n">
+      <c r="E25" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="E25" s="99" t="n">
+      <c r="F25" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="F25" s="99" t="n">
+      <c r="G25" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="G25" s="99" t="n">
+      <c r="H25" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="I25" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="99" t="n">
+      <c r="J25" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="J25" s="99" t="n">
+      <c r="K25" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="K25" s="99" t="n">
+      <c r="L25" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="L25" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="M25" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="N25" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="O25" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="O25" s="99" t="n">
+      <c r="P25" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="P25" s="99" t="n">
+      <c r="Q25" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="Q25" s="99" t="n">
+      <c r="R25" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="R25" s="99" t="n">
+      <c r="S25" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="S25" s="99" t="n">
+      <c r="T25" s="99" t="n">
         <v>30.49</v>
       </c>
-      <c r="T25" s="99" t="n">
+      <c r="U25" s="99" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="U25" s="99" t="n">
+      <c r="V25" s="99" t="n">
         <v>80.11</v>
       </c>
-      <c r="V25" s="99" t="n">
+      <c r="W25" s="99" t="n">
         <v>99.58</v>
       </c>
-      <c r="W25" s="99" t="n">
+      <c r="X25" s="99" t="n">
         <v>98.98</v>
       </c>
-      <c r="X25" s="99" t="n">
+      <c r="Y25" s="99" t="n">
         <v>98.8</v>
       </c>
-      <c r="Y25" s="99" t="n">
+      <c r="Z25" s="99" t="n">
         <v>96.18000000000001</v>
       </c>
-      <c r="Z25" s="99" t="n">
+      <c r="AA25" s="99" t="n">
         <v>94.84</v>
       </c>
-      <c r="AA25" s="99" t="n">
+      <c r="AB25" s="99" t="n">
         <v>79.02</v>
       </c>
-      <c r="AB25" s="99" t="n">
+      <c r="AC25" s="99" t="n">
         <v>78.93000000000001</v>
       </c>
-      <c r="AC25" s="99" t="n">
+      <c r="AD25" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="AD25" s="99" t="n">
+      <c r="AE25" s="99" t="n">
         <v>23.25</v>
-      </c>
-      <c r="AE25" s="99" t="n">
-        <v>33.99</v>
       </c>
     </row>
     <row r="26">
@@ -9145,91 +9145,91 @@
         <v>95.83</v>
       </c>
       <c r="C26" s="99" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="D26" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="D26" s="99" t="n">
+      <c r="E26" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="E26" s="99" t="n">
+      <c r="F26" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="F26" s="99" t="n">
+      <c r="G26" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="G26" s="99" t="n">
+      <c r="H26" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="H26" s="99" t="n">
+      <c r="I26" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="I26" s="99" t="n">
+      <c r="J26" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="J26" s="99" t="n">
+      <c r="K26" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="K26" s="99" t="n">
+      <c r="L26" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="L26" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="M26" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="N26" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="O26" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="O26" s="99" t="n">
+      <c r="P26" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="P26" s="99" t="n">
+      <c r="Q26" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="Q26" s="99" t="n">
+      <c r="R26" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="R26" s="99" t="n">
+      <c r="S26" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="S26" s="99" t="n">
+      <c r="T26" s="99" t="n">
         <v>30.49</v>
       </c>
-      <c r="T26" s="99" t="n">
+      <c r="U26" s="99" t="n">
         <v>89.15000000000001</v>
       </c>
-      <c r="U26" s="99" t="n">
+      <c r="V26" s="99" t="n">
         <v>80.11</v>
       </c>
-      <c r="V26" s="99" t="n">
+      <c r="W26" s="99" t="n">
         <v>99.58</v>
       </c>
-      <c r="W26" s="99" t="n">
+      <c r="X26" s="99" t="n">
         <v>98.98</v>
       </c>
-      <c r="X26" s="99" t="n">
+      <c r="Y26" s="99" t="n">
         <v>98.8</v>
       </c>
-      <c r="Y26" s="99" t="n">
+      <c r="Z26" s="99" t="n">
         <v>96.18000000000001</v>
       </c>
-      <c r="Z26" s="99" t="n">
+      <c r="AA26" s="99" t="n">
         <v>94.84</v>
       </c>
-      <c r="AA26" s="99" t="n">
+      <c r="AB26" s="99" t="n">
         <v>79.02</v>
       </c>
-      <c r="AB26" s="99" t="n">
+      <c r="AC26" s="99" t="n">
         <v>78.93000000000001</v>
       </c>
-      <c r="AC26" s="99" t="n">
+      <c r="AD26" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="AD26" s="99" t="n">
+      <c r="AE26" s="99" t="n">
         <v>23.25</v>
-      </c>
-      <c r="AE26" s="99" t="n">
-        <v>33.99</v>
       </c>
     </row>
     <row r="27">
@@ -9258,129 +9258,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F27" s="96" t="inlineStr">
+      <c r="F27" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G27" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G27" s="97" t="inlineStr">
+      <c r="H27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H27" s="96" t="inlineStr">
+      <c r="I27" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I27" s="96" t="inlineStr">
+      <c r="J27" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J27" s="97" t="inlineStr">
+      <c r="K27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K27" s="97" t="inlineStr">
+      <c r="L27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L27" s="98" t="inlineStr">
+      <c r="M27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M27" s="98" t="inlineStr">
+      <c r="N27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N27" s="97" t="inlineStr">
+      <c r="O27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O27" s="97" t="inlineStr">
+      <c r="P27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P27" s="97" t="inlineStr">
+      <c r="Q27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q27" s="98" t="inlineStr">
+      <c r="R27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R27" s="98" t="inlineStr">
+      <c r="S27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S27" s="97" t="inlineStr">
+      <c r="T27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="98" t="inlineStr">
+      <c r="U27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U27" s="98" t="inlineStr">
+      <c r="V27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V27" s="98" t="inlineStr">
+      <c r="W27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W27" s="98" t="inlineStr">
+      <c r="X27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X27" s="98" t="inlineStr">
+      <c r="Y27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y27" s="98" t="inlineStr">
+      <c r="Z27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z27" s="98" t="inlineStr">
+      <c r="AA27" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA27" s="97" t="inlineStr">
+      <c r="AB27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB27" s="97" t="inlineStr">
+      <c r="AC27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC27" s="97" t="inlineStr">
+      <c r="AD27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD27" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE27" s="96" t="inlineStr">
@@ -9396,94 +9396,94 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="C28" s="99" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="D28" s="99" t="n">
         <v>6.59</v>
       </c>
-      <c r="C28" s="99" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="D28" s="99" t="n">
+      <c r="E28" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="E28" s="99" t="n">
+      <c r="F28" s="99" t="n">
         <v>5.89</v>
       </c>
-      <c r="F28" s="99" t="n">
+      <c r="G28" s="99" t="n">
         <v>5.41</v>
       </c>
-      <c r="G28" s="99" t="n">
+      <c r="H28" s="99" t="n">
         <v>5.47</v>
       </c>
-      <c r="H28" s="99" t="n">
+      <c r="I28" s="99" t="n">
         <v>4.12</v>
       </c>
-      <c r="I28" s="99" t="n">
+      <c r="J28" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="J28" s="99" t="n">
+      <c r="K28" s="99" t="n">
         <v>5.61</v>
       </c>
-      <c r="K28" s="99" t="n">
+      <c r="L28" s="99" t="n">
         <v>5.27</v>
-      </c>
-      <c r="L28" s="99" t="n">
-        <v>7.1</v>
       </c>
       <c r="M28" s="99" t="n">
         <v>7.1</v>
       </c>
       <c r="N28" s="99" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O28" s="99" t="n">
         <v>6.78</v>
       </c>
-      <c r="O28" s="99" t="n">
+      <c r="P28" s="99" t="n">
         <v>6.53</v>
       </c>
-      <c r="P28" s="99" t="n">
+      <c r="Q28" s="99" t="n">
         <v>6.63</v>
       </c>
-      <c r="Q28" s="99" t="n">
+      <c r="R28" s="99" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="R28" s="99" t="n">
+      <c r="S28" s="99" t="n">
         <v>7.11</v>
       </c>
-      <c r="S28" s="99" t="n">
+      <c r="T28" s="99" t="n">
         <v>4.79</v>
       </c>
-      <c r="T28" s="99" t="n">
+      <c r="U28" s="99" t="n">
         <v>4.66</v>
       </c>
-      <c r="U28" s="99" t="n">
+      <c r="V28" s="99" t="n">
         <v>4.53</v>
       </c>
-      <c r="V28" s="99" t="n">
+      <c r="W28" s="99" t="n">
         <v>3.09</v>
       </c>
-      <c r="W28" s="99" t="n">
+      <c r="X28" s="99" t="n">
         <v>1.97</v>
       </c>
-      <c r="X28" s="99" t="n">
+      <c r="Y28" s="99" t="n">
         <v>1.9</v>
       </c>
-      <c r="Y28" s="99" t="n">
+      <c r="Z28" s="99" t="n">
         <v>0.01</v>
       </c>
-      <c r="Z28" s="99" t="n">
+      <c r="AA28" s="99" t="n">
         <v>-0.26</v>
       </c>
-      <c r="AA28" s="99" t="n">
+      <c r="AB28" s="99" t="n">
         <v>-1.38</v>
       </c>
-      <c r="AB28" s="99" t="n">
+      <c r="AC28" s="99" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AC28" s="99" t="n">
+      <c r="AD28" s="99" t="n">
         <v>0.04</v>
       </c>
-      <c r="AD28" s="99" t="n">
+      <c r="AE28" s="99" t="n">
         <v>-1.9</v>
-      </c>
-      <c r="AE28" s="99" t="n">
-        <v>-0.99</v>
       </c>
     </row>
     <row r="29">
@@ -9493,191 +9493,191 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="C29" s="99" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D29" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="C29" s="99" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="D29" s="99" t="n">
+      <c r="E29" s="99" t="n">
         <v>3.31</v>
       </c>
-      <c r="E29" s="99" t="n">
+      <c r="F29" s="99" t="n">
         <v>3.42</v>
       </c>
-      <c r="F29" s="99" t="n">
+      <c r="G29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="G29" s="99" t="n">
+      <c r="H29" s="99" t="n">
         <v>5.26</v>
       </c>
-      <c r="H29" s="99" t="n">
+      <c r="I29" s="99" t="n">
         <v>4.21</v>
       </c>
-      <c r="I29" s="99" t="n">
+      <c r="J29" s="99" t="n">
         <v>4.76</v>
-      </c>
-      <c r="J29" s="99" t="n">
-        <v>4.95</v>
       </c>
       <c r="K29" s="99" t="n">
         <v>4.95</v>
       </c>
       <c r="L29" s="99" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="M29" s="99" t="n">
         <v>7.21</v>
       </c>
       <c r="N29" s="99" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="O29" s="99" t="n">
         <v>6.75</v>
       </c>
-      <c r="O29" s="99" t="n">
+      <c r="P29" s="99" t="n">
         <v>5.93</v>
       </c>
-      <c r="P29" s="99" t="n">
+      <c r="Q29" s="99" t="n">
         <v>6.7</v>
       </c>
-      <c r="Q29" s="99" t="n">
+      <c r="R29" s="99" t="n">
         <v>6.88</v>
       </c>
-      <c r="R29" s="99" t="n">
+      <c r="S29" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="S29" s="99" t="n">
+      <c r="T29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="T29" s="99" t="n">
+      <c r="U29" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="U29" s="99" t="n">
+      <c r="V29" s="99" t="n">
         <v>4.84</v>
       </c>
-      <c r="V29" s="99" t="n">
+      <c r="W29" s="99" t="n">
         <v>4.94</v>
       </c>
-      <c r="W29" s="99" t="n">
+      <c r="X29" s="99" t="n">
         <v>4.07</v>
       </c>
-      <c r="X29" s="99" t="n">
+      <c r="Y29" s="99" t="n">
         <v>3.66</v>
       </c>
-      <c r="Y29" s="99" t="n">
+      <c r="Z29" s="99" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z29" s="99" t="n">
+      <c r="AA29" s="99" t="n">
         <v>2.99</v>
       </c>
-      <c r="AA29" s="99" t="n">
+      <c r="AB29" s="99" t="n">
         <v>2.06</v>
       </c>
-      <c r="AB29" s="99" t="n">
+      <c r="AC29" s="99" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC29" s="99" t="n">
+      <c r="AD29" s="99" t="n">
         <v>1.74</v>
       </c>
-      <c r="AD29" s="99" t="n">
+      <c r="AE29" s="99" t="n">
         <v>0.88</v>
       </c>
-      <c r="AE29" s="99" t="n">
-        <v>1.89</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="80" t="inlineStr">
+      <c r="A30" s="100" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="99" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="C30" s="99" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="D30" s="99" t="n">
         <v>82.94</v>
       </c>
-      <c r="C30" s="99" t="n">
-        <v>82.94</v>
-      </c>
-      <c r="D30" s="99" t="n">
+      <c r="E30" s="99" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="E30" s="99" t="n">
+      <c r="F30" s="99" t="n">
         <v>56.57</v>
       </c>
-      <c r="F30" s="99" t="n">
+      <c r="G30" s="99" t="n">
         <v>46.45</v>
       </c>
-      <c r="G30" s="99" t="n">
+      <c r="H30" s="99" t="n">
         <v>52.5</v>
       </c>
-      <c r="H30" s="99" t="n">
+      <c r="I30" s="99" t="n">
         <v>13.02</v>
       </c>
-      <c r="I30" s="99" t="n">
+      <c r="J30" s="99" t="n">
         <v>24.55</v>
       </c>
-      <c r="J30" s="99" t="n">
+      <c r="K30" s="99" t="n">
         <v>35.87</v>
       </c>
-      <c r="K30" s="99" t="n">
+      <c r="L30" s="99" t="n">
         <v>32.25</v>
-      </c>
-      <c r="L30" s="99" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="M30" s="99" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="N30" s="99" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="O30" s="99" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="O30" s="99" t="n">
+      <c r="P30" s="99" t="n">
         <v>52.49</v>
       </c>
-      <c r="P30" s="99" t="n">
+      <c r="Q30" s="99" t="n">
         <v>83.64</v>
       </c>
-      <c r="Q30" s="99" t="n">
+      <c r="R30" s="99" t="n">
         <v>83.23</v>
       </c>
-      <c r="R30" s="99" t="n">
+      <c r="S30" s="99" t="n">
         <v>81.13</v>
       </c>
-      <c r="S30" s="99" t="n">
+      <c r="T30" s="99" t="n">
         <v>54.01</v>
       </c>
-      <c r="T30" s="99" t="n">
+      <c r="U30" s="99" t="n">
         <v>85.48</v>
       </c>
-      <c r="U30" s="99" t="n">
+      <c r="V30" s="99" t="n">
         <v>83.48</v>
       </c>
-      <c r="V30" s="99" t="n">
+      <c r="W30" s="99" t="n">
         <v>92.97</v>
       </c>
-      <c r="W30" s="99" t="n">
+      <c r="X30" s="99" t="n">
         <v>90.08</v>
       </c>
-      <c r="X30" s="99" t="n">
+      <c r="Y30" s="99" t="n">
         <v>88.81999999999999</v>
       </c>
-      <c r="Y30" s="99" t="n">
+      <c r="Z30" s="99" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="Z30" s="99" t="n">
+      <c r="AA30" s="99" t="n">
         <v>70.31999999999999</v>
       </c>
-      <c r="AA30" s="99" t="n">
+      <c r="AB30" s="99" t="n">
         <v>48.86</v>
       </c>
-      <c r="AB30" s="99" t="n">
+      <c r="AC30" s="99" t="n">
         <v>58.57</v>
       </c>
-      <c r="AC30" s="99" t="n">
+      <c r="AD30" s="99" t="n">
         <v>56.47</v>
       </c>
-      <c r="AD30" s="99" t="n">
+      <c r="AE30" s="99" t="n">
         <v>20.7</v>
-      </c>
-      <c r="AE30" s="99" t="n">
-        <v>25.49</v>
       </c>
     </row>
     <row r="31">
@@ -9687,94 +9687,94 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="C31" s="99" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="D31" s="99" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="C31" s="99" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="D31" s="99" t="n">
+      <c r="E31" s="99" t="n">
         <v>60.93</v>
       </c>
-      <c r="E31" s="99" t="n">
+      <c r="F31" s="99" t="n">
         <v>51.28</v>
       </c>
-      <c r="F31" s="99" t="n">
+      <c r="G31" s="99" t="n">
         <v>45.58</v>
       </c>
-      <c r="G31" s="99" t="n">
+      <c r="H31" s="99" t="n">
         <v>48.99</v>
       </c>
-      <c r="H31" s="99" t="n">
+      <c r="I31" s="99" t="n">
         <v>25.8</v>
       </c>
-      <c r="I31" s="99" t="n">
+      <c r="J31" s="99" t="n">
         <v>37.29</v>
       </c>
-      <c r="J31" s="99" t="n">
+      <c r="K31" s="99" t="n">
         <v>46.06</v>
       </c>
-      <c r="K31" s="99" t="n">
+      <c r="L31" s="99" t="n">
         <v>44.24</v>
-      </c>
-      <c r="L31" s="99" t="n">
-        <v>79.63</v>
       </c>
       <c r="M31" s="99" t="n">
         <v>79.63</v>
       </c>
       <c r="N31" s="99" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="O31" s="99" t="n">
         <v>73.44</v>
       </c>
-      <c r="O31" s="99" t="n">
+      <c r="P31" s="99" t="n">
         <v>64.13</v>
       </c>
-      <c r="P31" s="99" t="n">
+      <c r="Q31" s="99" t="n">
         <v>78.52</v>
       </c>
-      <c r="Q31" s="99" t="n">
+      <c r="R31" s="99" t="n">
         <v>78.27</v>
       </c>
-      <c r="R31" s="99" t="n">
+      <c r="S31" s="99" t="n">
         <v>76.89</v>
       </c>
-      <c r="S31" s="99" t="n">
+      <c r="T31" s="99" t="n">
         <v>63.94</v>
       </c>
-      <c r="T31" s="99" t="n">
+      <c r="U31" s="99" t="n">
         <v>77.25</v>
       </c>
-      <c r="U31" s="99" t="n">
+      <c r="V31" s="99" t="n">
         <v>76</v>
       </c>
-      <c r="V31" s="99" t="n">
+      <c r="W31" s="99" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="W31" s="99" t="n">
+      <c r="X31" s="99" t="n">
         <v>76.14</v>
       </c>
-      <c r="X31" s="99" t="n">
+      <c r="Y31" s="99" t="n">
         <v>74.58</v>
       </c>
-      <c r="Y31" s="99" t="n">
+      <c r="Z31" s="99" t="n">
         <v>63.76</v>
       </c>
-      <c r="Z31" s="99" t="n">
+      <c r="AA31" s="99" t="n">
         <v>57.42</v>
       </c>
-      <c r="AA31" s="99" t="n">
+      <c r="AB31" s="99" t="n">
         <v>44.27</v>
       </c>
-      <c r="AB31" s="99" t="n">
+      <c r="AC31" s="99" t="n">
         <v>48.38</v>
       </c>
-      <c r="AC31" s="99" t="n">
+      <c r="AD31" s="99" t="n">
         <v>46.95</v>
       </c>
-      <c r="AD31" s="99" t="n">
+      <c r="AE31" s="99" t="n">
         <v>24.56</v>
-      </c>
-      <c r="AE31" s="99" t="n">
-        <v>27.77</v>
       </c>
     </row>
     <row r="32">
@@ -9803,129 +9803,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F32" s="97" t="inlineStr">
+      <c r="F32" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G32" s="96" t="inlineStr">
+      <c r="H32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H32" s="96" t="inlineStr">
+      <c r="I32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I32" s="96" t="inlineStr">
+      <c r="J32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J32" s="96" t="inlineStr">
+      <c r="K32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K32" s="96" t="inlineStr">
+      <c r="L32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L32" s="97" t="inlineStr">
+      <c r="M32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M32" s="97" t="inlineStr">
+      <c r="N32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N32" s="96" t="inlineStr">
+      <c r="O32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O32" s="96" t="inlineStr">
+      <c r="P32" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P32" s="97" t="inlineStr">
+      <c r="Q32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q32" s="97" t="inlineStr">
+      <c r="R32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R32" s="97" t="inlineStr">
+      <c r="S32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="97" t="inlineStr">
+      <c r="T32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T32" s="98" t="inlineStr">
+      <c r="U32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U32" s="98" t="inlineStr">
+      <c r="V32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V32" s="98" t="inlineStr">
+      <c r="W32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W32" s="98" t="inlineStr">
+      <c r="X32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X32" s="98" t="inlineStr">
+      <c r="Y32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y32" s="98" t="inlineStr">
+      <c r="Z32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z32" s="98" t="inlineStr">
+      <c r="AA32" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA32" s="97" t="inlineStr">
+      <c r="AB32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB32" s="97" t="inlineStr">
+      <c r="AC32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC32" s="97" t="inlineStr">
+      <c r="AD32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD32" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE32" s="96" t="inlineStr">
@@ -9941,94 +9941,94 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="C33" s="99" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D33" s="99" t="n">
         <v>-1</v>
       </c>
-      <c r="C33" s="99" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D33" s="99" t="n">
+      <c r="E33" s="99" t="n">
         <v>-1.61</v>
       </c>
-      <c r="E33" s="99" t="n">
+      <c r="F33" s="99" t="n">
         <v>-1.66</v>
       </c>
-      <c r="F33" s="99" t="n">
+      <c r="G33" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="G33" s="99" t="n">
+      <c r="H33" s="99" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H33" s="99" t="n">
+      <c r="I33" s="99" t="n">
         <v>-3.76</v>
       </c>
-      <c r="I33" s="99" t="n">
+      <c r="J33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="J33" s="99" t="n">
+      <c r="K33" s="99" t="n">
         <v>-0.28</v>
       </c>
-      <c r="K33" s="99" t="n">
+      <c r="L33" s="99" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="L33" s="99" t="n">
-        <v>3.06</v>
       </c>
       <c r="M33" s="99" t="n">
         <v>3.06</v>
       </c>
       <c r="N33" s="99" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O33" s="99" t="n">
         <v>3.91</v>
       </c>
-      <c r="O33" s="99" t="n">
+      <c r="P33" s="99" t="n">
         <v>4.32</v>
       </c>
-      <c r="P33" s="99" t="n">
+      <c r="Q33" s="99" t="n">
         <v>6.09</v>
       </c>
-      <c r="Q33" s="99" t="n">
+      <c r="R33" s="99" t="n">
         <v>5.91</v>
       </c>
-      <c r="R33" s="99" t="n">
+      <c r="S33" s="99" t="n">
         <v>5.66</v>
       </c>
-      <c r="S33" s="99" t="n">
+      <c r="T33" s="99" t="n">
         <v>3.52</v>
       </c>
-      <c r="T33" s="99" t="n">
+      <c r="U33" s="99" t="n">
         <v>5.9</v>
       </c>
-      <c r="U33" s="99" t="n">
+      <c r="V33" s="99" t="n">
         <v>6.46</v>
       </c>
-      <c r="V33" s="99" t="n">
+      <c r="W33" s="99" t="n">
         <v>6.4</v>
       </c>
-      <c r="W33" s="99" t="n">
+      <c r="X33" s="99" t="n">
         <v>4.75</v>
       </c>
-      <c r="X33" s="99" t="n">
+      <c r="Y33" s="99" t="n">
         <v>4.76</v>
       </c>
-      <c r="Y33" s="99" t="n">
+      <c r="Z33" s="99" t="n">
         <v>3.04</v>
       </c>
-      <c r="Z33" s="99" t="n">
+      <c r="AA33" s="99" t="n">
         <v>2.93</v>
       </c>
-      <c r="AA33" s="99" t="n">
+      <c r="AB33" s="99" t="n">
         <v>0.23</v>
       </c>
-      <c r="AB33" s="99" t="n">
+      <c r="AC33" s="99" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC33" s="99" t="n">
+      <c r="AD33" s="99" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD33" s="99" t="n">
+      <c r="AE33" s="99" t="n">
         <v>-0.89</v>
-      </c>
-      <c r="AE33" s="99" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="34">
@@ -10038,288 +10038,288 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="C34" s="99" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D34" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="C34" s="99" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="D34" s="99" t="n">
+      <c r="E34" s="99" t="n">
         <v>7.12</v>
       </c>
-      <c r="E34" s="99" t="n">
+      <c r="F34" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="F34" s="99" t="n">
+      <c r="G34" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="G34" s="99" t="n">
+      <c r="H34" s="99" t="n">
         <v>4.85</v>
       </c>
-      <c r="H34" s="99" t="n">
+      <c r="I34" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="I34" s="99" t="n">
+      <c r="J34" s="99" t="n">
         <v>6.19</v>
       </c>
-      <c r="J34" s="99" t="n">
+      <c r="K34" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="K34" s="99" t="n">
+      <c r="L34" s="99" t="n">
         <v>5.35</v>
-      </c>
-      <c r="L34" s="99" t="n">
-        <v>10.58</v>
       </c>
       <c r="M34" s="99" t="n">
         <v>10.58</v>
       </c>
       <c r="N34" s="99" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="O34" s="99" t="n">
         <v>8.9</v>
       </c>
-      <c r="O34" s="99" t="n">
+      <c r="P34" s="99" t="n">
         <v>7.88</v>
       </c>
-      <c r="P34" s="99" t="n">
+      <c r="Q34" s="99" t="n">
         <v>10.75</v>
       </c>
-      <c r="Q34" s="99" t="n">
+      <c r="R34" s="99" t="n">
         <v>11.21</v>
       </c>
-      <c r="R34" s="99" t="n">
+      <c r="S34" s="99" t="n">
         <v>10.31</v>
       </c>
-      <c r="S34" s="99" t="n">
+      <c r="T34" s="99" t="n">
         <v>8.26</v>
       </c>
-      <c r="T34" s="99" t="n">
+      <c r="U34" s="99" t="n">
         <v>11.35</v>
       </c>
-      <c r="U34" s="99" t="n">
+      <c r="V34" s="99" t="n">
         <v>11.72</v>
       </c>
-      <c r="V34" s="99" t="n">
+      <c r="W34" s="99" t="n">
         <v>11.48</v>
       </c>
-      <c r="W34" s="99" t="n">
+      <c r="X34" s="99" t="n">
         <v>10.36</v>
       </c>
-      <c r="X34" s="99" t="n">
+      <c r="Y34" s="99" t="n">
         <v>9.99</v>
       </c>
-      <c r="Y34" s="99" t="n">
+      <c r="Z34" s="99" t="n">
         <v>7.17</v>
       </c>
-      <c r="Z34" s="99" t="n">
+      <c r="AA34" s="99" t="n">
         <v>10.31</v>
       </c>
-      <c r="AA34" s="99" t="n">
+      <c r="AB34" s="99" t="n">
         <v>7.36</v>
       </c>
-      <c r="AB34" s="99" t="n">
+      <c r="AC34" s="99" t="n">
         <v>6.15</v>
       </c>
-      <c r="AC34" s="99" t="n">
+      <c r="AD34" s="99" t="n">
         <v>4.74</v>
       </c>
-      <c r="AD34" s="99" t="n">
+      <c r="AE34" s="99" t="n">
         <v>2.12</v>
       </c>
-      <c r="AE34" s="99" t="n">
-        <v>4.54</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="100" t="inlineStr">
+      <c r="A35" s="80" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="99" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="C35" s="99" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="D35" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="C35" s="99" t="n">
-        <v>95.17</v>
-      </c>
-      <c r="D35" s="99" t="n">
+      <c r="E35" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="E35" s="99" t="n">
+      <c r="F35" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="F35" s="99" t="n">
+      <c r="G35" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="G35" s="99" t="n">
+      <c r="H35" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="H35" s="99" t="n">
+      <c r="I35" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="I35" s="99" t="n">
+      <c r="J35" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="J35" s="99" t="n">
+      <c r="K35" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="K35" s="99" t="n">
+      <c r="L35" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="L35" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="M35" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="N35" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="O35" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="O35" s="99" t="n">
+      <c r="P35" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="P35" s="99" t="n">
+      <c r="Q35" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="Q35" s="99" t="n">
+      <c r="R35" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="R35" s="99" t="n">
+      <c r="S35" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="S35" s="99" t="n">
+      <c r="T35" s="99" t="n">
         <v>24.22</v>
       </c>
-      <c r="T35" s="99" t="n">
+      <c r="U35" s="99" t="n">
         <v>86.91</v>
       </c>
-      <c r="U35" s="99" t="n">
+      <c r="V35" s="99" t="n">
         <v>76.59</v>
       </c>
-      <c r="V35" s="99" t="n">
+      <c r="W35" s="99" t="n">
         <v>99.61</v>
       </c>
-      <c r="W35" s="99" t="n">
+      <c r="X35" s="99" t="n">
         <v>98.98999999999999</v>
       </c>
-      <c r="X35" s="99" t="n">
+      <c r="Y35" s="99" t="n">
         <v>98.84999999999999</v>
       </c>
-      <c r="Y35" s="99" t="n">
+      <c r="Z35" s="99" t="n">
         <v>95.44</v>
       </c>
-      <c r="Z35" s="99" t="n">
+      <c r="AA35" s="99" t="n">
         <v>95.36</v>
       </c>
-      <c r="AA35" s="99" t="n">
+      <c r="AB35" s="99" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="AB35" s="99" t="n">
+      <c r="AC35" s="99" t="n">
         <v>77.5</v>
       </c>
-      <c r="AC35" s="99" t="n">
+      <c r="AD35" s="99" t="n">
         <v>72.11</v>
       </c>
-      <c r="AD35" s="99" t="n">
+      <c r="AE35" s="99" t="n">
         <v>19.85</v>
       </c>
-      <c r="AE35" s="99" t="n">
-        <v>30.32</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="100" t="inlineStr">
+      <c r="A36" s="80" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="99" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="C36" s="99" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="D36" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="C36" s="99" t="n">
-        <v>95.17</v>
-      </c>
-      <c r="D36" s="99" t="n">
+      <c r="E36" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="E36" s="99" t="n">
+      <c r="F36" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="F36" s="99" t="n">
+      <c r="G36" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="G36" s="99" t="n">
+      <c r="H36" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="H36" s="99" t="n">
+      <c r="I36" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="I36" s="99" t="n">
+      <c r="J36" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="J36" s="99" t="n">
+      <c r="K36" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="K36" s="99" t="n">
+      <c r="L36" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="L36" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="M36" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="N36" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="O36" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="O36" s="99" t="n">
+      <c r="P36" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="P36" s="99" t="n">
+      <c r="Q36" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="Q36" s="99" t="n">
+      <c r="R36" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="R36" s="99" t="n">
+      <c r="S36" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="S36" s="99" t="n">
+      <c r="T36" s="99" t="n">
         <v>24.22</v>
       </c>
-      <c r="T36" s="99" t="n">
+      <c r="U36" s="99" t="n">
         <v>86.91</v>
       </c>
-      <c r="U36" s="99" t="n">
+      <c r="V36" s="99" t="n">
         <v>76.59</v>
       </c>
-      <c r="V36" s="99" t="n">
+      <c r="W36" s="99" t="n">
         <v>99.61</v>
       </c>
-      <c r="W36" s="99" t="n">
+      <c r="X36" s="99" t="n">
         <v>98.98999999999999</v>
       </c>
-      <c r="X36" s="99" t="n">
+      <c r="Y36" s="99" t="n">
         <v>98.84999999999999</v>
       </c>
-      <c r="Y36" s="99" t="n">
+      <c r="Z36" s="99" t="n">
         <v>95.44</v>
       </c>
-      <c r="Z36" s="99" t="n">
+      <c r="AA36" s="99" t="n">
         <v>95.36</v>
       </c>
-      <c r="AA36" s="99" t="n">
+      <c r="AB36" s="99" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="AB36" s="99" t="n">
+      <c r="AC36" s="99" t="n">
         <v>77.5</v>
       </c>
-      <c r="AC36" s="99" t="n">
+      <c r="AD36" s="99" t="n">
         <v>72.11</v>
       </c>
-      <c r="AD36" s="99" t="n">
+      <c r="AE36" s="99" t="n">
         <v>19.85</v>
-      </c>
-      <c r="AE36" s="99" t="n">
-        <v>30.32</v>
       </c>
     </row>
     <row r="37">
@@ -10343,119 +10343,119 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E37" s="96" t="inlineStr">
+      <c r="E37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F37" s="96" t="inlineStr">
+      <c r="G37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G37" s="96" t="inlineStr">
+      <c r="H37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H37" s="96" t="inlineStr">
+      <c r="I37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I37" s="96" t="inlineStr">
+      <c r="J37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J37" s="96" t="inlineStr">
+      <c r="K37" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K37" s="97" t="inlineStr">
+      <c r="L37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L37" s="97" t="inlineStr">
+      <c r="M37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M37" s="97" t="inlineStr">
+      <c r="N37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N37" s="97" t="inlineStr">
+      <c r="O37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="97" t="inlineStr">
+      <c r="P37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P37" s="97" t="inlineStr">
+      <c r="Q37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q37" s="97" t="inlineStr">
+      <c r="R37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R37" s="98" t="inlineStr">
+      <c r="S37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S37" s="98" t="inlineStr">
+      <c r="T37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T37" s="98" t="inlineStr">
+      <c r="U37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U37" s="98" t="inlineStr">
+      <c r="V37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V37" s="98" t="inlineStr">
+      <c r="W37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W37" s="98" t="inlineStr">
+      <c r="X37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X37" s="98" t="inlineStr">
+      <c r="Y37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y37" s="98" t="inlineStr">
+      <c r="Z37" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z37" s="98" t="inlineStr">
+      <c r="AA37" s="98" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA37" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AB37" s="97" t="inlineStr">
@@ -10486,94 +10486,94 @@
         </is>
       </c>
       <c r="B38" s="99" t="n">
-        <v>-5.31</v>
+        <v>-6.2</v>
       </c>
       <c r="C38" s="99" t="n">
         <v>-5.31</v>
       </c>
       <c r="D38" s="99" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="E38" s="99" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E38" s="99" t="n">
+      <c r="F38" s="99" t="n">
         <v>-7.44</v>
       </c>
-      <c r="F38" s="99" t="n">
+      <c r="G38" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G38" s="99" t="n">
+      <c r="H38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H38" s="99" t="n">
+      <c r="I38" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="I38" s="99" t="n">
+      <c r="J38" s="99" t="n">
         <v>-5.71</v>
       </c>
-      <c r="J38" s="99" t="n">
+      <c r="K38" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="K38" s="99" t="n">
+      <c r="L38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="L38" s="99" t="n">
+      <c r="M38" s="99" t="n">
         <v>0.04</v>
       </c>
-      <c r="M38" s="99" t="n">
+      <c r="N38" s="99" t="n">
         <v>-0.14</v>
       </c>
-      <c r="N38" s="99" t="n">
+      <c r="O38" s="99" t="n">
         <v>-0.33</v>
       </c>
-      <c r="O38" s="99" t="n">
+      <c r="P38" s="99" t="n">
         <v>-1.2</v>
       </c>
-      <c r="P38" s="99" t="n">
+      <c r="Q38" s="99" t="n">
         <v>-1.63</v>
       </c>
-      <c r="Q38" s="99" t="n">
+      <c r="R38" s="99" t="n">
         <v>-0.98</v>
       </c>
-      <c r="R38" s="99" t="n">
+      <c r="S38" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="S38" s="99" t="n">
+      <c r="T38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="T38" s="99" t="n">
+      <c r="U38" s="99" t="n">
         <v>-2.33</v>
       </c>
-      <c r="U38" s="99" t="n">
+      <c r="V38" s="99" t="n">
         <v>-2.15</v>
       </c>
-      <c r="V38" s="99" t="n">
+      <c r="W38" s="99" t="n">
         <v>-3.25</v>
       </c>
-      <c r="W38" s="99" t="n">
+      <c r="X38" s="99" t="n">
         <v>-2.66</v>
       </c>
-      <c r="X38" s="99" t="n">
+      <c r="Y38" s="99" t="n">
         <v>-4.9</v>
       </c>
-      <c r="Y38" s="99" t="n">
+      <c r="Z38" s="99" t="n">
         <v>-6.43</v>
       </c>
-      <c r="Z38" s="99" t="n">
+      <c r="AA38" s="99" t="n">
         <v>-7.26</v>
       </c>
-      <c r="AA38" s="99" t="n">
+      <c r="AB38" s="99" t="n">
         <v>-9.76</v>
       </c>
-      <c r="AB38" s="99" t="n">
+      <c r="AC38" s="99" t="n">
         <v>-10.01</v>
       </c>
-      <c r="AC38" s="99" t="n">
+      <c r="AD38" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="AD38" s="99" t="n">
+      <c r="AE38" s="99" t="n">
         <v>-8.52</v>
-      </c>
-      <c r="AE38" s="99" t="n">
-        <v>-9.18</v>
       </c>
     </row>
     <row r="39">
@@ -10583,94 +10583,94 @@
         </is>
       </c>
       <c r="B39" s="99" t="n">
-        <v>-9.48</v>
+        <v>-10.38</v>
       </c>
       <c r="C39" s="99" t="n">
         <v>-9.48</v>
       </c>
       <c r="D39" s="99" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="E39" s="99" t="n">
         <v>-9.92</v>
       </c>
-      <c r="E39" s="99" t="n">
+      <c r="F39" s="99" t="n">
         <v>-12.73</v>
       </c>
-      <c r="F39" s="99" t="n">
+      <c r="G39" s="99" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="G39" s="99" t="n">
+      <c r="H39" s="99" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="H39" s="99" t="n">
+      <c r="I39" s="99" t="n">
         <v>-5.98</v>
       </c>
-      <c r="I39" s="99" t="n">
+      <c r="J39" s="99" t="n">
         <v>-5.54</v>
       </c>
-      <c r="J39" s="99" t="n">
+      <c r="K39" s="99" t="n">
         <v>-4.26</v>
       </c>
-      <c r="K39" s="99" t="n">
+      <c r="L39" s="99" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L39" s="99" t="n">
+      <c r="M39" s="99" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M39" s="99" t="n">
+      <c r="N39" s="99" t="n">
         <v>-2.62</v>
       </c>
-      <c r="N39" s="99" t="n">
+      <c r="O39" s="99" t="n">
         <v>-3.12</v>
       </c>
-      <c r="O39" s="99" t="n">
+      <c r="P39" s="99" t="n">
         <v>-4.29</v>
       </c>
-      <c r="P39" s="99" t="n">
+      <c r="Q39" s="99" t="n">
         <v>-4.51</v>
       </c>
-      <c r="Q39" s="99" t="n">
+      <c r="R39" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="R39" s="99" t="n">
+      <c r="S39" s="99" t="n">
         <v>-3.88</v>
       </c>
-      <c r="S39" s="99" t="n">
+      <c r="T39" s="99" t="n">
         <v>-2.44</v>
       </c>
-      <c r="T39" s="99" t="n">
+      <c r="U39" s="99" t="n">
         <v>-3.2</v>
       </c>
-      <c r="U39" s="99" t="n">
+      <c r="V39" s="99" t="n">
         <v>-3</v>
       </c>
-      <c r="V39" s="99" t="n">
+      <c r="W39" s="99" t="n">
         <v>-4.7</v>
       </c>
-      <c r="W39" s="99" t="n">
+      <c r="X39" s="99" t="n">
         <v>-2.65</v>
       </c>
-      <c r="X39" s="99" t="n">
+      <c r="Y39" s="99" t="n">
         <v>-4.01</v>
       </c>
-      <c r="Y39" s="99" t="n">
+      <c r="Z39" s="99" t="n">
         <v>-5.01</v>
       </c>
-      <c r="Z39" s="99" t="n">
+      <c r="AA39" s="99" t="n">
         <v>-5.82</v>
       </c>
-      <c r="AA39" s="99" t="n">
+      <c r="AB39" s="99" t="n">
         <v>-9.050000000000001</v>
       </c>
-      <c r="AB39" s="99" t="n">
+      <c r="AC39" s="99" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="AC39" s="99" t="n">
+      <c r="AD39" s="99" t="n">
         <v>-7.62</v>
       </c>
-      <c r="AD39" s="99" t="n">
+      <c r="AE39" s="99" t="n">
         <v>-7.57</v>
-      </c>
-      <c r="AE39" s="99" t="n">
-        <v>-6.02</v>
       </c>
     </row>
     <row r="40">
@@ -10680,94 +10680,94 @@
         </is>
       </c>
       <c r="B40" s="99" t="n">
-        <v>46.07</v>
+        <v>38.36</v>
       </c>
       <c r="C40" s="99" t="n">
         <v>46.07</v>
       </c>
       <c r="D40" s="99" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="E40" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="E40" s="99" t="n">
+      <c r="F40" s="99" t="n">
         <v>10.06</v>
       </c>
-      <c r="F40" s="99" t="n">
+      <c r="G40" s="99" t="n">
         <v>14.47</v>
       </c>
-      <c r="G40" s="99" t="n">
+      <c r="H40" s="99" t="n">
         <v>15.02</v>
       </c>
-      <c r="H40" s="99" t="n">
+      <c r="I40" s="99" t="n">
         <v>16.6</v>
       </c>
-      <c r="I40" s="99" t="n">
+      <c r="J40" s="99" t="n">
         <v>19.01</v>
       </c>
-      <c r="J40" s="99" t="n">
+      <c r="K40" s="99" t="n">
         <v>22.94</v>
       </c>
-      <c r="K40" s="99" t="n">
+      <c r="L40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="L40" s="99" t="n">
+      <c r="M40" s="99" t="n">
         <v>75.7</v>
       </c>
-      <c r="M40" s="99" t="n">
+      <c r="N40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="N40" s="99" t="n">
+      <c r="O40" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="O40" s="99" t="n">
+      <c r="P40" s="99" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="P40" s="99" t="n">
+      <c r="Q40" s="99" t="n">
         <v>66.31999999999999</v>
       </c>
-      <c r="Q40" s="99" t="n">
+      <c r="R40" s="99" t="n">
         <v>62.89</v>
       </c>
-      <c r="R40" s="99" t="n">
+      <c r="S40" s="99" t="n">
         <v>71.14</v>
       </c>
-      <c r="S40" s="99" t="n">
+      <c r="T40" s="99" t="n">
         <v>69.19</v>
       </c>
-      <c r="T40" s="99" t="n">
+      <c r="U40" s="99" t="n">
         <v>66.09</v>
       </c>
-      <c r="U40" s="99" t="n">
+      <c r="V40" s="99" t="n">
         <v>68.45</v>
       </c>
-      <c r="V40" s="99" t="n">
+      <c r="W40" s="99" t="n">
         <v>61.83</v>
       </c>
-      <c r="W40" s="99" t="n">
+      <c r="X40" s="99" t="n">
         <v>74.31</v>
       </c>
-      <c r="X40" s="99" t="n">
+      <c r="Y40" s="99" t="n">
         <v>62.22</v>
       </c>
-      <c r="Y40" s="99" t="n">
+      <c r="Z40" s="99" t="n">
         <v>58.92</v>
       </c>
-      <c r="Z40" s="99" t="n">
+      <c r="AA40" s="99" t="n">
         <v>56.7</v>
       </c>
-      <c r="AA40" s="99" t="n">
+      <c r="AB40" s="99" t="n">
         <v>41.93</v>
       </c>
-      <c r="AB40" s="99" t="n">
+      <c r="AC40" s="99" t="n">
         <v>42.14</v>
       </c>
-      <c r="AC40" s="99" t="n">
+      <c r="AD40" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="AD40" s="99" t="n">
+      <c r="AE40" s="99" t="n">
         <v>41.66</v>
-      </c>
-      <c r="AE40" s="99" t="n">
-        <v>38.53</v>
       </c>
     </row>
     <row r="41">
@@ -10777,94 +10777,94 @@
         </is>
       </c>
       <c r="B41" s="99" t="n">
-        <v>43.96</v>
+        <v>39.87</v>
       </c>
       <c r="C41" s="99" t="n">
         <v>43.96</v>
       </c>
       <c r="D41" s="99" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="E41" s="99" t="n">
         <v>46.79</v>
       </c>
-      <c r="E41" s="99" t="n">
+      <c r="F41" s="99" t="n">
         <v>26.47</v>
       </c>
-      <c r="F41" s="99" t="n">
+      <c r="G41" s="99" t="n">
         <v>31.18</v>
       </c>
-      <c r="G41" s="99" t="n">
+      <c r="H41" s="99" t="n">
         <v>31.7</v>
       </c>
-      <c r="H41" s="99" t="n">
+      <c r="I41" s="99" t="n">
         <v>33.25</v>
       </c>
-      <c r="I41" s="99" t="n">
+      <c r="J41" s="99" t="n">
         <v>35.58</v>
       </c>
-      <c r="J41" s="99" t="n">
+      <c r="K41" s="99" t="n">
         <v>39.17</v>
       </c>
-      <c r="K41" s="99" t="n">
+      <c r="L41" s="99" t="n">
         <v>62.79</v>
       </c>
-      <c r="L41" s="99" t="n">
+      <c r="M41" s="99" t="n">
         <v>63.09</v>
       </c>
-      <c r="M41" s="99" t="n">
+      <c r="N41" s="99" t="n">
         <v>62.51</v>
       </c>
-      <c r="N41" s="99" t="n">
+      <c r="O41" s="99" t="n">
         <v>59.46</v>
       </c>
-      <c r="O41" s="99" t="n">
+      <c r="P41" s="99" t="n">
         <v>59.6</v>
       </c>
-      <c r="P41" s="99" t="n">
+      <c r="Q41" s="99" t="n">
         <v>58.83</v>
       </c>
-      <c r="Q41" s="99" t="n">
+      <c r="R41" s="99" t="n">
         <v>57.26</v>
       </c>
-      <c r="R41" s="99" t="n">
+      <c r="S41" s="99" t="n">
         <v>60.15</v>
       </c>
-      <c r="S41" s="99" t="n">
+      <c r="T41" s="99" t="n">
         <v>59.04</v>
       </c>
-      <c r="T41" s="99" t="n">
+      <c r="U41" s="99" t="n">
         <v>57.26</v>
       </c>
-      <c r="U41" s="99" t="n">
+      <c r="V41" s="99" t="n">
         <v>58.23</v>
       </c>
-      <c r="V41" s="99" t="n">
+      <c r="W41" s="99" t="n">
         <v>54.04</v>
       </c>
-      <c r="W41" s="99" t="n">
+      <c r="X41" s="99" t="n">
         <v>59.32</v>
       </c>
-      <c r="X41" s="99" t="n">
+      <c r="Y41" s="99" t="n">
         <v>50.86</v>
       </c>
-      <c r="Y41" s="99" t="n">
+      <c r="Z41" s="99" t="n">
         <v>48.85</v>
       </c>
-      <c r="Z41" s="99" t="n">
+      <c r="AA41" s="99" t="n">
         <v>47.43</v>
       </c>
-      <c r="AA41" s="99" t="n">
+      <c r="AB41" s="99" t="n">
         <v>38.6</v>
       </c>
-      <c r="AB41" s="99" t="n">
+      <c r="AC41" s="99" t="n">
         <v>38.7</v>
       </c>
-      <c r="AC41" s="99" t="n">
+      <c r="AD41" s="99" t="n">
         <v>37.39</v>
       </c>
-      <c r="AD41" s="99" t="n">
+      <c r="AE41" s="99" t="n">
         <v>38.36</v>
-      </c>
-      <c r="AE41" s="99" t="n">
-        <v>35.99</v>
       </c>
     </row>
     <row r="42">
@@ -10873,139 +10873,139 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="96" t="inlineStr">
+      <c r="B42" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="96" t="inlineStr">
+      <c r="D42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="96" t="inlineStr">
+      <c r="E42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="96" t="inlineStr">
+      <c r="F42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="96" t="inlineStr">
+      <c r="G42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="96" t="inlineStr">
+      <c r="H42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="97" t="inlineStr">
+      <c r="I42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I42" s="96" t="inlineStr">
+      <c r="J42" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="97" t="inlineStr">
+      <c r="K42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K42" s="97" t="inlineStr">
+      <c r="L42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="97" t="inlineStr">
+      <c r="M42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="97" t="inlineStr">
+      <c r="N42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="97" t="inlineStr">
+      <c r="O42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="97" t="inlineStr">
+      <c r="P42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="97" t="inlineStr">
+      <c r="Q42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="97" t="inlineStr">
+      <c r="R42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="98" t="inlineStr">
+      <c r="S42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="98" t="inlineStr">
+      <c r="T42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="98" t="inlineStr">
+      <c r="U42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="98" t="inlineStr">
+      <c r="V42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V42" s="98" t="inlineStr">
+      <c r="W42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W42" s="98" t="inlineStr">
+      <c r="X42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="97" t="inlineStr">
+      <c r="Y42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="98" t="inlineStr">
+      <c r="Z42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="98" t="inlineStr">
+      <c r="AA42" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="98" t="inlineStr">
+      <c r="AB42" s="98" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AB42" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AC42" s="97" t="inlineStr">
@@ -11031,34 +11031,34 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="C43" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="C43" s="99" t="n">
+      <c r="D43" s="99" t="n">
         <v>-2.39</v>
       </c>
-      <c r="D43" s="99" t="n">
+      <c r="E43" s="99" t="n">
         <v>-1.83</v>
       </c>
-      <c r="E43" s="99" t="n">
+      <c r="F43" s="99" t="n">
         <v>-2.05</v>
       </c>
-      <c r="F43" s="99" t="n">
+      <c r="G43" s="99" t="n">
         <v>-1.53</v>
       </c>
-      <c r="G43" s="99" t="n">
+      <c r="H43" s="99" t="n">
         <v>-0.95</v>
       </c>
-      <c r="H43" s="99" t="n">
+      <c r="I43" s="99" t="n">
         <v>-2.12</v>
       </c>
-      <c r="I43" s="99" t="n">
+      <c r="J43" s="99" t="n">
         <v>-2.46</v>
       </c>
-      <c r="J43" s="99" t="n">
+      <c r="K43" s="99" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="K43" s="99" t="n">
-        <v>-0.53</v>
       </c>
       <c r="L43" s="99" t="n">
         <v>-0.53</v>
@@ -11067,58 +11067,58 @@
         <v>-0.53</v>
       </c>
       <c r="N43" s="99" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="O43" s="99" t="n">
         <v>-0.47</v>
       </c>
-      <c r="O43" s="99" t="n">
+      <c r="P43" s="99" t="n">
         <v>-0.17</v>
       </c>
-      <c r="P43" s="99" t="n">
+      <c r="Q43" s="99" t="n">
         <v>-0.3</v>
       </c>
-      <c r="Q43" s="99" t="n">
+      <c r="R43" s="99" t="n">
         <v>-0.27</v>
       </c>
-      <c r="R43" s="99" t="n">
+      <c r="S43" s="99" t="n">
         <v>0.42</v>
       </c>
-      <c r="S43" s="99" t="n">
+      <c r="T43" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="T43" s="99" t="n">
+      <c r="U43" s="99" t="n">
         <v>1.4</v>
       </c>
-      <c r="U43" s="99" t="n">
+      <c r="V43" s="99" t="n">
         <v>-0.01</v>
       </c>
-      <c r="V43" s="99" t="n">
+      <c r="W43" s="99" t="n">
         <v>-1.57</v>
       </c>
-      <c r="W43" s="99" t="n">
+      <c r="X43" s="99" t="n">
         <v>-1.22</v>
       </c>
-      <c r="X43" s="99" t="n">
+      <c r="Y43" s="99" t="n">
         <v>-3.04</v>
       </c>
-      <c r="Y43" s="99" t="n">
+      <c r="Z43" s="99" t="n">
         <v>-3.96</v>
       </c>
-      <c r="Z43" s="99" t="n">
+      <c r="AA43" s="99" t="n">
         <v>-2.88</v>
       </c>
-      <c r="AA43" s="99" t="n">
+      <c r="AB43" s="99" t="n">
         <v>-3.67</v>
       </c>
-      <c r="AB43" s="99" t="n">
+      <c r="AC43" s="99" t="n">
         <v>-4.22</v>
       </c>
-      <c r="AC43" s="99" t="n">
+      <c r="AD43" s="99" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AD43" s="99" t="n">
+      <c r="AE43" s="99" t="n">
         <v>-4.17</v>
-      </c>
-      <c r="AE43" s="99" t="n">
-        <v>-3.52</v>
       </c>
     </row>
     <row r="44">
@@ -11128,34 +11128,34 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="C44" s="99" t="n">
         <v>-2.26</v>
       </c>
-      <c r="C44" s="99" t="n">
+      <c r="D44" s="99" t="n">
         <v>-2.35</v>
       </c>
-      <c r="D44" s="99" t="n">
+      <c r="E44" s="99" t="n">
         <v>-1.57</v>
       </c>
-      <c r="E44" s="99" t="n">
+      <c r="F44" s="99" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F44" s="99" t="n">
+      <c r="G44" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="G44" s="99" t="n">
+      <c r="H44" s="99" t="n">
         <v>1.94</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="I44" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I44" s="99" t="n">
+      <c r="J44" s="99" t="n">
         <v>0.31</v>
       </c>
-      <c r="J44" s="99" t="n">
+      <c r="K44" s="99" t="n">
         <v>0.42</v>
-      </c>
-      <c r="K44" s="99" t="n">
-        <v>3.12</v>
       </c>
       <c r="L44" s="99" t="n">
         <v>3.12</v>
@@ -11164,95 +11164,95 @@
         <v>3.12</v>
       </c>
       <c r="N44" s="99" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O44" s="99" t="n">
         <v>3.72</v>
       </c>
-      <c r="O44" s="99" t="n">
+      <c r="P44" s="99" t="n">
         <v>2.73</v>
       </c>
-      <c r="P44" s="99" t="n">
+      <c r="Q44" s="99" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q44" s="99" t="n">
+      <c r="R44" s="99" t="n">
         <v>1.37</v>
       </c>
-      <c r="R44" s="99" t="n">
+      <c r="S44" s="99" t="n">
         <v>1.21</v>
       </c>
-      <c r="S44" s="99" t="n">
+      <c r="T44" s="99" t="n">
         <v>1.69</v>
       </c>
-      <c r="T44" s="99" t="n">
+      <c r="U44" s="99" t="n">
         <v>2.05</v>
       </c>
-      <c r="U44" s="99" t="n">
+      <c r="V44" s="99" t="n">
         <v>1.58</v>
       </c>
-      <c r="V44" s="99" t="n">
+      <c r="W44" s="99" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="W44" s="99" t="n">
+      <c r="X44" s="99" t="n">
         <v>1.19</v>
       </c>
-      <c r="X44" s="99" t="n">
+      <c r="Y44" s="99" t="n">
         <v>-0.05</v>
       </c>
-      <c r="Y44" s="99" t="n">
+      <c r="Z44" s="99" t="n">
         <v>1.51</v>
       </c>
-      <c r="Z44" s="99" t="n">
+      <c r="AA44" s="99" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA44" s="99" t="n">
+      <c r="AB44" s="99" t="n">
         <v>0.02</v>
       </c>
-      <c r="AB44" s="99" t="n">
+      <c r="AC44" s="99" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AC44" s="99" t="n">
+      <c r="AD44" s="99" t="n">
         <v>-1.36</v>
       </c>
-      <c r="AD44" s="99" t="n">
+      <c r="AE44" s="99" t="n">
         <v>0.51</v>
       </c>
-      <c r="AE44" s="99" t="n">
-        <v>0.65</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="87" t="inlineStr">
+      <c r="A45" s="80" t="inlineStr">
         <is>
           <t>vn:RSI3</t>
         </is>
       </c>
       <c r="B45" s="99" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="C45" s="99" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="C45" s="99" t="n">
+      <c r="D45" s="99" t="n">
         <v>20.58</v>
       </c>
-      <c r="D45" s="99" t="n">
+      <c r="E45" s="99" t="n">
         <v>30.12</v>
       </c>
-      <c r="E45" s="99" t="n">
+      <c r="F45" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="F45" s="99" t="n">
+      <c r="G45" s="99" t="n">
         <v>13.57</v>
       </c>
-      <c r="G45" s="99" t="n">
+      <c r="H45" s="99" t="n">
         <v>28.44</v>
       </c>
-      <c r="H45" s="99" t="n">
+      <c r="I45" s="99" t="n">
         <v>44.72</v>
       </c>
-      <c r="I45" s="99" t="n">
+      <c r="J45" s="99" t="n">
         <v>14.66</v>
       </c>
-      <c r="J45" s="99" t="n">
+      <c r="K45" s="99" t="n">
         <v>28.1</v>
-      </c>
-      <c r="K45" s="99" t="n">
-        <v>80.38</v>
       </c>
       <c r="L45" s="99" t="n">
         <v>80.38</v>
@@ -11261,58 +11261,58 @@
         <v>80.38</v>
       </c>
       <c r="N45" s="99" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="O45" s="99" t="n">
         <v>68.92</v>
       </c>
-      <c r="O45" s="99" t="n">
+      <c r="P45" s="99" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="P45" s="99" t="n">
+      <c r="Q45" s="99" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="Q45" s="99" t="n">
+      <c r="R45" s="99" t="n">
         <v>63.9</v>
       </c>
-      <c r="R45" s="99" t="n">
+      <c r="S45" s="99" t="n">
         <v>90.77</v>
       </c>
-      <c r="S45" s="99" t="n">
+      <c r="T45" s="99" t="n">
         <v>89.34</v>
       </c>
-      <c r="T45" s="99" t="n">
+      <c r="U45" s="99" t="n">
         <v>94.22</v>
       </c>
-      <c r="U45" s="99" t="n">
+      <c r="V45" s="99" t="n">
         <v>91.38</v>
       </c>
-      <c r="V45" s="99" t="n">
+      <c r="W45" s="99" t="n">
         <v>87.48</v>
       </c>
-      <c r="W45" s="99" t="n">
+      <c r="X45" s="99" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="X45" s="99" t="n">
+      <c r="Y45" s="99" t="n">
         <v>41.47</v>
       </c>
-      <c r="Y45" s="99" t="n">
+      <c r="Z45" s="99" t="n">
         <v>67.94</v>
       </c>
-      <c r="Z45" s="99" t="n">
+      <c r="AA45" s="99" t="n">
         <v>68.19</v>
       </c>
-      <c r="AA45" s="99" t="n">
+      <c r="AB45" s="99" t="n">
         <v>68.01000000000001</v>
       </c>
-      <c r="AB45" s="99" t="n">
+      <c r="AC45" s="99" t="n">
         <v>60.67</v>
       </c>
-      <c r="AC45" s="99" t="n">
+      <c r="AD45" s="99" t="n">
         <v>39.27</v>
       </c>
-      <c r="AD45" s="99" t="n">
+      <c r="AE45" s="99" t="n">
         <v>47.83</v>
-      </c>
-      <c r="AE45" s="99" t="n">
-        <v>41.53</v>
       </c>
     </row>
     <row r="46">
@@ -11322,34 +11322,34 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="C46" s="99" t="n">
         <v>16.23</v>
       </c>
-      <c r="C46" s="99" t="n">
+      <c r="D46" s="99" t="n">
         <v>25.94</v>
       </c>
-      <c r="D46" s="99" t="n">
+      <c r="E46" s="99" t="n">
         <v>31.58</v>
       </c>
-      <c r="E46" s="99" t="n">
+      <c r="F46" s="99" t="n">
         <v>22.65</v>
       </c>
-      <c r="F46" s="99" t="n">
+      <c r="G46" s="99" t="n">
         <v>24.26</v>
       </c>
-      <c r="G46" s="99" t="n">
+      <c r="H46" s="99" t="n">
         <v>38.08</v>
       </c>
-      <c r="H46" s="99" t="n">
+      <c r="I46" s="99" t="n">
         <v>49.25</v>
       </c>
-      <c r="I46" s="99" t="n">
+      <c r="J46" s="99" t="n">
         <v>35.21</v>
       </c>
-      <c r="J46" s="99" t="n">
+      <c r="K46" s="99" t="n">
         <v>49.75</v>
-      </c>
-      <c r="K46" s="99" t="n">
-        <v>76.69</v>
       </c>
       <c r="L46" s="99" t="n">
         <v>76.69</v>
@@ -11358,58 +11358,58 @@
         <v>76.69</v>
       </c>
       <c r="N46" s="99" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="O46" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="O46" s="99" t="n">
+      <c r="P46" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="P46" s="99" t="n">
+      <c r="Q46" s="99" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="Q46" s="99" t="n">
+      <c r="R46" s="99" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="R46" s="99" t="n">
+      <c r="S46" s="99" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="S46" s="99" t="n">
+      <c r="T46" s="99" t="n">
         <v>82.43000000000001</v>
       </c>
-      <c r="T46" s="99" t="n">
+      <c r="U46" s="99" t="n">
         <v>84.70999999999999</v>
       </c>
-      <c r="U46" s="99" t="n">
+      <c r="V46" s="99" t="n">
         <v>80.88</v>
       </c>
-      <c r="V46" s="99" t="n">
+      <c r="W46" s="99" t="n">
         <v>76.37</v>
       </c>
-      <c r="W46" s="99" t="n">
+      <c r="X46" s="99" t="n">
         <v>71.81</v>
       </c>
-      <c r="X46" s="99" t="n">
+      <c r="Y46" s="99" t="n">
         <v>46.62</v>
       </c>
-      <c r="Y46" s="99" t="n">
+      <c r="Z46" s="99" t="n">
         <v>56.14</v>
       </c>
-      <c r="Z46" s="99" t="n">
+      <c r="AA46" s="99" t="n">
         <v>56.22</v>
       </c>
-      <c r="AA46" s="99" t="n">
+      <c r="AB46" s="99" t="n">
         <v>56.1</v>
       </c>
-      <c r="AB46" s="99" t="n">
+      <c r="AC46" s="99" t="n">
         <v>51.09</v>
       </c>
-      <c r="AC46" s="99" t="n">
+      <c r="AD46" s="99" t="n">
         <v>38.03</v>
       </c>
-      <c r="AD46" s="99" t="n">
+      <c r="AE46" s="99" t="n">
         <v>42.52</v>
-      </c>
-      <c r="AE46" s="99" t="n">
-        <v>38.2</v>
       </c>
     </row>
     <row r="47">
@@ -11433,129 +11433,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E47" s="96" t="inlineStr">
+      <c r="E47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F47" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F47" s="97" t="inlineStr">
+      <c r="G47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G47" s="96" t="inlineStr">
+      <c r="H47" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H47" s="96" t="inlineStr">
+      <c r="I47" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I47" s="97" t="inlineStr">
+      <c r="J47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J47" s="97" t="inlineStr">
+      <c r="K47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K47" s="97" t="inlineStr">
+      <c r="L47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L47" s="98" t="inlineStr">
+      <c r="M47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M47" s="98" t="inlineStr">
+      <c r="N47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="98" t="inlineStr">
+      <c r="O47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="98" t="inlineStr">
+      <c r="P47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P47" s="98" t="inlineStr">
+      <c r="Q47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q47" s="98" t="inlineStr">
+      <c r="R47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R47" s="98" t="inlineStr">
+      <c r="S47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S47" s="98" t="inlineStr">
+      <c r="T47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T47" s="98" t="inlineStr">
+      <c r="U47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U47" s="98" t="inlineStr">
+      <c r="V47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V47" s="98" t="inlineStr">
+      <c r="W47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W47" s="98" t="inlineStr">
+      <c r="X47" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X47" s="97" t="inlineStr">
+      <c r="Y47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y47" s="97" t="inlineStr">
+      <c r="Z47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z47" s="96" t="inlineStr">
+      <c r="AA47" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA47" s="97" t="inlineStr">
+      <c r="AB47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB47" s="97" t="inlineStr">
+      <c r="AC47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC47" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD47" s="96" t="inlineStr">
@@ -11576,94 +11576,94 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="C48" s="99" t="n">
         <v>7.48</v>
       </c>
-      <c r="C48" s="99" t="n">
+      <c r="D48" s="99" t="n">
         <v>6.99</v>
       </c>
-      <c r="D48" s="99" t="n">
+      <c r="E48" s="99" t="n">
         <v>7.27</v>
       </c>
-      <c r="E48" s="99" t="n">
+      <c r="F48" s="99" t="n">
         <v>5.46</v>
       </c>
-      <c r="F48" s="99" t="n">
+      <c r="G48" s="99" t="n">
         <v>6.4</v>
       </c>
-      <c r="G48" s="99" t="n">
+      <c r="H48" s="99" t="n">
         <v>6.18</v>
       </c>
-      <c r="H48" s="99" t="n">
+      <c r="I48" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="I48" s="99" t="n">
+      <c r="J48" s="99" t="n">
         <v>7.51</v>
       </c>
-      <c r="J48" s="99" t="n">
+      <c r="K48" s="99" t="n">
         <v>7.66</v>
       </c>
-      <c r="K48" s="99" t="n">
+      <c r="L48" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="L48" s="99" t="n">
+      <c r="M48" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="M48" s="99" t="n">
+      <c r="N48" s="99" t="n">
         <v>10.73</v>
       </c>
-      <c r="N48" s="99" t="n">
+      <c r="O48" s="99" t="n">
         <v>13.93</v>
       </c>
-      <c r="O48" s="99" t="n">
+      <c r="P48" s="99" t="n">
         <v>6.94</v>
       </c>
-      <c r="P48" s="99" t="n">
+      <c r="Q48" s="99" t="n">
         <v>10.46</v>
       </c>
-      <c r="Q48" s="99" t="n">
+      <c r="R48" s="99" t="n">
         <v>10.57</v>
       </c>
-      <c r="R48" s="99" t="n">
+      <c r="S48" s="99" t="n">
         <v>8.82</v>
       </c>
-      <c r="S48" s="99" t="n">
+      <c r="T48" s="99" t="n">
         <v>7.83</v>
       </c>
-      <c r="T48" s="99" t="n">
+      <c r="U48" s="99" t="n">
         <v>7.31</v>
       </c>
-      <c r="U48" s="99" t="n">
+      <c r="V48" s="99" t="n">
         <v>7.14</v>
       </c>
-      <c r="V48" s="99" t="n">
+      <c r="W48" s="99" t="n">
         <v>6.62</v>
       </c>
-      <c r="W48" s="99" t="n">
+      <c r="X48" s="99" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="X48" s="99" t="n">
+      <c r="Y48" s="99" t="n">
         <v>6.95</v>
       </c>
-      <c r="Y48" s="99" t="n">
+      <c r="Z48" s="99" t="n">
         <v>6.89</v>
       </c>
-      <c r="Z48" s="99" t="n">
+      <c r="AA48" s="99" t="n">
         <v>6.8</v>
       </c>
-      <c r="AA48" s="99" t="n">
+      <c r="AB48" s="99" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="AB48" s="99" t="n">
+      <c r="AC48" s="99" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="AC48" s="99" t="n">
+      <c r="AD48" s="99" t="n">
         <v>7.91</v>
       </c>
-      <c r="AD48" s="99" t="n">
+      <c r="AE48" s="99" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AE48" s="99" t="n">
-        <v>8.16</v>
       </c>
     </row>
     <row r="49">
@@ -11673,94 +11673,94 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="C49" s="99" t="n">
         <v>14.24</v>
       </c>
-      <c r="C49" s="99" t="n">
+      <c r="D49" s="99" t="n">
         <v>14.96</v>
       </c>
-      <c r="D49" s="99" t="n">
+      <c r="E49" s="99" t="n">
         <v>15.21</v>
       </c>
-      <c r="E49" s="99" t="n">
+      <c r="F49" s="99" t="n">
         <v>12.06</v>
       </c>
-      <c r="F49" s="99" t="n">
+      <c r="G49" s="99" t="n">
         <v>12.77</v>
       </c>
-      <c r="G49" s="99" t="n">
+      <c r="H49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="H49" s="99" t="n">
+      <c r="I49" s="99" t="n">
         <v>11.57</v>
       </c>
-      <c r="I49" s="99" t="n">
+      <c r="J49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="J49" s="99" t="n">
+      <c r="K49" s="99" t="n">
         <v>12.04</v>
       </c>
-      <c r="K49" s="99" t="n">
+      <c r="L49" s="99" t="n">
         <v>11.38</v>
       </c>
-      <c r="L49" s="99" t="n">
+      <c r="M49" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="M49" s="99" t="n">
+      <c r="N49" s="99" t="n">
         <v>11.79</v>
       </c>
-      <c r="N49" s="99" t="n">
+      <c r="O49" s="99" t="n">
         <v>11.17</v>
-      </c>
-      <c r="O49" s="99" t="n">
-        <v>10.79</v>
       </c>
       <c r="P49" s="99" t="n">
         <v>10.79</v>
       </c>
       <c r="Q49" s="99" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="R49" s="99" t="n">
         <v>12.69</v>
       </c>
-      <c r="R49" s="99" t="n">
+      <c r="S49" s="99" t="n">
         <v>12.13</v>
       </c>
-      <c r="S49" s="99" t="n">
+      <c r="T49" s="99" t="n">
         <v>10.89</v>
       </c>
-      <c r="T49" s="99" t="n">
+      <c r="U49" s="99" t="n">
         <v>11.15</v>
       </c>
-      <c r="U49" s="99" t="n">
+      <c r="V49" s="99" t="n">
         <v>10.46</v>
       </c>
-      <c r="V49" s="99" t="n">
+      <c r="W49" s="99" t="n">
         <v>9.92</v>
       </c>
-      <c r="W49" s="99" t="n">
+      <c r="X49" s="99" t="n">
         <v>10.76</v>
       </c>
-      <c r="X49" s="99" t="n">
+      <c r="Y49" s="99" t="n">
         <v>8.26</v>
       </c>
-      <c r="Y49" s="99" t="n">
+      <c r="Z49" s="99" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z49" s="99" t="n">
+      <c r="AA49" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="AA49" s="99" t="n">
+      <c r="AB49" s="99" t="n">
         <v>10.53</v>
       </c>
-      <c r="AB49" s="99" t="n">
+      <c r="AC49" s="99" t="n">
         <v>10.98</v>
       </c>
-      <c r="AC49" s="99" t="n">
+      <c r="AD49" s="99" t="n">
         <v>10.25</v>
       </c>
-      <c r="AD49" s="99" t="n">
+      <c r="AE49" s="99" t="n">
         <v>11.81</v>
-      </c>
-      <c r="AE49" s="99" t="n">
-        <v>9.77</v>
       </c>
     </row>
     <row r="50">
@@ -11770,94 +11770,94 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="C50" s="99" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="C50" s="99" t="n">
+      <c r="D50" s="99" t="n">
         <v>66.58</v>
       </c>
-      <c r="D50" s="99" t="n">
+      <c r="E50" s="99" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="E50" s="99" t="n">
+      <c r="F50" s="99" t="n">
         <v>46.37</v>
       </c>
-      <c r="F50" s="99" t="n">
+      <c r="G50" s="99" t="n">
         <v>55.34</v>
       </c>
-      <c r="G50" s="99" t="n">
+      <c r="H50" s="99" t="n">
         <v>47.41</v>
       </c>
-      <c r="H50" s="99" t="n">
+      <c r="I50" s="99" t="n">
         <v>37.56</v>
       </c>
-      <c r="I50" s="99" t="n">
+      <c r="J50" s="99" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="J50" s="99" t="n">
+      <c r="K50" s="99" t="n">
         <v>73.75</v>
       </c>
-      <c r="K50" s="99" t="n">
+      <c r="L50" s="99" t="n">
         <v>84.3</v>
       </c>
-      <c r="L50" s="99" t="n">
+      <c r="M50" s="99" t="n">
         <v>84.53</v>
       </c>
-      <c r="M50" s="99" t="n">
+      <c r="N50" s="99" t="n">
         <v>82.79000000000001</v>
       </c>
-      <c r="N50" s="99" t="n">
+      <c r="O50" s="99" t="n">
         <v>80.42</v>
       </c>
-      <c r="O50" s="99" t="n">
+      <c r="P50" s="99" t="n">
         <v>76.45</v>
       </c>
-      <c r="P50" s="99" t="n">
+      <c r="Q50" s="99" t="n">
         <v>75.56</v>
       </c>
-      <c r="Q50" s="99" t="n">
+      <c r="R50" s="99" t="n">
         <v>75.54000000000001</v>
       </c>
-      <c r="R50" s="99" t="n">
+      <c r="S50" s="99" t="n">
         <v>67.93000000000001</v>
       </c>
-      <c r="S50" s="99" t="n">
+      <c r="T50" s="99" t="n">
         <v>67.65000000000001</v>
       </c>
-      <c r="T50" s="99" t="n">
+      <c r="U50" s="99" t="n">
         <v>65.78</v>
       </c>
-      <c r="U50" s="99" t="n">
+      <c r="V50" s="99" t="n">
         <v>64.42</v>
       </c>
-      <c r="V50" s="99" t="n">
+      <c r="W50" s="99" t="n">
         <v>59.9</v>
       </c>
-      <c r="W50" s="99" t="n">
+      <c r="X50" s="99" t="n">
         <v>60.31</v>
       </c>
-      <c r="X50" s="99" t="n">
+      <c r="Y50" s="99" t="n">
         <v>40.39</v>
       </c>
-      <c r="Y50" s="99" t="n">
+      <c r="Z50" s="99" t="n">
         <v>40.54</v>
       </c>
-      <c r="Z50" s="99" t="n">
+      <c r="AA50" s="99" t="n">
         <v>37.77</v>
       </c>
-      <c r="AA50" s="99" t="n">
+      <c r="AB50" s="99" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB50" s="99" t="n">
+      <c r="AC50" s="99" t="n">
         <v>46.4</v>
       </c>
-      <c r="AC50" s="99" t="n">
+      <c r="AD50" s="99" t="n">
         <v>34.39</v>
       </c>
-      <c r="AD50" s="99" t="n">
+      <c r="AE50" s="99" t="n">
         <v>39.81</v>
-      </c>
-      <c r="AE50" s="99" t="n">
-        <v>24.45</v>
       </c>
     </row>
     <row r="51">
@@ -11867,94 +11867,94 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="C51" s="99" t="n">
         <v>63.4</v>
       </c>
-      <c r="C51" s="99" t="n">
+      <c r="D51" s="99" t="n">
         <v>62.85</v>
       </c>
-      <c r="D51" s="99" t="n">
+      <c r="E51" s="99" t="n">
         <v>63.51</v>
       </c>
-      <c r="E51" s="99" t="n">
+      <c r="F51" s="99" t="n">
         <v>54.49</v>
       </c>
-      <c r="F51" s="99" t="n">
+      <c r="G51" s="99" t="n">
         <v>58.24</v>
       </c>
-      <c r="G51" s="99" t="n">
+      <c r="H51" s="99" t="n">
         <v>55.63</v>
       </c>
-      <c r="H51" s="99" t="n">
+      <c r="I51" s="99" t="n">
         <v>52.74</v>
       </c>
-      <c r="I51" s="99" t="n">
+      <c r="J51" s="99" t="n">
         <v>63.22</v>
       </c>
-      <c r="J51" s="99" t="n">
+      <c r="K51" s="99" t="n">
         <v>65.03</v>
       </c>
-      <c r="K51" s="99" t="n">
+      <c r="L51" s="99" t="n">
         <v>67.47</v>
       </c>
-      <c r="L51" s="99" t="n">
+      <c r="M51" s="99" t="n">
         <v>67.52</v>
       </c>
-      <c r="M51" s="99" t="n">
+      <c r="N51" s="99" t="n">
         <v>66.45</v>
       </c>
-      <c r="N51" s="99" t="n">
+      <c r="O51" s="99" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="O51" s="99" t="n">
+      <c r="P51" s="99" t="n">
         <v>63.09</v>
-      </c>
-      <c r="P51" s="99" t="n">
-        <v>62.66</v>
       </c>
       <c r="Q51" s="99" t="n">
         <v>62.66</v>
       </c>
       <c r="R51" s="99" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="S51" s="99" t="n">
         <v>59.11</v>
       </c>
-      <c r="S51" s="99" t="n">
+      <c r="T51" s="99" t="n">
         <v>58.99</v>
       </c>
-      <c r="T51" s="99" t="n">
+      <c r="U51" s="99" t="n">
         <v>58.16</v>
       </c>
-      <c r="U51" s="99" t="n">
+      <c r="V51" s="99" t="n">
         <v>57.53</v>
       </c>
-      <c r="V51" s="99" t="n">
+      <c r="W51" s="99" t="n">
         <v>55.44</v>
       </c>
-      <c r="W51" s="99" t="n">
+      <c r="X51" s="99" t="n">
         <v>55.6</v>
       </c>
-      <c r="X51" s="99" t="n">
+      <c r="Y51" s="99" t="n">
         <v>47.44</v>
       </c>
-      <c r="Y51" s="99" t="n">
+      <c r="Z51" s="99" t="n">
         <v>47.52</v>
       </c>
-      <c r="Z51" s="99" t="n">
+      <c r="AA51" s="99" t="n">
         <v>46.46</v>
       </c>
-      <c r="AA51" s="99" t="n">
+      <c r="AB51" s="99" t="n">
         <v>50.55</v>
       </c>
-      <c r="AB51" s="99" t="n">
+      <c r="AC51" s="99" t="n">
         <v>50.96</v>
       </c>
-      <c r="AC51" s="99" t="n">
+      <c r="AD51" s="99" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD51" s="99" t="n">
+      <c r="AE51" s="99" t="n">
         <v>49.32</v>
-      </c>
-      <c r="AE51" s="99" t="n">
-        <v>43.45</v>
       </c>
     </row>
     <row r="52">
@@ -11963,154 +11963,154 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="97" t="inlineStr">
+      <c r="B52" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C52" s="98" t="inlineStr">
+      <c r="D52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D52" s="97" t="inlineStr">
+      <c r="E52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E52" s="96" t="inlineStr">
+      <c r="F52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F52" s="96" t="inlineStr">
+      <c r="G52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G52" s="96" t="inlineStr">
+      <c r="H52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H52" s="96" t="inlineStr">
+      <c r="I52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I52" s="96" t="inlineStr">
+      <c r="J52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J52" s="96" t="inlineStr">
+      <c r="K52" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K52" s="97" t="inlineStr">
+      <c r="L52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L52" s="97" t="inlineStr">
+      <c r="M52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M52" s="97" t="inlineStr">
+      <c r="N52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N52" s="98" t="inlineStr">
+      <c r="O52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O52" s="97" t="inlineStr">
+      <c r="P52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P52" s="97" t="inlineStr">
+      <c r="Q52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q52" s="98" t="inlineStr">
+      <c r="R52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R52" s="98" t="inlineStr">
+      <c r="S52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S52" s="98" t="inlineStr">
+      <c r="T52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T52" s="98" t="inlineStr">
+      <c r="U52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U52" s="98" t="inlineStr">
+      <c r="V52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V52" s="98" t="inlineStr">
+      <c r="W52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W52" s="98" t="inlineStr">
+      <c r="X52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X52" s="98" t="inlineStr">
+      <c r="Y52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y52" s="98" t="inlineStr">
+      <c r="Z52" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z52" s="97" t="inlineStr">
+      <c r="AA52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA52" s="97" t="inlineStr">
+      <c r="AB52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB52" s="97" t="inlineStr">
+      <c r="AC52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC52" s="97" t="inlineStr">
+      <c r="AD52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD52" s="97" t="inlineStr">
+      <c r="AE52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE52" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -12121,94 +12121,94 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="C53" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="C53" s="99" t="n">
+      <c r="D53" s="99" t="n">
         <v>-2.14</v>
       </c>
-      <c r="D53" s="99" t="n">
+      <c r="E53" s="99" t="n">
         <v>-3.08</v>
       </c>
-      <c r="E53" s="99" t="n">
+      <c r="F53" s="99" t="n">
         <v>-2.29</v>
       </c>
-      <c r="F53" s="99" t="n">
+      <c r="G53" s="99" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G53" s="99" t="n">
+      <c r="H53" s="99" t="n">
         <v>-1.93</v>
       </c>
-      <c r="H53" s="99" t="n">
+      <c r="I53" s="99" t="n">
         <v>-2.01</v>
       </c>
-      <c r="I53" s="99" t="n">
+      <c r="J53" s="99" t="n">
         <v>-3.58</v>
       </c>
-      <c r="J53" s="99" t="n">
+      <c r="K53" s="99" t="n">
         <v>-4.62</v>
       </c>
-      <c r="K53" s="99" t="n">
+      <c r="L53" s="99" t="n">
         <v>-2.75</v>
       </c>
-      <c r="L53" s="99" t="n">
+      <c r="M53" s="99" t="n">
         <v>-3.14</v>
       </c>
-      <c r="M53" s="99" t="n">
+      <c r="N53" s="99" t="n">
         <v>-4.63</v>
       </c>
-      <c r="N53" s="99" t="n">
+      <c r="O53" s="99" t="n">
         <v>-4.96</v>
       </c>
-      <c r="O53" s="99" t="n">
+      <c r="P53" s="99" t="n">
         <v>-5.36</v>
       </c>
-      <c r="P53" s="99" t="n">
+      <c r="Q53" s="99" t="n">
         <v>-4.69</v>
       </c>
-      <c r="Q53" s="99" t="n">
+      <c r="R53" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="R53" s="99" t="n">
+      <c r="S53" s="99" t="n">
         <v>-5.2</v>
       </c>
-      <c r="S53" s="99" t="n">
+      <c r="T53" s="99" t="n">
         <v>-5.7</v>
       </c>
-      <c r="T53" s="99" t="n">
+      <c r="U53" s="99" t="n">
         <v>-5.17</v>
       </c>
-      <c r="U53" s="99" t="n">
+      <c r="V53" s="99" t="n">
         <v>-7.1</v>
       </c>
-      <c r="V53" s="99" t="n">
+      <c r="W53" s="99" t="n">
         <v>-7.75</v>
       </c>
-      <c r="W53" s="99" t="n">
+      <c r="X53" s="99" t="n">
         <v>-7.97</v>
       </c>
-      <c r="X53" s="99" t="n">
+      <c r="Y53" s="99" t="n">
         <v>-8.380000000000001</v>
       </c>
-      <c r="Y53" s="99" t="n">
+      <c r="Z53" s="99" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="Z53" s="99" t="n">
+      <c r="AA53" s="99" t="n">
         <v>-10.63</v>
       </c>
-      <c r="AA53" s="99" t="n">
+      <c r="AB53" s="99" t="n">
         <v>-11.53</v>
       </c>
-      <c r="AB53" s="99" t="n">
+      <c r="AC53" s="99" t="n">
         <v>-10.99</v>
       </c>
-      <c r="AC53" s="99" t="n">
+      <c r="AD53" s="99" t="n">
         <v>-11.49</v>
       </c>
-      <c r="AD53" s="99" t="n">
+      <c r="AE53" s="99" t="n">
         <v>-11.82</v>
-      </c>
-      <c r="AE53" s="99" t="n">
-        <v>-13.32</v>
       </c>
     </row>
     <row r="54">
@@ -12218,191 +12218,191 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="C54" s="99" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="C54" s="99" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="D54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="E54" s="99" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="F54" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="F54" s="99" t="n">
+      <c r="G54" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="G54" s="99" t="n">
+      <c r="H54" s="99" t="n">
         <v>-9.02</v>
       </c>
-      <c r="H54" s="99" t="n">
+      <c r="I54" s="99" t="n">
         <v>-10.35</v>
       </c>
-      <c r="I54" s="99" t="n">
+      <c r="J54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="J54" s="99" t="n">
+      <c r="K54" s="99" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="K54" s="99" t="n">
+      <c r="L54" s="99" t="n">
         <v>-7.18</v>
       </c>
-      <c r="L54" s="99" t="n">
+      <c r="M54" s="99" t="n">
         <v>-6.04</v>
       </c>
-      <c r="M54" s="99" t="n">
+      <c r="N54" s="99" t="n">
         <v>-5.64</v>
       </c>
-      <c r="N54" s="99" t="n">
+      <c r="O54" s="99" t="n">
         <v>-4.72</v>
       </c>
-      <c r="O54" s="99" t="n">
+      <c r="P54" s="99" t="n">
         <v>-5.61</v>
       </c>
-      <c r="P54" s="99" t="n">
+      <c r="Q54" s="99" t="n">
         <v>-5.62</v>
       </c>
-      <c r="Q54" s="99" t="n">
+      <c r="R54" s="99" t="n">
         <v>-4.58</v>
       </c>
-      <c r="R54" s="99" t="n">
+      <c r="S54" s="99" t="n">
         <v>-4.48</v>
       </c>
-      <c r="S54" s="99" t="n">
+      <c r="T54" s="99" t="n">
         <v>-5.43</v>
       </c>
-      <c r="T54" s="99" t="n">
+      <c r="U54" s="99" t="n">
         <v>-5.16</v>
       </c>
-      <c r="U54" s="99" t="n">
+      <c r="V54" s="99" t="n">
         <v>-5.57</v>
       </c>
-      <c r="V54" s="99" t="n">
+      <c r="W54" s="99" t="n">
         <v>-5.69</v>
       </c>
-      <c r="W54" s="99" t="n">
+      <c r="X54" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="X54" s="99" t="n">
+      <c r="Y54" s="99" t="n">
         <v>-6.39</v>
       </c>
-      <c r="Y54" s="99" t="n">
+      <c r="Z54" s="99" t="n">
         <v>-7.95</v>
       </c>
-      <c r="Z54" s="99" t="n">
+      <c r="AA54" s="99" t="n">
         <v>-8.039999999999999</v>
       </c>
-      <c r="AA54" s="99" t="n">
+      <c r="AB54" s="99" t="n">
         <v>-7.19</v>
       </c>
-      <c r="AB54" s="99" t="n">
+      <c r="AC54" s="99" t="n">
         <v>-6.74</v>
       </c>
-      <c r="AC54" s="99" t="n">
+      <c r="AD54" s="99" t="n">
         <v>-6.71</v>
       </c>
-      <c r="AD54" s="99" t="n">
+      <c r="AE54" s="99" t="n">
         <v>-6.46</v>
       </c>
-      <c r="AE54" s="99" t="n">
-        <v>-7.92</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="100" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="99" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="C55" s="99" t="n">
         <v>55.36</v>
       </c>
-      <c r="C55" s="99" t="n">
+      <c r="D55" s="99" t="n">
         <v>67.8</v>
       </c>
-      <c r="D55" s="99" t="n">
+      <c r="E55" s="99" t="n">
         <v>54.91</v>
       </c>
-      <c r="E55" s="99" t="n">
+      <c r="F55" s="99" t="n">
         <v>31.87</v>
       </c>
-      <c r="F55" s="99" t="n">
+      <c r="G55" s="99" t="n">
         <v>35.24</v>
       </c>
-      <c r="G55" s="99" t="n">
+      <c r="H55" s="99" t="n">
         <v>39.87</v>
       </c>
-      <c r="H55" s="99" t="n">
+      <c r="I55" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="I55" s="99" t="n">
+      <c r="J55" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="J55" s="99" t="n">
+      <c r="K55" s="99" t="n">
         <v>16.74</v>
       </c>
-      <c r="K55" s="99" t="n">
+      <c r="L55" s="99" t="n">
         <v>32.54</v>
       </c>
-      <c r="L55" s="99" t="n">
+      <c r="M55" s="99" t="n">
         <v>82.56</v>
       </c>
-      <c r="M55" s="99" t="n">
+      <c r="N55" s="99" t="n">
         <v>77.58</v>
       </c>
-      <c r="N55" s="99" t="n">
+      <c r="O55" s="99" t="n">
         <v>88.48</v>
       </c>
-      <c r="O55" s="99" t="n">
+      <c r="P55" s="99" t="n">
         <v>71.72</v>
       </c>
-      <c r="P55" s="99" t="n">
+      <c r="Q55" s="99" t="n">
         <v>65.42</v>
       </c>
-      <c r="Q55" s="99" t="n">
+      <c r="R55" s="99" t="n">
         <v>94.41</v>
       </c>
-      <c r="R55" s="99" t="n">
+      <c r="S55" s="99" t="n">
         <v>93.34999999999999</v>
       </c>
-      <c r="S55" s="99" t="n">
+      <c r="T55" s="99" t="n">
         <v>86.56</v>
       </c>
-      <c r="T55" s="99" t="n">
+      <c r="U55" s="99" t="n">
         <v>87.25</v>
       </c>
-      <c r="U55" s="99" t="n">
+      <c r="V55" s="99" t="n">
         <v>80.78</v>
       </c>
-      <c r="V55" s="99" t="n">
+      <c r="W55" s="99" t="n">
         <v>94.06</v>
       </c>
-      <c r="W55" s="99" t="n">
+      <c r="X55" s="99" t="n">
         <v>90.83</v>
       </c>
-      <c r="X55" s="99" t="n">
+      <c r="Y55" s="99" t="n">
         <v>88.78</v>
       </c>
-      <c r="Y55" s="99" t="n">
+      <c r="Z55" s="99" t="n">
         <v>77.17</v>
       </c>
-      <c r="Z55" s="99" t="n">
+      <c r="AA55" s="99" t="n">
         <v>59.2</v>
       </c>
-      <c r="AA55" s="99" t="n">
+      <c r="AB55" s="99" t="n">
         <v>47</v>
       </c>
-      <c r="AB55" s="99" t="n">
+      <c r="AC55" s="99" t="n">
         <v>55.33</v>
       </c>
-      <c r="AC55" s="99" t="n">
+      <c r="AD55" s="99" t="n">
         <v>48.17</v>
       </c>
-      <c r="AD55" s="99" t="n">
+      <c r="AE55" s="99" t="n">
         <v>52.88</v>
-      </c>
-      <c r="AE55" s="99" t="n">
-        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -12412,94 +12412,94 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="C56" s="99" t="n">
         <v>48.71</v>
       </c>
-      <c r="C56" s="99" t="n">
+      <c r="D56" s="99" t="n">
         <v>53.61</v>
       </c>
-      <c r="D56" s="99" t="n">
+      <c r="E56" s="99" t="n">
         <v>45.19</v>
       </c>
-      <c r="E56" s="99" t="n">
+      <c r="F56" s="99" t="n">
         <v>32.83</v>
       </c>
-      <c r="F56" s="99" t="n">
+      <c r="G56" s="99" t="n">
         <v>34.58</v>
       </c>
-      <c r="G56" s="99" t="n">
+      <c r="H56" s="99" t="n">
         <v>37.2</v>
       </c>
-      <c r="H56" s="99" t="n">
+      <c r="I56" s="99" t="n">
         <v>16.31</v>
       </c>
-      <c r="I56" s="99" t="n">
+      <c r="J56" s="99" t="n">
         <v>22.99</v>
       </c>
-      <c r="J56" s="99" t="n">
+      <c r="K56" s="99" t="n">
         <v>32.1</v>
       </c>
-      <c r="K56" s="99" t="n">
+      <c r="L56" s="99" t="n">
         <v>48.66</v>
       </c>
-      <c r="L56" s="99" t="n">
+      <c r="M56" s="99" t="n">
         <v>80.73</v>
       </c>
-      <c r="M56" s="99" t="n">
+      <c r="N56" s="99" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="N56" s="99" t="n">
+      <c r="O56" s="99" t="n">
         <v>83.84</v>
       </c>
-      <c r="O56" s="99" t="n">
+      <c r="P56" s="99" t="n">
         <v>74.67</v>
       </c>
-      <c r="P56" s="99" t="n">
+      <c r="Q56" s="99" t="n">
         <v>72.3</v>
       </c>
-      <c r="Q56" s="99" t="n">
+      <c r="R56" s="99" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="R56" s="99" t="n">
+      <c r="S56" s="99" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="S56" s="99" t="n">
+      <c r="T56" s="99" t="n">
         <v>78.34</v>
       </c>
-      <c r="T56" s="99" t="n">
+      <c r="U56" s="99" t="n">
         <v>78.61</v>
       </c>
-      <c r="U56" s="99" t="n">
+      <c r="V56" s="99" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="V56" s="99" t="n">
+      <c r="W56" s="99" t="n">
         <v>79.75</v>
       </c>
-      <c r="W56" s="99" t="n">
+      <c r="X56" s="99" t="n">
         <v>74.68000000000001</v>
       </c>
-      <c r="X56" s="99" t="n">
+      <c r="Y56" s="99" t="n">
         <v>71.84</v>
       </c>
-      <c r="Y56" s="99" t="n">
+      <c r="Z56" s="99" t="n">
         <v>59.38</v>
       </c>
-      <c r="Z56" s="99" t="n">
+      <c r="AA56" s="99" t="n">
         <v>47.5</v>
       </c>
-      <c r="AA56" s="99" t="n">
+      <c r="AB56" s="99" t="n">
         <v>41.51</v>
       </c>
-      <c r="AB56" s="99" t="n">
+      <c r="AC56" s="99" t="n">
         <v>44.58</v>
       </c>
-      <c r="AC56" s="99" t="n">
+      <c r="AD56" s="99" t="n">
         <v>40.46</v>
       </c>
-      <c r="AD56" s="99" t="n">
+      <c r="AE56" s="99" t="n">
         <v>42.57</v>
-      </c>
-      <c r="AE56" s="99" t="n">
-        <v>17.19</v>
       </c>
     </row>
     <row r="57">
@@ -12523,139 +12523,139 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E57" s="96" t="inlineStr">
+      <c r="E57" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F57" s="96" t="inlineStr">
+      <c r="G57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G57" s="96" t="inlineStr">
+      <c r="H57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H57" s="96" t="inlineStr">
+      <c r="I57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I57" s="96" t="inlineStr">
+      <c r="J57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J57" s="96" t="inlineStr">
+      <c r="K57" s="96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K57" s="97" t="inlineStr">
+      <c r="L57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L57" s="97" t="inlineStr">
+      <c r="M57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M57" s="97" t="inlineStr">
+      <c r="N57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N57" s="98" t="inlineStr">
+      <c r="O57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O57" s="97" t="inlineStr">
+      <c r="P57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P57" s="97" t="inlineStr">
+      <c r="Q57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q57" s="97" t="inlineStr">
+      <c r="R57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R57" s="98" t="inlineStr">
+      <c r="S57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S57" s="98" t="inlineStr">
+      <c r="T57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T57" s="98" t="inlineStr">
+      <c r="U57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U57" s="98" t="inlineStr">
+      <c r="V57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V57" s="98" t="inlineStr">
+      <c r="W57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W57" s="98" t="inlineStr">
+      <c r="X57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X57" s="98" t="inlineStr">
+      <c r="Y57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y57" s="98" t="inlineStr">
+      <c r="Z57" s="98" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z57" s="97" t="inlineStr">
+      <c r="AA57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA57" s="97" t="inlineStr">
+      <c r="AB57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB57" s="97" t="inlineStr">
+      <c r="AC57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC57" s="97" t="inlineStr">
+      <c r="AD57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD57" s="97" t="inlineStr">
+      <c r="AE57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE57" s="96" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -12666,94 +12666,94 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C58" s="99" t="n">
         <v>1.68</v>
       </c>
-      <c r="C58" s="99" t="n">
+      <c r="D58" s="99" t="n">
         <v>2.95</v>
-      </c>
-      <c r="D58" s="99" t="n">
-        <v>1.45</v>
       </c>
       <c r="E58" s="99" t="n">
         <v>1.45</v>
       </c>
       <c r="F58" s="99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G58" s="99" t="n">
         <v>0.74</v>
       </c>
-      <c r="G58" s="99" t="n">
+      <c r="H58" s="99" t="n">
         <v>2.08</v>
       </c>
-      <c r="H58" s="99" t="n">
+      <c r="I58" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="I58" s="99" t="n">
+      <c r="J58" s="99" t="n">
         <v>1.7</v>
       </c>
-      <c r="J58" s="99" t="n">
+      <c r="K58" s="99" t="n">
         <v>-0.21</v>
       </c>
-      <c r="K58" s="99" t="n">
+      <c r="L58" s="99" t="n">
         <v>2.05</v>
       </c>
-      <c r="L58" s="99" t="n">
+      <c r="M58" s="99" t="n">
         <v>2.36</v>
       </c>
-      <c r="M58" s="99" t="n">
+      <c r="N58" s="99" t="n">
         <v>1.88</v>
       </c>
-      <c r="N58" s="99" t="n">
+      <c r="O58" s="99" t="n">
         <v>1.39</v>
       </c>
-      <c r="O58" s="99" t="n">
+      <c r="P58" s="99" t="n">
         <v>1.11</v>
       </c>
-      <c r="P58" s="99" t="n">
+      <c r="Q58" s="99" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q58" s="99" t="n">
+      <c r="R58" s="99" t="n">
         <v>0.05</v>
       </c>
-      <c r="R58" s="99" t="n">
+      <c r="S58" s="99" t="n">
         <v>0.73</v>
       </c>
-      <c r="S58" s="99" t="n">
+      <c r="T58" s="99" t="n">
         <v>-0.02</v>
       </c>
-      <c r="T58" s="99" t="n">
+      <c r="U58" s="99" t="n">
         <v>-0.13</v>
       </c>
-      <c r="U58" s="99" t="n">
+      <c r="V58" s="99" t="n">
         <v>-1.72</v>
       </c>
-      <c r="V58" s="99" t="n">
+      <c r="W58" s="99" t="n">
         <v>-1.88</v>
       </c>
-      <c r="W58" s="99" t="n">
+      <c r="X58" s="99" t="n">
         <v>-1.98</v>
       </c>
-      <c r="X58" s="99" t="n">
+      <c r="Y58" s="99" t="n">
         <v>-2.72</v>
       </c>
-      <c r="Y58" s="99" t="n">
+      <c r="Z58" s="99" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Z58" s="99" t="n">
+      <c r="AA58" s="99" t="n">
         <v>-4.88</v>
       </c>
-      <c r="AA58" s="99" t="n">
+      <c r="AB58" s="99" t="n">
         <v>-5.55</v>
       </c>
-      <c r="AB58" s="99" t="n">
+      <c r="AC58" s="99" t="n">
         <v>-5.25</v>
       </c>
-      <c r="AC58" s="99" t="n">
+      <c r="AD58" s="99" t="n">
         <v>-5.65</v>
       </c>
-      <c r="AD58" s="99" t="n">
+      <c r="AE58" s="99" t="n">
         <v>-6.65</v>
-      </c>
-      <c r="AE58" s="99" t="n">
-        <v>-7.28</v>
       </c>
     </row>
     <row r="59">
@@ -12763,94 +12763,94 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="C59" s="99" t="n">
         <v>0.84</v>
       </c>
-      <c r="C59" s="99" t="n">
+      <c r="D59" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="D59" s="99" t="n">
+      <c r="E59" s="99" t="n">
         <v>1.41</v>
       </c>
-      <c r="E59" s="99" t="n">
+      <c r="F59" s="99" t="n">
         <v>0.68</v>
       </c>
-      <c r="F59" s="99" t="n">
+      <c r="G59" s="99" t="n">
         <v>0.48</v>
       </c>
-      <c r="G59" s="99" t="n">
+      <c r="H59" s="99" t="n">
         <v>2.38</v>
       </c>
-      <c r="H59" s="99" t="n">
+      <c r="I59" s="99" t="n">
         <v>1.75</v>
       </c>
-      <c r="I59" s="99" t="n">
+      <c r="J59" s="99" t="n">
         <v>3.59</v>
       </c>
-      <c r="J59" s="99" t="n">
+      <c r="K59" s="99" t="n">
         <v>3.65</v>
       </c>
-      <c r="K59" s="99" t="n">
+      <c r="L59" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="L59" s="99" t="n">
+      <c r="M59" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="M59" s="99" t="n">
+      <c r="N59" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="N59" s="99" t="n">
+      <c r="O59" s="99" t="n">
         <v>6.57</v>
       </c>
-      <c r="O59" s="99" t="n">
+      <c r="P59" s="99" t="n">
         <v>5.43</v>
       </c>
-      <c r="P59" s="99" t="n">
+      <c r="Q59" s="99" t="n">
         <v>4.7</v>
       </c>
-      <c r="Q59" s="99" t="n">
+      <c r="R59" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="R59" s="99" t="n">
+      <c r="S59" s="99" t="n">
         <v>5.28</v>
       </c>
-      <c r="S59" s="99" t="n">
+      <c r="T59" s="99" t="n">
         <v>4.39</v>
       </c>
-      <c r="T59" s="99" t="n">
+      <c r="U59" s="99" t="n">
         <v>4.03</v>
       </c>
-      <c r="U59" s="99" t="n">
+      <c r="V59" s="99" t="n">
         <v>3.84</v>
       </c>
-      <c r="V59" s="99" t="n">
+      <c r="W59" s="99" t="n">
         <v>4.66</v>
-      </c>
-      <c r="W59" s="99" t="n">
-        <v>4.36</v>
       </c>
       <c r="X59" s="99" t="n">
         <v>4.36</v>
       </c>
       <c r="Y59" s="99" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Z59" s="99" t="n">
         <v>2.68</v>
       </c>
-      <c r="Z59" s="99" t="n">
+      <c r="AA59" s="99" t="n">
         <v>2.54</v>
       </c>
-      <c r="AA59" s="99" t="n">
+      <c r="AB59" s="99" t="n">
         <v>3.55</v>
       </c>
-      <c r="AB59" s="99" t="n">
+      <c r="AC59" s="99" t="n">
         <v>3.83</v>
       </c>
-      <c r="AC59" s="99" t="n">
+      <c r="AD59" s="99" t="n">
         <v>3.44</v>
       </c>
-      <c r="AD59" s="99" t="n">
+      <c r="AE59" s="99" t="n">
         <v>2.91</v>
-      </c>
-      <c r="AE59" s="99" t="n">
-        <v>1.8</v>
       </c>
     </row>
     <row r="60">
@@ -12860,94 +12860,94 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="C60" s="99" t="n">
         <v>60.74</v>
       </c>
-      <c r="C60" s="99" t="n">
+      <c r="D60" s="99" t="n">
         <v>69.64</v>
       </c>
-      <c r="D60" s="99" t="n">
+      <c r="E60" s="99" t="n">
         <v>56.63</v>
       </c>
-      <c r="E60" s="99" t="n">
+      <c r="F60" s="99" t="n">
         <v>34.87</v>
       </c>
-      <c r="F60" s="99" t="n">
+      <c r="G60" s="99" t="n">
         <v>25.25</v>
       </c>
-      <c r="G60" s="99" t="n">
+      <c r="H60" s="99" t="n">
         <v>36.38</v>
       </c>
-      <c r="H60" s="99" t="n">
+      <c r="I60" s="99" t="n">
         <v>13.61</v>
       </c>
-      <c r="I60" s="99" t="n">
+      <c r="J60" s="99" t="n">
         <v>28.38</v>
       </c>
-      <c r="J60" s="99" t="n">
+      <c r="K60" s="99" t="n">
         <v>29.73</v>
       </c>
-      <c r="K60" s="99" t="n">
+      <c r="L60" s="99" t="n">
         <v>46.54</v>
       </c>
-      <c r="L60" s="99" t="n">
+      <c r="M60" s="99" t="n">
         <v>93.47</v>
       </c>
-      <c r="M60" s="99" t="n">
+      <c r="N60" s="99" t="n">
         <v>92.75</v>
       </c>
-      <c r="N60" s="99" t="n">
+      <c r="O60" s="99" t="n">
         <v>94.58</v>
       </c>
-      <c r="O60" s="99" t="n">
+      <c r="P60" s="99" t="n">
         <v>91.78</v>
       </c>
-      <c r="P60" s="99" t="n">
+      <c r="Q60" s="99" t="n">
         <v>88.26000000000001</v>
       </c>
-      <c r="Q60" s="99" t="n">
+      <c r="R60" s="99" t="n">
         <v>85.2</v>
       </c>
-      <c r="R60" s="99" t="n">
+      <c r="S60" s="99" t="n">
         <v>89.55</v>
       </c>
-      <c r="S60" s="99" t="n">
+      <c r="T60" s="99" t="n">
         <v>84.34</v>
       </c>
-      <c r="T60" s="99" t="n">
+      <c r="U60" s="99" t="n">
         <v>82.23999999999999</v>
       </c>
-      <c r="U60" s="99" t="n">
+      <c r="V60" s="99" t="n">
         <v>77.56999999999999</v>
       </c>
-      <c r="V60" s="99" t="n">
+      <c r="W60" s="99" t="n">
         <v>90.01000000000001</v>
       </c>
-      <c r="W60" s="99" t="n">
+      <c r="X60" s="99" t="n">
         <v>87.73</v>
       </c>
-      <c r="X60" s="99" t="n">
+      <c r="Y60" s="99" t="n">
         <v>83.84</v>
       </c>
-      <c r="Y60" s="99" t="n">
+      <c r="Z60" s="99" t="n">
         <v>67.20999999999999</v>
       </c>
-      <c r="Z60" s="99" t="n">
+      <c r="AA60" s="99" t="n">
         <v>59.47</v>
       </c>
-      <c r="AA60" s="99" t="n">
+      <c r="AB60" s="99" t="n">
         <v>48.96</v>
       </c>
-      <c r="AB60" s="99" t="n">
+      <c r="AC60" s="99" t="n">
         <v>48.54</v>
       </c>
-      <c r="AC60" s="99" t="n">
+      <c r="AD60" s="99" t="n">
         <v>44.49</v>
       </c>
-      <c r="AD60" s="99" t="n">
+      <c r="AE60" s="99" t="n">
         <v>38.96</v>
-      </c>
-      <c r="AE60" s="99" t="n">
-        <v>12.93</v>
       </c>
     </row>
     <row r="61">
@@ -12957,107 +12957,107 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="C61" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="C61" s="99" t="n">
+      <c r="D61" s="99" t="n">
         <v>62.56</v>
       </c>
-      <c r="D61" s="99" t="n">
+      <c r="E61" s="99" t="n">
         <v>52.29</v>
       </c>
-      <c r="E61" s="99" t="n">
+      <c r="F61" s="99" t="n">
         <v>37.42</v>
       </c>
-      <c r="F61" s="99" t="n">
+      <c r="G61" s="99" t="n">
         <v>31.32</v>
       </c>
-      <c r="G61" s="99" t="n">
+      <c r="H61" s="99" t="n">
         <v>40.38</v>
       </c>
-      <c r="H61" s="99" t="n">
+      <c r="I61" s="99" t="n">
         <v>26.19</v>
       </c>
-      <c r="I61" s="99" t="n">
+      <c r="J61" s="99" t="n">
         <v>42.54</v>
       </c>
-      <c r="J61" s="99" t="n">
+      <c r="K61" s="99" t="n">
         <v>43.82</v>
       </c>
-      <c r="K61" s="99" t="n">
+      <c r="L61" s="99" t="n">
         <v>58.62</v>
       </c>
-      <c r="L61" s="99" t="n">
+      <c r="M61" s="99" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="M61" s="99" t="n">
+      <c r="N61" s="99" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="N61" s="99" t="n">
+      <c r="O61" s="99" t="n">
         <v>88.2</v>
       </c>
-      <c r="O61" s="99" t="n">
+      <c r="P61" s="99" t="n">
         <v>84.89</v>
       </c>
-      <c r="P61" s="99" t="n">
+      <c r="Q61" s="99" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="Q61" s="99" t="n">
+      <c r="R61" s="99" t="n">
         <v>79.09</v>
       </c>
-      <c r="R61" s="99" t="n">
+      <c r="S61" s="99" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="S61" s="99" t="n">
+      <c r="T61" s="99" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="T61" s="99" t="n">
+      <c r="U61" s="99" t="n">
         <v>74.75</v>
       </c>
-      <c r="U61" s="99" t="n">
+      <c r="V61" s="99" t="n">
         <v>71.06</v>
       </c>
-      <c r="V61" s="99" t="n">
+      <c r="W61" s="99" t="n">
         <v>77.69</v>
       </c>
-      <c r="W61" s="99" t="n">
+      <c r="X61" s="99" t="n">
         <v>74.64</v>
       </c>
-      <c r="X61" s="99" t="n">
+      <c r="Y61" s="99" t="n">
         <v>69.83</v>
       </c>
-      <c r="Y61" s="99" t="n">
+      <c r="Z61" s="99" t="n">
         <v>54.4</v>
       </c>
-      <c r="Z61" s="99" t="n">
+      <c r="AA61" s="99" t="n">
         <v>49.04</v>
       </c>
-      <c r="AA61" s="99" t="n">
+      <c r="AB61" s="99" t="n">
         <v>42.47</v>
       </c>
-      <c r="AB61" s="99" t="n">
+      <c r="AC61" s="99" t="n">
         <v>42.21</v>
       </c>
-      <c r="AC61" s="99" t="n">
+      <c r="AD61" s="99" t="n">
         <v>39.51</v>
       </c>
-      <c r="AD61" s="99" t="n">
+      <c r="AE61" s="99" t="n">
         <v>35.67</v>
-      </c>
-      <c r="AE61" s="99" t="n">
-        <v>18.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="95" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI11:18.87&lt;=27;sh:RSI2:4.21&lt;=7;cy:RNG60:-12.57&lt;=-10;vn:RSI3:9.05&lt;=25</t>
+          <t>今日买报：sh:RSI11:18.87&lt;=27;sh:RSI2:4.21&lt;=7;cy:RNG60:-12.57&lt;=-10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:95.83&gt;=91;us500:RSI2:95.83&gt;=85;ixic:RSI2:95.17&gt;=95;ixic:RSI2:95.17&gt;=85</t>
+          <t>今日卖报：us500:RSI2:95.83&gt;=91;us500:RSI2:95.83&gt;=85;us30:RSI3:88.3&gt;=85;fr40:RSI3:74.07&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>2.92</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>7.95</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>7.95</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>95.83</v>
+        <v>96.09</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>95.83</v>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>95.83</v>
+        <v>96.09</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>95.83</v>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>-0.51</v>
+        <v>0.39</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>-3.34</v>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>-2.69</v>
+        <v>-1.81</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>-2.26</v>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>42.16</v>
+        <v>60.96</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>9.050000000000001</v>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>36.48</v>
+        <v>51.86</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>16.23</v>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>7.48</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>14.1</v>
+        <v>14.07</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>14.24</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>69.23999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>67.76000000000001</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>64.06</v>
+        <v>63.93</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>63.4</v>
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>-2.24</v>
+        <v>-2.28</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>-3.34</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.75</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-9.210000000000001</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>74.06999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>55.36</v>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>60.53</v>
+        <v>59.76</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>48.71</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>1.68</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>0.84</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>67.37</v>
+        <v>68.61</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>60.74</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>61.87</v>
+        <v>62.83</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>57.16</v>
@@ -13057,7 +13057,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:95.83&gt;=91;us500:RSI2:95.83&gt;=85;us30:RSI3:88.3&gt;=85;fr40:RSI3:74.07&gt;=73</t>
+          <t>今日卖报：us500:RSI2:96.09&gt;=91;us500:RSI2:96.09&gt;=85;us30:RSI3:88.3&gt;=85;fr40:RSI3:73.12&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1073,7 +1073,6 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4004,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>-0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.25</v>
@@ -4101,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-0.61</v>
+        <v>-0.51</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-0.88</v>
@@ -8693,9 +8692,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="98" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="96" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="98" t="inlineStr">
@@ -8851,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>3.11</v>
@@ -8948,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>8.279999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>8.279999999999999</v>
@@ -9039,13 +9038,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="100" t="inlineStr">
+      <c r="A25" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>96.09</v>
+        <v>40.89</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>96.09</v>
@@ -9136,13 +9135,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="100" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>96.09</v>
+        <v>40.89</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>96.09</v>
@@ -9396,7 +9395,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>6.27</v>
+        <v>5.31</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>6.27</v>
@@ -9493,7 +9492,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>5.92</v>
+        <v>4.38</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>5.92</v>
@@ -9584,13 +9583,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="100" t="inlineStr">
+      <c r="A30" s="80" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>85.48999999999999</v>
+        <v>65.31</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>85.48999999999999</v>
@@ -9687,7 +9686,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>74.56999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>74.56999999999999</v>
@@ -9783,9 +9782,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="98" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B32" s="96" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="98" t="inlineStr">
@@ -9941,7 +9940,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>-0.35</v>
+        <v>0.44</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>-0.35</v>
@@ -10038,7 +10037,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>8.039999999999999</v>
+        <v>7.16</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>8.039999999999999</v>
@@ -10135,7 +10134,7 @@
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>70.06</v>
+        <v>42.32</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>70.06</v>
@@ -10232,7 +10231,7 @@
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>70.06</v>
+        <v>42.32</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>70.06</v>
@@ -11031,7 +11030,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>0.39</v>
@@ -11128,7 +11127,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>-1.17</v>
+        <v>-1.42</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>-1.81</v>
@@ -11225,7 +11224,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>72.02</v>
+        <v>68.98</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>60.96</v>
@@ -11322,7 +11321,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>61.35</v>
+        <v>58.52</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>51.86</v>
@@ -11576,7 +11575,7 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>7.42</v>
@@ -11673,7 +11672,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>14.07</v>
@@ -11770,7 +11769,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>63.24</v>
+        <v>63.06</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>65.26000000000001</v>
@@ -11867,7 +11866,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>59.93</v>
+        <v>59.86</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>60.75</v>
@@ -11963,9 +11962,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="98" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B52" s="96" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C52" s="98" t="inlineStr">
@@ -12121,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>-2.28</v>
+        <v>-2.16</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>-2.28</v>
@@ -12218,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-8.75</v>
+        <v>-8.43</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-8.75</v>
@@ -12309,13 +12308,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="100" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>73.12</v>
+        <v>43.83</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>73.12</v>
@@ -12412,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>59.76</v>
+        <v>45.92</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>59.76</v>
@@ -12666,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>3.02</v>
@@ -12763,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>1.26</v>
+        <v>2.34</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>1.26</v>
@@ -12860,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>68.31999999999999</v>
+        <v>65.67</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>68.31999999999999</v>
@@ -12957,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>62.6</v>
+        <v>61.14</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>62.6</v>
@@ -13057,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:96.09&gt;=91;us500:RSI2:96.09&gt;=85;us30:RSI3:85.49&gt;=85;fr40:RSI3:73.12&gt;=73</t>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -16709,13 +16708,13 @@
       <c r="G2" s="36" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="101" t="n">
+      <c r="H2" s="100" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="102">
+      <c r="J2" s="101">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16746,13 +16745,13 @@
       <c r="G3" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="101" t="n">
+      <c r="H3" s="100" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="36" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="102">
+      <c r="J3" s="101">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16783,13 +16782,13 @@
       <c r="G4" s="36" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="101" t="n">
+      <c r="H4" s="100" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="36" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="102">
+      <c r="J4" s="101">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16820,13 +16819,13 @@
       <c r="G5" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="101" t="n">
+      <c r="H5" s="100" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="36" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="102">
+      <c r="J5" s="101">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16857,13 +16856,13 @@
       <c r="G6" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="103" t="n">
+      <c r="H6" s="102" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="24" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="102">
+      <c r="J6" s="101">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16894,13 +16893,13 @@
       <c r="G7" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="101" t="n">
+      <c r="H7" s="100" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="36" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="102">
+      <c r="J7" s="101">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16931,13 +16930,13 @@
       <c r="G8" s="24" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="103" t="n">
+      <c r="H8" s="102" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="102">
+      <c r="J8" s="101">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16968,13 +16967,13 @@
       <c r="G9" s="24" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="103" t="n">
+      <c r="H9" s="102" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="101">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -17005,13 +17004,13 @@
       <c r="G10" s="24" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="103" t="n">
+      <c r="H10" s="102" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="104">
+      <c r="J10" s="103">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17042,13 +17041,13 @@
       <c r="G11" s="47" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="105" t="n">
+      <c r="H11" s="104" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="47" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="106">
+      <c r="J11" s="105">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17079,13 +17078,13 @@
       <c r="G12" s="24" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="103" t="n">
+      <c r="H12" s="102" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="104">
+      <c r="J12" s="103">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17116,13 +17115,13 @@
       <c r="G13" s="47" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="105" t="n">
+      <c r="H13" s="104" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="47" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="106">
+      <c r="J13" s="105">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17153,13 +17152,13 @@
       <c r="G14" s="24" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="103" t="n">
+      <c r="H14" s="102" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="24" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="104">
+      <c r="J14" s="103">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17190,13 +17189,13 @@
       <c r="G15" s="47" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="105" t="n">
+      <c r="H15" s="104" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="47" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="106">
+      <c r="J15" s="105">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17227,13 +17226,13 @@
       <c r="G16" s="24" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="103" t="n">
+      <c r="H16" s="102" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="104">
+      <c r="J16" s="103">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17264,13 +17263,13 @@
       <c r="G17" s="47" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="105" t="n">
+      <c r="H17" s="104" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="47" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="106">
+      <c r="J17" s="105">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17301,13 +17300,13 @@
       <c r="G18" s="24" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="103" t="n">
+      <c r="H18" s="102" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="104">
+      <c r="J18" s="103">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17338,13 +17337,13 @@
       <c r="G19" s="47" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="105" t="n">
+      <c r="H19" s="104" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="47" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="106">
+      <c r="J19" s="105">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17375,13 +17374,13 @@
       <c r="G20" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="103" t="n">
+      <c r="H20" s="102" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="104">
+      <c r="J20" s="103">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17412,13 +17411,13 @@
       <c r="G21" s="47" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="105" t="n">
+      <c r="H21" s="104" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="47" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="106">
+      <c r="J21" s="105">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17447,13 +17446,13 @@
       <c r="G22" s="68" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="107" t="n">
+      <c r="H22" s="106" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="68" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="104">
+      <c r="J22" s="103">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17482,13 +17481,13 @@
       <c r="G23" s="68" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="107" t="n">
+      <c r="H23" s="106" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="104">
+      <c r="J23" s="103">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17517,13 +17516,13 @@
       <c r="G24" s="24" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="103" t="n">
+      <c r="H24" s="102" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="104">
+      <c r="J24" s="103">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17552,13 +17551,13 @@
       <c r="G25" s="24" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="103" t="n">
+      <c r="H25" s="102" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="24" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="104">
+      <c r="J25" s="103">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17587,13 +17586,13 @@
       <c r="G26" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="103" t="n">
+      <c r="H26" s="102" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="104">
+      <c r="J26" s="103">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17622,13 +17621,13 @@
       <c r="G27" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="103" t="n">
+      <c r="H27" s="102" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="24" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="104">
+      <c r="J27" s="103">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17657,13 +17656,13 @@
       <c r="G28" s="68" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="107" t="n">
+      <c r="H28" s="106" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="68" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="104">
+      <c r="J28" s="103">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17692,13 +17691,13 @@
       <c r="G29" s="44" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="108" t="n">
+      <c r="H29" s="107" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="44" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="106">
+      <c r="J29" s="105">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17727,13 +17726,13 @@
       <c r="G30" s="68" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="107" t="n">
+      <c r="H30" s="106" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="68" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="104">
+      <c r="J30" s="103">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17762,13 +17761,13 @@
       <c r="G31" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="108" t="n">
+      <c r="H31" s="107" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="44" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="106">
+      <c r="J31" s="105">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17797,13 +17796,13 @@
       <c r="G32" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="107" t="n">
+      <c r="H32" s="106" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="68" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="104">
+      <c r="J32" s="103">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17832,13 +17831,13 @@
       <c r="G33" s="44" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="108" t="n">
+      <c r="H33" s="107" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="44" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="106">
+      <c r="J33" s="105">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17867,13 +17866,13 @@
       <c r="G34" s="44" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="108" t="n">
+      <c r="H34" s="107" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="44" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="106">
+      <c r="J34" s="105">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17902,13 +17901,13 @@
       <c r="G35" s="68" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="107" t="n">
+      <c r="H35" s="106" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="104">
+      <c r="J35" s="103">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17937,13 +17936,13 @@
       <c r="G36" s="44" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="108" t="n">
+      <c r="H36" s="107" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="44" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="106">
+      <c r="J36" s="105">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17972,13 +17971,13 @@
       <c r="G37" s="68" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="107" t="n">
+      <c r="H37" s="106" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="68" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="104">
+      <c r="J37" s="103">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18007,13 +18006,13 @@
       <c r="G38" s="68" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="107" t="n">
+      <c r="H38" s="106" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="68" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="104">
+      <c r="J38" s="103">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18042,13 +18041,13 @@
       <c r="G39" s="44" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="108" t="n">
+      <c r="H39" s="107" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="44" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="106">
+      <c r="J39" s="105">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>7.1</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>-0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.02</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-0.47</v>
@@ -8693,9 +8693,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="96" t="inlineStr">
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>3.13</v>
+        <v>4.47</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>3.13</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>7.05</v>
+        <v>8.74</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>7.05</v>
@@ -9039,13 +9039,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="inlineStr">
+      <c r="A25" s="100" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>40.89</v>
+        <v>92.34</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>40.89</v>
@@ -9136,13 +9136,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="100" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>40.89</v>
+        <v>92.34</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>40.89</v>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>0.66</v>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>-1.42</v>
+        <v>-1.47</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>-1.42</v>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>68.98</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>68.98</v>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>58.52</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>58.52</v>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>6.27</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>14.46</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>65.62</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>63.73</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>60.68</v>
+        <v>60.78</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>59.76</v>
@@ -11963,9 +11963,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B52" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C52" s="96" t="inlineStr">
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>-2.16</v>
+        <v>1.12</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>-2.16</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-8.43</v>
+        <v>-6.6</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-8.43</v>
@@ -12309,13 +12309,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="100" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>43.83</v>
+        <v>83.53</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>43.83</v>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>45.92</v>
+        <v>74.97</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>45.92</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>3.06</v>
+        <v>4.35</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>3.06</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>2.34</v>
+        <v>3.46</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>2.34</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>65.67</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>65.67</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>61.14</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>61.14</v>
@@ -13057,7 +13057,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：hk50:RSI6:77.72&gt;=76</t>
+          <t>今日卖报：hk50:RSI6:77.72&gt;=76;us500:RSI2:92.34&gt;=91;us500:RSI2:92.34&gt;=85;fr40:RSI3:83.53&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>7.07</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>-0.22</v>
+        <v>-0.44</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.34</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-0.59</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>4.47</v>
+        <v>4.1</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>4.47</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>8.74</v>
+        <v>8.75</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>8.74</v>
@@ -9039,13 +9039,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="100" t="inlineStr">
+      <c r="A25" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>92.34</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>92.34</v>
@@ -9136,13 +9136,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="100" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>92.34</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>92.34</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>7.45</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>5.57</v>
+        <v>6.31</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>5.57</v>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>87.58</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>87.58</v>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>80.31</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>80.31</v>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>1.67</v>
+        <v>0.8</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>1.67</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>9.98</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>9.98</v>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>92.18000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>92.18000000000001</v>
@@ -10226,13 +10226,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="100" t="inlineStr">
+      <c r="A36" s="80" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>92.18000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>92.18000000000001</v>
@@ -11423,29 +11423,29 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C47" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="D47" s="97" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="E47" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="F47" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="G47" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="C47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G47" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="H47" s="96" t="inlineStr">
@@ -11576,22 +11576,22 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>1.66</v>
+        <v>6.69</v>
       </c>
       <c r="C48" s="99" t="n">
-        <v>1.02</v>
+        <v>5.73</v>
       </c>
       <c r="D48" s="99" t="n">
-        <v>1.28</v>
+        <v>6.27</v>
       </c>
       <c r="E48" s="99" t="n">
-        <v>3.11</v>
+        <v>7.42</v>
       </c>
       <c r="F48" s="99" t="n">
-        <v>3.04</v>
+        <v>7.48</v>
       </c>
       <c r="G48" s="99" t="n">
-        <v>3.24</v>
+        <v>6.99</v>
       </c>
       <c r="H48" s="99" t="n">
         <v>3.56</v>
@@ -11673,22 +11673,22 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>9.380000000000001</v>
+        <v>14.79</v>
       </c>
       <c r="C49" s="99" t="n">
-        <v>8.869999999999999</v>
+        <v>13.96</v>
       </c>
       <c r="D49" s="99" t="n">
-        <v>9.08</v>
+        <v>14.46</v>
       </c>
       <c r="E49" s="99" t="n">
-        <v>9.49</v>
+        <v>14.07</v>
       </c>
       <c r="F49" s="99" t="n">
-        <v>9.52</v>
+        <v>14.24</v>
       </c>
       <c r="G49" s="99" t="n">
-        <v>10.94</v>
+        <v>14.96</v>
       </c>
       <c r="H49" s="99" t="n">
         <v>11.22</v>
@@ -11770,22 +11770,22 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>56.6</v>
+        <v>76.62</v>
       </c>
       <c r="C50" s="99" t="n">
-        <v>41.91</v>
+        <v>67.89</v>
       </c>
       <c r="D50" s="99" t="n">
-        <v>34.54</v>
+        <v>66</v>
       </c>
       <c r="E50" s="99" t="n">
-        <v>42.08</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F50" s="99" t="n">
-        <v>38.97</v>
+        <v>67.34</v>
       </c>
       <c r="G50" s="99" t="n">
-        <v>43.54</v>
+        <v>66.81</v>
       </c>
       <c r="H50" s="99" t="n">
         <v>44.64</v>
@@ -11867,22 +11867,22 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>51.73</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C51" s="99" t="n">
-        <v>45.06</v>
+        <v>61.46</v>
       </c>
       <c r="D51" s="99" t="n">
-        <v>42.14</v>
+        <v>60.46</v>
       </c>
       <c r="E51" s="99" t="n">
-        <v>45.92</v>
+        <v>61.29</v>
       </c>
       <c r="F51" s="99" t="n">
-        <v>44.65</v>
+        <v>60.94</v>
       </c>
       <c r="G51" s="99" t="n">
-        <v>47.03</v>
+        <v>60.59</v>
       </c>
       <c r="H51" s="99" t="n">
         <v>47.61</v>
@@ -11963,9 +11963,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="98" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B52" s="96" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C52" s="98" t="inlineStr">
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>1.12</v>
+        <v>0.28</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>1.12</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-6.6</v>
+        <v>-7.99</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-6.6</v>
@@ -12309,13 +12309,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="100" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>83.53</v>
+        <v>48.68</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>83.53</v>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>74.97</v>
+        <v>51.58</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>74.97</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>3.16</v>
+        <v>2.66</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>4.35</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>3.46</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>57.56</v>
+        <v>50.15</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>83.09999999999999</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>58.56</v>
+        <v>52.95</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>75.06999999999999</v>
@@ -13057,7 +13057,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：hk50:RSI6:82.63&gt;=76;us500:RSI2:92.34&gt;=91;us500:RSI2:92.34&gt;=85;us30:RSI3:87.58&gt;=85;ixic:RSI2:92.18&gt;=85;fr40:RSI3:83.53&gt;=73</t>
+          <t>今日卖报：hk50:RSI6:82.63&gt;=76;us30:RSI3:88.4&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.44</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.23</v>
+        <v>-1.2</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-1.26</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>4.1</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>8.75</v>
+        <v>9.85</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>8.75</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>76.79000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>76.79000000000001</v>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>76.79000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>76.79000000000001</v>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>7.32</v>
+        <v>7.46</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>6.69</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>14.6</v>
+        <v>14.75</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>14.79</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>78.02</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>76.62</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>67.53</v>
+        <v>67.89</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>66.59999999999999</v>
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>0.28</v>
+        <v>-0.7</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>0.28</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-7.99</v>
+        <v>-6.86</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-7.99</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>48.68</v>
+        <v>50.77</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>48.68</v>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>51.58</v>
+        <v>52.83</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>51.58</v>
@@ -12508,9 +12508,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="96" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B57" s="98" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C57" s="96" t="inlineStr">
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>2.66</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>1.72</v>
+        <v>3.7</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>1.72</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>50.15</v>
+        <v>59.71</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>50.15</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>52.95</v>
+        <v>59.4</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>52.95</v>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B25" s="91" t="n">
-        <v>7.03</v>
+        <v>7.01</v>
       </c>
       <c r="C25" s="91" t="n">
         <v>7.06</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="92" t="n">
-        <v>-0.39</v>
+        <v>-0.76</v>
       </c>
       <c r="C26" s="92" t="n">
         <v>0.27</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="92" t="n">
-        <v>-1.17</v>
+        <v>-1.53</v>
       </c>
       <c r="C27" s="92" t="n">
         <v>-1.2</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="98" t="n">
-        <v>4.3</v>
+        <v>4.99</v>
       </c>
       <c r="C23" s="98" t="n">
         <v>4.3</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="98" t="n">
-        <v>9.85</v>
+        <v>10.01</v>
       </c>
       <c r="C24" s="98" t="n">
         <v>9.85</v>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B25" s="98" t="n">
-        <v>84.39</v>
+        <v>90.16</v>
       </c>
       <c r="C25" s="98" t="n">
         <v>84.39</v>
@@ -9135,13 +9135,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="99" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="98" t="n">
-        <v>84.39</v>
+        <v>90.16</v>
       </c>
       <c r="C26" s="98" t="n">
         <v>84.39</v>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="B48" s="98" t="n">
-        <v>6.81</v>
+        <v>6.84</v>
       </c>
       <c r="C48" s="98" t="n">
         <v>7.46</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B49" s="98" t="n">
-        <v>14.87</v>
+        <v>14.9</v>
       </c>
       <c r="C49" s="98" t="n">
         <v>14.75</v>
@@ -11769,7 +11769,7 @@
         </is>
       </c>
       <c r="B50" s="98" t="n">
-        <v>83.05</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C50" s="98" t="n">
         <v>84.20999999999999</v>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="B51" s="98" t="n">
-        <v>72.28</v>
+        <v>72.53</v>
       </c>
       <c r="C51" s="98" t="n">
         <v>72.69</v>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="98" t="n">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="C53" s="98" t="n">
         <v>-0.7</v>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="98" t="n">
-        <v>-6.01</v>
+        <v>-6.35</v>
       </c>
       <c r="C54" s="98" t="n">
         <v>-6.86</v>
@@ -12308,13 +12308,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="99" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="98" t="n">
-        <v>74.93000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="C55" s="98" t="n">
         <v>50.77</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="98" t="n">
-        <v>68.72</v>
+        <v>66.2</v>
       </c>
       <c r="C56" s="98" t="n">
         <v>52.83</v>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="98" t="n">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
       <c r="C58" s="98" t="n">
         <v>3.04</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="98" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="C59" s="98" t="n">
         <v>3.7</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="98" t="n">
-        <v>67.98</v>
+        <v>69.06</v>
       </c>
       <c r="C60" s="98" t="n">
         <v>59.71</v>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="98" t="n">
-        <v>65.18000000000001</v>
+        <v>66</v>
       </c>
       <c r="C61" s="98" t="n">
         <v>59.4</v>
@@ -13056,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="94" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RSI2:99.4&gt;=96;cy:RSI9:69.36&gt;=65;hk50:RSI6:90.64&gt;=76;us30:RSI3:89.99&gt;=85;jp225:RSI5:76.04&gt;=74;fr40:RSI3:74.93&gt;=73</t>
+          <t>今日卖报：sh:RSI2:99.4&gt;=96;cy:RSI9:69.36&gt;=65;hk50:RSI6:90.64&gt;=76;us500:RSI2:90.16&gt;=85;us30:RSI3:89.99&gt;=85;jp225:RSI5:76.04&gt;=74</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>7.02</v>
+        <v>7.03</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>7</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.84</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.43</v>
+        <v>-1.3</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-1.61</v>
@@ -8692,9 +8692,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="96" t="inlineStr">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>4.99</v>
+        <v>4.51</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>4.99</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>10.01</v>
+        <v>11.17</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>10.01</v>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>90.16</v>
+        <v>58.19</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>90.16</v>
@@ -9135,13 +9135,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="91" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>90.16</v>
+        <v>58.19</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>90.16</v>
@@ -9237,9 +9237,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B27" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C27" s="96" t="inlineStr">
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>7.9</v>
+        <v>7.01</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>7.9</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>7.87</v>
+        <v>8.6</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>7.87</v>
@@ -9583,13 +9583,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="91" t="inlineStr">
+      <c r="A30" s="80" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>92.18000000000001</v>
+        <v>42.84</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>92.18000000000001</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>84.20999999999999</v>
+        <v>57.58</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>84.20999999999999</v>
@@ -9782,9 +9782,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B32" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="96" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>1.93</v>
+        <v>1.13</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>1.93</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>11.04</v>
+        <v>12.67</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>11.04</v>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>88.93000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>88.93000000000001</v>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>88.93000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>88.93000000000001</v>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>7.17</v>
+        <v>7.21</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>6.84</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>15.24</v>
+        <v>15.29</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>14.9</v>
@@ -11769,7 +11769,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>85.18000000000001</v>
+        <v>85.37</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>83.76000000000001</v>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>73.5</v>
+        <v>73.63</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>72.53</v>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>0.87</v>
+        <v>-0.87</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>0.87</v>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-6.35</v>
+        <v>-6.01</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-6.35</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>71.87</v>
+        <v>57.16</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>71.87</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>66.2</v>
+        <v>57.98</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>66.2</v>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>4.58</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>4.76</v>
+        <v>4.66</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>3.7</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>61.48</v>
+        <v>59.47</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>69.06</v>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>61.24</v>
+        <v>59.91</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>66</v>
@@ -13056,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RSI2:99.61&gt;=96;cy:RSI9:73.8&gt;=65;hk50:RSI6:91.5&gt;=76;us500:RSI2:90.16&gt;=85;us30:RSI3:92.18&gt;=85;ixic:RSI2:88.93&gt;=85;vn:RSI3:88.0&gt;=85</t>
+          <t>今日卖报：sh:RSI2:99.61&gt;=96;cy:RSI9:73.8&gt;=65;hk50:RSI6:91.5&gt;=76;ixic:RSI2:89.75&gt;=85;vn:RSI3:88.0&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>6.99</v>
+        <v>6.97</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>7.03</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>-0.59</v>
+        <v>-0.86</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>0.49</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.81</v>
+        <v>-2.07</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-1.27</v>
@@ -4585,22 +4585,22 @@
         </is>
       </c>
       <c r="B32" s="89" t="n">
-        <v>0</v>
+        <v>-39170</v>
       </c>
       <c r="C32" s="89" t="n">
-        <v>0</v>
+        <v>-25624</v>
       </c>
       <c r="D32" s="89" t="n">
-        <v>0</v>
+        <v>-27286</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>0</v>
+        <v>-15398</v>
       </c>
       <c r="F32" s="89" t="n">
-        <v>0</v>
+        <v>-19443</v>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0</v>
+        <v>-32280</v>
       </c>
       <c r="H32" s="89" t="n">
         <v>-23022</v>
@@ -4645,7 +4645,7 @@
         <v>-26728</v>
       </c>
       <c r="V32" s="89" t="n">
-        <v>0</v>
+        <v>-25843</v>
       </c>
       <c r="W32" s="89" t="n">
         <v>-30256</v>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="B33" s="89" t="n">
-        <v>0</v>
+        <v>703</v>
       </c>
       <c r="C33" s="89" t="n">
-        <v>0</v>
+        <v>7134</v>
       </c>
       <c r="D33" s="89" t="n">
-        <v>0</v>
+        <v>6476</v>
       </c>
       <c r="E33" s="89" t="n">
-        <v>0</v>
+        <v>13199</v>
       </c>
       <c r="F33" s="89" t="n">
-        <v>0</v>
+        <v>12591</v>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0</v>
+        <v>9543</v>
       </c>
       <c r="H33" s="89" t="n">
-        <v>7141</v>
+        <v>10679</v>
       </c>
       <c r="I33" s="89" t="n">
         <v>7507</v>
@@ -4742,7 +4742,7 @@
         <v>-3908</v>
       </c>
       <c r="V33" s="89" t="n">
-        <v>0</v>
+        <v>-2374</v>
       </c>
       <c r="W33" s="89" t="n">
         <v>-4680</v>
@@ -4779,22 +4779,22 @@
         </is>
       </c>
       <c r="B34" s="89" t="n">
-        <v>0</v>
+        <v>-28243</v>
       </c>
       <c r="C34" s="89" t="n">
-        <v>0</v>
+        <v>-19887</v>
       </c>
       <c r="D34" s="89" t="n">
-        <v>0</v>
+        <v>-21792</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>0</v>
+        <v>-16942</v>
       </c>
       <c r="F34" s="89" t="n">
-        <v>0</v>
+        <v>-18355</v>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0</v>
+        <v>-21603</v>
       </c>
       <c r="H34" s="89" t="n">
         <v>-20550</v>
@@ -4839,7 +4839,7 @@
         <v>-27546</v>
       </c>
       <c r="V34" s="89" t="n">
-        <v>0</v>
+        <v>-28104</v>
       </c>
       <c r="W34" s="89" t="n">
         <v>-29738</v>
@@ -4876,25 +4876,25 @@
         </is>
       </c>
       <c r="B35" s="89" t="n">
-        <v>0</v>
+        <v>-8727</v>
       </c>
       <c r="C35" s="89" t="n">
-        <v>0</v>
+        <v>-6282</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0</v>
+        <v>-6639</v>
       </c>
       <c r="E35" s="89" t="n">
-        <v>0</v>
+        <v>-3532</v>
       </c>
       <c r="F35" s="89" t="n">
-        <v>0</v>
+        <v>-2293</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0</v>
+        <v>-4574</v>
       </c>
       <c r="H35" s="89" t="n">
-        <v>-234</v>
+        <v>-2414</v>
       </c>
       <c r="I35" s="89" t="n">
         <v>-2494</v>
@@ -4936,7 +4936,7 @@
         <v>-12337</v>
       </c>
       <c r="V35" s="89" t="n">
-        <v>0</v>
+        <v>-14270</v>
       </c>
       <c r="W35" s="89" t="n">
         <v>-15565</v>
@@ -4973,25 +4973,25 @@
         </is>
       </c>
       <c r="B36" s="89" t="n">
-        <v>0</v>
+        <v>52065</v>
       </c>
       <c r="C36" s="89" t="n">
-        <v>0</v>
+        <v>44830</v>
       </c>
       <c r="D36" s="89" t="n">
-        <v>0</v>
+        <v>44611</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>0</v>
+        <v>43465</v>
       </c>
       <c r="F36" s="89" t="n">
-        <v>0</v>
+        <v>43814</v>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0</v>
+        <v>41323</v>
       </c>
       <c r="H36" s="89" t="n">
-        <v>31833</v>
+        <v>33152</v>
       </c>
       <c r="I36" s="89" t="n">
         <v>45049</v>
@@ -5033,7 +5033,7 @@
         <v>86384</v>
       </c>
       <c r="V36" s="89" t="n">
-        <v>0</v>
+        <v>87972</v>
       </c>
       <c r="W36" s="89" t="n">
         <v>91967</v>
@@ -5070,22 +5070,22 @@
         </is>
       </c>
       <c r="B37" s="89" t="n">
-        <v>0</v>
+        <v>138990</v>
       </c>
       <c r="C37" s="89" t="n">
-        <v>0</v>
+        <v>124265</v>
       </c>
       <c r="D37" s="89" t="n">
-        <v>0</v>
+        <v>129855</v>
       </c>
       <c r="E37" s="89" t="n">
-        <v>0</v>
+        <v>121593</v>
       </c>
       <c r="F37" s="89" t="n">
-        <v>0</v>
+        <v>126065</v>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0</v>
+        <v>114091</v>
       </c>
       <c r="H37" s="89" t="n">
         <v>120465</v>
@@ -5130,7 +5130,7 @@
         <v>129278</v>
       </c>
       <c r="V37" s="89" t="n">
-        <v>0</v>
+        <v>129820</v>
       </c>
       <c r="W37" s="89" t="n">
         <v>127965</v>
@@ -5167,22 +5167,22 @@
         </is>
       </c>
       <c r="B38" s="89" t="n">
-        <v>0</v>
+        <v>57916</v>
       </c>
       <c r="C38" s="89" t="n">
-        <v>0</v>
+        <v>54008</v>
       </c>
       <c r="D38" s="89" t="n">
-        <v>0</v>
+        <v>52754</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>0</v>
+        <v>49457</v>
       </c>
       <c r="F38" s="89" t="n">
-        <v>0</v>
+        <v>49214</v>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0</v>
+        <v>51881</v>
       </c>
       <c r="H38" s="89" t="n">
         <v>48370</v>
@@ -5227,7 +5227,7 @@
         <v>51534</v>
       </c>
       <c r="V38" s="89" t="n">
-        <v>0</v>
+        <v>50630</v>
       </c>
       <c r="W38" s="89" t="n">
         <v>51651</v>
@@ -5264,25 +5264,25 @@
         </is>
       </c>
       <c r="B39" s="89" t="n">
-        <v>0</v>
+        <v>16231</v>
       </c>
       <c r="C39" s="89" t="n">
-        <v>0</v>
+        <v>13658</v>
       </c>
       <c r="D39" s="89" t="n">
-        <v>0</v>
+        <v>16239</v>
       </c>
       <c r="E39" s="89" t="n">
-        <v>0</v>
+        <v>13971</v>
       </c>
       <c r="F39" s="89" t="n">
-        <v>0</v>
+        <v>15254</v>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0</v>
+        <v>13966</v>
       </c>
       <c r="H39" s="89" t="n">
-        <v>9909</v>
+        <v>9839</v>
       </c>
       <c r="I39" s="89" t="n">
         <v>16729</v>
@@ -5324,7 +5324,7 @@
         <v>33944</v>
       </c>
       <c r="V39" s="89" t="n">
-        <v>0</v>
+        <v>34381</v>
       </c>
       <c r="W39" s="89" t="n">
         <v>35985</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>4.51</v>
+        <v>4.29</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>4.51</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>11.17</v>
+        <v>10.4</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>11.17</v>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>58.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>58.19</v>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>58.19</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>58.19</v>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>-0.16</v>
+        <v>0.6</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>-0.87</v>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-4.5</v>
+        <v>-3.77</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-6.01</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>77.97</v>
+        <v>82.23</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>57.16</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>71.56</v>
+        <v>75.48</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>57.98</v>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>3.85</v>
+        <v>4.17</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>2.96</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>5.88</v>
+        <v>6.2</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>4.66</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>74.28</v>
+        <v>76.37</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>59.47</v>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>70.18000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>59.91</v>
@@ -13056,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RSI2:99.88&gt;=96;kc:RSI5:81.49&gt;=65;cy:RSI9:81.96&gt;=65;hk50:RSI6:94.93&gt;=76;hk50:RSI19:77.11&gt;=73;ixic:RSI2:89.75&gt;=85;jp225:RSI5:84.76&gt;=74;vn:RSI3:90.49&gt;=85;fr40:RSI3:77.97&gt;=73</t>
+          <t>今日卖报：sh:RSI2:99.88&gt;=96;kc:RSI5:81.49&gt;=65;cy:RSI9:81.96&gt;=65;hk50:RSI6:94.93&gt;=76;hk50:RSI19:77.11&gt;=73;ixic:RSI2:89.75&gt;=85;jp225:RSI5:84.76&gt;=74;vn:RSI3:90.49&gt;=85;fr40:RSI3:82.23&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>-0.79</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-2.09</v>
+        <v>-2.1</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-2</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>4.29</v>
+        <v>3.63</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>4.29</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>10.4</v>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>83.51000000000001</v>
+        <v>60.63</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>83.51000000000001</v>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>83.51000000000001</v>
+        <v>60.63</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>83.51000000000001</v>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>7.23</v>
+        <v>7.64</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>7.23</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>8.41</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>8.41</v>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>66.62</v>
+        <v>74.91</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>66.62</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>68.59</v>
+        <v>73.2</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>68.59</v>
@@ -9782,9 +9782,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B32" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="96" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>0.9</v>
+        <v>-0.38</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>0.9</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>11.95</v>
+        <v>11.48</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>11.95</v>
@@ -10128,13 +10128,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="91" t="inlineStr">
+      <c r="A35" s="80" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>96.66</v>
+        <v>51.35</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>96.66</v>
@@ -10225,13 +10225,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="91" t="inlineStr">
+      <c r="A36" s="80" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>96.66</v>
+        <v>51.35</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>96.66</v>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>1.71</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>1.83</v>
@@ -11224,7 +11224,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>91.40000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>90.48999999999999</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>81.47</v>
+        <v>78.83</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>80.52</v>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>0.6</v>
+        <v>1.51</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>0.6</v>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-3.77</v>
+        <v>-2.89</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-3.77</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>82.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>82.23</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>75.48</v>
+        <v>78.61</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>75.48</v>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>4.27</v>
+        <v>5.4</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>4.27</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>6.31</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>6.31</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>76.95</v>
+        <v>83.8</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>76.95</v>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>72.42</v>
+        <v>78.38</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>72.42</v>
@@ -13056,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RSI2:99.94&gt;=96;kc:RSI10:78.56&gt;=76;kc:RSI5:91.07&gt;=65;cy:RSI9:90.12&gt;=65;hk50:RSI6:96.46&gt;=76;hk50:RSI19:80.68&gt;=73;ixic:RSI2:96.66&gt;=95;ixic:RSI2:96.66&gt;=85;jp225:RSI5:89.62&gt;=74;vn:RSI3:91.4&gt;=85;fr40:RSI3:82.23&gt;=73</t>
+          <t>今日卖报：sh:RSI2:99.94&gt;=96;kc:RSI10:78.56&gt;=76;kc:RSI5:91.07&gt;=65;cy:RSI9:90.12&gt;=65;hk50:RSI6:96.46&gt;=76;hk50:RSI19:80.68&gt;=73;jp225:RSI5:89.62&gt;=74;vn:RSI3:86.66&gt;=85;fr40:RSI3:85.76&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>6.98</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>0.02</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.35</v>
+        <v>-1.18</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-2.1</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>3.63</v>
+        <v>3.51</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>3.63</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>10.3</v>
+        <v>10.61</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>10.3</v>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>60.63</v>
+        <v>86.19</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>60.63</v>
@@ -9135,13 +9135,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>60.63</v>
+        <v>86.19</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>60.63</v>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>7.64</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>8.789999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>8.789999999999999</v>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>74.91</v>
+        <v>76.02</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>74.91</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>73.2</v>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>-0.38</v>
+        <v>-0.89</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>-0.38</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>11.48</v>
+        <v>11.54</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>11.48</v>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>51.35</v>
+        <v>74.7</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>51.35</v>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>51.35</v>
+        <v>74.7</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>51.35</v>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>1.1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>2.85</v>
@@ -11224,7 +11224,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>67.92</v>
+        <v>65.09</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>86.66</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>70.78</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>78.83</v>
@@ -11962,9 +11962,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B52" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C52" s="96" t="inlineStr">
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>1.51</v>
+        <v>0.11</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>1.51</v>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-2.89</v>
+        <v>-4.68</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-2.89</v>
@@ -12308,13 +12308,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="86" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>85.76000000000001</v>
+        <v>44.35</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>85.76000000000001</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>78.61</v>
+        <v>52.35</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>78.61</v>
@@ -12507,9 +12507,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B57" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C57" s="96" t="inlineStr">
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>5.12</v>
+        <v>4.62</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>5.4</v>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>8.289999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>8.460000000000001</v>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>76.53</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>83.8</v>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>73.8</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>78.38</v>
@@ -13056,7 +13056,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:17.23&gt;=15;hk50:RNG120:26.37&gt;=25;hk50:RSI6:97.18&gt;=76;hk50:RSI19:82.69&gt;=73;fr40:RSI3:85.76&gt;=73</t>
+          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:17.23&gt;=15;hk50:RNG120:26.37&gt;=25;hk50:RSI6:97.18&gt;=76;hk50:RSI19:82.69&gt;=73;us500:RSI2:86.19&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B25" s="92" t="n">
-        <v>7</v>
+        <v>7.01</v>
       </c>
       <c r="C25" s="92" t="n">
         <v>6.98</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="B26" s="93" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="C26" s="93" t="n">
         <v>0.02</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>-1.18</v>
+        <v>-1.11</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>-2.1</v>
@@ -6357,152 +6357,152 @@
       </c>
       <c r="B1" s="81" t="inlineStr">
         <is>
+          <t>241001</t>
+        </is>
+      </c>
+      <c r="C1" s="81" t="inlineStr">
+        <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="T1" s="81" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="T1" s="81" t="inlineStr">
+      <c r="U1" s="81" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="U1" s="81" t="inlineStr">
+      <c r="V1" s="81" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="V1" s="81" t="inlineStr">
+      <c r="W1" s="81" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="W1" s="81" t="inlineStr">
+      <c r="X1" s="81" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="X1" s="81" t="inlineStr">
+      <c r="Y1" s="81" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="Y1" s="81" t="inlineStr">
+      <c r="Z1" s="81" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="Z1" s="81" t="inlineStr">
+      <c r="AA1" s="81" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="AA1" s="81" t="inlineStr">
+      <c r="AB1" s="81" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="AB1" s="81" t="inlineStr">
+      <c r="AC1" s="81" t="inlineStr">
         <is>
           <t>240823</t>
         </is>
       </c>
-      <c r="AC1" s="81" t="inlineStr">
+      <c r="AD1" s="81" t="inlineStr">
         <is>
           <t>240822</t>
         </is>
       </c>
-      <c r="AD1" s="81" t="inlineStr">
+      <c r="AE1" s="81" t="inlineStr">
         <is>
           <t>240821</t>
-        </is>
-      </c>
-      <c r="AE1" s="81" t="inlineStr">
-        <is>
-          <t>240820</t>
         </is>
       </c>
     </row>
@@ -6537,114 +6537,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G2" s="97" t="inlineStr">
+      <c r="G2" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="97" t="inlineStr">
+      <c r="I2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="97" t="inlineStr">
+      <c r="J2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="97" t="inlineStr">
+      <c r="K2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="98" t="inlineStr">
+      <c r="L2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L2" s="98" t="inlineStr">
+      <c r="M2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="N2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="98" t="inlineStr">
+      <c r="O2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="98" t="inlineStr">
+      <c r="P2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="98" t="inlineStr">
+      <c r="Q2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="98" t="inlineStr">
+      <c r="R2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="98" t="inlineStr">
+      <c r="S2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="98" t="inlineStr">
+      <c r="T2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="98" t="inlineStr">
+      <c r="U2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="98" t="inlineStr">
+      <c r="V2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="98" t="inlineStr">
+      <c r="W2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="97" t="inlineStr">
+      <c r="X2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X2" s="98" t="inlineStr">
+      <c r="Y2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="98" t="inlineStr">
+      <c r="Z2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="98" t="inlineStr">
+      <c r="AA2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="97" t="inlineStr">
+      <c r="AB2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB2" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC2" s="98" t="inlineStr">
@@ -6673,31 +6673,31 @@
         <v>12.81</v>
       </c>
       <c r="C3" s="99" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="D3" s="99" t="n">
         <v>3.53</v>
       </c>
-      <c r="D3" s="99" t="n">
+      <c r="E3" s="99" t="n">
         <v>0.13</v>
       </c>
-      <c r="E3" s="99" t="n">
+      <c r="F3" s="99" t="n">
         <v>-3.29</v>
       </c>
-      <c r="F3" s="99" t="n">
+      <c r="G3" s="99" t="n">
         <v>-3.51</v>
       </c>
-      <c r="G3" s="99" t="n">
+      <c r="H3" s="99" t="n">
         <v>-6.68</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="I3" s="99" t="n">
         <v>-7.93</v>
       </c>
-      <c r="I3" s="99" t="n">
+      <c r="J3" s="99" t="n">
         <v>-7.25</v>
       </c>
-      <c r="J3" s="99" t="n">
+      <c r="K3" s="99" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="K3" s="99" t="n">
-        <v>-9.81</v>
       </c>
       <c r="L3" s="99" t="n">
         <v>-9.81</v>
@@ -6706,58 +6706,58 @@
         <v>-9.81</v>
       </c>
       <c r="N3" s="99" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="O3" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="O3" s="99" t="n">
+      <c r="P3" s="99" t="n">
         <v>-9.82</v>
       </c>
-      <c r="P3" s="99" t="n">
+      <c r="Q3" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="Q3" s="99" t="n">
+      <c r="R3" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="R3" s="99" t="n">
+      <c r="S3" s="99" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="S3" s="99" t="n">
+      <c r="T3" s="99" t="n">
         <v>-7.94</v>
       </c>
-      <c r="T3" s="99" t="n">
+      <c r="U3" s="99" t="n">
         <v>-8.34</v>
       </c>
-      <c r="U3" s="99" t="n">
+      <c r="V3" s="99" t="n">
         <v>-7.43</v>
       </c>
-      <c r="V3" s="99" t="n">
+      <c r="W3" s="99" t="n">
         <v>-7.87</v>
       </c>
-      <c r="W3" s="99" t="n">
+      <c r="X3" s="99" t="n">
         <v>-6.78</v>
       </c>
-      <c r="X3" s="99" t="n">
+      <c r="Y3" s="99" t="n">
         <v>-7.9</v>
       </c>
-      <c r="Y3" s="99" t="n">
+      <c r="Z3" s="99" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="Z3" s="99" t="n">
+      <c r="AA3" s="99" t="n">
         <v>-7.46</v>
       </c>
-      <c r="AA3" s="99" t="n">
+      <c r="AB3" s="99" t="n">
         <v>-7.49</v>
       </c>
-      <c r="AB3" s="99" t="n">
+      <c r="AC3" s="99" t="n">
         <v>-7.68</v>
       </c>
-      <c r="AC3" s="99" t="n">
+      <c r="AD3" s="99" t="n">
         <v>-8.43</v>
       </c>
-      <c r="AD3" s="99" t="n">
+      <c r="AE3" s="99" t="n">
         <v>-8.140000000000001</v>
-      </c>
-      <c r="AE3" s="99" t="n">
-        <v>-8.24</v>
       </c>
     </row>
     <row r="4">
@@ -6770,31 +6770,31 @@
         <v>8.710000000000001</v>
       </c>
       <c r="C4" s="99" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="D4" s="99" t="n">
         <v>0.41</v>
       </c>
-      <c r="D4" s="99" t="n">
+      <c r="E4" s="99" t="n">
         <v>-2.48</v>
       </c>
-      <c r="E4" s="99" t="n">
+      <c r="F4" s="99" t="n">
         <v>-4.76</v>
       </c>
-      <c r="F4" s="99" t="n">
+      <c r="G4" s="99" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G4" s="99" t="n">
+      <c r="H4" s="99" t="n">
         <v>-8.16</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="I4" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="I4" s="99" t="n">
+      <c r="J4" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="J4" s="99" t="n">
+      <c r="K4" s="99" t="n">
         <v>-10.85</v>
-      </c>
-      <c r="K4" s="99" t="n">
-        <v>-12.12</v>
       </c>
       <c r="L4" s="99" t="n">
         <v>-12.12</v>
@@ -6803,58 +6803,58 @@
         <v>-12.12</v>
       </c>
       <c r="N4" s="99" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="O4" s="99" t="n">
         <v>-11.77</v>
       </c>
-      <c r="O4" s="99" t="n">
+      <c r="P4" s="99" t="n">
         <v>-11.13</v>
       </c>
-      <c r="P4" s="99" t="n">
+      <c r="Q4" s="99" t="n">
         <v>-11.05</v>
       </c>
-      <c r="Q4" s="99" t="n">
+      <c r="R4" s="99" t="n">
         <v>-10.42</v>
       </c>
-      <c r="R4" s="99" t="n">
+      <c r="S4" s="99" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="S4" s="99" t="n">
+      <c r="T4" s="99" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="T4" s="99" t="n">
+      <c r="U4" s="99" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="U4" s="99" t="n">
+      <c r="V4" s="99" t="n">
         <v>-8.65</v>
       </c>
-      <c r="V4" s="99" t="n">
+      <c r="W4" s="99" t="n">
         <v>-7.71</v>
       </c>
-      <c r="W4" s="99" t="n">
+      <c r="X4" s="99" t="n">
         <v>-6.12</v>
       </c>
-      <c r="X4" s="99" t="n">
+      <c r="Y4" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="Y4" s="99" t="n">
+      <c r="Z4" s="99" t="n">
         <v>-6.9</v>
       </c>
-      <c r="Z4" s="99" t="n">
+      <c r="AA4" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AA4" s="99" t="n">
+      <c r="AB4" s="99" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AB4" s="99" t="n">
+      <c r="AC4" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="AC4" s="99" t="n">
+      <c r="AD4" s="99" t="n">
         <v>-3.69</v>
       </c>
-      <c r="AD4" s="99" t="n">
+      <c r="AE4" s="99" t="n">
         <v>-5.27</v>
-      </c>
-      <c r="AE4" s="99" t="n">
-        <v>-3.71</v>
       </c>
     </row>
     <row r="5">
@@ -6867,31 +6867,31 @@
         <v>91.05</v>
       </c>
       <c r="C5" s="99" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="D5" s="99" t="n">
         <v>84.84</v>
       </c>
-      <c r="D5" s="99" t="n">
+      <c r="E5" s="99" t="n">
         <v>80.58</v>
       </c>
-      <c r="E5" s="99" t="n">
+      <c r="F5" s="99" t="n">
         <v>71.91</v>
       </c>
-      <c r="F5" s="99" t="n">
+      <c r="G5" s="99" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="G5" s="99" t="n">
+      <c r="H5" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="I5" s="99" t="n">
         <v>34.66</v>
       </c>
-      <c r="I5" s="99" t="n">
+      <c r="J5" s="99" t="n">
         <v>34.31</v>
       </c>
-      <c r="J5" s="99" t="n">
+      <c r="K5" s="99" t="n">
         <v>25.68</v>
-      </c>
-      <c r="K5" s="99" t="n">
-        <v>18.87</v>
       </c>
       <c r="L5" s="99" t="n">
         <v>18.87</v>
@@ -6900,58 +6900,58 @@
         <v>18.87</v>
       </c>
       <c r="N5" s="99" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="O5" s="99" t="n">
         <v>20.56</v>
       </c>
-      <c r="O5" s="99" t="n">
+      <c r="P5" s="99" t="n">
         <v>21.18</v>
       </c>
-      <c r="P5" s="99" t="n">
+      <c r="Q5" s="99" t="n">
         <v>24.39</v>
       </c>
-      <c r="Q5" s="99" t="n">
+      <c r="R5" s="99" t="n">
         <v>20.64</v>
       </c>
-      <c r="R5" s="99" t="n">
+      <c r="S5" s="99" t="n">
         <v>24.91</v>
       </c>
-      <c r="S5" s="99" t="n">
+      <c r="T5" s="99" t="n">
         <v>29.13</v>
       </c>
-      <c r="T5" s="99" t="n">
+      <c r="U5" s="99" t="n">
         <v>27.12</v>
       </c>
-      <c r="U5" s="99" t="n">
+      <c r="V5" s="99" t="n">
         <v>30.8</v>
       </c>
-      <c r="V5" s="99" t="n">
+      <c r="W5" s="99" t="n">
         <v>32.53</v>
       </c>
-      <c r="W5" s="99" t="n">
+      <c r="X5" s="99" t="n">
         <v>40.52</v>
       </c>
-      <c r="X5" s="99" t="n">
+      <c r="Y5" s="99" t="n">
         <v>31.09</v>
       </c>
-      <c r="Y5" s="99" t="n">
+      <c r="Z5" s="99" t="n">
         <v>34.85</v>
       </c>
-      <c r="Z5" s="99" t="n">
+      <c r="AA5" s="99" t="n">
         <v>38.18</v>
       </c>
-      <c r="AA5" s="99" t="n">
+      <c r="AB5" s="99" t="n">
         <v>40.27</v>
       </c>
-      <c r="AB5" s="99" t="n">
+      <c r="AC5" s="99" t="n">
         <v>39.76</v>
       </c>
-      <c r="AC5" s="99" t="n">
+      <c r="AD5" s="99" t="n">
         <v>37.4</v>
       </c>
-      <c r="AD5" s="99" t="n">
+      <c r="AE5" s="99" t="n">
         <v>39.36</v>
-      </c>
-      <c r="AE5" s="99" t="n">
-        <v>41.93</v>
       </c>
     </row>
     <row r="6">
@@ -6964,31 +6964,31 @@
         <v>99.98999999999999</v>
       </c>
       <c r="C6" s="99" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D6" s="99" t="n">
         <v>99.94</v>
       </c>
-      <c r="D6" s="99" t="n">
+      <c r="E6" s="99" t="n">
         <v>99.88</v>
       </c>
-      <c r="E6" s="99" t="n">
+      <c r="F6" s="99" t="n">
         <v>99.61</v>
       </c>
-      <c r="F6" s="99" t="n">
+      <c r="G6" s="99" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="G6" s="99" t="n">
+      <c r="H6" s="99" t="n">
         <v>92.72</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="I6" s="99" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="I6" s="99" t="n">
+      <c r="J6" s="99" t="n">
         <v>81.17</v>
       </c>
-      <c r="J6" s="99" t="n">
+      <c r="K6" s="99" t="n">
         <v>53.59</v>
-      </c>
-      <c r="K6" s="99" t="n">
-        <v>4.21</v>
       </c>
       <c r="L6" s="99" t="n">
         <v>4.21</v>
@@ -6997,58 +6997,58 @@
         <v>4.21</v>
       </c>
       <c r="N6" s="99" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="O6" s="99" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="O6" s="99" t="n">
+      <c r="P6" s="99" t="n">
         <v>11.08</v>
       </c>
-      <c r="P6" s="99" t="n">
+      <c r="Q6" s="99" t="n">
         <v>27.27</v>
       </c>
-      <c r="Q6" s="99" t="n">
+      <c r="R6" s="99" t="n">
         <v>2.86</v>
       </c>
-      <c r="R6" s="99" t="n">
+      <c r="S6" s="99" t="n">
         <v>7.92</v>
       </c>
-      <c r="S6" s="99" t="n">
+      <c r="T6" s="99" t="n">
         <v>24.73</v>
       </c>
-      <c r="T6" s="99" t="n">
+      <c r="U6" s="99" t="n">
         <v>7.06</v>
       </c>
-      <c r="U6" s="99" t="n">
+      <c r="V6" s="99" t="n">
         <v>15.5</v>
       </c>
-      <c r="V6" s="99" t="n">
+      <c r="W6" s="99" t="n">
         <v>20.88</v>
       </c>
-      <c r="W6" s="99" t="n">
+      <c r="X6" s="99" t="n">
         <v>63.5</v>
       </c>
-      <c r="X6" s="99" t="n">
+      <c r="Y6" s="99" t="n">
         <v>2.54</v>
       </c>
-      <c r="Y6" s="99" t="n">
+      <c r="Z6" s="99" t="n">
         <v>6.81</v>
       </c>
-      <c r="Z6" s="99" t="n">
+      <c r="AA6" s="99" t="n">
         <v>20.06</v>
       </c>
-      <c r="AA6" s="99" t="n">
+      <c r="AB6" s="99" t="n">
         <v>48.33</v>
       </c>
-      <c r="AB6" s="99" t="n">
+      <c r="AC6" s="99" t="n">
         <v>41.33</v>
       </c>
-      <c r="AC6" s="99" t="n">
+      <c r="AD6" s="99" t="n">
         <v>12.42</v>
       </c>
-      <c r="AD6" s="99" t="n">
+      <c r="AE6" s="99" t="n">
         <v>18.92</v>
-      </c>
-      <c r="AE6" s="99" t="n">
-        <v>28.57</v>
       </c>
     </row>
     <row r="7">
@@ -7082,99 +7082,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G7" s="98" t="inlineStr">
+      <c r="G7" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H7" s="97" t="inlineStr">
+      <c r="I7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I7" s="97" t="inlineStr">
+      <c r="J7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J7" s="98" t="inlineStr">
+      <c r="K7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K7" s="97" t="inlineStr">
+      <c r="L7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L7" s="97" t="inlineStr">
+      <c r="M7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M7" s="97" t="inlineStr">
+      <c r="N7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N7" s="97" t="inlineStr">
+      <c r="O7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="97" t="inlineStr">
+      <c r="P7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P7" s="97" t="inlineStr">
+      <c r="Q7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q7" s="98" t="inlineStr">
+      <c r="R7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R7" s="98" t="inlineStr">
+      <c r="S7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S7" s="97" t="inlineStr">
+      <c r="T7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T7" s="97" t="inlineStr">
+      <c r="U7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U7" s="97" t="inlineStr">
+      <c r="V7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V7" s="98" t="inlineStr">
+      <c r="W7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W7" s="96" t="inlineStr">
+      <c r="X7" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X7" s="97" t="inlineStr">
+      <c r="Y7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Y7" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="Z7" s="98" t="inlineStr">
@@ -7218,31 +7218,31 @@
         <v>26.36</v>
       </c>
       <c r="C8" s="99" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D8" s="99" t="n">
         <v>5.45</v>
       </c>
-      <c r="D8" s="99" t="n">
+      <c r="E8" s="99" t="n">
         <v>-0.85</v>
       </c>
-      <c r="E8" s="99" t="n">
+      <c r="F8" s="99" t="n">
         <v>-5.96</v>
       </c>
-      <c r="F8" s="99" t="n">
+      <c r="G8" s="99" t="n">
         <v>-6.32</v>
       </c>
-      <c r="G8" s="99" t="n">
+      <c r="H8" s="99" t="n">
         <v>-10.11</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="I8" s="99" t="n">
         <v>-11.14</v>
       </c>
-      <c r="I8" s="99" t="n">
+      <c r="J8" s="99" t="n">
         <v>-9.23</v>
       </c>
-      <c r="J8" s="99" t="n">
+      <c r="K8" s="99" t="n">
         <v>-12.41</v>
-      </c>
-      <c r="K8" s="99" t="n">
-        <v>-13.62</v>
       </c>
       <c r="L8" s="99" t="n">
         <v>-13.62</v>
@@ -7251,58 +7251,58 @@
         <v>-13.62</v>
       </c>
       <c r="N8" s="99" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="O8" s="99" t="n">
         <v>-12.75</v>
       </c>
-      <c r="O8" s="99" t="n">
+      <c r="P8" s="99" t="n">
         <v>-11.62</v>
       </c>
-      <c r="P8" s="99" t="n">
+      <c r="Q8" s="99" t="n">
         <v>-12.8</v>
       </c>
-      <c r="Q8" s="99" t="n">
+      <c r="R8" s="99" t="n">
         <v>-13.49</v>
       </c>
-      <c r="R8" s="99" t="n">
+      <c r="S8" s="99" t="n">
         <v>-12.19</v>
       </c>
-      <c r="S8" s="99" t="n">
+      <c r="T8" s="99" t="n">
         <v>-11.56</v>
       </c>
-      <c r="T8" s="99" t="n">
+      <c r="U8" s="99" t="n">
         <v>-10.95</v>
       </c>
-      <c r="U8" s="99" t="n">
+      <c r="V8" s="99" t="n">
         <v>-10.7</v>
       </c>
-      <c r="V8" s="99" t="n">
+      <c r="W8" s="99" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="W8" s="99" t="n">
+      <c r="X8" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="X8" s="99" t="n">
+      <c r="Y8" s="99" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="Y8" s="99" t="n">
+      <c r="Z8" s="99" t="n">
         <v>-10.94</v>
       </c>
-      <c r="Z8" s="99" t="n">
+      <c r="AA8" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AA8" s="99" t="n">
+      <c r="AB8" s="99" t="n">
         <v>-8.17</v>
       </c>
-      <c r="AB8" s="99" t="n">
+      <c r="AC8" s="99" t="n">
         <v>-7.67</v>
       </c>
-      <c r="AC8" s="99" t="n">
+      <c r="AD8" s="99" t="n">
         <v>-6.65</v>
       </c>
-      <c r="AD8" s="99" t="n">
+      <c r="AE8" s="99" t="n">
         <v>-5.88</v>
-      </c>
-      <c r="AE8" s="99" t="n">
-        <v>-6.11</v>
       </c>
     </row>
     <row r="9">
@@ -7315,31 +7315,31 @@
         <v>15.28</v>
       </c>
       <c r="C9" s="99" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="D9" s="99" t="n">
         <v>-3.74</v>
       </c>
-      <c r="D9" s="99" t="n">
+      <c r="E9" s="99" t="n">
         <v>-10.62</v>
       </c>
-      <c r="E9" s="99" t="n">
+      <c r="F9" s="99" t="n">
         <v>-12.51</v>
       </c>
-      <c r="F9" s="99" t="n">
+      <c r="G9" s="99" t="n">
         <v>-12.61</v>
       </c>
-      <c r="G9" s="99" t="n">
+      <c r="H9" s="99" t="n">
         <v>-14.58</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="I9" s="99" t="n">
         <v>-16.03</v>
       </c>
-      <c r="I9" s="99" t="n">
+      <c r="J9" s="99" t="n">
         <v>-16.65</v>
       </c>
-      <c r="J9" s="99" t="n">
+      <c r="K9" s="99" t="n">
         <v>-18.48</v>
-      </c>
-      <c r="K9" s="99" t="n">
-        <v>-18.74</v>
       </c>
       <c r="L9" s="99" t="n">
         <v>-18.74</v>
@@ -7348,58 +7348,58 @@
         <v>-18.74</v>
       </c>
       <c r="N9" s="99" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="O9" s="99" t="n">
         <v>-19.06</v>
       </c>
-      <c r="O9" s="99" t="n">
+      <c r="P9" s="99" t="n">
         <v>-18.16</v>
       </c>
-      <c r="P9" s="99" t="n">
+      <c r="Q9" s="99" t="n">
         <v>-20.04</v>
       </c>
-      <c r="Q9" s="99" t="n">
+      <c r="R9" s="99" t="n">
         <v>-19.01</v>
       </c>
-      <c r="R9" s="99" t="n">
+      <c r="S9" s="99" t="n">
         <v>-17.71</v>
       </c>
-      <c r="S9" s="99" t="n">
+      <c r="T9" s="99" t="n">
         <v>-17.63</v>
       </c>
-      <c r="T9" s="99" t="n">
+      <c r="U9" s="99" t="n">
         <v>-17.79</v>
       </c>
-      <c r="U9" s="99" t="n">
+      <c r="V9" s="99" t="n">
         <v>-17.53</v>
       </c>
-      <c r="V9" s="99" t="n">
+      <c r="W9" s="99" t="n">
         <v>-16.58</v>
       </c>
-      <c r="W9" s="99" t="n">
+      <c r="X9" s="99" t="n">
         <v>-12.6</v>
       </c>
-      <c r="X9" s="99" t="n">
+      <c r="Y9" s="99" t="n">
         <v>-16.3</v>
       </c>
-      <c r="Y9" s="99" t="n">
+      <c r="Z9" s="99" t="n">
         <v>-17.92</v>
       </c>
-      <c r="Z9" s="99" t="n">
+      <c r="AA9" s="99" t="n">
         <v>-17.61</v>
       </c>
-      <c r="AA9" s="99" t="n">
+      <c r="AB9" s="99" t="n">
         <v>-16.31</v>
       </c>
-      <c r="AB9" s="99" t="n">
+      <c r="AC9" s="99" t="n">
         <v>-15.1</v>
       </c>
-      <c r="AC9" s="99" t="n">
+      <c r="AD9" s="99" t="n">
         <v>-11.15</v>
       </c>
-      <c r="AD9" s="99" t="n">
+      <c r="AE9" s="99" t="n">
         <v>-13.21</v>
-      </c>
-      <c r="AE9" s="99" t="n">
-        <v>-9.76</v>
       </c>
     </row>
     <row r="10">
@@ -7412,31 +7412,31 @@
         <v>90.09999999999999</v>
       </c>
       <c r="C10" s="99" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="D10" s="99" t="n">
         <v>78.56</v>
       </c>
-      <c r="D10" s="99" t="n">
+      <c r="E10" s="99" t="n">
         <v>65.87</v>
       </c>
-      <c r="E10" s="99" t="n">
+      <c r="F10" s="99" t="n">
         <v>51.71</v>
       </c>
-      <c r="F10" s="99" t="n">
+      <c r="G10" s="99" t="n">
         <v>51.51</v>
       </c>
-      <c r="G10" s="99" t="n">
+      <c r="H10" s="99" t="n">
         <v>29.32</v>
       </c>
-      <c r="H10" s="99" t="n">
+      <c r="I10" s="99" t="n">
         <v>32.26</v>
       </c>
-      <c r="I10" s="99" t="n">
+      <c r="J10" s="99" t="n">
         <v>34.06</v>
       </c>
-      <c r="J10" s="99" t="n">
+      <c r="K10" s="99" t="n">
         <v>29.44</v>
-      </c>
-      <c r="K10" s="99" t="n">
-        <v>33.41</v>
       </c>
       <c r="L10" s="99" t="n">
         <v>33.41</v>
@@ -7445,58 +7445,58 @@
         <v>33.41</v>
       </c>
       <c r="N10" s="99" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="O10" s="99" t="n">
         <v>35.55</v>
       </c>
-      <c r="O10" s="99" t="n">
+      <c r="P10" s="99" t="n">
         <v>38.79</v>
       </c>
-      <c r="P10" s="99" t="n">
+      <c r="Q10" s="99" t="n">
         <v>34.56</v>
       </c>
-      <c r="Q10" s="99" t="n">
+      <c r="R10" s="99" t="n">
         <v>29.42</v>
       </c>
-      <c r="R10" s="99" t="n">
+      <c r="S10" s="99" t="n">
         <v>32.81</v>
       </c>
-      <c r="S10" s="99" t="n">
+      <c r="T10" s="99" t="n">
         <v>37.49</v>
       </c>
-      <c r="T10" s="99" t="n">
+      <c r="U10" s="99" t="n">
         <v>38.05</v>
       </c>
-      <c r="U10" s="99" t="n">
+      <c r="V10" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="V10" s="99" t="n">
+      <c r="W10" s="99" t="n">
         <v>35.52</v>
       </c>
-      <c r="W10" s="99" t="n">
+      <c r="X10" s="99" t="n">
         <v>49.6</v>
       </c>
-      <c r="X10" s="99" t="n">
+      <c r="Y10" s="99" t="n">
         <v>35.78</v>
       </c>
-      <c r="Y10" s="99" t="n">
+      <c r="Z10" s="99" t="n">
         <v>25.18</v>
       </c>
-      <c r="Z10" s="99" t="n">
+      <c r="AA10" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AA10" s="99" t="n">
+      <c r="AB10" s="99" t="n">
         <v>30.93</v>
       </c>
-      <c r="AB10" s="99" t="n">
+      <c r="AC10" s="99" t="n">
         <v>32.82</v>
       </c>
-      <c r="AC10" s="99" t="n">
+      <c r="AD10" s="99" t="n">
         <v>32.56</v>
       </c>
-      <c r="AD10" s="99" t="n">
+      <c r="AE10" s="99" t="n">
         <v>35.9</v>
-      </c>
-      <c r="AE10" s="99" t="n">
-        <v>36.95</v>
       </c>
     </row>
     <row r="11">
@@ -7509,31 +7509,31 @@
         <v>96.84</v>
       </c>
       <c r="C11" s="99" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="D11" s="99" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="D11" s="99" t="n">
+      <c r="E11" s="99" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="E11" s="99" t="n">
+      <c r="F11" s="99" t="n">
         <v>64.94</v>
       </c>
-      <c r="F11" s="99" t="n">
+      <c r="G11" s="99" t="n">
         <v>64.66</v>
       </c>
-      <c r="G11" s="99" t="n">
+      <c r="H11" s="99" t="n">
         <v>23.69</v>
       </c>
-      <c r="H11" s="99" t="n">
+      <c r="I11" s="99" t="n">
         <v>29.81</v>
       </c>
-      <c r="I11" s="99" t="n">
+      <c r="J11" s="99" t="n">
         <v>33.91</v>
       </c>
-      <c r="J11" s="99" t="n">
+      <c r="K11" s="99" t="n">
         <v>22.82</v>
-      </c>
-      <c r="K11" s="99" t="n">
-        <v>30.54</v>
       </c>
       <c r="L11" s="99" t="n">
         <v>30.54</v>
@@ -7542,58 +7542,58 @@
         <v>30.54</v>
       </c>
       <c r="N11" s="99" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="O11" s="99" t="n">
         <v>35.28</v>
       </c>
-      <c r="O11" s="99" t="n">
+      <c r="P11" s="99" t="n">
         <v>42.99</v>
       </c>
-      <c r="P11" s="99" t="n">
+      <c r="Q11" s="99" t="n">
         <v>33.88</v>
       </c>
-      <c r="Q11" s="99" t="n">
+      <c r="R11" s="99" t="n">
         <v>22.22</v>
       </c>
-      <c r="R11" s="99" t="n">
+      <c r="S11" s="99" t="n">
         <v>27.98</v>
       </c>
-      <c r="S11" s="99" t="n">
+      <c r="T11" s="99" t="n">
         <v>37.32</v>
       </c>
-      <c r="T11" s="99" t="n">
+      <c r="U11" s="99" t="n">
         <v>38.49</v>
       </c>
-      <c r="U11" s="99" t="n">
+      <c r="V11" s="99" t="n">
         <v>41.22</v>
       </c>
-      <c r="V11" s="99" t="n">
+      <c r="W11" s="99" t="n">
         <v>34.35</v>
       </c>
-      <c r="W11" s="99" t="n">
+      <c r="X11" s="99" t="n">
         <v>63.18</v>
       </c>
-      <c r="X11" s="99" t="n">
+      <c r="Y11" s="99" t="n">
         <v>38.1</v>
       </c>
-      <c r="Y11" s="99" t="n">
+      <c r="Z11" s="99" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="Z11" s="99" t="n">
+      <c r="AA11" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="AA11" s="99" t="n">
+      <c r="AB11" s="99" t="n">
         <v>17.04</v>
       </c>
-      <c r="AB11" s="99" t="n">
+      <c r="AC11" s="99" t="n">
         <v>20.21</v>
       </c>
-      <c r="AC11" s="99" t="n">
+      <c r="AD11" s="99" t="n">
         <v>19.37</v>
       </c>
-      <c r="AD11" s="99" t="n">
+      <c r="AE11" s="99" t="n">
         <v>25.01</v>
-      </c>
-      <c r="AE11" s="99" t="n">
-        <v>26.94</v>
       </c>
     </row>
     <row r="12">
@@ -7627,114 +7627,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G12" s="98" t="inlineStr">
+      <c r="G12" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H12" s="98" t="inlineStr">
+      <c r="I12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I12" s="97" t="inlineStr">
+      <c r="J12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J12" s="98" t="inlineStr">
+      <c r="K12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K12" s="98" t="inlineStr">
+      <c r="L12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L12" s="98" t="inlineStr">
+      <c r="M12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="98" t="inlineStr">
+      <c r="N12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="97" t="inlineStr">
+      <c r="O12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O12" s="96" t="inlineStr">
+      <c r="P12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P12" s="98" t="inlineStr">
+      <c r="Q12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q12" s="98" t="inlineStr">
+      <c r="R12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R12" s="98" t="inlineStr">
+      <c r="S12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S12" s="96" t="inlineStr">
+      <c r="T12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T12" s="97" t="inlineStr">
+      <c r="U12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U12" s="97" t="inlineStr">
+      <c r="V12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V12" s="98" t="inlineStr">
+      <c r="W12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W12" s="96" t="inlineStr">
+      <c r="X12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X12" s="97" t="inlineStr">
+      <c r="Y12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y12" s="97" t="inlineStr">
+      <c r="Z12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z12" s="98" t="inlineStr">
+      <c r="AA12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA12" s="97" t="inlineStr">
+      <c r="AB12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB12" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC12" s="98" t="inlineStr">
@@ -7763,31 +7763,31 @@
         <v>32.05</v>
       </c>
       <c r="C13" s="99" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="D13" s="99" t="n">
         <v>13.58</v>
       </c>
-      <c r="D13" s="99" t="n">
+      <c r="E13" s="99" t="n">
         <v>2.95</v>
       </c>
-      <c r="E13" s="99" t="n">
+      <c r="F13" s="99" t="n">
         <v>-2.45</v>
       </c>
-      <c r="F13" s="99" t="n">
+      <c r="G13" s="99" t="n">
         <v>-4.05</v>
       </c>
-      <c r="G13" s="99" t="n">
+      <c r="H13" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="H13" s="99" t="n">
+      <c r="I13" s="99" t="n">
         <v>-11.21</v>
       </c>
-      <c r="I13" s="99" t="n">
+      <c r="J13" s="99" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="J13" s="99" t="n">
+      <c r="K13" s="99" t="n">
         <v>-11.44</v>
-      </c>
-      <c r="K13" s="99" t="n">
-        <v>-12.57</v>
       </c>
       <c r="L13" s="99" t="n">
         <v>-12.57</v>
@@ -7796,58 +7796,58 @@
         <v>-12.57</v>
       </c>
       <c r="N13" s="99" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="O13" s="99" t="n">
         <v>-11.96</v>
       </c>
-      <c r="O13" s="99" t="n">
+      <c r="P13" s="99" t="n">
         <v>-12.87</v>
       </c>
-      <c r="P13" s="99" t="n">
+      <c r="Q13" s="99" t="n">
         <v>-14.98</v>
       </c>
-      <c r="Q13" s="99" t="n">
+      <c r="R13" s="99" t="n">
         <v>-14.79</v>
       </c>
-      <c r="R13" s="99" t="n">
+      <c r="S13" s="99" t="n">
         <v>-14.14</v>
       </c>
-      <c r="S13" s="99" t="n">
+      <c r="T13" s="99" t="n">
         <v>-11.99</v>
       </c>
-      <c r="T13" s="99" t="n">
+      <c r="U13" s="99" t="n">
         <v>-12.63</v>
       </c>
-      <c r="U13" s="99" t="n">
+      <c r="V13" s="99" t="n">
         <v>-12.92</v>
       </c>
-      <c r="V13" s="99" t="n">
+      <c r="W13" s="99" t="n">
         <v>-13.71</v>
       </c>
-      <c r="W13" s="99" t="n">
+      <c r="X13" s="99" t="n">
         <v>-13.18</v>
       </c>
-      <c r="X13" s="99" t="n">
+      <c r="Y13" s="99" t="n">
         <v>-15.93</v>
       </c>
-      <c r="Y13" s="99" t="n">
+      <c r="Z13" s="99" t="n">
         <v>-16.93</v>
       </c>
-      <c r="Z13" s="99" t="n">
+      <c r="AA13" s="99" t="n">
         <v>-15.87</v>
       </c>
-      <c r="AA13" s="99" t="n">
+      <c r="AB13" s="99" t="n">
         <v>-14.39</v>
       </c>
-      <c r="AB13" s="99" t="n">
+      <c r="AC13" s="99" t="n">
         <v>-14.68</v>
       </c>
-      <c r="AC13" s="99" t="n">
+      <c r="AD13" s="99" t="n">
         <v>-14.6</v>
       </c>
-      <c r="AD13" s="99" t="n">
+      <c r="AE13" s="99" t="n">
         <v>-13.72</v>
-      </c>
-      <c r="AE13" s="99" t="n">
-        <v>-14.36</v>
       </c>
     </row>
     <row r="14">
@@ -7860,31 +7860,31 @@
         <v>18.19</v>
       </c>
       <c r="C14" s="99" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="D14" s="99" t="n">
         <v>1.34</v>
       </c>
-      <c r="D14" s="99" t="n">
+      <c r="E14" s="99" t="n">
         <v>-8.44</v>
       </c>
-      <c r="E14" s="99" t="n">
+      <c r="F14" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="F14" s="99" t="n">
+      <c r="G14" s="99" t="n">
         <v>-10.6</v>
       </c>
-      <c r="G14" s="99" t="n">
+      <c r="H14" s="99" t="n">
         <v>-14.49</v>
       </c>
-      <c r="H14" s="99" t="n">
+      <c r="I14" s="99" t="n">
         <v>-16.56</v>
       </c>
-      <c r="I14" s="99" t="n">
+      <c r="J14" s="99" t="n">
         <v>-15.65</v>
       </c>
-      <c r="J14" s="99" t="n">
+      <c r="K14" s="99" t="n">
         <v>-17.96</v>
-      </c>
-      <c r="K14" s="99" t="n">
-        <v>-19.08</v>
       </c>
       <c r="L14" s="99" t="n">
         <v>-19.08</v>
@@ -7893,58 +7893,58 @@
         <v>-19.08</v>
       </c>
       <c r="N14" s="99" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="O14" s="99" t="n">
         <v>-18.72</v>
       </c>
-      <c r="O14" s="99" t="n">
+      <c r="P14" s="99" t="n">
         <v>-18.28</v>
       </c>
-      <c r="P14" s="99" t="n">
+      <c r="Q14" s="99" t="n">
         <v>-20.06</v>
       </c>
-      <c r="Q14" s="99" t="n">
+      <c r="R14" s="99" t="n">
         <v>-18.31</v>
       </c>
-      <c r="R14" s="99" t="n">
+      <c r="S14" s="99" t="n">
         <v>-18.32</v>
       </c>
-      <c r="S14" s="99" t="n">
+      <c r="T14" s="99" t="n">
         <v>-17.44</v>
       </c>
-      <c r="T14" s="99" t="n">
+      <c r="U14" s="99" t="n">
         <v>-18.44</v>
       </c>
-      <c r="U14" s="99" t="n">
+      <c r="V14" s="99" t="n">
         <v>-17.67</v>
       </c>
-      <c r="V14" s="99" t="n">
+      <c r="W14" s="99" t="n">
         <v>-14.96</v>
       </c>
-      <c r="W14" s="99" t="n">
+      <c r="X14" s="99" t="n">
         <v>-11.7</v>
       </c>
-      <c r="X14" s="99" t="n">
+      <c r="Y14" s="99" t="n">
         <v>-15.89</v>
       </c>
-      <c r="Y14" s="99" t="n">
+      <c r="Z14" s="99" t="n">
         <v>-16.48</v>
       </c>
-      <c r="Z14" s="99" t="n">
+      <c r="AA14" s="99" t="n">
         <v>-16.57</v>
       </c>
-      <c r="AA14" s="99" t="n">
+      <c r="AB14" s="99" t="n">
         <v>-15.28</v>
       </c>
-      <c r="AB14" s="99" t="n">
+      <c r="AC14" s="99" t="n">
         <v>-14.4</v>
       </c>
-      <c r="AC14" s="99" t="n">
+      <c r="AD14" s="99" t="n">
         <v>-11.57</v>
       </c>
-      <c r="AD14" s="99" t="n">
+      <c r="AE14" s="99" t="n">
         <v>-13.13</v>
-      </c>
-      <c r="AE14" s="99" t="n">
-        <v>-10.49</v>
       </c>
     </row>
     <row r="15">
@@ -7957,31 +7957,31 @@
         <v>93.78</v>
       </c>
       <c r="C15" s="99" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="D15" s="99" t="n">
         <v>88.70999999999999</v>
       </c>
-      <c r="D15" s="99" t="n">
+      <c r="E15" s="99" t="n">
         <v>80.03</v>
       </c>
-      <c r="E15" s="99" t="n">
+      <c r="F15" s="99" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="F15" s="99" t="n">
+      <c r="G15" s="99" t="n">
         <v>67.36</v>
       </c>
-      <c r="G15" s="99" t="n">
+      <c r="H15" s="99" t="n">
         <v>40.3</v>
       </c>
-      <c r="H15" s="99" t="n">
+      <c r="I15" s="99" t="n">
         <v>42.58</v>
       </c>
-      <c r="I15" s="99" t="n">
+      <c r="J15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="J15" s="99" t="n">
+      <c r="K15" s="99" t="n">
         <v>40.02</v>
-      </c>
-      <c r="K15" s="99" t="n">
-        <v>40.59</v>
       </c>
       <c r="L15" s="99" t="n">
         <v>40.59</v>
@@ -7990,58 +7990,58 @@
         <v>40.59</v>
       </c>
       <c r="N15" s="99" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="O15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="O15" s="99" t="n">
+      <c r="P15" s="99" t="n">
         <v>48.89</v>
       </c>
-      <c r="P15" s="99" t="n">
+      <c r="Q15" s="99" t="n">
         <v>40.91</v>
       </c>
-      <c r="Q15" s="99" t="n">
+      <c r="R15" s="99" t="n">
         <v>40.48</v>
       </c>
-      <c r="R15" s="99" t="n">
+      <c r="S15" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="S15" s="99" t="n">
+      <c r="T15" s="99" t="n">
         <v>48.15</v>
       </c>
-      <c r="T15" s="99" t="n">
+      <c r="U15" s="99" t="n">
         <v>44.33</v>
       </c>
-      <c r="U15" s="99" t="n">
+      <c r="V15" s="99" t="n">
         <v>44.83</v>
       </c>
-      <c r="V15" s="99" t="n">
+      <c r="W15" s="99" t="n">
         <v>37.59</v>
       </c>
-      <c r="W15" s="99" t="n">
+      <c r="X15" s="99" t="n">
         <v>51.16</v>
       </c>
-      <c r="X15" s="99" t="n">
+      <c r="Y15" s="99" t="n">
         <v>31.05</v>
       </c>
-      <c r="Y15" s="99" t="n">
+      <c r="Z15" s="99" t="n">
         <v>23.87</v>
       </c>
-      <c r="Z15" s="99" t="n">
+      <c r="AA15" s="99" t="n">
         <v>23.35</v>
       </c>
-      <c r="AA15" s="99" t="n">
+      <c r="AB15" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AB15" s="99" t="n">
+      <c r="AC15" s="99" t="n">
         <v>27.05</v>
       </c>
-      <c r="AC15" s="99" t="n">
+      <c r="AD15" s="99" t="n">
         <v>26.89</v>
       </c>
-      <c r="AD15" s="99" t="n">
+      <c r="AE15" s="99" t="n">
         <v>29.42</v>
-      </c>
-      <c r="AE15" s="99" t="n">
-        <v>31.54</v>
       </c>
     </row>
     <row r="16">
@@ -8054,31 +8054,31 @@
         <v>94.69</v>
       </c>
       <c r="C16" s="99" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="D16" s="99" t="n">
         <v>90.12</v>
       </c>
-      <c r="D16" s="99" t="n">
+      <c r="E16" s="99" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="E16" s="99" t="n">
+      <c r="F16" s="99" t="n">
         <v>73.8</v>
       </c>
-      <c r="F16" s="99" t="n">
+      <c r="G16" s="99" t="n">
         <v>69.36</v>
       </c>
-      <c r="G16" s="99" t="n">
+      <c r="H16" s="99" t="n">
         <v>40.16</v>
       </c>
-      <c r="H16" s="99" t="n">
+      <c r="I16" s="99" t="n">
         <v>42.76</v>
       </c>
-      <c r="I16" s="99" t="n">
+      <c r="J16" s="99" t="n">
         <v>47.16</v>
       </c>
-      <c r="J16" s="99" t="n">
+      <c r="K16" s="99" t="n">
         <v>39.93</v>
-      </c>
-      <c r="K16" s="99" t="n">
-        <v>40.57</v>
       </c>
       <c r="L16" s="99" t="n">
         <v>40.57</v>
@@ -8087,58 +8087,58 @@
         <v>40.57</v>
       </c>
       <c r="N16" s="99" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="O16" s="99" t="n">
         <v>47.22</v>
       </c>
-      <c r="O16" s="99" t="n">
+      <c r="P16" s="99" t="n">
         <v>50.08</v>
       </c>
-      <c r="P16" s="99" t="n">
+      <c r="Q16" s="99" t="n">
         <v>41.17</v>
       </c>
-      <c r="Q16" s="99" t="n">
+      <c r="R16" s="99" t="n">
         <v>40.69</v>
       </c>
-      <c r="R16" s="99" t="n">
+      <c r="S16" s="99" t="n">
         <v>40.24</v>
       </c>
-      <c r="S16" s="99" t="n">
+      <c r="T16" s="99" t="n">
         <v>49.36</v>
       </c>
-      <c r="T16" s="99" t="n">
+      <c r="U16" s="99" t="n">
         <v>45.18</v>
       </c>
-      <c r="U16" s="99" t="n">
+      <c r="V16" s="99" t="n">
         <v>45.74</v>
       </c>
-      <c r="V16" s="99" t="n">
+      <c r="W16" s="99" t="n">
         <v>37.86</v>
       </c>
-      <c r="W16" s="99" t="n">
+      <c r="X16" s="99" t="n">
         <v>53.33</v>
       </c>
-      <c r="X16" s="99" t="n">
+      <c r="Y16" s="99" t="n">
         <v>30.77</v>
       </c>
-      <c r="Y16" s="99" t="n">
+      <c r="Z16" s="99" t="n">
         <v>22.26</v>
       </c>
-      <c r="Z16" s="99" t="n">
+      <c r="AA16" s="99" t="n">
         <v>21.65</v>
       </c>
-      <c r="AA16" s="99" t="n">
+      <c r="AB16" s="99" t="n">
         <v>25.27</v>
       </c>
-      <c r="AB16" s="99" t="n">
+      <c r="AC16" s="99" t="n">
         <v>25.69</v>
       </c>
-      <c r="AC16" s="99" t="n">
+      <c r="AD16" s="99" t="n">
         <v>25.5</v>
       </c>
-      <c r="AD16" s="99" t="n">
+      <c r="AE16" s="99" t="n">
         <v>28.26</v>
-      </c>
-      <c r="AE16" s="99" t="n">
-        <v>30.6</v>
       </c>
     </row>
     <row r="17">
@@ -8202,99 +8202,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="M17" s="97" t="inlineStr">
+      <c r="M17" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N17" s="97" t="inlineStr">
+      <c r="O17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="98" t="inlineStr">
+      <c r="P17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P17" s="98" t="inlineStr">
+      <c r="Q17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q17" s="98" t="inlineStr">
+      <c r="R17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R17" s="98" t="inlineStr">
+      <c r="S17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S17" s="98" t="inlineStr">
+      <c r="T17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T17" s="98" t="inlineStr">
+      <c r="U17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U17" s="97" t="inlineStr">
+      <c r="V17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V17" s="97" t="inlineStr">
+      <c r="W17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W17" s="96" t="inlineStr">
+      <c r="X17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X17" s="97" t="inlineStr">
+      <c r="Y17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y17" s="97" t="inlineStr">
+      <c r="Z17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z17" s="96" t="inlineStr">
+      <c r="AA17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA17" s="96" t="inlineStr">
+      <c r="AB17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB17" s="97" t="inlineStr">
+      <c r="AC17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC17" s="96" t="inlineStr">
+      <c r="AD17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD17" s="97" t="inlineStr">
+      <c r="AE17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE17" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8308,91 +8308,91 @@
         <v>17.23</v>
       </c>
       <c r="C18" s="99" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="D18" s="99" t="n">
         <v>14.76</v>
       </c>
-      <c r="D18" s="99" t="n">
+      <c r="E18" s="99" t="n">
         <v>12.13</v>
       </c>
-      <c r="E18" s="99" t="n">
+      <c r="F18" s="99" t="n">
         <v>7.96</v>
       </c>
-      <c r="F18" s="99" t="n">
+      <c r="G18" s="99" t="n">
         <v>7.25</v>
       </c>
-      <c r="G18" s="99" t="n">
+      <c r="H18" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="H18" s="99" t="n">
+      <c r="I18" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="I18" s="99" t="n">
+      <c r="J18" s="99" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="J18" s="99" t="n">
-        <v>-2.04</v>
       </c>
       <c r="K18" s="99" t="n">
         <v>-2.04</v>
       </c>
       <c r="L18" s="99" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M18" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="M18" s="99" t="n">
+      <c r="N18" s="99" t="n">
         <v>-5.76</v>
       </c>
-      <c r="N18" s="99" t="n">
+      <c r="O18" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="O18" s="99" t="n">
+      <c r="P18" s="99" t="n">
         <v>-4.61</v>
       </c>
-      <c r="P18" s="99" t="n">
+      <c r="Q18" s="99" t="n">
         <v>-3.94</v>
       </c>
-      <c r="Q18" s="99" t="n">
+      <c r="R18" s="99" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="R18" s="99" t="n">
-        <v>-2.75</v>
       </c>
       <c r="S18" s="99" t="n">
         <v>-2.75</v>
       </c>
       <c r="T18" s="99" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="U18" s="99" t="n">
         <v>-3.96</v>
       </c>
-      <c r="U18" s="99" t="n">
+      <c r="V18" s="99" t="n">
         <v>-3.9</v>
       </c>
-      <c r="V18" s="99" t="n">
+      <c r="W18" s="99" t="n">
         <v>-4.25</v>
       </c>
-      <c r="W18" s="99" t="n">
+      <c r="X18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="X18" s="99" t="n">
+      <c r="Y18" s="99" t="n">
         <v>-3.57</v>
       </c>
-      <c r="Y18" s="99" t="n">
+      <c r="Z18" s="99" t="n">
         <v>-3.86</v>
       </c>
-      <c r="Z18" s="99" t="n">
+      <c r="AA18" s="99" t="n">
         <v>-1.13</v>
       </c>
-      <c r="AA18" s="99" t="n">
+      <c r="AB18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="AB18" s="99" t="n">
+      <c r="AC18" s="99" t="n">
         <v>-4.68</v>
       </c>
-      <c r="AC18" s="99" t="n">
+      <c r="AD18" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AD18" s="99" t="n">
+      <c r="AE18" s="99" t="n">
         <v>-7.63</v>
-      </c>
-      <c r="AE18" s="99" t="n">
-        <v>-5.9</v>
       </c>
     </row>
     <row r="19">
@@ -8405,91 +8405,91 @@
         <v>26.37</v>
       </c>
       <c r="C19" s="99" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="D19" s="99" t="n">
         <v>23.36</v>
       </c>
-      <c r="D19" s="99" t="n">
+      <c r="E19" s="99" t="n">
         <v>17.68</v>
       </c>
-      <c r="E19" s="99" t="n">
+      <c r="F19" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="F19" s="99" t="n">
+      <c r="G19" s="99" t="n">
         <v>15.91</v>
       </c>
-      <c r="G19" s="99" t="n">
+      <c r="H19" s="99" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H19" s="99" t="n">
+      <c r="I19" s="99" t="n">
         <v>10.84</v>
       </c>
-      <c r="I19" s="99" t="n">
+      <c r="J19" s="99" t="n">
         <v>9.17</v>
-      </c>
-      <c r="J19" s="99" t="n">
-        <v>4.73</v>
       </c>
       <c r="K19" s="99" t="n">
         <v>4.73</v>
       </c>
       <c r="L19" s="99" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="M19" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="M19" s="99" t="n">
+      <c r="N19" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="N19" s="99" t="n">
+      <c r="O19" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="O19" s="99" t="n">
+      <c r="P19" s="99" t="n">
         <v>2.32</v>
       </c>
-      <c r="P19" s="99" t="n">
+      <c r="Q19" s="99" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q19" s="99" t="n">
+      <c r="R19" s="99" t="n">
         <v>0.67</v>
-      </c>
-      <c r="R19" s="99" t="n">
-        <v>2.05</v>
       </c>
       <c r="S19" s="99" t="n">
         <v>2.05</v>
       </c>
       <c r="T19" s="99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U19" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="U19" s="99" t="n">
+      <c r="V19" s="99" t="n">
         <v>7.94</v>
       </c>
-      <c r="V19" s="99" t="n">
+      <c r="W19" s="99" t="n">
         <v>9.01</v>
       </c>
-      <c r="W19" s="99" t="n">
+      <c r="X19" s="99" t="n">
         <v>9.44</v>
       </c>
-      <c r="X19" s="99" t="n">
+      <c r="Y19" s="99" t="n">
         <v>10.05</v>
       </c>
-      <c r="Y19" s="99" t="n">
+      <c r="Z19" s="99" t="n">
         <v>6.61</v>
       </c>
-      <c r="Z19" s="99" t="n">
+      <c r="AA19" s="99" t="n">
         <v>7.75</v>
       </c>
-      <c r="AA19" s="99" t="n">
+      <c r="AB19" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="AB19" s="99" t="n">
+      <c r="AC19" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="AC19" s="99" t="n">
+      <c r="AD19" s="99" t="n">
         <v>5.06</v>
       </c>
-      <c r="AD19" s="99" t="n">
+      <c r="AE19" s="99" t="n">
         <v>4.55</v>
-      </c>
-      <c r="AE19" s="99" t="n">
-        <v>4.69</v>
       </c>
     </row>
     <row r="20">
@@ -8502,91 +8502,91 @@
         <v>97.18000000000001</v>
       </c>
       <c r="C20" s="99" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="D20" s="99" t="n">
         <v>96.45999999999999</v>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="E20" s="99" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="E20" s="99" t="n">
+      <c r="F20" s="99" t="n">
         <v>91.5</v>
       </c>
-      <c r="F20" s="99" t="n">
+      <c r="G20" s="99" t="n">
         <v>90.64</v>
       </c>
-      <c r="G20" s="99" t="n">
+      <c r="H20" s="99" t="n">
         <v>81.62</v>
       </c>
-      <c r="H20" s="99" t="n">
+      <c r="I20" s="99" t="n">
         <v>82.63</v>
       </c>
-      <c r="I20" s="99" t="n">
+      <c r="J20" s="99" t="n">
         <v>77.72</v>
-      </c>
-      <c r="J20" s="99" t="n">
-        <v>66.26000000000001</v>
       </c>
       <c r="K20" s="99" t="n">
         <v>66.26000000000001</v>
       </c>
       <c r="L20" s="99" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="M20" s="99" t="n">
         <v>52.57</v>
       </c>
-      <c r="M20" s="99" t="n">
+      <c r="N20" s="99" t="n">
         <v>48.7</v>
       </c>
-      <c r="N20" s="99" t="n">
+      <c r="O20" s="99" t="n">
         <v>38.58</v>
       </c>
-      <c r="O20" s="99" t="n">
+      <c r="P20" s="99" t="n">
         <v>26.15</v>
       </c>
-      <c r="P20" s="99" t="n">
+      <c r="Q20" s="99" t="n">
         <v>31.15</v>
       </c>
-      <c r="Q20" s="99" t="n">
+      <c r="R20" s="99" t="n">
         <v>27.74</v>
-      </c>
-      <c r="R20" s="99" t="n">
-        <v>38.27</v>
       </c>
       <c r="S20" s="99" t="n">
         <v>38.27</v>
       </c>
       <c r="T20" s="99" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="U20" s="99" t="n">
         <v>38.92</v>
       </c>
-      <c r="U20" s="99" t="n">
+      <c r="V20" s="99" t="n">
         <v>49.28</v>
       </c>
-      <c r="V20" s="99" t="n">
+      <c r="W20" s="99" t="n">
         <v>51.67</v>
       </c>
-      <c r="W20" s="99" t="n">
+      <c r="X20" s="99" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="X20" s="99" t="n">
+      <c r="Y20" s="99" t="n">
         <v>65.08</v>
       </c>
-      <c r="Y20" s="99" t="n">
+      <c r="Z20" s="99" t="n">
         <v>60.24</v>
       </c>
-      <c r="Z20" s="99" t="n">
+      <c r="AA20" s="99" t="n">
         <v>77.66</v>
       </c>
-      <c r="AA20" s="99" t="n">
+      <c r="AB20" s="99" t="n">
         <v>75.16</v>
       </c>
-      <c r="AB20" s="99" t="n">
+      <c r="AC20" s="99" t="n">
         <v>67.81</v>
       </c>
-      <c r="AC20" s="99" t="n">
+      <c r="AD20" s="99" t="n">
         <v>70.5</v>
       </c>
-      <c r="AD20" s="99" t="n">
+      <c r="AE20" s="99" t="n">
         <v>58.65</v>
-      </c>
-      <c r="AE20" s="99" t="n">
-        <v>69.89</v>
       </c>
     </row>
     <row r="21">
@@ -8599,91 +8599,91 @@
         <v>82.69</v>
       </c>
       <c r="C21" s="99" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="D21" s="99" t="n">
         <v>80.68000000000001</v>
       </c>
-      <c r="D21" s="99" t="n">
+      <c r="E21" s="99" t="n">
         <v>77.11</v>
       </c>
-      <c r="E21" s="99" t="n">
+      <c r="F21" s="99" t="n">
         <v>71.53</v>
       </c>
-      <c r="F21" s="99" t="n">
+      <c r="G21" s="99" t="n">
         <v>70.42</v>
       </c>
-      <c r="G21" s="99" t="n">
+      <c r="H21" s="99" t="n">
         <v>62.3</v>
       </c>
-      <c r="H21" s="99" t="n">
+      <c r="I21" s="99" t="n">
         <v>62.54</v>
       </c>
-      <c r="I21" s="99" t="n">
+      <c r="J21" s="99" t="n">
         <v>59.26</v>
-      </c>
-      <c r="J21" s="99" t="n">
-        <v>53.72</v>
       </c>
       <c r="K21" s="99" t="n">
         <v>53.72</v>
       </c>
       <c r="L21" s="99" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="M21" s="99" t="n">
         <v>49.33</v>
       </c>
-      <c r="M21" s="99" t="n">
+      <c r="N21" s="99" t="n">
         <v>48.3</v>
       </c>
-      <c r="N21" s="99" t="n">
+      <c r="O21" s="99" t="n">
         <v>45.75</v>
       </c>
-      <c r="O21" s="99" t="n">
+      <c r="P21" s="99" t="n">
         <v>43.02</v>
       </c>
-      <c r="P21" s="99" t="n">
+      <c r="Q21" s="99" t="n">
         <v>45.06</v>
       </c>
-      <c r="Q21" s="99" t="n">
+      <c r="R21" s="99" t="n">
         <v>44.32</v>
-      </c>
-      <c r="R21" s="99" t="n">
-        <v>48.45</v>
       </c>
       <c r="S21" s="99" t="n">
         <v>48.45</v>
       </c>
       <c r="T21" s="99" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="U21" s="99" t="n">
         <v>48.67</v>
       </c>
-      <c r="U21" s="99" t="n">
+      <c r="V21" s="99" t="n">
         <v>52.11</v>
       </c>
-      <c r="V21" s="99" t="n">
+      <c r="W21" s="99" t="n">
         <v>52.84</v>
       </c>
-      <c r="W21" s="99" t="n">
+      <c r="X21" s="99" t="n">
         <v>58.6</v>
       </c>
-      <c r="X21" s="99" t="n">
+      <c r="Y21" s="99" t="n">
         <v>55.46</v>
       </c>
-      <c r="Y21" s="99" t="n">
+      <c r="Z21" s="99" t="n">
         <v>53.93</v>
       </c>
-      <c r="Z21" s="99" t="n">
+      <c r="AA21" s="99" t="n">
         <v>57.57</v>
       </c>
-      <c r="AA21" s="99" t="n">
+      <c r="AB21" s="99" t="n">
         <v>56.41</v>
       </c>
-      <c r="AB21" s="99" t="n">
+      <c r="AC21" s="99" t="n">
         <v>53.44</v>
       </c>
-      <c r="AC21" s="99" t="n">
+      <c r="AD21" s="99" t="n">
         <v>53.98</v>
       </c>
-      <c r="AD21" s="99" t="n">
+      <c r="AE21" s="99" t="n">
         <v>49.84</v>
-      </c>
-      <c r="AE21" s="99" t="n">
-        <v>51.97</v>
       </c>
     </row>
     <row r="22">
@@ -8712,129 +8712,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F22" s="96" t="inlineStr">
+      <c r="F22" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="96" t="inlineStr">
+      <c r="H22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="96" t="inlineStr">
+      <c r="I22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="96" t="inlineStr">
+      <c r="J22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="97" t="inlineStr">
+      <c r="K22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K22" s="96" t="inlineStr">
+      <c r="L22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="96" t="inlineStr">
+      <c r="M22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="96" t="inlineStr">
+      <c r="N22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="96" t="inlineStr">
+      <c r="O22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="96" t="inlineStr">
+      <c r="P22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="97" t="inlineStr">
+      <c r="Q22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="98" t="inlineStr">
+      <c r="R22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R22" s="98" t="inlineStr">
+      <c r="S22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S22" s="98" t="inlineStr">
+      <c r="T22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="98" t="inlineStr">
+      <c r="U22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="98" t="inlineStr">
+      <c r="V22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="97" t="inlineStr">
+      <c r="W22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="97" t="inlineStr">
+      <c r="X22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="97" t="inlineStr">
+      <c r="Y22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="97" t="inlineStr">
+      <c r="Z22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="97" t="inlineStr">
+      <c r="AA22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="97" t="inlineStr">
+      <c r="AB22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="97" t="inlineStr">
+      <c r="AC22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="97" t="inlineStr">
+      <c r="AD22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE22" s="96" t="inlineStr">
@@ -8853,91 +8853,91 @@
         <v>3.51</v>
       </c>
       <c r="C23" s="99" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D23" s="99" t="n">
         <v>3.63</v>
       </c>
-      <c r="D23" s="99" t="n">
+      <c r="E23" s="99" t="n">
         <v>4.29</v>
       </c>
-      <c r="E23" s="99" t="n">
+      <c r="F23" s="99" t="n">
         <v>4.51</v>
       </c>
-      <c r="F23" s="99" t="n">
+      <c r="G23" s="99" t="n">
         <v>4.99</v>
       </c>
-      <c r="G23" s="99" t="n">
+      <c r="H23" s="99" t="n">
         <v>4.3</v>
       </c>
-      <c r="H23" s="99" t="n">
+      <c r="I23" s="99" t="n">
         <v>4.1</v>
       </c>
-      <c r="I23" s="99" t="n">
+      <c r="J23" s="99" t="n">
         <v>4.47</v>
       </c>
-      <c r="J23" s="99" t="n">
+      <c r="K23" s="99" t="n">
         <v>3.13</v>
       </c>
-      <c r="K23" s="99" t="n">
+      <c r="L23" s="99" t="n">
         <v>3.11</v>
       </c>
-      <c r="L23" s="99" t="n">
+      <c r="M23" s="99" t="n">
         <v>2.92</v>
       </c>
-      <c r="M23" s="99" t="n">
+      <c r="N23" s="99" t="n">
         <v>2.53</v>
       </c>
-      <c r="N23" s="99" t="n">
+      <c r="O23" s="99" t="n">
         <v>2.24</v>
       </c>
-      <c r="O23" s="99" t="n">
+      <c r="P23" s="99" t="n">
         <v>2.26</v>
       </c>
-      <c r="P23" s="99" t="n">
+      <c r="Q23" s="99" t="n">
         <v>1.14</v>
       </c>
-      <c r="Q23" s="99" t="n">
+      <c r="R23" s="99" t="n">
         <v>0.92</v>
       </c>
-      <c r="R23" s="99" t="n">
+      <c r="S23" s="99" t="n">
         <v>0.62</v>
       </c>
-      <c r="S23" s="99" t="n">
+      <c r="T23" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="T23" s="99" t="n">
+      <c r="U23" s="99" t="n">
         <v>3.24</v>
       </c>
-      <c r="U23" s="99" t="n">
+      <c r="V23" s="99" t="n">
         <v>3.29</v>
-      </c>
-      <c r="V23" s="99" t="n">
-        <v>5.5</v>
       </c>
       <c r="W23" s="99" t="n">
         <v>5.5</v>
       </c>
       <c r="X23" s="99" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y23" s="99" t="n">
         <v>5.68</v>
       </c>
-      <c r="Y23" s="99" t="n">
+      <c r="Z23" s="99" t="n">
         <v>5.84</v>
       </c>
-      <c r="Z23" s="99" t="n">
+      <c r="AA23" s="99" t="n">
         <v>6.6</v>
       </c>
-      <c r="AA23" s="99" t="n">
+      <c r="AB23" s="99" t="n">
         <v>7.28</v>
       </c>
-      <c r="AB23" s="99" t="n">
+      <c r="AC23" s="99" t="n">
         <v>6.98</v>
       </c>
-      <c r="AC23" s="99" t="n">
+      <c r="AD23" s="99" t="n">
         <v>4.99</v>
       </c>
-      <c r="AD23" s="99" t="n">
+      <c r="AE23" s="99" t="n">
         <v>5.96</v>
-      </c>
-      <c r="AE23" s="99" t="n">
-        <v>6.25</v>
       </c>
     </row>
     <row r="24">
@@ -8950,91 +8950,91 @@
         <v>10.61</v>
       </c>
       <c r="C24" s="99" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="D24" s="99" t="n">
         <v>10.3</v>
       </c>
-      <c r="D24" s="99" t="n">
+      <c r="E24" s="99" t="n">
         <v>10.4</v>
       </c>
-      <c r="E24" s="99" t="n">
+      <c r="F24" s="99" t="n">
         <v>11.17</v>
       </c>
-      <c r="F24" s="99" t="n">
+      <c r="G24" s="99" t="n">
         <v>10.01</v>
       </c>
-      <c r="G24" s="99" t="n">
+      <c r="H24" s="99" t="n">
         <v>9.85</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="I24" s="99" t="n">
         <v>8.75</v>
       </c>
-      <c r="I24" s="99" t="n">
+      <c r="J24" s="99" t="n">
         <v>8.74</v>
       </c>
-      <c r="J24" s="99" t="n">
+      <c r="K24" s="99" t="n">
         <v>7.05</v>
       </c>
-      <c r="K24" s="99" t="n">
+      <c r="L24" s="99" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="L24" s="99" t="n">
+      <c r="M24" s="99" t="n">
         <v>7.95</v>
       </c>
-      <c r="M24" s="99" t="n">
+      <c r="N24" s="99" t="n">
         <v>7.49</v>
       </c>
-      <c r="N24" s="99" t="n">
+      <c r="O24" s="99" t="n">
         <v>6.76</v>
       </c>
-      <c r="O24" s="99" t="n">
+      <c r="P24" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="P24" s="99" t="n">
+      <c r="Q24" s="99" t="n">
         <v>6.12</v>
       </c>
-      <c r="Q24" s="99" t="n">
+      <c r="R24" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="R24" s="99" t="n">
+      <c r="S24" s="99" t="n">
         <v>5.69</v>
       </c>
-      <c r="S24" s="99" t="n">
+      <c r="T24" s="99" t="n">
         <v>6.85</v>
       </c>
-      <c r="T24" s="99" t="n">
+      <c r="U24" s="99" t="n">
         <v>6.87</v>
       </c>
-      <c r="U24" s="99" t="n">
+      <c r="V24" s="99" t="n">
         <v>6.83</v>
-      </c>
-      <c r="V24" s="99" t="n">
-        <v>10.36</v>
       </c>
       <c r="W24" s="99" t="n">
         <v>10.36</v>
       </c>
       <c r="X24" s="99" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="Y24" s="99" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="Y24" s="99" t="n">
+      <c r="Z24" s="99" t="n">
         <v>8.43</v>
       </c>
-      <c r="Z24" s="99" t="n">
+      <c r="AA24" s="99" t="n">
         <v>10.21</v>
       </c>
-      <c r="AA24" s="99" t="n">
+      <c r="AB24" s="99" t="n">
         <v>10.6</v>
       </c>
-      <c r="AB24" s="99" t="n">
+      <c r="AC24" s="99" t="n">
         <v>9.82</v>
       </c>
-      <c r="AC24" s="99" t="n">
+      <c r="AD24" s="99" t="n">
         <v>8.44</v>
       </c>
-      <c r="AD24" s="99" t="n">
+      <c r="AE24" s="99" t="n">
         <v>10.29</v>
-      </c>
-      <c r="AE24" s="99" t="n">
-        <v>10.4</v>
       </c>
     </row>
     <row r="25">
@@ -9047,91 +9047,91 @@
         <v>86.19</v>
       </c>
       <c r="C25" s="99" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="D25" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="D25" s="99" t="n">
+      <c r="E25" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="E25" s="99" t="n">
+      <c r="F25" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="F25" s="99" t="n">
+      <c r="G25" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="G25" s="99" t="n">
+      <c r="H25" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="I25" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="I25" s="99" t="n">
+      <c r="J25" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="J25" s="99" t="n">
+      <c r="K25" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="K25" s="99" t="n">
+      <c r="L25" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="L25" s="99" t="n">
+      <c r="M25" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="M25" s="99" t="n">
+      <c r="N25" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="N25" s="99" t="n">
+      <c r="O25" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="O25" s="99" t="n">
+      <c r="P25" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="P25" s="99" t="n">
+      <c r="Q25" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="Q25" s="99" t="n">
+      <c r="R25" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="R25" s="99" t="n">
+      <c r="S25" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="S25" s="99" t="n">
+      <c r="T25" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="T25" s="99" t="n">
+      <c r="U25" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="U25" s="99" t="n">
+      <c r="V25" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="V25" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="W25" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="X25" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="Y25" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="Y25" s="99" t="n">
+      <c r="Z25" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="Z25" s="99" t="n">
+      <c r="AA25" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AA25" s="99" t="n">
+      <c r="AB25" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AB25" s="99" t="n">
+      <c r="AC25" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="AC25" s="99" t="n">
+      <c r="AD25" s="99" t="n">
         <v>30.49</v>
       </c>
-      <c r="AD25" s="99" t="n">
+      <c r="AE25" s="99" t="n">
         <v>89.15000000000001</v>
-      </c>
-      <c r="AE25" s="99" t="n">
-        <v>80.11</v>
       </c>
     </row>
     <row r="26">
@@ -9144,91 +9144,91 @@
         <v>86.19</v>
       </c>
       <c r="C26" s="99" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="D26" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="D26" s="99" t="n">
+      <c r="E26" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="E26" s="99" t="n">
+      <c r="F26" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="F26" s="99" t="n">
+      <c r="G26" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="G26" s="99" t="n">
+      <c r="H26" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="H26" s="99" t="n">
+      <c r="I26" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="I26" s="99" t="n">
+      <c r="J26" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="J26" s="99" t="n">
+      <c r="K26" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="K26" s="99" t="n">
+      <c r="L26" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="L26" s="99" t="n">
+      <c r="M26" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="M26" s="99" t="n">
+      <c r="N26" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="N26" s="99" t="n">
+      <c r="O26" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="O26" s="99" t="n">
+      <c r="P26" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="P26" s="99" t="n">
+      <c r="Q26" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="Q26" s="99" t="n">
+      <c r="R26" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="R26" s="99" t="n">
+      <c r="S26" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="S26" s="99" t="n">
+      <c r="T26" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="T26" s="99" t="n">
+      <c r="U26" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="U26" s="99" t="n">
+      <c r="V26" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="V26" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="W26" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="X26" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="Y26" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="Y26" s="99" t="n">
+      <c r="Z26" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="Z26" s="99" t="n">
+      <c r="AA26" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AA26" s="99" t="n">
+      <c r="AB26" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AB26" s="99" t="n">
+      <c r="AC26" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="AC26" s="99" t="n">
+      <c r="AD26" s="99" t="n">
         <v>30.49</v>
       </c>
-      <c r="AD26" s="99" t="n">
+      <c r="AE26" s="99" t="n">
         <v>89.15000000000001</v>
-      </c>
-      <c r="AE26" s="99" t="n">
-        <v>80.11</v>
       </c>
     </row>
     <row r="27">
@@ -9257,129 +9257,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F27" s="96" t="inlineStr">
+      <c r="F27" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G27" s="96" t="inlineStr">
+      <c r="H27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H27" s="96" t="inlineStr">
+      <c r="I27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I27" s="96" t="inlineStr">
+      <c r="J27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J27" s="96" t="inlineStr">
+      <c r="K27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K27" s="96" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L27" s="96" t="inlineStr">
+      <c r="M27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M27" s="96" t="inlineStr">
+      <c r="N27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N27" s="96" t="inlineStr">
+      <c r="O27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O27" s="96" t="inlineStr">
+      <c r="P27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P27" s="98" t="inlineStr">
+      <c r="Q27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q27" s="97" t="inlineStr">
+      <c r="R27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R27" s="98" t="inlineStr">
+      <c r="S27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S27" s="98" t="inlineStr">
+      <c r="T27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T27" s="97" t="inlineStr">
+      <c r="U27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U27" s="97" t="inlineStr">
+      <c r="V27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V27" s="96" t="inlineStr">
+      <c r="W27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W27" s="96" t="inlineStr">
+      <c r="X27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X27" s="97" t="inlineStr">
+      <c r="Y27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y27" s="97" t="inlineStr">
+      <c r="Z27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z27" s="97" t="inlineStr">
+      <c r="AA27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA27" s="96" t="inlineStr">
+      <c r="AB27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB27" s="96" t="inlineStr">
+      <c r="AC27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC27" s="97" t="inlineStr">
+      <c r="AD27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD27" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE27" s="96" t="inlineStr">
@@ -9398,91 +9398,91 @@
         <v>7.5</v>
       </c>
       <c r="C28" s="99" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D28" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="D28" s="99" t="n">
+      <c r="E28" s="99" t="n">
         <v>7.23</v>
       </c>
-      <c r="E28" s="99" t="n">
+      <c r="F28" s="99" t="n">
         <v>7.01</v>
       </c>
-      <c r="F28" s="99" t="n">
+      <c r="G28" s="99" t="n">
         <v>7.9</v>
       </c>
-      <c r="G28" s="99" t="n">
+      <c r="H28" s="99" t="n">
         <v>7.56</v>
       </c>
-      <c r="H28" s="99" t="n">
+      <c r="I28" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="I28" s="99" t="n">
+      <c r="J28" s="99" t="n">
         <v>7.45</v>
       </c>
-      <c r="J28" s="99" t="n">
+      <c r="K28" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="K28" s="99" t="n">
+      <c r="L28" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="L28" s="99" t="n">
+      <c r="M28" s="99" t="n">
         <v>6.36</v>
       </c>
-      <c r="M28" s="99" t="n">
+      <c r="N28" s="99" t="n">
         <v>6.59</v>
       </c>
-      <c r="N28" s="99" t="n">
+      <c r="O28" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="O28" s="99" t="n">
+      <c r="P28" s="99" t="n">
         <v>5.89</v>
       </c>
-      <c r="P28" s="99" t="n">
+      <c r="Q28" s="99" t="n">
         <v>5.41</v>
       </c>
-      <c r="Q28" s="99" t="n">
+      <c r="R28" s="99" t="n">
         <v>5.47</v>
       </c>
-      <c r="R28" s="99" t="n">
+      <c r="S28" s="99" t="n">
         <v>4.12</v>
       </c>
-      <c r="S28" s="99" t="n">
+      <c r="T28" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="T28" s="99" t="n">
+      <c r="U28" s="99" t="n">
         <v>5.61</v>
       </c>
-      <c r="U28" s="99" t="n">
+      <c r="V28" s="99" t="n">
         <v>5.27</v>
-      </c>
-      <c r="V28" s="99" t="n">
-        <v>7.1</v>
       </c>
       <c r="W28" s="99" t="n">
         <v>7.1</v>
       </c>
       <c r="X28" s="99" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y28" s="99" t="n">
         <v>6.78</v>
       </c>
-      <c r="Y28" s="99" t="n">
+      <c r="Z28" s="99" t="n">
         <v>6.53</v>
       </c>
-      <c r="Z28" s="99" t="n">
+      <c r="AA28" s="99" t="n">
         <v>6.63</v>
       </c>
-      <c r="AA28" s="99" t="n">
+      <c r="AB28" s="99" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="AB28" s="99" t="n">
+      <c r="AC28" s="99" t="n">
         <v>7.11</v>
       </c>
-      <c r="AC28" s="99" t="n">
+      <c r="AD28" s="99" t="n">
         <v>4.79</v>
       </c>
-      <c r="AD28" s="99" t="n">
+      <c r="AE28" s="99" t="n">
         <v>4.66</v>
-      </c>
-      <c r="AE28" s="99" t="n">
-        <v>4.53</v>
       </c>
     </row>
     <row r="29">
@@ -9495,91 +9495,91 @@
         <v>8.859999999999999</v>
       </c>
       <c r="C29" s="99" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D29" s="99" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="D29" s="99" t="n">
+      <c r="E29" s="99" t="n">
         <v>8.41</v>
       </c>
-      <c r="E29" s="99" t="n">
+      <c r="F29" s="99" t="n">
         <v>8.6</v>
       </c>
-      <c r="F29" s="99" t="n">
+      <c r="G29" s="99" t="n">
         <v>7.87</v>
       </c>
-      <c r="G29" s="99" t="n">
+      <c r="H29" s="99" t="n">
         <v>7.54</v>
       </c>
-      <c r="H29" s="99" t="n">
+      <c r="I29" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="I29" s="99" t="n">
+      <c r="J29" s="99" t="n">
         <v>5.57</v>
       </c>
-      <c r="J29" s="99" t="n">
+      <c r="K29" s="99" t="n">
         <v>4.38</v>
       </c>
-      <c r="K29" s="99" t="n">
+      <c r="L29" s="99" t="n">
         <v>5.92</v>
       </c>
-      <c r="L29" s="99" t="n">
+      <c r="M29" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="M29" s="99" t="n">
+      <c r="N29" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="N29" s="99" t="n">
+      <c r="O29" s="99" t="n">
         <v>3.31</v>
       </c>
-      <c r="O29" s="99" t="n">
+      <c r="P29" s="99" t="n">
         <v>3.42</v>
       </c>
-      <c r="P29" s="99" t="n">
+      <c r="Q29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q29" s="99" t="n">
+      <c r="R29" s="99" t="n">
         <v>5.26</v>
       </c>
-      <c r="R29" s="99" t="n">
+      <c r="S29" s="99" t="n">
         <v>4.21</v>
       </c>
-      <c r="S29" s="99" t="n">
+      <c r="T29" s="99" t="n">
         <v>4.76</v>
-      </c>
-      <c r="T29" s="99" t="n">
-        <v>4.95</v>
       </c>
       <c r="U29" s="99" t="n">
         <v>4.95</v>
       </c>
       <c r="V29" s="99" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="W29" s="99" t="n">
         <v>7.21</v>
       </c>
       <c r="X29" s="99" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="Y29" s="99" t="n">
         <v>6.75</v>
       </c>
-      <c r="Y29" s="99" t="n">
+      <c r="Z29" s="99" t="n">
         <v>5.93</v>
       </c>
-      <c r="Z29" s="99" t="n">
+      <c r="AA29" s="99" t="n">
         <v>6.7</v>
       </c>
-      <c r="AA29" s="99" t="n">
+      <c r="AB29" s="99" t="n">
         <v>6.88</v>
       </c>
-      <c r="AB29" s="99" t="n">
+      <c r="AC29" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="AC29" s="99" t="n">
+      <c r="AD29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="AD29" s="99" t="n">
+      <c r="AE29" s="99" t="n">
         <v>4.86</v>
-      </c>
-      <c r="AE29" s="99" t="n">
-        <v>4.84</v>
       </c>
     </row>
     <row r="30">
@@ -9592,91 +9592,91 @@
         <v>76.02</v>
       </c>
       <c r="C30" s="99" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="D30" s="99" t="n">
         <v>74.91</v>
       </c>
-      <c r="D30" s="99" t="n">
+      <c r="E30" s="99" t="n">
         <v>66.62</v>
       </c>
-      <c r="E30" s="99" t="n">
+      <c r="F30" s="99" t="n">
         <v>42.84</v>
       </c>
-      <c r="F30" s="99" t="n">
+      <c r="G30" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="G30" s="99" t="n">
+      <c r="H30" s="99" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="H30" s="99" t="n">
+      <c r="I30" s="99" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I30" s="99" t="n">
+      <c r="J30" s="99" t="n">
         <v>87.58</v>
       </c>
-      <c r="J30" s="99" t="n">
+      <c r="K30" s="99" t="n">
         <v>65.31</v>
       </c>
-      <c r="K30" s="99" t="n">
+      <c r="L30" s="99" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="L30" s="99" t="n">
+      <c r="M30" s="99" t="n">
         <v>88.3</v>
       </c>
-      <c r="M30" s="99" t="n">
+      <c r="N30" s="99" t="n">
         <v>82.94</v>
       </c>
-      <c r="N30" s="99" t="n">
+      <c r="O30" s="99" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="O30" s="99" t="n">
+      <c r="P30" s="99" t="n">
         <v>56.57</v>
       </c>
-      <c r="P30" s="99" t="n">
+      <c r="Q30" s="99" t="n">
         <v>46.45</v>
       </c>
-      <c r="Q30" s="99" t="n">
+      <c r="R30" s="99" t="n">
         <v>52.5</v>
       </c>
-      <c r="R30" s="99" t="n">
+      <c r="S30" s="99" t="n">
         <v>13.02</v>
       </c>
-      <c r="S30" s="99" t="n">
+      <c r="T30" s="99" t="n">
         <v>24.55</v>
       </c>
-      <c r="T30" s="99" t="n">
+      <c r="U30" s="99" t="n">
         <v>35.87</v>
       </c>
-      <c r="U30" s="99" t="n">
+      <c r="V30" s="99" t="n">
         <v>32.25</v>
-      </c>
-      <c r="V30" s="99" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="W30" s="99" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="X30" s="99" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="Y30" s="99" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="Y30" s="99" t="n">
+      <c r="Z30" s="99" t="n">
         <v>52.49</v>
       </c>
-      <c r="Z30" s="99" t="n">
+      <c r="AA30" s="99" t="n">
         <v>83.64</v>
       </c>
-      <c r="AA30" s="99" t="n">
+      <c r="AB30" s="99" t="n">
         <v>83.23</v>
       </c>
-      <c r="AB30" s="99" t="n">
+      <c r="AC30" s="99" t="n">
         <v>81.13</v>
       </c>
-      <c r="AC30" s="99" t="n">
+      <c r="AD30" s="99" t="n">
         <v>54.01</v>
       </c>
-      <c r="AD30" s="99" t="n">
+      <c r="AE30" s="99" t="n">
         <v>85.48</v>
-      </c>
-      <c r="AE30" s="99" t="n">
-        <v>83.48</v>
       </c>
     </row>
     <row r="31">
@@ -9689,91 +9689,91 @@
         <v>73.8</v>
       </c>
       <c r="C31" s="99" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D31" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="D31" s="99" t="n">
+      <c r="E31" s="99" t="n">
         <v>68.59</v>
       </c>
-      <c r="E31" s="99" t="n">
+      <c r="F31" s="99" t="n">
         <v>57.58</v>
       </c>
-      <c r="F31" s="99" t="n">
+      <c r="G31" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="G31" s="99" t="n">
+      <c r="H31" s="99" t="n">
         <v>82.34</v>
       </c>
-      <c r="H31" s="99" t="n">
+      <c r="I31" s="99" t="n">
         <v>81.04000000000001</v>
       </c>
-      <c r="I31" s="99" t="n">
+      <c r="J31" s="99" t="n">
         <v>80.31</v>
       </c>
-      <c r="J31" s="99" t="n">
+      <c r="K31" s="99" t="n">
         <v>66.03</v>
       </c>
-      <c r="K31" s="99" t="n">
+      <c r="L31" s="99" t="n">
         <v>74.56999999999999</v>
       </c>
-      <c r="L31" s="99" t="n">
+      <c r="M31" s="99" t="n">
         <v>75.78</v>
       </c>
-      <c r="M31" s="99" t="n">
+      <c r="N31" s="99" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="N31" s="99" t="n">
+      <c r="O31" s="99" t="n">
         <v>60.93</v>
       </c>
-      <c r="O31" s="99" t="n">
+      <c r="P31" s="99" t="n">
         <v>51.28</v>
       </c>
-      <c r="P31" s="99" t="n">
+      <c r="Q31" s="99" t="n">
         <v>45.58</v>
       </c>
-      <c r="Q31" s="99" t="n">
+      <c r="R31" s="99" t="n">
         <v>48.99</v>
       </c>
-      <c r="R31" s="99" t="n">
+      <c r="S31" s="99" t="n">
         <v>25.8</v>
       </c>
-      <c r="S31" s="99" t="n">
+      <c r="T31" s="99" t="n">
         <v>37.29</v>
       </c>
-      <c r="T31" s="99" t="n">
+      <c r="U31" s="99" t="n">
         <v>46.06</v>
       </c>
-      <c r="U31" s="99" t="n">
+      <c r="V31" s="99" t="n">
         <v>44.24</v>
-      </c>
-      <c r="V31" s="99" t="n">
-        <v>79.63</v>
       </c>
       <c r="W31" s="99" t="n">
         <v>79.63</v>
       </c>
       <c r="X31" s="99" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="Y31" s="99" t="n">
         <v>73.44</v>
       </c>
-      <c r="Y31" s="99" t="n">
+      <c r="Z31" s="99" t="n">
         <v>64.13</v>
       </c>
-      <c r="Z31" s="99" t="n">
+      <c r="AA31" s="99" t="n">
         <v>78.52</v>
       </c>
-      <c r="AA31" s="99" t="n">
+      <c r="AB31" s="99" t="n">
         <v>78.27</v>
       </c>
-      <c r="AB31" s="99" t="n">
+      <c r="AC31" s="99" t="n">
         <v>76.89</v>
       </c>
-      <c r="AC31" s="99" t="n">
+      <c r="AD31" s="99" t="n">
         <v>63.94</v>
       </c>
-      <c r="AD31" s="99" t="n">
+      <c r="AE31" s="99" t="n">
         <v>77.25</v>
-      </c>
-      <c r="AE31" s="99" t="n">
-        <v>76</v>
       </c>
     </row>
     <row r="32">
@@ -9792,139 +9792,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D32" s="96" t="inlineStr">
+      <c r="D32" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E32" s="97" t="inlineStr">
+      <c r="F32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F32" s="96" t="inlineStr">
+      <c r="G32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G32" s="96" t="inlineStr">
+      <c r="H32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H32" s="96" t="inlineStr">
+      <c r="I32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I32" s="96" t="inlineStr">
+      <c r="J32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J32" s="97" t="inlineStr">
+      <c r="K32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K32" s="96" t="inlineStr">
+      <c r="L32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L32" s="96" t="inlineStr">
+      <c r="M32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M32" s="96" t="inlineStr">
+      <c r="N32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N32" s="96" t="inlineStr">
+      <c r="O32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O32" s="96" t="inlineStr">
+      <c r="P32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P32" s="97" t="inlineStr">
+      <c r="Q32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q32" s="98" t="inlineStr">
+      <c r="R32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R32" s="98" t="inlineStr">
+      <c r="S32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S32" s="98" t="inlineStr">
+      <c r="T32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T32" s="98" t="inlineStr">
+      <c r="U32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U32" s="98" t="inlineStr">
+      <c r="V32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V32" s="97" t="inlineStr">
+      <c r="W32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W32" s="97" t="inlineStr">
+      <c r="X32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X32" s="98" t="inlineStr">
+      <c r="Y32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y32" s="98" t="inlineStr">
+      <c r="Z32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z32" s="97" t="inlineStr">
+      <c r="AA32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA32" s="97" t="inlineStr">
+      <c r="AB32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB32" s="97" t="inlineStr">
+      <c r="AC32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC32" s="97" t="inlineStr">
+      <c r="AD32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD32" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE32" s="96" t="inlineStr">
@@ -9943,91 +9943,91 @@
         <v>-0.89</v>
       </c>
       <c r="C33" s="99" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="D33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="D33" s="99" t="n">
+      <c r="E33" s="99" t="n">
         <v>0.9</v>
       </c>
-      <c r="E33" s="99" t="n">
+      <c r="F33" s="99" t="n">
         <v>1.13</v>
       </c>
-      <c r="F33" s="99" t="n">
+      <c r="G33" s="99" t="n">
         <v>1.93</v>
       </c>
-      <c r="G33" s="99" t="n">
+      <c r="H33" s="99" t="n">
         <v>0.65</v>
       </c>
-      <c r="H33" s="99" t="n">
+      <c r="I33" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="I33" s="99" t="n">
+      <c r="J33" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="J33" s="99" t="n">
+      <c r="K33" s="99" t="n">
         <v>0.44</v>
       </c>
-      <c r="K33" s="99" t="n">
+      <c r="L33" s="99" t="n">
         <v>-0.35</v>
       </c>
-      <c r="L33" s="99" t="n">
+      <c r="M33" s="99" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M33" s="99" t="n">
+      <c r="N33" s="99" t="n">
         <v>-1</v>
       </c>
-      <c r="N33" s="99" t="n">
+      <c r="O33" s="99" t="n">
         <v>-1.61</v>
       </c>
-      <c r="O33" s="99" t="n">
+      <c r="P33" s="99" t="n">
         <v>-1.66</v>
       </c>
-      <c r="P33" s="99" t="n">
+      <c r="Q33" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="Q33" s="99" t="n">
+      <c r="R33" s="99" t="n">
         <v>-4.11</v>
       </c>
-      <c r="R33" s="99" t="n">
+      <c r="S33" s="99" t="n">
         <v>-3.76</v>
       </c>
-      <c r="S33" s="99" t="n">
+      <c r="T33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="T33" s="99" t="n">
+      <c r="U33" s="99" t="n">
         <v>-0.28</v>
       </c>
-      <c r="U33" s="99" t="n">
+      <c r="V33" s="99" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="V33" s="99" t="n">
-        <v>3.06</v>
       </c>
       <c r="W33" s="99" t="n">
         <v>3.06</v>
       </c>
       <c r="X33" s="99" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y33" s="99" t="n">
         <v>3.91</v>
       </c>
-      <c r="Y33" s="99" t="n">
+      <c r="Z33" s="99" t="n">
         <v>4.32</v>
       </c>
-      <c r="Z33" s="99" t="n">
+      <c r="AA33" s="99" t="n">
         <v>6.09</v>
       </c>
-      <c r="AA33" s="99" t="n">
+      <c r="AB33" s="99" t="n">
         <v>5.91</v>
       </c>
-      <c r="AB33" s="99" t="n">
+      <c r="AC33" s="99" t="n">
         <v>5.66</v>
       </c>
-      <c r="AC33" s="99" t="n">
+      <c r="AD33" s="99" t="n">
         <v>3.52</v>
       </c>
-      <c r="AD33" s="99" t="n">
+      <c r="AE33" s="99" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AE33" s="99" t="n">
-        <v>6.46</v>
       </c>
     </row>
     <row r="34">
@@ -10040,91 +10040,91 @@
         <v>11.54</v>
       </c>
       <c r="C34" s="99" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="D34" s="99" t="n">
         <v>11.48</v>
       </c>
-      <c r="D34" s="99" t="n">
+      <c r="E34" s="99" t="n">
         <v>11.95</v>
       </c>
-      <c r="E34" s="99" t="n">
+      <c r="F34" s="99" t="n">
         <v>12.67</v>
       </c>
-      <c r="F34" s="99" t="n">
+      <c r="G34" s="99" t="n">
         <v>11.04</v>
       </c>
-      <c r="G34" s="99" t="n">
+      <c r="H34" s="99" t="n">
         <v>10.68</v>
       </c>
-      <c r="H34" s="99" t="n">
+      <c r="I34" s="99" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="I34" s="99" t="n">
+      <c r="J34" s="99" t="n">
         <v>9.98</v>
       </c>
-      <c r="J34" s="99" t="n">
+      <c r="K34" s="99" t="n">
         <v>7.16</v>
       </c>
-      <c r="K34" s="99" t="n">
+      <c r="L34" s="99" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="L34" s="99" t="n">
+      <c r="M34" s="99" t="n">
         <v>7.37</v>
       </c>
-      <c r="M34" s="99" t="n">
+      <c r="N34" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="N34" s="99" t="n">
+      <c r="O34" s="99" t="n">
         <v>7.12</v>
       </c>
-      <c r="O34" s="99" t="n">
+      <c r="P34" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="P34" s="99" t="n">
+      <c r="Q34" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="Q34" s="99" t="n">
+      <c r="R34" s="99" t="n">
         <v>4.85</v>
       </c>
-      <c r="R34" s="99" t="n">
+      <c r="S34" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="S34" s="99" t="n">
+      <c r="T34" s="99" t="n">
         <v>6.19</v>
       </c>
-      <c r="T34" s="99" t="n">
+      <c r="U34" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="U34" s="99" t="n">
+      <c r="V34" s="99" t="n">
         <v>5.35</v>
-      </c>
-      <c r="V34" s="99" t="n">
-        <v>10.58</v>
       </c>
       <c r="W34" s="99" t="n">
         <v>10.58</v>
       </c>
       <c r="X34" s="99" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="Y34" s="99" t="n">
         <v>8.9</v>
       </c>
-      <c r="Y34" s="99" t="n">
+      <c r="Z34" s="99" t="n">
         <v>7.88</v>
       </c>
-      <c r="Z34" s="99" t="n">
+      <c r="AA34" s="99" t="n">
         <v>10.75</v>
       </c>
-      <c r="AA34" s="99" t="n">
+      <c r="AB34" s="99" t="n">
         <v>11.21</v>
       </c>
-      <c r="AB34" s="99" t="n">
+      <c r="AC34" s="99" t="n">
         <v>10.31</v>
       </c>
-      <c r="AC34" s="99" t="n">
+      <c r="AD34" s="99" t="n">
         <v>8.26</v>
       </c>
-      <c r="AD34" s="99" t="n">
+      <c r="AE34" s="99" t="n">
         <v>11.35</v>
-      </c>
-      <c r="AE34" s="99" t="n">
-        <v>11.72</v>
       </c>
     </row>
     <row r="35">
@@ -10137,91 +10137,91 @@
         <v>74.7</v>
       </c>
       <c r="C35" s="99" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="D35" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="D35" s="99" t="n">
+      <c r="E35" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="E35" s="99" t="n">
+      <c r="F35" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="F35" s="99" t="n">
+      <c r="G35" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="G35" s="99" t="n">
+      <c r="H35" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="H35" s="99" t="n">
+      <c r="I35" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="I35" s="99" t="n">
+      <c r="J35" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="J35" s="99" t="n">
+      <c r="K35" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="K35" s="99" t="n">
+      <c r="L35" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="L35" s="99" t="n">
+      <c r="M35" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="M35" s="99" t="n">
+      <c r="N35" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="N35" s="99" t="n">
+      <c r="O35" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="O35" s="99" t="n">
+      <c r="P35" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="P35" s="99" t="n">
+      <c r="Q35" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="Q35" s="99" t="n">
+      <c r="R35" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="R35" s="99" t="n">
+      <c r="S35" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="S35" s="99" t="n">
+      <c r="T35" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="T35" s="99" t="n">
+      <c r="U35" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="U35" s="99" t="n">
+      <c r="V35" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="V35" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="W35" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="X35" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="Y35" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="Y35" s="99" t="n">
+      <c r="Z35" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="Z35" s="99" t="n">
+      <c r="AA35" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AA35" s="99" t="n">
+      <c r="AB35" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AB35" s="99" t="n">
+      <c r="AC35" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="AC35" s="99" t="n">
+      <c r="AD35" s="99" t="n">
         <v>24.22</v>
       </c>
-      <c r="AD35" s="99" t="n">
+      <c r="AE35" s="99" t="n">
         <v>86.91</v>
-      </c>
-      <c r="AE35" s="99" t="n">
-        <v>76.59</v>
       </c>
     </row>
     <row r="36">
@@ -10234,91 +10234,91 @@
         <v>74.7</v>
       </c>
       <c r="C36" s="99" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="D36" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="D36" s="99" t="n">
+      <c r="E36" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="E36" s="99" t="n">
+      <c r="F36" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="F36" s="99" t="n">
+      <c r="G36" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="G36" s="99" t="n">
+      <c r="H36" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="H36" s="99" t="n">
+      <c r="I36" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="I36" s="99" t="n">
+      <c r="J36" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="J36" s="99" t="n">
+      <c r="K36" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="K36" s="99" t="n">
+      <c r="L36" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="L36" s="99" t="n">
+      <c r="M36" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="M36" s="99" t="n">
+      <c r="N36" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="N36" s="99" t="n">
+      <c r="O36" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="O36" s="99" t="n">
+      <c r="P36" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="P36" s="99" t="n">
+      <c r="Q36" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="Q36" s="99" t="n">
+      <c r="R36" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="R36" s="99" t="n">
+      <c r="S36" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="S36" s="99" t="n">
+      <c r="T36" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="T36" s="99" t="n">
+      <c r="U36" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="U36" s="99" t="n">
+      <c r="V36" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="V36" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="W36" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="X36" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="Y36" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="Y36" s="99" t="n">
+      <c r="Z36" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="Z36" s="99" t="n">
+      <c r="AA36" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AA36" s="99" t="n">
+      <c r="AB36" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AB36" s="99" t="n">
+      <c r="AC36" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="AC36" s="99" t="n">
+      <c r="AD36" s="99" t="n">
         <v>24.22</v>
       </c>
-      <c r="AD36" s="99" t="n">
+      <c r="AE36" s="99" t="n">
         <v>86.91</v>
-      </c>
-      <c r="AE36" s="99" t="n">
-        <v>76.59</v>
       </c>
     </row>
     <row r="37">
@@ -10332,134 +10332,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C37" s="96" t="inlineStr">
+      <c r="C37" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D37" s="96" t="inlineStr">
+      <c r="E37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E37" s="96" t="inlineStr">
+      <c r="F37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F37" s="96" t="inlineStr">
+      <c r="G37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G37" s="96" t="inlineStr">
+      <c r="H37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H37" s="96" t="inlineStr">
+      <c r="I37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I37" s="96" t="inlineStr">
+      <c r="J37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J37" s="97" t="inlineStr">
+      <c r="K37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K37" s="97" t="inlineStr">
+      <c r="L37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L37" s="97" t="inlineStr">
+      <c r="M37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M37" s="97" t="inlineStr">
+      <c r="N37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N37" s="97" t="inlineStr">
+      <c r="O37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="98" t="inlineStr">
+      <c r="P37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P37" s="98" t="inlineStr">
+      <c r="Q37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q37" s="98" t="inlineStr">
+      <c r="R37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R37" s="98" t="inlineStr">
+      <c r="S37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S37" s="98" t="inlineStr">
+      <c r="T37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T37" s="98" t="inlineStr">
+      <c r="U37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U37" s="97" t="inlineStr">
+      <c r="V37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V37" s="97" t="inlineStr">
+      <c r="W37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W37" s="97" t="inlineStr">
+      <c r="X37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X37" s="97" t="inlineStr">
+      <c r="Y37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y37" s="97" t="inlineStr">
+      <c r="Z37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z37" s="97" t="inlineStr">
+      <c r="AA37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA37" s="97" t="inlineStr">
+      <c r="AB37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC37" s="96" t="inlineStr">
@@ -10485,94 +10485,94 @@
         </is>
       </c>
       <c r="B38" s="99" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="C38" s="99" t="n">
         <v>-7.32</v>
       </c>
-      <c r="C38" s="99" t="n">
+      <c r="D38" s="99" t="n">
         <v>-1.85</v>
       </c>
-      <c r="D38" s="99" t="n">
+      <c r="E38" s="99" t="n">
         <v>-2.87</v>
       </c>
-      <c r="E38" s="99" t="n">
+      <c r="F38" s="99" t="n">
         <v>-4.44</v>
       </c>
-      <c r="F38" s="99" t="n">
+      <c r="G38" s="99" t="n">
         <v>-4.15</v>
-      </c>
-      <c r="G38" s="99" t="n">
-        <v>-4.11</v>
       </c>
       <c r="H38" s="99" t="n">
         <v>-4.11</v>
       </c>
       <c r="I38" s="99" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="J38" s="99" t="n">
         <v>-6.33</v>
       </c>
-      <c r="J38" s="99" t="n">
+      <c r="K38" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="K38" s="99" t="n">
+      <c r="L38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="L38" s="99" t="n">
+      <c r="M38" s="99" t="n">
         <v>-5.28</v>
       </c>
-      <c r="M38" s="99" t="n">
+      <c r="N38" s="99" t="n">
         <v>-5.31</v>
       </c>
-      <c r="N38" s="99" t="n">
+      <c r="O38" s="99" t="n">
         <v>-4.5</v>
       </c>
-      <c r="O38" s="99" t="n">
+      <c r="P38" s="99" t="n">
         <v>-7.44</v>
       </c>
-      <c r="P38" s="99" t="n">
+      <c r="Q38" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="Q38" s="99" t="n">
+      <c r="R38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="R38" s="99" t="n">
+      <c r="S38" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="S38" s="99" t="n">
+      <c r="T38" s="99" t="n">
         <v>-5.71</v>
       </c>
-      <c r="T38" s="99" t="n">
+      <c r="U38" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="U38" s="99" t="n">
+      <c r="V38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="V38" s="99" t="n">
+      <c r="W38" s="99" t="n">
         <v>0.04</v>
       </c>
-      <c r="W38" s="99" t="n">
+      <c r="X38" s="99" t="n">
         <v>-0.14</v>
       </c>
-      <c r="X38" s="99" t="n">
+      <c r="Y38" s="99" t="n">
         <v>-0.33</v>
       </c>
-      <c r="Y38" s="99" t="n">
+      <c r="Z38" s="99" t="n">
         <v>-1.2</v>
       </c>
-      <c r="Z38" s="99" t="n">
+      <c r="AA38" s="99" t="n">
         <v>-1.63</v>
       </c>
-      <c r="AA38" s="99" t="n">
+      <c r="AB38" s="99" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AB38" s="99" t="n">
+      <c r="AC38" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AC38" s="99" t="n">
+      <c r="AD38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AD38" s="99" t="n">
+      <c r="AE38" s="99" t="n">
         <v>-2.33</v>
-      </c>
-      <c r="AE38" s="99" t="n">
-        <v>-2.15</v>
       </c>
     </row>
     <row r="39">
@@ -10582,94 +10582,94 @@
         </is>
       </c>
       <c r="B39" s="99" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="C39" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="C39" s="99" t="n">
+      <c r="D39" s="99" t="n">
         <v>2.15</v>
       </c>
-      <c r="D39" s="99" t="n">
+      <c r="E39" s="99" t="n">
         <v>-2.13</v>
       </c>
-      <c r="E39" s="99" t="n">
+      <c r="F39" s="99" t="n">
         <v>-4.01</v>
       </c>
-      <c r="F39" s="99" t="n">
+      <c r="G39" s="99" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="G39" s="99" t="n">
-        <v>-5.22</v>
       </c>
       <c r="H39" s="99" t="n">
         <v>-5.22</v>
       </c>
       <c r="I39" s="99" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="J39" s="99" t="n">
         <v>-7.96</v>
       </c>
-      <c r="J39" s="99" t="n">
+      <c r="K39" s="99" t="n">
         <v>-9.43</v>
       </c>
-      <c r="K39" s="99" t="n">
+      <c r="L39" s="99" t="n">
         <v>-11.19</v>
       </c>
-      <c r="L39" s="99" t="n">
+      <c r="M39" s="99" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M39" s="99" t="n">
+      <c r="N39" s="99" t="n">
         <v>-9.48</v>
       </c>
-      <c r="N39" s="99" t="n">
+      <c r="O39" s="99" t="n">
         <v>-9.92</v>
       </c>
-      <c r="O39" s="99" t="n">
+      <c r="P39" s="99" t="n">
         <v>-12.73</v>
       </c>
-      <c r="P39" s="99" t="n">
+      <c r="Q39" s="99" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="Q39" s="99" t="n">
+      <c r="R39" s="99" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="R39" s="99" t="n">
+      <c r="S39" s="99" t="n">
         <v>-5.98</v>
       </c>
-      <c r="S39" s="99" t="n">
+      <c r="T39" s="99" t="n">
         <v>-5.54</v>
       </c>
-      <c r="T39" s="99" t="n">
+      <c r="U39" s="99" t="n">
         <v>-4.26</v>
       </c>
-      <c r="U39" s="99" t="n">
+      <c r="V39" s="99" t="n">
         <v>-0.29</v>
       </c>
-      <c r="V39" s="99" t="n">
+      <c r="W39" s="99" t="n">
         <v>-0.31</v>
       </c>
-      <c r="W39" s="99" t="n">
+      <c r="X39" s="99" t="n">
         <v>-2.62</v>
       </c>
-      <c r="X39" s="99" t="n">
+      <c r="Y39" s="99" t="n">
         <v>-3.12</v>
       </c>
-      <c r="Y39" s="99" t="n">
+      <c r="Z39" s="99" t="n">
         <v>-4.29</v>
       </c>
-      <c r="Z39" s="99" t="n">
+      <c r="AA39" s="99" t="n">
         <v>-4.51</v>
       </c>
-      <c r="AA39" s="99" t="n">
+      <c r="AB39" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="AB39" s="99" t="n">
+      <c r="AC39" s="99" t="n">
         <v>-3.88</v>
       </c>
-      <c r="AC39" s="99" t="n">
+      <c r="AD39" s="99" t="n">
         <v>-2.44</v>
       </c>
-      <c r="AD39" s="99" t="n">
+      <c r="AE39" s="99" t="n">
         <v>-3.2</v>
-      </c>
-      <c r="AE39" s="99" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="40">
@@ -10679,94 +10679,94 @@
         </is>
       </c>
       <c r="B40" s="99" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="C40" s="99" t="n">
         <v>48.63</v>
       </c>
-      <c r="C40" s="99" t="n">
+      <c r="D40" s="99" t="n">
         <v>89.62</v>
       </c>
-      <c r="D40" s="99" t="n">
+      <c r="E40" s="99" t="n">
         <v>84.76000000000001</v>
       </c>
-      <c r="E40" s="99" t="n">
+      <c r="F40" s="99" t="n">
         <v>72.89</v>
       </c>
-      <c r="F40" s="99" t="n">
+      <c r="G40" s="99" t="n">
         <v>76.04000000000001</v>
-      </c>
-      <c r="G40" s="99" t="n">
-        <v>73.18000000000001</v>
       </c>
       <c r="H40" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
       <c r="I40" s="99" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="J40" s="99" t="n">
         <v>64.19</v>
       </c>
-      <c r="J40" s="99" t="n">
+      <c r="K40" s="99" t="n">
         <v>43.55</v>
       </c>
-      <c r="K40" s="99" t="n">
+      <c r="L40" s="99" t="n">
         <v>36.91</v>
       </c>
-      <c r="L40" s="99" t="n">
+      <c r="M40" s="99" t="n">
         <v>45.5</v>
       </c>
-      <c r="M40" s="99" t="n">
+      <c r="N40" s="99" t="n">
         <v>46.07</v>
       </c>
-      <c r="N40" s="99" t="n">
+      <c r="O40" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="O40" s="99" t="n">
+      <c r="P40" s="99" t="n">
         <v>10.06</v>
       </c>
-      <c r="P40" s="99" t="n">
+      <c r="Q40" s="99" t="n">
         <v>14.47</v>
       </c>
-      <c r="Q40" s="99" t="n">
+      <c r="R40" s="99" t="n">
         <v>15.02</v>
       </c>
-      <c r="R40" s="99" t="n">
+      <c r="S40" s="99" t="n">
         <v>16.6</v>
       </c>
-      <c r="S40" s="99" t="n">
+      <c r="T40" s="99" t="n">
         <v>19.01</v>
       </c>
-      <c r="T40" s="99" t="n">
+      <c r="U40" s="99" t="n">
         <v>22.94</v>
       </c>
-      <c r="U40" s="99" t="n">
+      <c r="V40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="V40" s="99" t="n">
+      <c r="W40" s="99" t="n">
         <v>75.7</v>
       </c>
-      <c r="W40" s="99" t="n">
+      <c r="X40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="X40" s="99" t="n">
+      <c r="Y40" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="Y40" s="99" t="n">
+      <c r="Z40" s="99" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="Z40" s="99" t="n">
+      <c r="AA40" s="99" t="n">
         <v>66.31999999999999</v>
       </c>
-      <c r="AA40" s="99" t="n">
+      <c r="AB40" s="99" t="n">
         <v>62.89</v>
       </c>
-      <c r="AB40" s="99" t="n">
+      <c r="AC40" s="99" t="n">
         <v>71.14</v>
       </c>
-      <c r="AC40" s="99" t="n">
+      <c r="AD40" s="99" t="n">
         <v>69.19</v>
       </c>
-      <c r="AD40" s="99" t="n">
+      <c r="AE40" s="99" t="n">
         <v>66.09</v>
-      </c>
-      <c r="AE40" s="99" t="n">
-        <v>68.45</v>
       </c>
     </row>
     <row r="41">
@@ -10776,94 +10776,94 @@
         </is>
       </c>
       <c r="B41" s="99" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="C41" s="99" t="n">
         <v>52.42</v>
       </c>
-      <c r="C41" s="99" t="n">
+      <c r="D41" s="99" t="n">
         <v>77.31</v>
       </c>
-      <c r="D41" s="99" t="n">
+      <c r="E41" s="99" t="n">
         <v>71.64</v>
       </c>
-      <c r="E41" s="99" t="n">
+      <c r="F41" s="99" t="n">
         <v>61.74</v>
       </c>
-      <c r="F41" s="99" t="n">
+      <c r="G41" s="99" t="n">
         <v>63.04</v>
-      </c>
-      <c r="G41" s="99" t="n">
-        <v>60.77</v>
       </c>
       <c r="H41" s="99" t="n">
         <v>60.77</v>
       </c>
       <c r="I41" s="99" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="J41" s="99" t="n">
         <v>54.21</v>
       </c>
-      <c r="J41" s="99" t="n">
+      <c r="K41" s="99" t="n">
         <v>42.56</v>
       </c>
-      <c r="K41" s="99" t="n">
+      <c r="L41" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="L41" s="99" t="n">
+      <c r="M41" s="99" t="n">
         <v>43.68</v>
       </c>
-      <c r="M41" s="99" t="n">
+      <c r="N41" s="99" t="n">
         <v>43.96</v>
       </c>
-      <c r="N41" s="99" t="n">
+      <c r="O41" s="99" t="n">
         <v>46.79</v>
       </c>
-      <c r="O41" s="99" t="n">
+      <c r="P41" s="99" t="n">
         <v>26.47</v>
       </c>
-      <c r="P41" s="99" t="n">
+      <c r="Q41" s="99" t="n">
         <v>31.18</v>
       </c>
-      <c r="Q41" s="99" t="n">
+      <c r="R41" s="99" t="n">
         <v>31.7</v>
       </c>
-      <c r="R41" s="99" t="n">
+      <c r="S41" s="99" t="n">
         <v>33.25</v>
       </c>
-      <c r="S41" s="99" t="n">
+      <c r="T41" s="99" t="n">
         <v>35.58</v>
       </c>
-      <c r="T41" s="99" t="n">
+      <c r="U41" s="99" t="n">
         <v>39.17</v>
       </c>
-      <c r="U41" s="99" t="n">
+      <c r="V41" s="99" t="n">
         <v>62.79</v>
       </c>
-      <c r="V41" s="99" t="n">
+      <c r="W41" s="99" t="n">
         <v>63.09</v>
       </c>
-      <c r="W41" s="99" t="n">
+      <c r="X41" s="99" t="n">
         <v>62.51</v>
       </c>
-      <c r="X41" s="99" t="n">
+      <c r="Y41" s="99" t="n">
         <v>59.46</v>
       </c>
-      <c r="Y41" s="99" t="n">
+      <c r="Z41" s="99" t="n">
         <v>59.6</v>
       </c>
-      <c r="Z41" s="99" t="n">
+      <c r="AA41" s="99" t="n">
         <v>58.83</v>
       </c>
-      <c r="AA41" s="99" t="n">
+      <c r="AB41" s="99" t="n">
         <v>57.26</v>
       </c>
-      <c r="AB41" s="99" t="n">
+      <c r="AC41" s="99" t="n">
         <v>60.15</v>
       </c>
-      <c r="AC41" s="99" t="n">
+      <c r="AD41" s="99" t="n">
         <v>59.04</v>
       </c>
-      <c r="AD41" s="99" t="n">
+      <c r="AE41" s="99" t="n">
         <v>57.26</v>
-      </c>
-      <c r="AE41" s="99" t="n">
-        <v>58.23</v>
       </c>
     </row>
     <row r="42">
@@ -10877,134 +10877,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C42" s="96" t="inlineStr">
+      <c r="C42" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D42" s="96" t="inlineStr">
+      <c r="E42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="96" t="inlineStr">
+      <c r="F42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="96" t="inlineStr">
+      <c r="G42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="96" t="inlineStr">
+      <c r="H42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="96" t="inlineStr">
+      <c r="I42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="96" t="inlineStr">
+      <c r="J42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="96" t="inlineStr">
+      <c r="K42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="97" t="inlineStr">
+      <c r="L42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="98" t="inlineStr">
+      <c r="M42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="98" t="inlineStr">
+      <c r="N42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N42" s="98" t="inlineStr">
+      <c r="O42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O42" s="98" t="inlineStr">
+      <c r="P42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P42" s="98" t="inlineStr">
+      <c r="Q42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q42" s="98" t="inlineStr">
+      <c r="R42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R42" s="97" t="inlineStr">
+      <c r="S42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="98" t="inlineStr">
+      <c r="T42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="97" t="inlineStr">
+      <c r="U42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U42" s="97" t="inlineStr">
+      <c r="V42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="97" t="inlineStr">
+      <c r="W42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="97" t="inlineStr">
+      <c r="X42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="97" t="inlineStr">
+      <c r="Y42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="97" t="inlineStr">
+      <c r="Z42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="97" t="inlineStr">
+      <c r="AA42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="97" t="inlineStr">
+      <c r="AB42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC42" s="96" t="inlineStr">
@@ -11033,61 +11033,61 @@
         <v>0.63</v>
       </c>
       <c r="C43" s="99" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D43" s="99" t="n">
         <v>1.1</v>
       </c>
-      <c r="D43" s="99" t="n">
+      <c r="E43" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="E43" s="99" t="n">
+      <c r="F43" s="99" t="n">
         <v>2.62</v>
       </c>
-      <c r="F43" s="99" t="n">
+      <c r="G43" s="99" t="n">
         <v>1.79</v>
       </c>
-      <c r="G43" s="99" t="n">
+      <c r="H43" s="99" t="n">
         <v>1.86</v>
       </c>
-      <c r="H43" s="99" t="n">
+      <c r="I43" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="I43" s="99" t="n">
+      <c r="J43" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="J43" s="99" t="n">
+      <c r="K43" s="99" t="n">
         <v>0.66</v>
       </c>
-      <c r="K43" s="99" t="n">
+      <c r="L43" s="99" t="n">
         <v>0.39</v>
       </c>
-      <c r="L43" s="99" t="n">
+      <c r="M43" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="M43" s="99" t="n">
+      <c r="N43" s="99" t="n">
         <v>-2.39</v>
       </c>
-      <c r="N43" s="99" t="n">
+      <c r="O43" s="99" t="n">
         <v>-1.83</v>
       </c>
-      <c r="O43" s="99" t="n">
+      <c r="P43" s="99" t="n">
         <v>-2.05</v>
       </c>
-      <c r="P43" s="99" t="n">
+      <c r="Q43" s="99" t="n">
         <v>-1.53</v>
       </c>
-      <c r="Q43" s="99" t="n">
+      <c r="R43" s="99" t="n">
         <v>-0.95</v>
       </c>
-      <c r="R43" s="99" t="n">
+      <c r="S43" s="99" t="n">
         <v>-2.12</v>
       </c>
-      <c r="S43" s="99" t="n">
+      <c r="T43" s="99" t="n">
         <v>-2.46</v>
       </c>
-      <c r="T43" s="99" t="n">
+      <c r="U43" s="99" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="U43" s="99" t="n">
-        <v>-0.53</v>
       </c>
       <c r="V43" s="99" t="n">
         <v>-0.53</v>
@@ -11096,28 +11096,28 @@
         <v>-0.53</v>
       </c>
       <c r="X43" s="99" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Y43" s="99" t="n">
         <v>-0.47</v>
       </c>
-      <c r="Y43" s="99" t="n">
+      <c r="Z43" s="99" t="n">
         <v>-0.17</v>
       </c>
-      <c r="Z43" s="99" t="n">
+      <c r="AA43" s="99" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AA43" s="99" t="n">
+      <c r="AB43" s="99" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AB43" s="99" t="n">
+      <c r="AC43" s="99" t="n">
         <v>0.42</v>
       </c>
-      <c r="AC43" s="99" t="n">
+      <c r="AD43" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD43" s="99" t="n">
+      <c r="AE43" s="99" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AE43" s="99" t="n">
-        <v>-0.01</v>
       </c>
     </row>
     <row r="44">
@@ -11130,61 +11130,61 @@
         <v>3.01</v>
       </c>
       <c r="C44" s="99" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D44" s="99" t="n">
         <v>2.85</v>
       </c>
-      <c r="D44" s="99" t="n">
+      <c r="E44" s="99" t="n">
         <v>1.83</v>
       </c>
-      <c r="E44" s="99" t="n">
+      <c r="F44" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="F44" s="99" t="n">
+      <c r="G44" s="99" t="n">
         <v>-0.78</v>
       </c>
-      <c r="G44" s="99" t="n">
+      <c r="H44" s="99" t="n">
         <v>-1.02</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="I44" s="99" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="I44" s="99" t="n">
+      <c r="J44" s="99" t="n">
         <v>-1.47</v>
       </c>
-      <c r="J44" s="99" t="n">
+      <c r="K44" s="99" t="n">
         <v>-1.42</v>
       </c>
-      <c r="K44" s="99" t="n">
+      <c r="L44" s="99" t="n">
         <v>-1.81</v>
       </c>
-      <c r="L44" s="99" t="n">
+      <c r="M44" s="99" t="n">
         <v>-2.26</v>
       </c>
-      <c r="M44" s="99" t="n">
+      <c r="N44" s="99" t="n">
         <v>-2.35</v>
       </c>
-      <c r="N44" s="99" t="n">
+      <c r="O44" s="99" t="n">
         <v>-1.57</v>
       </c>
-      <c r="O44" s="99" t="n">
+      <c r="P44" s="99" t="n">
         <v>-0.54</v>
       </c>
-      <c r="P44" s="99" t="n">
+      <c r="Q44" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="Q44" s="99" t="n">
+      <c r="R44" s="99" t="n">
         <v>1.94</v>
       </c>
-      <c r="R44" s="99" t="n">
+      <c r="S44" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="S44" s="99" t="n">
+      <c r="T44" s="99" t="n">
         <v>0.31</v>
       </c>
-      <c r="T44" s="99" t="n">
+      <c r="U44" s="99" t="n">
         <v>0.42</v>
-      </c>
-      <c r="U44" s="99" t="n">
-        <v>3.12</v>
       </c>
       <c r="V44" s="99" t="n">
         <v>3.12</v>
@@ -11193,28 +11193,28 @@
         <v>3.12</v>
       </c>
       <c r="X44" s="99" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y44" s="99" t="n">
         <v>3.72</v>
       </c>
-      <c r="Y44" s="99" t="n">
+      <c r="Z44" s="99" t="n">
         <v>2.73</v>
       </c>
-      <c r="Z44" s="99" t="n">
+      <c r="AA44" s="99" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA44" s="99" t="n">
+      <c r="AB44" s="99" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB44" s="99" t="n">
+      <c r="AC44" s="99" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC44" s="99" t="n">
+      <c r="AD44" s="99" t="n">
         <v>1.69</v>
       </c>
-      <c r="AD44" s="99" t="n">
+      <c r="AE44" s="99" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AE44" s="99" t="n">
-        <v>1.58</v>
       </c>
     </row>
     <row r="45">
@@ -11227,61 +11227,61 @@
         <v>65.09</v>
       </c>
       <c r="C45" s="99" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="D45" s="99" t="n">
         <v>86.66</v>
       </c>
-      <c r="D45" s="99" t="n">
+      <c r="E45" s="99" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="E45" s="99" t="n">
+      <c r="F45" s="99" t="n">
         <v>88</v>
       </c>
-      <c r="F45" s="99" t="n">
+      <c r="G45" s="99" t="n">
         <v>77.98</v>
       </c>
-      <c r="G45" s="99" t="n">
+      <c r="H45" s="99" t="n">
         <v>59.82</v>
       </c>
-      <c r="H45" s="99" t="n">
+      <c r="I45" s="99" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="I45" s="99" t="n">
+      <c r="J45" s="99" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="J45" s="99" t="n">
+      <c r="K45" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="K45" s="99" t="n">
+      <c r="L45" s="99" t="n">
         <v>60.96</v>
       </c>
-      <c r="L45" s="99" t="n">
+      <c r="M45" s="99" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="M45" s="99" t="n">
+      <c r="N45" s="99" t="n">
         <v>20.58</v>
       </c>
-      <c r="N45" s="99" t="n">
+      <c r="O45" s="99" t="n">
         <v>30.12</v>
       </c>
-      <c r="O45" s="99" t="n">
+      <c r="P45" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="P45" s="99" t="n">
+      <c r="Q45" s="99" t="n">
         <v>13.57</v>
       </c>
-      <c r="Q45" s="99" t="n">
+      <c r="R45" s="99" t="n">
         <v>28.44</v>
       </c>
-      <c r="R45" s="99" t="n">
+      <c r="S45" s="99" t="n">
         <v>44.72</v>
       </c>
-      <c r="S45" s="99" t="n">
+      <c r="T45" s="99" t="n">
         <v>14.66</v>
       </c>
-      <c r="T45" s="99" t="n">
+      <c r="U45" s="99" t="n">
         <v>28.1</v>
-      </c>
-      <c r="U45" s="99" t="n">
-        <v>80.38</v>
       </c>
       <c r="V45" s="99" t="n">
         <v>80.38</v>
@@ -11290,28 +11290,28 @@
         <v>80.38</v>
       </c>
       <c r="X45" s="99" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="Y45" s="99" t="n">
         <v>68.92</v>
       </c>
-      <c r="Y45" s="99" t="n">
+      <c r="Z45" s="99" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="Z45" s="99" t="n">
+      <c r="AA45" s="99" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="AA45" s="99" t="n">
+      <c r="AB45" s="99" t="n">
         <v>63.9</v>
       </c>
-      <c r="AB45" s="99" t="n">
+      <c r="AC45" s="99" t="n">
         <v>90.77</v>
       </c>
-      <c r="AC45" s="99" t="n">
+      <c r="AD45" s="99" t="n">
         <v>89.34</v>
       </c>
-      <c r="AD45" s="99" t="n">
+      <c r="AE45" s="99" t="n">
         <v>94.22</v>
-      </c>
-      <c r="AE45" s="99" t="n">
-        <v>91.38</v>
       </c>
     </row>
     <row r="46">
@@ -11324,61 +11324,61 @@
         <v>69.34999999999999</v>
       </c>
       <c r="C46" s="99" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="D46" s="99" t="n">
         <v>78.83</v>
       </c>
-      <c r="D46" s="99" t="n">
+      <c r="E46" s="99" t="n">
         <v>80.52</v>
       </c>
-      <c r="E46" s="99" t="n">
+      <c r="F46" s="99" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="F46" s="99" t="n">
+      <c r="G46" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="G46" s="99" t="n">
+      <c r="H46" s="99" t="n">
         <v>58.07</v>
       </c>
-      <c r="H46" s="99" t="n">
+      <c r="I46" s="99" t="n">
         <v>65.81</v>
       </c>
-      <c r="I46" s="99" t="n">
+      <c r="J46" s="99" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="J46" s="99" t="n">
+      <c r="K46" s="99" t="n">
         <v>58.52</v>
       </c>
-      <c r="K46" s="99" t="n">
+      <c r="L46" s="99" t="n">
         <v>51.86</v>
       </c>
-      <c r="L46" s="99" t="n">
+      <c r="M46" s="99" t="n">
         <v>16.23</v>
       </c>
-      <c r="M46" s="99" t="n">
+      <c r="N46" s="99" t="n">
         <v>25.94</v>
       </c>
-      <c r="N46" s="99" t="n">
+      <c r="O46" s="99" t="n">
         <v>31.58</v>
       </c>
-      <c r="O46" s="99" t="n">
+      <c r="P46" s="99" t="n">
         <v>22.65</v>
       </c>
-      <c r="P46" s="99" t="n">
+      <c r="Q46" s="99" t="n">
         <v>24.26</v>
       </c>
-      <c r="Q46" s="99" t="n">
+      <c r="R46" s="99" t="n">
         <v>38.08</v>
       </c>
-      <c r="R46" s="99" t="n">
+      <c r="S46" s="99" t="n">
         <v>49.25</v>
       </c>
-      <c r="S46" s="99" t="n">
+      <c r="T46" s="99" t="n">
         <v>35.21</v>
       </c>
-      <c r="T46" s="99" t="n">
+      <c r="U46" s="99" t="n">
         <v>49.75</v>
-      </c>
-      <c r="U46" s="99" t="n">
-        <v>76.69</v>
       </c>
       <c r="V46" s="99" t="n">
         <v>76.69</v>
@@ -11387,28 +11387,28 @@
         <v>76.69</v>
       </c>
       <c r="X46" s="99" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="Y46" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="Y46" s="99" t="n">
+      <c r="Z46" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="Z46" s="99" t="n">
+      <c r="AA46" s="99" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="AA46" s="99" t="n">
+      <c r="AB46" s="99" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="AB46" s="99" t="n">
+      <c r="AC46" s="99" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="AC46" s="99" t="n">
+      <c r="AD46" s="99" t="n">
         <v>82.43000000000001</v>
       </c>
-      <c r="AD46" s="99" t="n">
+      <c r="AE46" s="99" t="n">
         <v>84.70999999999999</v>
-      </c>
-      <c r="AE46" s="99" t="n">
-        <v>80.88</v>
       </c>
     </row>
     <row r="47">
@@ -11427,99 +11427,99 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D47" s="96" t="inlineStr">
+      <c r="D47" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E47" s="96" t="inlineStr">
+      <c r="F47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F47" s="96" t="inlineStr">
+      <c r="G47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G47" s="96" t="inlineStr">
+      <c r="H47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H47" s="96" t="inlineStr">
+      <c r="I47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I47" s="96" t="inlineStr">
+      <c r="J47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J47" s="97" t="inlineStr">
+      <c r="K47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K47" s="96" t="inlineStr">
+      <c r="L47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L47" s="96" t="inlineStr">
+      <c r="M47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M47" s="96" t="inlineStr">
+      <c r="N47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="96" t="inlineStr">
+      <c r="O47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="98" t="inlineStr">
+      <c r="P47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P47" s="97" t="inlineStr">
+      <c r="Q47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q47" s="98" t="inlineStr">
+      <c r="R47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R47" s="98" t="inlineStr">
+      <c r="S47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S47" s="97" t="inlineStr">
+      <c r="T47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T47" s="97" t="inlineStr">
+      <c r="U47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U47" s="97" t="inlineStr">
+      <c r="V47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="V47" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="W47" s="96" t="inlineStr">
@@ -11575,94 +11575,94 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="C48" s="99" t="n">
         <v>5.38</v>
       </c>
-      <c r="C48" s="99" t="n">
+      <c r="D48" s="99" t="n">
         <v>6.9</v>
       </c>
-      <c r="D48" s="99" t="n">
+      <c r="E48" s="99" t="n">
         <v>7.31</v>
       </c>
-      <c r="E48" s="99" t="n">
+      <c r="F48" s="99" t="n">
         <v>7.21</v>
       </c>
-      <c r="F48" s="99" t="n">
+      <c r="G48" s="99" t="n">
         <v>6.84</v>
       </c>
-      <c r="G48" s="99" t="n">
+      <c r="H48" s="99" t="n">
         <v>7.46</v>
       </c>
-      <c r="H48" s="99" t="n">
+      <c r="I48" s="99" t="n">
         <v>6.69</v>
       </c>
-      <c r="I48" s="99" t="n">
+      <c r="J48" s="99" t="n">
         <v>5.73</v>
       </c>
-      <c r="J48" s="99" t="n">
+      <c r="K48" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="K48" s="99" t="n">
+      <c r="L48" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="L48" s="99" t="n">
+      <c r="M48" s="99" t="n">
         <v>7.48</v>
       </c>
-      <c r="M48" s="99" t="n">
+      <c r="N48" s="99" t="n">
         <v>6.99</v>
       </c>
-      <c r="N48" s="99" t="n">
+      <c r="O48" s="99" t="n">
         <v>7.27</v>
       </c>
-      <c r="O48" s="99" t="n">
+      <c r="P48" s="99" t="n">
         <v>5.46</v>
       </c>
-      <c r="P48" s="99" t="n">
+      <c r="Q48" s="99" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q48" s="99" t="n">
+      <c r="R48" s="99" t="n">
         <v>6.18</v>
       </c>
-      <c r="R48" s="99" t="n">
+      <c r="S48" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="S48" s="99" t="n">
+      <c r="T48" s="99" t="n">
         <v>7.51</v>
       </c>
-      <c r="T48" s="99" t="n">
+      <c r="U48" s="99" t="n">
         <v>7.66</v>
       </c>
-      <c r="U48" s="99" t="n">
+      <c r="V48" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="V48" s="99" t="n">
+      <c r="W48" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="W48" s="99" t="n">
+      <c r="X48" s="99" t="n">
         <v>10.73</v>
       </c>
-      <c r="X48" s="99" t="n">
+      <c r="Y48" s="99" t="n">
         <v>13.95</v>
       </c>
-      <c r="Y48" s="99" t="n">
+      <c r="Z48" s="99" t="n">
         <v>6.95</v>
       </c>
-      <c r="Z48" s="99" t="n">
+      <c r="AA48" s="99" t="n">
         <v>10.48</v>
       </c>
-      <c r="AA48" s="99" t="n">
+      <c r="AB48" s="99" t="n">
         <v>10.57</v>
       </c>
-      <c r="AB48" s="99" t="n">
+      <c r="AC48" s="99" t="n">
         <v>8.84</v>
       </c>
-      <c r="AC48" s="99" t="n">
+      <c r="AD48" s="99" t="n">
         <v>7.83</v>
       </c>
-      <c r="AD48" s="99" t="n">
+      <c r="AE48" s="99" t="n">
         <v>7.31</v>
-      </c>
-      <c r="AE48" s="99" t="n">
-        <v>7.15</v>
       </c>
     </row>
     <row r="49">
@@ -11672,94 +11672,94 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="C49" s="99" t="n">
         <v>12.79</v>
       </c>
-      <c r="C49" s="99" t="n">
+      <c r="D49" s="99" t="n">
         <v>15.25</v>
       </c>
-      <c r="D49" s="99" t="n">
+      <c r="E49" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="E49" s="99" t="n">
+      <c r="F49" s="99" t="n">
         <v>15.29</v>
       </c>
-      <c r="F49" s="99" t="n">
+      <c r="G49" s="99" t="n">
         <v>14.9</v>
       </c>
-      <c r="G49" s="99" t="n">
+      <c r="H49" s="99" t="n">
         <v>14.75</v>
       </c>
-      <c r="H49" s="99" t="n">
+      <c r="I49" s="99" t="n">
         <v>14.79</v>
       </c>
-      <c r="I49" s="99" t="n">
+      <c r="J49" s="99" t="n">
         <v>13.96</v>
       </c>
-      <c r="J49" s="99" t="n">
+      <c r="K49" s="99" t="n">
         <v>14.46</v>
       </c>
-      <c r="K49" s="99" t="n">
+      <c r="L49" s="99" t="n">
         <v>14.07</v>
       </c>
-      <c r="L49" s="99" t="n">
+      <c r="M49" s="99" t="n">
         <v>14.24</v>
       </c>
-      <c r="M49" s="99" t="n">
+      <c r="N49" s="99" t="n">
         <v>14.96</v>
       </c>
-      <c r="N49" s="99" t="n">
+      <c r="O49" s="99" t="n">
         <v>15.21</v>
       </c>
-      <c r="O49" s="99" t="n">
+      <c r="P49" s="99" t="n">
         <v>12.06</v>
       </c>
-      <c r="P49" s="99" t="n">
+      <c r="Q49" s="99" t="n">
         <v>12.77</v>
       </c>
-      <c r="Q49" s="99" t="n">
+      <c r="R49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="R49" s="99" t="n">
+      <c r="S49" s="99" t="n">
         <v>11.57</v>
       </c>
-      <c r="S49" s="99" t="n">
+      <c r="T49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="T49" s="99" t="n">
+      <c r="U49" s="99" t="n">
         <v>12.04</v>
       </c>
-      <c r="U49" s="99" t="n">
+      <c r="V49" s="99" t="n">
         <v>11.38</v>
       </c>
-      <c r="V49" s="99" t="n">
+      <c r="W49" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="W49" s="99" t="n">
+      <c r="X49" s="99" t="n">
         <v>11.79</v>
       </c>
-      <c r="X49" s="99" t="n">
+      <c r="Y49" s="99" t="n">
         <v>11.18</v>
       </c>
-      <c r="Y49" s="99" t="n">
+      <c r="Z49" s="99" t="n">
         <v>10.81</v>
       </c>
-      <c r="Z49" s="99" t="n">
+      <c r="AA49" s="99" t="n">
         <v>10.8</v>
       </c>
-      <c r="AA49" s="99" t="n">
+      <c r="AB49" s="99" t="n">
         <v>12.69</v>
       </c>
-      <c r="AB49" s="99" t="n">
+      <c r="AC49" s="99" t="n">
         <v>12.14</v>
       </c>
-      <c r="AC49" s="99" t="n">
+      <c r="AD49" s="99" t="n">
         <v>10.89</v>
       </c>
-      <c r="AD49" s="99" t="n">
+      <c r="AE49" s="99" t="n">
         <v>11.15</v>
-      </c>
-      <c r="AE49" s="99" t="n">
-        <v>10.47</v>
       </c>
     </row>
     <row r="50">
@@ -11769,94 +11769,94 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="C50" s="99" t="n">
         <v>51.88</v>
       </c>
-      <c r="C50" s="99" t="n">
+      <c r="D50" s="99" t="n">
         <v>80.16</v>
       </c>
-      <c r="D50" s="99" t="n">
+      <c r="E50" s="99" t="n">
         <v>88.77</v>
       </c>
-      <c r="E50" s="99" t="n">
+      <c r="F50" s="99" t="n">
         <v>85.37</v>
       </c>
-      <c r="F50" s="99" t="n">
+      <c r="G50" s="99" t="n">
         <v>83.76000000000001</v>
       </c>
-      <c r="G50" s="99" t="n">
+      <c r="H50" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="H50" s="99" t="n">
+      <c r="I50" s="99" t="n">
         <v>82</v>
       </c>
-      <c r="I50" s="99" t="n">
+      <c r="J50" s="99" t="n">
         <v>68.75</v>
       </c>
-      <c r="J50" s="99" t="n">
+      <c r="K50" s="99" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="K50" s="99" t="n">
+      <c r="L50" s="99" t="n">
         <v>68.95</v>
       </c>
-      <c r="L50" s="99" t="n">
+      <c r="M50" s="99" t="n">
         <v>67.75</v>
       </c>
-      <c r="M50" s="99" t="n">
+      <c r="N50" s="99" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="N50" s="99" t="n">
+      <c r="O50" s="99" t="n">
         <v>68.14</v>
       </c>
-      <c r="O50" s="99" t="n">
+      <c r="P50" s="99" t="n">
         <v>46.32</v>
       </c>
-      <c r="P50" s="99" t="n">
+      <c r="Q50" s="99" t="n">
         <v>55.3</v>
       </c>
-      <c r="Q50" s="99" t="n">
+      <c r="R50" s="99" t="n">
         <v>47.35</v>
       </c>
-      <c r="R50" s="99" t="n">
+      <c r="S50" s="99" t="n">
         <v>37.44</v>
       </c>
-      <c r="S50" s="99" t="n">
+      <c r="T50" s="99" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="T50" s="99" t="n">
+      <c r="U50" s="99" t="n">
         <v>73.75</v>
       </c>
-      <c r="U50" s="99" t="n">
+      <c r="V50" s="99" t="n">
         <v>84.38</v>
       </c>
-      <c r="V50" s="99" t="n">
+      <c r="W50" s="99" t="n">
         <v>84.61</v>
       </c>
-      <c r="W50" s="99" t="n">
+      <c r="X50" s="99" t="n">
         <v>82.87</v>
       </c>
-      <c r="X50" s="99" t="n">
+      <c r="Y50" s="99" t="n">
         <v>80.63</v>
       </c>
-      <c r="Y50" s="99" t="n">
+      <c r="Z50" s="99" t="n">
         <v>76.7</v>
       </c>
-      <c r="Z50" s="99" t="n">
+      <c r="AA50" s="99" t="n">
         <v>75.8</v>
       </c>
-      <c r="AA50" s="99" t="n">
+      <c r="AB50" s="99" t="n">
         <v>75.66</v>
       </c>
-      <c r="AB50" s="99" t="n">
+      <c r="AC50" s="99" t="n">
         <v>68.2</v>
       </c>
-      <c r="AC50" s="99" t="n">
+      <c r="AD50" s="99" t="n">
         <v>67.75</v>
       </c>
-      <c r="AD50" s="99" t="n">
+      <c r="AE50" s="99" t="n">
         <v>65.86</v>
-      </c>
-      <c r="AE50" s="99" t="n">
-        <v>64.64</v>
       </c>
     </row>
     <row r="51">
@@ -11866,94 +11866,94 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="C51" s="99" t="n">
         <v>60.68</v>
       </c>
-      <c r="C51" s="99" t="n">
+      <c r="D51" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="D51" s="99" t="n">
+      <c r="E51" s="99" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="E51" s="99" t="n">
+      <c r="F51" s="99" t="n">
         <v>73.63</v>
       </c>
-      <c r="F51" s="99" t="n">
+      <c r="G51" s="99" t="n">
         <v>72.53</v>
       </c>
-      <c r="G51" s="99" t="n">
+      <c r="H51" s="99" t="n">
         <v>72.69</v>
       </c>
-      <c r="H51" s="99" t="n">
+      <c r="I51" s="99" t="n">
         <v>71.09</v>
       </c>
-      <c r="I51" s="99" t="n">
+      <c r="J51" s="99" t="n">
         <v>64.05</v>
       </c>
-      <c r="J51" s="99" t="n">
+      <c r="K51" s="99" t="n">
         <v>62.55</v>
       </c>
-      <c r="K51" s="99" t="n">
+      <c r="L51" s="99" t="n">
         <v>63.94</v>
       </c>
-      <c r="L51" s="99" t="n">
+      <c r="M51" s="99" t="n">
         <v>63.41</v>
       </c>
-      <c r="M51" s="99" t="n">
+      <c r="N51" s="99" t="n">
         <v>62.86</v>
       </c>
-      <c r="N51" s="99" t="n">
+      <c r="O51" s="99" t="n">
         <v>63.52</v>
       </c>
-      <c r="O51" s="99" t="n">
+      <c r="P51" s="99" t="n">
         <v>54.48</v>
       </c>
-      <c r="P51" s="99" t="n">
+      <c r="Q51" s="99" t="n">
         <v>58.24</v>
       </c>
-      <c r="Q51" s="99" t="n">
+      <c r="R51" s="99" t="n">
         <v>55.62</v>
       </c>
-      <c r="R51" s="99" t="n">
+      <c r="S51" s="99" t="n">
         <v>52.73</v>
       </c>
-      <c r="S51" s="99" t="n">
+      <c r="T51" s="99" t="n">
         <v>63.24</v>
       </c>
-      <c r="T51" s="99" t="n">
+      <c r="U51" s="99" t="n">
         <v>65.06</v>
       </c>
-      <c r="U51" s="99" t="n">
+      <c r="V51" s="99" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="V51" s="99" t="n">
+      <c r="W51" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="W51" s="99" t="n">
+      <c r="X51" s="99" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="X51" s="99" t="n">
+      <c r="Y51" s="99" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="Y51" s="99" t="n">
+      <c r="Z51" s="99" t="n">
         <v>63.2</v>
       </c>
-      <c r="Z51" s="99" t="n">
+      <c r="AA51" s="99" t="n">
         <v>62.77</v>
       </c>
-      <c r="AA51" s="99" t="n">
+      <c r="AB51" s="99" t="n">
         <v>62.7</v>
       </c>
-      <c r="AB51" s="99" t="n">
+      <c r="AC51" s="99" t="n">
         <v>59.22</v>
       </c>
-      <c r="AC51" s="99" t="n">
+      <c r="AD51" s="99" t="n">
         <v>59.02</v>
       </c>
-      <c r="AD51" s="99" t="n">
+      <c r="AE51" s="99" t="n">
         <v>58.18</v>
-      </c>
-      <c r="AE51" s="99" t="n">
-        <v>57.62</v>
       </c>
     </row>
     <row r="52">
@@ -11967,129 +11967,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C52" s="96" t="inlineStr">
+      <c r="C52" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D52" s="96" t="inlineStr">
+      <c r="E52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E52" s="96" t="inlineStr">
+      <c r="F52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F52" s="96" t="inlineStr">
+      <c r="G52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G52" s="97" t="inlineStr">
+      <c r="H52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="97" t="inlineStr">
+      <c r="I52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I52" s="96" t="inlineStr">
+      <c r="J52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J52" s="97" t="inlineStr">
+      <c r="K52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K52" s="96" t="inlineStr">
+      <c r="L52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L52" s="97" t="inlineStr">
+      <c r="M52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M52" s="96" t="inlineStr">
+      <c r="N52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N52" s="97" t="inlineStr">
+      <c r="O52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O52" s="98" t="inlineStr">
+      <c r="P52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P52" s="98" t="inlineStr">
+      <c r="Q52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q52" s="98" t="inlineStr">
+      <c r="R52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R52" s="98" t="inlineStr">
+      <c r="S52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S52" s="98" t="inlineStr">
+      <c r="T52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T52" s="98" t="inlineStr">
+      <c r="U52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U52" s="97" t="inlineStr">
+      <c r="V52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V52" s="97" t="inlineStr">
+      <c r="W52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W52" s="97" t="inlineStr">
+      <c r="X52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X52" s="96" t="inlineStr">
+      <c r="Y52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y52" s="97" t="inlineStr">
+      <c r="Z52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z52" s="97" t="inlineStr">
+      <c r="AA52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AA52" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB52" s="96" t="inlineStr">
@@ -12123,91 +12123,91 @@
         <v>0.11</v>
       </c>
       <c r="C53" s="99" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D53" s="99" t="n">
         <v>1.51</v>
       </c>
-      <c r="D53" s="99" t="n">
+      <c r="E53" s="99" t="n">
         <v>0.6</v>
       </c>
-      <c r="E53" s="99" t="n">
+      <c r="F53" s="99" t="n">
         <v>-0.87</v>
       </c>
-      <c r="F53" s="99" t="n">
+      <c r="G53" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="G53" s="99" t="n">
+      <c r="H53" s="99" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H53" s="99" t="n">
+      <c r="I53" s="99" t="n">
         <v>0.28</v>
       </c>
-      <c r="I53" s="99" t="n">
+      <c r="J53" s="99" t="n">
         <v>1.12</v>
       </c>
-      <c r="J53" s="99" t="n">
+      <c r="K53" s="99" t="n">
         <v>-2.16</v>
       </c>
-      <c r="K53" s="99" t="n">
+      <c r="L53" s="99" t="n">
         <v>-2.28</v>
       </c>
-      <c r="L53" s="99" t="n">
+      <c r="M53" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="M53" s="99" t="n">
+      <c r="N53" s="99" t="n">
         <v>-2.14</v>
       </c>
-      <c r="N53" s="99" t="n">
+      <c r="O53" s="99" t="n">
         <v>-3.08</v>
       </c>
-      <c r="O53" s="99" t="n">
+      <c r="P53" s="99" t="n">
         <v>-2.29</v>
       </c>
-      <c r="P53" s="99" t="n">
+      <c r="Q53" s="99" t="n">
         <v>-2.9</v>
       </c>
-      <c r="Q53" s="99" t="n">
+      <c r="R53" s="99" t="n">
         <v>-1.93</v>
       </c>
-      <c r="R53" s="99" t="n">
+      <c r="S53" s="99" t="n">
         <v>-2.01</v>
       </c>
-      <c r="S53" s="99" t="n">
+      <c r="T53" s="99" t="n">
         <v>-3.58</v>
       </c>
-      <c r="T53" s="99" t="n">
+      <c r="U53" s="99" t="n">
         <v>-4.62</v>
       </c>
-      <c r="U53" s="99" t="n">
+      <c r="V53" s="99" t="n">
         <v>-2.75</v>
       </c>
-      <c r="V53" s="99" t="n">
+      <c r="W53" s="99" t="n">
         <v>-3.14</v>
       </c>
-      <c r="W53" s="99" t="n">
+      <c r="X53" s="99" t="n">
         <v>-4.63</v>
       </c>
-      <c r="X53" s="99" t="n">
+      <c r="Y53" s="99" t="n">
         <v>-4.96</v>
       </c>
-      <c r="Y53" s="99" t="n">
+      <c r="Z53" s="99" t="n">
         <v>-5.36</v>
       </c>
-      <c r="Z53" s="99" t="n">
+      <c r="AA53" s="99" t="n">
         <v>-4.69</v>
       </c>
-      <c r="AA53" s="99" t="n">
+      <c r="AB53" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="AB53" s="99" t="n">
+      <c r="AC53" s="99" t="n">
         <v>-5.2</v>
       </c>
-      <c r="AC53" s="99" t="n">
+      <c r="AD53" s="99" t="n">
         <v>-5.7</v>
       </c>
-      <c r="AD53" s="99" t="n">
+      <c r="AE53" s="99" t="n">
         <v>-5.17</v>
-      </c>
-      <c r="AE53" s="99" t="n">
-        <v>-7.1</v>
       </c>
     </row>
     <row r="54">
@@ -12220,91 +12220,91 @@
         <v>-4.68</v>
       </c>
       <c r="C54" s="99" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="D54" s="99" t="n">
         <v>-2.89</v>
       </c>
-      <c r="D54" s="99" t="n">
+      <c r="E54" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="E54" s="99" t="n">
+      <c r="F54" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="F54" s="99" t="n">
+      <c r="G54" s="99" t="n">
         <v>-6.35</v>
       </c>
-      <c r="G54" s="99" t="n">
+      <c r="H54" s="99" t="n">
         <v>-6.86</v>
       </c>
-      <c r="H54" s="99" t="n">
+      <c r="I54" s="99" t="n">
         <v>-7.99</v>
       </c>
-      <c r="I54" s="99" t="n">
+      <c r="J54" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="J54" s="99" t="n">
+      <c r="K54" s="99" t="n">
         <v>-8.43</v>
       </c>
-      <c r="K54" s="99" t="n">
+      <c r="L54" s="99" t="n">
         <v>-8.75</v>
       </c>
-      <c r="L54" s="99" t="n">
+      <c r="M54" s="99" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="M54" s="99" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="N54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="O54" s="99" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="P54" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="P54" s="99" t="n">
+      <c r="Q54" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="Q54" s="99" t="n">
+      <c r="R54" s="99" t="n">
         <v>-9.02</v>
       </c>
-      <c r="R54" s="99" t="n">
+      <c r="S54" s="99" t="n">
         <v>-10.35</v>
       </c>
-      <c r="S54" s="99" t="n">
+      <c r="T54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="T54" s="99" t="n">
+      <c r="U54" s="99" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="U54" s="99" t="n">
+      <c r="V54" s="99" t="n">
         <v>-7.18</v>
       </c>
-      <c r="V54" s="99" t="n">
+      <c r="W54" s="99" t="n">
         <v>-6.04</v>
       </c>
-      <c r="W54" s="99" t="n">
+      <c r="X54" s="99" t="n">
         <v>-5.64</v>
       </c>
-      <c r="X54" s="99" t="n">
+      <c r="Y54" s="99" t="n">
         <v>-4.72</v>
       </c>
-      <c r="Y54" s="99" t="n">
+      <c r="Z54" s="99" t="n">
         <v>-5.61</v>
       </c>
-      <c r="Z54" s="99" t="n">
+      <c r="AA54" s="99" t="n">
         <v>-5.62</v>
       </c>
-      <c r="AA54" s="99" t="n">
+      <c r="AB54" s="99" t="n">
         <v>-4.58</v>
       </c>
-      <c r="AB54" s="99" t="n">
+      <c r="AC54" s="99" t="n">
         <v>-4.48</v>
       </c>
-      <c r="AC54" s="99" t="n">
+      <c r="AD54" s="99" t="n">
         <v>-5.43</v>
       </c>
-      <c r="AD54" s="99" t="n">
+      <c r="AE54" s="99" t="n">
         <v>-5.16</v>
-      </c>
-      <c r="AE54" s="99" t="n">
-        <v>-5.57</v>
       </c>
     </row>
     <row r="55">
@@ -12317,91 +12317,91 @@
         <v>44.35</v>
       </c>
       <c r="C55" s="99" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="D55" s="99" t="n">
         <v>85.76000000000001</v>
       </c>
-      <c r="D55" s="99" t="n">
+      <c r="E55" s="99" t="n">
         <v>82.23</v>
       </c>
-      <c r="E55" s="99" t="n">
+      <c r="F55" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="F55" s="99" t="n">
+      <c r="G55" s="99" t="n">
         <v>71.87</v>
       </c>
-      <c r="G55" s="99" t="n">
+      <c r="H55" s="99" t="n">
         <v>50.77</v>
       </c>
-      <c r="H55" s="99" t="n">
+      <c r="I55" s="99" t="n">
         <v>48.68</v>
       </c>
-      <c r="I55" s="99" t="n">
+      <c r="J55" s="99" t="n">
         <v>83.53</v>
       </c>
-      <c r="J55" s="99" t="n">
+      <c r="K55" s="99" t="n">
         <v>43.83</v>
       </c>
-      <c r="K55" s="99" t="n">
+      <c r="L55" s="99" t="n">
         <v>73.12</v>
       </c>
-      <c r="L55" s="99" t="n">
+      <c r="M55" s="99" t="n">
         <v>55.36</v>
       </c>
-      <c r="M55" s="99" t="n">
+      <c r="N55" s="99" t="n">
         <v>67.8</v>
       </c>
-      <c r="N55" s="99" t="n">
+      <c r="O55" s="99" t="n">
         <v>54.91</v>
       </c>
-      <c r="O55" s="99" t="n">
+      <c r="P55" s="99" t="n">
         <v>31.87</v>
       </c>
-      <c r="P55" s="99" t="n">
+      <c r="Q55" s="99" t="n">
         <v>35.24</v>
       </c>
-      <c r="Q55" s="99" t="n">
+      <c r="R55" s="99" t="n">
         <v>39.87</v>
       </c>
-      <c r="R55" s="99" t="n">
+      <c r="S55" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="S55" s="99" t="n">
+      <c r="T55" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="T55" s="99" t="n">
+      <c r="U55" s="99" t="n">
         <v>16.74</v>
       </c>
-      <c r="U55" s="99" t="n">
+      <c r="V55" s="99" t="n">
         <v>32.54</v>
       </c>
-      <c r="V55" s="99" t="n">
+      <c r="W55" s="99" t="n">
         <v>82.56</v>
       </c>
-      <c r="W55" s="99" t="n">
+      <c r="X55" s="99" t="n">
         <v>77.58</v>
       </c>
-      <c r="X55" s="99" t="n">
+      <c r="Y55" s="99" t="n">
         <v>88.48</v>
       </c>
-      <c r="Y55" s="99" t="n">
+      <c r="Z55" s="99" t="n">
         <v>71.72</v>
       </c>
-      <c r="Z55" s="99" t="n">
+      <c r="AA55" s="99" t="n">
         <v>65.42</v>
       </c>
-      <c r="AA55" s="99" t="n">
+      <c r="AB55" s="99" t="n">
         <v>94.41</v>
       </c>
-      <c r="AB55" s="99" t="n">
+      <c r="AC55" s="99" t="n">
         <v>93.34999999999999</v>
       </c>
-      <c r="AC55" s="99" t="n">
+      <c r="AD55" s="99" t="n">
         <v>86.56</v>
       </c>
-      <c r="AD55" s="99" t="n">
+      <c r="AE55" s="99" t="n">
         <v>87.25</v>
-      </c>
-      <c r="AE55" s="99" t="n">
-        <v>80.78</v>
       </c>
     </row>
     <row r="56">
@@ -12414,91 +12414,91 @@
         <v>52.35</v>
       </c>
       <c r="C56" s="99" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="D56" s="99" t="n">
         <v>78.61</v>
       </c>
-      <c r="D56" s="99" t="n">
+      <c r="E56" s="99" t="n">
         <v>75.48</v>
       </c>
-      <c r="E56" s="99" t="n">
+      <c r="F56" s="99" t="n">
         <v>57.98</v>
       </c>
-      <c r="F56" s="99" t="n">
+      <c r="G56" s="99" t="n">
         <v>66.2</v>
       </c>
-      <c r="G56" s="99" t="n">
+      <c r="H56" s="99" t="n">
         <v>52.83</v>
       </c>
-      <c r="H56" s="99" t="n">
+      <c r="I56" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="I56" s="99" t="n">
+      <c r="J56" s="99" t="n">
         <v>74.97</v>
       </c>
-      <c r="J56" s="99" t="n">
+      <c r="K56" s="99" t="n">
         <v>45.92</v>
       </c>
-      <c r="K56" s="99" t="n">
+      <c r="L56" s="99" t="n">
         <v>59.76</v>
       </c>
-      <c r="L56" s="99" t="n">
+      <c r="M56" s="99" t="n">
         <v>48.71</v>
       </c>
-      <c r="M56" s="99" t="n">
+      <c r="N56" s="99" t="n">
         <v>53.61</v>
       </c>
-      <c r="N56" s="99" t="n">
+      <c r="O56" s="99" t="n">
         <v>45.19</v>
       </c>
-      <c r="O56" s="99" t="n">
+      <c r="P56" s="99" t="n">
         <v>32.83</v>
       </c>
-      <c r="P56" s="99" t="n">
+      <c r="Q56" s="99" t="n">
         <v>34.58</v>
       </c>
-      <c r="Q56" s="99" t="n">
+      <c r="R56" s="99" t="n">
         <v>37.2</v>
       </c>
-      <c r="R56" s="99" t="n">
+      <c r="S56" s="99" t="n">
         <v>16.31</v>
       </c>
-      <c r="S56" s="99" t="n">
+      <c r="T56" s="99" t="n">
         <v>22.99</v>
       </c>
-      <c r="T56" s="99" t="n">
+      <c r="U56" s="99" t="n">
         <v>32.1</v>
       </c>
-      <c r="U56" s="99" t="n">
+      <c r="V56" s="99" t="n">
         <v>48.66</v>
       </c>
-      <c r="V56" s="99" t="n">
+      <c r="W56" s="99" t="n">
         <v>80.73</v>
       </c>
-      <c r="W56" s="99" t="n">
+      <c r="X56" s="99" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="X56" s="99" t="n">
+      <c r="Y56" s="99" t="n">
         <v>83.84</v>
       </c>
-      <c r="Y56" s="99" t="n">
+      <c r="Z56" s="99" t="n">
         <v>74.67</v>
       </c>
-      <c r="Z56" s="99" t="n">
+      <c r="AA56" s="99" t="n">
         <v>72.3</v>
       </c>
-      <c r="AA56" s="99" t="n">
+      <c r="AB56" s="99" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="AB56" s="99" t="n">
+      <c r="AC56" s="99" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="AC56" s="99" t="n">
+      <c r="AD56" s="99" t="n">
         <v>78.34</v>
       </c>
-      <c r="AD56" s="99" t="n">
+      <c r="AE56" s="99" t="n">
         <v>78.61</v>
-      </c>
-      <c r="AE56" s="99" t="n">
-        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -12507,139 +12507,139 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="97" t="inlineStr">
+      <c r="B57" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C57" s="96" t="inlineStr">
+      <c r="D57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D57" s="96" t="inlineStr">
+      <c r="E57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E57" s="97" t="inlineStr">
+      <c r="F57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F57" s="96" t="inlineStr">
+      <c r="G57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G57" s="96" t="inlineStr">
+      <c r="H57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H57" s="97" t="inlineStr">
+      <c r="I57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I57" s="96" t="inlineStr">
+      <c r="J57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J57" s="96" t="inlineStr">
+      <c r="K57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K57" s="96" t="inlineStr">
+      <c r="L57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L57" s="96" t="inlineStr">
+      <c r="M57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M57" s="96" t="inlineStr">
+      <c r="N57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N57" s="96" t="inlineStr">
+      <c r="O57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O57" s="98" t="inlineStr">
+      <c r="P57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P57" s="98" t="inlineStr">
+      <c r="Q57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q57" s="98" t="inlineStr">
+      <c r="R57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R57" s="98" t="inlineStr">
+      <c r="S57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S57" s="98" t="inlineStr">
+      <c r="T57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T57" s="98" t="inlineStr">
+      <c r="U57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U57" s="97" t="inlineStr">
+      <c r="V57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V57" s="97" t="inlineStr">
+      <c r="W57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W57" s="97" t="inlineStr">
+      <c r="X57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X57" s="96" t="inlineStr">
+      <c r="Y57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y57" s="97" t="inlineStr">
+      <c r="Z57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z57" s="97" t="inlineStr">
+      <c r="AA57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA57" s="97" t="inlineStr">
+      <c r="AB57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB57" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC57" s="96" t="inlineStr">
@@ -12665,94 +12665,94 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="C58" s="99" t="n">
         <v>4.62</v>
       </c>
-      <c r="C58" s="99" t="n">
+      <c r="D58" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="D58" s="99" t="n">
+      <c r="E58" s="99" t="n">
         <v>4.27</v>
       </c>
-      <c r="E58" s="99" t="n">
+      <c r="F58" s="99" t="n">
         <v>2.96</v>
       </c>
-      <c r="F58" s="99" t="n">
+      <c r="G58" s="99" t="n">
         <v>4.58</v>
       </c>
-      <c r="G58" s="99" t="n">
+      <c r="H58" s="99" t="n">
         <v>3.04</v>
       </c>
-      <c r="H58" s="99" t="n">
+      <c r="I58" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="I58" s="99" t="n">
+      <c r="J58" s="99" t="n">
         <v>4.35</v>
       </c>
-      <c r="J58" s="99" t="n">
+      <c r="K58" s="99" t="n">
         <v>3.06</v>
       </c>
-      <c r="K58" s="99" t="n">
+      <c r="L58" s="99" t="n">
         <v>3.02</v>
       </c>
-      <c r="L58" s="99" t="n">
+      <c r="M58" s="99" t="n">
         <v>1.68</v>
       </c>
-      <c r="M58" s="99" t="n">
+      <c r="N58" s="99" t="n">
         <v>2.95</v>
-      </c>
-      <c r="N58" s="99" t="n">
-        <v>1.45</v>
       </c>
       <c r="O58" s="99" t="n">
         <v>1.45</v>
       </c>
       <c r="P58" s="99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q58" s="99" t="n">
         <v>0.74</v>
       </c>
-      <c r="Q58" s="99" t="n">
+      <c r="R58" s="99" t="n">
         <v>2.08</v>
       </c>
-      <c r="R58" s="99" t="n">
+      <c r="S58" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="S58" s="99" t="n">
+      <c r="T58" s="99" t="n">
         <v>1.7</v>
       </c>
-      <c r="T58" s="99" t="n">
+      <c r="U58" s="99" t="n">
         <v>-0.21</v>
       </c>
-      <c r="U58" s="99" t="n">
+      <c r="V58" s="99" t="n">
         <v>2.05</v>
       </c>
-      <c r="V58" s="99" t="n">
+      <c r="W58" s="99" t="n">
         <v>2.36</v>
       </c>
-      <c r="W58" s="99" t="n">
+      <c r="X58" s="99" t="n">
         <v>1.88</v>
       </c>
-      <c r="X58" s="99" t="n">
+      <c r="Y58" s="99" t="n">
         <v>1.39</v>
       </c>
-      <c r="Y58" s="99" t="n">
+      <c r="Z58" s="99" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z58" s="99" t="n">
+      <c r="AA58" s="99" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA58" s="99" t="n">
+      <c r="AB58" s="99" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB58" s="99" t="n">
+      <c r="AC58" s="99" t="n">
         <v>0.73</v>
       </c>
-      <c r="AC58" s="99" t="n">
+      <c r="AD58" s="99" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AD58" s="99" t="n">
+      <c r="AE58" s="99" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="AE58" s="99" t="n">
-        <v>-1.72</v>
       </c>
     </row>
     <row r="59">
@@ -12762,94 +12762,94 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="C59" s="99" t="n">
         <v>7.78</v>
       </c>
-      <c r="C59" s="99" t="n">
+      <c r="D59" s="99" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="D59" s="99" t="n">
+      <c r="E59" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="E59" s="99" t="n">
+      <c r="F59" s="99" t="n">
         <v>4.66</v>
-      </c>
-      <c r="F59" s="99" t="n">
-        <v>3.7</v>
       </c>
       <c r="G59" s="99" t="n">
         <v>3.7</v>
       </c>
       <c r="H59" s="99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I59" s="99" t="n">
         <v>1.72</v>
       </c>
-      <c r="I59" s="99" t="n">
+      <c r="J59" s="99" t="n">
         <v>3.46</v>
       </c>
-      <c r="J59" s="99" t="n">
+      <c r="K59" s="99" t="n">
         <v>2.34</v>
       </c>
-      <c r="K59" s="99" t="n">
+      <c r="L59" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="L59" s="99" t="n">
+      <c r="M59" s="99" t="n">
         <v>0.84</v>
       </c>
-      <c r="M59" s="99" t="n">
+      <c r="N59" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="N59" s="99" t="n">
+      <c r="O59" s="99" t="n">
         <v>1.41</v>
       </c>
-      <c r="O59" s="99" t="n">
+      <c r="P59" s="99" t="n">
         <v>0.68</v>
       </c>
-      <c r="P59" s="99" t="n">
+      <c r="Q59" s="99" t="n">
         <v>0.48</v>
       </c>
-      <c r="Q59" s="99" t="n">
+      <c r="R59" s="99" t="n">
         <v>2.38</v>
       </c>
-      <c r="R59" s="99" t="n">
+      <c r="S59" s="99" t="n">
         <v>1.75</v>
       </c>
-      <c r="S59" s="99" t="n">
+      <c r="T59" s="99" t="n">
         <v>3.59</v>
       </c>
-      <c r="T59" s="99" t="n">
+      <c r="U59" s="99" t="n">
         <v>3.65</v>
       </c>
-      <c r="U59" s="99" t="n">
+      <c r="V59" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="V59" s="99" t="n">
+      <c r="W59" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="W59" s="99" t="n">
+      <c r="X59" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="X59" s="99" t="n">
+      <c r="Y59" s="99" t="n">
         <v>6.57</v>
       </c>
-      <c r="Y59" s="99" t="n">
+      <c r="Z59" s="99" t="n">
         <v>5.43</v>
       </c>
-      <c r="Z59" s="99" t="n">
+      <c r="AA59" s="99" t="n">
         <v>4.7</v>
       </c>
-      <c r="AA59" s="99" t="n">
+      <c r="AB59" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="AB59" s="99" t="n">
+      <c r="AC59" s="99" t="n">
         <v>5.28</v>
       </c>
-      <c r="AC59" s="99" t="n">
+      <c r="AD59" s="99" t="n">
         <v>4.39</v>
       </c>
-      <c r="AD59" s="99" t="n">
+      <c r="AE59" s="99" t="n">
         <v>4.03</v>
-      </c>
-      <c r="AE59" s="99" t="n">
-        <v>3.84</v>
       </c>
     </row>
     <row r="60">
@@ -12859,94 +12859,94 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="C60" s="99" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="C60" s="99" t="n">
+      <c r="D60" s="99" t="n">
         <v>83.8</v>
       </c>
-      <c r="D60" s="99" t="n">
+      <c r="E60" s="99" t="n">
         <v>76.95</v>
       </c>
-      <c r="E60" s="99" t="n">
+      <c r="F60" s="99" t="n">
         <v>59.47</v>
       </c>
-      <c r="F60" s="99" t="n">
+      <c r="G60" s="99" t="n">
         <v>69.06</v>
       </c>
-      <c r="G60" s="99" t="n">
+      <c r="H60" s="99" t="n">
         <v>59.71</v>
       </c>
-      <c r="H60" s="99" t="n">
+      <c r="I60" s="99" t="n">
         <v>50.15</v>
       </c>
-      <c r="I60" s="99" t="n">
+      <c r="J60" s="99" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="J60" s="99" t="n">
+      <c r="K60" s="99" t="n">
         <v>65.67</v>
       </c>
-      <c r="K60" s="99" t="n">
+      <c r="L60" s="99" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="L60" s="99" t="n">
+      <c r="M60" s="99" t="n">
         <v>60.74</v>
       </c>
-      <c r="M60" s="99" t="n">
+      <c r="N60" s="99" t="n">
         <v>69.64</v>
       </c>
-      <c r="N60" s="99" t="n">
+      <c r="O60" s="99" t="n">
         <v>56.63</v>
       </c>
-      <c r="O60" s="99" t="n">
+      <c r="P60" s="99" t="n">
         <v>34.87</v>
       </c>
-      <c r="P60" s="99" t="n">
+      <c r="Q60" s="99" t="n">
         <v>25.25</v>
       </c>
-      <c r="Q60" s="99" t="n">
+      <c r="R60" s="99" t="n">
         <v>36.38</v>
       </c>
-      <c r="R60" s="99" t="n">
+      <c r="S60" s="99" t="n">
         <v>13.61</v>
       </c>
-      <c r="S60" s="99" t="n">
+      <c r="T60" s="99" t="n">
         <v>28.38</v>
       </c>
-      <c r="T60" s="99" t="n">
+      <c r="U60" s="99" t="n">
         <v>29.73</v>
       </c>
-      <c r="U60" s="99" t="n">
+      <c r="V60" s="99" t="n">
         <v>46.54</v>
       </c>
-      <c r="V60" s="99" t="n">
+      <c r="W60" s="99" t="n">
         <v>93.47</v>
       </c>
-      <c r="W60" s="99" t="n">
+      <c r="X60" s="99" t="n">
         <v>92.75</v>
       </c>
-      <c r="X60" s="99" t="n">
+      <c r="Y60" s="99" t="n">
         <v>94.58</v>
       </c>
-      <c r="Y60" s="99" t="n">
+      <c r="Z60" s="99" t="n">
         <v>91.78</v>
       </c>
-      <c r="Z60" s="99" t="n">
+      <c r="AA60" s="99" t="n">
         <v>88.26000000000001</v>
       </c>
-      <c r="AA60" s="99" t="n">
+      <c r="AB60" s="99" t="n">
         <v>85.2</v>
       </c>
-      <c r="AB60" s="99" t="n">
+      <c r="AC60" s="99" t="n">
         <v>89.55</v>
       </c>
-      <c r="AC60" s="99" t="n">
+      <c r="AD60" s="99" t="n">
         <v>84.34</v>
       </c>
-      <c r="AD60" s="99" t="n">
+      <c r="AE60" s="99" t="n">
         <v>82.23999999999999</v>
-      </c>
-      <c r="AE60" s="99" t="n">
-        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -12956,94 +12956,94 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="C61" s="99" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="C61" s="99" t="n">
+      <c r="D61" s="99" t="n">
         <v>78.38</v>
       </c>
-      <c r="D61" s="99" t="n">
+      <c r="E61" s="99" t="n">
         <v>72.42</v>
       </c>
-      <c r="E61" s="99" t="n">
+      <c r="F61" s="99" t="n">
         <v>59.91</v>
       </c>
-      <c r="F61" s="99" t="n">
+      <c r="G61" s="99" t="n">
         <v>66</v>
       </c>
-      <c r="G61" s="99" t="n">
+      <c r="H61" s="99" t="n">
         <v>59.4</v>
       </c>
-      <c r="H61" s="99" t="n">
+      <c r="I61" s="99" t="n">
         <v>52.95</v>
       </c>
-      <c r="I61" s="99" t="n">
+      <c r="J61" s="99" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="J61" s="99" t="n">
+      <c r="K61" s="99" t="n">
         <v>61.14</v>
       </c>
-      <c r="K61" s="99" t="n">
+      <c r="L61" s="99" t="n">
         <v>62.6</v>
       </c>
-      <c r="L61" s="99" t="n">
+      <c r="M61" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="M61" s="99" t="n">
+      <c r="N61" s="99" t="n">
         <v>62.56</v>
       </c>
-      <c r="N61" s="99" t="n">
+      <c r="O61" s="99" t="n">
         <v>52.29</v>
       </c>
-      <c r="O61" s="99" t="n">
+      <c r="P61" s="99" t="n">
         <v>37.42</v>
       </c>
-      <c r="P61" s="99" t="n">
+      <c r="Q61" s="99" t="n">
         <v>31.32</v>
       </c>
-      <c r="Q61" s="99" t="n">
+      <c r="R61" s="99" t="n">
         <v>40.38</v>
       </c>
-      <c r="R61" s="99" t="n">
+      <c r="S61" s="99" t="n">
         <v>26.19</v>
       </c>
-      <c r="S61" s="99" t="n">
+      <c r="T61" s="99" t="n">
         <v>42.54</v>
       </c>
-      <c r="T61" s="99" t="n">
+      <c r="U61" s="99" t="n">
         <v>43.82</v>
       </c>
-      <c r="U61" s="99" t="n">
+      <c r="V61" s="99" t="n">
         <v>58.62</v>
       </c>
-      <c r="V61" s="99" t="n">
+      <c r="W61" s="99" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="W61" s="99" t="n">
+      <c r="X61" s="99" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="X61" s="99" t="n">
+      <c r="Y61" s="99" t="n">
         <v>88.2</v>
       </c>
-      <c r="Y61" s="99" t="n">
+      <c r="Z61" s="99" t="n">
         <v>84.89</v>
       </c>
-      <c r="Z61" s="99" t="n">
+      <c r="AA61" s="99" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="AA61" s="99" t="n">
+      <c r="AB61" s="99" t="n">
         <v>79.09</v>
       </c>
-      <c r="AB61" s="99" t="n">
+      <c r="AC61" s="99" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="AC61" s="99" t="n">
+      <c r="AD61" s="99" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="AD61" s="99" t="n">
+      <c r="AE61" s="99" t="n">
         <v>74.75</v>
-      </c>
-      <c r="AE61" s="99" t="n">
-        <v>71.06</v>
       </c>
     </row>
     <row r="63">

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -800,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1073,6 +1073,7 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9940,7 +9941,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>-0.89</v>
+        <v>-2.68</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>-0.89</v>
@@ -10037,7 +10038,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>11.54</v>
+        <v>10.76</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>11.54</v>
@@ -10128,13 +10129,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="80" t="inlineStr">
+      <c r="A35" s="100" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>74.7</v>
+        <v>15.42</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>74.7</v>
@@ -10225,13 +10226,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="80" t="inlineStr">
+      <c r="A36" s="100" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>74.7</v>
+        <v>15.42</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>74.7</v>
@@ -10485,7 +10486,7 @@
         </is>
       </c>
       <c r="B38" s="99" t="n">
-        <v>-6.4</v>
+        <v>-5.52</v>
       </c>
       <c r="C38" s="99" t="n">
         <v>-7.32</v>
@@ -10582,7 +10583,7 @@
         </is>
       </c>
       <c r="B39" s="99" t="n">
-        <v>-3.72</v>
+        <v>-2.82</v>
       </c>
       <c r="C39" s="99" t="n">
         <v>-3.63</v>
@@ -10679,7 +10680,7 @@
         </is>
       </c>
       <c r="B40" s="99" t="n">
-        <v>53.79</v>
+        <v>57.87</v>
       </c>
       <c r="C40" s="99" t="n">
         <v>48.63</v>
@@ -10776,7 +10777,7 @@
         </is>
       </c>
       <c r="B41" s="99" t="n">
-        <v>55.56</v>
+        <v>58.22</v>
       </c>
       <c r="C41" s="99" t="n">
         <v>52.42</v>
@@ -11030,7 +11031,7 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="C43" s="99" t="n">
         <v>0.63</v>
@@ -11127,7 +11128,7 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>3.01</v>
@@ -11224,7 +11225,7 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
-        <v>65.09</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="C45" s="99" t="n">
         <v>65.09</v>
@@ -11321,7 +11322,7 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
-        <v>69.34999999999999</v>
+        <v>74.77</v>
       </c>
       <c r="C46" s="99" t="n">
         <v>69.34999999999999</v>
@@ -11672,7 +11673,7 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>12.84</v>
+        <v>12.83</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>12.79</v>
@@ -11769,7 +11770,7 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>51.41</v>
+        <v>51.33</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>51.88</v>
@@ -11866,7 +11867,7 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>60.44</v>
+        <v>60.39</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>60.68</v>
@@ -11962,9 +11963,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B52" s="98" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C52" s="97" t="inlineStr">
@@ -12120,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>0.11</v>
+        <v>0.87</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>0.11</v>
@@ -12217,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-4.68</v>
+        <v>-5.85</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-4.68</v>
@@ -12314,7 +12315,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>44.35</v>
+        <v>34.48</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>44.35</v>
@@ -12411,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>52.35</v>
+        <v>44.93</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>52.35</v>
@@ -12507,9 +12508,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B57" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C57" s="97" t="inlineStr">
@@ -12665,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>6.48</v>
+        <v>5.36</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>4.62</v>
@@ -12762,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>7.72</v>
+        <v>6.58</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>7.78</v>
@@ -12859,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>71.76000000000001</v>
+        <v>55.81</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>67.01000000000001</v>
@@ -12956,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>70.48</v>
+        <v>59.76</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>67.34999999999999</v>
@@ -13049,7 +13050,7 @@
     <row r="63">
       <c r="A63" s="95" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：ixic:RSI2:15.42&lt;=36;ixic:RSI2:15.42&lt;=35</t>
         </is>
       </c>
     </row>
@@ -16708,13 +16709,13 @@
       <c r="G2" s="36" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="100" t="n">
+      <c r="H2" s="101" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="36" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="101">
+      <c r="J2" s="102">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16745,13 +16746,13 @@
       <c r="G3" s="39" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="100" t="n">
+      <c r="H3" s="101" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="36" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="101">
+      <c r="J3" s="102">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16782,13 +16783,13 @@
       <c r="G4" s="36" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="100" t="n">
+      <c r="H4" s="101" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="36" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="101">
+      <c r="J4" s="102">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16819,13 +16820,13 @@
       <c r="G5" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="100" t="n">
+      <c r="H5" s="101" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="36" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="101">
+      <c r="J5" s="102">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16856,13 +16857,13 @@
       <c r="G6" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="102" t="n">
+      <c r="H6" s="103" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="24" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="101">
+      <c r="J6" s="102">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16893,13 +16894,13 @@
       <c r="G7" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="100" t="n">
+      <c r="H7" s="101" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="36" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="101">
+      <c r="J7" s="102">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16930,13 +16931,13 @@
       <c r="G8" s="24" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="102" t="n">
+      <c r="H8" s="103" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="101">
+      <c r="J8" s="102">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16967,13 +16968,13 @@
       <c r="G9" s="24" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="102" t="n">
+      <c r="H9" s="103" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="102">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -17004,13 +17005,13 @@
       <c r="G10" s="24" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="102" t="n">
+      <c r="H10" s="103" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="104">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17041,13 +17042,13 @@
       <c r="G11" s="47" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="104" t="n">
+      <c r="H11" s="105" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="47" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="105">
+      <c r="J11" s="106">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17078,13 +17079,13 @@
       <c r="G12" s="24" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="102" t="n">
+      <c r="H12" s="103" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="103">
+      <c r="J12" s="104">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17115,13 +17116,13 @@
       <c r="G13" s="47" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="104" t="n">
+      <c r="H13" s="105" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="47" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="105">
+      <c r="J13" s="106">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17152,13 +17153,13 @@
       <c r="G14" s="24" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="102" t="n">
+      <c r="H14" s="103" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="24" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="103">
+      <c r="J14" s="104">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17189,13 +17190,13 @@
       <c r="G15" s="47" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="104" t="n">
+      <c r="H15" s="105" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="47" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="105">
+      <c r="J15" s="106">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17226,13 +17227,13 @@
       <c r="G16" s="24" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="102" t="n">
+      <c r="H16" s="103" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="103">
+      <c r="J16" s="104">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17263,13 +17264,13 @@
       <c r="G17" s="47" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="104" t="n">
+      <c r="H17" s="105" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="47" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="105">
+      <c r="J17" s="106">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17300,13 +17301,13 @@
       <c r="G18" s="24" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="102" t="n">
+      <c r="H18" s="103" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="103">
+      <c r="J18" s="104">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17337,13 +17338,13 @@
       <c r="G19" s="47" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="104" t="n">
+      <c r="H19" s="105" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="47" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="105">
+      <c r="J19" s="106">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17374,13 +17375,13 @@
       <c r="G20" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="102" t="n">
+      <c r="H20" s="103" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="103">
+      <c r="J20" s="104">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17411,13 +17412,13 @@
       <c r="G21" s="47" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="104" t="n">
+      <c r="H21" s="105" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="47" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="105">
+      <c r="J21" s="106">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17446,13 +17447,13 @@
       <c r="G22" s="68" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="106" t="n">
+      <c r="H22" s="107" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="68" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="103">
+      <c r="J22" s="104">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17481,13 +17482,13 @@
       <c r="G23" s="68" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="106" t="n">
+      <c r="H23" s="107" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="103">
+      <c r="J23" s="104">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17516,13 +17517,13 @@
       <c r="G24" s="24" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="102" t="n">
+      <c r="H24" s="103" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="103">
+      <c r="J24" s="104">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17551,13 +17552,13 @@
       <c r="G25" s="24" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="102" t="n">
+      <c r="H25" s="103" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="24" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="103">
+      <c r="J25" s="104">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17586,13 +17587,13 @@
       <c r="G26" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="102" t="n">
+      <c r="H26" s="103" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="103">
+      <c r="J26" s="104">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17621,13 +17622,13 @@
       <c r="G27" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="102" t="n">
+      <c r="H27" s="103" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="24" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="103">
+      <c r="J27" s="104">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17656,13 +17657,13 @@
       <c r="G28" s="68" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="106" t="n">
+      <c r="H28" s="107" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="68" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="103">
+      <c r="J28" s="104">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17691,13 +17692,13 @@
       <c r="G29" s="44" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="107" t="n">
+      <c r="H29" s="108" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="44" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="105">
+      <c r="J29" s="106">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17726,13 +17727,13 @@
       <c r="G30" s="68" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="106" t="n">
+      <c r="H30" s="107" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="68" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="103">
+      <c r="J30" s="104">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17761,13 +17762,13 @@
       <c r="G31" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="107" t="n">
+      <c r="H31" s="108" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="44" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="105">
+      <c r="J31" s="106">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17796,13 +17797,13 @@
       <c r="G32" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="106" t="n">
+      <c r="H32" s="107" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="68" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="103">
+      <c r="J32" s="104">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17831,13 +17832,13 @@
       <c r="G33" s="44" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="107" t="n">
+      <c r="H33" s="108" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="44" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="105">
+      <c r="J33" s="106">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17866,13 +17867,13 @@
       <c r="G34" s="44" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="107" t="n">
+      <c r="H34" s="108" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="44" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="105">
+      <c r="J34" s="106">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17901,13 +17902,13 @@
       <c r="G35" s="68" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="106" t="n">
+      <c r="H35" s="107" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="103">
+      <c r="J35" s="104">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17936,13 +17937,13 @@
       <c r="G36" s="44" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="107" t="n">
+      <c r="H36" s="108" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="44" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="105">
+      <c r="J36" s="106">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17971,13 +17972,13 @@
       <c r="G37" s="68" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="106" t="n">
+      <c r="H37" s="107" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="68" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="103">
+      <c r="J37" s="104">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18006,13 +18007,13 @@
       <c r="G38" s="68" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="106" t="n">
+      <c r="H38" s="107" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="68" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="103">
+      <c r="J38" s="104">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18041,13 +18042,13 @@
       <c r="G39" s="44" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="107" t="n">
+      <c r="H39" s="108" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="44" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="105">
+      <c r="J39" s="106">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -6358,152 +6358,152 @@
       </c>
       <c r="B1" s="81" t="inlineStr">
         <is>
+          <t>241002</t>
+        </is>
+      </c>
+      <c r="C1" s="81" t="inlineStr">
+        <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="T1" s="81" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="T1" s="81" t="inlineStr">
+      <c r="U1" s="81" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="U1" s="81" t="inlineStr">
+      <c r="V1" s="81" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="V1" s="81" t="inlineStr">
+      <c r="W1" s="81" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="W1" s="81" t="inlineStr">
+      <c r="X1" s="81" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="X1" s="81" t="inlineStr">
+      <c r="Y1" s="81" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="Y1" s="81" t="inlineStr">
+      <c r="Z1" s="81" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="Z1" s="81" t="inlineStr">
+      <c r="AA1" s="81" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="AA1" s="81" t="inlineStr">
+      <c r="AB1" s="81" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="AB1" s="81" t="inlineStr">
+      <c r="AC1" s="81" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="AC1" s="81" t="inlineStr">
+      <c r="AD1" s="81" t="inlineStr">
         <is>
           <t>240823</t>
         </is>
       </c>
-      <c r="AD1" s="81" t="inlineStr">
+      <c r="AE1" s="81" t="inlineStr">
         <is>
           <t>240822</t>
-        </is>
-      </c>
-      <c r="AE1" s="81" t="inlineStr">
-        <is>
-          <t>240821</t>
         </is>
       </c>
     </row>
@@ -6543,114 +6543,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H2" s="97" t="inlineStr">
+      <c r="H2" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="97" t="inlineStr">
+      <c r="J2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="97" t="inlineStr">
+      <c r="K2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="97" t="inlineStr">
+      <c r="L2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="98" t="inlineStr">
+      <c r="M2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="N2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="98" t="inlineStr">
+      <c r="O2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="98" t="inlineStr">
+      <c r="P2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="98" t="inlineStr">
+      <c r="Q2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="98" t="inlineStr">
+      <c r="R2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="98" t="inlineStr">
+      <c r="S2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="98" t="inlineStr">
+      <c r="T2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="98" t="inlineStr">
+      <c r="U2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="98" t="inlineStr">
+      <c r="V2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="98" t="inlineStr">
+      <c r="W2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="98" t="inlineStr">
+      <c r="X2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="97" t="inlineStr">
+      <c r="Y2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y2" s="98" t="inlineStr">
+      <c r="Z2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="98" t="inlineStr">
+      <c r="AA2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="98" t="inlineStr">
+      <c r="AB2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB2" s="97" t="inlineStr">
+      <c r="AC2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC2" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD2" s="98" t="inlineStr">
@@ -6677,31 +6677,31 @@
         <v>12.81</v>
       </c>
       <c r="D3" s="99" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="E3" s="99" t="n">
         <v>3.53</v>
       </c>
-      <c r="E3" s="99" t="n">
+      <c r="F3" s="99" t="n">
         <v>0.13</v>
       </c>
-      <c r="F3" s="99" t="n">
+      <c r="G3" s="99" t="n">
         <v>-3.29</v>
       </c>
-      <c r="G3" s="99" t="n">
+      <c r="H3" s="99" t="n">
         <v>-3.51</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="I3" s="99" t="n">
         <v>-6.68</v>
       </c>
-      <c r="I3" s="99" t="n">
+      <c r="J3" s="99" t="n">
         <v>-7.93</v>
       </c>
-      <c r="J3" s="99" t="n">
+      <c r="K3" s="99" t="n">
         <v>-7.25</v>
       </c>
-      <c r="K3" s="99" t="n">
+      <c r="L3" s="99" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="L3" s="99" t="n">
-        <v>-9.81</v>
       </c>
       <c r="M3" s="99" t="n">
         <v>-9.81</v>
@@ -6710,55 +6710,55 @@
         <v>-9.81</v>
       </c>
       <c r="O3" s="99" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="P3" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="P3" s="99" t="n">
+      <c r="Q3" s="99" t="n">
         <v>-9.82</v>
       </c>
-      <c r="Q3" s="99" t="n">
+      <c r="R3" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="R3" s="99" t="n">
+      <c r="S3" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="S3" s="99" t="n">
+      <c r="T3" s="99" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="T3" s="99" t="n">
+      <c r="U3" s="99" t="n">
         <v>-7.94</v>
       </c>
-      <c r="U3" s="99" t="n">
+      <c r="V3" s="99" t="n">
         <v>-8.34</v>
       </c>
-      <c r="V3" s="99" t="n">
+      <c r="W3" s="99" t="n">
         <v>-7.43</v>
       </c>
-      <c r="W3" s="99" t="n">
+      <c r="X3" s="99" t="n">
         <v>-7.87</v>
       </c>
-      <c r="X3" s="99" t="n">
+      <c r="Y3" s="99" t="n">
         <v>-6.78</v>
       </c>
-      <c r="Y3" s="99" t="n">
+      <c r="Z3" s="99" t="n">
         <v>-7.9</v>
       </c>
-      <c r="Z3" s="99" t="n">
+      <c r="AA3" s="99" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="AA3" s="99" t="n">
+      <c r="AB3" s="99" t="n">
         <v>-7.46</v>
       </c>
-      <c r="AB3" s="99" t="n">
+      <c r="AC3" s="99" t="n">
         <v>-7.49</v>
       </c>
-      <c r="AC3" s="99" t="n">
+      <c r="AD3" s="99" t="n">
         <v>-7.68</v>
       </c>
-      <c r="AD3" s="99" t="n">
+      <c r="AE3" s="99" t="n">
         <v>-8.43</v>
-      </c>
-      <c r="AE3" s="99" t="n">
-        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -6774,31 +6774,31 @@
         <v>8.710000000000001</v>
       </c>
       <c r="D4" s="99" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="E4" s="99" t="n">
         <v>0.41</v>
       </c>
-      <c r="E4" s="99" t="n">
+      <c r="F4" s="99" t="n">
         <v>-2.48</v>
       </c>
-      <c r="F4" s="99" t="n">
+      <c r="G4" s="99" t="n">
         <v>-4.76</v>
       </c>
-      <c r="G4" s="99" t="n">
+      <c r="H4" s="99" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="I4" s="99" t="n">
         <v>-8.16</v>
       </c>
-      <c r="I4" s="99" t="n">
+      <c r="J4" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="J4" s="99" t="n">
+      <c r="K4" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="K4" s="99" t="n">
+      <c r="L4" s="99" t="n">
         <v>-10.85</v>
-      </c>
-      <c r="L4" s="99" t="n">
-        <v>-12.12</v>
       </c>
       <c r="M4" s="99" t="n">
         <v>-12.12</v>
@@ -6807,55 +6807,55 @@
         <v>-12.12</v>
       </c>
       <c r="O4" s="99" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="P4" s="99" t="n">
         <v>-11.77</v>
       </c>
-      <c r="P4" s="99" t="n">
+      <c r="Q4" s="99" t="n">
         <v>-11.13</v>
       </c>
-      <c r="Q4" s="99" t="n">
+      <c r="R4" s="99" t="n">
         <v>-11.05</v>
       </c>
-      <c r="R4" s="99" t="n">
+      <c r="S4" s="99" t="n">
         <v>-10.42</v>
       </c>
-      <c r="S4" s="99" t="n">
+      <c r="T4" s="99" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="T4" s="99" t="n">
+      <c r="U4" s="99" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="U4" s="99" t="n">
+      <c r="V4" s="99" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="V4" s="99" t="n">
+      <c r="W4" s="99" t="n">
         <v>-8.65</v>
       </c>
-      <c r="W4" s="99" t="n">
+      <c r="X4" s="99" t="n">
         <v>-7.71</v>
       </c>
-      <c r="X4" s="99" t="n">
+      <c r="Y4" s="99" t="n">
         <v>-6.12</v>
       </c>
-      <c r="Y4" s="99" t="n">
+      <c r="Z4" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="Z4" s="99" t="n">
+      <c r="AA4" s="99" t="n">
         <v>-6.9</v>
       </c>
-      <c r="AA4" s="99" t="n">
+      <c r="AB4" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AB4" s="99" t="n">
+      <c r="AC4" s="99" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AC4" s="99" t="n">
+      <c r="AD4" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="AD4" s="99" t="n">
+      <c r="AE4" s="99" t="n">
         <v>-3.69</v>
-      </c>
-      <c r="AE4" s="99" t="n">
-        <v>-5.27</v>
       </c>
     </row>
     <row r="5">
@@ -6871,31 +6871,31 @@
         <v>91.05</v>
       </c>
       <c r="D5" s="99" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="E5" s="99" t="n">
         <v>84.84</v>
       </c>
-      <c r="E5" s="99" t="n">
+      <c r="F5" s="99" t="n">
         <v>80.58</v>
       </c>
-      <c r="F5" s="99" t="n">
+      <c r="G5" s="99" t="n">
         <v>71.91</v>
       </c>
-      <c r="G5" s="99" t="n">
+      <c r="H5" s="99" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="I5" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="I5" s="99" t="n">
+      <c r="J5" s="99" t="n">
         <v>34.66</v>
       </c>
-      <c r="J5" s="99" t="n">
+      <c r="K5" s="99" t="n">
         <v>34.31</v>
       </c>
-      <c r="K5" s="99" t="n">
+      <c r="L5" s="99" t="n">
         <v>25.68</v>
-      </c>
-      <c r="L5" s="99" t="n">
-        <v>18.87</v>
       </c>
       <c r="M5" s="99" t="n">
         <v>18.87</v>
@@ -6904,55 +6904,55 @@
         <v>18.87</v>
       </c>
       <c r="O5" s="99" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="P5" s="99" t="n">
         <v>20.56</v>
       </c>
-      <c r="P5" s="99" t="n">
+      <c r="Q5" s="99" t="n">
         <v>21.18</v>
       </c>
-      <c r="Q5" s="99" t="n">
+      <c r="R5" s="99" t="n">
         <v>24.39</v>
       </c>
-      <c r="R5" s="99" t="n">
+      <c r="S5" s="99" t="n">
         <v>20.64</v>
       </c>
-      <c r="S5" s="99" t="n">
+      <c r="T5" s="99" t="n">
         <v>24.91</v>
       </c>
-      <c r="T5" s="99" t="n">
+      <c r="U5" s="99" t="n">
         <v>29.13</v>
       </c>
-      <c r="U5" s="99" t="n">
+      <c r="V5" s="99" t="n">
         <v>27.12</v>
       </c>
-      <c r="V5" s="99" t="n">
+      <c r="W5" s="99" t="n">
         <v>30.8</v>
       </c>
-      <c r="W5" s="99" t="n">
+      <c r="X5" s="99" t="n">
         <v>32.53</v>
       </c>
-      <c r="X5" s="99" t="n">
+      <c r="Y5" s="99" t="n">
         <v>40.52</v>
       </c>
-      <c r="Y5" s="99" t="n">
+      <c r="Z5" s="99" t="n">
         <v>31.09</v>
       </c>
-      <c r="Z5" s="99" t="n">
+      <c r="AA5" s="99" t="n">
         <v>34.85</v>
       </c>
-      <c r="AA5" s="99" t="n">
+      <c r="AB5" s="99" t="n">
         <v>38.18</v>
       </c>
-      <c r="AB5" s="99" t="n">
+      <c r="AC5" s="99" t="n">
         <v>40.27</v>
       </c>
-      <c r="AC5" s="99" t="n">
+      <c r="AD5" s="99" t="n">
         <v>39.76</v>
       </c>
-      <c r="AD5" s="99" t="n">
+      <c r="AE5" s="99" t="n">
         <v>37.4</v>
-      </c>
-      <c r="AE5" s="99" t="n">
-        <v>39.36</v>
       </c>
     </row>
     <row r="6">
@@ -6968,31 +6968,31 @@
         <v>99.98999999999999</v>
       </c>
       <c r="D6" s="99" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="E6" s="99" t="n">
         <v>99.94</v>
       </c>
-      <c r="E6" s="99" t="n">
+      <c r="F6" s="99" t="n">
         <v>99.88</v>
       </c>
-      <c r="F6" s="99" t="n">
+      <c r="G6" s="99" t="n">
         <v>99.61</v>
       </c>
-      <c r="G6" s="99" t="n">
+      <c r="H6" s="99" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="I6" s="99" t="n">
         <v>92.72</v>
       </c>
-      <c r="I6" s="99" t="n">
+      <c r="J6" s="99" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="J6" s="99" t="n">
+      <c r="K6" s="99" t="n">
         <v>81.17</v>
       </c>
-      <c r="K6" s="99" t="n">
+      <c r="L6" s="99" t="n">
         <v>53.59</v>
-      </c>
-      <c r="L6" s="99" t="n">
-        <v>4.21</v>
       </c>
       <c r="M6" s="99" t="n">
         <v>4.21</v>
@@ -7001,55 +7001,55 @@
         <v>4.21</v>
       </c>
       <c r="O6" s="99" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="P6" s="99" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="P6" s="99" t="n">
+      <c r="Q6" s="99" t="n">
         <v>11.08</v>
       </c>
-      <c r="Q6" s="99" t="n">
+      <c r="R6" s="99" t="n">
         <v>27.27</v>
       </c>
-      <c r="R6" s="99" t="n">
+      <c r="S6" s="99" t="n">
         <v>2.86</v>
       </c>
-      <c r="S6" s="99" t="n">
+      <c r="T6" s="99" t="n">
         <v>7.92</v>
       </c>
-      <c r="T6" s="99" t="n">
+      <c r="U6" s="99" t="n">
         <v>24.73</v>
       </c>
-      <c r="U6" s="99" t="n">
+      <c r="V6" s="99" t="n">
         <v>7.06</v>
       </c>
-      <c r="V6" s="99" t="n">
+      <c r="W6" s="99" t="n">
         <v>15.5</v>
       </c>
-      <c r="W6" s="99" t="n">
+      <c r="X6" s="99" t="n">
         <v>20.88</v>
       </c>
-      <c r="X6" s="99" t="n">
+      <c r="Y6" s="99" t="n">
         <v>63.5</v>
       </c>
-      <c r="Y6" s="99" t="n">
+      <c r="Z6" s="99" t="n">
         <v>2.54</v>
       </c>
-      <c r="Z6" s="99" t="n">
+      <c r="AA6" s="99" t="n">
         <v>6.81</v>
       </c>
-      <c r="AA6" s="99" t="n">
+      <c r="AB6" s="99" t="n">
         <v>20.06</v>
       </c>
-      <c r="AB6" s="99" t="n">
+      <c r="AC6" s="99" t="n">
         <v>48.33</v>
       </c>
-      <c r="AC6" s="99" t="n">
+      <c r="AD6" s="99" t="n">
         <v>41.33</v>
       </c>
-      <c r="AD6" s="99" t="n">
+      <c r="AE6" s="99" t="n">
         <v>12.42</v>
-      </c>
-      <c r="AE6" s="99" t="n">
-        <v>18.92</v>
       </c>
     </row>
     <row r="7">
@@ -7088,99 +7088,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H7" s="98" t="inlineStr">
+      <c r="H7" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I7" s="97" t="inlineStr">
+      <c r="J7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J7" s="97" t="inlineStr">
+      <c r="K7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K7" s="98" t="inlineStr">
+      <c r="L7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L7" s="97" t="inlineStr">
+      <c r="M7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M7" s="97" t="inlineStr">
+      <c r="N7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N7" s="97" t="inlineStr">
+      <c r="O7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="97" t="inlineStr">
+      <c r="P7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P7" s="97" t="inlineStr">
+      <c r="Q7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q7" s="97" t="inlineStr">
+      <c r="R7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R7" s="98" t="inlineStr">
+      <c r="S7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S7" s="98" t="inlineStr">
+      <c r="T7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T7" s="97" t="inlineStr">
+      <c r="U7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U7" s="97" t="inlineStr">
+      <c r="V7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V7" s="97" t="inlineStr">
+      <c r="W7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W7" s="98" t="inlineStr">
+      <c r="X7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X7" s="96" t="inlineStr">
+      <c r="Y7" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y7" s="97" t="inlineStr">
+      <c r="Z7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Z7" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AA7" s="98" t="inlineStr">
@@ -7222,31 +7222,31 @@
         <v>26.36</v>
       </c>
       <c r="D8" s="99" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="E8" s="99" t="n">
         <v>5.45</v>
       </c>
-      <c r="E8" s="99" t="n">
+      <c r="F8" s="99" t="n">
         <v>-0.85</v>
       </c>
-      <c r="F8" s="99" t="n">
+      <c r="G8" s="99" t="n">
         <v>-5.96</v>
       </c>
-      <c r="G8" s="99" t="n">
+      <c r="H8" s="99" t="n">
         <v>-6.32</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="I8" s="99" t="n">
         <v>-10.11</v>
       </c>
-      <c r="I8" s="99" t="n">
+      <c r="J8" s="99" t="n">
         <v>-11.14</v>
       </c>
-      <c r="J8" s="99" t="n">
+      <c r="K8" s="99" t="n">
         <v>-9.23</v>
       </c>
-      <c r="K8" s="99" t="n">
+      <c r="L8" s="99" t="n">
         <v>-12.41</v>
-      </c>
-      <c r="L8" s="99" t="n">
-        <v>-13.62</v>
       </c>
       <c r="M8" s="99" t="n">
         <v>-13.62</v>
@@ -7255,55 +7255,55 @@
         <v>-13.62</v>
       </c>
       <c r="O8" s="99" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="P8" s="99" t="n">
         <v>-12.75</v>
       </c>
-      <c r="P8" s="99" t="n">
+      <c r="Q8" s="99" t="n">
         <v>-11.62</v>
       </c>
-      <c r="Q8" s="99" t="n">
+      <c r="R8" s="99" t="n">
         <v>-12.8</v>
       </c>
-      <c r="R8" s="99" t="n">
+      <c r="S8" s="99" t="n">
         <v>-13.49</v>
       </c>
-      <c r="S8" s="99" t="n">
+      <c r="T8" s="99" t="n">
         <v>-12.19</v>
       </c>
-      <c r="T8" s="99" t="n">
+      <c r="U8" s="99" t="n">
         <v>-11.56</v>
       </c>
-      <c r="U8" s="99" t="n">
+      <c r="V8" s="99" t="n">
         <v>-10.95</v>
       </c>
-      <c r="V8" s="99" t="n">
+      <c r="W8" s="99" t="n">
         <v>-10.7</v>
       </c>
-      <c r="W8" s="99" t="n">
+      <c r="X8" s="99" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="X8" s="99" t="n">
+      <c r="Y8" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="Y8" s="99" t="n">
+      <c r="Z8" s="99" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="Z8" s="99" t="n">
+      <c r="AA8" s="99" t="n">
         <v>-10.94</v>
       </c>
-      <c r="AA8" s="99" t="n">
+      <c r="AB8" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AB8" s="99" t="n">
+      <c r="AC8" s="99" t="n">
         <v>-8.17</v>
       </c>
-      <c r="AC8" s="99" t="n">
+      <c r="AD8" s="99" t="n">
         <v>-7.67</v>
       </c>
-      <c r="AD8" s="99" t="n">
+      <c r="AE8" s="99" t="n">
         <v>-6.65</v>
-      </c>
-      <c r="AE8" s="99" t="n">
-        <v>-5.88</v>
       </c>
     </row>
     <row r="9">
@@ -7319,31 +7319,31 @@
         <v>15.28</v>
       </c>
       <c r="D9" s="99" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="E9" s="99" t="n">
         <v>-3.74</v>
       </c>
-      <c r="E9" s="99" t="n">
+      <c r="F9" s="99" t="n">
         <v>-10.62</v>
       </c>
-      <c r="F9" s="99" t="n">
+      <c r="G9" s="99" t="n">
         <v>-12.51</v>
       </c>
-      <c r="G9" s="99" t="n">
+      <c r="H9" s="99" t="n">
         <v>-12.61</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="I9" s="99" t="n">
         <v>-14.58</v>
       </c>
-      <c r="I9" s="99" t="n">
+      <c r="J9" s="99" t="n">
         <v>-16.03</v>
       </c>
-      <c r="J9" s="99" t="n">
+      <c r="K9" s="99" t="n">
         <v>-16.65</v>
       </c>
-      <c r="K9" s="99" t="n">
+      <c r="L9" s="99" t="n">
         <v>-18.48</v>
-      </c>
-      <c r="L9" s="99" t="n">
-        <v>-18.74</v>
       </c>
       <c r="M9" s="99" t="n">
         <v>-18.74</v>
@@ -7352,55 +7352,55 @@
         <v>-18.74</v>
       </c>
       <c r="O9" s="99" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="P9" s="99" t="n">
         <v>-19.06</v>
       </c>
-      <c r="P9" s="99" t="n">
+      <c r="Q9" s="99" t="n">
         <v>-18.16</v>
       </c>
-      <c r="Q9" s="99" t="n">
+      <c r="R9" s="99" t="n">
         <v>-20.04</v>
       </c>
-      <c r="R9" s="99" t="n">
+      <c r="S9" s="99" t="n">
         <v>-19.01</v>
       </c>
-      <c r="S9" s="99" t="n">
+      <c r="T9" s="99" t="n">
         <v>-17.71</v>
       </c>
-      <c r="T9" s="99" t="n">
+      <c r="U9" s="99" t="n">
         <v>-17.63</v>
       </c>
-      <c r="U9" s="99" t="n">
+      <c r="V9" s="99" t="n">
         <v>-17.79</v>
       </c>
-      <c r="V9" s="99" t="n">
+      <c r="W9" s="99" t="n">
         <v>-17.53</v>
       </c>
-      <c r="W9" s="99" t="n">
+      <c r="X9" s="99" t="n">
         <v>-16.58</v>
       </c>
-      <c r="X9" s="99" t="n">
+      <c r="Y9" s="99" t="n">
         <v>-12.6</v>
       </c>
-      <c r="Y9" s="99" t="n">
+      <c r="Z9" s="99" t="n">
         <v>-16.3</v>
       </c>
-      <c r="Z9" s="99" t="n">
+      <c r="AA9" s="99" t="n">
         <v>-17.92</v>
       </c>
-      <c r="AA9" s="99" t="n">
+      <c r="AB9" s="99" t="n">
         <v>-17.61</v>
       </c>
-      <c r="AB9" s="99" t="n">
+      <c r="AC9" s="99" t="n">
         <v>-16.31</v>
       </c>
-      <c r="AC9" s="99" t="n">
+      <c r="AD9" s="99" t="n">
         <v>-15.1</v>
       </c>
-      <c r="AD9" s="99" t="n">
+      <c r="AE9" s="99" t="n">
         <v>-11.15</v>
-      </c>
-      <c r="AE9" s="99" t="n">
-        <v>-13.21</v>
       </c>
     </row>
     <row r="10">
@@ -7416,31 +7416,31 @@
         <v>90.09999999999999</v>
       </c>
       <c r="D10" s="99" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E10" s="99" t="n">
         <v>78.56</v>
       </c>
-      <c r="E10" s="99" t="n">
+      <c r="F10" s="99" t="n">
         <v>65.87</v>
       </c>
-      <c r="F10" s="99" t="n">
+      <c r="G10" s="99" t="n">
         <v>51.71</v>
       </c>
-      <c r="G10" s="99" t="n">
+      <c r="H10" s="99" t="n">
         <v>51.51</v>
       </c>
-      <c r="H10" s="99" t="n">
+      <c r="I10" s="99" t="n">
         <v>29.32</v>
       </c>
-      <c r="I10" s="99" t="n">
+      <c r="J10" s="99" t="n">
         <v>32.26</v>
       </c>
-      <c r="J10" s="99" t="n">
+      <c r="K10" s="99" t="n">
         <v>34.06</v>
       </c>
-      <c r="K10" s="99" t="n">
+      <c r="L10" s="99" t="n">
         <v>29.44</v>
-      </c>
-      <c r="L10" s="99" t="n">
-        <v>33.41</v>
       </c>
       <c r="M10" s="99" t="n">
         <v>33.41</v>
@@ -7449,55 +7449,55 @@
         <v>33.41</v>
       </c>
       <c r="O10" s="99" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="P10" s="99" t="n">
         <v>35.55</v>
       </c>
-      <c r="P10" s="99" t="n">
+      <c r="Q10" s="99" t="n">
         <v>38.79</v>
       </c>
-      <c r="Q10" s="99" t="n">
+      <c r="R10" s="99" t="n">
         <v>34.56</v>
       </c>
-      <c r="R10" s="99" t="n">
+      <c r="S10" s="99" t="n">
         <v>29.42</v>
       </c>
-      <c r="S10" s="99" t="n">
+      <c r="T10" s="99" t="n">
         <v>32.81</v>
       </c>
-      <c r="T10" s="99" t="n">
+      <c r="U10" s="99" t="n">
         <v>37.49</v>
       </c>
-      <c r="U10" s="99" t="n">
+      <c r="V10" s="99" t="n">
         <v>38.05</v>
       </c>
-      <c r="V10" s="99" t="n">
+      <c r="W10" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="W10" s="99" t="n">
+      <c r="X10" s="99" t="n">
         <v>35.52</v>
       </c>
-      <c r="X10" s="99" t="n">
+      <c r="Y10" s="99" t="n">
         <v>49.6</v>
       </c>
-      <c r="Y10" s="99" t="n">
+      <c r="Z10" s="99" t="n">
         <v>35.78</v>
       </c>
-      <c r="Z10" s="99" t="n">
+      <c r="AA10" s="99" t="n">
         <v>25.18</v>
       </c>
-      <c r="AA10" s="99" t="n">
+      <c r="AB10" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AB10" s="99" t="n">
+      <c r="AC10" s="99" t="n">
         <v>30.93</v>
       </c>
-      <c r="AC10" s="99" t="n">
+      <c r="AD10" s="99" t="n">
         <v>32.82</v>
       </c>
-      <c r="AD10" s="99" t="n">
+      <c r="AE10" s="99" t="n">
         <v>32.56</v>
-      </c>
-      <c r="AE10" s="99" t="n">
-        <v>35.9</v>
       </c>
     </row>
     <row r="11">
@@ -7513,31 +7513,31 @@
         <v>96.84</v>
       </c>
       <c r="D11" s="99" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="E11" s="99" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="E11" s="99" t="n">
+      <c r="F11" s="99" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="F11" s="99" t="n">
+      <c r="G11" s="99" t="n">
         <v>64.94</v>
       </c>
-      <c r="G11" s="99" t="n">
+      <c r="H11" s="99" t="n">
         <v>64.66</v>
       </c>
-      <c r="H11" s="99" t="n">
+      <c r="I11" s="99" t="n">
         <v>23.69</v>
       </c>
-      <c r="I11" s="99" t="n">
+      <c r="J11" s="99" t="n">
         <v>29.81</v>
       </c>
-      <c r="J11" s="99" t="n">
+      <c r="K11" s="99" t="n">
         <v>33.91</v>
       </c>
-      <c r="K11" s="99" t="n">
+      <c r="L11" s="99" t="n">
         <v>22.82</v>
-      </c>
-      <c r="L11" s="99" t="n">
-        <v>30.54</v>
       </c>
       <c r="M11" s="99" t="n">
         <v>30.54</v>
@@ -7546,55 +7546,55 @@
         <v>30.54</v>
       </c>
       <c r="O11" s="99" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="P11" s="99" t="n">
         <v>35.28</v>
       </c>
-      <c r="P11" s="99" t="n">
+      <c r="Q11" s="99" t="n">
         <v>42.99</v>
       </c>
-      <c r="Q11" s="99" t="n">
+      <c r="R11" s="99" t="n">
         <v>33.88</v>
       </c>
-      <c r="R11" s="99" t="n">
+      <c r="S11" s="99" t="n">
         <v>22.22</v>
       </c>
-      <c r="S11" s="99" t="n">
+      <c r="T11" s="99" t="n">
         <v>27.98</v>
       </c>
-      <c r="T11" s="99" t="n">
+      <c r="U11" s="99" t="n">
         <v>37.32</v>
       </c>
-      <c r="U11" s="99" t="n">
+      <c r="V11" s="99" t="n">
         <v>38.49</v>
       </c>
-      <c r="V11" s="99" t="n">
+      <c r="W11" s="99" t="n">
         <v>41.22</v>
       </c>
-      <c r="W11" s="99" t="n">
+      <c r="X11" s="99" t="n">
         <v>34.35</v>
       </c>
-      <c r="X11" s="99" t="n">
+      <c r="Y11" s="99" t="n">
         <v>63.18</v>
       </c>
-      <c r="Y11" s="99" t="n">
+      <c r="Z11" s="99" t="n">
         <v>38.1</v>
       </c>
-      <c r="Z11" s="99" t="n">
+      <c r="AA11" s="99" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AA11" s="99" t="n">
+      <c r="AB11" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="AB11" s="99" t="n">
+      <c r="AC11" s="99" t="n">
         <v>17.04</v>
       </c>
-      <c r="AC11" s="99" t="n">
+      <c r="AD11" s="99" t="n">
         <v>20.21</v>
       </c>
-      <c r="AD11" s="99" t="n">
+      <c r="AE11" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="AE11" s="99" t="n">
-        <v>25.01</v>
       </c>
     </row>
     <row r="12">
@@ -7633,114 +7633,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H12" s="98" t="inlineStr">
+      <c r="H12" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I12" s="98" t="inlineStr">
+      <c r="J12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J12" s="97" t="inlineStr">
+      <c r="K12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K12" s="98" t="inlineStr">
+      <c r="L12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L12" s="98" t="inlineStr">
+      <c r="M12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="98" t="inlineStr">
+      <c r="N12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="98" t="inlineStr">
+      <c r="O12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O12" s="97" t="inlineStr">
+      <c r="P12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P12" s="96" t="inlineStr">
+      <c r="Q12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q12" s="98" t="inlineStr">
+      <c r="R12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R12" s="98" t="inlineStr">
+      <c r="S12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S12" s="98" t="inlineStr">
+      <c r="T12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T12" s="96" t="inlineStr">
+      <c r="U12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U12" s="97" t="inlineStr">
+      <c r="V12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V12" s="97" t="inlineStr">
+      <c r="W12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W12" s="98" t="inlineStr">
+      <c r="X12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X12" s="96" t="inlineStr">
+      <c r="Y12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y12" s="97" t="inlineStr">
+      <c r="Z12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z12" s="97" t="inlineStr">
+      <c r="AA12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA12" s="98" t="inlineStr">
+      <c r="AB12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB12" s="97" t="inlineStr">
+      <c r="AC12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC12" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD12" s="98" t="inlineStr">
@@ -7767,31 +7767,31 @@
         <v>32.05</v>
       </c>
       <c r="D13" s="99" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="E13" s="99" t="n">
         <v>13.58</v>
       </c>
-      <c r="E13" s="99" t="n">
+      <c r="F13" s="99" t="n">
         <v>2.95</v>
       </c>
-      <c r="F13" s="99" t="n">
+      <c r="G13" s="99" t="n">
         <v>-2.45</v>
       </c>
-      <c r="G13" s="99" t="n">
+      <c r="H13" s="99" t="n">
         <v>-4.05</v>
       </c>
-      <c r="H13" s="99" t="n">
+      <c r="I13" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="I13" s="99" t="n">
+      <c r="J13" s="99" t="n">
         <v>-11.21</v>
       </c>
-      <c r="J13" s="99" t="n">
+      <c r="K13" s="99" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="K13" s="99" t="n">
+      <c r="L13" s="99" t="n">
         <v>-11.44</v>
-      </c>
-      <c r="L13" s="99" t="n">
-        <v>-12.57</v>
       </c>
       <c r="M13" s="99" t="n">
         <v>-12.57</v>
@@ -7800,55 +7800,55 @@
         <v>-12.57</v>
       </c>
       <c r="O13" s="99" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="P13" s="99" t="n">
         <v>-11.96</v>
       </c>
-      <c r="P13" s="99" t="n">
+      <c r="Q13" s="99" t="n">
         <v>-12.87</v>
       </c>
-      <c r="Q13" s="99" t="n">
+      <c r="R13" s="99" t="n">
         <v>-14.98</v>
       </c>
-      <c r="R13" s="99" t="n">
+      <c r="S13" s="99" t="n">
         <v>-14.79</v>
       </c>
-      <c r="S13" s="99" t="n">
+      <c r="T13" s="99" t="n">
         <v>-14.14</v>
       </c>
-      <c r="T13" s="99" t="n">
+      <c r="U13" s="99" t="n">
         <v>-11.99</v>
       </c>
-      <c r="U13" s="99" t="n">
+      <c r="V13" s="99" t="n">
         <v>-12.63</v>
       </c>
-      <c r="V13" s="99" t="n">
+      <c r="W13" s="99" t="n">
         <v>-12.92</v>
       </c>
-      <c r="W13" s="99" t="n">
+      <c r="X13" s="99" t="n">
         <v>-13.71</v>
       </c>
-      <c r="X13" s="99" t="n">
+      <c r="Y13" s="99" t="n">
         <v>-13.18</v>
       </c>
-      <c r="Y13" s="99" t="n">
+      <c r="Z13" s="99" t="n">
         <v>-15.93</v>
       </c>
-      <c r="Z13" s="99" t="n">
+      <c r="AA13" s="99" t="n">
         <v>-16.93</v>
       </c>
-      <c r="AA13" s="99" t="n">
+      <c r="AB13" s="99" t="n">
         <v>-15.87</v>
       </c>
-      <c r="AB13" s="99" t="n">
+      <c r="AC13" s="99" t="n">
         <v>-14.39</v>
       </c>
-      <c r="AC13" s="99" t="n">
+      <c r="AD13" s="99" t="n">
         <v>-14.68</v>
       </c>
-      <c r="AD13" s="99" t="n">
+      <c r="AE13" s="99" t="n">
         <v>-14.6</v>
-      </c>
-      <c r="AE13" s="99" t="n">
-        <v>-13.72</v>
       </c>
     </row>
     <row r="14">
@@ -7864,31 +7864,31 @@
         <v>18.19</v>
       </c>
       <c r="D14" s="99" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="E14" s="99" t="n">
         <v>1.34</v>
       </c>
-      <c r="E14" s="99" t="n">
+      <c r="F14" s="99" t="n">
         <v>-8.44</v>
       </c>
-      <c r="F14" s="99" t="n">
+      <c r="G14" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="G14" s="99" t="n">
+      <c r="H14" s="99" t="n">
         <v>-10.6</v>
       </c>
-      <c r="H14" s="99" t="n">
+      <c r="I14" s="99" t="n">
         <v>-14.49</v>
       </c>
-      <c r="I14" s="99" t="n">
+      <c r="J14" s="99" t="n">
         <v>-16.56</v>
       </c>
-      <c r="J14" s="99" t="n">
+      <c r="K14" s="99" t="n">
         <v>-15.65</v>
       </c>
-      <c r="K14" s="99" t="n">
+      <c r="L14" s="99" t="n">
         <v>-17.96</v>
-      </c>
-      <c r="L14" s="99" t="n">
-        <v>-19.08</v>
       </c>
       <c r="M14" s="99" t="n">
         <v>-19.08</v>
@@ -7897,55 +7897,55 @@
         <v>-19.08</v>
       </c>
       <c r="O14" s="99" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="P14" s="99" t="n">
         <v>-18.72</v>
       </c>
-      <c r="P14" s="99" t="n">
+      <c r="Q14" s="99" t="n">
         <v>-18.28</v>
       </c>
-      <c r="Q14" s="99" t="n">
+      <c r="R14" s="99" t="n">
         <v>-20.06</v>
       </c>
-      <c r="R14" s="99" t="n">
+      <c r="S14" s="99" t="n">
         <v>-18.31</v>
       </c>
-      <c r="S14" s="99" t="n">
+      <c r="T14" s="99" t="n">
         <v>-18.32</v>
       </c>
-      <c r="T14" s="99" t="n">
+      <c r="U14" s="99" t="n">
         <v>-17.44</v>
       </c>
-      <c r="U14" s="99" t="n">
+      <c r="V14" s="99" t="n">
         <v>-18.44</v>
       </c>
-      <c r="V14" s="99" t="n">
+      <c r="W14" s="99" t="n">
         <v>-17.67</v>
       </c>
-      <c r="W14" s="99" t="n">
+      <c r="X14" s="99" t="n">
         <v>-14.96</v>
       </c>
-      <c r="X14" s="99" t="n">
+      <c r="Y14" s="99" t="n">
         <v>-11.7</v>
       </c>
-      <c r="Y14" s="99" t="n">
+      <c r="Z14" s="99" t="n">
         <v>-15.89</v>
       </c>
-      <c r="Z14" s="99" t="n">
+      <c r="AA14" s="99" t="n">
         <v>-16.48</v>
       </c>
-      <c r="AA14" s="99" t="n">
+      <c r="AB14" s="99" t="n">
         <v>-16.57</v>
       </c>
-      <c r="AB14" s="99" t="n">
+      <c r="AC14" s="99" t="n">
         <v>-15.28</v>
       </c>
-      <c r="AC14" s="99" t="n">
+      <c r="AD14" s="99" t="n">
         <v>-14.4</v>
       </c>
-      <c r="AD14" s="99" t="n">
+      <c r="AE14" s="99" t="n">
         <v>-11.57</v>
-      </c>
-      <c r="AE14" s="99" t="n">
-        <v>-13.13</v>
       </c>
     </row>
     <row r="15">
@@ -7961,31 +7961,31 @@
         <v>93.78</v>
       </c>
       <c r="D15" s="99" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="E15" s="99" t="n">
         <v>88.70999999999999</v>
       </c>
-      <c r="E15" s="99" t="n">
+      <c r="F15" s="99" t="n">
         <v>80.03</v>
       </c>
-      <c r="F15" s="99" t="n">
+      <c r="G15" s="99" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="G15" s="99" t="n">
+      <c r="H15" s="99" t="n">
         <v>67.36</v>
       </c>
-      <c r="H15" s="99" t="n">
+      <c r="I15" s="99" t="n">
         <v>40.3</v>
       </c>
-      <c r="I15" s="99" t="n">
+      <c r="J15" s="99" t="n">
         <v>42.58</v>
       </c>
-      <c r="J15" s="99" t="n">
+      <c r="K15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="K15" s="99" t="n">
+      <c r="L15" s="99" t="n">
         <v>40.02</v>
-      </c>
-      <c r="L15" s="99" t="n">
-        <v>40.59</v>
       </c>
       <c r="M15" s="99" t="n">
         <v>40.59</v>
@@ -7994,55 +7994,55 @@
         <v>40.59</v>
       </c>
       <c r="O15" s="99" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="P15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="P15" s="99" t="n">
+      <c r="Q15" s="99" t="n">
         <v>48.89</v>
       </c>
-      <c r="Q15" s="99" t="n">
+      <c r="R15" s="99" t="n">
         <v>40.91</v>
       </c>
-      <c r="R15" s="99" t="n">
+      <c r="S15" s="99" t="n">
         <v>40.48</v>
       </c>
-      <c r="S15" s="99" t="n">
+      <c r="T15" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="T15" s="99" t="n">
+      <c r="U15" s="99" t="n">
         <v>48.15</v>
       </c>
-      <c r="U15" s="99" t="n">
+      <c r="V15" s="99" t="n">
         <v>44.33</v>
       </c>
-      <c r="V15" s="99" t="n">
+      <c r="W15" s="99" t="n">
         <v>44.83</v>
       </c>
-      <c r="W15" s="99" t="n">
+      <c r="X15" s="99" t="n">
         <v>37.59</v>
       </c>
-      <c r="X15" s="99" t="n">
+      <c r="Y15" s="99" t="n">
         <v>51.16</v>
       </c>
-      <c r="Y15" s="99" t="n">
+      <c r="Z15" s="99" t="n">
         <v>31.05</v>
       </c>
-      <c r="Z15" s="99" t="n">
+      <c r="AA15" s="99" t="n">
         <v>23.87</v>
       </c>
-      <c r="AA15" s="99" t="n">
+      <c r="AB15" s="99" t="n">
         <v>23.35</v>
       </c>
-      <c r="AB15" s="99" t="n">
+      <c r="AC15" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AC15" s="99" t="n">
+      <c r="AD15" s="99" t="n">
         <v>27.05</v>
       </c>
-      <c r="AD15" s="99" t="n">
+      <c r="AE15" s="99" t="n">
         <v>26.89</v>
-      </c>
-      <c r="AE15" s="99" t="n">
-        <v>29.42</v>
       </c>
     </row>
     <row r="16">
@@ -8058,31 +8058,31 @@
         <v>94.69</v>
       </c>
       <c r="D16" s="99" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="E16" s="99" t="n">
         <v>90.12</v>
       </c>
-      <c r="E16" s="99" t="n">
+      <c r="F16" s="99" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="F16" s="99" t="n">
+      <c r="G16" s="99" t="n">
         <v>73.8</v>
       </c>
-      <c r="G16" s="99" t="n">
+      <c r="H16" s="99" t="n">
         <v>69.36</v>
       </c>
-      <c r="H16" s="99" t="n">
+      <c r="I16" s="99" t="n">
         <v>40.16</v>
       </c>
-      <c r="I16" s="99" t="n">
+      <c r="J16" s="99" t="n">
         <v>42.76</v>
       </c>
-      <c r="J16" s="99" t="n">
+      <c r="K16" s="99" t="n">
         <v>47.16</v>
       </c>
-      <c r="K16" s="99" t="n">
+      <c r="L16" s="99" t="n">
         <v>39.93</v>
-      </c>
-      <c r="L16" s="99" t="n">
-        <v>40.57</v>
       </c>
       <c r="M16" s="99" t="n">
         <v>40.57</v>
@@ -8091,55 +8091,55 @@
         <v>40.57</v>
       </c>
       <c r="O16" s="99" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="P16" s="99" t="n">
         <v>47.22</v>
       </c>
-      <c r="P16" s="99" t="n">
+      <c r="Q16" s="99" t="n">
         <v>50.08</v>
       </c>
-      <c r="Q16" s="99" t="n">
+      <c r="R16" s="99" t="n">
         <v>41.17</v>
       </c>
-      <c r="R16" s="99" t="n">
+      <c r="S16" s="99" t="n">
         <v>40.69</v>
       </c>
-      <c r="S16" s="99" t="n">
+      <c r="T16" s="99" t="n">
         <v>40.24</v>
       </c>
-      <c r="T16" s="99" t="n">
+      <c r="U16" s="99" t="n">
         <v>49.36</v>
       </c>
-      <c r="U16" s="99" t="n">
+      <c r="V16" s="99" t="n">
         <v>45.18</v>
       </c>
-      <c r="V16" s="99" t="n">
+      <c r="W16" s="99" t="n">
         <v>45.74</v>
       </c>
-      <c r="W16" s="99" t="n">
+      <c r="X16" s="99" t="n">
         <v>37.86</v>
       </c>
-      <c r="X16" s="99" t="n">
+      <c r="Y16" s="99" t="n">
         <v>53.33</v>
       </c>
-      <c r="Y16" s="99" t="n">
+      <c r="Z16" s="99" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z16" s="99" t="n">
+      <c r="AA16" s="99" t="n">
         <v>22.26</v>
       </c>
-      <c r="AA16" s="99" t="n">
+      <c r="AB16" s="99" t="n">
         <v>21.65</v>
       </c>
-      <c r="AB16" s="99" t="n">
+      <c r="AC16" s="99" t="n">
         <v>25.27</v>
       </c>
-      <c r="AC16" s="99" t="n">
+      <c r="AD16" s="99" t="n">
         <v>25.69</v>
       </c>
-      <c r="AD16" s="99" t="n">
+      <c r="AE16" s="99" t="n">
         <v>25.5</v>
-      </c>
-      <c r="AE16" s="99" t="n">
-        <v>28.26</v>
       </c>
     </row>
     <row r="17">
@@ -8208,94 +8208,94 @@
           <t>red</t>
         </is>
       </c>
-      <c r="N17" s="97" t="inlineStr">
+      <c r="N17" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="97" t="inlineStr">
+      <c r="P17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="98" t="inlineStr">
+      <c r="Q17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q17" s="98" t="inlineStr">
+      <c r="R17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R17" s="98" t="inlineStr">
+      <c r="S17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S17" s="98" t="inlineStr">
+      <c r="T17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T17" s="98" t="inlineStr">
+      <c r="U17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U17" s="98" t="inlineStr">
+      <c r="V17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V17" s="97" t="inlineStr">
+      <c r="W17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W17" s="97" t="inlineStr">
+      <c r="X17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X17" s="96" t="inlineStr">
+      <c r="Y17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y17" s="97" t="inlineStr">
+      <c r="Z17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z17" s="97" t="inlineStr">
+      <c r="AA17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA17" s="96" t="inlineStr">
+      <c r="AB17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB17" s="96" t="inlineStr">
+      <c r="AC17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC17" s="97" t="inlineStr">
+      <c r="AD17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD17" s="96" t="inlineStr">
+      <c r="AE17" s="96" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE17" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -8306,94 +8306,94 @@
         </is>
       </c>
       <c r="B18" s="99" t="n">
-        <v>17.23</v>
+        <v>26.09</v>
       </c>
       <c r="C18" s="99" t="n">
         <v>17.23</v>
       </c>
       <c r="D18" s="99" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="E18" s="99" t="n">
         <v>14.76</v>
       </c>
-      <c r="E18" s="99" t="n">
+      <c r="F18" s="99" t="n">
         <v>12.13</v>
       </c>
-      <c r="F18" s="99" t="n">
+      <c r="G18" s="99" t="n">
         <v>7.96</v>
       </c>
-      <c r="G18" s="99" t="n">
+      <c r="H18" s="99" t="n">
         <v>7.25</v>
       </c>
-      <c r="H18" s="99" t="n">
+      <c r="I18" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="I18" s="99" t="n">
+      <c r="J18" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="J18" s="99" t="n">
+      <c r="K18" s="99" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="K18" s="99" t="n">
-        <v>-2.04</v>
       </c>
       <c r="L18" s="99" t="n">
         <v>-2.04</v>
       </c>
       <c r="M18" s="99" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="N18" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="N18" s="99" t="n">
+      <c r="O18" s="99" t="n">
         <v>-5.76</v>
       </c>
-      <c r="O18" s="99" t="n">
+      <c r="P18" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="P18" s="99" t="n">
+      <c r="Q18" s="99" t="n">
         <v>-4.61</v>
       </c>
-      <c r="Q18" s="99" t="n">
+      <c r="R18" s="99" t="n">
         <v>-3.94</v>
       </c>
-      <c r="R18" s="99" t="n">
+      <c r="S18" s="99" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="S18" s="99" t="n">
-        <v>-2.75</v>
       </c>
       <c r="T18" s="99" t="n">
         <v>-2.75</v>
       </c>
       <c r="U18" s="99" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="V18" s="99" t="n">
         <v>-3.96</v>
       </c>
-      <c r="V18" s="99" t="n">
+      <c r="W18" s="99" t="n">
         <v>-3.9</v>
       </c>
-      <c r="W18" s="99" t="n">
+      <c r="X18" s="99" t="n">
         <v>-4.25</v>
       </c>
-      <c r="X18" s="99" t="n">
+      <c r="Y18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="Y18" s="99" t="n">
+      <c r="Z18" s="99" t="n">
         <v>-3.57</v>
       </c>
-      <c r="Z18" s="99" t="n">
+      <c r="AA18" s="99" t="n">
         <v>-3.86</v>
       </c>
-      <c r="AA18" s="99" t="n">
+      <c r="AB18" s="99" t="n">
         <v>-1.13</v>
       </c>
-      <c r="AB18" s="99" t="n">
+      <c r="AC18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="AC18" s="99" t="n">
+      <c r="AD18" s="99" t="n">
         <v>-4.68</v>
       </c>
-      <c r="AD18" s="99" t="n">
+      <c r="AE18" s="99" t="n">
         <v>-6.27</v>
-      </c>
-      <c r="AE18" s="99" t="n">
-        <v>-7.63</v>
       </c>
     </row>
     <row r="19">
@@ -8403,94 +8403,94 @@
         </is>
       </c>
       <c r="B19" s="99" t="n">
-        <v>26.37</v>
+        <v>34.13</v>
       </c>
       <c r="C19" s="99" t="n">
         <v>26.37</v>
       </c>
       <c r="D19" s="99" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="E19" s="99" t="n">
         <v>23.36</v>
       </c>
-      <c r="E19" s="99" t="n">
+      <c r="F19" s="99" t="n">
         <v>17.68</v>
       </c>
-      <c r="F19" s="99" t="n">
+      <c r="G19" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="G19" s="99" t="n">
+      <c r="H19" s="99" t="n">
         <v>15.91</v>
       </c>
-      <c r="H19" s="99" t="n">
+      <c r="I19" s="99" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I19" s="99" t="n">
+      <c r="J19" s="99" t="n">
         <v>10.84</v>
       </c>
-      <c r="J19" s="99" t="n">
+      <c r="K19" s="99" t="n">
         <v>9.17</v>
-      </c>
-      <c r="K19" s="99" t="n">
-        <v>4.73</v>
       </c>
       <c r="L19" s="99" t="n">
         <v>4.73</v>
       </c>
       <c r="M19" s="99" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="N19" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="N19" s="99" t="n">
+      <c r="O19" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="O19" s="99" t="n">
+      <c r="P19" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="P19" s="99" t="n">
+      <c r="Q19" s="99" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q19" s="99" t="n">
+      <c r="R19" s="99" t="n">
         <v>1.61</v>
       </c>
-      <c r="R19" s="99" t="n">
+      <c r="S19" s="99" t="n">
         <v>0.67</v>
-      </c>
-      <c r="S19" s="99" t="n">
-        <v>2.05</v>
       </c>
       <c r="T19" s="99" t="n">
         <v>2.05</v>
       </c>
       <c r="U19" s="99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V19" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="V19" s="99" t="n">
+      <c r="W19" s="99" t="n">
         <v>7.94</v>
       </c>
-      <c r="W19" s="99" t="n">
+      <c r="X19" s="99" t="n">
         <v>9.01</v>
       </c>
-      <c r="X19" s="99" t="n">
+      <c r="Y19" s="99" t="n">
         <v>9.44</v>
       </c>
-      <c r="Y19" s="99" t="n">
+      <c r="Z19" s="99" t="n">
         <v>10.05</v>
       </c>
-      <c r="Z19" s="99" t="n">
+      <c r="AA19" s="99" t="n">
         <v>6.61</v>
       </c>
-      <c r="AA19" s="99" t="n">
+      <c r="AB19" s="99" t="n">
         <v>7.75</v>
       </c>
-      <c r="AB19" s="99" t="n">
+      <c r="AC19" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC19" s="99" t="n">
+      <c r="AD19" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="AD19" s="99" t="n">
+      <c r="AE19" s="99" t="n">
         <v>5.06</v>
-      </c>
-      <c r="AE19" s="99" t="n">
-        <v>4.55</v>
       </c>
     </row>
     <row r="20">
@@ -8500,94 +8500,94 @@
         </is>
       </c>
       <c r="B20" s="99" t="n">
-        <v>97.18000000000001</v>
+        <v>98.28</v>
       </c>
       <c r="C20" s="99" t="n">
         <v>97.18000000000001</v>
       </c>
       <c r="D20" s="99" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="E20" s="99" t="n">
         <v>96.45999999999999</v>
       </c>
-      <c r="E20" s="99" t="n">
+      <c r="F20" s="99" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="F20" s="99" t="n">
+      <c r="G20" s="99" t="n">
         <v>91.5</v>
       </c>
-      <c r="G20" s="99" t="n">
+      <c r="H20" s="99" t="n">
         <v>90.64</v>
       </c>
-      <c r="H20" s="99" t="n">
+      <c r="I20" s="99" t="n">
         <v>81.62</v>
       </c>
-      <c r="I20" s="99" t="n">
+      <c r="J20" s="99" t="n">
         <v>82.63</v>
       </c>
-      <c r="J20" s="99" t="n">
+      <c r="K20" s="99" t="n">
         <v>77.72</v>
-      </c>
-      <c r="K20" s="99" t="n">
-        <v>66.26000000000001</v>
       </c>
       <c r="L20" s="99" t="n">
         <v>66.26000000000001</v>
       </c>
       <c r="M20" s="99" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="N20" s="99" t="n">
         <v>52.57</v>
       </c>
-      <c r="N20" s="99" t="n">
+      <c r="O20" s="99" t="n">
         <v>48.7</v>
       </c>
-      <c r="O20" s="99" t="n">
+      <c r="P20" s="99" t="n">
         <v>38.58</v>
       </c>
-      <c r="P20" s="99" t="n">
+      <c r="Q20" s="99" t="n">
         <v>26.15</v>
       </c>
-      <c r="Q20" s="99" t="n">
+      <c r="R20" s="99" t="n">
         <v>31.15</v>
       </c>
-      <c r="R20" s="99" t="n">
+      <c r="S20" s="99" t="n">
         <v>27.74</v>
-      </c>
-      <c r="S20" s="99" t="n">
-        <v>38.27</v>
       </c>
       <c r="T20" s="99" t="n">
         <v>38.27</v>
       </c>
       <c r="U20" s="99" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="V20" s="99" t="n">
         <v>38.92</v>
       </c>
-      <c r="V20" s="99" t="n">
+      <c r="W20" s="99" t="n">
         <v>49.28</v>
       </c>
-      <c r="W20" s="99" t="n">
+      <c r="X20" s="99" t="n">
         <v>51.67</v>
       </c>
-      <c r="X20" s="99" t="n">
+      <c r="Y20" s="99" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="Y20" s="99" t="n">
+      <c r="Z20" s="99" t="n">
         <v>65.08</v>
       </c>
-      <c r="Z20" s="99" t="n">
+      <c r="AA20" s="99" t="n">
         <v>60.24</v>
       </c>
-      <c r="AA20" s="99" t="n">
+      <c r="AB20" s="99" t="n">
         <v>77.66</v>
       </c>
-      <c r="AB20" s="99" t="n">
+      <c r="AC20" s="99" t="n">
         <v>75.16</v>
       </c>
-      <c r="AC20" s="99" t="n">
+      <c r="AD20" s="99" t="n">
         <v>67.81</v>
       </c>
-      <c r="AD20" s="99" t="n">
+      <c r="AE20" s="99" t="n">
         <v>70.5</v>
-      </c>
-      <c r="AE20" s="99" t="n">
-        <v>58.65</v>
       </c>
     </row>
     <row r="21">
@@ -8597,94 +8597,94 @@
         </is>
       </c>
       <c r="B21" s="99" t="n">
-        <v>82.69</v>
+        <v>86.55</v>
       </c>
       <c r="C21" s="99" t="n">
         <v>82.69</v>
       </c>
       <c r="D21" s="99" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="E21" s="99" t="n">
         <v>80.68000000000001</v>
       </c>
-      <c r="E21" s="99" t="n">
+      <c r="F21" s="99" t="n">
         <v>77.11</v>
       </c>
-      <c r="F21" s="99" t="n">
+      <c r="G21" s="99" t="n">
         <v>71.53</v>
       </c>
-      <c r="G21" s="99" t="n">
+      <c r="H21" s="99" t="n">
         <v>70.42</v>
       </c>
-      <c r="H21" s="99" t="n">
+      <c r="I21" s="99" t="n">
         <v>62.3</v>
       </c>
-      <c r="I21" s="99" t="n">
+      <c r="J21" s="99" t="n">
         <v>62.54</v>
       </c>
-      <c r="J21" s="99" t="n">
+      <c r="K21" s="99" t="n">
         <v>59.26</v>
-      </c>
-      <c r="K21" s="99" t="n">
-        <v>53.72</v>
       </c>
       <c r="L21" s="99" t="n">
         <v>53.72</v>
       </c>
       <c r="M21" s="99" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="N21" s="99" t="n">
         <v>49.33</v>
       </c>
-      <c r="N21" s="99" t="n">
+      <c r="O21" s="99" t="n">
         <v>48.3</v>
       </c>
-      <c r="O21" s="99" t="n">
+      <c r="P21" s="99" t="n">
         <v>45.75</v>
       </c>
-      <c r="P21" s="99" t="n">
+      <c r="Q21" s="99" t="n">
         <v>43.02</v>
       </c>
-      <c r="Q21" s="99" t="n">
+      <c r="R21" s="99" t="n">
         <v>45.06</v>
       </c>
-      <c r="R21" s="99" t="n">
+      <c r="S21" s="99" t="n">
         <v>44.32</v>
-      </c>
-      <c r="S21" s="99" t="n">
-        <v>48.45</v>
       </c>
       <c r="T21" s="99" t="n">
         <v>48.45</v>
       </c>
       <c r="U21" s="99" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="V21" s="99" t="n">
         <v>48.67</v>
       </c>
-      <c r="V21" s="99" t="n">
+      <c r="W21" s="99" t="n">
         <v>52.11</v>
       </c>
-      <c r="W21" s="99" t="n">
+      <c r="X21" s="99" t="n">
         <v>52.84</v>
       </c>
-      <c r="X21" s="99" t="n">
+      <c r="Y21" s="99" t="n">
         <v>58.6</v>
       </c>
-      <c r="Y21" s="99" t="n">
+      <c r="Z21" s="99" t="n">
         <v>55.46</v>
       </c>
-      <c r="Z21" s="99" t="n">
+      <c r="AA21" s="99" t="n">
         <v>53.93</v>
       </c>
-      <c r="AA21" s="99" t="n">
+      <c r="AB21" s="99" t="n">
         <v>57.57</v>
       </c>
-      <c r="AB21" s="99" t="n">
+      <c r="AC21" s="99" t="n">
         <v>56.41</v>
       </c>
-      <c r="AC21" s="99" t="n">
+      <c r="AD21" s="99" t="n">
         <v>53.44</v>
       </c>
-      <c r="AD21" s="99" t="n">
+      <c r="AE21" s="99" t="n">
         <v>53.98</v>
-      </c>
-      <c r="AE21" s="99" t="n">
-        <v>49.84</v>
       </c>
     </row>
     <row r="22">
@@ -8718,129 +8718,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G22" s="96" t="inlineStr">
+      <c r="G22" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="96" t="inlineStr">
+      <c r="I22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="96" t="inlineStr">
+      <c r="J22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="96" t="inlineStr">
+      <c r="K22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="97" t="inlineStr">
+      <c r="L22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="96" t="inlineStr">
+      <c r="M22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="96" t="inlineStr">
+      <c r="N22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="96" t="inlineStr">
+      <c r="O22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="96" t="inlineStr">
+      <c r="P22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="96" t="inlineStr">
+      <c r="Q22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="97" t="inlineStr">
+      <c r="R22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="98" t="inlineStr">
+      <c r="S22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S22" s="98" t="inlineStr">
+      <c r="T22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="98" t="inlineStr">
+      <c r="U22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="98" t="inlineStr">
+      <c r="V22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="98" t="inlineStr">
+      <c r="W22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="97" t="inlineStr">
+      <c r="X22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="97" t="inlineStr">
+      <c r="Y22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="97" t="inlineStr">
+      <c r="Z22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="97" t="inlineStr">
+      <c r="AA22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="97" t="inlineStr">
+      <c r="AB22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="97" t="inlineStr">
+      <c r="AC22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="97" t="inlineStr">
+      <c r="AD22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="97" t="inlineStr">
+      <c r="AE22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8851,94 +8851,94 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C23" s="99" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D23" s="99" t="n">
         <v>3.51</v>
       </c>
-      <c r="C23" s="99" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="D23" s="99" t="n">
+      <c r="E23" s="99" t="n">
         <v>3.63</v>
       </c>
-      <c r="E23" s="99" t="n">
+      <c r="F23" s="99" t="n">
         <v>4.29</v>
       </c>
-      <c r="F23" s="99" t="n">
+      <c r="G23" s="99" t="n">
         <v>4.51</v>
       </c>
-      <c r="G23" s="99" t="n">
+      <c r="H23" s="99" t="n">
         <v>4.99</v>
       </c>
-      <c r="H23" s="99" t="n">
+      <c r="I23" s="99" t="n">
         <v>4.3</v>
       </c>
-      <c r="I23" s="99" t="n">
+      <c r="J23" s="99" t="n">
         <v>4.1</v>
       </c>
-      <c r="J23" s="99" t="n">
+      <c r="K23" s="99" t="n">
         <v>4.47</v>
       </c>
-      <c r="K23" s="99" t="n">
+      <c r="L23" s="99" t="n">
         <v>3.13</v>
       </c>
-      <c r="L23" s="99" t="n">
+      <c r="M23" s="99" t="n">
         <v>3.11</v>
       </c>
-      <c r="M23" s="99" t="n">
+      <c r="N23" s="99" t="n">
         <v>2.92</v>
       </c>
-      <c r="N23" s="99" t="n">
+      <c r="O23" s="99" t="n">
         <v>2.53</v>
       </c>
-      <c r="O23" s="99" t="n">
+      <c r="P23" s="99" t="n">
         <v>2.24</v>
       </c>
-      <c r="P23" s="99" t="n">
+      <c r="Q23" s="99" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q23" s="99" t="n">
+      <c r="R23" s="99" t="n">
         <v>1.14</v>
       </c>
-      <c r="R23" s="99" t="n">
+      <c r="S23" s="99" t="n">
         <v>0.92</v>
       </c>
-      <c r="S23" s="99" t="n">
+      <c r="T23" s="99" t="n">
         <v>0.62</v>
       </c>
-      <c r="T23" s="99" t="n">
+      <c r="U23" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="U23" s="99" t="n">
+      <c r="V23" s="99" t="n">
         <v>3.24</v>
       </c>
-      <c r="V23" s="99" t="n">
+      <c r="W23" s="99" t="n">
         <v>3.29</v>
-      </c>
-      <c r="W23" s="99" t="n">
-        <v>5.5</v>
       </c>
       <c r="X23" s="99" t="n">
         <v>5.5</v>
       </c>
       <c r="Y23" s="99" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z23" s="99" t="n">
         <v>5.68</v>
       </c>
-      <c r="Z23" s="99" t="n">
+      <c r="AA23" s="99" t="n">
         <v>5.84</v>
       </c>
-      <c r="AA23" s="99" t="n">
+      <c r="AB23" s="99" t="n">
         <v>6.6</v>
       </c>
-      <c r="AB23" s="99" t="n">
+      <c r="AC23" s="99" t="n">
         <v>7.28</v>
       </c>
-      <c r="AC23" s="99" t="n">
+      <c r="AD23" s="99" t="n">
         <v>6.98</v>
       </c>
-      <c r="AD23" s="99" t="n">
+      <c r="AE23" s="99" t="n">
         <v>4.99</v>
-      </c>
-      <c r="AE23" s="99" t="n">
-        <v>5.96</v>
       </c>
     </row>
     <row r="24">
@@ -8948,288 +8948,288 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="C24" s="99" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="D24" s="99" t="n">
         <v>10.61</v>
       </c>
-      <c r="C24" s="99" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="D24" s="99" t="n">
+      <c r="E24" s="99" t="n">
         <v>10.3</v>
       </c>
-      <c r="E24" s="99" t="n">
+      <c r="F24" s="99" t="n">
         <v>10.4</v>
       </c>
-      <c r="F24" s="99" t="n">
+      <c r="G24" s="99" t="n">
         <v>11.17</v>
       </c>
-      <c r="G24" s="99" t="n">
+      <c r="H24" s="99" t="n">
         <v>10.01</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="I24" s="99" t="n">
         <v>9.85</v>
       </c>
-      <c r="I24" s="99" t="n">
+      <c r="J24" s="99" t="n">
         <v>8.75</v>
       </c>
-      <c r="J24" s="99" t="n">
+      <c r="K24" s="99" t="n">
         <v>8.74</v>
       </c>
-      <c r="K24" s="99" t="n">
+      <c r="L24" s="99" t="n">
         <v>7.05</v>
       </c>
-      <c r="L24" s="99" t="n">
+      <c r="M24" s="99" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="M24" s="99" t="n">
+      <c r="N24" s="99" t="n">
         <v>7.95</v>
       </c>
-      <c r="N24" s="99" t="n">
+      <c r="O24" s="99" t="n">
         <v>7.49</v>
       </c>
-      <c r="O24" s="99" t="n">
+      <c r="P24" s="99" t="n">
         <v>6.76</v>
       </c>
-      <c r="P24" s="99" t="n">
+      <c r="Q24" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="Q24" s="99" t="n">
+      <c r="R24" s="99" t="n">
         <v>6.12</v>
       </c>
-      <c r="R24" s="99" t="n">
+      <c r="S24" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="S24" s="99" t="n">
+      <c r="T24" s="99" t="n">
         <v>5.69</v>
       </c>
-      <c r="T24" s="99" t="n">
+      <c r="U24" s="99" t="n">
         <v>6.85</v>
       </c>
-      <c r="U24" s="99" t="n">
+      <c r="V24" s="99" t="n">
         <v>6.87</v>
       </c>
-      <c r="V24" s="99" t="n">
+      <c r="W24" s="99" t="n">
         <v>6.83</v>
-      </c>
-      <c r="W24" s="99" t="n">
-        <v>10.36</v>
       </c>
       <c r="X24" s="99" t="n">
         <v>10.36</v>
       </c>
       <c r="Y24" s="99" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="Z24" s="99" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="Z24" s="99" t="n">
+      <c r="AA24" s="99" t="n">
         <v>8.43</v>
       </c>
-      <c r="AA24" s="99" t="n">
+      <c r="AB24" s="99" t="n">
         <v>10.21</v>
       </c>
-      <c r="AB24" s="99" t="n">
+      <c r="AC24" s="99" t="n">
         <v>10.6</v>
       </c>
-      <c r="AC24" s="99" t="n">
+      <c r="AD24" s="99" t="n">
         <v>9.82</v>
       </c>
-      <c r="AD24" s="99" t="n">
+      <c r="AE24" s="99" t="n">
         <v>8.44</v>
       </c>
-      <c r="AE24" s="99" t="n">
-        <v>10.29</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="inlineStr">
+      <c r="A25" s="100" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="99" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="C25" s="99" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="D25" s="99" t="n">
         <v>86.19</v>
       </c>
-      <c r="C25" s="99" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="D25" s="99" t="n">
+      <c r="E25" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="E25" s="99" t="n">
+      <c r="F25" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="F25" s="99" t="n">
+      <c r="G25" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="G25" s="99" t="n">
+      <c r="H25" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="I25" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="I25" s="99" t="n">
+      <c r="J25" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="J25" s="99" t="n">
+      <c r="K25" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="K25" s="99" t="n">
+      <c r="L25" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="L25" s="99" t="n">
+      <c r="M25" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="M25" s="99" t="n">
+      <c r="N25" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="N25" s="99" t="n">
+      <c r="O25" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="O25" s="99" t="n">
+      <c r="P25" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="P25" s="99" t="n">
+      <c r="Q25" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="Q25" s="99" t="n">
+      <c r="R25" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="R25" s="99" t="n">
+      <c r="S25" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="S25" s="99" t="n">
+      <c r="T25" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="T25" s="99" t="n">
+      <c r="U25" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="U25" s="99" t="n">
+      <c r="V25" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="V25" s="99" t="n">
+      <c r="W25" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="W25" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="X25" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="Y25" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="Z25" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="Z25" s="99" t="n">
+      <c r="AA25" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="AA25" s="99" t="n">
+      <c r="AB25" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AB25" s="99" t="n">
+      <c r="AC25" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AC25" s="99" t="n">
+      <c r="AD25" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="AD25" s="99" t="n">
+      <c r="AE25" s="99" t="n">
         <v>30.49</v>
       </c>
-      <c r="AE25" s="99" t="n">
-        <v>89.15000000000001</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="99" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="C26" s="99" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="D26" s="99" t="n">
         <v>86.19</v>
       </c>
-      <c r="C26" s="99" t="n">
-        <v>86.19</v>
-      </c>
-      <c r="D26" s="99" t="n">
+      <c r="E26" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="E26" s="99" t="n">
+      <c r="F26" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="F26" s="99" t="n">
+      <c r="G26" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="G26" s="99" t="n">
+      <c r="H26" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="H26" s="99" t="n">
+      <c r="I26" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="I26" s="99" t="n">
+      <c r="J26" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="J26" s="99" t="n">
+      <c r="K26" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="K26" s="99" t="n">
+      <c r="L26" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="L26" s="99" t="n">
+      <c r="M26" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="M26" s="99" t="n">
+      <c r="N26" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="N26" s="99" t="n">
+      <c r="O26" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="O26" s="99" t="n">
+      <c r="P26" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="P26" s="99" t="n">
+      <c r="Q26" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="Q26" s="99" t="n">
+      <c r="R26" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="R26" s="99" t="n">
+      <c r="S26" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="S26" s="99" t="n">
+      <c r="T26" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="T26" s="99" t="n">
+      <c r="U26" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="U26" s="99" t="n">
+      <c r="V26" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="V26" s="99" t="n">
+      <c r="W26" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="W26" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="X26" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="Y26" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="Z26" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="Z26" s="99" t="n">
+      <c r="AA26" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="AA26" s="99" t="n">
+      <c r="AB26" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AB26" s="99" t="n">
+      <c r="AC26" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AC26" s="99" t="n">
+      <c r="AD26" s="99" t="n">
         <v>74.03</v>
       </c>
-      <c r="AD26" s="99" t="n">
+      <c r="AE26" s="99" t="n">
         <v>30.49</v>
-      </c>
-      <c r="AE26" s="99" t="n">
-        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -9263,129 +9263,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G27" s="96" t="inlineStr">
+      <c r="G27" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H27" s="96" t="inlineStr">
+      <c r="I27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I27" s="96" t="inlineStr">
+      <c r="J27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J27" s="96" t="inlineStr">
+      <c r="K27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K27" s="96" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L27" s="96" t="inlineStr">
+      <c r="M27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M27" s="96" t="inlineStr">
+      <c r="N27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N27" s="96" t="inlineStr">
+      <c r="O27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O27" s="96" t="inlineStr">
+      <c r="P27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P27" s="96" t="inlineStr">
+      <c r="Q27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q27" s="98" t="inlineStr">
+      <c r="R27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R27" s="97" t="inlineStr">
+      <c r="S27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S27" s="98" t="inlineStr">
+      <c r="T27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T27" s="98" t="inlineStr">
+      <c r="U27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U27" s="97" t="inlineStr">
+      <c r="V27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V27" s="97" t="inlineStr">
+      <c r="W27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W27" s="96" t="inlineStr">
+      <c r="X27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X27" s="96" t="inlineStr">
+      <c r="Y27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y27" s="97" t="inlineStr">
+      <c r="Z27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z27" s="97" t="inlineStr">
+      <c r="AA27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA27" s="97" t="inlineStr">
+      <c r="AB27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB27" s="96" t="inlineStr">
+      <c r="AC27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC27" s="96" t="inlineStr">
+      <c r="AD27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD27" s="97" t="inlineStr">
+      <c r="AE27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE27" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -9396,94 +9396,94 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="C28" s="99" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D28" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="C28" s="99" t="n">
+      <c r="E28" s="99" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="F28" s="99" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G28" s="99" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="H28" s="99" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I28" s="99" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J28" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="D28" s="99" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="E28" s="99" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="F28" s="99" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="G28" s="99" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H28" s="99" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="I28" s="99" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J28" s="99" t="n">
+      <c r="K28" s="99" t="n">
         <v>7.45</v>
       </c>
-      <c r="K28" s="99" t="n">
+      <c r="L28" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="L28" s="99" t="n">
+      <c r="M28" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="M28" s="99" t="n">
+      <c r="N28" s="99" t="n">
         <v>6.36</v>
       </c>
-      <c r="N28" s="99" t="n">
+      <c r="O28" s="99" t="n">
         <v>6.59</v>
       </c>
-      <c r="O28" s="99" t="n">
+      <c r="P28" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="P28" s="99" t="n">
+      <c r="Q28" s="99" t="n">
         <v>5.89</v>
       </c>
-      <c r="Q28" s="99" t="n">
+      <c r="R28" s="99" t="n">
         <v>5.41</v>
       </c>
-      <c r="R28" s="99" t="n">
+      <c r="S28" s="99" t="n">
         <v>5.47</v>
       </c>
-      <c r="S28" s="99" t="n">
+      <c r="T28" s="99" t="n">
         <v>4.12</v>
       </c>
-      <c r="T28" s="99" t="n">
+      <c r="U28" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="U28" s="99" t="n">
+      <c r="V28" s="99" t="n">
         <v>5.61</v>
       </c>
-      <c r="V28" s="99" t="n">
+      <c r="W28" s="99" t="n">
         <v>5.27</v>
-      </c>
-      <c r="W28" s="99" t="n">
-        <v>7.1</v>
       </c>
       <c r="X28" s="99" t="n">
         <v>7.1</v>
       </c>
       <c r="Y28" s="99" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Z28" s="99" t="n">
         <v>6.78</v>
       </c>
-      <c r="Z28" s="99" t="n">
+      <c r="AA28" s="99" t="n">
         <v>6.53</v>
       </c>
-      <c r="AA28" s="99" t="n">
+      <c r="AB28" s="99" t="n">
         <v>6.63</v>
       </c>
-      <c r="AB28" s="99" t="n">
+      <c r="AC28" s="99" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="AC28" s="99" t="n">
+      <c r="AD28" s="99" t="n">
         <v>7.11</v>
       </c>
-      <c r="AD28" s="99" t="n">
+      <c r="AE28" s="99" t="n">
         <v>4.79</v>
-      </c>
-      <c r="AE28" s="99" t="n">
-        <v>4.66</v>
       </c>
     </row>
     <row r="29">
@@ -9493,94 +9493,94 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="C29" s="99" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D29" s="99" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="C29" s="99" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="D29" s="99" t="n">
+      <c r="E29" s="99" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="E29" s="99" t="n">
+      <c r="F29" s="99" t="n">
         <v>8.41</v>
       </c>
-      <c r="F29" s="99" t="n">
+      <c r="G29" s="99" t="n">
         <v>8.6</v>
       </c>
-      <c r="G29" s="99" t="n">
+      <c r="H29" s="99" t="n">
         <v>7.87</v>
       </c>
-      <c r="H29" s="99" t="n">
+      <c r="I29" s="99" t="n">
         <v>7.54</v>
       </c>
-      <c r="I29" s="99" t="n">
+      <c r="J29" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="J29" s="99" t="n">
+      <c r="K29" s="99" t="n">
         <v>5.57</v>
       </c>
-      <c r="K29" s="99" t="n">
+      <c r="L29" s="99" t="n">
         <v>4.38</v>
       </c>
-      <c r="L29" s="99" t="n">
+      <c r="M29" s="99" t="n">
         <v>5.92</v>
       </c>
-      <c r="M29" s="99" t="n">
+      <c r="N29" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="N29" s="99" t="n">
+      <c r="O29" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="O29" s="99" t="n">
+      <c r="P29" s="99" t="n">
         <v>3.31</v>
       </c>
-      <c r="P29" s="99" t="n">
+      <c r="Q29" s="99" t="n">
         <v>3.42</v>
       </c>
-      <c r="Q29" s="99" t="n">
+      <c r="R29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="R29" s="99" t="n">
+      <c r="S29" s="99" t="n">
         <v>5.26</v>
       </c>
-      <c r="S29" s="99" t="n">
+      <c r="T29" s="99" t="n">
         <v>4.21</v>
       </c>
-      <c r="T29" s="99" t="n">
+      <c r="U29" s="99" t="n">
         <v>4.76</v>
-      </c>
-      <c r="U29" s="99" t="n">
-        <v>4.95</v>
       </c>
       <c r="V29" s="99" t="n">
         <v>4.95</v>
       </c>
       <c r="W29" s="99" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="X29" s="99" t="n">
         <v>7.21</v>
       </c>
       <c r="Y29" s="99" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="Z29" s="99" t="n">
         <v>6.75</v>
       </c>
-      <c r="Z29" s="99" t="n">
+      <c r="AA29" s="99" t="n">
         <v>5.93</v>
       </c>
-      <c r="AA29" s="99" t="n">
+      <c r="AB29" s="99" t="n">
         <v>6.7</v>
       </c>
-      <c r="AB29" s="99" t="n">
+      <c r="AC29" s="99" t="n">
         <v>6.88</v>
       </c>
-      <c r="AC29" s="99" t="n">
+      <c r="AD29" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="AD29" s="99" t="n">
+      <c r="AE29" s="99" t="n">
         <v>4.16</v>
-      </c>
-      <c r="AE29" s="99" t="n">
-        <v>4.86</v>
       </c>
     </row>
     <row r="30">
@@ -9590,94 +9590,94 @@
         </is>
       </c>
       <c r="B30" s="99" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="C30" s="99" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D30" s="99" t="n">
         <v>76.02</v>
       </c>
-      <c r="C30" s="99" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="D30" s="99" t="n">
+      <c r="E30" s="99" t="n">
         <v>74.91</v>
       </c>
-      <c r="E30" s="99" t="n">
+      <c r="F30" s="99" t="n">
         <v>66.62</v>
       </c>
-      <c r="F30" s="99" t="n">
+      <c r="G30" s="99" t="n">
         <v>42.84</v>
       </c>
-      <c r="G30" s="99" t="n">
+      <c r="H30" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="H30" s="99" t="n">
+      <c r="I30" s="99" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="I30" s="99" t="n">
+      <c r="J30" s="99" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="J30" s="99" t="n">
+      <c r="K30" s="99" t="n">
         <v>87.58</v>
       </c>
-      <c r="K30" s="99" t="n">
+      <c r="L30" s="99" t="n">
         <v>65.31</v>
       </c>
-      <c r="L30" s="99" t="n">
+      <c r="M30" s="99" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="M30" s="99" t="n">
+      <c r="N30" s="99" t="n">
         <v>88.3</v>
       </c>
-      <c r="N30" s="99" t="n">
+      <c r="O30" s="99" t="n">
         <v>82.94</v>
       </c>
-      <c r="O30" s="99" t="n">
+      <c r="P30" s="99" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="P30" s="99" t="n">
+      <c r="Q30" s="99" t="n">
         <v>56.57</v>
       </c>
-      <c r="Q30" s="99" t="n">
+      <c r="R30" s="99" t="n">
         <v>46.45</v>
       </c>
-      <c r="R30" s="99" t="n">
+      <c r="S30" s="99" t="n">
         <v>52.5</v>
       </c>
-      <c r="S30" s="99" t="n">
+      <c r="T30" s="99" t="n">
         <v>13.02</v>
       </c>
-      <c r="T30" s="99" t="n">
+      <c r="U30" s="99" t="n">
         <v>24.55</v>
       </c>
-      <c r="U30" s="99" t="n">
+      <c r="V30" s="99" t="n">
         <v>35.87</v>
       </c>
-      <c r="V30" s="99" t="n">
+      <c r="W30" s="99" t="n">
         <v>32.25</v>
-      </c>
-      <c r="W30" s="99" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="X30" s="99" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="Y30" s="99" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="Z30" s="99" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="Z30" s="99" t="n">
+      <c r="AA30" s="99" t="n">
         <v>52.49</v>
       </c>
-      <c r="AA30" s="99" t="n">
+      <c r="AB30" s="99" t="n">
         <v>83.64</v>
       </c>
-      <c r="AB30" s="99" t="n">
+      <c r="AC30" s="99" t="n">
         <v>83.23</v>
       </c>
-      <c r="AC30" s="99" t="n">
+      <c r="AD30" s="99" t="n">
         <v>81.13</v>
       </c>
-      <c r="AD30" s="99" t="n">
+      <c r="AE30" s="99" t="n">
         <v>54.01</v>
-      </c>
-      <c r="AE30" s="99" t="n">
-        <v>85.48</v>
       </c>
     </row>
     <row r="31">
@@ -9687,94 +9687,94 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="C31" s="99" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="D31" s="99" t="n">
         <v>73.8</v>
       </c>
-      <c r="C31" s="99" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="D31" s="99" t="n">
+      <c r="E31" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="E31" s="99" t="n">
+      <c r="F31" s="99" t="n">
         <v>68.59</v>
       </c>
-      <c r="F31" s="99" t="n">
+      <c r="G31" s="99" t="n">
         <v>57.58</v>
       </c>
-      <c r="G31" s="99" t="n">
+      <c r="H31" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="H31" s="99" t="n">
+      <c r="I31" s="99" t="n">
         <v>82.34</v>
       </c>
-      <c r="I31" s="99" t="n">
+      <c r="J31" s="99" t="n">
         <v>81.04000000000001</v>
       </c>
-      <c r="J31" s="99" t="n">
+      <c r="K31" s="99" t="n">
         <v>80.31</v>
       </c>
-      <c r="K31" s="99" t="n">
+      <c r="L31" s="99" t="n">
         <v>66.03</v>
       </c>
-      <c r="L31" s="99" t="n">
+      <c r="M31" s="99" t="n">
         <v>74.56999999999999</v>
       </c>
-      <c r="M31" s="99" t="n">
+      <c r="N31" s="99" t="n">
         <v>75.78</v>
       </c>
-      <c r="N31" s="99" t="n">
+      <c r="O31" s="99" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="O31" s="99" t="n">
+      <c r="P31" s="99" t="n">
         <v>60.93</v>
       </c>
-      <c r="P31" s="99" t="n">
+      <c r="Q31" s="99" t="n">
         <v>51.28</v>
       </c>
-      <c r="Q31" s="99" t="n">
+      <c r="R31" s="99" t="n">
         <v>45.58</v>
       </c>
-      <c r="R31" s="99" t="n">
+      <c r="S31" s="99" t="n">
         <v>48.99</v>
       </c>
-      <c r="S31" s="99" t="n">
+      <c r="T31" s="99" t="n">
         <v>25.8</v>
       </c>
-      <c r="T31" s="99" t="n">
+      <c r="U31" s="99" t="n">
         <v>37.29</v>
       </c>
-      <c r="U31" s="99" t="n">
+      <c r="V31" s="99" t="n">
         <v>46.06</v>
       </c>
-      <c r="V31" s="99" t="n">
+      <c r="W31" s="99" t="n">
         <v>44.24</v>
-      </c>
-      <c r="W31" s="99" t="n">
-        <v>79.63</v>
       </c>
       <c r="X31" s="99" t="n">
         <v>79.63</v>
       </c>
       <c r="Y31" s="99" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="Z31" s="99" t="n">
         <v>73.44</v>
       </c>
-      <c r="Z31" s="99" t="n">
+      <c r="AA31" s="99" t="n">
         <v>64.13</v>
       </c>
-      <c r="AA31" s="99" t="n">
+      <c r="AB31" s="99" t="n">
         <v>78.52</v>
       </c>
-      <c r="AB31" s="99" t="n">
+      <c r="AC31" s="99" t="n">
         <v>78.27</v>
       </c>
-      <c r="AC31" s="99" t="n">
+      <c r="AD31" s="99" t="n">
         <v>76.89</v>
       </c>
-      <c r="AD31" s="99" t="n">
+      <c r="AE31" s="99" t="n">
         <v>63.94</v>
-      </c>
-      <c r="AE31" s="99" t="n">
-        <v>77.25</v>
       </c>
     </row>
     <row r="32">
@@ -9798,139 +9798,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E32" s="96" t="inlineStr">
+      <c r="E32" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F32" s="97" t="inlineStr">
+      <c r="G32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G32" s="96" t="inlineStr">
+      <c r="H32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H32" s="96" t="inlineStr">
+      <c r="I32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I32" s="96" t="inlineStr">
+      <c r="J32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J32" s="96" t="inlineStr">
+      <c r="K32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K32" s="97" t="inlineStr">
+      <c r="L32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L32" s="96" t="inlineStr">
+      <c r="M32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M32" s="96" t="inlineStr">
+      <c r="N32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N32" s="96" t="inlineStr">
+      <c r="O32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O32" s="96" t="inlineStr">
+      <c r="P32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P32" s="96" t="inlineStr">
+      <c r="Q32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q32" s="97" t="inlineStr">
+      <c r="R32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R32" s="98" t="inlineStr">
+      <c r="S32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S32" s="98" t="inlineStr">
+      <c r="T32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T32" s="98" t="inlineStr">
+      <c r="U32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U32" s="98" t="inlineStr">
+      <c r="V32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V32" s="98" t="inlineStr">
+      <c r="W32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W32" s="97" t="inlineStr">
+      <c r="X32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X32" s="97" t="inlineStr">
+      <c r="Y32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y32" s="98" t="inlineStr">
+      <c r="Z32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z32" s="98" t="inlineStr">
+      <c r="AA32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA32" s="97" t="inlineStr">
+      <c r="AB32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB32" s="97" t="inlineStr">
+      <c r="AC32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC32" s="97" t="inlineStr">
+      <c r="AD32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD32" s="97" t="inlineStr">
+      <c r="AE32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE32" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -9944,91 +9944,91 @@
         <v>-2.68</v>
       </c>
       <c r="C33" s="99" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="D33" s="99" t="n">
         <v>-0.89</v>
       </c>
-      <c r="D33" s="99" t="n">
+      <c r="E33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="E33" s="99" t="n">
+      <c r="F33" s="99" t="n">
         <v>0.9</v>
       </c>
-      <c r="F33" s="99" t="n">
+      <c r="G33" s="99" t="n">
         <v>1.13</v>
       </c>
-      <c r="G33" s="99" t="n">
+      <c r="H33" s="99" t="n">
         <v>1.93</v>
       </c>
-      <c r="H33" s="99" t="n">
+      <c r="I33" s="99" t="n">
         <v>0.65</v>
       </c>
-      <c r="I33" s="99" t="n">
+      <c r="J33" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="J33" s="99" t="n">
+      <c r="K33" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="K33" s="99" t="n">
+      <c r="L33" s="99" t="n">
         <v>0.44</v>
       </c>
-      <c r="L33" s="99" t="n">
+      <c r="M33" s="99" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M33" s="99" t="n">
+      <c r="N33" s="99" t="n">
         <v>-0.73</v>
       </c>
-      <c r="N33" s="99" t="n">
+      <c r="O33" s="99" t="n">
         <v>-1</v>
       </c>
-      <c r="O33" s="99" t="n">
+      <c r="P33" s="99" t="n">
         <v>-1.61</v>
       </c>
-      <c r="P33" s="99" t="n">
+      <c r="Q33" s="99" t="n">
         <v>-1.66</v>
       </c>
-      <c r="Q33" s="99" t="n">
+      <c r="R33" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="R33" s="99" t="n">
+      <c r="S33" s="99" t="n">
         <v>-4.11</v>
       </c>
-      <c r="S33" s="99" t="n">
+      <c r="T33" s="99" t="n">
         <v>-3.76</v>
       </c>
-      <c r="T33" s="99" t="n">
+      <c r="U33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="U33" s="99" t="n">
+      <c r="V33" s="99" t="n">
         <v>-0.28</v>
       </c>
-      <c r="V33" s="99" t="n">
+      <c r="W33" s="99" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="W33" s="99" t="n">
-        <v>3.06</v>
       </c>
       <c r="X33" s="99" t="n">
         <v>3.06</v>
       </c>
       <c r="Y33" s="99" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Z33" s="99" t="n">
         <v>3.91</v>
       </c>
-      <c r="Z33" s="99" t="n">
+      <c r="AA33" s="99" t="n">
         <v>4.32</v>
       </c>
-      <c r="AA33" s="99" t="n">
+      <c r="AB33" s="99" t="n">
         <v>6.09</v>
       </c>
-      <c r="AB33" s="99" t="n">
+      <c r="AC33" s="99" t="n">
         <v>5.91</v>
       </c>
-      <c r="AC33" s="99" t="n">
+      <c r="AD33" s="99" t="n">
         <v>5.66</v>
       </c>
-      <c r="AD33" s="99" t="n">
+      <c r="AE33" s="99" t="n">
         <v>3.52</v>
-      </c>
-      <c r="AE33" s="99" t="n">
-        <v>5.9</v>
       </c>
     </row>
     <row r="34">
@@ -10041,91 +10041,91 @@
         <v>10.76</v>
       </c>
       <c r="C34" s="99" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="D34" s="99" t="n">
         <v>11.54</v>
       </c>
-      <c r="D34" s="99" t="n">
+      <c r="E34" s="99" t="n">
         <v>11.48</v>
       </c>
-      <c r="E34" s="99" t="n">
+      <c r="F34" s="99" t="n">
         <v>11.95</v>
       </c>
-      <c r="F34" s="99" t="n">
+      <c r="G34" s="99" t="n">
         <v>12.67</v>
       </c>
-      <c r="G34" s="99" t="n">
+      <c r="H34" s="99" t="n">
         <v>11.04</v>
       </c>
-      <c r="H34" s="99" t="n">
+      <c r="I34" s="99" t="n">
         <v>10.68</v>
       </c>
-      <c r="I34" s="99" t="n">
+      <c r="J34" s="99" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J34" s="99" t="n">
+      <c r="K34" s="99" t="n">
         <v>9.98</v>
       </c>
-      <c r="K34" s="99" t="n">
+      <c r="L34" s="99" t="n">
         <v>7.16</v>
       </c>
-      <c r="L34" s="99" t="n">
+      <c r="M34" s="99" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="M34" s="99" t="n">
+      <c r="N34" s="99" t="n">
         <v>7.37</v>
       </c>
-      <c r="N34" s="99" t="n">
+      <c r="O34" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="O34" s="99" t="n">
+      <c r="P34" s="99" t="n">
         <v>7.12</v>
       </c>
-      <c r="P34" s="99" t="n">
+      <c r="Q34" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="Q34" s="99" t="n">
+      <c r="R34" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="R34" s="99" t="n">
+      <c r="S34" s="99" t="n">
         <v>4.85</v>
       </c>
-      <c r="S34" s="99" t="n">
+      <c r="T34" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="T34" s="99" t="n">
+      <c r="U34" s="99" t="n">
         <v>6.19</v>
       </c>
-      <c r="U34" s="99" t="n">
+      <c r="V34" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="V34" s="99" t="n">
+      <c r="W34" s="99" t="n">
         <v>5.35</v>
-      </c>
-      <c r="W34" s="99" t="n">
-        <v>10.58</v>
       </c>
       <c r="X34" s="99" t="n">
         <v>10.58</v>
       </c>
       <c r="Y34" s="99" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="Z34" s="99" t="n">
         <v>8.9</v>
       </c>
-      <c r="Z34" s="99" t="n">
+      <c r="AA34" s="99" t="n">
         <v>7.88</v>
       </c>
-      <c r="AA34" s="99" t="n">
+      <c r="AB34" s="99" t="n">
         <v>10.75</v>
       </c>
-      <c r="AB34" s="99" t="n">
+      <c r="AC34" s="99" t="n">
         <v>11.21</v>
       </c>
-      <c r="AC34" s="99" t="n">
+      <c r="AD34" s="99" t="n">
         <v>10.31</v>
       </c>
-      <c r="AD34" s="99" t="n">
+      <c r="AE34" s="99" t="n">
         <v>8.26</v>
-      </c>
-      <c r="AE34" s="99" t="n">
-        <v>11.35</v>
       </c>
     </row>
     <row r="35">
@@ -10138,91 +10138,91 @@
         <v>15.42</v>
       </c>
       <c r="C35" s="99" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="D35" s="99" t="n">
         <v>74.7</v>
       </c>
-      <c r="D35" s="99" t="n">
+      <c r="E35" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="E35" s="99" t="n">
+      <c r="F35" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="F35" s="99" t="n">
+      <c r="G35" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="G35" s="99" t="n">
+      <c r="H35" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="H35" s="99" t="n">
+      <c r="I35" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="I35" s="99" t="n">
+      <c r="J35" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="J35" s="99" t="n">
+      <c r="K35" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="K35" s="99" t="n">
+      <c r="L35" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="L35" s="99" t="n">
+      <c r="M35" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="M35" s="99" t="n">
+      <c r="N35" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="N35" s="99" t="n">
+      <c r="O35" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="O35" s="99" t="n">
+      <c r="P35" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="P35" s="99" t="n">
+      <c r="Q35" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="Q35" s="99" t="n">
+      <c r="R35" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="R35" s="99" t="n">
+      <c r="S35" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="S35" s="99" t="n">
+      <c r="T35" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="T35" s="99" t="n">
+      <c r="U35" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="U35" s="99" t="n">
+      <c r="V35" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="V35" s="99" t="n">
+      <c r="W35" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="W35" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="X35" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="Y35" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="Z35" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="Z35" s="99" t="n">
+      <c r="AA35" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="AA35" s="99" t="n">
+      <c r="AB35" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AB35" s="99" t="n">
+      <c r="AC35" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AC35" s="99" t="n">
+      <c r="AD35" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="AD35" s="99" t="n">
+      <c r="AE35" s="99" t="n">
         <v>24.22</v>
-      </c>
-      <c r="AE35" s="99" t="n">
-        <v>86.91</v>
       </c>
     </row>
     <row r="36">
@@ -10235,91 +10235,91 @@
         <v>15.42</v>
       </c>
       <c r="C36" s="99" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="D36" s="99" t="n">
         <v>74.7</v>
       </c>
-      <c r="D36" s="99" t="n">
+      <c r="E36" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="E36" s="99" t="n">
+      <c r="F36" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="F36" s="99" t="n">
+      <c r="G36" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="G36" s="99" t="n">
+      <c r="H36" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="H36" s="99" t="n">
+      <c r="I36" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="I36" s="99" t="n">
+      <c r="J36" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="J36" s="99" t="n">
+      <c r="K36" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="K36" s="99" t="n">
+      <c r="L36" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="L36" s="99" t="n">
+      <c r="M36" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="M36" s="99" t="n">
+      <c r="N36" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="N36" s="99" t="n">
+      <c r="O36" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="O36" s="99" t="n">
+      <c r="P36" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="P36" s="99" t="n">
+      <c r="Q36" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="Q36" s="99" t="n">
+      <c r="R36" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="R36" s="99" t="n">
+      <c r="S36" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="S36" s="99" t="n">
+      <c r="T36" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="T36" s="99" t="n">
+      <c r="U36" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="U36" s="99" t="n">
+      <c r="V36" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="V36" s="99" t="n">
+      <c r="W36" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="W36" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="X36" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="Y36" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="Z36" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="Z36" s="99" t="n">
+      <c r="AA36" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="AA36" s="99" t="n">
+      <c r="AB36" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AB36" s="99" t="n">
+      <c r="AC36" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AC36" s="99" t="n">
+      <c r="AD36" s="99" t="n">
         <v>66.23</v>
       </c>
-      <c r="AD36" s="99" t="n">
+      <c r="AE36" s="99" t="n">
         <v>24.22</v>
-      </c>
-      <c r="AE36" s="99" t="n">
-        <v>86.91</v>
       </c>
     </row>
     <row r="37">
@@ -10328,144 +10328,144 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B37" s="97" t="inlineStr">
+      <c r="B37" s="98" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C37" s="97" t="inlineStr">
+      <c r="D37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D37" s="96" t="inlineStr">
+      <c r="E37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E37" s="96" t="inlineStr">
+      <c r="F37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F37" s="96" t="inlineStr">
+      <c r="G37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G37" s="96" t="inlineStr">
+      <c r="H37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H37" s="96" t="inlineStr">
+      <c r="I37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I37" s="96" t="inlineStr">
+      <c r="J37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J37" s="96" t="inlineStr">
+      <c r="K37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K37" s="97" t="inlineStr">
+      <c r="L37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L37" s="97" t="inlineStr">
+      <c r="M37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M37" s="97" t="inlineStr">
+      <c r="N37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N37" s="97" t="inlineStr">
+      <c r="O37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="97" t="inlineStr">
+      <c r="P37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P37" s="98" t="inlineStr">
+      <c r="Q37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q37" s="98" t="inlineStr">
+      <c r="R37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R37" s="98" t="inlineStr">
+      <c r="S37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S37" s="98" t="inlineStr">
+      <c r="T37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T37" s="98" t="inlineStr">
+      <c r="U37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U37" s="98" t="inlineStr">
+      <c r="V37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V37" s="97" t="inlineStr">
+      <c r="W37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W37" s="97" t="inlineStr">
+      <c r="X37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X37" s="97" t="inlineStr">
+      <c r="Y37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y37" s="97" t="inlineStr">
+      <c r="Z37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z37" s="97" t="inlineStr">
+      <c r="AA37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA37" s="97" t="inlineStr">
+      <c r="AB37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB37" s="97" t="inlineStr">
+      <c r="AC37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AD37" s="96" t="inlineStr">
@@ -10486,94 +10486,94 @@
         </is>
       </c>
       <c r="B38" s="99" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="C38" s="99" t="n">
         <v>-5.52</v>
       </c>
-      <c r="C38" s="99" t="n">
+      <c r="D38" s="99" t="n">
         <v>-7.32</v>
       </c>
-      <c r="D38" s="99" t="n">
+      <c r="E38" s="99" t="n">
         <v>-1.85</v>
       </c>
-      <c r="E38" s="99" t="n">
+      <c r="F38" s="99" t="n">
         <v>-2.87</v>
       </c>
-      <c r="F38" s="99" t="n">
+      <c r="G38" s="99" t="n">
         <v>-4.44</v>
       </c>
-      <c r="G38" s="99" t="n">
+      <c r="H38" s="99" t="n">
         <v>-4.15</v>
-      </c>
-      <c r="H38" s="99" t="n">
-        <v>-4.11</v>
       </c>
       <c r="I38" s="99" t="n">
         <v>-4.11</v>
       </c>
       <c r="J38" s="99" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="K38" s="99" t="n">
         <v>-6.33</v>
       </c>
-      <c r="K38" s="99" t="n">
+      <c r="L38" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="L38" s="99" t="n">
+      <c r="M38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="M38" s="99" t="n">
+      <c r="N38" s="99" t="n">
         <v>-5.28</v>
       </c>
-      <c r="N38" s="99" t="n">
+      <c r="O38" s="99" t="n">
         <v>-5.31</v>
       </c>
-      <c r="O38" s="99" t="n">
+      <c r="P38" s="99" t="n">
         <v>-4.5</v>
       </c>
-      <c r="P38" s="99" t="n">
+      <c r="Q38" s="99" t="n">
         <v>-7.44</v>
       </c>
-      <c r="Q38" s="99" t="n">
+      <c r="R38" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="R38" s="99" t="n">
+      <c r="S38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="S38" s="99" t="n">
+      <c r="T38" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="T38" s="99" t="n">
+      <c r="U38" s="99" t="n">
         <v>-5.71</v>
       </c>
-      <c r="U38" s="99" t="n">
+      <c r="V38" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="V38" s="99" t="n">
+      <c r="W38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="W38" s="99" t="n">
+      <c r="X38" s="99" t="n">
         <v>0.04</v>
       </c>
-      <c r="X38" s="99" t="n">
+      <c r="Y38" s="99" t="n">
         <v>-0.14</v>
       </c>
-      <c r="Y38" s="99" t="n">
+      <c r="Z38" s="99" t="n">
         <v>-0.33</v>
       </c>
-      <c r="Z38" s="99" t="n">
+      <c r="AA38" s="99" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AA38" s="99" t="n">
+      <c r="AB38" s="99" t="n">
         <v>-1.63</v>
       </c>
-      <c r="AB38" s="99" t="n">
+      <c r="AC38" s="99" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AC38" s="99" t="n">
+      <c r="AD38" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AD38" s="99" t="n">
+      <c r="AE38" s="99" t="n">
         <v>-0.9</v>
-      </c>
-      <c r="AE38" s="99" t="n">
-        <v>-2.33</v>
       </c>
     </row>
     <row r="39">
@@ -10583,94 +10583,94 @@
         </is>
       </c>
       <c r="B39" s="99" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="C39" s="99" t="n">
         <v>-2.82</v>
       </c>
-      <c r="C39" s="99" t="n">
+      <c r="D39" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="D39" s="99" t="n">
+      <c r="E39" s="99" t="n">
         <v>2.15</v>
       </c>
-      <c r="E39" s="99" t="n">
+      <c r="F39" s="99" t="n">
         <v>-2.13</v>
       </c>
-      <c r="F39" s="99" t="n">
+      <c r="G39" s="99" t="n">
         <v>-4.01</v>
       </c>
-      <c r="G39" s="99" t="n">
+      <c r="H39" s="99" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="H39" s="99" t="n">
-        <v>-5.22</v>
       </c>
       <c r="I39" s="99" t="n">
         <v>-5.22</v>
       </c>
       <c r="J39" s="99" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="K39" s="99" t="n">
         <v>-7.96</v>
       </c>
-      <c r="K39" s="99" t="n">
+      <c r="L39" s="99" t="n">
         <v>-9.43</v>
       </c>
-      <c r="L39" s="99" t="n">
+      <c r="M39" s="99" t="n">
         <v>-11.19</v>
       </c>
-      <c r="M39" s="99" t="n">
+      <c r="N39" s="99" t="n">
         <v>-9.5</v>
       </c>
-      <c r="N39" s="99" t="n">
+      <c r="O39" s="99" t="n">
         <v>-9.48</v>
       </c>
-      <c r="O39" s="99" t="n">
+      <c r="P39" s="99" t="n">
         <v>-9.92</v>
       </c>
-      <c r="P39" s="99" t="n">
+      <c r="Q39" s="99" t="n">
         <v>-12.73</v>
       </c>
-      <c r="Q39" s="99" t="n">
+      <c r="R39" s="99" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="R39" s="99" t="n">
+      <c r="S39" s="99" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="S39" s="99" t="n">
+      <c r="T39" s="99" t="n">
         <v>-5.98</v>
       </c>
-      <c r="T39" s="99" t="n">
+      <c r="U39" s="99" t="n">
         <v>-5.54</v>
       </c>
-      <c r="U39" s="99" t="n">
+      <c r="V39" s="99" t="n">
         <v>-4.26</v>
       </c>
-      <c r="V39" s="99" t="n">
+      <c r="W39" s="99" t="n">
         <v>-0.29</v>
       </c>
-      <c r="W39" s="99" t="n">
+      <c r="X39" s="99" t="n">
         <v>-0.31</v>
       </c>
-      <c r="X39" s="99" t="n">
+      <c r="Y39" s="99" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Y39" s="99" t="n">
+      <c r="Z39" s="99" t="n">
         <v>-3.12</v>
       </c>
-      <c r="Z39" s="99" t="n">
+      <c r="AA39" s="99" t="n">
         <v>-4.29</v>
       </c>
-      <c r="AA39" s="99" t="n">
+      <c r="AB39" s="99" t="n">
         <v>-4.51</v>
       </c>
-      <c r="AB39" s="99" t="n">
+      <c r="AC39" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="AC39" s="99" t="n">
+      <c r="AD39" s="99" t="n">
         <v>-3.88</v>
       </c>
-      <c r="AD39" s="99" t="n">
+      <c r="AE39" s="99" t="n">
         <v>-2.44</v>
-      </c>
-      <c r="AE39" s="99" t="n">
-        <v>-3.2</v>
       </c>
     </row>
     <row r="40">
@@ -10680,94 +10680,94 @@
         </is>
       </c>
       <c r="B40" s="99" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="C40" s="99" t="n">
         <v>57.87</v>
       </c>
-      <c r="C40" s="99" t="n">
+      <c r="D40" s="99" t="n">
         <v>48.63</v>
       </c>
-      <c r="D40" s="99" t="n">
+      <c r="E40" s="99" t="n">
         <v>89.62</v>
       </c>
-      <c r="E40" s="99" t="n">
+      <c r="F40" s="99" t="n">
         <v>84.76000000000001</v>
       </c>
-      <c r="F40" s="99" t="n">
+      <c r="G40" s="99" t="n">
         <v>72.89</v>
       </c>
-      <c r="G40" s="99" t="n">
+      <c r="H40" s="99" t="n">
         <v>76.04000000000001</v>
-      </c>
-      <c r="H40" s="99" t="n">
-        <v>73.18000000000001</v>
       </c>
       <c r="I40" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
       <c r="J40" s="99" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="K40" s="99" t="n">
         <v>64.19</v>
       </c>
-      <c r="K40" s="99" t="n">
+      <c r="L40" s="99" t="n">
         <v>43.55</v>
       </c>
-      <c r="L40" s="99" t="n">
+      <c r="M40" s="99" t="n">
         <v>36.91</v>
       </c>
-      <c r="M40" s="99" t="n">
+      <c r="N40" s="99" t="n">
         <v>45.5</v>
       </c>
-      <c r="N40" s="99" t="n">
+      <c r="O40" s="99" t="n">
         <v>46.07</v>
       </c>
-      <c r="O40" s="99" t="n">
+      <c r="P40" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="P40" s="99" t="n">
+      <c r="Q40" s="99" t="n">
         <v>10.06</v>
       </c>
-      <c r="Q40" s="99" t="n">
+      <c r="R40" s="99" t="n">
         <v>14.47</v>
       </c>
-      <c r="R40" s="99" t="n">
+      <c r="S40" s="99" t="n">
         <v>15.02</v>
       </c>
-      <c r="S40" s="99" t="n">
+      <c r="T40" s="99" t="n">
         <v>16.6</v>
       </c>
-      <c r="T40" s="99" t="n">
+      <c r="U40" s="99" t="n">
         <v>19.01</v>
       </c>
-      <c r="U40" s="99" t="n">
+      <c r="V40" s="99" t="n">
         <v>22.94</v>
       </c>
-      <c r="V40" s="99" t="n">
+      <c r="W40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="W40" s="99" t="n">
+      <c r="X40" s="99" t="n">
         <v>75.7</v>
       </c>
-      <c r="X40" s="99" t="n">
+      <c r="Y40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="Y40" s="99" t="n">
+      <c r="Z40" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="Z40" s="99" t="n">
+      <c r="AA40" s="99" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="AA40" s="99" t="n">
+      <c r="AB40" s="99" t="n">
         <v>66.31999999999999</v>
       </c>
-      <c r="AB40" s="99" t="n">
+      <c r="AC40" s="99" t="n">
         <v>62.89</v>
       </c>
-      <c r="AC40" s="99" t="n">
+      <c r="AD40" s="99" t="n">
         <v>71.14</v>
       </c>
-      <c r="AD40" s="99" t="n">
+      <c r="AE40" s="99" t="n">
         <v>69.19</v>
-      </c>
-      <c r="AE40" s="99" t="n">
-        <v>66.09</v>
       </c>
     </row>
     <row r="41">
@@ -10777,94 +10777,94 @@
         </is>
       </c>
       <c r="B41" s="99" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="C41" s="99" t="n">
         <v>58.22</v>
       </c>
-      <c r="C41" s="99" t="n">
+      <c r="D41" s="99" t="n">
         <v>52.42</v>
       </c>
-      <c r="D41" s="99" t="n">
+      <c r="E41" s="99" t="n">
         <v>77.31</v>
       </c>
-      <c r="E41" s="99" t="n">
+      <c r="F41" s="99" t="n">
         <v>71.64</v>
       </c>
-      <c r="F41" s="99" t="n">
+      <c r="G41" s="99" t="n">
         <v>61.74</v>
       </c>
-      <c r="G41" s="99" t="n">
+      <c r="H41" s="99" t="n">
         <v>63.04</v>
-      </c>
-      <c r="H41" s="99" t="n">
-        <v>60.77</v>
       </c>
       <c r="I41" s="99" t="n">
         <v>60.77</v>
       </c>
       <c r="J41" s="99" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="K41" s="99" t="n">
         <v>54.21</v>
       </c>
-      <c r="K41" s="99" t="n">
+      <c r="L41" s="99" t="n">
         <v>42.56</v>
       </c>
-      <c r="L41" s="99" t="n">
+      <c r="M41" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="M41" s="99" t="n">
+      <c r="N41" s="99" t="n">
         <v>43.68</v>
       </c>
-      <c r="N41" s="99" t="n">
+      <c r="O41" s="99" t="n">
         <v>43.96</v>
       </c>
-      <c r="O41" s="99" t="n">
+      <c r="P41" s="99" t="n">
         <v>46.79</v>
       </c>
-      <c r="P41" s="99" t="n">
+      <c r="Q41" s="99" t="n">
         <v>26.47</v>
       </c>
-      <c r="Q41" s="99" t="n">
+      <c r="R41" s="99" t="n">
         <v>31.18</v>
       </c>
-      <c r="R41" s="99" t="n">
+      <c r="S41" s="99" t="n">
         <v>31.7</v>
       </c>
-      <c r="S41" s="99" t="n">
+      <c r="T41" s="99" t="n">
         <v>33.25</v>
       </c>
-      <c r="T41" s="99" t="n">
+      <c r="U41" s="99" t="n">
         <v>35.58</v>
       </c>
-      <c r="U41" s="99" t="n">
+      <c r="V41" s="99" t="n">
         <v>39.17</v>
       </c>
-      <c r="V41" s="99" t="n">
+      <c r="W41" s="99" t="n">
         <v>62.79</v>
       </c>
-      <c r="W41" s="99" t="n">
+      <c r="X41" s="99" t="n">
         <v>63.09</v>
       </c>
-      <c r="X41" s="99" t="n">
+      <c r="Y41" s="99" t="n">
         <v>62.51</v>
       </c>
-      <c r="Y41" s="99" t="n">
+      <c r="Z41" s="99" t="n">
         <v>59.46</v>
       </c>
-      <c r="Z41" s="99" t="n">
+      <c r="AA41" s="99" t="n">
         <v>59.6</v>
       </c>
-      <c r="AA41" s="99" t="n">
+      <c r="AB41" s="99" t="n">
         <v>58.83</v>
       </c>
-      <c r="AB41" s="99" t="n">
+      <c r="AC41" s="99" t="n">
         <v>57.26</v>
       </c>
-      <c r="AC41" s="99" t="n">
+      <c r="AD41" s="99" t="n">
         <v>60.15</v>
       </c>
-      <c r="AD41" s="99" t="n">
+      <c r="AE41" s="99" t="n">
         <v>59.04</v>
-      </c>
-      <c r="AE41" s="99" t="n">
-        <v>57.26</v>
       </c>
     </row>
     <row r="42">
@@ -10883,134 +10883,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D42" s="96" t="inlineStr">
+      <c r="D42" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="96" t="inlineStr">
+      <c r="F42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="96" t="inlineStr">
+      <c r="G42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="96" t="inlineStr">
+      <c r="H42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="96" t="inlineStr">
+      <c r="I42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="96" t="inlineStr">
+      <c r="J42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="96" t="inlineStr">
+      <c r="K42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="96" t="inlineStr">
+      <c r="L42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="97" t="inlineStr">
+      <c r="M42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="98" t="inlineStr">
+      <c r="N42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N42" s="98" t="inlineStr">
+      <c r="O42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O42" s="98" t="inlineStr">
+      <c r="P42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P42" s="98" t="inlineStr">
+      <c r="Q42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q42" s="98" t="inlineStr">
+      <c r="R42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R42" s="98" t="inlineStr">
+      <c r="S42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S42" s="97" t="inlineStr">
+      <c r="T42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T42" s="98" t="inlineStr">
+      <c r="U42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="97" t="inlineStr">
+      <c r="V42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="97" t="inlineStr">
+      <c r="W42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="97" t="inlineStr">
+      <c r="X42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="97" t="inlineStr">
+      <c r="Y42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="97" t="inlineStr">
+      <c r="Z42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="97" t="inlineStr">
+      <c r="AA42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="97" t="inlineStr">
+      <c r="AB42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="97" t="inlineStr">
+      <c r="AC42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC42" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AD42" s="96" t="inlineStr">
@@ -11031,67 +11031,67 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C43" s="99" t="n">
         <v>0.71</v>
       </c>
-      <c r="C43" s="99" t="n">
+      <c r="D43" s="99" t="n">
         <v>0.63</v>
       </c>
-      <c r="D43" s="99" t="n">
+      <c r="E43" s="99" t="n">
         <v>1.1</v>
       </c>
-      <c r="E43" s="99" t="n">
+      <c r="F43" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="F43" s="99" t="n">
+      <c r="G43" s="99" t="n">
         <v>2.62</v>
       </c>
-      <c r="G43" s="99" t="n">
+      <c r="H43" s="99" t="n">
         <v>1.79</v>
       </c>
-      <c r="H43" s="99" t="n">
+      <c r="I43" s="99" t="n">
         <v>1.86</v>
       </c>
-      <c r="I43" s="99" t="n">
+      <c r="J43" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="J43" s="99" t="n">
+      <c r="K43" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="K43" s="99" t="n">
+      <c r="L43" s="99" t="n">
         <v>0.66</v>
       </c>
-      <c r="L43" s="99" t="n">
+      <c r="M43" s="99" t="n">
         <v>0.39</v>
       </c>
-      <c r="M43" s="99" t="n">
+      <c r="N43" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="N43" s="99" t="n">
+      <c r="O43" s="99" t="n">
         <v>-2.39</v>
       </c>
-      <c r="O43" s="99" t="n">
+      <c r="P43" s="99" t="n">
         <v>-1.83</v>
       </c>
-      <c r="P43" s="99" t="n">
+      <c r="Q43" s="99" t="n">
         <v>-2.05</v>
       </c>
-      <c r="Q43" s="99" t="n">
+      <c r="R43" s="99" t="n">
         <v>-1.53</v>
       </c>
-      <c r="R43" s="99" t="n">
+      <c r="S43" s="99" t="n">
         <v>-0.95</v>
       </c>
-      <c r="S43" s="99" t="n">
+      <c r="T43" s="99" t="n">
         <v>-2.12</v>
       </c>
-      <c r="T43" s="99" t="n">
+      <c r="U43" s="99" t="n">
         <v>-2.46</v>
       </c>
-      <c r="U43" s="99" t="n">
+      <c r="V43" s="99" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="V43" s="99" t="n">
-        <v>-0.53</v>
       </c>
       <c r="W43" s="99" t="n">
         <v>-0.53</v>
@@ -11100,25 +11100,25 @@
         <v>-0.53</v>
       </c>
       <c r="Y43" s="99" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Z43" s="99" t="n">
         <v>-0.47</v>
       </c>
-      <c r="Z43" s="99" t="n">
+      <c r="AA43" s="99" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AA43" s="99" t="n">
+      <c r="AB43" s="99" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AB43" s="99" t="n">
+      <c r="AC43" s="99" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AC43" s="99" t="n">
+      <c r="AD43" s="99" t="n">
         <v>0.42</v>
       </c>
-      <c r="AD43" s="99" t="n">
+      <c r="AE43" s="99" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AE43" s="99" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="44">
@@ -11131,64 +11131,64 @@
         <v>2.33</v>
       </c>
       <c r="C44" s="99" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D44" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="D44" s="99" t="n">
+      <c r="E44" s="99" t="n">
         <v>2.85</v>
       </c>
-      <c r="E44" s="99" t="n">
+      <c r="F44" s="99" t="n">
         <v>1.83</v>
       </c>
-      <c r="F44" s="99" t="n">
+      <c r="G44" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="G44" s="99" t="n">
+      <c r="H44" s="99" t="n">
         <v>-0.78</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="I44" s="99" t="n">
         <v>-1.02</v>
       </c>
-      <c r="I44" s="99" t="n">
+      <c r="J44" s="99" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="J44" s="99" t="n">
+      <c r="K44" s="99" t="n">
         <v>-1.47</v>
       </c>
-      <c r="K44" s="99" t="n">
+      <c r="L44" s="99" t="n">
         <v>-1.42</v>
       </c>
-      <c r="L44" s="99" t="n">
+      <c r="M44" s="99" t="n">
         <v>-1.81</v>
       </c>
-      <c r="M44" s="99" t="n">
+      <c r="N44" s="99" t="n">
         <v>-2.26</v>
       </c>
-      <c r="N44" s="99" t="n">
+      <c r="O44" s="99" t="n">
         <v>-2.35</v>
       </c>
-      <c r="O44" s="99" t="n">
+      <c r="P44" s="99" t="n">
         <v>-1.57</v>
       </c>
-      <c r="P44" s="99" t="n">
+      <c r="Q44" s="99" t="n">
         <v>-0.54</v>
       </c>
-      <c r="Q44" s="99" t="n">
+      <c r="R44" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="R44" s="99" t="n">
+      <c r="S44" s="99" t="n">
         <v>1.94</v>
       </c>
-      <c r="S44" s="99" t="n">
+      <c r="T44" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="T44" s="99" t="n">
+      <c r="U44" s="99" t="n">
         <v>0.31</v>
       </c>
-      <c r="U44" s="99" t="n">
+      <c r="V44" s="99" t="n">
         <v>0.42</v>
-      </c>
-      <c r="V44" s="99" t="n">
-        <v>3.12</v>
       </c>
       <c r="W44" s="99" t="n">
         <v>3.12</v>
@@ -11197,25 +11197,25 @@
         <v>3.12</v>
       </c>
       <c r="Y44" s="99" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Z44" s="99" t="n">
         <v>3.72</v>
       </c>
-      <c r="Z44" s="99" t="n">
+      <c r="AA44" s="99" t="n">
         <v>2.73</v>
       </c>
-      <c r="AA44" s="99" t="n">
+      <c r="AB44" s="99" t="n">
         <v>0.95</v>
       </c>
-      <c r="AB44" s="99" t="n">
+      <c r="AC44" s="99" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC44" s="99" t="n">
+      <c r="AD44" s="99" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD44" s="99" t="n">
+      <c r="AE44" s="99" t="n">
         <v>1.69</v>
-      </c>
-      <c r="AE44" s="99" t="n">
-        <v>2.05</v>
       </c>
     </row>
     <row r="45">
@@ -11225,67 +11225,67 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="C45" s="99" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="C45" s="99" t="n">
+      <c r="D45" s="99" t="n">
         <v>65.09</v>
       </c>
-      <c r="D45" s="99" t="n">
+      <c r="E45" s="99" t="n">
         <v>86.66</v>
       </c>
-      <c r="E45" s="99" t="n">
+      <c r="F45" s="99" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="F45" s="99" t="n">
+      <c r="G45" s="99" t="n">
         <v>88</v>
       </c>
-      <c r="G45" s="99" t="n">
+      <c r="H45" s="99" t="n">
         <v>77.98</v>
       </c>
-      <c r="H45" s="99" t="n">
+      <c r="I45" s="99" t="n">
         <v>59.82</v>
       </c>
-      <c r="I45" s="99" t="n">
+      <c r="J45" s="99" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="J45" s="99" t="n">
+      <c r="K45" s="99" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="K45" s="99" t="n">
+      <c r="L45" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="L45" s="99" t="n">
+      <c r="M45" s="99" t="n">
         <v>60.96</v>
       </c>
-      <c r="M45" s="99" t="n">
+      <c r="N45" s="99" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="N45" s="99" t="n">
+      <c r="O45" s="99" t="n">
         <v>20.58</v>
       </c>
-      <c r="O45" s="99" t="n">
+      <c r="P45" s="99" t="n">
         <v>30.12</v>
       </c>
-      <c r="P45" s="99" t="n">
+      <c r="Q45" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="Q45" s="99" t="n">
+      <c r="R45" s="99" t="n">
         <v>13.57</v>
       </c>
-      <c r="R45" s="99" t="n">
+      <c r="S45" s="99" t="n">
         <v>28.44</v>
       </c>
-      <c r="S45" s="99" t="n">
+      <c r="T45" s="99" t="n">
         <v>44.72</v>
       </c>
-      <c r="T45" s="99" t="n">
+      <c r="U45" s="99" t="n">
         <v>14.66</v>
       </c>
-      <c r="U45" s="99" t="n">
+      <c r="V45" s="99" t="n">
         <v>28.1</v>
-      </c>
-      <c r="V45" s="99" t="n">
-        <v>80.38</v>
       </c>
       <c r="W45" s="99" t="n">
         <v>80.38</v>
@@ -11294,25 +11294,25 @@
         <v>80.38</v>
       </c>
       <c r="Y45" s="99" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="Z45" s="99" t="n">
         <v>68.92</v>
       </c>
-      <c r="Z45" s="99" t="n">
+      <c r="AA45" s="99" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="AA45" s="99" t="n">
+      <c r="AB45" s="99" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="AB45" s="99" t="n">
+      <c r="AC45" s="99" t="n">
         <v>63.9</v>
       </c>
-      <c r="AC45" s="99" t="n">
+      <c r="AD45" s="99" t="n">
         <v>90.77</v>
       </c>
-      <c r="AD45" s="99" t="n">
+      <c r="AE45" s="99" t="n">
         <v>89.34</v>
-      </c>
-      <c r="AE45" s="99" t="n">
-        <v>94.22</v>
       </c>
     </row>
     <row r="46">
@@ -11322,67 +11322,67 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
+        <v>60.97</v>
+      </c>
+      <c r="C46" s="99" t="n">
         <v>74.77</v>
       </c>
-      <c r="C46" s="99" t="n">
+      <c r="D46" s="99" t="n">
         <v>69.34999999999999</v>
       </c>
-      <c r="D46" s="99" t="n">
+      <c r="E46" s="99" t="n">
         <v>78.83</v>
       </c>
-      <c r="E46" s="99" t="n">
+      <c r="F46" s="99" t="n">
         <v>80.52</v>
       </c>
-      <c r="F46" s="99" t="n">
+      <c r="G46" s="99" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="G46" s="99" t="n">
+      <c r="H46" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="H46" s="99" t="n">
+      <c r="I46" s="99" t="n">
         <v>58.07</v>
       </c>
-      <c r="I46" s="99" t="n">
+      <c r="J46" s="99" t="n">
         <v>65.81</v>
       </c>
-      <c r="J46" s="99" t="n">
+      <c r="K46" s="99" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="K46" s="99" t="n">
+      <c r="L46" s="99" t="n">
         <v>58.52</v>
       </c>
-      <c r="L46" s="99" t="n">
+      <c r="M46" s="99" t="n">
         <v>51.86</v>
       </c>
-      <c r="M46" s="99" t="n">
+      <c r="N46" s="99" t="n">
         <v>16.23</v>
       </c>
-      <c r="N46" s="99" t="n">
+      <c r="O46" s="99" t="n">
         <v>25.94</v>
       </c>
-      <c r="O46" s="99" t="n">
+      <c r="P46" s="99" t="n">
         <v>31.58</v>
       </c>
-      <c r="P46" s="99" t="n">
+      <c r="Q46" s="99" t="n">
         <v>22.65</v>
       </c>
-      <c r="Q46" s="99" t="n">
+      <c r="R46" s="99" t="n">
         <v>24.26</v>
       </c>
-      <c r="R46" s="99" t="n">
+      <c r="S46" s="99" t="n">
         <v>38.08</v>
       </c>
-      <c r="S46" s="99" t="n">
+      <c r="T46" s="99" t="n">
         <v>49.25</v>
       </c>
-      <c r="T46" s="99" t="n">
+      <c r="U46" s="99" t="n">
         <v>35.21</v>
       </c>
-      <c r="U46" s="99" t="n">
+      <c r="V46" s="99" t="n">
         <v>49.75</v>
-      </c>
-      <c r="V46" s="99" t="n">
-        <v>76.69</v>
       </c>
       <c r="W46" s="99" t="n">
         <v>76.69</v>
@@ -11391,25 +11391,25 @@
         <v>76.69</v>
       </c>
       <c r="Y46" s="99" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="Z46" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="Z46" s="99" t="n">
+      <c r="AA46" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="AA46" s="99" t="n">
+      <c r="AB46" s="99" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="AB46" s="99" t="n">
+      <c r="AC46" s="99" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="AC46" s="99" t="n">
+      <c r="AD46" s="99" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="AD46" s="99" t="n">
+      <c r="AE46" s="99" t="n">
         <v>82.43000000000001</v>
-      </c>
-      <c r="AE46" s="99" t="n">
-        <v>84.70999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -11433,99 +11433,99 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E47" s="96" t="inlineStr">
+      <c r="E47" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F47" s="96" t="inlineStr">
+      <c r="G47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G47" s="96" t="inlineStr">
+      <c r="H47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H47" s="96" t="inlineStr">
+      <c r="I47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I47" s="96" t="inlineStr">
+      <c r="J47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J47" s="96" t="inlineStr">
+      <c r="K47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K47" s="97" t="inlineStr">
+      <c r="L47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L47" s="96" t="inlineStr">
+      <c r="M47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M47" s="96" t="inlineStr">
+      <c r="N47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="96" t="inlineStr">
+      <c r="O47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="96" t="inlineStr">
+      <c r="P47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P47" s="98" t="inlineStr">
+      <c r="Q47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q47" s="97" t="inlineStr">
+      <c r="R47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R47" s="98" t="inlineStr">
+      <c r="S47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S47" s="98" t="inlineStr">
+      <c r="T47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T47" s="97" t="inlineStr">
+      <c r="U47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U47" s="97" t="inlineStr">
+      <c r="V47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V47" s="97" t="inlineStr">
+      <c r="W47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="W47" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="X47" s="96" t="inlineStr">
@@ -11579,91 +11579,91 @@
         <v>5.39</v>
       </c>
       <c r="C48" s="99" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D48" s="99" t="n">
         <v>5.38</v>
       </c>
-      <c r="D48" s="99" t="n">
+      <c r="E48" s="99" t="n">
         <v>6.9</v>
       </c>
-      <c r="E48" s="99" t="n">
+      <c r="F48" s="99" t="n">
         <v>7.31</v>
       </c>
-      <c r="F48" s="99" t="n">
+      <c r="G48" s="99" t="n">
         <v>7.21</v>
       </c>
-      <c r="G48" s="99" t="n">
+      <c r="H48" s="99" t="n">
         <v>6.84</v>
       </c>
-      <c r="H48" s="99" t="n">
+      <c r="I48" s="99" t="n">
         <v>7.46</v>
       </c>
-      <c r="I48" s="99" t="n">
+      <c r="J48" s="99" t="n">
         <v>6.69</v>
       </c>
-      <c r="J48" s="99" t="n">
+      <c r="K48" s="99" t="n">
         <v>5.73</v>
       </c>
-      <c r="K48" s="99" t="n">
+      <c r="L48" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="L48" s="99" t="n">
+      <c r="M48" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="M48" s="99" t="n">
+      <c r="N48" s="99" t="n">
         <v>7.48</v>
       </c>
-      <c r="N48" s="99" t="n">
+      <c r="O48" s="99" t="n">
         <v>6.99</v>
       </c>
-      <c r="O48" s="99" t="n">
+      <c r="P48" s="99" t="n">
         <v>7.27</v>
       </c>
-      <c r="P48" s="99" t="n">
+      <c r="Q48" s="99" t="n">
         <v>5.46</v>
       </c>
-      <c r="Q48" s="99" t="n">
+      <c r="R48" s="99" t="n">
         <v>6.4</v>
       </c>
-      <c r="R48" s="99" t="n">
+      <c r="S48" s="99" t="n">
         <v>6.18</v>
       </c>
-      <c r="S48" s="99" t="n">
+      <c r="T48" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="T48" s="99" t="n">
+      <c r="U48" s="99" t="n">
         <v>7.51</v>
       </c>
-      <c r="U48" s="99" t="n">
+      <c r="V48" s="99" t="n">
         <v>7.66</v>
       </c>
-      <c r="V48" s="99" t="n">
+      <c r="W48" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="W48" s="99" t="n">
+      <c r="X48" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="X48" s="99" t="n">
+      <c r="Y48" s="99" t="n">
         <v>10.73</v>
       </c>
-      <c r="Y48" s="99" t="n">
+      <c r="Z48" s="99" t="n">
         <v>13.95</v>
       </c>
-      <c r="Z48" s="99" t="n">
+      <c r="AA48" s="99" t="n">
         <v>6.95</v>
       </c>
-      <c r="AA48" s="99" t="n">
+      <c r="AB48" s="99" t="n">
         <v>10.48</v>
       </c>
-      <c r="AB48" s="99" t="n">
+      <c r="AC48" s="99" t="n">
         <v>10.57</v>
       </c>
-      <c r="AC48" s="99" t="n">
+      <c r="AD48" s="99" t="n">
         <v>8.84</v>
       </c>
-      <c r="AD48" s="99" t="n">
+      <c r="AE48" s="99" t="n">
         <v>7.83</v>
-      </c>
-      <c r="AE48" s="99" t="n">
-        <v>7.31</v>
       </c>
     </row>
     <row r="49">
@@ -11676,91 +11676,91 @@
         <v>12.83</v>
       </c>
       <c r="C49" s="99" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="D49" s="99" t="n">
         <v>12.79</v>
       </c>
-      <c r="D49" s="99" t="n">
+      <c r="E49" s="99" t="n">
         <v>15.25</v>
       </c>
-      <c r="E49" s="99" t="n">
+      <c r="F49" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="F49" s="99" t="n">
+      <c r="G49" s="99" t="n">
         <v>15.29</v>
       </c>
-      <c r="G49" s="99" t="n">
+      <c r="H49" s="99" t="n">
         <v>14.9</v>
       </c>
-      <c r="H49" s="99" t="n">
+      <c r="I49" s="99" t="n">
         <v>14.75</v>
       </c>
-      <c r="I49" s="99" t="n">
+      <c r="J49" s="99" t="n">
         <v>14.79</v>
       </c>
-      <c r="J49" s="99" t="n">
+      <c r="K49" s="99" t="n">
         <v>13.96</v>
       </c>
-      <c r="K49" s="99" t="n">
+      <c r="L49" s="99" t="n">
         <v>14.46</v>
       </c>
-      <c r="L49" s="99" t="n">
+      <c r="M49" s="99" t="n">
         <v>14.07</v>
       </c>
-      <c r="M49" s="99" t="n">
+      <c r="N49" s="99" t="n">
         <v>14.24</v>
       </c>
-      <c r="N49" s="99" t="n">
+      <c r="O49" s="99" t="n">
         <v>14.96</v>
       </c>
-      <c r="O49" s="99" t="n">
+      <c r="P49" s="99" t="n">
         <v>15.21</v>
       </c>
-      <c r="P49" s="99" t="n">
+      <c r="Q49" s="99" t="n">
         <v>12.06</v>
       </c>
-      <c r="Q49" s="99" t="n">
+      <c r="R49" s="99" t="n">
         <v>12.77</v>
       </c>
-      <c r="R49" s="99" t="n">
+      <c r="S49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="S49" s="99" t="n">
+      <c r="T49" s="99" t="n">
         <v>11.57</v>
       </c>
-      <c r="T49" s="99" t="n">
+      <c r="U49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="U49" s="99" t="n">
+      <c r="V49" s="99" t="n">
         <v>12.04</v>
       </c>
-      <c r="V49" s="99" t="n">
+      <c r="W49" s="99" t="n">
         <v>11.38</v>
       </c>
-      <c r="W49" s="99" t="n">
+      <c r="X49" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="X49" s="99" t="n">
+      <c r="Y49" s="99" t="n">
         <v>11.79</v>
       </c>
-      <c r="Y49" s="99" t="n">
+      <c r="Z49" s="99" t="n">
         <v>11.18</v>
       </c>
-      <c r="Z49" s="99" t="n">
+      <c r="AA49" s="99" t="n">
         <v>10.81</v>
       </c>
-      <c r="AA49" s="99" t="n">
+      <c r="AB49" s="99" t="n">
         <v>10.8</v>
       </c>
-      <c r="AB49" s="99" t="n">
+      <c r="AC49" s="99" t="n">
         <v>12.69</v>
       </c>
-      <c r="AC49" s="99" t="n">
+      <c r="AD49" s="99" t="n">
         <v>12.14</v>
       </c>
-      <c r="AD49" s="99" t="n">
+      <c r="AE49" s="99" t="n">
         <v>10.89</v>
-      </c>
-      <c r="AE49" s="99" t="n">
-        <v>11.15</v>
       </c>
     </row>
     <row r="50">
@@ -11773,91 +11773,91 @@
         <v>51.33</v>
       </c>
       <c r="C50" s="99" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="D50" s="99" t="n">
         <v>51.88</v>
       </c>
-      <c r="D50" s="99" t="n">
+      <c r="E50" s="99" t="n">
         <v>80.16</v>
       </c>
-      <c r="E50" s="99" t="n">
+      <c r="F50" s="99" t="n">
         <v>88.77</v>
       </c>
-      <c r="F50" s="99" t="n">
+      <c r="G50" s="99" t="n">
         <v>85.37</v>
       </c>
-      <c r="G50" s="99" t="n">
+      <c r="H50" s="99" t="n">
         <v>83.76000000000001</v>
       </c>
-      <c r="H50" s="99" t="n">
+      <c r="I50" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="I50" s="99" t="n">
+      <c r="J50" s="99" t="n">
         <v>82</v>
       </c>
-      <c r="J50" s="99" t="n">
+      <c r="K50" s="99" t="n">
         <v>68.75</v>
       </c>
-      <c r="K50" s="99" t="n">
+      <c r="L50" s="99" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L50" s="99" t="n">
+      <c r="M50" s="99" t="n">
         <v>68.95</v>
       </c>
-      <c r="M50" s="99" t="n">
+      <c r="N50" s="99" t="n">
         <v>67.75</v>
       </c>
-      <c r="N50" s="99" t="n">
+      <c r="O50" s="99" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="O50" s="99" t="n">
+      <c r="P50" s="99" t="n">
         <v>68.14</v>
       </c>
-      <c r="P50" s="99" t="n">
+      <c r="Q50" s="99" t="n">
         <v>46.32</v>
       </c>
-      <c r="Q50" s="99" t="n">
+      <c r="R50" s="99" t="n">
         <v>55.3</v>
       </c>
-      <c r="R50" s="99" t="n">
+      <c r="S50" s="99" t="n">
         <v>47.35</v>
       </c>
-      <c r="S50" s="99" t="n">
+      <c r="T50" s="99" t="n">
         <v>37.44</v>
       </c>
-      <c r="T50" s="99" t="n">
+      <c r="U50" s="99" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="U50" s="99" t="n">
+      <c r="V50" s="99" t="n">
         <v>73.75</v>
       </c>
-      <c r="V50" s="99" t="n">
+      <c r="W50" s="99" t="n">
         <v>84.38</v>
       </c>
-      <c r="W50" s="99" t="n">
+      <c r="X50" s="99" t="n">
         <v>84.61</v>
       </c>
-      <c r="X50" s="99" t="n">
+      <c r="Y50" s="99" t="n">
         <v>82.87</v>
       </c>
-      <c r="Y50" s="99" t="n">
+      <c r="Z50" s="99" t="n">
         <v>80.63</v>
       </c>
-      <c r="Z50" s="99" t="n">
+      <c r="AA50" s="99" t="n">
         <v>76.7</v>
       </c>
-      <c r="AA50" s="99" t="n">
+      <c r="AB50" s="99" t="n">
         <v>75.8</v>
       </c>
-      <c r="AB50" s="99" t="n">
+      <c r="AC50" s="99" t="n">
         <v>75.66</v>
       </c>
-      <c r="AC50" s="99" t="n">
+      <c r="AD50" s="99" t="n">
         <v>68.2</v>
       </c>
-      <c r="AD50" s="99" t="n">
+      <c r="AE50" s="99" t="n">
         <v>67.75</v>
-      </c>
-      <c r="AE50" s="99" t="n">
-        <v>65.86</v>
       </c>
     </row>
     <row r="51">
@@ -11870,91 +11870,91 @@
         <v>60.39</v>
       </c>
       <c r="C51" s="99" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="D51" s="99" t="n">
         <v>60.68</v>
       </c>
-      <c r="D51" s="99" t="n">
+      <c r="E51" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="E51" s="99" t="n">
+      <c r="F51" s="99" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="F51" s="99" t="n">
+      <c r="G51" s="99" t="n">
         <v>73.63</v>
       </c>
-      <c r="G51" s="99" t="n">
+      <c r="H51" s="99" t="n">
         <v>72.53</v>
       </c>
-      <c r="H51" s="99" t="n">
+      <c r="I51" s="99" t="n">
         <v>72.69</v>
       </c>
-      <c r="I51" s="99" t="n">
+      <c r="J51" s="99" t="n">
         <v>71.09</v>
       </c>
-      <c r="J51" s="99" t="n">
+      <c r="K51" s="99" t="n">
         <v>64.05</v>
       </c>
-      <c r="K51" s="99" t="n">
+      <c r="L51" s="99" t="n">
         <v>62.55</v>
       </c>
-      <c r="L51" s="99" t="n">
+      <c r="M51" s="99" t="n">
         <v>63.94</v>
       </c>
-      <c r="M51" s="99" t="n">
+      <c r="N51" s="99" t="n">
         <v>63.41</v>
       </c>
-      <c r="N51" s="99" t="n">
+      <c r="O51" s="99" t="n">
         <v>62.86</v>
       </c>
-      <c r="O51" s="99" t="n">
+      <c r="P51" s="99" t="n">
         <v>63.52</v>
       </c>
-      <c r="P51" s="99" t="n">
+      <c r="Q51" s="99" t="n">
         <v>54.48</v>
       </c>
-      <c r="Q51" s="99" t="n">
+      <c r="R51" s="99" t="n">
         <v>58.24</v>
       </c>
-      <c r="R51" s="99" t="n">
+      <c r="S51" s="99" t="n">
         <v>55.62</v>
       </c>
-      <c r="S51" s="99" t="n">
+      <c r="T51" s="99" t="n">
         <v>52.73</v>
       </c>
-      <c r="T51" s="99" t="n">
+      <c r="U51" s="99" t="n">
         <v>63.24</v>
       </c>
-      <c r="U51" s="99" t="n">
+      <c r="V51" s="99" t="n">
         <v>65.06</v>
       </c>
-      <c r="V51" s="99" t="n">
+      <c r="W51" s="99" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="W51" s="99" t="n">
+      <c r="X51" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="X51" s="99" t="n">
+      <c r="Y51" s="99" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="Y51" s="99" t="n">
+      <c r="Z51" s="99" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="Z51" s="99" t="n">
+      <c r="AA51" s="99" t="n">
         <v>63.2</v>
       </c>
-      <c r="AA51" s="99" t="n">
+      <c r="AB51" s="99" t="n">
         <v>62.77</v>
       </c>
-      <c r="AB51" s="99" t="n">
+      <c r="AC51" s="99" t="n">
         <v>62.7</v>
       </c>
-      <c r="AC51" s="99" t="n">
+      <c r="AD51" s="99" t="n">
         <v>59.22</v>
       </c>
-      <c r="AD51" s="99" t="n">
+      <c r="AE51" s="99" t="n">
         <v>59.02</v>
-      </c>
-      <c r="AE51" s="99" t="n">
-        <v>58.18</v>
       </c>
     </row>
     <row r="52">
@@ -11963,139 +11963,139 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="98" t="inlineStr">
+      <c r="B52" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C52" s="97" t="inlineStr">
+      <c r="D52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D52" s="96" t="inlineStr">
+      <c r="E52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E52" s="96" t="inlineStr">
+      <c r="F52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F52" s="96" t="inlineStr">
+      <c r="G52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G52" s="96" t="inlineStr">
+      <c r="H52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H52" s="97" t="inlineStr">
+      <c r="I52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I52" s="97" t="inlineStr">
+      <c r="J52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J52" s="96" t="inlineStr">
+      <c r="K52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K52" s="97" t="inlineStr">
+      <c r="L52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L52" s="96" t="inlineStr">
+      <c r="M52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M52" s="97" t="inlineStr">
+      <c r="N52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N52" s="96" t="inlineStr">
+      <c r="O52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O52" s="97" t="inlineStr">
+      <c r="P52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P52" s="98" t="inlineStr">
+      <c r="Q52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q52" s="98" t="inlineStr">
+      <c r="R52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R52" s="98" t="inlineStr">
+      <c r="S52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S52" s="98" t="inlineStr">
+      <c r="T52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T52" s="98" t="inlineStr">
+      <c r="U52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U52" s="98" t="inlineStr">
+      <c r="V52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V52" s="97" t="inlineStr">
+      <c r="W52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W52" s="97" t="inlineStr">
+      <c r="X52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X52" s="97" t="inlineStr">
+      <c r="Y52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y52" s="96" t="inlineStr">
+      <c r="Z52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z52" s="97" t="inlineStr">
+      <c r="AA52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA52" s="97" t="inlineStr">
+      <c r="AB52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB52" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC52" s="96" t="inlineStr">
@@ -12121,94 +12121,94 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C53" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="C53" s="99" t="n">
+      <c r="D53" s="99" t="n">
         <v>0.11</v>
       </c>
-      <c r="D53" s="99" t="n">
+      <c r="E53" s="99" t="n">
         <v>1.51</v>
       </c>
-      <c r="E53" s="99" t="n">
+      <c r="F53" s="99" t="n">
         <v>0.6</v>
       </c>
-      <c r="F53" s="99" t="n">
+      <c r="G53" s="99" t="n">
         <v>-0.87</v>
       </c>
-      <c r="G53" s="99" t="n">
+      <c r="H53" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="H53" s="99" t="n">
+      <c r="I53" s="99" t="n">
         <v>-0.7</v>
       </c>
-      <c r="I53" s="99" t="n">
+      <c r="J53" s="99" t="n">
         <v>0.28</v>
       </c>
-      <c r="J53" s="99" t="n">
+      <c r="K53" s="99" t="n">
         <v>1.12</v>
       </c>
-      <c r="K53" s="99" t="n">
+      <c r="L53" s="99" t="n">
         <v>-2.16</v>
       </c>
-      <c r="L53" s="99" t="n">
+      <c r="M53" s="99" t="n">
         <v>-2.28</v>
       </c>
-      <c r="M53" s="99" t="n">
+      <c r="N53" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="N53" s="99" t="n">
+      <c r="O53" s="99" t="n">
         <v>-2.14</v>
       </c>
-      <c r="O53" s="99" t="n">
+      <c r="P53" s="99" t="n">
         <v>-3.08</v>
       </c>
-      <c r="P53" s="99" t="n">
+      <c r="Q53" s="99" t="n">
         <v>-2.29</v>
       </c>
-      <c r="Q53" s="99" t="n">
+      <c r="R53" s="99" t="n">
         <v>-2.9</v>
       </c>
-      <c r="R53" s="99" t="n">
+      <c r="S53" s="99" t="n">
         <v>-1.93</v>
       </c>
-      <c r="S53" s="99" t="n">
+      <c r="T53" s="99" t="n">
         <v>-2.01</v>
       </c>
-      <c r="T53" s="99" t="n">
+      <c r="U53" s="99" t="n">
         <v>-3.58</v>
       </c>
-      <c r="U53" s="99" t="n">
+      <c r="V53" s="99" t="n">
         <v>-4.62</v>
       </c>
-      <c r="V53" s="99" t="n">
+      <c r="W53" s="99" t="n">
         <v>-2.75</v>
       </c>
-      <c r="W53" s="99" t="n">
+      <c r="X53" s="99" t="n">
         <v>-3.14</v>
       </c>
-      <c r="X53" s="99" t="n">
+      <c r="Y53" s="99" t="n">
         <v>-4.63</v>
       </c>
-      <c r="Y53" s="99" t="n">
+      <c r="Z53" s="99" t="n">
         <v>-4.96</v>
       </c>
-      <c r="Z53" s="99" t="n">
+      <c r="AA53" s="99" t="n">
         <v>-5.36</v>
       </c>
-      <c r="AA53" s="99" t="n">
+      <c r="AB53" s="99" t="n">
         <v>-4.69</v>
       </c>
-      <c r="AB53" s="99" t="n">
+      <c r="AC53" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="AC53" s="99" t="n">
+      <c r="AD53" s="99" t="n">
         <v>-5.2</v>
       </c>
-      <c r="AD53" s="99" t="n">
+      <c r="AE53" s="99" t="n">
         <v>-5.7</v>
-      </c>
-      <c r="AE53" s="99" t="n">
-        <v>-5.17</v>
       </c>
     </row>
     <row r="54">
@@ -12218,94 +12218,94 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="C54" s="99" t="n">
         <v>-5.85</v>
       </c>
-      <c r="C54" s="99" t="n">
+      <c r="D54" s="99" t="n">
         <v>-4.68</v>
       </c>
-      <c r="D54" s="99" t="n">
+      <c r="E54" s="99" t="n">
         <v>-2.89</v>
       </c>
-      <c r="E54" s="99" t="n">
+      <c r="F54" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="F54" s="99" t="n">
+      <c r="G54" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="G54" s="99" t="n">
+      <c r="H54" s="99" t="n">
         <v>-6.35</v>
       </c>
-      <c r="H54" s="99" t="n">
+      <c r="I54" s="99" t="n">
         <v>-6.86</v>
       </c>
-      <c r="I54" s="99" t="n">
+      <c r="J54" s="99" t="n">
         <v>-7.99</v>
       </c>
-      <c r="J54" s="99" t="n">
+      <c r="K54" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="K54" s="99" t="n">
+      <c r="L54" s="99" t="n">
         <v>-8.43</v>
       </c>
-      <c r="L54" s="99" t="n">
+      <c r="M54" s="99" t="n">
         <v>-8.75</v>
       </c>
-      <c r="M54" s="99" t="n">
+      <c r="N54" s="99" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="N54" s="99" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="O54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="P54" s="99" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="Q54" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="Q54" s="99" t="n">
+      <c r="R54" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="R54" s="99" t="n">
+      <c r="S54" s="99" t="n">
         <v>-9.02</v>
       </c>
-      <c r="S54" s="99" t="n">
+      <c r="T54" s="99" t="n">
         <v>-10.35</v>
       </c>
-      <c r="T54" s="99" t="n">
+      <c r="U54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="U54" s="99" t="n">
+      <c r="V54" s="99" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="V54" s="99" t="n">
+      <c r="W54" s="99" t="n">
         <v>-7.18</v>
       </c>
-      <c r="W54" s="99" t="n">
+      <c r="X54" s="99" t="n">
         <v>-6.04</v>
       </c>
-      <c r="X54" s="99" t="n">
+      <c r="Y54" s="99" t="n">
         <v>-5.64</v>
       </c>
-      <c r="Y54" s="99" t="n">
+      <c r="Z54" s="99" t="n">
         <v>-4.72</v>
       </c>
-      <c r="Z54" s="99" t="n">
+      <c r="AA54" s="99" t="n">
         <v>-5.61</v>
       </c>
-      <c r="AA54" s="99" t="n">
+      <c r="AB54" s="99" t="n">
         <v>-5.62</v>
       </c>
-      <c r="AB54" s="99" t="n">
+      <c r="AC54" s="99" t="n">
         <v>-4.58</v>
       </c>
-      <c r="AC54" s="99" t="n">
+      <c r="AD54" s="99" t="n">
         <v>-4.48</v>
       </c>
-      <c r="AD54" s="99" t="n">
+      <c r="AE54" s="99" t="n">
         <v>-5.43</v>
-      </c>
-      <c r="AE54" s="99" t="n">
-        <v>-5.16</v>
       </c>
     </row>
     <row r="55">
@@ -12315,94 +12315,94 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="C55" s="99" t="n">
         <v>34.48</v>
       </c>
-      <c r="C55" s="99" t="n">
+      <c r="D55" s="99" t="n">
         <v>44.35</v>
       </c>
-      <c r="D55" s="99" t="n">
+      <c r="E55" s="99" t="n">
         <v>85.76000000000001</v>
       </c>
-      <c r="E55" s="99" t="n">
+      <c r="F55" s="99" t="n">
         <v>82.23</v>
       </c>
-      <c r="F55" s="99" t="n">
+      <c r="G55" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="G55" s="99" t="n">
+      <c r="H55" s="99" t="n">
         <v>71.87</v>
       </c>
-      <c r="H55" s="99" t="n">
+      <c r="I55" s="99" t="n">
         <v>50.77</v>
       </c>
-      <c r="I55" s="99" t="n">
+      <c r="J55" s="99" t="n">
         <v>48.68</v>
       </c>
-      <c r="J55" s="99" t="n">
+      <c r="K55" s="99" t="n">
         <v>83.53</v>
       </c>
-      <c r="K55" s="99" t="n">
+      <c r="L55" s="99" t="n">
         <v>43.83</v>
       </c>
-      <c r="L55" s="99" t="n">
+      <c r="M55" s="99" t="n">
         <v>73.12</v>
       </c>
-      <c r="M55" s="99" t="n">
+      <c r="N55" s="99" t="n">
         <v>55.36</v>
       </c>
-      <c r="N55" s="99" t="n">
+      <c r="O55" s="99" t="n">
         <v>67.8</v>
       </c>
-      <c r="O55" s="99" t="n">
+      <c r="P55" s="99" t="n">
         <v>54.91</v>
       </c>
-      <c r="P55" s="99" t="n">
+      <c r="Q55" s="99" t="n">
         <v>31.87</v>
       </c>
-      <c r="Q55" s="99" t="n">
+      <c r="R55" s="99" t="n">
         <v>35.24</v>
       </c>
-      <c r="R55" s="99" t="n">
+      <c r="S55" s="99" t="n">
         <v>39.87</v>
       </c>
-      <c r="S55" s="99" t="n">
+      <c r="T55" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="T55" s="99" t="n">
+      <c r="U55" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="U55" s="99" t="n">
+      <c r="V55" s="99" t="n">
         <v>16.74</v>
       </c>
-      <c r="V55" s="99" t="n">
+      <c r="W55" s="99" t="n">
         <v>32.54</v>
       </c>
-      <c r="W55" s="99" t="n">
+      <c r="X55" s="99" t="n">
         <v>82.56</v>
       </c>
-      <c r="X55" s="99" t="n">
+      <c r="Y55" s="99" t="n">
         <v>77.58</v>
       </c>
-      <c r="Y55" s="99" t="n">
+      <c r="Z55" s="99" t="n">
         <v>88.48</v>
       </c>
-      <c r="Z55" s="99" t="n">
+      <c r="AA55" s="99" t="n">
         <v>71.72</v>
       </c>
-      <c r="AA55" s="99" t="n">
+      <c r="AB55" s="99" t="n">
         <v>65.42</v>
       </c>
-      <c r="AB55" s="99" t="n">
+      <c r="AC55" s="99" t="n">
         <v>94.41</v>
       </c>
-      <c r="AC55" s="99" t="n">
+      <c r="AD55" s="99" t="n">
         <v>93.34999999999999</v>
       </c>
-      <c r="AD55" s="99" t="n">
+      <c r="AE55" s="99" t="n">
         <v>86.56</v>
-      </c>
-      <c r="AE55" s="99" t="n">
-        <v>87.25</v>
       </c>
     </row>
     <row r="56">
@@ -12412,94 +12412,94 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="C56" s="99" t="n">
         <v>44.93</v>
       </c>
-      <c r="C56" s="99" t="n">
+      <c r="D56" s="99" t="n">
         <v>52.35</v>
       </c>
-      <c r="D56" s="99" t="n">
+      <c r="E56" s="99" t="n">
         <v>78.61</v>
       </c>
-      <c r="E56" s="99" t="n">
+      <c r="F56" s="99" t="n">
         <v>75.48</v>
       </c>
-      <c r="F56" s="99" t="n">
+      <c r="G56" s="99" t="n">
         <v>57.98</v>
       </c>
-      <c r="G56" s="99" t="n">
+      <c r="H56" s="99" t="n">
         <v>66.2</v>
       </c>
-      <c r="H56" s="99" t="n">
+      <c r="I56" s="99" t="n">
         <v>52.83</v>
       </c>
-      <c r="I56" s="99" t="n">
+      <c r="J56" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="J56" s="99" t="n">
+      <c r="K56" s="99" t="n">
         <v>74.97</v>
       </c>
-      <c r="K56" s="99" t="n">
+      <c r="L56" s="99" t="n">
         <v>45.92</v>
       </c>
-      <c r="L56" s="99" t="n">
+      <c r="M56" s="99" t="n">
         <v>59.76</v>
       </c>
-      <c r="M56" s="99" t="n">
+      <c r="N56" s="99" t="n">
         <v>48.71</v>
       </c>
-      <c r="N56" s="99" t="n">
+      <c r="O56" s="99" t="n">
         <v>53.61</v>
       </c>
-      <c r="O56" s="99" t="n">
+      <c r="P56" s="99" t="n">
         <v>45.19</v>
       </c>
-      <c r="P56" s="99" t="n">
+      <c r="Q56" s="99" t="n">
         <v>32.83</v>
       </c>
-      <c r="Q56" s="99" t="n">
+      <c r="R56" s="99" t="n">
         <v>34.58</v>
       </c>
-      <c r="R56" s="99" t="n">
+      <c r="S56" s="99" t="n">
         <v>37.2</v>
       </c>
-      <c r="S56" s="99" t="n">
+      <c r="T56" s="99" t="n">
         <v>16.31</v>
       </c>
-      <c r="T56" s="99" t="n">
+      <c r="U56" s="99" t="n">
         <v>22.99</v>
       </c>
-      <c r="U56" s="99" t="n">
+      <c r="V56" s="99" t="n">
         <v>32.1</v>
       </c>
-      <c r="V56" s="99" t="n">
+      <c r="W56" s="99" t="n">
         <v>48.66</v>
       </c>
-      <c r="W56" s="99" t="n">
+      <c r="X56" s="99" t="n">
         <v>80.73</v>
       </c>
-      <c r="X56" s="99" t="n">
+      <c r="Y56" s="99" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="Y56" s="99" t="n">
+      <c r="Z56" s="99" t="n">
         <v>83.84</v>
       </c>
-      <c r="Z56" s="99" t="n">
+      <c r="AA56" s="99" t="n">
         <v>74.67</v>
       </c>
-      <c r="AA56" s="99" t="n">
+      <c r="AB56" s="99" t="n">
         <v>72.3</v>
       </c>
-      <c r="AB56" s="99" t="n">
+      <c r="AC56" s="99" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="AC56" s="99" t="n">
+      <c r="AD56" s="99" t="n">
         <v>84.26000000000001</v>
       </c>
-      <c r="AD56" s="99" t="n">
+      <c r="AE56" s="99" t="n">
         <v>78.34</v>
-      </c>
-      <c r="AE56" s="99" t="n">
-        <v>78.61</v>
       </c>
     </row>
     <row r="57">
@@ -12518,134 +12518,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D57" s="96" t="inlineStr">
+      <c r="D57" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E57" s="96" t="inlineStr">
+      <c r="F57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F57" s="97" t="inlineStr">
+      <c r="G57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G57" s="96" t="inlineStr">
+      <c r="H57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H57" s="96" t="inlineStr">
+      <c r="I57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I57" s="97" t="inlineStr">
+      <c r="J57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J57" s="96" t="inlineStr">
+      <c r="K57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K57" s="96" t="inlineStr">
+      <c r="L57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L57" s="96" t="inlineStr">
+      <c r="M57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M57" s="96" t="inlineStr">
+      <c r="N57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N57" s="96" t="inlineStr">
+      <c r="O57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O57" s="96" t="inlineStr">
+      <c r="P57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P57" s="98" t="inlineStr">
+      <c r="Q57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q57" s="98" t="inlineStr">
+      <c r="R57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R57" s="98" t="inlineStr">
+      <c r="S57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S57" s="98" t="inlineStr">
+      <c r="T57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T57" s="98" t="inlineStr">
+      <c r="U57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U57" s="98" t="inlineStr">
+      <c r="V57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V57" s="97" t="inlineStr">
+      <c r="W57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W57" s="97" t="inlineStr">
+      <c r="X57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X57" s="97" t="inlineStr">
+      <c r="Y57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y57" s="96" t="inlineStr">
+      <c r="Z57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z57" s="97" t="inlineStr">
+      <c r="AA57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA57" s="97" t="inlineStr">
+      <c r="AB57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB57" s="97" t="inlineStr">
+      <c r="AC57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC57" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AD57" s="96" t="inlineStr">
@@ -12666,94 +12666,94 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="C58" s="99" t="n">
         <v>5.36</v>
       </c>
-      <c r="C58" s="99" t="n">
+      <c r="D58" s="99" t="n">
         <v>4.62</v>
       </c>
-      <c r="D58" s="99" t="n">
+      <c r="E58" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="E58" s="99" t="n">
+      <c r="F58" s="99" t="n">
         <v>4.27</v>
       </c>
-      <c r="F58" s="99" t="n">
+      <c r="G58" s="99" t="n">
         <v>2.96</v>
       </c>
-      <c r="G58" s="99" t="n">
+      <c r="H58" s="99" t="n">
         <v>4.58</v>
       </c>
-      <c r="H58" s="99" t="n">
+      <c r="I58" s="99" t="n">
         <v>3.04</v>
       </c>
-      <c r="I58" s="99" t="n">
+      <c r="J58" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="J58" s="99" t="n">
+      <c r="K58" s="99" t="n">
         <v>4.35</v>
       </c>
-      <c r="K58" s="99" t="n">
+      <c r="L58" s="99" t="n">
         <v>3.06</v>
       </c>
-      <c r="L58" s="99" t="n">
+      <c r="M58" s="99" t="n">
         <v>3.02</v>
       </c>
-      <c r="M58" s="99" t="n">
+      <c r="N58" s="99" t="n">
         <v>1.68</v>
       </c>
-      <c r="N58" s="99" t="n">
+      <c r="O58" s="99" t="n">
         <v>2.95</v>
-      </c>
-      <c r="O58" s="99" t="n">
-        <v>1.45</v>
       </c>
       <c r="P58" s="99" t="n">
         <v>1.45</v>
       </c>
       <c r="Q58" s="99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R58" s="99" t="n">
         <v>0.74</v>
       </c>
-      <c r="R58" s="99" t="n">
+      <c r="S58" s="99" t="n">
         <v>2.08</v>
       </c>
-      <c r="S58" s="99" t="n">
+      <c r="T58" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="T58" s="99" t="n">
+      <c r="U58" s="99" t="n">
         <v>1.7</v>
       </c>
-      <c r="U58" s="99" t="n">
+      <c r="V58" s="99" t="n">
         <v>-0.21</v>
       </c>
-      <c r="V58" s="99" t="n">
+      <c r="W58" s="99" t="n">
         <v>2.05</v>
       </c>
-      <c r="W58" s="99" t="n">
+      <c r="X58" s="99" t="n">
         <v>2.36</v>
       </c>
-      <c r="X58" s="99" t="n">
+      <c r="Y58" s="99" t="n">
         <v>1.88</v>
       </c>
-      <c r="Y58" s="99" t="n">
+      <c r="Z58" s="99" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z58" s="99" t="n">
+      <c r="AA58" s="99" t="n">
         <v>1.11</v>
       </c>
-      <c r="AA58" s="99" t="n">
+      <c r="AB58" s="99" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB58" s="99" t="n">
+      <c r="AC58" s="99" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC58" s="99" t="n">
+      <c r="AD58" s="99" t="n">
         <v>0.73</v>
       </c>
-      <c r="AD58" s="99" t="n">
+      <c r="AE58" s="99" t="n">
         <v>-0.02</v>
-      </c>
-      <c r="AE58" s="99" t="n">
-        <v>-0.13</v>
       </c>
     </row>
     <row r="59">
@@ -12763,94 +12763,94 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C59" s="99" t="n">
         <v>6.58</v>
       </c>
-      <c r="C59" s="99" t="n">
+      <c r="D59" s="99" t="n">
         <v>7.78</v>
       </c>
-      <c r="D59" s="99" t="n">
+      <c r="E59" s="99" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="E59" s="99" t="n">
+      <c r="F59" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="F59" s="99" t="n">
+      <c r="G59" s="99" t="n">
         <v>4.66</v>
-      </c>
-      <c r="G59" s="99" t="n">
-        <v>3.7</v>
       </c>
       <c r="H59" s="99" t="n">
         <v>3.7</v>
       </c>
       <c r="I59" s="99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J59" s="99" t="n">
         <v>1.72</v>
       </c>
-      <c r="J59" s="99" t="n">
+      <c r="K59" s="99" t="n">
         <v>3.46</v>
       </c>
-      <c r="K59" s="99" t="n">
+      <c r="L59" s="99" t="n">
         <v>2.34</v>
       </c>
-      <c r="L59" s="99" t="n">
+      <c r="M59" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="M59" s="99" t="n">
+      <c r="N59" s="99" t="n">
         <v>0.84</v>
       </c>
-      <c r="N59" s="99" t="n">
+      <c r="O59" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="O59" s="99" t="n">
+      <c r="P59" s="99" t="n">
         <v>1.41</v>
       </c>
-      <c r="P59" s="99" t="n">
+      <c r="Q59" s="99" t="n">
         <v>0.68</v>
       </c>
-      <c r="Q59" s="99" t="n">
+      <c r="R59" s="99" t="n">
         <v>0.48</v>
       </c>
-      <c r="R59" s="99" t="n">
+      <c r="S59" s="99" t="n">
         <v>2.38</v>
       </c>
-      <c r="S59" s="99" t="n">
+      <c r="T59" s="99" t="n">
         <v>1.75</v>
       </c>
-      <c r="T59" s="99" t="n">
+      <c r="U59" s="99" t="n">
         <v>3.59</v>
       </c>
-      <c r="U59" s="99" t="n">
+      <c r="V59" s="99" t="n">
         <v>3.65</v>
       </c>
-      <c r="V59" s="99" t="n">
+      <c r="W59" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="W59" s="99" t="n">
+      <c r="X59" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="X59" s="99" t="n">
+      <c r="Y59" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="Y59" s="99" t="n">
+      <c r="Z59" s="99" t="n">
         <v>6.57</v>
       </c>
-      <c r="Z59" s="99" t="n">
+      <c r="AA59" s="99" t="n">
         <v>5.43</v>
       </c>
-      <c r="AA59" s="99" t="n">
+      <c r="AB59" s="99" t="n">
         <v>4.7</v>
       </c>
-      <c r="AB59" s="99" t="n">
+      <c r="AC59" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="AC59" s="99" t="n">
+      <c r="AD59" s="99" t="n">
         <v>5.28</v>
       </c>
-      <c r="AD59" s="99" t="n">
+      <c r="AE59" s="99" t="n">
         <v>4.39</v>
-      </c>
-      <c r="AE59" s="99" t="n">
-        <v>4.03</v>
       </c>
     </row>
     <row r="60">
@@ -12860,94 +12860,94 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="C60" s="99" t="n">
         <v>55.81</v>
       </c>
-      <c r="C60" s="99" t="n">
+      <c r="D60" s="99" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="D60" s="99" t="n">
+      <c r="E60" s="99" t="n">
         <v>83.8</v>
       </c>
-      <c r="E60" s="99" t="n">
+      <c r="F60" s="99" t="n">
         <v>76.95</v>
       </c>
-      <c r="F60" s="99" t="n">
+      <c r="G60" s="99" t="n">
         <v>59.47</v>
       </c>
-      <c r="G60" s="99" t="n">
+      <c r="H60" s="99" t="n">
         <v>69.06</v>
       </c>
-      <c r="H60" s="99" t="n">
+      <c r="I60" s="99" t="n">
         <v>59.71</v>
       </c>
-      <c r="I60" s="99" t="n">
+      <c r="J60" s="99" t="n">
         <v>50.15</v>
       </c>
-      <c r="J60" s="99" t="n">
+      <c r="K60" s="99" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="K60" s="99" t="n">
+      <c r="L60" s="99" t="n">
         <v>65.67</v>
       </c>
-      <c r="L60" s="99" t="n">
+      <c r="M60" s="99" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="M60" s="99" t="n">
+      <c r="N60" s="99" t="n">
         <v>60.74</v>
       </c>
-      <c r="N60" s="99" t="n">
+      <c r="O60" s="99" t="n">
         <v>69.64</v>
       </c>
-      <c r="O60" s="99" t="n">
+      <c r="P60" s="99" t="n">
         <v>56.63</v>
       </c>
-      <c r="P60" s="99" t="n">
+      <c r="Q60" s="99" t="n">
         <v>34.87</v>
       </c>
-      <c r="Q60" s="99" t="n">
+      <c r="R60" s="99" t="n">
         <v>25.25</v>
       </c>
-      <c r="R60" s="99" t="n">
+      <c r="S60" s="99" t="n">
         <v>36.38</v>
       </c>
-      <c r="S60" s="99" t="n">
+      <c r="T60" s="99" t="n">
         <v>13.61</v>
       </c>
-      <c r="T60" s="99" t="n">
+      <c r="U60" s="99" t="n">
         <v>28.38</v>
       </c>
-      <c r="U60" s="99" t="n">
+      <c r="V60" s="99" t="n">
         <v>29.73</v>
       </c>
-      <c r="V60" s="99" t="n">
+      <c r="W60" s="99" t="n">
         <v>46.54</v>
       </c>
-      <c r="W60" s="99" t="n">
+      <c r="X60" s="99" t="n">
         <v>93.47</v>
       </c>
-      <c r="X60" s="99" t="n">
+      <c r="Y60" s="99" t="n">
         <v>92.75</v>
       </c>
-      <c r="Y60" s="99" t="n">
+      <c r="Z60" s="99" t="n">
         <v>94.58</v>
       </c>
-      <c r="Z60" s="99" t="n">
+      <c r="AA60" s="99" t="n">
         <v>91.78</v>
       </c>
-      <c r="AA60" s="99" t="n">
+      <c r="AB60" s="99" t="n">
         <v>88.26000000000001</v>
       </c>
-      <c r="AB60" s="99" t="n">
+      <c r="AC60" s="99" t="n">
         <v>85.2</v>
       </c>
-      <c r="AC60" s="99" t="n">
+      <c r="AD60" s="99" t="n">
         <v>89.55</v>
       </c>
-      <c r="AD60" s="99" t="n">
+      <c r="AE60" s="99" t="n">
         <v>84.34</v>
-      </c>
-      <c r="AE60" s="99" t="n">
-        <v>82.23999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -12957,107 +12957,107 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="C61" s="99" t="n">
         <v>59.76</v>
       </c>
-      <c r="C61" s="99" t="n">
+      <c r="D61" s="99" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="D61" s="99" t="n">
+      <c r="E61" s="99" t="n">
         <v>78.38</v>
       </c>
-      <c r="E61" s="99" t="n">
+      <c r="F61" s="99" t="n">
         <v>72.42</v>
       </c>
-      <c r="F61" s="99" t="n">
+      <c r="G61" s="99" t="n">
         <v>59.91</v>
       </c>
-      <c r="G61" s="99" t="n">
+      <c r="H61" s="99" t="n">
         <v>66</v>
       </c>
-      <c r="H61" s="99" t="n">
+      <c r="I61" s="99" t="n">
         <v>59.4</v>
       </c>
-      <c r="I61" s="99" t="n">
+      <c r="J61" s="99" t="n">
         <v>52.95</v>
       </c>
-      <c r="J61" s="99" t="n">
+      <c r="K61" s="99" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="K61" s="99" t="n">
+      <c r="L61" s="99" t="n">
         <v>61.14</v>
       </c>
-      <c r="L61" s="99" t="n">
+      <c r="M61" s="99" t="n">
         <v>62.6</v>
       </c>
-      <c r="M61" s="99" t="n">
+      <c r="N61" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="N61" s="99" t="n">
+      <c r="O61" s="99" t="n">
         <v>62.56</v>
       </c>
-      <c r="O61" s="99" t="n">
+      <c r="P61" s="99" t="n">
         <v>52.29</v>
       </c>
-      <c r="P61" s="99" t="n">
+      <c r="Q61" s="99" t="n">
         <v>37.42</v>
       </c>
-      <c r="Q61" s="99" t="n">
+      <c r="R61" s="99" t="n">
         <v>31.32</v>
       </c>
-      <c r="R61" s="99" t="n">
+      <c r="S61" s="99" t="n">
         <v>40.38</v>
       </c>
-      <c r="S61" s="99" t="n">
+      <c r="T61" s="99" t="n">
         <v>26.19</v>
       </c>
-      <c r="T61" s="99" t="n">
+      <c r="U61" s="99" t="n">
         <v>42.54</v>
       </c>
-      <c r="U61" s="99" t="n">
+      <c r="V61" s="99" t="n">
         <v>43.82</v>
       </c>
-      <c r="V61" s="99" t="n">
+      <c r="W61" s="99" t="n">
         <v>58.62</v>
       </c>
-      <c r="W61" s="99" t="n">
+      <c r="X61" s="99" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="X61" s="99" t="n">
+      <c r="Y61" s="99" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="Y61" s="99" t="n">
+      <c r="Z61" s="99" t="n">
         <v>88.2</v>
       </c>
-      <c r="Z61" s="99" t="n">
+      <c r="AA61" s="99" t="n">
         <v>84.89</v>
       </c>
-      <c r="AA61" s="99" t="n">
+      <c r="AB61" s="99" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="AB61" s="99" t="n">
+      <c r="AC61" s="99" t="n">
         <v>79.09</v>
       </c>
-      <c r="AC61" s="99" t="n">
+      <c r="AD61" s="99" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="AD61" s="99" t="n">
+      <c r="AE61" s="99" t="n">
         <v>76.48999999999999</v>
-      </c>
-      <c r="AE61" s="99" t="n">
-        <v>74.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="95" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RSI2:15.42&lt;=36;ixic:RSI2:15.42&lt;=35</t>
+          <t>今日买报：us500:RSI2:22.27&lt;=28;ixic:RSI2:15.42&lt;=36;ixic:RSI2:15.42&lt;=35</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:17.23&gt;=15;hk50:RNG120:26.37&gt;=25;hk50:RSI6:97.18&gt;=76;hk50:RSI19:82.69&gt;=73;us500:RSI2:86.19&gt;=85</t>
+          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:26.09&gt;=15;hk50:RNG120:34.13&gt;=25;hk50:RSI6:98.28&gt;=76;hk50:RSI19:86.55&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B23" s="99" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="C23" s="99" t="n">
         <v>2.44</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="B24" s="99" t="n">
-        <v>10.62</v>
+        <v>9.82</v>
       </c>
       <c r="C24" s="99" t="n">
         <v>10.62</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B25" s="99" t="n">
-        <v>22.27</v>
+        <v>23.93</v>
       </c>
       <c r="C25" s="99" t="n">
         <v>22.27</v>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="B26" s="99" t="n">
-        <v>22.27</v>
+        <v>23.93</v>
       </c>
       <c r="C26" s="99" t="n">
         <v>22.27</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B28" s="99" t="n">
-        <v>7.15</v>
+        <v>7.39</v>
       </c>
       <c r="C28" s="99" t="n">
         <v>7.15</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="B29" s="99" t="n">
-        <v>9.609999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C29" s="99" t="n">
         <v>9.609999999999999</v>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="B30" s="99" t="n">
-        <v>45.5</v>
+        <v>52.09</v>
       </c>
       <c r="C30" s="99" t="n">
         <v>45.5</v>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="B31" s="99" t="n">
-        <v>57.59</v>
+        <v>60.09</v>
       </c>
       <c r="C31" s="99" t="n">
         <v>57.59</v>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="B33" s="99" t="n">
-        <v>-2.68</v>
+        <v>-2.74</v>
       </c>
       <c r="C33" s="99" t="n">
         <v>-2.68</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="B34" s="99" t="n">
-        <v>10.76</v>
+        <v>9.02</v>
       </c>
       <c r="C34" s="99" t="n">
         <v>10.76</v>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="B35" s="99" t="n">
-        <v>15.42</v>
+        <v>21.97</v>
       </c>
       <c r="C35" s="99" t="n">
         <v>15.42</v>
@@ -10232,7 +10232,7 @@
         </is>
       </c>
       <c r="B36" s="99" t="n">
-        <v>15.42</v>
+        <v>21.97</v>
       </c>
       <c r="C36" s="99" t="n">
         <v>15.42</v>
@@ -11963,9 +11963,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B52" s="98" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C52" s="98" t="inlineStr">
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="C53" s="99" t="n">
         <v>0.87</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
-        <v>-4.2</v>
+        <v>-4.48</v>
       </c>
       <c r="C54" s="99" t="n">
         <v>-5.85</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
-        <v>42.33</v>
+        <v>35.7</v>
       </c>
       <c r="C55" s="99" t="n">
         <v>34.48</v>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
-        <v>48.64</v>
+        <v>45.48</v>
       </c>
       <c r="C56" s="99" t="n">
         <v>44.93</v>
@@ -12666,7 +12666,7 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>4.47</v>
+        <v>4.03</v>
       </c>
       <c r="C58" s="99" t="n">
         <v>5.36</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
-        <v>8.24</v>
+        <v>7.78</v>
       </c>
       <c r="C59" s="99" t="n">
         <v>6.58</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>57.19</v>
+        <v>49.48</v>
       </c>
       <c r="C60" s="99" t="n">
         <v>55.81</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>60.53</v>
+        <v>55.46</v>
       </c>
       <c r="C61" s="99" t="n">
         <v>59.76</v>
@@ -13050,7 +13050,7 @@
     <row r="63">
       <c r="A63" s="95" t="inlineStr">
         <is>
-          <t>今日买报：us500:RSI2:22.27&lt;=28;ixic:RSI2:15.42&lt;=36;ixic:RSI2:15.42&lt;=35</t>
+          <t>今日买报：us500:RSI2:23.93&lt;=28;ixic:RSI2:21.97&lt;=36;ixic:RSI2:21.97&lt;=35</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -6358,152 +6358,152 @@
       </c>
       <c r="B1" s="81" t="inlineStr">
         <is>
+          <t>241003</t>
+        </is>
+      </c>
+      <c r="C1" s="81" t="inlineStr">
+        <is>
           <t>241002</t>
         </is>
       </c>
-      <c r="C1" s="81" t="inlineStr">
+      <c r="D1" s="81" t="inlineStr">
         <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="D1" s="81" t="inlineStr">
+      <c r="E1" s="81" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="E1" s="81" t="inlineStr">
+      <c r="F1" s="81" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="F1" s="81" t="inlineStr">
+      <c r="G1" s="81" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="G1" s="81" t="inlineStr">
+      <c r="H1" s="81" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="H1" s="81" t="inlineStr">
+      <c r="I1" s="81" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="I1" s="81" t="inlineStr">
+      <c r="J1" s="81" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="J1" s="81" t="inlineStr">
+      <c r="K1" s="81" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="K1" s="81" t="inlineStr">
+      <c r="L1" s="81" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="L1" s="81" t="inlineStr">
+      <c r="M1" s="81" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="N1" s="81" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="O1" s="81" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="P1" s="81" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="Q1" s="81" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="R1" s="81" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="S1" s="81" t="inlineStr">
+      <c r="T1" s="81" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="T1" s="81" t="inlineStr">
+      <c r="U1" s="81" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="U1" s="81" t="inlineStr">
+      <c r="V1" s="81" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="V1" s="81" t="inlineStr">
+      <c r="W1" s="81" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="W1" s="81" t="inlineStr">
+      <c r="X1" s="81" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="X1" s="81" t="inlineStr">
+      <c r="Y1" s="81" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="Y1" s="81" t="inlineStr">
+      <c r="Z1" s="81" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="Z1" s="81" t="inlineStr">
+      <c r="AA1" s="81" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="AA1" s="81" t="inlineStr">
+      <c r="AB1" s="81" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="AB1" s="81" t="inlineStr">
+      <c r="AC1" s="81" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="AC1" s="81" t="inlineStr">
+      <c r="AD1" s="81" t="inlineStr">
         <is>
           <t>240826</t>
         </is>
       </c>
-      <c r="AD1" s="81" t="inlineStr">
+      <c r="AE1" s="81" t="inlineStr">
         <is>
           <t>240823</t>
-        </is>
-      </c>
-      <c r="AE1" s="81" t="inlineStr">
-        <is>
-          <t>240822</t>
         </is>
       </c>
     </row>
@@ -6548,114 +6548,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I2" s="97" t="inlineStr">
+      <c r="I2" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="97" t="inlineStr">
+      <c r="K2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="97" t="inlineStr">
+      <c r="L2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="97" t="inlineStr">
+      <c r="M2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="98" t="inlineStr">
+      <c r="N2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="98" t="inlineStr">
+      <c r="O2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="98" t="inlineStr">
+      <c r="P2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="98" t="inlineStr">
+      <c r="Q2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="98" t="inlineStr">
+      <c r="R2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="98" t="inlineStr">
+      <c r="S2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="98" t="inlineStr">
+      <c r="T2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="98" t="inlineStr">
+      <c r="U2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="98" t="inlineStr">
+      <c r="V2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="98" t="inlineStr">
+      <c r="W2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="98" t="inlineStr">
+      <c r="X2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="98" t="inlineStr">
+      <c r="Y2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="97" t="inlineStr">
+      <c r="Z2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z2" s="98" t="inlineStr">
+      <c r="AA2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="98" t="inlineStr">
+      <c r="AB2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB2" s="98" t="inlineStr">
+      <c r="AC2" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="97" t="inlineStr">
+      <c r="AD2" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD2" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE2" s="98" t="inlineStr">
@@ -6680,31 +6680,31 @@
         <v>12.81</v>
       </c>
       <c r="E3" s="99" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="F3" s="99" t="n">
         <v>3.53</v>
       </c>
-      <c r="F3" s="99" t="n">
+      <c r="G3" s="99" t="n">
         <v>0.13</v>
       </c>
-      <c r="G3" s="99" t="n">
+      <c r="H3" s="99" t="n">
         <v>-3.29</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="I3" s="99" t="n">
         <v>-3.51</v>
       </c>
-      <c r="I3" s="99" t="n">
+      <c r="J3" s="99" t="n">
         <v>-6.68</v>
       </c>
-      <c r="J3" s="99" t="n">
+      <c r="K3" s="99" t="n">
         <v>-7.93</v>
       </c>
-      <c r="K3" s="99" t="n">
+      <c r="L3" s="99" t="n">
         <v>-7.25</v>
       </c>
-      <c r="L3" s="99" t="n">
+      <c r="M3" s="99" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="M3" s="99" t="n">
-        <v>-9.81</v>
       </c>
       <c r="N3" s="99" t="n">
         <v>-9.81</v>
@@ -6713,52 +6713,52 @@
         <v>-9.81</v>
       </c>
       <c r="P3" s="99" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="Q3" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="Q3" s="99" t="n">
+      <c r="R3" s="99" t="n">
         <v>-9.82</v>
       </c>
-      <c r="R3" s="99" t="n">
+      <c r="S3" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="S3" s="99" t="n">
+      <c r="T3" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="T3" s="99" t="n">
+      <c r="U3" s="99" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="U3" s="99" t="n">
+      <c r="V3" s="99" t="n">
         <v>-7.94</v>
       </c>
-      <c r="V3" s="99" t="n">
+      <c r="W3" s="99" t="n">
         <v>-8.34</v>
       </c>
-      <c r="W3" s="99" t="n">
+      <c r="X3" s="99" t="n">
         <v>-7.43</v>
       </c>
-      <c r="X3" s="99" t="n">
+      <c r="Y3" s="99" t="n">
         <v>-7.87</v>
       </c>
-      <c r="Y3" s="99" t="n">
+      <c r="Z3" s="99" t="n">
         <v>-6.78</v>
       </c>
-      <c r="Z3" s="99" t="n">
+      <c r="AA3" s="99" t="n">
         <v>-7.9</v>
       </c>
-      <c r="AA3" s="99" t="n">
+      <c r="AB3" s="99" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="AB3" s="99" t="n">
+      <c r="AC3" s="99" t="n">
         <v>-7.46</v>
       </c>
-      <c r="AC3" s="99" t="n">
+      <c r="AD3" s="99" t="n">
         <v>-7.49</v>
       </c>
-      <c r="AD3" s="99" t="n">
+      <c r="AE3" s="99" t="n">
         <v>-7.68</v>
-      </c>
-      <c r="AE3" s="99" t="n">
-        <v>-8.43</v>
       </c>
     </row>
     <row r="4">
@@ -6777,31 +6777,31 @@
         <v>8.710000000000001</v>
       </c>
       <c r="E4" s="99" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="F4" s="99" t="n">
         <v>0.41</v>
       </c>
-      <c r="F4" s="99" t="n">
+      <c r="G4" s="99" t="n">
         <v>-2.48</v>
       </c>
-      <c r="G4" s="99" t="n">
+      <c r="H4" s="99" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="I4" s="99" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I4" s="99" t="n">
+      <c r="J4" s="99" t="n">
         <v>-8.16</v>
       </c>
-      <c r="J4" s="99" t="n">
+      <c r="K4" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="K4" s="99" t="n">
+      <c r="L4" s="99" t="n">
         <v>-9.59</v>
       </c>
-      <c r="L4" s="99" t="n">
+      <c r="M4" s="99" t="n">
         <v>-10.85</v>
-      </c>
-      <c r="M4" s="99" t="n">
-        <v>-12.12</v>
       </c>
       <c r="N4" s="99" t="n">
         <v>-12.12</v>
@@ -6810,52 +6810,52 @@
         <v>-12.12</v>
       </c>
       <c r="P4" s="99" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="Q4" s="99" t="n">
         <v>-11.77</v>
       </c>
-      <c r="Q4" s="99" t="n">
+      <c r="R4" s="99" t="n">
         <v>-11.13</v>
       </c>
-      <c r="R4" s="99" t="n">
+      <c r="S4" s="99" t="n">
         <v>-11.05</v>
       </c>
-      <c r="S4" s="99" t="n">
+      <c r="T4" s="99" t="n">
         <v>-10.42</v>
       </c>
-      <c r="T4" s="99" t="n">
+      <c r="U4" s="99" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="U4" s="99" t="n">
+      <c r="V4" s="99" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="V4" s="99" t="n">
+      <c r="W4" s="99" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="W4" s="99" t="n">
+      <c r="X4" s="99" t="n">
         <v>-8.65</v>
       </c>
-      <c r="X4" s="99" t="n">
+      <c r="Y4" s="99" t="n">
         <v>-7.71</v>
       </c>
-      <c r="Y4" s="99" t="n">
+      <c r="Z4" s="99" t="n">
         <v>-6.12</v>
       </c>
-      <c r="Z4" s="99" t="n">
+      <c r="AA4" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="AA4" s="99" t="n">
+      <c r="AB4" s="99" t="n">
         <v>-6.9</v>
       </c>
-      <c r="AB4" s="99" t="n">
+      <c r="AC4" s="99" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AC4" s="99" t="n">
+      <c r="AD4" s="99" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AD4" s="99" t="n">
+      <c r="AE4" s="99" t="n">
         <v>-5.33</v>
-      </c>
-      <c r="AE4" s="99" t="n">
-        <v>-3.69</v>
       </c>
     </row>
     <row r="5">
@@ -6874,31 +6874,31 @@
         <v>91.05</v>
       </c>
       <c r="E5" s="99" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="F5" s="99" t="n">
         <v>84.84</v>
       </c>
-      <c r="F5" s="99" t="n">
+      <c r="G5" s="99" t="n">
         <v>80.58</v>
       </c>
-      <c r="G5" s="99" t="n">
+      <c r="H5" s="99" t="n">
         <v>71.91</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="I5" s="99" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="I5" s="99" t="n">
+      <c r="J5" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="J5" s="99" t="n">
+      <c r="K5" s="99" t="n">
         <v>34.66</v>
       </c>
-      <c r="K5" s="99" t="n">
+      <c r="L5" s="99" t="n">
         <v>34.31</v>
       </c>
-      <c r="L5" s="99" t="n">
+      <c r="M5" s="99" t="n">
         <v>25.68</v>
-      </c>
-      <c r="M5" s="99" t="n">
-        <v>18.87</v>
       </c>
       <c r="N5" s="99" t="n">
         <v>18.87</v>
@@ -6907,52 +6907,52 @@
         <v>18.87</v>
       </c>
       <c r="P5" s="99" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="Q5" s="99" t="n">
         <v>20.56</v>
       </c>
-      <c r="Q5" s="99" t="n">
+      <c r="R5" s="99" t="n">
         <v>21.18</v>
       </c>
-      <c r="R5" s="99" t="n">
+      <c r="S5" s="99" t="n">
         <v>24.39</v>
       </c>
-      <c r="S5" s="99" t="n">
+      <c r="T5" s="99" t="n">
         <v>20.64</v>
       </c>
-      <c r="T5" s="99" t="n">
+      <c r="U5" s="99" t="n">
         <v>24.91</v>
       </c>
-      <c r="U5" s="99" t="n">
+      <c r="V5" s="99" t="n">
         <v>29.13</v>
       </c>
-      <c r="V5" s="99" t="n">
+      <c r="W5" s="99" t="n">
         <v>27.12</v>
       </c>
-      <c r="W5" s="99" t="n">
+      <c r="X5" s="99" t="n">
         <v>30.8</v>
       </c>
-      <c r="X5" s="99" t="n">
+      <c r="Y5" s="99" t="n">
         <v>32.53</v>
       </c>
-      <c r="Y5" s="99" t="n">
+      <c r="Z5" s="99" t="n">
         <v>40.52</v>
       </c>
-      <c r="Z5" s="99" t="n">
+      <c r="AA5" s="99" t="n">
         <v>31.09</v>
       </c>
-      <c r="AA5" s="99" t="n">
+      <c r="AB5" s="99" t="n">
         <v>34.85</v>
       </c>
-      <c r="AB5" s="99" t="n">
+      <c r="AC5" s="99" t="n">
         <v>38.18</v>
       </c>
-      <c r="AC5" s="99" t="n">
+      <c r="AD5" s="99" t="n">
         <v>40.27</v>
       </c>
-      <c r="AD5" s="99" t="n">
+      <c r="AE5" s="99" t="n">
         <v>39.76</v>
-      </c>
-      <c r="AE5" s="99" t="n">
-        <v>37.4</v>
       </c>
     </row>
     <row r="6">
@@ -6971,31 +6971,31 @@
         <v>99.98999999999999</v>
       </c>
       <c r="E6" s="99" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F6" s="99" t="n">
         <v>99.94</v>
       </c>
-      <c r="F6" s="99" t="n">
+      <c r="G6" s="99" t="n">
         <v>99.88</v>
       </c>
-      <c r="G6" s="99" t="n">
+      <c r="H6" s="99" t="n">
         <v>99.61</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="I6" s="99" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="I6" s="99" t="n">
+      <c r="J6" s="99" t="n">
         <v>92.72</v>
       </c>
-      <c r="J6" s="99" t="n">
+      <c r="K6" s="99" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="K6" s="99" t="n">
+      <c r="L6" s="99" t="n">
         <v>81.17</v>
       </c>
-      <c r="L6" s="99" t="n">
+      <c r="M6" s="99" t="n">
         <v>53.59</v>
-      </c>
-      <c r="M6" s="99" t="n">
-        <v>4.21</v>
       </c>
       <c r="N6" s="99" t="n">
         <v>4.21</v>
@@ -7004,52 +7004,52 @@
         <v>4.21</v>
       </c>
       <c r="P6" s="99" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Q6" s="99" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="Q6" s="99" t="n">
+      <c r="R6" s="99" t="n">
         <v>11.08</v>
       </c>
-      <c r="R6" s="99" t="n">
+      <c r="S6" s="99" t="n">
         <v>27.27</v>
       </c>
-      <c r="S6" s="99" t="n">
+      <c r="T6" s="99" t="n">
         <v>2.86</v>
       </c>
-      <c r="T6" s="99" t="n">
+      <c r="U6" s="99" t="n">
         <v>7.92</v>
       </c>
-      <c r="U6" s="99" t="n">
+      <c r="V6" s="99" t="n">
         <v>24.73</v>
       </c>
-      <c r="V6" s="99" t="n">
+      <c r="W6" s="99" t="n">
         <v>7.06</v>
       </c>
-      <c r="W6" s="99" t="n">
+      <c r="X6" s="99" t="n">
         <v>15.5</v>
       </c>
-      <c r="X6" s="99" t="n">
+      <c r="Y6" s="99" t="n">
         <v>20.88</v>
       </c>
-      <c r="Y6" s="99" t="n">
+      <c r="Z6" s="99" t="n">
         <v>63.5</v>
       </c>
-      <c r="Z6" s="99" t="n">
+      <c r="AA6" s="99" t="n">
         <v>2.54</v>
       </c>
-      <c r="AA6" s="99" t="n">
+      <c r="AB6" s="99" t="n">
         <v>6.81</v>
       </c>
-      <c r="AB6" s="99" t="n">
+      <c r="AC6" s="99" t="n">
         <v>20.06</v>
       </c>
-      <c r="AC6" s="99" t="n">
+      <c r="AD6" s="99" t="n">
         <v>48.33</v>
       </c>
-      <c r="AD6" s="99" t="n">
+      <c r="AE6" s="99" t="n">
         <v>41.33</v>
-      </c>
-      <c r="AE6" s="99" t="n">
-        <v>12.42</v>
       </c>
     </row>
     <row r="7">
@@ -7093,99 +7093,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I7" s="98" t="inlineStr">
+      <c r="I7" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J7" s="97" t="inlineStr">
+      <c r="K7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K7" s="97" t="inlineStr">
+      <c r="L7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L7" s="98" t="inlineStr">
+      <c r="M7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M7" s="97" t="inlineStr">
+      <c r="N7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N7" s="97" t="inlineStr">
+      <c r="O7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="97" t="inlineStr">
+      <c r="P7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P7" s="97" t="inlineStr">
+      <c r="Q7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q7" s="97" t="inlineStr">
+      <c r="R7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R7" s="97" t="inlineStr">
+      <c r="S7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S7" s="98" t="inlineStr">
+      <c r="T7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T7" s="98" t="inlineStr">
+      <c r="U7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U7" s="97" t="inlineStr">
+      <c r="V7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V7" s="97" t="inlineStr">
+      <c r="W7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W7" s="97" t="inlineStr">
+      <c r="X7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X7" s="98" t="inlineStr">
+      <c r="Y7" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y7" s="96" t="inlineStr">
+      <c r="Z7" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z7" s="97" t="inlineStr">
+      <c r="AA7" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AA7" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AB7" s="98" t="inlineStr">
@@ -7225,31 +7225,31 @@
         <v>26.36</v>
       </c>
       <c r="E8" s="99" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="F8" s="99" t="n">
         <v>5.45</v>
       </c>
-      <c r="F8" s="99" t="n">
+      <c r="G8" s="99" t="n">
         <v>-0.85</v>
       </c>
-      <c r="G8" s="99" t="n">
+      <c r="H8" s="99" t="n">
         <v>-5.96</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="I8" s="99" t="n">
         <v>-6.32</v>
       </c>
-      <c r="I8" s="99" t="n">
+      <c r="J8" s="99" t="n">
         <v>-10.11</v>
       </c>
-      <c r="J8" s="99" t="n">
+      <c r="K8" s="99" t="n">
         <v>-11.14</v>
       </c>
-      <c r="K8" s="99" t="n">
+      <c r="L8" s="99" t="n">
         <v>-9.23</v>
       </c>
-      <c r="L8" s="99" t="n">
+      <c r="M8" s="99" t="n">
         <v>-12.41</v>
-      </c>
-      <c r="M8" s="99" t="n">
-        <v>-13.62</v>
       </c>
       <c r="N8" s="99" t="n">
         <v>-13.62</v>
@@ -7258,52 +7258,52 @@
         <v>-13.62</v>
       </c>
       <c r="P8" s="99" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="Q8" s="99" t="n">
         <v>-12.75</v>
       </c>
-      <c r="Q8" s="99" t="n">
+      <c r="R8" s="99" t="n">
         <v>-11.62</v>
       </c>
-      <c r="R8" s="99" t="n">
+      <c r="S8" s="99" t="n">
         <v>-12.8</v>
       </c>
-      <c r="S8" s="99" t="n">
+      <c r="T8" s="99" t="n">
         <v>-13.49</v>
       </c>
-      <c r="T8" s="99" t="n">
+      <c r="U8" s="99" t="n">
         <v>-12.19</v>
       </c>
-      <c r="U8" s="99" t="n">
+      <c r="V8" s="99" t="n">
         <v>-11.56</v>
       </c>
-      <c r="V8" s="99" t="n">
+      <c r="W8" s="99" t="n">
         <v>-10.95</v>
       </c>
-      <c r="W8" s="99" t="n">
+      <c r="X8" s="99" t="n">
         <v>-10.7</v>
       </c>
-      <c r="X8" s="99" t="n">
+      <c r="Y8" s="99" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="Y8" s="99" t="n">
+      <c r="Z8" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="Z8" s="99" t="n">
+      <c r="AA8" s="99" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="AA8" s="99" t="n">
+      <c r="AB8" s="99" t="n">
         <v>-10.94</v>
       </c>
-      <c r="AB8" s="99" t="n">
+      <c r="AC8" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AC8" s="99" t="n">
+      <c r="AD8" s="99" t="n">
         <v>-8.17</v>
       </c>
-      <c r="AD8" s="99" t="n">
+      <c r="AE8" s="99" t="n">
         <v>-7.67</v>
-      </c>
-      <c r="AE8" s="99" t="n">
-        <v>-6.65</v>
       </c>
     </row>
     <row r="9">
@@ -7322,31 +7322,31 @@
         <v>15.28</v>
       </c>
       <c r="E9" s="99" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="F9" s="99" t="n">
         <v>-3.74</v>
       </c>
-      <c r="F9" s="99" t="n">
+      <c r="G9" s="99" t="n">
         <v>-10.62</v>
       </c>
-      <c r="G9" s="99" t="n">
+      <c r="H9" s="99" t="n">
         <v>-12.51</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="I9" s="99" t="n">
         <v>-12.61</v>
       </c>
-      <c r="I9" s="99" t="n">
+      <c r="J9" s="99" t="n">
         <v>-14.58</v>
       </c>
-      <c r="J9" s="99" t="n">
+      <c r="K9" s="99" t="n">
         <v>-16.03</v>
       </c>
-      <c r="K9" s="99" t="n">
+      <c r="L9" s="99" t="n">
         <v>-16.65</v>
       </c>
-      <c r="L9" s="99" t="n">
+      <c r="M9" s="99" t="n">
         <v>-18.48</v>
-      </c>
-      <c r="M9" s="99" t="n">
-        <v>-18.74</v>
       </c>
       <c r="N9" s="99" t="n">
         <v>-18.74</v>
@@ -7355,52 +7355,52 @@
         <v>-18.74</v>
       </c>
       <c r="P9" s="99" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="Q9" s="99" t="n">
         <v>-19.06</v>
       </c>
-      <c r="Q9" s="99" t="n">
+      <c r="R9" s="99" t="n">
         <v>-18.16</v>
       </c>
-      <c r="R9" s="99" t="n">
+      <c r="S9" s="99" t="n">
         <v>-20.04</v>
       </c>
-      <c r="S9" s="99" t="n">
+      <c r="T9" s="99" t="n">
         <v>-19.01</v>
       </c>
-      <c r="T9" s="99" t="n">
+      <c r="U9" s="99" t="n">
         <v>-17.71</v>
       </c>
-      <c r="U9" s="99" t="n">
+      <c r="V9" s="99" t="n">
         <v>-17.63</v>
       </c>
-      <c r="V9" s="99" t="n">
+      <c r="W9" s="99" t="n">
         <v>-17.79</v>
       </c>
-      <c r="W9" s="99" t="n">
+      <c r="X9" s="99" t="n">
         <v>-17.53</v>
       </c>
-      <c r="X9" s="99" t="n">
+      <c r="Y9" s="99" t="n">
         <v>-16.58</v>
       </c>
-      <c r="Y9" s="99" t="n">
+      <c r="Z9" s="99" t="n">
         <v>-12.6</v>
       </c>
-      <c r="Z9" s="99" t="n">
+      <c r="AA9" s="99" t="n">
         <v>-16.3</v>
       </c>
-      <c r="AA9" s="99" t="n">
+      <c r="AB9" s="99" t="n">
         <v>-17.92</v>
       </c>
-      <c r="AB9" s="99" t="n">
+      <c r="AC9" s="99" t="n">
         <v>-17.61</v>
       </c>
-      <c r="AC9" s="99" t="n">
+      <c r="AD9" s="99" t="n">
         <v>-16.31</v>
       </c>
-      <c r="AD9" s="99" t="n">
+      <c r="AE9" s="99" t="n">
         <v>-15.1</v>
-      </c>
-      <c r="AE9" s="99" t="n">
-        <v>-11.15</v>
       </c>
     </row>
     <row r="10">
@@ -7419,31 +7419,31 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E10" s="99" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F10" s="99" t="n">
         <v>78.56</v>
       </c>
-      <c r="F10" s="99" t="n">
+      <c r="G10" s="99" t="n">
         <v>65.87</v>
       </c>
-      <c r="G10" s="99" t="n">
+      <c r="H10" s="99" t="n">
         <v>51.71</v>
       </c>
-      <c r="H10" s="99" t="n">
+      <c r="I10" s="99" t="n">
         <v>51.51</v>
       </c>
-      <c r="I10" s="99" t="n">
+      <c r="J10" s="99" t="n">
         <v>29.32</v>
       </c>
-      <c r="J10" s="99" t="n">
+      <c r="K10" s="99" t="n">
         <v>32.26</v>
       </c>
-      <c r="K10" s="99" t="n">
+      <c r="L10" s="99" t="n">
         <v>34.06</v>
       </c>
-      <c r="L10" s="99" t="n">
+      <c r="M10" s="99" t="n">
         <v>29.44</v>
-      </c>
-      <c r="M10" s="99" t="n">
-        <v>33.41</v>
       </c>
       <c r="N10" s="99" t="n">
         <v>33.41</v>
@@ -7452,52 +7452,52 @@
         <v>33.41</v>
       </c>
       <c r="P10" s="99" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="Q10" s="99" t="n">
         <v>35.55</v>
       </c>
-      <c r="Q10" s="99" t="n">
+      <c r="R10" s="99" t="n">
         <v>38.79</v>
       </c>
-      <c r="R10" s="99" t="n">
+      <c r="S10" s="99" t="n">
         <v>34.56</v>
       </c>
-      <c r="S10" s="99" t="n">
+      <c r="T10" s="99" t="n">
         <v>29.42</v>
       </c>
-      <c r="T10" s="99" t="n">
+      <c r="U10" s="99" t="n">
         <v>32.81</v>
       </c>
-      <c r="U10" s="99" t="n">
+      <c r="V10" s="99" t="n">
         <v>37.49</v>
       </c>
-      <c r="V10" s="99" t="n">
+      <c r="W10" s="99" t="n">
         <v>38.05</v>
       </c>
-      <c r="W10" s="99" t="n">
+      <c r="X10" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="X10" s="99" t="n">
+      <c r="Y10" s="99" t="n">
         <v>35.52</v>
       </c>
-      <c r="Y10" s="99" t="n">
+      <c r="Z10" s="99" t="n">
         <v>49.6</v>
       </c>
-      <c r="Z10" s="99" t="n">
+      <c r="AA10" s="99" t="n">
         <v>35.78</v>
       </c>
-      <c r="AA10" s="99" t="n">
+      <c r="AB10" s="99" t="n">
         <v>25.18</v>
       </c>
-      <c r="AB10" s="99" t="n">
+      <c r="AC10" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AC10" s="99" t="n">
+      <c r="AD10" s="99" t="n">
         <v>30.93</v>
       </c>
-      <c r="AD10" s="99" t="n">
+      <c r="AE10" s="99" t="n">
         <v>32.82</v>
-      </c>
-      <c r="AE10" s="99" t="n">
-        <v>32.56</v>
       </c>
     </row>
     <row r="11">
@@ -7516,31 +7516,31 @@
         <v>96.84</v>
       </c>
       <c r="E11" s="99" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="F11" s="99" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="F11" s="99" t="n">
+      <c r="G11" s="99" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="G11" s="99" t="n">
+      <c r="H11" s="99" t="n">
         <v>64.94</v>
       </c>
-      <c r="H11" s="99" t="n">
+      <c r="I11" s="99" t="n">
         <v>64.66</v>
       </c>
-      <c r="I11" s="99" t="n">
+      <c r="J11" s="99" t="n">
         <v>23.69</v>
       </c>
-      <c r="J11" s="99" t="n">
+      <c r="K11" s="99" t="n">
         <v>29.81</v>
       </c>
-      <c r="K11" s="99" t="n">
+      <c r="L11" s="99" t="n">
         <v>33.91</v>
       </c>
-      <c r="L11" s="99" t="n">
+      <c r="M11" s="99" t="n">
         <v>22.82</v>
-      </c>
-      <c r="M11" s="99" t="n">
-        <v>30.54</v>
       </c>
       <c r="N11" s="99" t="n">
         <v>30.54</v>
@@ -7549,52 +7549,52 @@
         <v>30.54</v>
       </c>
       <c r="P11" s="99" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="Q11" s="99" t="n">
         <v>35.28</v>
       </c>
-      <c r="Q11" s="99" t="n">
+      <c r="R11" s="99" t="n">
         <v>42.99</v>
       </c>
-      <c r="R11" s="99" t="n">
+      <c r="S11" s="99" t="n">
         <v>33.88</v>
       </c>
-      <c r="S11" s="99" t="n">
+      <c r="T11" s="99" t="n">
         <v>22.22</v>
       </c>
-      <c r="T11" s="99" t="n">
+      <c r="U11" s="99" t="n">
         <v>27.98</v>
       </c>
-      <c r="U11" s="99" t="n">
+      <c r="V11" s="99" t="n">
         <v>37.32</v>
       </c>
-      <c r="V11" s="99" t="n">
+      <c r="W11" s="99" t="n">
         <v>38.49</v>
       </c>
-      <c r="W11" s="99" t="n">
+      <c r="X11" s="99" t="n">
         <v>41.22</v>
       </c>
-      <c r="X11" s="99" t="n">
+      <c r="Y11" s="99" t="n">
         <v>34.35</v>
       </c>
-      <c r="Y11" s="99" t="n">
+      <c r="Z11" s="99" t="n">
         <v>63.18</v>
       </c>
-      <c r="Z11" s="99" t="n">
+      <c r="AA11" s="99" t="n">
         <v>38.1</v>
       </c>
-      <c r="AA11" s="99" t="n">
+      <c r="AB11" s="99" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AB11" s="99" t="n">
+      <c r="AC11" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="AC11" s="99" t="n">
+      <c r="AD11" s="99" t="n">
         <v>17.04</v>
       </c>
-      <c r="AD11" s="99" t="n">
+      <c r="AE11" s="99" t="n">
         <v>20.21</v>
-      </c>
-      <c r="AE11" s="99" t="n">
-        <v>19.37</v>
       </c>
     </row>
     <row r="12">
@@ -7638,114 +7638,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I12" s="98" t="inlineStr">
+      <c r="I12" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J12" s="98" t="inlineStr">
+      <c r="K12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K12" s="97" t="inlineStr">
+      <c r="L12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L12" s="98" t="inlineStr">
+      <c r="M12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="98" t="inlineStr">
+      <c r="N12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="98" t="inlineStr">
+      <c r="O12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O12" s="98" t="inlineStr">
+      <c r="P12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P12" s="97" t="inlineStr">
+      <c r="Q12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q12" s="96" t="inlineStr">
+      <c r="R12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R12" s="98" t="inlineStr">
+      <c r="S12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S12" s="98" t="inlineStr">
+      <c r="T12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T12" s="98" t="inlineStr">
+      <c r="U12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U12" s="96" t="inlineStr">
+      <c r="V12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V12" s="97" t="inlineStr">
+      <c r="W12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W12" s="97" t="inlineStr">
+      <c r="X12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X12" s="98" t="inlineStr">
+      <c r="Y12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y12" s="96" t="inlineStr">
+      <c r="Z12" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z12" s="97" t="inlineStr">
+      <c r="AA12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA12" s="97" t="inlineStr">
+      <c r="AB12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB12" s="98" t="inlineStr">
+      <c r="AC12" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC12" s="97" t="inlineStr">
+      <c r="AD12" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD12" s="98" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE12" s="98" t="inlineStr">
@@ -7770,31 +7770,31 @@
         <v>32.05</v>
       </c>
       <c r="E13" s="99" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F13" s="99" t="n">
         <v>13.58</v>
       </c>
-      <c r="F13" s="99" t="n">
+      <c r="G13" s="99" t="n">
         <v>2.95</v>
       </c>
-      <c r="G13" s="99" t="n">
+      <c r="H13" s="99" t="n">
         <v>-2.45</v>
       </c>
-      <c r="H13" s="99" t="n">
+      <c r="I13" s="99" t="n">
         <v>-4.05</v>
       </c>
-      <c r="I13" s="99" t="n">
+      <c r="J13" s="99" t="n">
         <v>-10.14</v>
       </c>
-      <c r="J13" s="99" t="n">
+      <c r="K13" s="99" t="n">
         <v>-11.21</v>
       </c>
-      <c r="K13" s="99" t="n">
+      <c r="L13" s="99" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="L13" s="99" t="n">
+      <c r="M13" s="99" t="n">
         <v>-11.44</v>
-      </c>
-      <c r="M13" s="99" t="n">
-        <v>-12.57</v>
       </c>
       <c r="N13" s="99" t="n">
         <v>-12.57</v>
@@ -7803,52 +7803,52 @@
         <v>-12.57</v>
       </c>
       <c r="P13" s="99" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="Q13" s="99" t="n">
         <v>-11.96</v>
       </c>
-      <c r="Q13" s="99" t="n">
+      <c r="R13" s="99" t="n">
         <v>-12.87</v>
       </c>
-      <c r="R13" s="99" t="n">
+      <c r="S13" s="99" t="n">
         <v>-14.98</v>
       </c>
-      <c r="S13" s="99" t="n">
+      <c r="T13" s="99" t="n">
         <v>-14.79</v>
       </c>
-      <c r="T13" s="99" t="n">
+      <c r="U13" s="99" t="n">
         <v>-14.14</v>
       </c>
-      <c r="U13" s="99" t="n">
+      <c r="V13" s="99" t="n">
         <v>-11.99</v>
       </c>
-      <c r="V13" s="99" t="n">
+      <c r="W13" s="99" t="n">
         <v>-12.63</v>
       </c>
-      <c r="W13" s="99" t="n">
+      <c r="X13" s="99" t="n">
         <v>-12.92</v>
       </c>
-      <c r="X13" s="99" t="n">
+      <c r="Y13" s="99" t="n">
         <v>-13.71</v>
       </c>
-      <c r="Y13" s="99" t="n">
+      <c r="Z13" s="99" t="n">
         <v>-13.18</v>
       </c>
-      <c r="Z13" s="99" t="n">
+      <c r="AA13" s="99" t="n">
         <v>-15.93</v>
       </c>
-      <c r="AA13" s="99" t="n">
+      <c r="AB13" s="99" t="n">
         <v>-16.93</v>
       </c>
-      <c r="AB13" s="99" t="n">
+      <c r="AC13" s="99" t="n">
         <v>-15.87</v>
       </c>
-      <c r="AC13" s="99" t="n">
+      <c r="AD13" s="99" t="n">
         <v>-14.39</v>
       </c>
-      <c r="AD13" s="99" t="n">
+      <c r="AE13" s="99" t="n">
         <v>-14.68</v>
-      </c>
-      <c r="AE13" s="99" t="n">
-        <v>-14.6</v>
       </c>
     </row>
     <row r="14">
@@ -7867,31 +7867,31 @@
         <v>18.19</v>
       </c>
       <c r="E14" s="99" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="F14" s="99" t="n">
         <v>1.34</v>
       </c>
-      <c r="F14" s="99" t="n">
+      <c r="G14" s="99" t="n">
         <v>-8.44</v>
       </c>
-      <c r="G14" s="99" t="n">
+      <c r="H14" s="99" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="H14" s="99" t="n">
+      <c r="I14" s="99" t="n">
         <v>-10.6</v>
       </c>
-      <c r="I14" s="99" t="n">
+      <c r="J14" s="99" t="n">
         <v>-14.49</v>
       </c>
-      <c r="J14" s="99" t="n">
+      <c r="K14" s="99" t="n">
         <v>-16.56</v>
       </c>
-      <c r="K14" s="99" t="n">
+      <c r="L14" s="99" t="n">
         <v>-15.65</v>
       </c>
-      <c r="L14" s="99" t="n">
+      <c r="M14" s="99" t="n">
         <v>-17.96</v>
-      </c>
-      <c r="M14" s="99" t="n">
-        <v>-19.08</v>
       </c>
       <c r="N14" s="99" t="n">
         <v>-19.08</v>
@@ -7900,52 +7900,52 @@
         <v>-19.08</v>
       </c>
       <c r="P14" s="99" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="Q14" s="99" t="n">
         <v>-18.72</v>
       </c>
-      <c r="Q14" s="99" t="n">
+      <c r="R14" s="99" t="n">
         <v>-18.28</v>
       </c>
-      <c r="R14" s="99" t="n">
+      <c r="S14" s="99" t="n">
         <v>-20.06</v>
       </c>
-      <c r="S14" s="99" t="n">
+      <c r="T14" s="99" t="n">
         <v>-18.31</v>
       </c>
-      <c r="T14" s="99" t="n">
+      <c r="U14" s="99" t="n">
         <v>-18.32</v>
       </c>
-      <c r="U14" s="99" t="n">
+      <c r="V14" s="99" t="n">
         <v>-17.44</v>
       </c>
-      <c r="V14" s="99" t="n">
+      <c r="W14" s="99" t="n">
         <v>-18.44</v>
       </c>
-      <c r="W14" s="99" t="n">
+      <c r="X14" s="99" t="n">
         <v>-17.67</v>
       </c>
-      <c r="X14" s="99" t="n">
+      <c r="Y14" s="99" t="n">
         <v>-14.96</v>
       </c>
-      <c r="Y14" s="99" t="n">
+      <c r="Z14" s="99" t="n">
         <v>-11.7</v>
       </c>
-      <c r="Z14" s="99" t="n">
+      <c r="AA14" s="99" t="n">
         <v>-15.89</v>
       </c>
-      <c r="AA14" s="99" t="n">
+      <c r="AB14" s="99" t="n">
         <v>-16.48</v>
       </c>
-      <c r="AB14" s="99" t="n">
+      <c r="AC14" s="99" t="n">
         <v>-16.57</v>
       </c>
-      <c r="AC14" s="99" t="n">
+      <c r="AD14" s="99" t="n">
         <v>-15.28</v>
       </c>
-      <c r="AD14" s="99" t="n">
+      <c r="AE14" s="99" t="n">
         <v>-14.4</v>
-      </c>
-      <c r="AE14" s="99" t="n">
-        <v>-11.57</v>
       </c>
     </row>
     <row r="15">
@@ -7964,31 +7964,31 @@
         <v>93.78</v>
       </c>
       <c r="E15" s="99" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="F15" s="99" t="n">
         <v>88.70999999999999</v>
       </c>
-      <c r="F15" s="99" t="n">
+      <c r="G15" s="99" t="n">
         <v>80.03</v>
       </c>
-      <c r="G15" s="99" t="n">
+      <c r="H15" s="99" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="H15" s="99" t="n">
+      <c r="I15" s="99" t="n">
         <v>67.36</v>
       </c>
-      <c r="I15" s="99" t="n">
+      <c r="J15" s="99" t="n">
         <v>40.3</v>
       </c>
-      <c r="J15" s="99" t="n">
+      <c r="K15" s="99" t="n">
         <v>42.58</v>
       </c>
-      <c r="K15" s="99" t="n">
+      <c r="L15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="L15" s="99" t="n">
+      <c r="M15" s="99" t="n">
         <v>40.02</v>
-      </c>
-      <c r="M15" s="99" t="n">
-        <v>40.59</v>
       </c>
       <c r="N15" s="99" t="n">
         <v>40.59</v>
@@ -7997,52 +7997,52 @@
         <v>40.59</v>
       </c>
       <c r="P15" s="99" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="Q15" s="99" t="n">
         <v>46.42</v>
       </c>
-      <c r="Q15" s="99" t="n">
+      <c r="R15" s="99" t="n">
         <v>48.89</v>
       </c>
-      <c r="R15" s="99" t="n">
+      <c r="S15" s="99" t="n">
         <v>40.91</v>
       </c>
-      <c r="S15" s="99" t="n">
+      <c r="T15" s="99" t="n">
         <v>40.48</v>
       </c>
-      <c r="T15" s="99" t="n">
+      <c r="U15" s="99" t="n">
         <v>40.07</v>
       </c>
-      <c r="U15" s="99" t="n">
+      <c r="V15" s="99" t="n">
         <v>48.15</v>
       </c>
-      <c r="V15" s="99" t="n">
+      <c r="W15" s="99" t="n">
         <v>44.33</v>
       </c>
-      <c r="W15" s="99" t="n">
+      <c r="X15" s="99" t="n">
         <v>44.83</v>
       </c>
-      <c r="X15" s="99" t="n">
+      <c r="Y15" s="99" t="n">
         <v>37.59</v>
       </c>
-      <c r="Y15" s="99" t="n">
+      <c r="Z15" s="99" t="n">
         <v>51.16</v>
       </c>
-      <c r="Z15" s="99" t="n">
+      <c r="AA15" s="99" t="n">
         <v>31.05</v>
       </c>
-      <c r="AA15" s="99" t="n">
+      <c r="AB15" s="99" t="n">
         <v>23.87</v>
       </c>
-      <c r="AB15" s="99" t="n">
+      <c r="AC15" s="99" t="n">
         <v>23.35</v>
       </c>
-      <c r="AC15" s="99" t="n">
+      <c r="AD15" s="99" t="n">
         <v>26.67</v>
       </c>
-      <c r="AD15" s="99" t="n">
+      <c r="AE15" s="99" t="n">
         <v>27.05</v>
-      </c>
-      <c r="AE15" s="99" t="n">
-        <v>26.89</v>
       </c>
     </row>
     <row r="16">
@@ -8061,31 +8061,31 @@
         <v>94.69</v>
       </c>
       <c r="E16" s="99" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="F16" s="99" t="n">
         <v>90.12</v>
       </c>
-      <c r="F16" s="99" t="n">
+      <c r="G16" s="99" t="n">
         <v>81.95999999999999</v>
       </c>
-      <c r="G16" s="99" t="n">
+      <c r="H16" s="99" t="n">
         <v>73.8</v>
       </c>
-      <c r="H16" s="99" t="n">
+      <c r="I16" s="99" t="n">
         <v>69.36</v>
       </c>
-      <c r="I16" s="99" t="n">
+      <c r="J16" s="99" t="n">
         <v>40.16</v>
       </c>
-      <c r="J16" s="99" t="n">
+      <c r="K16" s="99" t="n">
         <v>42.76</v>
       </c>
-      <c r="K16" s="99" t="n">
+      <c r="L16" s="99" t="n">
         <v>47.16</v>
       </c>
-      <c r="L16" s="99" t="n">
+      <c r="M16" s="99" t="n">
         <v>39.93</v>
-      </c>
-      <c r="M16" s="99" t="n">
-        <v>40.57</v>
       </c>
       <c r="N16" s="99" t="n">
         <v>40.57</v>
@@ -8094,52 +8094,52 @@
         <v>40.57</v>
       </c>
       <c r="P16" s="99" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="Q16" s="99" t="n">
         <v>47.22</v>
       </c>
-      <c r="Q16" s="99" t="n">
+      <c r="R16" s="99" t="n">
         <v>50.08</v>
       </c>
-      <c r="R16" s="99" t="n">
+      <c r="S16" s="99" t="n">
         <v>41.17</v>
       </c>
-      <c r="S16" s="99" t="n">
+      <c r="T16" s="99" t="n">
         <v>40.69</v>
       </c>
-      <c r="T16" s="99" t="n">
+      <c r="U16" s="99" t="n">
         <v>40.24</v>
       </c>
-      <c r="U16" s="99" t="n">
+      <c r="V16" s="99" t="n">
         <v>49.36</v>
       </c>
-      <c r="V16" s="99" t="n">
+      <c r="W16" s="99" t="n">
         <v>45.18</v>
       </c>
-      <c r="W16" s="99" t="n">
+      <c r="X16" s="99" t="n">
         <v>45.74</v>
       </c>
-      <c r="X16" s="99" t="n">
+      <c r="Y16" s="99" t="n">
         <v>37.86</v>
       </c>
-      <c r="Y16" s="99" t="n">
+      <c r="Z16" s="99" t="n">
         <v>53.33</v>
       </c>
-      <c r="Z16" s="99" t="n">
+      <c r="AA16" s="99" t="n">
         <v>30.77</v>
       </c>
-      <c r="AA16" s="99" t="n">
+      <c r="AB16" s="99" t="n">
         <v>22.26</v>
       </c>
-      <c r="AB16" s="99" t="n">
+      <c r="AC16" s="99" t="n">
         <v>21.65</v>
       </c>
-      <c r="AC16" s="99" t="n">
+      <c r="AD16" s="99" t="n">
         <v>25.27</v>
       </c>
-      <c r="AD16" s="99" t="n">
+      <c r="AE16" s="99" t="n">
         <v>25.69</v>
-      </c>
-      <c r="AE16" s="99" t="n">
-        <v>25.5</v>
       </c>
     </row>
     <row r="17">
@@ -8213,89 +8213,89 @@
           <t>red</t>
         </is>
       </c>
-      <c r="O17" s="97" t="inlineStr">
+      <c r="O17" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="97" t="inlineStr">
+      <c r="Q17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q17" s="98" t="inlineStr">
+      <c r="R17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R17" s="98" t="inlineStr">
+      <c r="S17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S17" s="98" t="inlineStr">
+      <c r="T17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T17" s="98" t="inlineStr">
+      <c r="U17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U17" s="98" t="inlineStr">
+      <c r="V17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V17" s="98" t="inlineStr">
+      <c r="W17" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W17" s="97" t="inlineStr">
+      <c r="X17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X17" s="97" t="inlineStr">
+      <c r="Y17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y17" s="96" t="inlineStr">
+      <c r="Z17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z17" s="97" t="inlineStr">
+      <c r="AA17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA17" s="97" t="inlineStr">
+      <c r="AB17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB17" s="96" t="inlineStr">
+      <c r="AC17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC17" s="96" t="inlineStr">
+      <c r="AD17" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD17" s="97" t="inlineStr">
+      <c r="AE17" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE17" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8306,94 +8306,94 @@
         </is>
       </c>
       <c r="B18" s="99" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="C18" s="99" t="n">
         <v>26.09</v>
-      </c>
-      <c r="C18" s="99" t="n">
-        <v>17.23</v>
       </c>
       <c r="D18" s="99" t="n">
         <v>17.23</v>
       </c>
       <c r="E18" s="99" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="F18" s="99" t="n">
         <v>14.76</v>
       </c>
-      <c r="F18" s="99" t="n">
+      <c r="G18" s="99" t="n">
         <v>12.13</v>
       </c>
-      <c r="G18" s="99" t="n">
+      <c r="H18" s="99" t="n">
         <v>7.96</v>
       </c>
-      <c r="H18" s="99" t="n">
+      <c r="I18" s="99" t="n">
         <v>7.25</v>
       </c>
-      <c r="I18" s="99" t="n">
+      <c r="J18" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="J18" s="99" t="n">
+      <c r="K18" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="K18" s="99" t="n">
+      <c r="L18" s="99" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="L18" s="99" t="n">
-        <v>-2.04</v>
       </c>
       <c r="M18" s="99" t="n">
         <v>-2.04</v>
       </c>
       <c r="N18" s="99" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="O18" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="O18" s="99" t="n">
+      <c r="P18" s="99" t="n">
         <v>-5.76</v>
       </c>
-      <c r="P18" s="99" t="n">
+      <c r="Q18" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="Q18" s="99" t="n">
+      <c r="R18" s="99" t="n">
         <v>-4.61</v>
       </c>
-      <c r="R18" s="99" t="n">
+      <c r="S18" s="99" t="n">
         <v>-3.94</v>
       </c>
-      <c r="S18" s="99" t="n">
+      <c r="T18" s="99" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="T18" s="99" t="n">
-        <v>-2.75</v>
       </c>
       <c r="U18" s="99" t="n">
         <v>-2.75</v>
       </c>
       <c r="V18" s="99" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="W18" s="99" t="n">
         <v>-3.96</v>
       </c>
-      <c r="W18" s="99" t="n">
+      <c r="X18" s="99" t="n">
         <v>-3.9</v>
       </c>
-      <c r="X18" s="99" t="n">
+      <c r="Y18" s="99" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Y18" s="99" t="n">
+      <c r="Z18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="Z18" s="99" t="n">
+      <c r="AA18" s="99" t="n">
         <v>-3.57</v>
       </c>
-      <c r="AA18" s="99" t="n">
+      <c r="AB18" s="99" t="n">
         <v>-3.86</v>
       </c>
-      <c r="AB18" s="99" t="n">
+      <c r="AC18" s="99" t="n">
         <v>-1.13</v>
       </c>
-      <c r="AC18" s="99" t="n">
+      <c r="AD18" s="99" t="n">
         <v>-2.37</v>
       </c>
-      <c r="AD18" s="99" t="n">
+      <c r="AE18" s="99" t="n">
         <v>-4.68</v>
-      </c>
-      <c r="AE18" s="99" t="n">
-        <v>-6.27</v>
       </c>
     </row>
     <row r="19">
@@ -8403,94 +8403,94 @@
         </is>
       </c>
       <c r="B19" s="99" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="C19" s="99" t="n">
         <v>34.13</v>
-      </c>
-      <c r="C19" s="99" t="n">
-        <v>26.37</v>
       </c>
       <c r="D19" s="99" t="n">
         <v>26.37</v>
       </c>
       <c r="E19" s="99" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="F19" s="99" t="n">
         <v>23.36</v>
       </c>
-      <c r="F19" s="99" t="n">
+      <c r="G19" s="99" t="n">
         <v>17.68</v>
       </c>
-      <c r="G19" s="99" t="n">
+      <c r="H19" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="H19" s="99" t="n">
+      <c r="I19" s="99" t="n">
         <v>15.91</v>
       </c>
-      <c r="I19" s="99" t="n">
+      <c r="J19" s="99" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J19" s="99" t="n">
+      <c r="K19" s="99" t="n">
         <v>10.84</v>
       </c>
-      <c r="K19" s="99" t="n">
+      <c r="L19" s="99" t="n">
         <v>9.17</v>
-      </c>
-      <c r="L19" s="99" t="n">
-        <v>4.73</v>
       </c>
       <c r="M19" s="99" t="n">
         <v>4.73</v>
       </c>
       <c r="N19" s="99" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="O19" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="O19" s="99" t="n">
+      <c r="P19" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="P19" s="99" t="n">
+      <c r="Q19" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q19" s="99" t="n">
+      <c r="R19" s="99" t="n">
         <v>2.32</v>
       </c>
-      <c r="R19" s="99" t="n">
+      <c r="S19" s="99" t="n">
         <v>1.61</v>
       </c>
-      <c r="S19" s="99" t="n">
+      <c r="T19" s="99" t="n">
         <v>0.67</v>
-      </c>
-      <c r="T19" s="99" t="n">
-        <v>2.05</v>
       </c>
       <c r="U19" s="99" t="n">
         <v>2.05</v>
       </c>
       <c r="V19" s="99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W19" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="W19" s="99" t="n">
+      <c r="X19" s="99" t="n">
         <v>7.94</v>
       </c>
-      <c r="X19" s="99" t="n">
+      <c r="Y19" s="99" t="n">
         <v>9.01</v>
       </c>
-      <c r="Y19" s="99" t="n">
+      <c r="Z19" s="99" t="n">
         <v>9.44</v>
       </c>
-      <c r="Z19" s="99" t="n">
+      <c r="AA19" s="99" t="n">
         <v>10.05</v>
       </c>
-      <c r="AA19" s="99" t="n">
+      <c r="AB19" s="99" t="n">
         <v>6.61</v>
       </c>
-      <c r="AB19" s="99" t="n">
+      <c r="AC19" s="99" t="n">
         <v>7.75</v>
       </c>
-      <c r="AC19" s="99" t="n">
+      <c r="AD19" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD19" s="99" t="n">
+      <c r="AE19" s="99" t="n">
         <v>6.5</v>
-      </c>
-      <c r="AE19" s="99" t="n">
-        <v>5.06</v>
       </c>
     </row>
     <row r="20">
@@ -8500,94 +8500,94 @@
         </is>
       </c>
       <c r="B20" s="99" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="C20" s="99" t="n">
         <v>98.28</v>
-      </c>
-      <c r="C20" s="99" t="n">
-        <v>97.18000000000001</v>
       </c>
       <c r="D20" s="99" t="n">
         <v>97.18000000000001</v>
       </c>
       <c r="E20" s="99" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="F20" s="99" t="n">
         <v>96.45999999999999</v>
       </c>
-      <c r="F20" s="99" t="n">
+      <c r="G20" s="99" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="G20" s="99" t="n">
+      <c r="H20" s="99" t="n">
         <v>91.5</v>
       </c>
-      <c r="H20" s="99" t="n">
+      <c r="I20" s="99" t="n">
         <v>90.64</v>
       </c>
-      <c r="I20" s="99" t="n">
+      <c r="J20" s="99" t="n">
         <v>81.62</v>
       </c>
-      <c r="J20" s="99" t="n">
+      <c r="K20" s="99" t="n">
         <v>82.63</v>
       </c>
-      <c r="K20" s="99" t="n">
+      <c r="L20" s="99" t="n">
         <v>77.72</v>
-      </c>
-      <c r="L20" s="99" t="n">
-        <v>66.26000000000001</v>
       </c>
       <c r="M20" s="99" t="n">
         <v>66.26000000000001</v>
       </c>
       <c r="N20" s="99" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="O20" s="99" t="n">
         <v>52.57</v>
       </c>
-      <c r="O20" s="99" t="n">
+      <c r="P20" s="99" t="n">
         <v>48.7</v>
       </c>
-      <c r="P20" s="99" t="n">
+      <c r="Q20" s="99" t="n">
         <v>38.58</v>
       </c>
-      <c r="Q20" s="99" t="n">
+      <c r="R20" s="99" t="n">
         <v>26.15</v>
       </c>
-      <c r="R20" s="99" t="n">
+      <c r="S20" s="99" t="n">
         <v>31.15</v>
       </c>
-      <c r="S20" s="99" t="n">
+      <c r="T20" s="99" t="n">
         <v>27.74</v>
-      </c>
-      <c r="T20" s="99" t="n">
-        <v>38.27</v>
       </c>
       <c r="U20" s="99" t="n">
         <v>38.27</v>
       </c>
       <c r="V20" s="99" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="W20" s="99" t="n">
         <v>38.92</v>
       </c>
-      <c r="W20" s="99" t="n">
+      <c r="X20" s="99" t="n">
         <v>49.28</v>
       </c>
-      <c r="X20" s="99" t="n">
+      <c r="Y20" s="99" t="n">
         <v>51.67</v>
       </c>
-      <c r="Y20" s="99" t="n">
+      <c r="Z20" s="99" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="Z20" s="99" t="n">
+      <c r="AA20" s="99" t="n">
         <v>65.08</v>
       </c>
-      <c r="AA20" s="99" t="n">
+      <c r="AB20" s="99" t="n">
         <v>60.24</v>
       </c>
-      <c r="AB20" s="99" t="n">
+      <c r="AC20" s="99" t="n">
         <v>77.66</v>
       </c>
-      <c r="AC20" s="99" t="n">
+      <c r="AD20" s="99" t="n">
         <v>75.16</v>
       </c>
-      <c r="AD20" s="99" t="n">
+      <c r="AE20" s="99" t="n">
         <v>67.81</v>
-      </c>
-      <c r="AE20" s="99" t="n">
-        <v>70.5</v>
       </c>
     </row>
     <row r="21">
@@ -8597,94 +8597,94 @@
         </is>
       </c>
       <c r="B21" s="99" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="C21" s="99" t="n">
         <v>86.55</v>
-      </c>
-      <c r="C21" s="99" t="n">
-        <v>82.69</v>
       </c>
       <c r="D21" s="99" t="n">
         <v>82.69</v>
       </c>
       <c r="E21" s="99" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="F21" s="99" t="n">
         <v>80.68000000000001</v>
       </c>
-      <c r="F21" s="99" t="n">
+      <c r="G21" s="99" t="n">
         <v>77.11</v>
       </c>
-      <c r="G21" s="99" t="n">
+      <c r="H21" s="99" t="n">
         <v>71.53</v>
       </c>
-      <c r="H21" s="99" t="n">
+      <c r="I21" s="99" t="n">
         <v>70.42</v>
       </c>
-      <c r="I21" s="99" t="n">
+      <c r="J21" s="99" t="n">
         <v>62.3</v>
       </c>
-      <c r="J21" s="99" t="n">
+      <c r="K21" s="99" t="n">
         <v>62.54</v>
       </c>
-      <c r="K21" s="99" t="n">
+      <c r="L21" s="99" t="n">
         <v>59.26</v>
-      </c>
-      <c r="L21" s="99" t="n">
-        <v>53.72</v>
       </c>
       <c r="M21" s="99" t="n">
         <v>53.72</v>
       </c>
       <c r="N21" s="99" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="O21" s="99" t="n">
         <v>49.33</v>
       </c>
-      <c r="O21" s="99" t="n">
+      <c r="P21" s="99" t="n">
         <v>48.3</v>
       </c>
-      <c r="P21" s="99" t="n">
+      <c r="Q21" s="99" t="n">
         <v>45.75</v>
       </c>
-      <c r="Q21" s="99" t="n">
+      <c r="R21" s="99" t="n">
         <v>43.02</v>
       </c>
-      <c r="R21" s="99" t="n">
+      <c r="S21" s="99" t="n">
         <v>45.06</v>
       </c>
-      <c r="S21" s="99" t="n">
+      <c r="T21" s="99" t="n">
         <v>44.32</v>
-      </c>
-      <c r="T21" s="99" t="n">
-        <v>48.45</v>
       </c>
       <c r="U21" s="99" t="n">
         <v>48.45</v>
       </c>
       <c r="V21" s="99" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="W21" s="99" t="n">
         <v>48.67</v>
       </c>
-      <c r="W21" s="99" t="n">
+      <c r="X21" s="99" t="n">
         <v>52.11</v>
       </c>
-      <c r="X21" s="99" t="n">
+      <c r="Y21" s="99" t="n">
         <v>52.84</v>
       </c>
-      <c r="Y21" s="99" t="n">
+      <c r="Z21" s="99" t="n">
         <v>58.6</v>
       </c>
-      <c r="Z21" s="99" t="n">
+      <c r="AA21" s="99" t="n">
         <v>55.46</v>
       </c>
-      <c r="AA21" s="99" t="n">
+      <c r="AB21" s="99" t="n">
         <v>53.93</v>
       </c>
-      <c r="AB21" s="99" t="n">
+      <c r="AC21" s="99" t="n">
         <v>57.57</v>
       </c>
-      <c r="AC21" s="99" t="n">
+      <c r="AD21" s="99" t="n">
         <v>56.41</v>
       </c>
-      <c r="AD21" s="99" t="n">
+      <c r="AE21" s="99" t="n">
         <v>53.44</v>
-      </c>
-      <c r="AE21" s="99" t="n">
-        <v>53.98</v>
       </c>
     </row>
     <row r="22">
@@ -8723,89 +8723,89 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="96" t="inlineStr">
+      <c r="H22" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="96" t="inlineStr">
+      <c r="J22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="96" t="inlineStr">
+      <c r="K22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="96" t="inlineStr">
+      <c r="L22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="97" t="inlineStr">
+      <c r="M22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="96" t="inlineStr">
+      <c r="N22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="96" t="inlineStr">
+      <c r="O22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="96" t="inlineStr">
+      <c r="P22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="96" t="inlineStr">
+      <c r="Q22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="96" t="inlineStr">
+      <c r="R22" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R22" s="97" t="inlineStr">
+      <c r="S22" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="98" t="inlineStr">
+      <c r="T22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="98" t="inlineStr">
+      <c r="U22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="98" t="inlineStr">
+      <c r="V22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="98" t="inlineStr">
+      <c r="W22" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="98" t="inlineStr">
+      <c r="X22" s="98" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="X22" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="Y22" s="97" t="inlineStr">
@@ -8854,91 +8854,91 @@
         <v>2.38</v>
       </c>
       <c r="C23" s="99" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D23" s="99" t="n">
         <v>2.44</v>
       </c>
-      <c r="D23" s="99" t="n">
+      <c r="E23" s="99" t="n">
         <v>3.51</v>
       </c>
-      <c r="E23" s="99" t="n">
+      <c r="F23" s="99" t="n">
         <v>3.63</v>
       </c>
-      <c r="F23" s="99" t="n">
+      <c r="G23" s="99" t="n">
         <v>4.29</v>
       </c>
-      <c r="G23" s="99" t="n">
+      <c r="H23" s="99" t="n">
         <v>4.51</v>
       </c>
-      <c r="H23" s="99" t="n">
+      <c r="I23" s="99" t="n">
         <v>4.99</v>
       </c>
-      <c r="I23" s="99" t="n">
+      <c r="J23" s="99" t="n">
         <v>4.3</v>
       </c>
-      <c r="J23" s="99" t="n">
+      <c r="K23" s="99" t="n">
         <v>4.1</v>
       </c>
-      <c r="K23" s="99" t="n">
+      <c r="L23" s="99" t="n">
         <v>4.47</v>
       </c>
-      <c r="L23" s="99" t="n">
+      <c r="M23" s="99" t="n">
         <v>3.13</v>
       </c>
-      <c r="M23" s="99" t="n">
+      <c r="N23" s="99" t="n">
         <v>3.11</v>
       </c>
-      <c r="N23" s="99" t="n">
+      <c r="O23" s="99" t="n">
         <v>2.92</v>
       </c>
-      <c r="O23" s="99" t="n">
+      <c r="P23" s="99" t="n">
         <v>2.53</v>
       </c>
-      <c r="P23" s="99" t="n">
+      <c r="Q23" s="99" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q23" s="99" t="n">
+      <c r="R23" s="99" t="n">
         <v>2.26</v>
       </c>
-      <c r="R23" s="99" t="n">
+      <c r="S23" s="99" t="n">
         <v>1.14</v>
       </c>
-      <c r="S23" s="99" t="n">
+      <c r="T23" s="99" t="n">
         <v>0.92</v>
       </c>
-      <c r="T23" s="99" t="n">
+      <c r="U23" s="99" t="n">
         <v>0.62</v>
       </c>
-      <c r="U23" s="99" t="n">
+      <c r="V23" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="V23" s="99" t="n">
+      <c r="W23" s="99" t="n">
         <v>3.24</v>
       </c>
-      <c r="W23" s="99" t="n">
+      <c r="X23" s="99" t="n">
         <v>3.29</v>
-      </c>
-      <c r="X23" s="99" t="n">
-        <v>5.5</v>
       </c>
       <c r="Y23" s="99" t="n">
         <v>5.5</v>
       </c>
       <c r="Z23" s="99" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA23" s="99" t="n">
         <v>5.68</v>
       </c>
-      <c r="AA23" s="99" t="n">
+      <c r="AB23" s="99" t="n">
         <v>5.84</v>
       </c>
-      <c r="AB23" s="99" t="n">
+      <c r="AC23" s="99" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC23" s="99" t="n">
+      <c r="AD23" s="99" t="n">
         <v>7.28</v>
       </c>
-      <c r="AD23" s="99" t="n">
+      <c r="AE23" s="99" t="n">
         <v>6.98</v>
-      </c>
-      <c r="AE23" s="99" t="n">
-        <v>4.99</v>
       </c>
     </row>
     <row r="24">
@@ -8951,91 +8951,91 @@
         <v>9.82</v>
       </c>
       <c r="C24" s="99" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D24" s="99" t="n">
         <v>10.62</v>
       </c>
-      <c r="D24" s="99" t="n">
+      <c r="E24" s="99" t="n">
         <v>10.61</v>
       </c>
-      <c r="E24" s="99" t="n">
+      <c r="F24" s="99" t="n">
         <v>10.3</v>
       </c>
-      <c r="F24" s="99" t="n">
+      <c r="G24" s="99" t="n">
         <v>10.4</v>
       </c>
-      <c r="G24" s="99" t="n">
+      <c r="H24" s="99" t="n">
         <v>11.17</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="I24" s="99" t="n">
         <v>10.01</v>
       </c>
-      <c r="I24" s="99" t="n">
+      <c r="J24" s="99" t="n">
         <v>9.85</v>
       </c>
-      <c r="J24" s="99" t="n">
+      <c r="K24" s="99" t="n">
         <v>8.75</v>
       </c>
-      <c r="K24" s="99" t="n">
+      <c r="L24" s="99" t="n">
         <v>8.74</v>
       </c>
-      <c r="L24" s="99" t="n">
+      <c r="M24" s="99" t="n">
         <v>7.05</v>
       </c>
-      <c r="M24" s="99" t="n">
+      <c r="N24" s="99" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="N24" s="99" t="n">
+      <c r="O24" s="99" t="n">
         <v>7.95</v>
       </c>
-      <c r="O24" s="99" t="n">
+      <c r="P24" s="99" t="n">
         <v>7.49</v>
       </c>
-      <c r="P24" s="99" t="n">
+      <c r="Q24" s="99" t="n">
         <v>6.76</v>
       </c>
-      <c r="Q24" s="99" t="n">
+      <c r="R24" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="R24" s="99" t="n">
+      <c r="S24" s="99" t="n">
         <v>6.12</v>
       </c>
-      <c r="S24" s="99" t="n">
+      <c r="T24" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="T24" s="99" t="n">
+      <c r="U24" s="99" t="n">
         <v>5.69</v>
       </c>
-      <c r="U24" s="99" t="n">
+      <c r="V24" s="99" t="n">
         <v>6.85</v>
       </c>
-      <c r="V24" s="99" t="n">
+      <c r="W24" s="99" t="n">
         <v>6.87</v>
       </c>
-      <c r="W24" s="99" t="n">
+      <c r="X24" s="99" t="n">
         <v>6.83</v>
-      </c>
-      <c r="X24" s="99" t="n">
-        <v>10.36</v>
       </c>
       <c r="Y24" s="99" t="n">
         <v>10.36</v>
       </c>
       <c r="Z24" s="99" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AA24" s="99" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="AA24" s="99" t="n">
+      <c r="AB24" s="99" t="n">
         <v>8.43</v>
       </c>
-      <c r="AB24" s="99" t="n">
+      <c r="AC24" s="99" t="n">
         <v>10.21</v>
       </c>
-      <c r="AC24" s="99" t="n">
+      <c r="AD24" s="99" t="n">
         <v>10.6</v>
       </c>
-      <c r="AD24" s="99" t="n">
+      <c r="AE24" s="99" t="n">
         <v>9.82</v>
-      </c>
-      <c r="AE24" s="99" t="n">
-        <v>8.44</v>
       </c>
     </row>
     <row r="25">
@@ -9048,91 +9048,91 @@
         <v>23.93</v>
       </c>
       <c r="C25" s="99" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="D25" s="99" t="n">
         <v>22.27</v>
       </c>
-      <c r="D25" s="99" t="n">
+      <c r="E25" s="99" t="n">
         <v>86.19</v>
       </c>
-      <c r="E25" s="99" t="n">
+      <c r="F25" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="F25" s="99" t="n">
+      <c r="G25" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="G25" s="99" t="n">
+      <c r="H25" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="I25" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="I25" s="99" t="n">
+      <c r="J25" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="J25" s="99" t="n">
+      <c r="K25" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="K25" s="99" t="n">
+      <c r="L25" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="L25" s="99" t="n">
+      <c r="M25" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="M25" s="99" t="n">
+      <c r="N25" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="N25" s="99" t="n">
+      <c r="O25" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="O25" s="99" t="n">
+      <c r="P25" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="P25" s="99" t="n">
+      <c r="Q25" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="Q25" s="99" t="n">
+      <c r="R25" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="R25" s="99" t="n">
+      <c r="S25" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="S25" s="99" t="n">
+      <c r="T25" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="T25" s="99" t="n">
+      <c r="U25" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="U25" s="99" t="n">
+      <c r="V25" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="V25" s="99" t="n">
+      <c r="W25" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="W25" s="99" t="n">
+      <c r="X25" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="X25" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="Y25" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="Z25" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="AA25" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="AA25" s="99" t="n">
+      <c r="AB25" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="AB25" s="99" t="n">
+      <c r="AC25" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AC25" s="99" t="n">
+      <c r="AD25" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AD25" s="99" t="n">
+      <c r="AE25" s="99" t="n">
         <v>74.03</v>
-      </c>
-      <c r="AE25" s="99" t="n">
-        <v>30.49</v>
       </c>
     </row>
     <row r="26">
@@ -9145,91 +9145,91 @@
         <v>23.93</v>
       </c>
       <c r="C26" s="99" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="D26" s="99" t="n">
         <v>22.27</v>
       </c>
-      <c r="D26" s="99" t="n">
+      <c r="E26" s="99" t="n">
         <v>86.19</v>
       </c>
-      <c r="E26" s="99" t="n">
+      <c r="F26" s="99" t="n">
         <v>60.63</v>
       </c>
-      <c r="F26" s="99" t="n">
+      <c r="G26" s="99" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="G26" s="99" t="n">
+      <c r="H26" s="99" t="n">
         <v>58.19</v>
       </c>
-      <c r="H26" s="99" t="n">
+      <c r="I26" s="99" t="n">
         <v>90.16</v>
       </c>
-      <c r="I26" s="99" t="n">
+      <c r="J26" s="99" t="n">
         <v>84.39</v>
       </c>
-      <c r="J26" s="99" t="n">
+      <c r="K26" s="99" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="K26" s="99" t="n">
+      <c r="L26" s="99" t="n">
         <v>92.34</v>
       </c>
-      <c r="L26" s="99" t="n">
+      <c r="M26" s="99" t="n">
         <v>40.89</v>
       </c>
-      <c r="M26" s="99" t="n">
+      <c r="N26" s="99" t="n">
         <v>96.09</v>
       </c>
-      <c r="N26" s="99" t="n">
+      <c r="O26" s="99" t="n">
         <v>95.83</v>
       </c>
-      <c r="O26" s="99" t="n">
+      <c r="P26" s="99" t="n">
         <v>95.06</v>
       </c>
-      <c r="P26" s="99" t="n">
+      <c r="Q26" s="99" t="n">
         <v>91.83</v>
       </c>
-      <c r="Q26" s="99" t="n">
+      <c r="R26" s="99" t="n">
         <v>85.17</v>
       </c>
-      <c r="R26" s="99" t="n">
+      <c r="S26" s="99" t="n">
         <v>65.2</v>
       </c>
-      <c r="S26" s="99" t="n">
+      <c r="T26" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="T26" s="99" t="n">
+      <c r="U26" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="U26" s="99" t="n">
+      <c r="V26" s="99" t="n">
         <v>12.54</v>
       </c>
-      <c r="V26" s="99" t="n">
+      <c r="W26" s="99" t="n">
         <v>17.38</v>
       </c>
-      <c r="W26" s="99" t="n">
+      <c r="X26" s="99" t="n">
         <v>19.37</v>
-      </c>
-      <c r="X26" s="99" t="n">
-        <v>85.14</v>
       </c>
       <c r="Y26" s="99" t="n">
         <v>85.14</v>
       </c>
       <c r="Z26" s="99" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="AA26" s="99" t="n">
         <v>24.99</v>
       </c>
-      <c r="AA26" s="99" t="n">
+      <c r="AB26" s="99" t="n">
         <v>25.19</v>
       </c>
-      <c r="AB26" s="99" t="n">
+      <c r="AC26" s="99" t="n">
         <v>64.23</v>
       </c>
-      <c r="AC26" s="99" t="n">
+      <c r="AD26" s="99" t="n">
         <v>54.92</v>
       </c>
-      <c r="AD26" s="99" t="n">
+      <c r="AE26" s="99" t="n">
         <v>74.03</v>
-      </c>
-      <c r="AE26" s="99" t="n">
-        <v>30.49</v>
       </c>
     </row>
     <row r="27">
@@ -9268,124 +9268,124 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H27" s="96" t="inlineStr">
+      <c r="H27" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I27" s="96" t="inlineStr">
+      <c r="J27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J27" s="96" t="inlineStr">
+      <c r="K27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K27" s="96" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L27" s="96" t="inlineStr">
+      <c r="M27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M27" s="96" t="inlineStr">
+      <c r="N27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N27" s="96" t="inlineStr">
+      <c r="O27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O27" s="96" t="inlineStr">
+      <c r="P27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P27" s="96" t="inlineStr">
+      <c r="Q27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q27" s="96" t="inlineStr">
+      <c r="R27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R27" s="98" t="inlineStr">
+      <c r="S27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S27" s="97" t="inlineStr">
+      <c r="T27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="98" t="inlineStr">
+      <c r="U27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U27" s="98" t="inlineStr">
+      <c r="V27" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V27" s="97" t="inlineStr">
+      <c r="W27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W27" s="97" t="inlineStr">
+      <c r="X27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X27" s="96" t="inlineStr">
+      <c r="Y27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y27" s="96" t="inlineStr">
+      <c r="Z27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z27" s="97" t="inlineStr">
+      <c r="AA27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA27" s="97" t="inlineStr">
+      <c r="AB27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB27" s="97" t="inlineStr">
+      <c r="AC27" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC27" s="96" t="inlineStr">
+      <c r="AD27" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD27" s="96" t="inlineStr">
+      <c r="AE27" s="96" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE27" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -9399,91 +9399,91 @@
         <v>7.39</v>
       </c>
       <c r="C28" s="99" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="D28" s="99" t="n">
         <v>7.15</v>
       </c>
-      <c r="D28" s="99" t="n">
+      <c r="E28" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="E28" s="99" t="n">
+      <c r="F28" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="F28" s="99" t="n">
+      <c r="G28" s="99" t="n">
         <v>7.23</v>
       </c>
-      <c r="G28" s="99" t="n">
+      <c r="H28" s="99" t="n">
         <v>7.01</v>
       </c>
-      <c r="H28" s="99" t="n">
+      <c r="I28" s="99" t="n">
         <v>7.9</v>
       </c>
-      <c r="I28" s="99" t="n">
+      <c r="J28" s="99" t="n">
         <v>7.56</v>
       </c>
-      <c r="J28" s="99" t="n">
+      <c r="K28" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="K28" s="99" t="n">
+      <c r="L28" s="99" t="n">
         <v>7.45</v>
       </c>
-      <c r="L28" s="99" t="n">
+      <c r="M28" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="M28" s="99" t="n">
+      <c r="N28" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="N28" s="99" t="n">
+      <c r="O28" s="99" t="n">
         <v>6.36</v>
       </c>
-      <c r="O28" s="99" t="n">
+      <c r="P28" s="99" t="n">
         <v>6.59</v>
       </c>
-      <c r="P28" s="99" t="n">
+      <c r="Q28" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="Q28" s="99" t="n">
+      <c r="R28" s="99" t="n">
         <v>5.89</v>
       </c>
-      <c r="R28" s="99" t="n">
+      <c r="S28" s="99" t="n">
         <v>5.41</v>
       </c>
-      <c r="S28" s="99" t="n">
+      <c r="T28" s="99" t="n">
         <v>5.47</v>
       </c>
-      <c r="T28" s="99" t="n">
+      <c r="U28" s="99" t="n">
         <v>4.12</v>
       </c>
-      <c r="U28" s="99" t="n">
+      <c r="V28" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="V28" s="99" t="n">
+      <c r="W28" s="99" t="n">
         <v>5.61</v>
       </c>
-      <c r="W28" s="99" t="n">
+      <c r="X28" s="99" t="n">
         <v>5.27</v>
-      </c>
-      <c r="X28" s="99" t="n">
-        <v>7.1</v>
       </c>
       <c r="Y28" s="99" t="n">
         <v>7.1</v>
       </c>
       <c r="Z28" s="99" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA28" s="99" t="n">
         <v>6.78</v>
       </c>
-      <c r="AA28" s="99" t="n">
+      <c r="AB28" s="99" t="n">
         <v>6.53</v>
       </c>
-      <c r="AB28" s="99" t="n">
+      <c r="AC28" s="99" t="n">
         <v>6.63</v>
       </c>
-      <c r="AC28" s="99" t="n">
+      <c r="AD28" s="99" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="AD28" s="99" t="n">
+      <c r="AE28" s="99" t="n">
         <v>7.11</v>
-      </c>
-      <c r="AE28" s="99" t="n">
-        <v>4.79</v>
       </c>
     </row>
     <row r="29">
@@ -9496,91 +9496,91 @@
         <v>9.720000000000001</v>
       </c>
       <c r="C29" s="99" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D29" s="99" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D29" s="99" t="n">
+      <c r="E29" s="99" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="E29" s="99" t="n">
+      <c r="F29" s="99" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="F29" s="99" t="n">
+      <c r="G29" s="99" t="n">
         <v>8.41</v>
       </c>
-      <c r="G29" s="99" t="n">
+      <c r="H29" s="99" t="n">
         <v>8.6</v>
       </c>
-      <c r="H29" s="99" t="n">
+      <c r="I29" s="99" t="n">
         <v>7.87</v>
       </c>
-      <c r="I29" s="99" t="n">
+      <c r="J29" s="99" t="n">
         <v>7.54</v>
       </c>
-      <c r="J29" s="99" t="n">
+      <c r="K29" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="K29" s="99" t="n">
+      <c r="L29" s="99" t="n">
         <v>5.57</v>
       </c>
-      <c r="L29" s="99" t="n">
+      <c r="M29" s="99" t="n">
         <v>4.38</v>
       </c>
-      <c r="M29" s="99" t="n">
+      <c r="N29" s="99" t="n">
         <v>5.92</v>
       </c>
-      <c r="N29" s="99" t="n">
+      <c r="O29" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="O29" s="99" t="n">
+      <c r="P29" s="99" t="n">
         <v>4.86</v>
       </c>
-      <c r="P29" s="99" t="n">
+      <c r="Q29" s="99" t="n">
         <v>3.31</v>
       </c>
-      <c r="Q29" s="99" t="n">
+      <c r="R29" s="99" t="n">
         <v>3.42</v>
       </c>
-      <c r="R29" s="99" t="n">
+      <c r="S29" s="99" t="n">
         <v>4.16</v>
       </c>
-      <c r="S29" s="99" t="n">
+      <c r="T29" s="99" t="n">
         <v>5.26</v>
       </c>
-      <c r="T29" s="99" t="n">
+      <c r="U29" s="99" t="n">
         <v>4.21</v>
       </c>
-      <c r="U29" s="99" t="n">
+      <c r="V29" s="99" t="n">
         <v>4.76</v>
-      </c>
-      <c r="V29" s="99" t="n">
-        <v>4.95</v>
       </c>
       <c r="W29" s="99" t="n">
         <v>4.95</v>
       </c>
       <c r="X29" s="99" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="Y29" s="99" t="n">
         <v>7.21</v>
       </c>
       <c r="Z29" s="99" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AA29" s="99" t="n">
         <v>6.75</v>
       </c>
-      <c r="AA29" s="99" t="n">
+      <c r="AB29" s="99" t="n">
         <v>5.93</v>
       </c>
-      <c r="AB29" s="99" t="n">
+      <c r="AC29" s="99" t="n">
         <v>6.7</v>
       </c>
-      <c r="AC29" s="99" t="n">
+      <c r="AD29" s="99" t="n">
         <v>6.88</v>
       </c>
-      <c r="AD29" s="99" t="n">
+      <c r="AE29" s="99" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AE29" s="99" t="n">
-        <v>4.16</v>
       </c>
     </row>
     <row r="30">
@@ -9593,91 +9593,91 @@
         <v>52.09</v>
       </c>
       <c r="C30" s="99" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="D30" s="99" t="n">
         <v>45.5</v>
       </c>
-      <c r="D30" s="99" t="n">
+      <c r="E30" s="99" t="n">
         <v>76.02</v>
       </c>
-      <c r="E30" s="99" t="n">
+      <c r="F30" s="99" t="n">
         <v>74.91</v>
       </c>
-      <c r="F30" s="99" t="n">
+      <c r="G30" s="99" t="n">
         <v>66.62</v>
       </c>
-      <c r="G30" s="99" t="n">
+      <c r="H30" s="99" t="n">
         <v>42.84</v>
       </c>
-      <c r="H30" s="99" t="n">
+      <c r="I30" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="I30" s="99" t="n">
+      <c r="J30" s="99" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="J30" s="99" t="n">
+      <c r="K30" s="99" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="K30" s="99" t="n">
+      <c r="L30" s="99" t="n">
         <v>87.58</v>
       </c>
-      <c r="L30" s="99" t="n">
+      <c r="M30" s="99" t="n">
         <v>65.31</v>
       </c>
-      <c r="M30" s="99" t="n">
+      <c r="N30" s="99" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="N30" s="99" t="n">
+      <c r="O30" s="99" t="n">
         <v>88.3</v>
       </c>
-      <c r="O30" s="99" t="n">
+      <c r="P30" s="99" t="n">
         <v>82.94</v>
       </c>
-      <c r="P30" s="99" t="n">
+      <c r="Q30" s="99" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="Q30" s="99" t="n">
+      <c r="R30" s="99" t="n">
         <v>56.57</v>
       </c>
-      <c r="R30" s="99" t="n">
+      <c r="S30" s="99" t="n">
         <v>46.45</v>
       </c>
-      <c r="S30" s="99" t="n">
+      <c r="T30" s="99" t="n">
         <v>52.5</v>
       </c>
-      <c r="T30" s="99" t="n">
+      <c r="U30" s="99" t="n">
         <v>13.02</v>
       </c>
-      <c r="U30" s="99" t="n">
+      <c r="V30" s="99" t="n">
         <v>24.55</v>
       </c>
-      <c r="V30" s="99" t="n">
+      <c r="W30" s="99" t="n">
         <v>35.87</v>
       </c>
-      <c r="W30" s="99" t="n">
+      <c r="X30" s="99" t="n">
         <v>32.25</v>
-      </c>
-      <c r="X30" s="99" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="Y30" s="99" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="Z30" s="99" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="AA30" s="99" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="AA30" s="99" t="n">
+      <c r="AB30" s="99" t="n">
         <v>52.49</v>
       </c>
-      <c r="AB30" s="99" t="n">
+      <c r="AC30" s="99" t="n">
         <v>83.64</v>
       </c>
-      <c r="AC30" s="99" t="n">
+      <c r="AD30" s="99" t="n">
         <v>83.23</v>
       </c>
-      <c r="AD30" s="99" t="n">
+      <c r="AE30" s="99" t="n">
         <v>81.13</v>
-      </c>
-      <c r="AE30" s="99" t="n">
-        <v>54.01</v>
       </c>
     </row>
     <row r="31">
@@ -9690,91 +9690,91 @@
         <v>60.09</v>
       </c>
       <c r="C31" s="99" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="D31" s="99" t="n">
         <v>57.59</v>
       </c>
-      <c r="D31" s="99" t="n">
+      <c r="E31" s="99" t="n">
         <v>73.8</v>
       </c>
-      <c r="E31" s="99" t="n">
+      <c r="F31" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="F31" s="99" t="n">
+      <c r="G31" s="99" t="n">
         <v>68.59</v>
       </c>
-      <c r="G31" s="99" t="n">
+      <c r="H31" s="99" t="n">
         <v>57.58</v>
       </c>
-      <c r="H31" s="99" t="n">
+      <c r="I31" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="I31" s="99" t="n">
+      <c r="J31" s="99" t="n">
         <v>82.34</v>
       </c>
-      <c r="J31" s="99" t="n">
+      <c r="K31" s="99" t="n">
         <v>81.04000000000001</v>
       </c>
-      <c r="K31" s="99" t="n">
+      <c r="L31" s="99" t="n">
         <v>80.31</v>
       </c>
-      <c r="L31" s="99" t="n">
+      <c r="M31" s="99" t="n">
         <v>66.03</v>
       </c>
-      <c r="M31" s="99" t="n">
+      <c r="N31" s="99" t="n">
         <v>74.56999999999999</v>
       </c>
-      <c r="N31" s="99" t="n">
+      <c r="O31" s="99" t="n">
         <v>75.78</v>
       </c>
-      <c r="O31" s="99" t="n">
+      <c r="P31" s="99" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="P31" s="99" t="n">
+      <c r="Q31" s="99" t="n">
         <v>60.93</v>
       </c>
-      <c r="Q31" s="99" t="n">
+      <c r="R31" s="99" t="n">
         <v>51.28</v>
       </c>
-      <c r="R31" s="99" t="n">
+      <c r="S31" s="99" t="n">
         <v>45.58</v>
       </c>
-      <c r="S31" s="99" t="n">
+      <c r="T31" s="99" t="n">
         <v>48.99</v>
       </c>
-      <c r="T31" s="99" t="n">
+      <c r="U31" s="99" t="n">
         <v>25.8</v>
       </c>
-      <c r="U31" s="99" t="n">
+      <c r="V31" s="99" t="n">
         <v>37.29</v>
       </c>
-      <c r="V31" s="99" t="n">
+      <c r="W31" s="99" t="n">
         <v>46.06</v>
       </c>
-      <c r="W31" s="99" t="n">
+      <c r="X31" s="99" t="n">
         <v>44.24</v>
-      </c>
-      <c r="X31" s="99" t="n">
-        <v>79.63</v>
       </c>
       <c r="Y31" s="99" t="n">
         <v>79.63</v>
       </c>
       <c r="Z31" s="99" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="AA31" s="99" t="n">
         <v>73.44</v>
       </c>
-      <c r="AA31" s="99" t="n">
+      <c r="AB31" s="99" t="n">
         <v>64.13</v>
       </c>
-      <c r="AB31" s="99" t="n">
+      <c r="AC31" s="99" t="n">
         <v>78.52</v>
       </c>
-      <c r="AC31" s="99" t="n">
+      <c r="AD31" s="99" t="n">
         <v>78.27</v>
       </c>
-      <c r="AD31" s="99" t="n">
+      <c r="AE31" s="99" t="n">
         <v>76.89</v>
-      </c>
-      <c r="AE31" s="99" t="n">
-        <v>63.94</v>
       </c>
     </row>
     <row r="32">
@@ -9803,119 +9803,119 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F32" s="96" t="inlineStr">
+      <c r="F32" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G32" s="97" t="inlineStr">
+      <c r="H32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H32" s="96" t="inlineStr">
+      <c r="I32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I32" s="96" t="inlineStr">
+      <c r="J32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J32" s="96" t="inlineStr">
+      <c r="K32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K32" s="96" t="inlineStr">
+      <c r="L32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L32" s="97" t="inlineStr">
+      <c r="M32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M32" s="96" t="inlineStr">
+      <c r="N32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N32" s="96" t="inlineStr">
+      <c r="O32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O32" s="96" t="inlineStr">
+      <c r="P32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P32" s="96" t="inlineStr">
+      <c r="Q32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q32" s="96" t="inlineStr">
+      <c r="R32" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R32" s="97" t="inlineStr">
+      <c r="S32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="98" t="inlineStr">
+      <c r="T32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T32" s="98" t="inlineStr">
+      <c r="U32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U32" s="98" t="inlineStr">
+      <c r="V32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V32" s="98" t="inlineStr">
+      <c r="W32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W32" s="98" t="inlineStr">
+      <c r="X32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X32" s="97" t="inlineStr">
+      <c r="Y32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y32" s="97" t="inlineStr">
+      <c r="Z32" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z32" s="98" t="inlineStr">
+      <c r="AA32" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA32" s="98" t="inlineStr">
+      <c r="AB32" s="98" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AB32" s="97" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AC32" s="97" t="inlineStr">
@@ -9944,91 +9944,91 @@
         <v>-2.74</v>
       </c>
       <c r="C33" s="99" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="D33" s="99" t="n">
         <v>-2.68</v>
       </c>
-      <c r="D33" s="99" t="n">
+      <c r="E33" s="99" t="n">
         <v>-0.89</v>
       </c>
-      <c r="E33" s="99" t="n">
+      <c r="F33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="F33" s="99" t="n">
+      <c r="G33" s="99" t="n">
         <v>0.9</v>
       </c>
-      <c r="G33" s="99" t="n">
+      <c r="H33" s="99" t="n">
         <v>1.13</v>
       </c>
-      <c r="H33" s="99" t="n">
+      <c r="I33" s="99" t="n">
         <v>1.93</v>
       </c>
-      <c r="I33" s="99" t="n">
+      <c r="J33" s="99" t="n">
         <v>0.65</v>
       </c>
-      <c r="J33" s="99" t="n">
+      <c r="K33" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="K33" s="99" t="n">
+      <c r="L33" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="L33" s="99" t="n">
+      <c r="M33" s="99" t="n">
         <v>0.44</v>
       </c>
-      <c r="M33" s="99" t="n">
+      <c r="N33" s="99" t="n">
         <v>-0.35</v>
       </c>
-      <c r="N33" s="99" t="n">
+      <c r="O33" s="99" t="n">
         <v>-0.73</v>
       </c>
-      <c r="O33" s="99" t="n">
+      <c r="P33" s="99" t="n">
         <v>-1</v>
       </c>
-      <c r="P33" s="99" t="n">
+      <c r="Q33" s="99" t="n">
         <v>-1.61</v>
       </c>
-      <c r="Q33" s="99" t="n">
+      <c r="R33" s="99" t="n">
         <v>-1.66</v>
       </c>
-      <c r="R33" s="99" t="n">
+      <c r="S33" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="S33" s="99" t="n">
+      <c r="T33" s="99" t="n">
         <v>-4.11</v>
       </c>
-      <c r="T33" s="99" t="n">
+      <c r="U33" s="99" t="n">
         <v>-3.76</v>
       </c>
-      <c r="U33" s="99" t="n">
+      <c r="V33" s="99" t="n">
         <v>-0.38</v>
       </c>
-      <c r="V33" s="99" t="n">
+      <c r="W33" s="99" t="n">
         <v>-0.28</v>
       </c>
-      <c r="W33" s="99" t="n">
+      <c r="X33" s="99" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="X33" s="99" t="n">
-        <v>3.06</v>
       </c>
       <c r="Y33" s="99" t="n">
         <v>3.06</v>
       </c>
       <c r="Z33" s="99" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA33" s="99" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA33" s="99" t="n">
+      <c r="AB33" s="99" t="n">
         <v>4.32</v>
       </c>
-      <c r="AB33" s="99" t="n">
+      <c r="AC33" s="99" t="n">
         <v>6.09</v>
       </c>
-      <c r="AC33" s="99" t="n">
+      <c r="AD33" s="99" t="n">
         <v>5.91</v>
       </c>
-      <c r="AD33" s="99" t="n">
+      <c r="AE33" s="99" t="n">
         <v>5.66</v>
-      </c>
-      <c r="AE33" s="99" t="n">
-        <v>3.52</v>
       </c>
     </row>
     <row r="34">
@@ -10041,91 +10041,91 @@
         <v>9.02</v>
       </c>
       <c r="C34" s="99" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D34" s="99" t="n">
         <v>10.76</v>
       </c>
-      <c r="D34" s="99" t="n">
+      <c r="E34" s="99" t="n">
         <v>11.54</v>
       </c>
-      <c r="E34" s="99" t="n">
+      <c r="F34" s="99" t="n">
         <v>11.48</v>
       </c>
-      <c r="F34" s="99" t="n">
+      <c r="G34" s="99" t="n">
         <v>11.95</v>
       </c>
-      <c r="G34" s="99" t="n">
+      <c r="H34" s="99" t="n">
         <v>12.67</v>
       </c>
-      <c r="H34" s="99" t="n">
+      <c r="I34" s="99" t="n">
         <v>11.04</v>
       </c>
-      <c r="I34" s="99" t="n">
+      <c r="J34" s="99" t="n">
         <v>10.68</v>
       </c>
-      <c r="J34" s="99" t="n">
+      <c r="K34" s="99" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="K34" s="99" t="n">
+      <c r="L34" s="99" t="n">
         <v>9.98</v>
       </c>
-      <c r="L34" s="99" t="n">
+      <c r="M34" s="99" t="n">
         <v>7.16</v>
       </c>
-      <c r="M34" s="99" t="n">
+      <c r="N34" s="99" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="N34" s="99" t="n">
+      <c r="O34" s="99" t="n">
         <v>7.37</v>
       </c>
-      <c r="O34" s="99" t="n">
+      <c r="P34" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="P34" s="99" t="n">
+      <c r="Q34" s="99" t="n">
         <v>7.12</v>
       </c>
-      <c r="Q34" s="99" t="n">
+      <c r="R34" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="R34" s="99" t="n">
+      <c r="S34" s="99" t="n">
         <v>5.31</v>
       </c>
-      <c r="S34" s="99" t="n">
+      <c r="T34" s="99" t="n">
         <v>4.85</v>
       </c>
-      <c r="T34" s="99" t="n">
+      <c r="U34" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="U34" s="99" t="n">
+      <c r="V34" s="99" t="n">
         <v>6.19</v>
       </c>
-      <c r="V34" s="99" t="n">
+      <c r="W34" s="99" t="n">
         <v>5.6</v>
       </c>
-      <c r="W34" s="99" t="n">
+      <c r="X34" s="99" t="n">
         <v>5.35</v>
-      </c>
-      <c r="X34" s="99" t="n">
-        <v>10.58</v>
       </c>
       <c r="Y34" s="99" t="n">
         <v>10.58</v>
       </c>
       <c r="Z34" s="99" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AA34" s="99" t="n">
         <v>8.9</v>
       </c>
-      <c r="AA34" s="99" t="n">
+      <c r="AB34" s="99" t="n">
         <v>7.88</v>
       </c>
-      <c r="AB34" s="99" t="n">
+      <c r="AC34" s="99" t="n">
         <v>10.75</v>
       </c>
-      <c r="AC34" s="99" t="n">
+      <c r="AD34" s="99" t="n">
         <v>11.21</v>
       </c>
-      <c r="AD34" s="99" t="n">
+      <c r="AE34" s="99" t="n">
         <v>10.31</v>
-      </c>
-      <c r="AE34" s="99" t="n">
-        <v>8.26</v>
       </c>
     </row>
     <row r="35">
@@ -10138,91 +10138,91 @@
         <v>21.97</v>
       </c>
       <c r="C35" s="99" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="D35" s="99" t="n">
         <v>15.42</v>
       </c>
-      <c r="D35" s="99" t="n">
+      <c r="E35" s="99" t="n">
         <v>74.7</v>
       </c>
-      <c r="E35" s="99" t="n">
+      <c r="F35" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="F35" s="99" t="n">
+      <c r="G35" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="G35" s="99" t="n">
+      <c r="H35" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="H35" s="99" t="n">
+      <c r="I35" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="I35" s="99" t="n">
+      <c r="J35" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="J35" s="99" t="n">
+      <c r="K35" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="K35" s="99" t="n">
+      <c r="L35" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="L35" s="99" t="n">
+      <c r="M35" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="M35" s="99" t="n">
+      <c r="N35" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="N35" s="99" t="n">
+      <c r="O35" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="O35" s="99" t="n">
+      <c r="P35" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="P35" s="99" t="n">
+      <c r="Q35" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="Q35" s="99" t="n">
+      <c r="R35" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="R35" s="99" t="n">
+      <c r="S35" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="S35" s="99" t="n">
+      <c r="T35" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="T35" s="99" t="n">
+      <c r="U35" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="U35" s="99" t="n">
+      <c r="V35" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="V35" s="99" t="n">
+      <c r="W35" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="W35" s="99" t="n">
+      <c r="X35" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="X35" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="Y35" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="Z35" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="AA35" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="AA35" s="99" t="n">
+      <c r="AB35" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="AB35" s="99" t="n">
+      <c r="AC35" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AC35" s="99" t="n">
+      <c r="AD35" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AD35" s="99" t="n">
+      <c r="AE35" s="99" t="n">
         <v>66.23</v>
-      </c>
-      <c r="AE35" s="99" t="n">
-        <v>24.22</v>
       </c>
     </row>
     <row r="36">
@@ -10235,91 +10235,91 @@
         <v>21.97</v>
       </c>
       <c r="C36" s="99" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="D36" s="99" t="n">
         <v>15.42</v>
       </c>
-      <c r="D36" s="99" t="n">
+      <c r="E36" s="99" t="n">
         <v>74.7</v>
       </c>
-      <c r="E36" s="99" t="n">
+      <c r="F36" s="99" t="n">
         <v>51.35</v>
       </c>
-      <c r="F36" s="99" t="n">
+      <c r="G36" s="99" t="n">
         <v>96.66</v>
       </c>
-      <c r="G36" s="99" t="n">
+      <c r="H36" s="99" t="n">
         <v>89.75</v>
       </c>
-      <c r="H36" s="99" t="n">
+      <c r="I36" s="99" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="I36" s="99" t="n">
+      <c r="J36" s="99" t="n">
         <v>77.02</v>
       </c>
-      <c r="J36" s="99" t="n">
+      <c r="K36" s="99" t="n">
         <v>73.3</v>
       </c>
-      <c r="K36" s="99" t="n">
+      <c r="L36" s="99" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="L36" s="99" t="n">
+      <c r="M36" s="99" t="n">
         <v>42.32</v>
       </c>
-      <c r="M36" s="99" t="n">
+      <c r="N36" s="99" t="n">
         <v>70.06</v>
       </c>
-      <c r="N36" s="99" t="n">
+      <c r="O36" s="99" t="n">
         <v>61.86</v>
       </c>
-      <c r="O36" s="99" t="n">
+      <c r="P36" s="99" t="n">
         <v>95.17</v>
       </c>
-      <c r="P36" s="99" t="n">
+      <c r="Q36" s="99" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="Q36" s="99" t="n">
+      <c r="R36" s="99" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="R36" s="99" t="n">
+      <c r="S36" s="99" t="n">
         <v>65.19</v>
       </c>
-      <c r="S36" s="99" t="n">
+      <c r="T36" s="99" t="n">
         <v>44.48</v>
       </c>
-      <c r="T36" s="99" t="n">
+      <c r="U36" s="99" t="n">
         <v>6.2</v>
       </c>
-      <c r="U36" s="99" t="n">
+      <c r="V36" s="99" t="n">
         <v>27.81</v>
       </c>
-      <c r="V36" s="99" t="n">
+      <c r="W36" s="99" t="n">
         <v>12.7</v>
       </c>
-      <c r="W36" s="99" t="n">
+      <c r="X36" s="99" t="n">
         <v>14.52</v>
-      </c>
-      <c r="X36" s="99" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="Y36" s="99" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="Z36" s="99" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="AA36" s="99" t="n">
         <v>13.66</v>
       </c>
-      <c r="AA36" s="99" t="n">
+      <c r="AB36" s="99" t="n">
         <v>17.16</v>
       </c>
-      <c r="AB36" s="99" t="n">
+      <c r="AC36" s="99" t="n">
         <v>47.94</v>
       </c>
-      <c r="AC36" s="99" t="n">
+      <c r="AD36" s="99" t="n">
         <v>40.09</v>
       </c>
-      <c r="AD36" s="99" t="n">
+      <c r="AE36" s="99" t="n">
         <v>66.23</v>
-      </c>
-      <c r="AE36" s="99" t="n">
-        <v>24.22</v>
       </c>
     </row>
     <row r="37">
@@ -10328,149 +10328,149 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B37" s="98" t="inlineStr">
+      <c r="B37" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C37" s="97" t="inlineStr">
+      <c r="D37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D37" s="97" t="inlineStr">
+      <c r="E37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E37" s="96" t="inlineStr">
+      <c r="F37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F37" s="96" t="inlineStr">
+      <c r="G37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G37" s="96" t="inlineStr">
+      <c r="H37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H37" s="96" t="inlineStr">
+      <c r="I37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I37" s="96" t="inlineStr">
+      <c r="J37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J37" s="96" t="inlineStr">
+      <c r="K37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K37" s="96" t="inlineStr">
+      <c r="L37" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L37" s="97" t="inlineStr">
+      <c r="M37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M37" s="97" t="inlineStr">
+      <c r="N37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N37" s="97" t="inlineStr">
+      <c r="O37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="97" t="inlineStr">
+      <c r="P37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P37" s="97" t="inlineStr">
+      <c r="Q37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q37" s="98" t="inlineStr">
+      <c r="R37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R37" s="98" t="inlineStr">
+      <c r="S37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S37" s="98" t="inlineStr">
+      <c r="T37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T37" s="98" t="inlineStr">
+      <c r="U37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U37" s="98" t="inlineStr">
+      <c r="V37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V37" s="98" t="inlineStr">
+      <c r="W37" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W37" s="97" t="inlineStr">
+      <c r="X37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X37" s="97" t="inlineStr">
+      <c r="Y37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y37" s="97" t="inlineStr">
+      <c r="Z37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z37" s="97" t="inlineStr">
+      <c r="AA37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA37" s="97" t="inlineStr">
+      <c r="AB37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB37" s="97" t="inlineStr">
+      <c r="AC37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC37" s="97" t="inlineStr">
+      <c r="AD37" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD37" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE37" s="96" t="inlineStr">
@@ -10486,94 +10486,94 @@
         </is>
       </c>
       <c r="B38" s="99" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="C38" s="99" t="n">
         <v>-7.29</v>
       </c>
-      <c r="C38" s="99" t="n">
+      <c r="D38" s="99" t="n">
         <v>-5.52</v>
       </c>
-      <c r="D38" s="99" t="n">
+      <c r="E38" s="99" t="n">
         <v>-7.32</v>
       </c>
-      <c r="E38" s="99" t="n">
+      <c r="F38" s="99" t="n">
         <v>-1.85</v>
       </c>
-      <c r="F38" s="99" t="n">
+      <c r="G38" s="99" t="n">
         <v>-2.87</v>
       </c>
-      <c r="G38" s="99" t="n">
+      <c r="H38" s="99" t="n">
         <v>-4.44</v>
       </c>
-      <c r="H38" s="99" t="n">
+      <c r="I38" s="99" t="n">
         <v>-4.15</v>
-      </c>
-      <c r="I38" s="99" t="n">
-        <v>-4.11</v>
       </c>
       <c r="J38" s="99" t="n">
         <v>-4.11</v>
       </c>
       <c r="K38" s="99" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="L38" s="99" t="n">
         <v>-6.33</v>
       </c>
-      <c r="L38" s="99" t="n">
+      <c r="M38" s="99" t="n">
         <v>-7.13</v>
       </c>
-      <c r="M38" s="99" t="n">
+      <c r="N38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="N38" s="99" t="n">
+      <c r="O38" s="99" t="n">
         <v>-5.28</v>
       </c>
-      <c r="O38" s="99" t="n">
+      <c r="P38" s="99" t="n">
         <v>-5.31</v>
       </c>
-      <c r="P38" s="99" t="n">
+      <c r="Q38" s="99" t="n">
         <v>-4.5</v>
       </c>
-      <c r="Q38" s="99" t="n">
+      <c r="R38" s="99" t="n">
         <v>-7.44</v>
       </c>
-      <c r="R38" s="99" t="n">
+      <c r="S38" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="S38" s="99" t="n">
+      <c r="T38" s="99" t="n">
         <v>-6.7</v>
       </c>
-      <c r="T38" s="99" t="n">
+      <c r="U38" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="U38" s="99" t="n">
+      <c r="V38" s="99" t="n">
         <v>-5.71</v>
       </c>
-      <c r="V38" s="99" t="n">
+      <c r="W38" s="99" t="n">
         <v>-5.33</v>
       </c>
-      <c r="W38" s="99" t="n">
+      <c r="X38" s="99" t="n">
         <v>-0.9</v>
       </c>
-      <c r="X38" s="99" t="n">
+      <c r="Y38" s="99" t="n">
         <v>0.04</v>
       </c>
-      <c r="Y38" s="99" t="n">
+      <c r="Z38" s="99" t="n">
         <v>-0.14</v>
       </c>
-      <c r="Z38" s="99" t="n">
+      <c r="AA38" s="99" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AA38" s="99" t="n">
+      <c r="AB38" s="99" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AB38" s="99" t="n">
+      <c r="AC38" s="99" t="n">
         <v>-1.63</v>
       </c>
-      <c r="AC38" s="99" t="n">
+      <c r="AD38" s="99" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AD38" s="99" t="n">
+      <c r="AE38" s="99" t="n">
         <v>0.8100000000000001</v>
-      </c>
-      <c r="AE38" s="99" t="n">
-        <v>-0.9</v>
       </c>
     </row>
     <row r="39">
@@ -10583,94 +10583,94 @@
         </is>
       </c>
       <c r="B39" s="99" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="C39" s="99" t="n">
         <v>-4.48</v>
       </c>
-      <c r="C39" s="99" t="n">
+      <c r="D39" s="99" t="n">
         <v>-2.82</v>
       </c>
-      <c r="D39" s="99" t="n">
+      <c r="E39" s="99" t="n">
         <v>-3.63</v>
       </c>
-      <c r="E39" s="99" t="n">
+      <c r="F39" s="99" t="n">
         <v>2.15</v>
       </c>
-      <c r="F39" s="99" t="n">
+      <c r="G39" s="99" t="n">
         <v>-2.13</v>
       </c>
-      <c r="G39" s="99" t="n">
+      <c r="H39" s="99" t="n">
         <v>-4.01</v>
       </c>
-      <c r="H39" s="99" t="n">
+      <c r="I39" s="99" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="I39" s="99" t="n">
-        <v>-5.22</v>
       </c>
       <c r="J39" s="99" t="n">
         <v>-5.22</v>
       </c>
       <c r="K39" s="99" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="L39" s="99" t="n">
         <v>-7.96</v>
       </c>
-      <c r="L39" s="99" t="n">
+      <c r="M39" s="99" t="n">
         <v>-9.43</v>
       </c>
-      <c r="M39" s="99" t="n">
+      <c r="N39" s="99" t="n">
         <v>-11.19</v>
       </c>
-      <c r="N39" s="99" t="n">
+      <c r="O39" s="99" t="n">
         <v>-9.5</v>
       </c>
-      <c r="O39" s="99" t="n">
+      <c r="P39" s="99" t="n">
         <v>-9.48</v>
       </c>
-      <c r="P39" s="99" t="n">
+      <c r="Q39" s="99" t="n">
         <v>-9.92</v>
       </c>
-      <c r="Q39" s="99" t="n">
+      <c r="R39" s="99" t="n">
         <v>-12.73</v>
       </c>
-      <c r="R39" s="99" t="n">
+      <c r="S39" s="99" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="S39" s="99" t="n">
+      <c r="T39" s="99" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="T39" s="99" t="n">
+      <c r="U39" s="99" t="n">
         <v>-5.98</v>
       </c>
-      <c r="U39" s="99" t="n">
+      <c r="V39" s="99" t="n">
         <v>-5.54</v>
       </c>
-      <c r="V39" s="99" t="n">
+      <c r="W39" s="99" t="n">
         <v>-4.26</v>
       </c>
-      <c r="W39" s="99" t="n">
+      <c r="X39" s="99" t="n">
         <v>-0.29</v>
       </c>
-      <c r="X39" s="99" t="n">
+      <c r="Y39" s="99" t="n">
         <v>-0.31</v>
       </c>
-      <c r="Y39" s="99" t="n">
+      <c r="Z39" s="99" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Z39" s="99" t="n">
+      <c r="AA39" s="99" t="n">
         <v>-3.12</v>
       </c>
-      <c r="AA39" s="99" t="n">
+      <c r="AB39" s="99" t="n">
         <v>-4.29</v>
       </c>
-      <c r="AB39" s="99" t="n">
+      <c r="AC39" s="99" t="n">
         <v>-4.51</v>
       </c>
-      <c r="AC39" s="99" t="n">
+      <c r="AD39" s="99" t="n">
         <v>-4.98</v>
       </c>
-      <c r="AD39" s="99" t="n">
+      <c r="AE39" s="99" t="n">
         <v>-3.88</v>
-      </c>
-      <c r="AE39" s="99" t="n">
-        <v>-2.44</v>
       </c>
     </row>
     <row r="40">
@@ -10680,94 +10680,94 @@
         </is>
       </c>
       <c r="B40" s="99" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="C40" s="99" t="n">
         <v>45.97</v>
       </c>
-      <c r="C40" s="99" t="n">
+      <c r="D40" s="99" t="n">
         <v>57.87</v>
       </c>
-      <c r="D40" s="99" t="n">
+      <c r="E40" s="99" t="n">
         <v>48.63</v>
       </c>
-      <c r="E40" s="99" t="n">
+      <c r="F40" s="99" t="n">
         <v>89.62</v>
       </c>
-      <c r="F40" s="99" t="n">
+      <c r="G40" s="99" t="n">
         <v>84.76000000000001</v>
       </c>
-      <c r="G40" s="99" t="n">
+      <c r="H40" s="99" t="n">
         <v>72.89</v>
       </c>
-      <c r="H40" s="99" t="n">
+      <c r="I40" s="99" t="n">
         <v>76.04000000000001</v>
-      </c>
-      <c r="I40" s="99" t="n">
-        <v>73.18000000000001</v>
       </c>
       <c r="J40" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
       <c r="K40" s="99" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="L40" s="99" t="n">
         <v>64.19</v>
       </c>
-      <c r="L40" s="99" t="n">
+      <c r="M40" s="99" t="n">
         <v>43.55</v>
       </c>
-      <c r="M40" s="99" t="n">
+      <c r="N40" s="99" t="n">
         <v>36.91</v>
       </c>
-      <c r="N40" s="99" t="n">
+      <c r="O40" s="99" t="n">
         <v>45.5</v>
       </c>
-      <c r="O40" s="99" t="n">
+      <c r="P40" s="99" t="n">
         <v>46.07</v>
       </c>
-      <c r="P40" s="99" t="n">
+      <c r="Q40" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="Q40" s="99" t="n">
+      <c r="R40" s="99" t="n">
         <v>10.06</v>
       </c>
-      <c r="R40" s="99" t="n">
+      <c r="S40" s="99" t="n">
         <v>14.47</v>
       </c>
-      <c r="S40" s="99" t="n">
+      <c r="T40" s="99" t="n">
         <v>15.02</v>
       </c>
-      <c r="T40" s="99" t="n">
+      <c r="U40" s="99" t="n">
         <v>16.6</v>
       </c>
-      <c r="U40" s="99" t="n">
+      <c r="V40" s="99" t="n">
         <v>19.01</v>
       </c>
-      <c r="V40" s="99" t="n">
+      <c r="W40" s="99" t="n">
         <v>22.94</v>
       </c>
-      <c r="W40" s="99" t="n">
+      <c r="X40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="X40" s="99" t="n">
+      <c r="Y40" s="99" t="n">
         <v>75.7</v>
       </c>
-      <c r="Y40" s="99" t="n">
+      <c r="Z40" s="99" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="Z40" s="99" t="n">
+      <c r="AA40" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="AA40" s="99" t="n">
+      <c r="AB40" s="99" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="AB40" s="99" t="n">
+      <c r="AC40" s="99" t="n">
         <v>66.31999999999999</v>
       </c>
-      <c r="AC40" s="99" t="n">
+      <c r="AD40" s="99" t="n">
         <v>62.89</v>
       </c>
-      <c r="AD40" s="99" t="n">
+      <c r="AE40" s="99" t="n">
         <v>71.14</v>
-      </c>
-      <c r="AE40" s="99" t="n">
-        <v>69.19</v>
       </c>
     </row>
     <row r="41">
@@ -10777,94 +10777,94 @@
         </is>
       </c>
       <c r="B41" s="99" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="C41" s="99" t="n">
         <v>50.28</v>
       </c>
-      <c r="C41" s="99" t="n">
+      <c r="D41" s="99" t="n">
         <v>58.22</v>
       </c>
-      <c r="D41" s="99" t="n">
+      <c r="E41" s="99" t="n">
         <v>52.42</v>
       </c>
-      <c r="E41" s="99" t="n">
+      <c r="F41" s="99" t="n">
         <v>77.31</v>
       </c>
-      <c r="F41" s="99" t="n">
+      <c r="G41" s="99" t="n">
         <v>71.64</v>
       </c>
-      <c r="G41" s="99" t="n">
+      <c r="H41" s="99" t="n">
         <v>61.74</v>
       </c>
-      <c r="H41" s="99" t="n">
+      <c r="I41" s="99" t="n">
         <v>63.04</v>
-      </c>
-      <c r="I41" s="99" t="n">
-        <v>60.77</v>
       </c>
       <c r="J41" s="99" t="n">
         <v>60.77</v>
       </c>
       <c r="K41" s="99" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="L41" s="99" t="n">
         <v>54.21</v>
       </c>
-      <c r="L41" s="99" t="n">
+      <c r="M41" s="99" t="n">
         <v>42.56</v>
       </c>
-      <c r="M41" s="99" t="n">
+      <c r="N41" s="99" t="n">
         <v>39.44</v>
       </c>
-      <c r="N41" s="99" t="n">
+      <c r="O41" s="99" t="n">
         <v>43.68</v>
       </c>
-      <c r="O41" s="99" t="n">
+      <c r="P41" s="99" t="n">
         <v>43.96</v>
       </c>
-      <c r="P41" s="99" t="n">
+      <c r="Q41" s="99" t="n">
         <v>46.79</v>
       </c>
-      <c r="Q41" s="99" t="n">
+      <c r="R41" s="99" t="n">
         <v>26.47</v>
       </c>
-      <c r="R41" s="99" t="n">
+      <c r="S41" s="99" t="n">
         <v>31.18</v>
       </c>
-      <c r="S41" s="99" t="n">
+      <c r="T41" s="99" t="n">
         <v>31.7</v>
       </c>
-      <c r="T41" s="99" t="n">
+      <c r="U41" s="99" t="n">
         <v>33.25</v>
       </c>
-      <c r="U41" s="99" t="n">
+      <c r="V41" s="99" t="n">
         <v>35.58</v>
       </c>
-      <c r="V41" s="99" t="n">
+      <c r="W41" s="99" t="n">
         <v>39.17</v>
       </c>
-      <c r="W41" s="99" t="n">
+      <c r="X41" s="99" t="n">
         <v>62.79</v>
       </c>
-      <c r="X41" s="99" t="n">
+      <c r="Y41" s="99" t="n">
         <v>63.09</v>
       </c>
-      <c r="Y41" s="99" t="n">
+      <c r="Z41" s="99" t="n">
         <v>62.51</v>
       </c>
-      <c r="Z41" s="99" t="n">
+      <c r="AA41" s="99" t="n">
         <v>59.46</v>
       </c>
-      <c r="AA41" s="99" t="n">
+      <c r="AB41" s="99" t="n">
         <v>59.6</v>
       </c>
-      <c r="AB41" s="99" t="n">
+      <c r="AC41" s="99" t="n">
         <v>58.83</v>
       </c>
-      <c r="AC41" s="99" t="n">
+      <c r="AD41" s="99" t="n">
         <v>57.26</v>
       </c>
-      <c r="AD41" s="99" t="n">
+      <c r="AE41" s="99" t="n">
         <v>60.15</v>
-      </c>
-      <c r="AE41" s="99" t="n">
-        <v>59.04</v>
       </c>
     </row>
     <row r="42">
@@ -10888,134 +10888,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="96" t="inlineStr">
+      <c r="E42" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="96" t="inlineStr">
+      <c r="G42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="96" t="inlineStr">
+      <c r="H42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="96" t="inlineStr">
+      <c r="I42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="96" t="inlineStr">
+      <c r="J42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="96" t="inlineStr">
+      <c r="K42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="96" t="inlineStr">
+      <c r="L42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="96" t="inlineStr">
+      <c r="M42" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="97" t="inlineStr">
+      <c r="N42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="98" t="inlineStr">
+      <c r="O42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O42" s="98" t="inlineStr">
+      <c r="P42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P42" s="98" t="inlineStr">
+      <c r="Q42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q42" s="98" t="inlineStr">
+      <c r="R42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R42" s="98" t="inlineStr">
+      <c r="S42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S42" s="98" t="inlineStr">
+      <c r="T42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="97" t="inlineStr">
+      <c r="U42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U42" s="98" t="inlineStr">
+      <c r="V42" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="97" t="inlineStr">
+      <c r="W42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="97" t="inlineStr">
+      <c r="X42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="97" t="inlineStr">
+      <c r="Y42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="97" t="inlineStr">
+      <c r="Z42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="97" t="inlineStr">
+      <c r="AA42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="97" t="inlineStr">
+      <c r="AB42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="97" t="inlineStr">
+      <c r="AC42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC42" s="97" t="inlineStr">
+      <c r="AD42" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE42" s="96" t="inlineStr">
@@ -11031,70 +11031,70 @@
         </is>
       </c>
       <c r="B43" s="99" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="C43" s="99" t="n">
         <v>0.33</v>
       </c>
-      <c r="C43" s="99" t="n">
+      <c r="D43" s="99" t="n">
         <v>0.71</v>
       </c>
-      <c r="D43" s="99" t="n">
+      <c r="E43" s="99" t="n">
         <v>0.63</v>
       </c>
-      <c r="E43" s="99" t="n">
+      <c r="F43" s="99" t="n">
         <v>1.1</v>
       </c>
-      <c r="F43" s="99" t="n">
+      <c r="G43" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="G43" s="99" t="n">
+      <c r="H43" s="99" t="n">
         <v>2.62</v>
       </c>
-      <c r="H43" s="99" t="n">
+      <c r="I43" s="99" t="n">
         <v>1.79</v>
       </c>
-      <c r="I43" s="99" t="n">
+      <c r="J43" s="99" t="n">
         <v>1.86</v>
       </c>
-      <c r="J43" s="99" t="n">
+      <c r="K43" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="K43" s="99" t="n">
+      <c r="L43" s="99" t="n">
         <v>0.8</v>
       </c>
-      <c r="L43" s="99" t="n">
+      <c r="M43" s="99" t="n">
         <v>0.66</v>
       </c>
-      <c r="M43" s="99" t="n">
+      <c r="N43" s="99" t="n">
         <v>0.39</v>
       </c>
-      <c r="N43" s="99" t="n">
+      <c r="O43" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="O43" s="99" t="n">
+      <c r="P43" s="99" t="n">
         <v>-2.39</v>
       </c>
-      <c r="P43" s="99" t="n">
+      <c r="Q43" s="99" t="n">
         <v>-1.83</v>
       </c>
-      <c r="Q43" s="99" t="n">
+      <c r="R43" s="99" t="n">
         <v>-2.05</v>
       </c>
-      <c r="R43" s="99" t="n">
+      <c r="S43" s="99" t="n">
         <v>-1.53</v>
       </c>
-      <c r="S43" s="99" t="n">
+      <c r="T43" s="99" t="n">
         <v>-0.95</v>
       </c>
-      <c r="T43" s="99" t="n">
+      <c r="U43" s="99" t="n">
         <v>-2.12</v>
       </c>
-      <c r="U43" s="99" t="n">
+      <c r="V43" s="99" t="n">
         <v>-2.46</v>
       </c>
-      <c r="V43" s="99" t="n">
+      <c r="W43" s="99" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="W43" s="99" t="n">
-        <v>-0.53</v>
       </c>
       <c r="X43" s="99" t="n">
         <v>-0.53</v>
@@ -11103,22 +11103,22 @@
         <v>-0.53</v>
       </c>
       <c r="Z43" s="99" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AA43" s="99" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AA43" s="99" t="n">
+      <c r="AB43" s="99" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AB43" s="99" t="n">
+      <c r="AC43" s="99" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AC43" s="99" t="n">
+      <c r="AD43" s="99" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AD43" s="99" t="n">
+      <c r="AE43" s="99" t="n">
         <v>0.42</v>
-      </c>
-      <c r="AE43" s="99" t="n">
-        <v>1.67</v>
       </c>
     </row>
     <row r="44">
@@ -11128,70 +11128,70 @@
         </is>
       </c>
       <c r="B44" s="99" t="n">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="C44" s="99" t="n">
         <v>2.33</v>
       </c>
       <c r="D44" s="99" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E44" s="99" t="n">
         <v>3.01</v>
       </c>
-      <c r="E44" s="99" t="n">
+      <c r="F44" s="99" t="n">
         <v>2.85</v>
       </c>
-      <c r="F44" s="99" t="n">
+      <c r="G44" s="99" t="n">
         <v>1.83</v>
       </c>
-      <c r="G44" s="99" t="n">
+      <c r="H44" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="I44" s="99" t="n">
         <v>-0.78</v>
       </c>
-      <c r="I44" s="99" t="n">
+      <c r="J44" s="99" t="n">
         <v>-1.02</v>
       </c>
-      <c r="J44" s="99" t="n">
+      <c r="K44" s="99" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="K44" s="99" t="n">
+      <c r="L44" s="99" t="n">
         <v>-1.47</v>
       </c>
-      <c r="L44" s="99" t="n">
+      <c r="M44" s="99" t="n">
         <v>-1.42</v>
       </c>
-      <c r="M44" s="99" t="n">
+      <c r="N44" s="99" t="n">
         <v>-1.81</v>
       </c>
-      <c r="N44" s="99" t="n">
+      <c r="O44" s="99" t="n">
         <v>-2.26</v>
       </c>
-      <c r="O44" s="99" t="n">
+      <c r="P44" s="99" t="n">
         <v>-2.35</v>
       </c>
-      <c r="P44" s="99" t="n">
+      <c r="Q44" s="99" t="n">
         <v>-1.57</v>
       </c>
-      <c r="Q44" s="99" t="n">
+      <c r="R44" s="99" t="n">
         <v>-0.54</v>
       </c>
-      <c r="R44" s="99" t="n">
+      <c r="S44" s="99" t="n">
         <v>1.03</v>
       </c>
-      <c r="S44" s="99" t="n">
+      <c r="T44" s="99" t="n">
         <v>1.94</v>
       </c>
-      <c r="T44" s="99" t="n">
+      <c r="U44" s="99" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="U44" s="99" t="n">
+      <c r="V44" s="99" t="n">
         <v>0.31</v>
       </c>
-      <c r="V44" s="99" t="n">
+      <c r="W44" s="99" t="n">
         <v>0.42</v>
-      </c>
-      <c r="W44" s="99" t="n">
-        <v>3.12</v>
       </c>
       <c r="X44" s="99" t="n">
         <v>3.12</v>
@@ -11200,22 +11200,22 @@
         <v>3.12</v>
       </c>
       <c r="Z44" s="99" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA44" s="99" t="n">
         <v>3.72</v>
       </c>
-      <c r="AA44" s="99" t="n">
+      <c r="AB44" s="99" t="n">
         <v>2.73</v>
       </c>
-      <c r="AB44" s="99" t="n">
+      <c r="AC44" s="99" t="n">
         <v>0.95</v>
       </c>
-      <c r="AC44" s="99" t="n">
+      <c r="AD44" s="99" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD44" s="99" t="n">
+      <c r="AE44" s="99" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AE44" s="99" t="n">
-        <v>1.69</v>
       </c>
     </row>
     <row r="45">
@@ -11225,70 +11225,70 @@
         </is>
       </c>
       <c r="B45" s="99" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="C45" s="99" t="n">
         <v>50.34</v>
       </c>
-      <c r="C45" s="99" t="n">
+      <c r="D45" s="99" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="D45" s="99" t="n">
+      <c r="E45" s="99" t="n">
         <v>65.09</v>
       </c>
-      <c r="E45" s="99" t="n">
+      <c r="F45" s="99" t="n">
         <v>86.66</v>
       </c>
-      <c r="F45" s="99" t="n">
+      <c r="G45" s="99" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="G45" s="99" t="n">
+      <c r="H45" s="99" t="n">
         <v>88</v>
       </c>
-      <c r="H45" s="99" t="n">
+      <c r="I45" s="99" t="n">
         <v>77.98</v>
       </c>
-      <c r="I45" s="99" t="n">
+      <c r="J45" s="99" t="n">
         <v>59.82</v>
       </c>
-      <c r="J45" s="99" t="n">
+      <c r="K45" s="99" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="K45" s="99" t="n">
+      <c r="L45" s="99" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="L45" s="99" t="n">
+      <c r="M45" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="M45" s="99" t="n">
+      <c r="N45" s="99" t="n">
         <v>60.96</v>
       </c>
-      <c r="N45" s="99" t="n">
+      <c r="O45" s="99" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="O45" s="99" t="n">
+      <c r="P45" s="99" t="n">
         <v>20.58</v>
       </c>
-      <c r="P45" s="99" t="n">
+      <c r="Q45" s="99" t="n">
         <v>30.12</v>
       </c>
-      <c r="Q45" s="99" t="n">
+      <c r="R45" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="R45" s="99" t="n">
+      <c r="S45" s="99" t="n">
         <v>13.57</v>
       </c>
-      <c r="S45" s="99" t="n">
+      <c r="T45" s="99" t="n">
         <v>28.44</v>
       </c>
-      <c r="T45" s="99" t="n">
+      <c r="U45" s="99" t="n">
         <v>44.72</v>
       </c>
-      <c r="U45" s="99" t="n">
+      <c r="V45" s="99" t="n">
         <v>14.66</v>
       </c>
-      <c r="V45" s="99" t="n">
+      <c r="W45" s="99" t="n">
         <v>28.1</v>
-      </c>
-      <c r="W45" s="99" t="n">
-        <v>80.38</v>
       </c>
       <c r="X45" s="99" t="n">
         <v>80.38</v>
@@ -11297,22 +11297,22 @@
         <v>80.38</v>
       </c>
       <c r="Z45" s="99" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="AA45" s="99" t="n">
         <v>68.92</v>
       </c>
-      <c r="AA45" s="99" t="n">
+      <c r="AB45" s="99" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="AB45" s="99" t="n">
+      <c r="AC45" s="99" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="AC45" s="99" t="n">
+      <c r="AD45" s="99" t="n">
         <v>63.9</v>
       </c>
-      <c r="AD45" s="99" t="n">
+      <c r="AE45" s="99" t="n">
         <v>90.77</v>
-      </c>
-      <c r="AE45" s="99" t="n">
-        <v>89.34</v>
       </c>
     </row>
     <row r="46">
@@ -11322,70 +11322,70 @@
         </is>
       </c>
       <c r="B46" s="99" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="C46" s="99" t="n">
         <v>60.97</v>
       </c>
-      <c r="C46" s="99" t="n">
+      <c r="D46" s="99" t="n">
         <v>74.77</v>
       </c>
-      <c r="D46" s="99" t="n">
+      <c r="E46" s="99" t="n">
         <v>69.34999999999999</v>
       </c>
-      <c r="E46" s="99" t="n">
+      <c r="F46" s="99" t="n">
         <v>78.83</v>
       </c>
-      <c r="F46" s="99" t="n">
+      <c r="G46" s="99" t="n">
         <v>80.52</v>
       </c>
-      <c r="G46" s="99" t="n">
+      <c r="H46" s="99" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="H46" s="99" t="n">
+      <c r="I46" s="99" t="n">
         <v>68.98</v>
       </c>
-      <c r="I46" s="99" t="n">
+      <c r="J46" s="99" t="n">
         <v>58.07</v>
       </c>
-      <c r="J46" s="99" t="n">
+      <c r="K46" s="99" t="n">
         <v>65.81</v>
       </c>
-      <c r="K46" s="99" t="n">
+      <c r="L46" s="99" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="L46" s="99" t="n">
+      <c r="M46" s="99" t="n">
         <v>58.52</v>
       </c>
-      <c r="M46" s="99" t="n">
+      <c r="N46" s="99" t="n">
         <v>51.86</v>
       </c>
-      <c r="N46" s="99" t="n">
+      <c r="O46" s="99" t="n">
         <v>16.23</v>
       </c>
-      <c r="O46" s="99" t="n">
+      <c r="P46" s="99" t="n">
         <v>25.94</v>
       </c>
-      <c r="P46" s="99" t="n">
+      <c r="Q46" s="99" t="n">
         <v>31.58</v>
       </c>
-      <c r="Q46" s="99" t="n">
+      <c r="R46" s="99" t="n">
         <v>22.65</v>
       </c>
-      <c r="R46" s="99" t="n">
+      <c r="S46" s="99" t="n">
         <v>24.26</v>
       </c>
-      <c r="S46" s="99" t="n">
+      <c r="T46" s="99" t="n">
         <v>38.08</v>
       </c>
-      <c r="T46" s="99" t="n">
+      <c r="U46" s="99" t="n">
         <v>49.25</v>
       </c>
-      <c r="U46" s="99" t="n">
+      <c r="V46" s="99" t="n">
         <v>35.21</v>
       </c>
-      <c r="V46" s="99" t="n">
+      <c r="W46" s="99" t="n">
         <v>49.75</v>
-      </c>
-      <c r="W46" s="99" t="n">
-        <v>76.69</v>
       </c>
       <c r="X46" s="99" t="n">
         <v>76.69</v>
@@ -11394,22 +11394,22 @@
         <v>76.69</v>
       </c>
       <c r="Z46" s="99" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="AA46" s="99" t="n">
         <v>73.23999999999999</v>
       </c>
-      <c r="AA46" s="99" t="n">
+      <c r="AB46" s="99" t="n">
         <v>73.2</v>
       </c>
-      <c r="AB46" s="99" t="n">
+      <c r="AC46" s="99" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="AC46" s="99" t="n">
+      <c r="AD46" s="99" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="AD46" s="99" t="n">
+      <c r="AE46" s="99" t="n">
         <v>83.54000000000001</v>
-      </c>
-      <c r="AE46" s="99" t="n">
-        <v>82.43000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -11418,119 +11418,119 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B47" s="97" t="inlineStr">
+      <c r="B47" s="98" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C47" s="97" t="inlineStr">
+      <c r="D47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D47" s="97" t="inlineStr">
+      <c r="E47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E47" s="97" t="inlineStr">
+      <c r="F47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F47" s="96" t="inlineStr">
+      <c r="G47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G47" s="96" t="inlineStr">
+      <c r="H47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H47" s="96" t="inlineStr">
+      <c r="I47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I47" s="96" t="inlineStr">
+      <c r="J47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J47" s="96" t="inlineStr">
+      <c r="K47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K47" s="96" t="inlineStr">
+      <c r="L47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L47" s="97" t="inlineStr">
+      <c r="M47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M47" s="96" t="inlineStr">
+      <c r="N47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="96" t="inlineStr">
+      <c r="O47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="96" t="inlineStr">
+      <c r="P47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P47" s="96" t="inlineStr">
+      <c r="Q47" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q47" s="98" t="inlineStr">
+      <c r="R47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R47" s="97" t="inlineStr">
+      <c r="S47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S47" s="98" t="inlineStr">
+      <c r="T47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T47" s="98" t="inlineStr">
+      <c r="U47" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U47" s="97" t="inlineStr">
+      <c r="V47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V47" s="97" t="inlineStr">
+      <c r="W47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W47" s="97" t="inlineStr">
+      <c r="X47" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="X47" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="Y47" s="96" t="inlineStr">
@@ -11576,94 +11576,94 @@
         </is>
       </c>
       <c r="B48" s="99" t="n">
-        <v>5.39</v>
+        <v>2.72</v>
       </c>
       <c r="C48" s="99" t="n">
         <v>5.39</v>
       </c>
       <c r="D48" s="99" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E48" s="99" t="n">
         <v>5.38</v>
       </c>
-      <c r="E48" s="99" t="n">
+      <c r="F48" s="99" t="n">
         <v>6.9</v>
       </c>
-      <c r="F48" s="99" t="n">
+      <c r="G48" s="99" t="n">
         <v>7.31</v>
       </c>
-      <c r="G48" s="99" t="n">
+      <c r="H48" s="99" t="n">
         <v>7.21</v>
       </c>
-      <c r="H48" s="99" t="n">
+      <c r="I48" s="99" t="n">
         <v>6.84</v>
       </c>
-      <c r="I48" s="99" t="n">
+      <c r="J48" s="99" t="n">
         <v>7.46</v>
       </c>
-      <c r="J48" s="99" t="n">
+      <c r="K48" s="99" t="n">
         <v>6.69</v>
       </c>
-      <c r="K48" s="99" t="n">
+      <c r="L48" s="99" t="n">
         <v>5.73</v>
       </c>
-      <c r="L48" s="99" t="n">
+      <c r="M48" s="99" t="n">
         <v>6.27</v>
       </c>
-      <c r="M48" s="99" t="n">
+      <c r="N48" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="N48" s="99" t="n">
+      <c r="O48" s="99" t="n">
         <v>7.48</v>
       </c>
-      <c r="O48" s="99" t="n">
+      <c r="P48" s="99" t="n">
         <v>6.99</v>
       </c>
-      <c r="P48" s="99" t="n">
+      <c r="Q48" s="99" t="n">
         <v>7.27</v>
       </c>
-      <c r="Q48" s="99" t="n">
+      <c r="R48" s="99" t="n">
         <v>5.46</v>
       </c>
-      <c r="R48" s="99" t="n">
+      <c r="S48" s="99" t="n">
         <v>6.4</v>
       </c>
-      <c r="S48" s="99" t="n">
+      <c r="T48" s="99" t="n">
         <v>6.18</v>
       </c>
-      <c r="T48" s="99" t="n">
+      <c r="U48" s="99" t="n">
         <v>5.98</v>
       </c>
-      <c r="U48" s="99" t="n">
+      <c r="V48" s="99" t="n">
         <v>7.51</v>
       </c>
-      <c r="V48" s="99" t="n">
+      <c r="W48" s="99" t="n">
         <v>7.66</v>
       </c>
-      <c r="W48" s="99" t="n">
+      <c r="X48" s="99" t="n">
         <v>7.64</v>
       </c>
-      <c r="X48" s="99" t="n">
+      <c r="Y48" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="Y48" s="99" t="n">
+      <c r="Z48" s="99" t="n">
         <v>10.73</v>
       </c>
-      <c r="Z48" s="99" t="n">
+      <c r="AA48" s="99" t="n">
         <v>13.95</v>
       </c>
-      <c r="AA48" s="99" t="n">
+      <c r="AB48" s="99" t="n">
         <v>6.95</v>
       </c>
-      <c r="AB48" s="99" t="n">
+      <c r="AC48" s="99" t="n">
         <v>10.48</v>
       </c>
-      <c r="AC48" s="99" t="n">
+      <c r="AD48" s="99" t="n">
         <v>10.57</v>
       </c>
-      <c r="AD48" s="99" t="n">
+      <c r="AE48" s="99" t="n">
         <v>8.84</v>
-      </c>
-      <c r="AE48" s="99" t="n">
-        <v>7.83</v>
       </c>
     </row>
     <row r="49">
@@ -11673,94 +11673,94 @@
         </is>
       </c>
       <c r="B49" s="99" t="n">
-        <v>12.83</v>
+        <v>10</v>
       </c>
       <c r="C49" s="99" t="n">
         <v>12.83</v>
       </c>
       <c r="D49" s="99" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="E49" s="99" t="n">
         <v>12.79</v>
       </c>
-      <c r="E49" s="99" t="n">
+      <c r="F49" s="99" t="n">
         <v>15.25</v>
       </c>
-      <c r="F49" s="99" t="n">
+      <c r="G49" s="99" t="n">
         <v>15.64</v>
       </c>
-      <c r="G49" s="99" t="n">
+      <c r="H49" s="99" t="n">
         <v>15.29</v>
       </c>
-      <c r="H49" s="99" t="n">
+      <c r="I49" s="99" t="n">
         <v>14.9</v>
       </c>
-      <c r="I49" s="99" t="n">
+      <c r="J49" s="99" t="n">
         <v>14.75</v>
       </c>
-      <c r="J49" s="99" t="n">
+      <c r="K49" s="99" t="n">
         <v>14.79</v>
       </c>
-      <c r="K49" s="99" t="n">
+      <c r="L49" s="99" t="n">
         <v>13.96</v>
       </c>
-      <c r="L49" s="99" t="n">
+      <c r="M49" s="99" t="n">
         <v>14.46</v>
       </c>
-      <c r="M49" s="99" t="n">
+      <c r="N49" s="99" t="n">
         <v>14.07</v>
       </c>
-      <c r="N49" s="99" t="n">
+      <c r="O49" s="99" t="n">
         <v>14.24</v>
       </c>
-      <c r="O49" s="99" t="n">
+      <c r="P49" s="99" t="n">
         <v>14.96</v>
       </c>
-      <c r="P49" s="99" t="n">
+      <c r="Q49" s="99" t="n">
         <v>15.21</v>
       </c>
-      <c r="Q49" s="99" t="n">
+      <c r="R49" s="99" t="n">
         <v>12.06</v>
       </c>
-      <c r="R49" s="99" t="n">
+      <c r="S49" s="99" t="n">
         <v>12.77</v>
       </c>
-      <c r="S49" s="99" t="n">
+      <c r="T49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="T49" s="99" t="n">
+      <c r="U49" s="99" t="n">
         <v>11.57</v>
       </c>
-      <c r="U49" s="99" t="n">
+      <c r="V49" s="99" t="n">
         <v>11.58</v>
       </c>
-      <c r="V49" s="99" t="n">
+      <c r="W49" s="99" t="n">
         <v>12.04</v>
       </c>
-      <c r="W49" s="99" t="n">
+      <c r="X49" s="99" t="n">
         <v>11.38</v>
       </c>
-      <c r="X49" s="99" t="n">
+      <c r="Y49" s="99" t="n">
         <v>11.44</v>
       </c>
-      <c r="Y49" s="99" t="n">
+      <c r="Z49" s="99" t="n">
         <v>11.79</v>
       </c>
-      <c r="Z49" s="99" t="n">
+      <c r="AA49" s="99" t="n">
         <v>11.18</v>
       </c>
-      <c r="AA49" s="99" t="n">
+      <c r="AB49" s="99" t="n">
         <v>10.81</v>
       </c>
-      <c r="AB49" s="99" t="n">
+      <c r="AC49" s="99" t="n">
         <v>10.8</v>
       </c>
-      <c r="AC49" s="99" t="n">
+      <c r="AD49" s="99" t="n">
         <v>12.69</v>
       </c>
-      <c r="AD49" s="99" t="n">
+      <c r="AE49" s="99" t="n">
         <v>12.14</v>
-      </c>
-      <c r="AE49" s="99" t="n">
-        <v>10.89</v>
       </c>
     </row>
     <row r="50">
@@ -11770,94 +11770,94 @@
         </is>
       </c>
       <c r="B50" s="99" t="n">
-        <v>51.33</v>
+        <v>31.21</v>
       </c>
       <c r="C50" s="99" t="n">
         <v>51.33</v>
       </c>
       <c r="D50" s="99" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="E50" s="99" t="n">
         <v>51.88</v>
       </c>
-      <c r="E50" s="99" t="n">
+      <c r="F50" s="99" t="n">
         <v>80.16</v>
       </c>
-      <c r="F50" s="99" t="n">
+      <c r="G50" s="99" t="n">
         <v>88.77</v>
       </c>
-      <c r="G50" s="99" t="n">
+      <c r="H50" s="99" t="n">
         <v>85.37</v>
       </c>
-      <c r="H50" s="99" t="n">
+      <c r="I50" s="99" t="n">
         <v>83.76000000000001</v>
       </c>
-      <c r="I50" s="99" t="n">
+      <c r="J50" s="99" t="n">
         <v>84.20999999999999</v>
       </c>
-      <c r="J50" s="99" t="n">
+      <c r="K50" s="99" t="n">
         <v>82</v>
       </c>
-      <c r="K50" s="99" t="n">
+      <c r="L50" s="99" t="n">
         <v>68.75</v>
       </c>
-      <c r="L50" s="99" t="n">
+      <c r="M50" s="99" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="M50" s="99" t="n">
+      <c r="N50" s="99" t="n">
         <v>68.95</v>
       </c>
-      <c r="N50" s="99" t="n">
+      <c r="O50" s="99" t="n">
         <v>67.75</v>
       </c>
-      <c r="O50" s="99" t="n">
+      <c r="P50" s="99" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="P50" s="99" t="n">
+      <c r="Q50" s="99" t="n">
         <v>68.14</v>
       </c>
-      <c r="Q50" s="99" t="n">
+      <c r="R50" s="99" t="n">
         <v>46.32</v>
       </c>
-      <c r="R50" s="99" t="n">
+      <c r="S50" s="99" t="n">
         <v>55.3</v>
       </c>
-      <c r="S50" s="99" t="n">
+      <c r="T50" s="99" t="n">
         <v>47.35</v>
       </c>
-      <c r="T50" s="99" t="n">
+      <c r="U50" s="99" t="n">
         <v>37.44</v>
       </c>
-      <c r="U50" s="99" t="n">
+      <c r="V50" s="99" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="V50" s="99" t="n">
+      <c r="W50" s="99" t="n">
         <v>73.75</v>
       </c>
-      <c r="W50" s="99" t="n">
+      <c r="X50" s="99" t="n">
         <v>84.38</v>
       </c>
-      <c r="X50" s="99" t="n">
+      <c r="Y50" s="99" t="n">
         <v>84.61</v>
       </c>
-      <c r="Y50" s="99" t="n">
+      <c r="Z50" s="99" t="n">
         <v>82.87</v>
       </c>
-      <c r="Z50" s="99" t="n">
+      <c r="AA50" s="99" t="n">
         <v>80.63</v>
       </c>
-      <c r="AA50" s="99" t="n">
+      <c r="AB50" s="99" t="n">
         <v>76.7</v>
       </c>
-      <c r="AB50" s="99" t="n">
+      <c r="AC50" s="99" t="n">
         <v>75.8</v>
       </c>
-      <c r="AC50" s="99" t="n">
+      <c r="AD50" s="99" t="n">
         <v>75.66</v>
       </c>
-      <c r="AD50" s="99" t="n">
+      <c r="AE50" s="99" t="n">
         <v>68.2</v>
-      </c>
-      <c r="AE50" s="99" t="n">
-        <v>67.75</v>
       </c>
     </row>
     <row r="51">
@@ -11867,94 +11867,94 @@
         </is>
       </c>
       <c r="B51" s="99" t="n">
-        <v>60.39</v>
+        <v>47.91</v>
       </c>
       <c r="C51" s="99" t="n">
         <v>60.39</v>
       </c>
       <c r="D51" s="99" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="E51" s="99" t="n">
         <v>60.68</v>
       </c>
-      <c r="E51" s="99" t="n">
+      <c r="F51" s="99" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="F51" s="99" t="n">
+      <c r="G51" s="99" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="G51" s="99" t="n">
+      <c r="H51" s="99" t="n">
         <v>73.63</v>
       </c>
-      <c r="H51" s="99" t="n">
+      <c r="I51" s="99" t="n">
         <v>72.53</v>
       </c>
-      <c r="I51" s="99" t="n">
+      <c r="J51" s="99" t="n">
         <v>72.69</v>
       </c>
-      <c r="J51" s="99" t="n">
+      <c r="K51" s="99" t="n">
         <v>71.09</v>
       </c>
-      <c r="K51" s="99" t="n">
+      <c r="L51" s="99" t="n">
         <v>64.05</v>
       </c>
-      <c r="L51" s="99" t="n">
+      <c r="M51" s="99" t="n">
         <v>62.55</v>
       </c>
-      <c r="M51" s="99" t="n">
+      <c r="N51" s="99" t="n">
         <v>63.94</v>
       </c>
-      <c r="N51" s="99" t="n">
+      <c r="O51" s="99" t="n">
         <v>63.41</v>
       </c>
-      <c r="O51" s="99" t="n">
+      <c r="P51" s="99" t="n">
         <v>62.86</v>
       </c>
-      <c r="P51" s="99" t="n">
+      <c r="Q51" s="99" t="n">
         <v>63.52</v>
       </c>
-      <c r="Q51" s="99" t="n">
+      <c r="R51" s="99" t="n">
         <v>54.48</v>
       </c>
-      <c r="R51" s="99" t="n">
+      <c r="S51" s="99" t="n">
         <v>58.24</v>
       </c>
-      <c r="S51" s="99" t="n">
+      <c r="T51" s="99" t="n">
         <v>55.62</v>
       </c>
-      <c r="T51" s="99" t="n">
+      <c r="U51" s="99" t="n">
         <v>52.73</v>
       </c>
-      <c r="U51" s="99" t="n">
+      <c r="V51" s="99" t="n">
         <v>63.24</v>
       </c>
-      <c r="V51" s="99" t="n">
+      <c r="W51" s="99" t="n">
         <v>65.06</v>
       </c>
-      <c r="W51" s="99" t="n">
+      <c r="X51" s="99" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="X51" s="99" t="n">
+      <c r="Y51" s="99" t="n">
         <v>67.56</v>
       </c>
-      <c r="Y51" s="99" t="n">
+      <c r="Z51" s="99" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="Z51" s="99" t="n">
+      <c r="AA51" s="99" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="AA51" s="99" t="n">
+      <c r="AB51" s="99" t="n">
         <v>63.2</v>
       </c>
-      <c r="AB51" s="99" t="n">
+      <c r="AC51" s="99" t="n">
         <v>62.77</v>
       </c>
-      <c r="AC51" s="99" t="n">
+      <c r="AD51" s="99" t="n">
         <v>62.7</v>
       </c>
-      <c r="AD51" s="99" t="n">
+      <c r="AE51" s="99" t="n">
         <v>59.22</v>
-      </c>
-      <c r="AE51" s="99" t="n">
-        <v>59.02</v>
       </c>
     </row>
     <row r="52">
@@ -11973,134 +11973,134 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D52" s="97" t="inlineStr">
+      <c r="D52" s="98" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E52" s="96" t="inlineStr">
+      <c r="F52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F52" s="96" t="inlineStr">
+      <c r="G52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G52" s="96" t="inlineStr">
+      <c r="H52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H52" s="96" t="inlineStr">
+      <c r="I52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I52" s="97" t="inlineStr">
+      <c r="J52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J52" s="97" t="inlineStr">
+      <c r="K52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K52" s="96" t="inlineStr">
+      <c r="L52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L52" s="97" t="inlineStr">
+      <c r="M52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M52" s="96" t="inlineStr">
+      <c r="N52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N52" s="97" t="inlineStr">
+      <c r="O52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O52" s="96" t="inlineStr">
+      <c r="P52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P52" s="97" t="inlineStr">
+      <c r="Q52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q52" s="98" t="inlineStr">
+      <c r="R52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R52" s="98" t="inlineStr">
+      <c r="S52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S52" s="98" t="inlineStr">
+      <c r="T52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T52" s="98" t="inlineStr">
+      <c r="U52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U52" s="98" t="inlineStr">
+      <c r="V52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V52" s="98" t="inlineStr">
+      <c r="W52" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W52" s="97" t="inlineStr">
+      <c r="X52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X52" s="97" t="inlineStr">
+      <c r="Y52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y52" s="97" t="inlineStr">
+      <c r="Z52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z52" s="96" t="inlineStr">
+      <c r="AA52" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA52" s="97" t="inlineStr">
+      <c r="AB52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB52" s="97" t="inlineStr">
+      <c r="AC52" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC52" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AD52" s="96" t="inlineStr">
@@ -12121,94 +12121,94 @@
         </is>
       </c>
       <c r="B53" s="99" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="C53" s="99" t="n">
         <v>0.05</v>
       </c>
-      <c r="C53" s="99" t="n">
+      <c r="D53" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="D53" s="99" t="n">
+      <c r="E53" s="99" t="n">
         <v>0.11</v>
       </c>
-      <c r="E53" s="99" t="n">
+      <c r="F53" s="99" t="n">
         <v>1.51</v>
       </c>
-      <c r="F53" s="99" t="n">
+      <c r="G53" s="99" t="n">
         <v>0.6</v>
       </c>
-      <c r="G53" s="99" t="n">
+      <c r="H53" s="99" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H53" s="99" t="n">
+      <c r="I53" s="99" t="n">
         <v>0.87</v>
       </c>
-      <c r="I53" s="99" t="n">
+      <c r="J53" s="99" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J53" s="99" t="n">
+      <c r="K53" s="99" t="n">
         <v>0.28</v>
       </c>
-      <c r="K53" s="99" t="n">
+      <c r="L53" s="99" t="n">
         <v>1.12</v>
       </c>
-      <c r="L53" s="99" t="n">
+      <c r="M53" s="99" t="n">
         <v>-2.16</v>
       </c>
-      <c r="M53" s="99" t="n">
+      <c r="N53" s="99" t="n">
         <v>-2.28</v>
       </c>
-      <c r="N53" s="99" t="n">
+      <c r="O53" s="99" t="n">
         <v>-3.34</v>
       </c>
-      <c r="O53" s="99" t="n">
+      <c r="P53" s="99" t="n">
         <v>-2.14</v>
       </c>
-      <c r="P53" s="99" t="n">
+      <c r="Q53" s="99" t="n">
         <v>-3.08</v>
       </c>
-      <c r="Q53" s="99" t="n">
+      <c r="R53" s="99" t="n">
         <v>-2.29</v>
       </c>
-      <c r="R53" s="99" t="n">
+      <c r="S53" s="99" t="n">
         <v>-2.9</v>
       </c>
-      <c r="S53" s="99" t="n">
+      <c r="T53" s="99" t="n">
         <v>-1.93</v>
       </c>
-      <c r="T53" s="99" t="n">
+      <c r="U53" s="99" t="n">
         <v>-2.01</v>
       </c>
-      <c r="U53" s="99" t="n">
+      <c r="V53" s="99" t="n">
         <v>-3.58</v>
       </c>
-      <c r="V53" s="99" t="n">
+      <c r="W53" s="99" t="n">
         <v>-4.62</v>
       </c>
-      <c r="W53" s="99" t="n">
+      <c r="X53" s="99" t="n">
         <v>-2.75</v>
       </c>
-      <c r="X53" s="99" t="n">
+      <c r="Y53" s="99" t="n">
         <v>-3.14</v>
       </c>
-      <c r="Y53" s="99" t="n">
+      <c r="Z53" s="99" t="n">
         <v>-4.63</v>
       </c>
-      <c r="Z53" s="99" t="n">
+      <c r="AA53" s="99" t="n">
         <v>-4.96</v>
       </c>
-      <c r="AA53" s="99" t="n">
+      <c r="AB53" s="99" t="n">
         <v>-5.36</v>
       </c>
-      <c r="AB53" s="99" t="n">
+      <c r="AC53" s="99" t="n">
         <v>-4.69</v>
       </c>
-      <c r="AC53" s="99" t="n">
+      <c r="AD53" s="99" t="n">
         <v>-5.1</v>
       </c>
-      <c r="AD53" s="99" t="n">
+      <c r="AE53" s="99" t="n">
         <v>-5.2</v>
-      </c>
-      <c r="AE53" s="99" t="n">
-        <v>-5.7</v>
       </c>
     </row>
     <row r="54">
@@ -12218,94 +12218,94 @@
         </is>
       </c>
       <c r="B54" s="99" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="C54" s="99" t="n">
         <v>-4.48</v>
       </c>
-      <c r="C54" s="99" t="n">
+      <c r="D54" s="99" t="n">
         <v>-5.85</v>
       </c>
-      <c r="D54" s="99" t="n">
+      <c r="E54" s="99" t="n">
         <v>-4.68</v>
       </c>
-      <c r="E54" s="99" t="n">
+      <c r="F54" s="99" t="n">
         <v>-2.89</v>
       </c>
-      <c r="F54" s="99" t="n">
+      <c r="G54" s="99" t="n">
         <v>-3.77</v>
       </c>
-      <c r="G54" s="99" t="n">
+      <c r="H54" s="99" t="n">
         <v>-6.01</v>
       </c>
-      <c r="H54" s="99" t="n">
+      <c r="I54" s="99" t="n">
         <v>-6.35</v>
       </c>
-      <c r="I54" s="99" t="n">
+      <c r="J54" s="99" t="n">
         <v>-6.86</v>
       </c>
-      <c r="J54" s="99" t="n">
+      <c r="K54" s="99" t="n">
         <v>-7.99</v>
       </c>
-      <c r="K54" s="99" t="n">
+      <c r="L54" s="99" t="n">
         <v>-6.6</v>
       </c>
-      <c r="L54" s="99" t="n">
+      <c r="M54" s="99" t="n">
         <v>-8.43</v>
       </c>
-      <c r="M54" s="99" t="n">
+      <c r="N54" s="99" t="n">
         <v>-8.75</v>
       </c>
-      <c r="N54" s="99" t="n">
+      <c r="O54" s="99" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="O54" s="99" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="P54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="Q54" s="99" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="R54" s="99" t="n">
         <v>-9.26</v>
       </c>
-      <c r="R54" s="99" t="n">
+      <c r="S54" s="99" t="n">
         <v>-9.44</v>
       </c>
-      <c r="S54" s="99" t="n">
+      <c r="T54" s="99" t="n">
         <v>-9.02</v>
       </c>
-      <c r="T54" s="99" t="n">
+      <c r="U54" s="99" t="n">
         <v>-10.35</v>
       </c>
-      <c r="U54" s="99" t="n">
+      <c r="V54" s="99" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="V54" s="99" t="n">
+      <c r="W54" s="99" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="W54" s="99" t="n">
+      <c r="X54" s="99" t="n">
         <v>-7.18</v>
       </c>
-      <c r="X54" s="99" t="n">
+      <c r="Y54" s="99" t="n">
         <v>-6.04</v>
       </c>
-      <c r="Y54" s="99" t="n">
+      <c r="Z54" s="99" t="n">
         <v>-5.64</v>
       </c>
-      <c r="Z54" s="99" t="n">
+      <c r="AA54" s="99" t="n">
         <v>-4.72</v>
       </c>
-      <c r="AA54" s="99" t="n">
+      <c r="AB54" s="99" t="n">
         <v>-5.61</v>
       </c>
-      <c r="AB54" s="99" t="n">
+      <c r="AC54" s="99" t="n">
         <v>-5.62</v>
       </c>
-      <c r="AC54" s="99" t="n">
+      <c r="AD54" s="99" t="n">
         <v>-4.58</v>
       </c>
-      <c r="AD54" s="99" t="n">
+      <c r="AE54" s="99" t="n">
         <v>-4.48</v>
-      </c>
-      <c r="AE54" s="99" t="n">
-        <v>-5.43</v>
       </c>
     </row>
     <row r="55">
@@ -12315,94 +12315,94 @@
         </is>
       </c>
       <c r="B55" s="99" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="C55" s="99" t="n">
         <v>35.7</v>
       </c>
-      <c r="C55" s="99" t="n">
+      <c r="D55" s="99" t="n">
         <v>34.48</v>
       </c>
-      <c r="D55" s="99" t="n">
+      <c r="E55" s="99" t="n">
         <v>44.35</v>
       </c>
-      <c r="E55" s="99" t="n">
+      <c r="F55" s="99" t="n">
         <v>85.76000000000001</v>
       </c>
-      <c r="F55" s="99" t="n">
+      <c r="G55" s="99" t="n">
         <v>82.23</v>
       </c>
-      <c r="G55" s="99" t="n">
+      <c r="H55" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="H55" s="99" t="n">
+      <c r="I55" s="99" t="n">
         <v>71.87</v>
       </c>
-      <c r="I55" s="99" t="n">
+      <c r="J55" s="99" t="n">
         <v>50.77</v>
       </c>
-      <c r="J55" s="99" t="n">
+      <c r="K55" s="99" t="n">
         <v>48.68</v>
       </c>
-      <c r="K55" s="99" t="n">
+      <c r="L55" s="99" t="n">
         <v>83.53</v>
       </c>
-      <c r="L55" s="99" t="n">
+      <c r="M55" s="99" t="n">
         <v>43.83</v>
       </c>
-      <c r="M55" s="99" t="n">
+      <c r="N55" s="99" t="n">
         <v>73.12</v>
       </c>
-      <c r="N55" s="99" t="n">
+      <c r="O55" s="99" t="n">
         <v>55.36</v>
       </c>
-      <c r="O55" s="99" t="n">
+      <c r="P55" s="99" t="n">
         <v>67.8</v>
       </c>
-      <c r="P55" s="99" t="n">
+      <c r="Q55" s="99" t="n">
         <v>54.91</v>
       </c>
-      <c r="Q55" s="99" t="n">
+      <c r="R55" s="99" t="n">
         <v>31.87</v>
       </c>
-      <c r="R55" s="99" t="n">
+      <c r="S55" s="99" t="n">
         <v>35.24</v>
       </c>
-      <c r="S55" s="99" t="n">
+      <c r="T55" s="99" t="n">
         <v>39.87</v>
       </c>
-      <c r="T55" s="99" t="n">
+      <c r="U55" s="99" t="n">
         <v>5.87</v>
       </c>
-      <c r="U55" s="99" t="n">
+      <c r="V55" s="99" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="V55" s="99" t="n">
+      <c r="W55" s="99" t="n">
         <v>16.74</v>
       </c>
-      <c r="W55" s="99" t="n">
+      <c r="X55" s="99" t="n">
         <v>32.54</v>
       </c>
-      <c r="X55" s="99" t="n">
+      <c r="Y55" s="99" t="n">
         <v>82.56</v>
       </c>
-      <c r="Y55" s="99" t="n">
+      <c r="Z55" s="99" t="n">
         <v>77.58</v>
       </c>
-      <c r="Z55" s="99" t="n">
+      <c r="AA55" s="99" t="n">
         <v>88.48</v>
       </c>
-      <c r="AA55" s="99" t="n">
+      <c r="AB55" s="99" t="n">
         <v>71.72</v>
       </c>
-      <c r="AB55" s="99" t="n">
+      <c r="AC55" s="99" t="n">
         <v>65.42</v>
       </c>
-      <c r="AC55" s="99" t="n">
+      <c r="AD55" s="99" t="n">
         <v>94.41</v>
       </c>
-      <c r="AD55" s="99" t="n">
+      <c r="AE55" s="99" t="n">
         <v>93.34999999999999</v>
-      </c>
-      <c r="AE55" s="99" t="n">
-        <v>86.56</v>
       </c>
     </row>
     <row r="56">
@@ -12412,94 +12412,94 @@
         </is>
       </c>
       <c r="B56" s="99" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="C56" s="99" t="n">
         <v>45.48</v>
       </c>
-      <c r="C56" s="99" t="n">
+      <c r="D56" s="99" t="n">
         <v>44.93</v>
       </c>
-      <c r="D56" s="99" t="n">
+      <c r="E56" s="99" t="n">
         <v>52.35</v>
       </c>
-      <c r="E56" s="99" t="n">
+      <c r="F56" s="99" t="n">
         <v>78.61</v>
       </c>
-      <c r="F56" s="99" t="n">
+      <c r="G56" s="99" t="n">
         <v>75.48</v>
       </c>
-      <c r="G56" s="99" t="n">
+      <c r="H56" s="99" t="n">
         <v>57.98</v>
       </c>
-      <c r="H56" s="99" t="n">
+      <c r="I56" s="99" t="n">
         <v>66.2</v>
       </c>
-      <c r="I56" s="99" t="n">
+      <c r="J56" s="99" t="n">
         <v>52.83</v>
       </c>
-      <c r="J56" s="99" t="n">
+      <c r="K56" s="99" t="n">
         <v>51.58</v>
       </c>
-      <c r="K56" s="99" t="n">
+      <c r="L56" s="99" t="n">
         <v>74.97</v>
       </c>
-      <c r="L56" s="99" t="n">
+      <c r="M56" s="99" t="n">
         <v>45.92</v>
       </c>
-      <c r="M56" s="99" t="n">
+      <c r="N56" s="99" t="n">
         <v>59.76</v>
       </c>
-      <c r="N56" s="99" t="n">
+      <c r="O56" s="99" t="n">
         <v>48.71</v>
       </c>
-      <c r="O56" s="99" t="n">
+      <c r="P56" s="99" t="n">
         <v>53.61</v>
       </c>
-      <c r="P56" s="99" t="n">
+      <c r="Q56" s="99" t="n">
         <v>45.19</v>
       </c>
-      <c r="Q56" s="99" t="n">
+      <c r="R56" s="99" t="n">
         <v>32.83</v>
       </c>
-      <c r="R56" s="99" t="n">
+      <c r="S56" s="99" t="n">
         <v>34.58</v>
       </c>
-      <c r="S56" s="99" t="n">
+      <c r="T56" s="99" t="n">
         <v>37.2</v>
       </c>
-      <c r="T56" s="99" t="n">
+      <c r="U56" s="99" t="n">
         <v>16.31</v>
       </c>
-      <c r="U56" s="99" t="n">
+      <c r="V56" s="99" t="n">
         <v>22.99</v>
       </c>
-      <c r="V56" s="99" t="n">
+      <c r="W56" s="99" t="n">
         <v>32.1</v>
       </c>
-      <c r="W56" s="99" t="n">
+      <c r="X56" s="99" t="n">
         <v>48.66</v>
       </c>
-      <c r="X56" s="99" t="n">
+      <c r="Y56" s="99" t="n">
         <v>80.73</v>
       </c>
-      <c r="Y56" s="99" t="n">
+      <c r="Z56" s="99" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="Z56" s="99" t="n">
+      <c r="AA56" s="99" t="n">
         <v>83.84</v>
       </c>
-      <c r="AA56" s="99" t="n">
+      <c r="AB56" s="99" t="n">
         <v>74.67</v>
       </c>
-      <c r="AB56" s="99" t="n">
+      <c r="AC56" s="99" t="n">
         <v>72.3</v>
       </c>
-      <c r="AC56" s="99" t="n">
+      <c r="AD56" s="99" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="AD56" s="99" t="n">
+      <c r="AE56" s="99" t="n">
         <v>84.26000000000001</v>
-      </c>
-      <c r="AE56" s="99" t="n">
-        <v>78.34</v>
       </c>
     </row>
     <row r="57">
@@ -12523,134 +12523,134 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="E57" s="96" t="inlineStr">
+      <c r="E57" s="97" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F57" s="96" t="inlineStr">
+      <c r="G57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G57" s="97" t="inlineStr">
+      <c r="H57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H57" s="96" t="inlineStr">
+      <c r="I57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I57" s="96" t="inlineStr">
+      <c r="J57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J57" s="97" t="inlineStr">
+      <c r="K57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K57" s="96" t="inlineStr">
+      <c r="L57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L57" s="96" t="inlineStr">
+      <c r="M57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M57" s="96" t="inlineStr">
+      <c r="N57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N57" s="96" t="inlineStr">
+      <c r="O57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O57" s="96" t="inlineStr">
+      <c r="P57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P57" s="96" t="inlineStr">
+      <c r="Q57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q57" s="98" t="inlineStr">
+      <c r="R57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R57" s="98" t="inlineStr">
+      <c r="S57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S57" s="98" t="inlineStr">
+      <c r="T57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T57" s="98" t="inlineStr">
+      <c r="U57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U57" s="98" t="inlineStr">
+      <c r="V57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V57" s="98" t="inlineStr">
+      <c r="W57" s="98" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W57" s="97" t="inlineStr">
+      <c r="X57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X57" s="97" t="inlineStr">
+      <c r="Y57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y57" s="97" t="inlineStr">
+      <c r="Z57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z57" s="96" t="inlineStr">
+      <c r="AA57" s="96" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA57" s="97" t="inlineStr">
+      <c r="AB57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB57" s="97" t="inlineStr">
+      <c r="AC57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC57" s="97" t="inlineStr">
+      <c r="AD57" s="97" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD57" s="96" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE57" s="96" t="inlineStr">
@@ -12666,94 +12666,94 @@
         </is>
       </c>
       <c r="B58" s="99" t="n">
-        <v>4.03</v>
+        <v>2.94</v>
       </c>
       <c r="C58" s="99" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="D58" s="99" t="n">
         <v>5.36</v>
       </c>
-      <c r="D58" s="99" t="n">
+      <c r="E58" s="99" t="n">
         <v>4.62</v>
       </c>
-      <c r="E58" s="99" t="n">
+      <c r="F58" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="F58" s="99" t="n">
+      <c r="G58" s="99" t="n">
         <v>4.27</v>
       </c>
-      <c r="G58" s="99" t="n">
+      <c r="H58" s="99" t="n">
         <v>2.96</v>
       </c>
-      <c r="H58" s="99" t="n">
+      <c r="I58" s="99" t="n">
         <v>4.58</v>
       </c>
-      <c r="I58" s="99" t="n">
+      <c r="J58" s="99" t="n">
         <v>3.04</v>
       </c>
-      <c r="J58" s="99" t="n">
+      <c r="K58" s="99" t="n">
         <v>2.66</v>
       </c>
-      <c r="K58" s="99" t="n">
+      <c r="L58" s="99" t="n">
         <v>4.35</v>
       </c>
-      <c r="L58" s="99" t="n">
+      <c r="M58" s="99" t="n">
         <v>3.06</v>
       </c>
-      <c r="M58" s="99" t="n">
+      <c r="N58" s="99" t="n">
         <v>3.02</v>
       </c>
-      <c r="N58" s="99" t="n">
+      <c r="O58" s="99" t="n">
         <v>1.68</v>
       </c>
-      <c r="O58" s="99" t="n">
+      <c r="P58" s="99" t="n">
         <v>2.95</v>
-      </c>
-      <c r="P58" s="99" t="n">
-        <v>1.45</v>
       </c>
       <c r="Q58" s="99" t="n">
         <v>1.45</v>
       </c>
       <c r="R58" s="99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S58" s="99" t="n">
         <v>0.74</v>
       </c>
-      <c r="S58" s="99" t="n">
+      <c r="T58" s="99" t="n">
         <v>2.08</v>
       </c>
-      <c r="T58" s="99" t="n">
+      <c r="U58" s="99" t="n">
         <v>1.67</v>
       </c>
-      <c r="U58" s="99" t="n">
+      <c r="V58" s="99" t="n">
         <v>1.7</v>
       </c>
-      <c r="V58" s="99" t="n">
+      <c r="W58" s="99" t="n">
         <v>-0.21</v>
       </c>
-      <c r="W58" s="99" t="n">
+      <c r="X58" s="99" t="n">
         <v>2.05</v>
       </c>
-      <c r="X58" s="99" t="n">
+      <c r="Y58" s="99" t="n">
         <v>2.36</v>
       </c>
-      <c r="Y58" s="99" t="n">
+      <c r="Z58" s="99" t="n">
         <v>1.88</v>
       </c>
-      <c r="Z58" s="99" t="n">
+      <c r="AA58" s="99" t="n">
         <v>1.39</v>
       </c>
-      <c r="AA58" s="99" t="n">
+      <c r="AB58" s="99" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB58" s="99" t="n">
+      <c r="AC58" s="99" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC58" s="99" t="n">
+      <c r="AD58" s="99" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD58" s="99" t="n">
+      <c r="AE58" s="99" t="n">
         <v>0.73</v>
-      </c>
-      <c r="AE58" s="99" t="n">
-        <v>-0.02</v>
       </c>
     </row>
     <row r="59">
@@ -12763,94 +12763,94 @@
         </is>
       </c>
       <c r="B59" s="99" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="C59" s="99" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="D59" s="99" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="E59" s="99" t="n">
         <v>7.78</v>
       </c>
-      <c r="C59" s="99" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="D59" s="99" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="E59" s="99" t="n">
+      <c r="F59" s="99" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="F59" s="99" t="n">
+      <c r="G59" s="99" t="n">
         <v>6.31</v>
       </c>
-      <c r="G59" s="99" t="n">
+      <c r="H59" s="99" t="n">
         <v>4.66</v>
-      </c>
-      <c r="H59" s="99" t="n">
-        <v>3.7</v>
       </c>
       <c r="I59" s="99" t="n">
         <v>3.7</v>
       </c>
       <c r="J59" s="99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K59" s="99" t="n">
         <v>1.72</v>
       </c>
-      <c r="K59" s="99" t="n">
+      <c r="L59" s="99" t="n">
         <v>3.46</v>
       </c>
-      <c r="L59" s="99" t="n">
+      <c r="M59" s="99" t="n">
         <v>2.34</v>
       </c>
-      <c r="M59" s="99" t="n">
+      <c r="N59" s="99" t="n">
         <v>1.26</v>
       </c>
-      <c r="N59" s="99" t="n">
+      <c r="O59" s="99" t="n">
         <v>0.84</v>
       </c>
-      <c r="O59" s="99" t="n">
+      <c r="P59" s="99" t="n">
         <v>1.71</v>
       </c>
-      <c r="P59" s="99" t="n">
+      <c r="Q59" s="99" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q59" s="99" t="n">
+      <c r="R59" s="99" t="n">
         <v>0.68</v>
       </c>
-      <c r="R59" s="99" t="n">
+      <c r="S59" s="99" t="n">
         <v>0.48</v>
       </c>
-      <c r="S59" s="99" t="n">
+      <c r="T59" s="99" t="n">
         <v>2.38</v>
       </c>
-      <c r="T59" s="99" t="n">
+      <c r="U59" s="99" t="n">
         <v>1.75</v>
       </c>
-      <c r="U59" s="99" t="n">
+      <c r="V59" s="99" t="n">
         <v>3.59</v>
       </c>
-      <c r="V59" s="99" t="n">
+      <c r="W59" s="99" t="n">
         <v>3.65</v>
       </c>
-      <c r="W59" s="99" t="n">
+      <c r="X59" s="99" t="n">
         <v>4.49</v>
       </c>
-      <c r="X59" s="99" t="n">
+      <c r="Y59" s="99" t="n">
         <v>5.4</v>
       </c>
-      <c r="Y59" s="99" t="n">
+      <c r="Z59" s="99" t="n">
         <v>5.24</v>
       </c>
-      <c r="Z59" s="99" t="n">
+      <c r="AA59" s="99" t="n">
         <v>6.57</v>
       </c>
-      <c r="AA59" s="99" t="n">
+      <c r="AB59" s="99" t="n">
         <v>5.43</v>
       </c>
-      <c r="AB59" s="99" t="n">
+      <c r="AC59" s="99" t="n">
         <v>4.7</v>
       </c>
-      <c r="AC59" s="99" t="n">
+      <c r="AD59" s="99" t="n">
         <v>5.08</v>
       </c>
-      <c r="AD59" s="99" t="n">
+      <c r="AE59" s="99" t="n">
         <v>5.28</v>
-      </c>
-      <c r="AE59" s="99" t="n">
-        <v>4.39</v>
       </c>
     </row>
     <row r="60">
@@ -12860,94 +12860,94 @@
         </is>
       </c>
       <c r="B60" s="99" t="n">
-        <v>49.48</v>
+        <v>42.18</v>
       </c>
       <c r="C60" s="99" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D60" s="99" t="n">
         <v>55.81</v>
       </c>
-      <c r="D60" s="99" t="n">
+      <c r="E60" s="99" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="E60" s="99" t="n">
+      <c r="F60" s="99" t="n">
         <v>83.8</v>
       </c>
-      <c r="F60" s="99" t="n">
+      <c r="G60" s="99" t="n">
         <v>76.95</v>
       </c>
-      <c r="G60" s="99" t="n">
+      <c r="H60" s="99" t="n">
         <v>59.47</v>
       </c>
-      <c r="H60" s="99" t="n">
+      <c r="I60" s="99" t="n">
         <v>69.06</v>
       </c>
-      <c r="I60" s="99" t="n">
+      <c r="J60" s="99" t="n">
         <v>59.71</v>
       </c>
-      <c r="J60" s="99" t="n">
+      <c r="K60" s="99" t="n">
         <v>50.15</v>
       </c>
-      <c r="K60" s="99" t="n">
+      <c r="L60" s="99" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="L60" s="99" t="n">
+      <c r="M60" s="99" t="n">
         <v>65.67</v>
       </c>
-      <c r="M60" s="99" t="n">
+      <c r="N60" s="99" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="N60" s="99" t="n">
+      <c r="O60" s="99" t="n">
         <v>60.74</v>
       </c>
-      <c r="O60" s="99" t="n">
+      <c r="P60" s="99" t="n">
         <v>69.64</v>
       </c>
-      <c r="P60" s="99" t="n">
+      <c r="Q60" s="99" t="n">
         <v>56.63</v>
       </c>
-      <c r="Q60" s="99" t="n">
+      <c r="R60" s="99" t="n">
         <v>34.87</v>
       </c>
-      <c r="R60" s="99" t="n">
+      <c r="S60" s="99" t="n">
         <v>25.25</v>
       </c>
-      <c r="S60" s="99" t="n">
+      <c r="T60" s="99" t="n">
         <v>36.38</v>
       </c>
-      <c r="T60" s="99" t="n">
+      <c r="U60" s="99" t="n">
         <v>13.61</v>
       </c>
-      <c r="U60" s="99" t="n">
+      <c r="V60" s="99" t="n">
         <v>28.38</v>
       </c>
-      <c r="V60" s="99" t="n">
+      <c r="W60" s="99" t="n">
         <v>29.73</v>
       </c>
-      <c r="W60" s="99" t="n">
+      <c r="X60" s="99" t="n">
         <v>46.54</v>
       </c>
-      <c r="X60" s="99" t="n">
+      <c r="Y60" s="99" t="n">
         <v>93.47</v>
       </c>
-      <c r="Y60" s="99" t="n">
+      <c r="Z60" s="99" t="n">
         <v>92.75</v>
       </c>
-      <c r="Z60" s="99" t="n">
+      <c r="AA60" s="99" t="n">
         <v>94.58</v>
       </c>
-      <c r="AA60" s="99" t="n">
+      <c r="AB60" s="99" t="n">
         <v>91.78</v>
       </c>
-      <c r="AB60" s="99" t="n">
+      <c r="AC60" s="99" t="n">
         <v>88.26000000000001</v>
       </c>
-      <c r="AC60" s="99" t="n">
+      <c r="AD60" s="99" t="n">
         <v>85.2</v>
       </c>
-      <c r="AD60" s="99" t="n">
+      <c r="AE60" s="99" t="n">
         <v>89.55</v>
-      </c>
-      <c r="AE60" s="99" t="n">
-        <v>84.34</v>
       </c>
     </row>
     <row r="61">
@@ -12957,94 +12957,94 @@
         </is>
       </c>
       <c r="B61" s="99" t="n">
-        <v>55.46</v>
+        <v>50.55</v>
       </c>
       <c r="C61" s="99" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="D61" s="99" t="n">
         <v>59.76</v>
       </c>
-      <c r="D61" s="99" t="n">
+      <c r="E61" s="99" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="E61" s="99" t="n">
+      <c r="F61" s="99" t="n">
         <v>78.38</v>
       </c>
-      <c r="F61" s="99" t="n">
+      <c r="G61" s="99" t="n">
         <v>72.42</v>
       </c>
-      <c r="G61" s="99" t="n">
+      <c r="H61" s="99" t="n">
         <v>59.91</v>
       </c>
-      <c r="H61" s="99" t="n">
+      <c r="I61" s="99" t="n">
         <v>66</v>
       </c>
-      <c r="I61" s="99" t="n">
+      <c r="J61" s="99" t="n">
         <v>59.4</v>
       </c>
-      <c r="J61" s="99" t="n">
+      <c r="K61" s="99" t="n">
         <v>52.95</v>
       </c>
-      <c r="K61" s="99" t="n">
+      <c r="L61" s="99" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="L61" s="99" t="n">
+      <c r="M61" s="99" t="n">
         <v>61.14</v>
       </c>
-      <c r="M61" s="99" t="n">
+      <c r="N61" s="99" t="n">
         <v>62.6</v>
       </c>
-      <c r="N61" s="99" t="n">
+      <c r="O61" s="99" t="n">
         <v>57.16</v>
       </c>
-      <c r="O61" s="99" t="n">
+      <c r="P61" s="99" t="n">
         <v>62.56</v>
       </c>
-      <c r="P61" s="99" t="n">
+      <c r="Q61" s="99" t="n">
         <v>52.29</v>
       </c>
-      <c r="Q61" s="99" t="n">
+      <c r="R61" s="99" t="n">
         <v>37.42</v>
       </c>
-      <c r="R61" s="99" t="n">
+      <c r="S61" s="99" t="n">
         <v>31.32</v>
       </c>
-      <c r="S61" s="99" t="n">
+      <c r="T61" s="99" t="n">
         <v>40.38</v>
       </c>
-      <c r="T61" s="99" t="n">
+      <c r="U61" s="99" t="n">
         <v>26.19</v>
       </c>
-      <c r="U61" s="99" t="n">
+      <c r="V61" s="99" t="n">
         <v>42.54</v>
       </c>
-      <c r="V61" s="99" t="n">
+      <c r="W61" s="99" t="n">
         <v>43.82</v>
       </c>
-      <c r="W61" s="99" t="n">
+      <c r="X61" s="99" t="n">
         <v>58.62</v>
       </c>
-      <c r="X61" s="99" t="n">
+      <c r="Y61" s="99" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="Y61" s="99" t="n">
+      <c r="Z61" s="99" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="Z61" s="99" t="n">
+      <c r="AA61" s="99" t="n">
         <v>88.2</v>
       </c>
-      <c r="AA61" s="99" t="n">
+      <c r="AB61" s="99" t="n">
         <v>84.89</v>
       </c>
-      <c r="AB61" s="99" t="n">
+      <c r="AC61" s="99" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="AC61" s="99" t="n">
+      <c r="AD61" s="99" t="n">
         <v>79.09</v>
       </c>
-      <c r="AD61" s="99" t="n">
+      <c r="AE61" s="99" t="n">
         <v>81.34999999999999</v>
-      </c>
-      <c r="AE61" s="99" t="n">
-        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -13057,7 +13057,7 @@
     <row r="64">
       <c r="A64" s="95" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:26.09&gt;=15;hk50:RNG120:34.13&gt;=25;hk50:RSI6:98.28&gt;=76;hk50:RSI19:86.55&gt;=73</t>
+          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RSI11:91.05&gt;=87;sh:RSI2:99.99&gt;=96;kc:RNG60:26.36&gt;=25;kc:RSI10:90.1&gt;=76;kc:RSI5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RSI10:93.78&gt;=90;cy:RSI9:94.69&gt;=65;hk50:RNG60:26.19&gt;=15;hk50:RNG120:31.41&gt;=25;hk50:RSI6:87.91&gt;=76;hk50:RSI19:81.7&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>241004</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>241003</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>241002</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>240827</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>240826</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>240823</t>
         </is>
       </c>
     </row>
@@ -6537,114 +6537,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J2" s="93" t="inlineStr">
+      <c r="J2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="93" t="inlineStr">
+      <c r="L2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="93" t="inlineStr">
+      <c r="M2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="93" t="inlineStr">
+      <c r="N2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="94" t="inlineStr">
+      <c r="O2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="94" t="inlineStr">
+      <c r="P2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="94" t="inlineStr">
+      <c r="Q2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="94" t="inlineStr">
+      <c r="R2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="94" t="inlineStr">
+      <c r="S2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="94" t="inlineStr">
+      <c r="T2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="94" t="inlineStr">
+      <c r="U2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="94" t="inlineStr">
+      <c r="V2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="94" t="inlineStr">
+      <c r="W2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="94" t="inlineStr">
+      <c r="X2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="94" t="inlineStr">
+      <c r="Y2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="94" t="inlineStr">
+      <c r="Z2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA2" s="94" t="inlineStr">
+      <c r="AB2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB2" s="94" t="inlineStr">
+      <c r="AC2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="94" t="inlineStr">
+      <c r="AD2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD2" s="93" t="inlineStr">
+      <c r="AE2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE2" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -6667,31 +6667,31 @@
         <v>12.81</v>
       </c>
       <c r="F3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="G3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="G3" s="95" t="n">
+      <c r="H3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="H3" s="95" t="n">
+      <c r="I3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="I3" s="95" t="n">
+      <c r="J3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="J3" s="95" t="n">
+      <c r="K3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="K3" s="95" t="n">
+      <c r="L3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="L3" s="95" t="n">
+      <c r="M3" s="95" t="n">
         <v>-7.25</v>
       </c>
-      <c r="M3" s="95" t="n">
+      <c r="N3" s="95" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="N3" s="95" t="n">
-        <v>-9.81</v>
       </c>
       <c r="O3" s="95" t="n">
         <v>-9.81</v>
@@ -6700,49 +6700,49 @@
         <v>-9.81</v>
       </c>
       <c r="Q3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="R3" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="R3" s="95" t="n">
+      <c r="S3" s="95" t="n">
         <v>-9.82</v>
       </c>
-      <c r="S3" s="95" t="n">
+      <c r="T3" s="95" t="n">
         <v>-9.44</v>
       </c>
-      <c r="T3" s="95" t="n">
+      <c r="U3" s="95" t="n">
         <v>-9.26</v>
       </c>
-      <c r="U3" s="95" t="n">
+      <c r="V3" s="95" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="V3" s="95" t="n">
+      <c r="W3" s="95" t="n">
         <v>-7.94</v>
       </c>
-      <c r="W3" s="95" t="n">
+      <c r="X3" s="95" t="n">
         <v>-8.34</v>
       </c>
-      <c r="X3" s="95" t="n">
+      <c r="Y3" s="95" t="n">
         <v>-7.43</v>
       </c>
-      <c r="Y3" s="95" t="n">
+      <c r="Z3" s="95" t="n">
         <v>-7.87</v>
       </c>
-      <c r="Z3" s="95" t="n">
+      <c r="AA3" s="95" t="n">
         <v>-6.78</v>
       </c>
-      <c r="AA3" s="95" t="n">
+      <c r="AB3" s="95" t="n">
         <v>-7.9</v>
       </c>
-      <c r="AB3" s="95" t="n">
+      <c r="AC3" s="95" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="AC3" s="95" t="n">
+      <c r="AD3" s="95" t="n">
         <v>-7.46</v>
       </c>
-      <c r="AD3" s="95" t="n">
+      <c r="AE3" s="95" t="n">
         <v>-7.49</v>
-      </c>
-      <c r="AE3" s="95" t="n">
-        <v>-7.68</v>
       </c>
     </row>
     <row r="4">
@@ -6764,31 +6764,31 @@
         <v>8.710000000000001</v>
       </c>
       <c r="F4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="G4" s="95" t="n">
+      <c r="H4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="H4" s="95" t="n">
+      <c r="I4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="I4" s="95" t="n">
+      <c r="J4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="J4" s="95" t="n">
+      <c r="K4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="K4" s="95" t="n">
+      <c r="L4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="L4" s="95" t="n">
+      <c r="M4" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="M4" s="95" t="n">
+      <c r="N4" s="95" t="n">
         <v>-10.85</v>
-      </c>
-      <c r="N4" s="95" t="n">
-        <v>-12.12</v>
       </c>
       <c r="O4" s="95" t="n">
         <v>-12.12</v>
@@ -6797,49 +6797,49 @@
         <v>-12.12</v>
       </c>
       <c r="Q4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="R4" s="95" t="n">
         <v>-11.77</v>
       </c>
-      <c r="R4" s="95" t="n">
+      <c r="S4" s="95" t="n">
         <v>-11.13</v>
       </c>
-      <c r="S4" s="95" t="n">
+      <c r="T4" s="95" t="n">
         <v>-11.05</v>
       </c>
-      <c r="T4" s="95" t="n">
+      <c r="U4" s="95" t="n">
         <v>-10.42</v>
       </c>
-      <c r="U4" s="95" t="n">
+      <c r="V4" s="95" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="V4" s="95" t="n">
+      <c r="W4" s="95" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="W4" s="95" t="n">
+      <c r="X4" s="95" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="X4" s="95" t="n">
+      <c r="Y4" s="95" t="n">
         <v>-8.65</v>
       </c>
-      <c r="Y4" s="95" t="n">
+      <c r="Z4" s="95" t="n">
         <v>-7.71</v>
       </c>
-      <c r="Z4" s="95" t="n">
+      <c r="AA4" s="95" t="n">
         <v>-6.12</v>
       </c>
-      <c r="AA4" s="95" t="n">
+      <c r="AB4" s="95" t="n">
         <v>-7.13</v>
       </c>
-      <c r="AB4" s="95" t="n">
+      <c r="AC4" s="95" t="n">
         <v>-6.9</v>
       </c>
-      <c r="AC4" s="95" t="n">
+      <c r="AD4" s="95" t="n">
         <v>-6.27</v>
       </c>
-      <c r="AD4" s="95" t="n">
+      <c r="AE4" s="95" t="n">
         <v>-5.67</v>
-      </c>
-      <c r="AE4" s="95" t="n">
-        <v>-5.33</v>
       </c>
     </row>
     <row r="5">
@@ -6861,31 +6861,31 @@
         <v>99.75</v>
       </c>
       <c r="F5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="G5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="G5" s="95" t="n">
+      <c r="H5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="H5" s="95" t="n">
+      <c r="I5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="I5" s="95" t="n">
+      <c r="J5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="J5" s="95" t="n">
+      <c r="K5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="K5" s="95" t="n">
+      <c r="L5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="L5" s="95" t="n">
+      <c r="M5" s="95" t="n">
         <v>63.45</v>
       </c>
-      <c r="M5" s="95" t="n">
+      <c r="N5" s="95" t="n">
         <v>37.85</v>
-      </c>
-      <c r="N5" s="95" t="n">
-        <v>7.42</v>
       </c>
       <c r="O5" s="95" t="n">
         <v>7.42</v>
@@ -6894,49 +6894,49 @@
         <v>7.42</v>
       </c>
       <c r="Q5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="R5" s="95" t="n">
         <v>10.95</v>
       </c>
-      <c r="R5" s="95" t="n">
+      <c r="S5" s="95" t="n">
         <v>12.36</v>
       </c>
-      <c r="S5" s="95" t="n">
+      <c r="T5" s="95" t="n">
         <v>20.95</v>
       </c>
-      <c r="T5" s="95" t="n">
+      <c r="U5" s="95" t="n">
         <v>5.95</v>
       </c>
-      <c r="U5" s="95" t="n">
+      <c r="V5" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="V5" s="95" t="n">
+      <c r="W5" s="95" t="n">
         <v>21.9</v>
       </c>
-      <c r="W5" s="95" t="n">
+      <c r="X5" s="95" t="n">
         <v>12.41</v>
       </c>
-      <c r="X5" s="95" t="n">
+      <c r="Y5" s="95" t="n">
         <v>19.88</v>
       </c>
-      <c r="Y5" s="95" t="n">
+      <c r="Z5" s="95" t="n">
         <v>24.04</v>
       </c>
-      <c r="Z5" s="95" t="n">
+      <c r="AA5" s="95" t="n">
         <v>52.18</v>
       </c>
-      <c r="AA5" s="95" t="n">
+      <c r="AB5" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="AB5" s="95" t="n">
+      <c r="AC5" s="95" t="n">
         <v>15.44</v>
       </c>
-      <c r="AC5" s="95" t="n">
+      <c r="AD5" s="95" t="n">
         <v>27.78</v>
       </c>
-      <c r="AD5" s="95" t="n">
+      <c r="AE5" s="95" t="n">
         <v>40.86</v>
-      </c>
-      <c r="AE5" s="95" t="n">
-        <v>37.54</v>
       </c>
     </row>
     <row r="6">
@@ -6985,99 +6985,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J6" s="94" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K6" s="93" t="inlineStr">
+      <c r="L6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="M6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="94" t="inlineStr">
+      <c r="N6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N6" s="93" t="inlineStr">
+      <c r="O6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O6" s="93" t="inlineStr">
+      <c r="P6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="93" t="inlineStr">
+      <c r="Q6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="93" t="inlineStr">
+      <c r="R6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="93" t="inlineStr">
+      <c r="S6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="93" t="inlineStr">
+      <c r="T6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="94" t="inlineStr">
+      <c r="U6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U6" s="94" t="inlineStr">
+      <c r="V6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="W6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="Y6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="94" t="inlineStr">
+      <c r="Z6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z6" s="92" t="inlineStr">
+      <c r="AA6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
+      <c r="AB6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AC6" s="94" t="inlineStr">
@@ -7115,31 +7115,31 @@
         <v>26.36</v>
       </c>
       <c r="F7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="G7" s="95" t="n">
         <v>5.45</v>
       </c>
-      <c r="G7" s="95" t="n">
+      <c r="H7" s="95" t="n">
         <v>-0.85</v>
       </c>
-      <c r="H7" s="95" t="n">
+      <c r="I7" s="95" t="n">
         <v>-5.96</v>
       </c>
-      <c r="I7" s="95" t="n">
+      <c r="J7" s="95" t="n">
         <v>-6.32</v>
       </c>
-      <c r="J7" s="95" t="n">
+      <c r="K7" s="95" t="n">
         <v>-10.11</v>
       </c>
-      <c r="K7" s="95" t="n">
+      <c r="L7" s="95" t="n">
         <v>-11.14</v>
       </c>
-      <c r="L7" s="95" t="n">
+      <c r="M7" s="95" t="n">
         <v>-9.23</v>
       </c>
-      <c r="M7" s="95" t="n">
+      <c r="N7" s="95" t="n">
         <v>-12.41</v>
-      </c>
-      <c r="N7" s="95" t="n">
-        <v>-13.62</v>
       </c>
       <c r="O7" s="95" t="n">
         <v>-13.62</v>
@@ -7148,49 +7148,49 @@
         <v>-13.62</v>
       </c>
       <c r="Q7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="R7" s="95" t="n">
         <v>-12.75</v>
       </c>
-      <c r="R7" s="95" t="n">
+      <c r="S7" s="95" t="n">
         <v>-11.62</v>
       </c>
-      <c r="S7" s="95" t="n">
+      <c r="T7" s="95" t="n">
         <v>-12.8</v>
       </c>
-      <c r="T7" s="95" t="n">
+      <c r="U7" s="95" t="n">
         <v>-13.49</v>
       </c>
-      <c r="U7" s="95" t="n">
+      <c r="V7" s="95" t="n">
         <v>-12.19</v>
       </c>
-      <c r="V7" s="95" t="n">
+      <c r="W7" s="95" t="n">
         <v>-11.56</v>
       </c>
-      <c r="W7" s="95" t="n">
+      <c r="X7" s="95" t="n">
         <v>-10.95</v>
       </c>
-      <c r="X7" s="95" t="n">
+      <c r="Y7" s="95" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Y7" s="95" t="n">
+      <c r="Z7" s="95" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="Z7" s="95" t="n">
+      <c r="AA7" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="AA7" s="95" t="n">
+      <c r="AB7" s="95" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="AB7" s="95" t="n">
+      <c r="AC7" s="95" t="n">
         <v>-10.94</v>
       </c>
-      <c r="AC7" s="95" t="n">
+      <c r="AD7" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="AD7" s="95" t="n">
+      <c r="AE7" s="95" t="n">
         <v>-8.17</v>
-      </c>
-      <c r="AE7" s="95" t="n">
-        <v>-7.67</v>
       </c>
     </row>
     <row r="8">
@@ -7212,31 +7212,31 @@
         <v>15.28</v>
       </c>
       <c r="F8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="G8" s="95" t="n">
         <v>-3.74</v>
       </c>
-      <c r="G8" s="95" t="n">
+      <c r="H8" s="95" t="n">
         <v>-10.62</v>
       </c>
-      <c r="H8" s="95" t="n">
+      <c r="I8" s="95" t="n">
         <v>-12.51</v>
       </c>
-      <c r="I8" s="95" t="n">
+      <c r="J8" s="95" t="n">
         <v>-12.61</v>
       </c>
-      <c r="J8" s="95" t="n">
+      <c r="K8" s="95" t="n">
         <v>-14.58</v>
       </c>
-      <c r="K8" s="95" t="n">
+      <c r="L8" s="95" t="n">
         <v>-16.03</v>
       </c>
-      <c r="L8" s="95" t="n">
+      <c r="M8" s="95" t="n">
         <v>-16.65</v>
       </c>
-      <c r="M8" s="95" t="n">
+      <c r="N8" s="95" t="n">
         <v>-18.48</v>
-      </c>
-      <c r="N8" s="95" t="n">
-        <v>-18.74</v>
       </c>
       <c r="O8" s="95" t="n">
         <v>-18.74</v>
@@ -7245,49 +7245,49 @@
         <v>-18.74</v>
       </c>
       <c r="Q8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="R8" s="95" t="n">
         <v>-19.06</v>
       </c>
-      <c r="R8" s="95" t="n">
+      <c r="S8" s="95" t="n">
         <v>-18.16</v>
       </c>
-      <c r="S8" s="95" t="n">
+      <c r="T8" s="95" t="n">
         <v>-20.04</v>
       </c>
-      <c r="T8" s="95" t="n">
+      <c r="U8" s="95" t="n">
         <v>-19.01</v>
       </c>
-      <c r="U8" s="95" t="n">
+      <c r="V8" s="95" t="n">
         <v>-17.71</v>
       </c>
-      <c r="V8" s="95" t="n">
+      <c r="W8" s="95" t="n">
         <v>-17.63</v>
       </c>
-      <c r="W8" s="95" t="n">
+      <c r="X8" s="95" t="n">
         <v>-17.79</v>
       </c>
-      <c r="X8" s="95" t="n">
+      <c r="Y8" s="95" t="n">
         <v>-17.53</v>
       </c>
-      <c r="Y8" s="95" t="n">
+      <c r="Z8" s="95" t="n">
         <v>-16.58</v>
       </c>
-      <c r="Z8" s="95" t="n">
+      <c r="AA8" s="95" t="n">
         <v>-12.6</v>
       </c>
-      <c r="AA8" s="95" t="n">
+      <c r="AB8" s="95" t="n">
         <v>-16.3</v>
       </c>
-      <c r="AB8" s="95" t="n">
+      <c r="AC8" s="95" t="n">
         <v>-17.92</v>
       </c>
-      <c r="AC8" s="95" t="n">
+      <c r="AD8" s="95" t="n">
         <v>-17.61</v>
       </c>
-      <c r="AD8" s="95" t="n">
+      <c r="AE8" s="95" t="n">
         <v>-16.31</v>
-      </c>
-      <c r="AE8" s="95" t="n">
-        <v>-15.1</v>
       </c>
     </row>
     <row r="9">
@@ -7309,31 +7309,31 @@
         <v>96.84</v>
       </c>
       <c r="F9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="G9" s="95" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="G9" s="95" t="n">
+      <c r="H9" s="95" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="H9" s="95" t="n">
+      <c r="I9" s="95" t="n">
         <v>64.94</v>
       </c>
-      <c r="I9" s="95" t="n">
+      <c r="J9" s="95" t="n">
         <v>64.66</v>
       </c>
-      <c r="J9" s="95" t="n">
+      <c r="K9" s="95" t="n">
         <v>23.69</v>
       </c>
-      <c r="K9" s="95" t="n">
+      <c r="L9" s="95" t="n">
         <v>29.81</v>
       </c>
-      <c r="L9" s="95" t="n">
+      <c r="M9" s="95" t="n">
         <v>33.91</v>
       </c>
-      <c r="M9" s="95" t="n">
+      <c r="N9" s="95" t="n">
         <v>22.82</v>
-      </c>
-      <c r="N9" s="95" t="n">
-        <v>30.54</v>
       </c>
       <c r="O9" s="95" t="n">
         <v>30.54</v>
@@ -7342,49 +7342,49 @@
         <v>30.54</v>
       </c>
       <c r="Q9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="R9" s="95" t="n">
         <v>35.28</v>
       </c>
-      <c r="R9" s="95" t="n">
+      <c r="S9" s="95" t="n">
         <v>42.99</v>
       </c>
-      <c r="S9" s="95" t="n">
+      <c r="T9" s="95" t="n">
         <v>33.88</v>
       </c>
-      <c r="T9" s="95" t="n">
+      <c r="U9" s="95" t="n">
         <v>22.22</v>
       </c>
-      <c r="U9" s="95" t="n">
+      <c r="V9" s="95" t="n">
         <v>27.98</v>
       </c>
-      <c r="V9" s="95" t="n">
+      <c r="W9" s="95" t="n">
         <v>37.32</v>
       </c>
-      <c r="W9" s="95" t="n">
+      <c r="X9" s="95" t="n">
         <v>38.49</v>
       </c>
-      <c r="X9" s="95" t="n">
+      <c r="Y9" s="95" t="n">
         <v>41.22</v>
       </c>
-      <c r="Y9" s="95" t="n">
+      <c r="Z9" s="95" t="n">
         <v>34.35</v>
       </c>
-      <c r="Z9" s="95" t="n">
+      <c r="AA9" s="95" t="n">
         <v>63.18</v>
       </c>
-      <c r="AA9" s="95" t="n">
+      <c r="AB9" s="95" t="n">
         <v>38.1</v>
       </c>
-      <c r="AB9" s="95" t="n">
+      <c r="AC9" s="95" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AC9" s="95" t="n">
+      <c r="AD9" s="95" t="n">
         <v>11.44</v>
       </c>
-      <c r="AD9" s="95" t="n">
+      <c r="AE9" s="95" t="n">
         <v>17.04</v>
-      </c>
-      <c r="AE9" s="95" t="n">
-        <v>20.21</v>
       </c>
     </row>
     <row r="10">
@@ -7433,114 +7433,114 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J10" s="94" t="inlineStr">
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K10" s="94" t="inlineStr">
+      <c r="L10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L10" s="93" t="inlineStr">
+      <c r="M10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M10" s="94" t="inlineStr">
+      <c r="N10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N10" s="94" t="inlineStr">
+      <c r="O10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O10" s="94" t="inlineStr">
+      <c r="P10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P10" s="94" t="inlineStr">
+      <c r="Q10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q10" s="93" t="inlineStr">
+      <c r="R10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S10" s="94" t="inlineStr">
+      <c r="T10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T10" s="94" t="inlineStr">
+      <c r="U10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U10" s="94" t="inlineStr">
+      <c r="V10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="X10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y10" s="94" t="inlineStr">
+      <c r="Z10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z10" s="92" t="inlineStr">
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA10" s="93" t="inlineStr">
+      <c r="AB10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB10" s="93" t="inlineStr">
+      <c r="AC10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC10" s="94" t="inlineStr">
+      <c r="AD10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD10" s="93" t="inlineStr">
+      <c r="AE10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE10" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -7563,31 +7563,31 @@
         <v>32.05</v>
       </c>
       <c r="F11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="G11" s="95" t="n">
         <v>13.58</v>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="H11" s="95" t="n">
         <v>2.95</v>
       </c>
-      <c r="H11" s="95" t="n">
+      <c r="I11" s="95" t="n">
         <v>-2.45</v>
       </c>
-      <c r="I11" s="95" t="n">
+      <c r="J11" s="95" t="n">
         <v>-4.05</v>
       </c>
-      <c r="J11" s="95" t="n">
+      <c r="K11" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="K11" s="95" t="n">
+      <c r="L11" s="95" t="n">
         <v>-11.21</v>
       </c>
-      <c r="L11" s="95" t="n">
+      <c r="M11" s="95" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="M11" s="95" t="n">
+      <c r="N11" s="95" t="n">
         <v>-11.44</v>
-      </c>
-      <c r="N11" s="95" t="n">
-        <v>-12.57</v>
       </c>
       <c r="O11" s="95" t="n">
         <v>-12.57</v>
@@ -7596,49 +7596,49 @@
         <v>-12.57</v>
       </c>
       <c r="Q11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="R11" s="95" t="n">
         <v>-11.96</v>
       </c>
-      <c r="R11" s="95" t="n">
+      <c r="S11" s="95" t="n">
         <v>-12.87</v>
       </c>
-      <c r="S11" s="95" t="n">
+      <c r="T11" s="95" t="n">
         <v>-14.98</v>
       </c>
-      <c r="T11" s="95" t="n">
+      <c r="U11" s="95" t="n">
         <v>-14.79</v>
       </c>
-      <c r="U11" s="95" t="n">
+      <c r="V11" s="95" t="n">
         <v>-14.14</v>
       </c>
-      <c r="V11" s="95" t="n">
+      <c r="W11" s="95" t="n">
         <v>-11.99</v>
       </c>
-      <c r="W11" s="95" t="n">
+      <c r="X11" s="95" t="n">
         <v>-12.63</v>
       </c>
-      <c r="X11" s="95" t="n">
+      <c r="Y11" s="95" t="n">
         <v>-12.92</v>
       </c>
-      <c r="Y11" s="95" t="n">
+      <c r="Z11" s="95" t="n">
         <v>-13.71</v>
       </c>
-      <c r="Z11" s="95" t="n">
+      <c r="AA11" s="95" t="n">
         <v>-13.18</v>
       </c>
-      <c r="AA11" s="95" t="n">
+      <c r="AB11" s="95" t="n">
         <v>-15.93</v>
       </c>
-      <c r="AB11" s="95" t="n">
+      <c r="AC11" s="95" t="n">
         <v>-16.93</v>
       </c>
-      <c r="AC11" s="95" t="n">
+      <c r="AD11" s="95" t="n">
         <v>-15.87</v>
       </c>
-      <c r="AD11" s="95" t="n">
+      <c r="AE11" s="95" t="n">
         <v>-14.39</v>
-      </c>
-      <c r="AE11" s="95" t="n">
-        <v>-14.68</v>
       </c>
     </row>
     <row r="12">
@@ -7660,31 +7660,31 @@
         <v>18.19</v>
       </c>
       <c r="F12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="G12" s="95" t="n">
         <v>1.34</v>
       </c>
-      <c r="G12" s="95" t="n">
+      <c r="H12" s="95" t="n">
         <v>-8.44</v>
       </c>
-      <c r="H12" s="95" t="n">
+      <c r="I12" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="I12" s="95" t="n">
+      <c r="J12" s="95" t="n">
         <v>-10.6</v>
       </c>
-      <c r="J12" s="95" t="n">
+      <c r="K12" s="95" t="n">
         <v>-14.49</v>
       </c>
-      <c r="K12" s="95" t="n">
+      <c r="L12" s="95" t="n">
         <v>-16.56</v>
       </c>
-      <c r="L12" s="95" t="n">
+      <c r="M12" s="95" t="n">
         <v>-15.65</v>
       </c>
-      <c r="M12" s="95" t="n">
+      <c r="N12" s="95" t="n">
         <v>-17.96</v>
-      </c>
-      <c r="N12" s="95" t="n">
-        <v>-19.08</v>
       </c>
       <c r="O12" s="95" t="n">
         <v>-19.08</v>
@@ -7693,49 +7693,49 @@
         <v>-19.08</v>
       </c>
       <c r="Q12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="R12" s="95" t="n">
         <v>-18.72</v>
       </c>
-      <c r="R12" s="95" t="n">
+      <c r="S12" s="95" t="n">
         <v>-18.28</v>
       </c>
-      <c r="S12" s="95" t="n">
+      <c r="T12" s="95" t="n">
         <v>-20.06</v>
       </c>
-      <c r="T12" s="95" t="n">
+      <c r="U12" s="95" t="n">
         <v>-18.31</v>
       </c>
-      <c r="U12" s="95" t="n">
+      <c r="V12" s="95" t="n">
         <v>-18.32</v>
       </c>
-      <c r="V12" s="95" t="n">
+      <c r="W12" s="95" t="n">
         <v>-17.44</v>
       </c>
-      <c r="W12" s="95" t="n">
+      <c r="X12" s="95" t="n">
         <v>-18.44</v>
       </c>
-      <c r="X12" s="95" t="n">
+      <c r="Y12" s="95" t="n">
         <v>-17.67</v>
       </c>
-      <c r="Y12" s="95" t="n">
+      <c r="Z12" s="95" t="n">
         <v>-14.96</v>
       </c>
-      <c r="Z12" s="95" t="n">
+      <c r="AA12" s="95" t="n">
         <v>-11.7</v>
       </c>
-      <c r="AA12" s="95" t="n">
+      <c r="AB12" s="95" t="n">
         <v>-15.89</v>
       </c>
-      <c r="AB12" s="95" t="n">
+      <c r="AC12" s="95" t="n">
         <v>-16.48</v>
       </c>
-      <c r="AC12" s="95" t="n">
+      <c r="AD12" s="95" t="n">
         <v>-16.57</v>
       </c>
-      <c r="AD12" s="95" t="n">
+      <c r="AE12" s="95" t="n">
         <v>-15.28</v>
-      </c>
-      <c r="AE12" s="95" t="n">
-        <v>-14.4</v>
       </c>
     </row>
     <row r="13">
@@ -7757,31 +7757,31 @@
         <v>99.48</v>
       </c>
       <c r="F13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="G13" s="95" t="n">
         <v>98.62</v>
       </c>
-      <c r="G13" s="95" t="n">
+      <c r="H13" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="H13" s="95" t="n">
+      <c r="I13" s="95" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="I13" s="95" t="n">
+      <c r="J13" s="95" t="n">
         <v>88.09</v>
       </c>
-      <c r="J13" s="95" t="n">
+      <c r="K13" s="95" t="n">
         <v>30.34</v>
       </c>
-      <c r="K13" s="95" t="n">
+      <c r="L13" s="95" t="n">
         <v>39.51</v>
       </c>
-      <c r="L13" s="95" t="n">
+      <c r="M13" s="95" t="n">
         <v>58.67</v>
       </c>
-      <c r="M13" s="95" t="n">
+      <c r="N13" s="95" t="n">
         <v>28.04</v>
-      </c>
-      <c r="N13" s="95" t="n">
-        <v>29.98</v>
       </c>
       <c r="O13" s="95" t="n">
         <v>29.98</v>
@@ -7790,49 +7790,49 @@
         <v>29.98</v>
       </c>
       <c r="Q13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="R13" s="95" t="n">
         <v>54.57</v>
       </c>
-      <c r="R13" s="95" t="n">
+      <c r="S13" s="95" t="n">
         <v>69.45</v>
       </c>
-      <c r="S13" s="95" t="n">
+      <c r="T13" s="95" t="n">
         <v>37.43</v>
       </c>
-      <c r="T13" s="95" t="n">
+      <c r="U13" s="95" t="n">
         <v>35.11</v>
       </c>
-      <c r="U13" s="95" t="n">
+      <c r="V13" s="95" t="n">
         <v>33.41</v>
       </c>
-      <c r="V13" s="95" t="n">
+      <c r="W13" s="95" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="W13" s="95" t="n">
+      <c r="X13" s="95" t="n">
         <v>53.41</v>
       </c>
-      <c r="X13" s="95" t="n">
+      <c r="Y13" s="95" t="n">
         <v>55.28</v>
       </c>
-      <c r="Y13" s="95" t="n">
+      <c r="Z13" s="95" t="n">
         <v>38.88</v>
       </c>
-      <c r="Z13" s="95" t="n">
+      <c r="AA13" s="95" t="n">
         <v>86.18000000000001</v>
       </c>
-      <c r="AA13" s="95" t="n">
+      <c r="AB13" s="95" t="n">
         <v>49.2</v>
       </c>
-      <c r="AB13" s="95" t="n">
+      <c r="AC13" s="95" t="n">
         <v>6.86</v>
       </c>
-      <c r="AC13" s="95" t="n">
+      <c r="AD13" s="95" t="n">
         <v>3.02</v>
       </c>
-      <c r="AD13" s="95" t="n">
+      <c r="AE13" s="95" t="n">
         <v>6.93</v>
-      </c>
-      <c r="AE13" s="95" t="n">
-        <v>7.65</v>
       </c>
     </row>
     <row r="14">
@@ -7911,84 +7911,84 @@
           <t>red</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="P14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R14" s="94" t="inlineStr">
+      <c r="S14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S14" s="94" t="inlineStr">
+      <c r="T14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="94" t="inlineStr">
+      <c r="U14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="94" t="inlineStr">
+      <c r="V14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="94" t="inlineStr">
+      <c r="W14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="94" t="inlineStr">
+      <c r="X14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z14" s="92" t="inlineStr">
+      <c r="AA14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="93" t="inlineStr">
+      <c r="AB14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB14" s="93" t="inlineStr">
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC14" s="92" t="inlineStr">
+      <c r="AD14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD14" s="92" t="inlineStr">
+      <c r="AE14" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -7999,94 +7999,94 @@
         </is>
       </c>
       <c r="B15" s="95" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="C15" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="D15" s="95" t="n">
         <v>26.09</v>
-      </c>
-      <c r="D15" s="95" t="n">
-        <v>17.23</v>
       </c>
       <c r="E15" s="95" t="n">
         <v>17.23</v>
       </c>
       <c r="F15" s="95" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="G15" s="95" t="n">
         <v>14.76</v>
       </c>
-      <c r="G15" s="95" t="n">
+      <c r="H15" s="95" t="n">
         <v>12.13</v>
       </c>
-      <c r="H15" s="95" t="n">
+      <c r="I15" s="95" t="n">
         <v>7.96</v>
       </c>
-      <c r="I15" s="95" t="n">
+      <c r="J15" s="95" t="n">
         <v>7.25</v>
       </c>
-      <c r="J15" s="95" t="n">
+      <c r="K15" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="K15" s="95" t="n">
+      <c r="L15" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="L15" s="95" t="n">
+      <c r="M15" s="95" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="M15" s="95" t="n">
-        <v>-2.04</v>
       </c>
       <c r="N15" s="95" t="n">
         <v>-2.04</v>
       </c>
       <c r="O15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="P15" s="95" t="n">
         <v>-4.98</v>
       </c>
-      <c r="P15" s="95" t="n">
+      <c r="Q15" s="95" t="n">
         <v>-5.76</v>
       </c>
-      <c r="Q15" s="95" t="n">
+      <c r="R15" s="95" t="n">
         <v>-3.77</v>
       </c>
-      <c r="R15" s="95" t="n">
+      <c r="S15" s="95" t="n">
         <v>-4.61</v>
       </c>
-      <c r="S15" s="95" t="n">
+      <c r="T15" s="95" t="n">
         <v>-3.94</v>
       </c>
-      <c r="T15" s="95" t="n">
+      <c r="U15" s="95" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="U15" s="95" t="n">
-        <v>-2.75</v>
       </c>
       <c r="V15" s="95" t="n">
         <v>-2.75</v>
       </c>
       <c r="W15" s="95" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="X15" s="95" t="n">
         <v>-3.96</v>
       </c>
-      <c r="X15" s="95" t="n">
+      <c r="Y15" s="95" t="n">
         <v>-3.9</v>
       </c>
-      <c r="Y15" s="95" t="n">
+      <c r="Z15" s="95" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Z15" s="95" t="n">
+      <c r="AA15" s="95" t="n">
         <v>-2.37</v>
       </c>
-      <c r="AA15" s="95" t="n">
+      <c r="AB15" s="95" t="n">
         <v>-3.57</v>
       </c>
-      <c r="AB15" s="95" t="n">
+      <c r="AC15" s="95" t="n">
         <v>-3.86</v>
       </c>
-      <c r="AC15" s="95" t="n">
+      <c r="AD15" s="95" t="n">
         <v>-1.13</v>
       </c>
-      <c r="AD15" s="95" t="n">
+      <c r="AE15" s="95" t="n">
         <v>-2.37</v>
-      </c>
-      <c r="AE15" s="95" t="n">
-        <v>-4.68</v>
       </c>
     </row>
     <row r="16">
@@ -8096,94 +8096,94 @@
         </is>
       </c>
       <c r="B16" s="95" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="C16" s="95" t="n">
         <v>31.41</v>
       </c>
-      <c r="C16" s="95" t="n">
+      <c r="D16" s="95" t="n">
         <v>34.13</v>
-      </c>
-      <c r="D16" s="95" t="n">
-        <v>26.37</v>
       </c>
       <c r="E16" s="95" t="n">
         <v>26.37</v>
       </c>
       <c r="F16" s="95" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="G16" s="95" t="n">
         <v>23.36</v>
       </c>
-      <c r="G16" s="95" t="n">
+      <c r="H16" s="95" t="n">
         <v>17.68</v>
       </c>
-      <c r="H16" s="95" t="n">
+      <c r="I16" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="I16" s="95" t="n">
+      <c r="J16" s="95" t="n">
         <v>15.91</v>
       </c>
-      <c r="J16" s="95" t="n">
+      <c r="K16" s="95" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K16" s="95" t="n">
+      <c r="L16" s="95" t="n">
         <v>10.84</v>
       </c>
-      <c r="L16" s="95" t="n">
+      <c r="M16" s="95" t="n">
         <v>9.17</v>
-      </c>
-      <c r="M16" s="95" t="n">
-        <v>4.73</v>
       </c>
       <c r="N16" s="95" t="n">
         <v>4.73</v>
       </c>
       <c r="O16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="P16" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="P16" s="95" t="n">
+      <c r="Q16" s="95" t="n">
         <v>5.08</v>
       </c>
-      <c r="Q16" s="95" t="n">
+      <c r="R16" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="R16" s="95" t="n">
+      <c r="S16" s="95" t="n">
         <v>2.32</v>
       </c>
-      <c r="S16" s="95" t="n">
+      <c r="T16" s="95" t="n">
         <v>1.61</v>
       </c>
-      <c r="T16" s="95" t="n">
+      <c r="U16" s="95" t="n">
         <v>0.67</v>
-      </c>
-      <c r="U16" s="95" t="n">
-        <v>2.05</v>
       </c>
       <c r="V16" s="95" t="n">
         <v>2.05</v>
       </c>
       <c r="W16" s="95" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X16" s="95" t="n">
         <v>5.24</v>
       </c>
-      <c r="X16" s="95" t="n">
+      <c r="Y16" s="95" t="n">
         <v>7.94</v>
       </c>
-      <c r="Y16" s="95" t="n">
+      <c r="Z16" s="95" t="n">
         <v>9.01</v>
       </c>
-      <c r="Z16" s="95" t="n">
+      <c r="AA16" s="95" t="n">
         <v>9.44</v>
       </c>
-      <c r="AA16" s="95" t="n">
+      <c r="AB16" s="95" t="n">
         <v>10.05</v>
       </c>
-      <c r="AB16" s="95" t="n">
+      <c r="AC16" s="95" t="n">
         <v>6.61</v>
       </c>
-      <c r="AC16" s="95" t="n">
+      <c r="AD16" s="95" t="n">
         <v>7.75</v>
       </c>
-      <c r="AD16" s="95" t="n">
+      <c r="AE16" s="95" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AE16" s="95" t="n">
-        <v>6.5</v>
       </c>
     </row>
     <row r="17">
@@ -8193,94 +8193,94 @@
         </is>
       </c>
       <c r="B17" s="95" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="C17" s="95" t="n">
         <v>85.84</v>
       </c>
-      <c r="C17" s="95" t="n">
+      <c r="D17" s="95" t="n">
         <v>99.56999999999999</v>
-      </c>
-      <c r="D17" s="95" t="n">
-        <v>99.18000000000001</v>
       </c>
       <c r="E17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
       <c r="F17" s="95" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="G17" s="95" t="n">
         <v>98.89</v>
       </c>
-      <c r="G17" s="95" t="n">
+      <c r="H17" s="95" t="n">
         <v>98.23</v>
       </c>
-      <c r="H17" s="95" t="n">
+      <c r="I17" s="95" t="n">
         <v>96.44</v>
       </c>
-      <c r="I17" s="95" t="n">
+      <c r="J17" s="95" t="n">
         <v>95.94</v>
       </c>
-      <c r="J17" s="95" t="n">
+      <c r="K17" s="95" t="n">
         <v>89.48</v>
       </c>
-      <c r="K17" s="95" t="n">
+      <c r="L17" s="95" t="n">
         <v>91.13</v>
       </c>
-      <c r="L17" s="95" t="n">
+      <c r="M17" s="95" t="n">
         <v>87.39</v>
-      </c>
-      <c r="M17" s="95" t="n">
-        <v>76.86</v>
       </c>
       <c r="N17" s="95" t="n">
         <v>76.86</v>
       </c>
       <c r="O17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="P17" s="95" t="n">
         <v>59.96</v>
       </c>
-      <c r="P17" s="95" t="n">
+      <c r="Q17" s="95" t="n">
         <v>54.39</v>
       </c>
-      <c r="Q17" s="95" t="n">
+      <c r="R17" s="95" t="n">
         <v>38.93</v>
       </c>
-      <c r="R17" s="95" t="n">
+      <c r="S17" s="95" t="n">
         <v>17.46</v>
       </c>
-      <c r="S17" s="95" t="n">
+      <c r="T17" s="95" t="n">
         <v>23.32</v>
       </c>
-      <c r="T17" s="95" t="n">
+      <c r="U17" s="95" t="n">
         <v>17.15</v>
-      </c>
-      <c r="U17" s="95" t="n">
-        <v>28.67</v>
       </c>
       <c r="V17" s="95" t="n">
         <v>28.67</v>
       </c>
       <c r="W17" s="95" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="X17" s="95" t="n">
         <v>29.45</v>
       </c>
-      <c r="X17" s="95" t="n">
+      <c r="Y17" s="95" t="n">
         <v>42.37</v>
       </c>
-      <c r="Y17" s="95" t="n">
+      <c r="Z17" s="95" t="n">
         <v>45.49</v>
       </c>
-      <c r="Z17" s="95" t="n">
+      <c r="AA17" s="95" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="AA17" s="95" t="n">
+      <c r="AB17" s="95" t="n">
         <v>63.9</v>
       </c>
-      <c r="AB17" s="95" t="n">
+      <c r="AC17" s="95" t="n">
         <v>55.65</v>
       </c>
-      <c r="AC17" s="95" t="n">
+      <c r="AD17" s="95" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="AD17" s="95" t="n">
+      <c r="AE17" s="95" t="n">
         <v>80.33</v>
-      </c>
-      <c r="AE17" s="95" t="n">
-        <v>70.19</v>
       </c>
     </row>
     <row r="18">
@@ -8324,89 +8324,89 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I18" s="92" t="inlineStr">
+      <c r="I18" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
+      <c r="K18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
+      <c r="L18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="92" t="inlineStr">
+      <c r="M18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="93" t="inlineStr">
+      <c r="N18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N18" s="92" t="inlineStr">
+      <c r="O18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="92" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P18" s="92" t="inlineStr">
+      <c r="Q18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="92" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R18" s="92" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S18" s="93" t="inlineStr">
+      <c r="T18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T18" s="94" t="inlineStr">
+      <c r="U18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U18" s="94" t="inlineStr">
+      <c r="V18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V18" s="94" t="inlineStr">
+      <c r="W18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W18" s="94" t="inlineStr">
+      <c r="X18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X18" s="94" t="inlineStr">
+      <c r="Y18" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Y18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="Z18" s="93" t="inlineStr">
@@ -8450,91 +8450,91 @@
         <v>1.17</v>
       </c>
       <c r="C19" s="95" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D19" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="D19" s="95" t="n">
+      <c r="E19" s="95" t="n">
         <v>2.44</v>
       </c>
-      <c r="E19" s="95" t="n">
+      <c r="F19" s="95" t="n">
         <v>3.51</v>
       </c>
-      <c r="F19" s="95" t="n">
+      <c r="G19" s="95" t="n">
         <v>3.63</v>
       </c>
-      <c r="G19" s="95" t="n">
+      <c r="H19" s="95" t="n">
         <v>4.29</v>
       </c>
-      <c r="H19" s="95" t="n">
+      <c r="I19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="I19" s="95" t="n">
+      <c r="J19" s="95" t="n">
         <v>4.99</v>
       </c>
-      <c r="J19" s="95" t="n">
+      <c r="K19" s="95" t="n">
         <v>4.3</v>
       </c>
-      <c r="K19" s="95" t="n">
+      <c r="L19" s="95" t="n">
         <v>4.1</v>
       </c>
-      <c r="L19" s="95" t="n">
+      <c r="M19" s="95" t="n">
         <v>4.47</v>
       </c>
-      <c r="M19" s="95" t="n">
+      <c r="N19" s="95" t="n">
         <v>3.13</v>
       </c>
-      <c r="N19" s="95" t="n">
+      <c r="O19" s="95" t="n">
         <v>3.11</v>
       </c>
-      <c r="O19" s="95" t="n">
+      <c r="P19" s="95" t="n">
         <v>2.92</v>
       </c>
-      <c r="P19" s="95" t="n">
+      <c r="Q19" s="95" t="n">
         <v>2.53</v>
       </c>
-      <c r="Q19" s="95" t="n">
+      <c r="R19" s="95" t="n">
         <v>2.24</v>
       </c>
-      <c r="R19" s="95" t="n">
+      <c r="S19" s="95" t="n">
         <v>2.26</v>
       </c>
-      <c r="S19" s="95" t="n">
+      <c r="T19" s="95" t="n">
         <v>1.14</v>
       </c>
-      <c r="T19" s="95" t="n">
+      <c r="U19" s="95" t="n">
         <v>0.92</v>
       </c>
-      <c r="U19" s="95" t="n">
+      <c r="V19" s="95" t="n">
         <v>0.62</v>
       </c>
-      <c r="V19" s="95" t="n">
+      <c r="W19" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="W19" s="95" t="n">
+      <c r="X19" s="95" t="n">
         <v>3.24</v>
       </c>
-      <c r="X19" s="95" t="n">
+      <c r="Y19" s="95" t="n">
         <v>3.29</v>
-      </c>
-      <c r="Y19" s="95" t="n">
-        <v>5.5</v>
       </c>
       <c r="Z19" s="95" t="n">
         <v>5.5</v>
       </c>
       <c r="AA19" s="95" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB19" s="95" t="n">
         <v>5.68</v>
       </c>
-      <c r="AB19" s="95" t="n">
+      <c r="AC19" s="95" t="n">
         <v>5.84</v>
       </c>
-      <c r="AC19" s="95" t="n">
+      <c r="AD19" s="95" t="n">
         <v>6.6</v>
       </c>
-      <c r="AD19" s="95" t="n">
+      <c r="AE19" s="95" t="n">
         <v>7.28</v>
-      </c>
-      <c r="AE19" s="95" t="n">
-        <v>6.98</v>
       </c>
     </row>
     <row r="20">
@@ -8547,91 +8547,91 @@
         <v>11.25</v>
       </c>
       <c r="C20" s="95" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D20" s="95" t="n">
         <v>9.82</v>
       </c>
-      <c r="D20" s="95" t="n">
+      <c r="E20" s="95" t="n">
         <v>10.62</v>
       </c>
-      <c r="E20" s="95" t="n">
+      <c r="F20" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="F20" s="95" t="n">
+      <c r="G20" s="95" t="n">
         <v>10.3</v>
       </c>
-      <c r="G20" s="95" t="n">
+      <c r="H20" s="95" t="n">
         <v>10.4</v>
       </c>
-      <c r="H20" s="95" t="n">
+      <c r="I20" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="I20" s="95" t="n">
+      <c r="J20" s="95" t="n">
         <v>10.01</v>
       </c>
-      <c r="J20" s="95" t="n">
+      <c r="K20" s="95" t="n">
         <v>9.85</v>
       </c>
-      <c r="K20" s="95" t="n">
+      <c r="L20" s="95" t="n">
         <v>8.75</v>
       </c>
-      <c r="L20" s="95" t="n">
+      <c r="M20" s="95" t="n">
         <v>8.74</v>
       </c>
-      <c r="M20" s="95" t="n">
+      <c r="N20" s="95" t="n">
         <v>7.05</v>
       </c>
-      <c r="N20" s="95" t="n">
+      <c r="O20" s="95" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="O20" s="95" t="n">
+      <c r="P20" s="95" t="n">
         <v>7.95</v>
       </c>
-      <c r="P20" s="95" t="n">
+      <c r="Q20" s="95" t="n">
         <v>7.49</v>
       </c>
-      <c r="Q20" s="95" t="n">
+      <c r="R20" s="95" t="n">
         <v>6.76</v>
       </c>
-      <c r="R20" s="95" t="n">
+      <c r="S20" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="S20" s="95" t="n">
+      <c r="T20" s="95" t="n">
         <v>6.12</v>
       </c>
-      <c r="T20" s="95" t="n">
+      <c r="U20" s="95" t="n">
         <v>6.25</v>
       </c>
-      <c r="U20" s="95" t="n">
+      <c r="V20" s="95" t="n">
         <v>5.69</v>
       </c>
-      <c r="V20" s="95" t="n">
+      <c r="W20" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="W20" s="95" t="n">
+      <c r="X20" s="95" t="n">
         <v>6.87</v>
       </c>
-      <c r="X20" s="95" t="n">
+      <c r="Y20" s="95" t="n">
         <v>6.83</v>
-      </c>
-      <c r="Y20" s="95" t="n">
-        <v>10.36</v>
       </c>
       <c r="Z20" s="95" t="n">
         <v>10.36</v>
       </c>
       <c r="AA20" s="95" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AB20" s="95" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="AB20" s="95" t="n">
+      <c r="AC20" s="95" t="n">
         <v>8.43</v>
       </c>
-      <c r="AC20" s="95" t="n">
+      <c r="AD20" s="95" t="n">
         <v>10.21</v>
       </c>
-      <c r="AD20" s="95" t="n">
+      <c r="AE20" s="95" t="n">
         <v>10.6</v>
-      </c>
-      <c r="AE20" s="95" t="n">
-        <v>9.82</v>
       </c>
     </row>
     <row r="21">
@@ -8644,91 +8644,91 @@
         <v>15.76</v>
       </c>
       <c r="C21" s="95" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="D21" s="95" t="n">
         <v>23.93</v>
       </c>
-      <c r="D21" s="95" t="n">
+      <c r="E21" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="E21" s="95" t="n">
+      <c r="F21" s="95" t="n">
         <v>86.19</v>
       </c>
-      <c r="F21" s="95" t="n">
+      <c r="G21" s="95" t="n">
         <v>60.63</v>
       </c>
-      <c r="G21" s="95" t="n">
+      <c r="H21" s="95" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="H21" s="95" t="n">
+      <c r="I21" s="95" t="n">
         <v>58.19</v>
       </c>
-      <c r="I21" s="95" t="n">
+      <c r="J21" s="95" t="n">
         <v>90.16</v>
       </c>
-      <c r="J21" s="95" t="n">
+      <c r="K21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="K21" s="95" t="n">
+      <c r="L21" s="95" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="L21" s="95" t="n">
+      <c r="M21" s="95" t="n">
         <v>92.34</v>
       </c>
-      <c r="M21" s="95" t="n">
+      <c r="N21" s="95" t="n">
         <v>40.89</v>
       </c>
-      <c r="N21" s="95" t="n">
+      <c r="O21" s="95" t="n">
         <v>96.09</v>
       </c>
-      <c r="O21" s="95" t="n">
+      <c r="P21" s="95" t="n">
         <v>95.83</v>
       </c>
-      <c r="P21" s="95" t="n">
+      <c r="Q21" s="95" t="n">
         <v>95.06</v>
       </c>
-      <c r="Q21" s="95" t="n">
+      <c r="R21" s="95" t="n">
         <v>91.83</v>
       </c>
-      <c r="R21" s="95" t="n">
+      <c r="S21" s="95" t="n">
         <v>85.17</v>
       </c>
-      <c r="S21" s="95" t="n">
+      <c r="T21" s="95" t="n">
         <v>65.2</v>
       </c>
-      <c r="T21" s="95" t="n">
+      <c r="U21" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="U21" s="95" t="n">
+      <c r="V21" s="95" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="95" t="n">
+      <c r="W21" s="95" t="n">
         <v>12.54</v>
       </c>
-      <c r="W21" s="95" t="n">
+      <c r="X21" s="95" t="n">
         <v>17.38</v>
       </c>
-      <c r="X21" s="95" t="n">
+      <c r="Y21" s="95" t="n">
         <v>19.37</v>
-      </c>
-      <c r="Y21" s="95" t="n">
-        <v>85.14</v>
       </c>
       <c r="Z21" s="95" t="n">
         <v>85.14</v>
       </c>
       <c r="AA21" s="95" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="AB21" s="95" t="n">
         <v>24.99</v>
       </c>
-      <c r="AB21" s="95" t="n">
+      <c r="AC21" s="95" t="n">
         <v>25.19</v>
       </c>
-      <c r="AC21" s="95" t="n">
+      <c r="AD21" s="95" t="n">
         <v>64.23</v>
       </c>
-      <c r="AD21" s="95" t="n">
+      <c r="AE21" s="95" t="n">
         <v>54.92</v>
-      </c>
-      <c r="AE21" s="95" t="n">
-        <v>74.03</v>
       </c>
     </row>
     <row r="22">
@@ -8772,114 +8772,114 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="92" t="inlineStr">
+      <c r="I22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="K22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="L22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
+      <c r="M22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="92" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="92" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="92" t="inlineStr">
+      <c r="Q22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="92" t="inlineStr">
+      <c r="R22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R22" s="92" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S22" s="94" t="inlineStr">
+      <c r="T22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T22" s="93" t="inlineStr">
+      <c r="U22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="94" t="inlineStr">
+      <c r="V22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="94" t="inlineStr">
+      <c r="W22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="93" t="inlineStr">
+      <c r="X22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="93" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="92" t="inlineStr">
+      <c r="Z22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA22" s="93" t="inlineStr">
+      <c r="AB22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="93" t="inlineStr">
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="93" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE22" s="92" t="inlineStr">
@@ -8895,94 +8895,94 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="C23" s="95" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="D23" s="95" t="n">
         <v>7.39</v>
       </c>
-      <c r="C23" s="95" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="D23" s="95" t="n">
+      <c r="E23" s="95" t="n">
         <v>7.15</v>
       </c>
-      <c r="E23" s="95" t="n">
+      <c r="F23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="F23" s="95" t="n">
+      <c r="G23" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="G23" s="95" t="n">
+      <c r="H23" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="H23" s="95" t="n">
+      <c r="I23" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="I23" s="95" t="n">
+      <c r="J23" s="95" t="n">
         <v>7.9</v>
       </c>
-      <c r="J23" s="95" t="n">
+      <c r="K23" s="95" t="n">
         <v>7.56</v>
       </c>
-      <c r="K23" s="95" t="n">
+      <c r="L23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="L23" s="95" t="n">
+      <c r="M23" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="M23" s="95" t="n">
+      <c r="N23" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="N23" s="95" t="n">
+      <c r="O23" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="O23" s="95" t="n">
+      <c r="P23" s="95" t="n">
         <v>6.36</v>
       </c>
-      <c r="P23" s="95" t="n">
+      <c r="Q23" s="95" t="n">
         <v>6.59</v>
       </c>
-      <c r="Q23" s="95" t="n">
+      <c r="R23" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="R23" s="95" t="n">
+      <c r="S23" s="95" t="n">
         <v>5.89</v>
       </c>
-      <c r="S23" s="95" t="n">
+      <c r="T23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="T23" s="95" t="n">
+      <c r="U23" s="95" t="n">
         <v>5.47</v>
       </c>
-      <c r="U23" s="95" t="n">
+      <c r="V23" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="V23" s="95" t="n">
+      <c r="W23" s="95" t="n">
         <v>4.86</v>
       </c>
-      <c r="W23" s="95" t="n">
+      <c r="X23" s="95" t="n">
         <v>5.61</v>
       </c>
-      <c r="X23" s="95" t="n">
+      <c r="Y23" s="95" t="n">
         <v>5.27</v>
-      </c>
-      <c r="Y23" s="95" t="n">
-        <v>7.1</v>
       </c>
       <c r="Z23" s="95" t="n">
         <v>7.1</v>
       </c>
       <c r="AA23" s="95" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB23" s="95" t="n">
         <v>6.78</v>
       </c>
-      <c r="AB23" s="95" t="n">
+      <c r="AC23" s="95" t="n">
         <v>6.53</v>
       </c>
-      <c r="AC23" s="95" t="n">
+      <c r="AD23" s="95" t="n">
         <v>6.63</v>
       </c>
-      <c r="AD23" s="95" t="n">
+      <c r="AE23" s="95" t="n">
         <v>8.210000000000001</v>
-      </c>
-      <c r="AE23" s="95" t="n">
-        <v>7.11</v>
       </c>
     </row>
     <row r="24">
@@ -8992,94 +8992,94 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="C24" s="95" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="D24" s="95" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="C24" s="95" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="D24" s="95" t="n">
+      <c r="E24" s="95" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E24" s="95" t="n">
+      <c r="F24" s="95" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="F24" s="95" t="n">
+      <c r="G24" s="95" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="G24" s="95" t="n">
+      <c r="H24" s="95" t="n">
         <v>8.41</v>
       </c>
-      <c r="H24" s="95" t="n">
+      <c r="I24" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="I24" s="95" t="n">
+      <c r="J24" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="J24" s="95" t="n">
+      <c r="K24" s="95" t="n">
         <v>7.54</v>
       </c>
-      <c r="K24" s="95" t="n">
+      <c r="L24" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="L24" s="95" t="n">
+      <c r="M24" s="95" t="n">
         <v>5.57</v>
       </c>
-      <c r="M24" s="95" t="n">
+      <c r="N24" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="N24" s="95" t="n">
+      <c r="O24" s="95" t="n">
         <v>5.92</v>
       </c>
-      <c r="O24" s="95" t="n">
+      <c r="P24" s="95" t="n">
         <v>5.87</v>
       </c>
-      <c r="P24" s="95" t="n">
+      <c r="Q24" s="95" t="n">
         <v>4.86</v>
       </c>
-      <c r="Q24" s="95" t="n">
+      <c r="R24" s="95" t="n">
         <v>3.31</v>
       </c>
-      <c r="R24" s="95" t="n">
+      <c r="S24" s="95" t="n">
         <v>3.42</v>
       </c>
-      <c r="S24" s="95" t="n">
+      <c r="T24" s="95" t="n">
         <v>4.16</v>
       </c>
-      <c r="T24" s="95" t="n">
+      <c r="U24" s="95" t="n">
         <v>5.26</v>
       </c>
-      <c r="U24" s="95" t="n">
+      <c r="V24" s="95" t="n">
         <v>4.21</v>
       </c>
-      <c r="V24" s="95" t="n">
+      <c r="W24" s="95" t="n">
         <v>4.76</v>
-      </c>
-      <c r="W24" s="95" t="n">
-        <v>4.95</v>
       </c>
       <c r="X24" s="95" t="n">
         <v>4.95</v>
       </c>
       <c r="Y24" s="95" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="Z24" s="95" t="n">
         <v>7.21</v>
       </c>
       <c r="AA24" s="95" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AB24" s="95" t="n">
         <v>6.75</v>
       </c>
-      <c r="AB24" s="95" t="n">
+      <c r="AC24" s="95" t="n">
         <v>5.93</v>
       </c>
-      <c r="AC24" s="95" t="n">
+      <c r="AD24" s="95" t="n">
         <v>6.7</v>
       </c>
-      <c r="AD24" s="95" t="n">
+      <c r="AE24" s="95" t="n">
         <v>6.88</v>
-      </c>
-      <c r="AE24" s="95" t="n">
-        <v>5.6</v>
       </c>
     </row>
     <row r="25">
@@ -9089,94 +9089,94 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="C25" s="95" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="D25" s="95" t="n">
         <v>52.09</v>
       </c>
-      <c r="C25" s="95" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="D25" s="95" t="n">
+      <c r="E25" s="95" t="n">
         <v>45.5</v>
       </c>
-      <c r="E25" s="95" t="n">
+      <c r="F25" s="95" t="n">
         <v>76.02</v>
       </c>
-      <c r="F25" s="95" t="n">
+      <c r="G25" s="95" t="n">
         <v>74.91</v>
       </c>
-      <c r="G25" s="95" t="n">
+      <c r="H25" s="95" t="n">
         <v>66.62</v>
       </c>
-      <c r="H25" s="95" t="n">
+      <c r="I25" s="95" t="n">
         <v>42.84</v>
       </c>
-      <c r="I25" s="95" t="n">
+      <c r="J25" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="J25" s="95" t="n">
+      <c r="K25" s="95" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="K25" s="95" t="n">
+      <c r="L25" s="95" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="L25" s="95" t="n">
+      <c r="M25" s="95" t="n">
         <v>87.58</v>
       </c>
-      <c r="M25" s="95" t="n">
+      <c r="N25" s="95" t="n">
         <v>65.31</v>
       </c>
-      <c r="N25" s="95" t="n">
+      <c r="O25" s="95" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="O25" s="95" t="n">
+      <c r="P25" s="95" t="n">
         <v>88.3</v>
       </c>
-      <c r="P25" s="95" t="n">
+      <c r="Q25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="Q25" s="95" t="n">
+      <c r="R25" s="95" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="R25" s="95" t="n">
+      <c r="S25" s="95" t="n">
         <v>56.57</v>
       </c>
-      <c r="S25" s="95" t="n">
+      <c r="T25" s="95" t="n">
         <v>46.45</v>
       </c>
-      <c r="T25" s="95" t="n">
+      <c r="U25" s="95" t="n">
         <v>52.5</v>
       </c>
-      <c r="U25" s="95" t="n">
+      <c r="V25" s="95" t="n">
         <v>13.02</v>
       </c>
-      <c r="V25" s="95" t="n">
+      <c r="W25" s="95" t="n">
         <v>24.55</v>
       </c>
-      <c r="W25" s="95" t="n">
+      <c r="X25" s="95" t="n">
         <v>35.87</v>
       </c>
-      <c r="X25" s="95" t="n">
+      <c r="Y25" s="95" t="n">
         <v>32.25</v>
-      </c>
-      <c r="Y25" s="95" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="Z25" s="95" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="AA25" s="95" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="AB25" s="95" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="AB25" s="95" t="n">
+      <c r="AC25" s="95" t="n">
         <v>52.49</v>
       </c>
-      <c r="AC25" s="95" t="n">
+      <c r="AD25" s="95" t="n">
         <v>83.64</v>
       </c>
-      <c r="AD25" s="95" t="n">
+      <c r="AE25" s="95" t="n">
         <v>83.23</v>
-      </c>
-      <c r="AE25" s="95" t="n">
-        <v>81.13</v>
       </c>
     </row>
     <row r="26">
@@ -9210,119 +9210,119 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="G26" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="93" t="inlineStr">
+      <c r="I26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="J26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="K26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
+      <c r="M26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="93" t="inlineStr">
+      <c r="N26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N26" s="92" t="inlineStr">
+      <c r="O26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O26" s="92" t="inlineStr">
+      <c r="P26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P26" s="92" t="inlineStr">
+      <c r="Q26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q26" s="92" t="inlineStr">
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R26" s="92" t="inlineStr">
+      <c r="S26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="T26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T26" s="94" t="inlineStr">
+      <c r="U26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U26" s="94" t="inlineStr">
+      <c r="V26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V26" s="94" t="inlineStr">
+      <c r="W26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="94" t="inlineStr">
+      <c r="X26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X26" s="94" t="inlineStr">
+      <c r="Y26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="93" t="inlineStr">
+      <c r="Z26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA26" s="94" t="inlineStr">
+      <c r="AB26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB26" s="94" t="inlineStr">
+      <c r="AC26" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AC26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AD26" s="93" t="inlineStr">
@@ -9343,94 +9343,94 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="C27" s="95" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="D27" s="95" t="n">
         <v>-2.74</v>
       </c>
-      <c r="C27" s="95" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="D27" s="95" t="n">
+      <c r="E27" s="95" t="n">
         <v>-2.68</v>
       </c>
-      <c r="E27" s="95" t="n">
+      <c r="F27" s="95" t="n">
         <v>-0.89</v>
       </c>
-      <c r="F27" s="95" t="n">
+      <c r="G27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G27" s="95" t="n">
+      <c r="H27" s="95" t="n">
         <v>0.9</v>
       </c>
-      <c r="H27" s="95" t="n">
+      <c r="I27" s="95" t="n">
         <v>1.13</v>
       </c>
-      <c r="I27" s="95" t="n">
+      <c r="J27" s="95" t="n">
         <v>1.93</v>
       </c>
-      <c r="J27" s="95" t="n">
+      <c r="K27" s="95" t="n">
         <v>0.65</v>
       </c>
-      <c r="K27" s="95" t="n">
+      <c r="L27" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="L27" s="95" t="n">
+      <c r="M27" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="M27" s="95" t="n">
+      <c r="N27" s="95" t="n">
         <v>0.44</v>
       </c>
-      <c r="N27" s="95" t="n">
+      <c r="O27" s="95" t="n">
         <v>-0.35</v>
       </c>
-      <c r="O27" s="95" t="n">
+      <c r="P27" s="95" t="n">
         <v>-0.73</v>
       </c>
-      <c r="P27" s="95" t="n">
+      <c r="Q27" s="95" t="n">
         <v>-1</v>
       </c>
-      <c r="Q27" s="95" t="n">
+      <c r="R27" s="95" t="n">
         <v>-1.61</v>
       </c>
-      <c r="R27" s="95" t="n">
+      <c r="S27" s="95" t="n">
         <v>-1.66</v>
       </c>
-      <c r="S27" s="95" t="n">
+      <c r="T27" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="T27" s="95" t="n">
+      <c r="U27" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="U27" s="95" t="n">
+      <c r="V27" s="95" t="n">
         <v>-3.76</v>
       </c>
-      <c r="V27" s="95" t="n">
+      <c r="W27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="W27" s="95" t="n">
+      <c r="X27" s="95" t="n">
         <v>-0.28</v>
       </c>
-      <c r="X27" s="95" t="n">
+      <c r="Y27" s="95" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="Y27" s="95" t="n">
-        <v>3.06</v>
       </c>
       <c r="Z27" s="95" t="n">
         <v>3.06</v>
       </c>
       <c r="AA27" s="95" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB27" s="95" t="n">
         <v>3.91</v>
       </c>
-      <c r="AB27" s="95" t="n">
+      <c r="AC27" s="95" t="n">
         <v>4.32</v>
       </c>
-      <c r="AC27" s="95" t="n">
+      <c r="AD27" s="95" t="n">
         <v>6.09</v>
       </c>
-      <c r="AD27" s="95" t="n">
+      <c r="AE27" s="95" t="n">
         <v>5.91</v>
-      </c>
-      <c r="AE27" s="95" t="n">
-        <v>5.66</v>
       </c>
     </row>
     <row r="28">
@@ -9440,94 +9440,94 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="C28" s="95" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="D28" s="95" t="n">
         <v>9.02</v>
       </c>
-      <c r="C28" s="95" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="D28" s="95" t="n">
+      <c r="E28" s="95" t="n">
         <v>10.76</v>
       </c>
-      <c r="E28" s="95" t="n">
+      <c r="F28" s="95" t="n">
         <v>11.54</v>
       </c>
-      <c r="F28" s="95" t="n">
+      <c r="G28" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="G28" s="95" t="n">
+      <c r="H28" s="95" t="n">
         <v>11.95</v>
       </c>
-      <c r="H28" s="95" t="n">
+      <c r="I28" s="95" t="n">
         <v>12.67</v>
       </c>
-      <c r="I28" s="95" t="n">
+      <c r="J28" s="95" t="n">
         <v>11.04</v>
       </c>
-      <c r="J28" s="95" t="n">
+      <c r="K28" s="95" t="n">
         <v>10.68</v>
       </c>
-      <c r="K28" s="95" t="n">
+      <c r="L28" s="95" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="L28" s="95" t="n">
+      <c r="M28" s="95" t="n">
         <v>9.98</v>
       </c>
-      <c r="M28" s="95" t="n">
+      <c r="N28" s="95" t="n">
         <v>7.16</v>
       </c>
-      <c r="N28" s="95" t="n">
+      <c r="O28" s="95" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="O28" s="95" t="n">
+      <c r="P28" s="95" t="n">
         <v>7.37</v>
       </c>
-      <c r="P28" s="95" t="n">
+      <c r="Q28" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="Q28" s="95" t="n">
+      <c r="R28" s="95" t="n">
         <v>7.12</v>
       </c>
-      <c r="R28" s="95" t="n">
+      <c r="S28" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="S28" s="95" t="n">
+      <c r="T28" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="T28" s="95" t="n">
+      <c r="U28" s="95" t="n">
         <v>4.85</v>
       </c>
-      <c r="U28" s="95" t="n">
+      <c r="V28" s="95" t="n">
         <v>4.49</v>
       </c>
-      <c r="V28" s="95" t="n">
+      <c r="W28" s="95" t="n">
         <v>6.19</v>
       </c>
-      <c r="W28" s="95" t="n">
+      <c r="X28" s="95" t="n">
         <v>5.6</v>
       </c>
-      <c r="X28" s="95" t="n">
+      <c r="Y28" s="95" t="n">
         <v>5.35</v>
-      </c>
-      <c r="Y28" s="95" t="n">
-        <v>10.58</v>
       </c>
       <c r="Z28" s="95" t="n">
         <v>10.58</v>
       </c>
       <c r="AA28" s="95" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AB28" s="95" t="n">
         <v>8.9</v>
       </c>
-      <c r="AB28" s="95" t="n">
+      <c r="AC28" s="95" t="n">
         <v>7.88</v>
       </c>
-      <c r="AC28" s="95" t="n">
+      <c r="AD28" s="95" t="n">
         <v>10.75</v>
       </c>
-      <c r="AD28" s="95" t="n">
+      <c r="AE28" s="95" t="n">
         <v>11.21</v>
-      </c>
-      <c r="AE28" s="95" t="n">
-        <v>10.31</v>
       </c>
     </row>
     <row r="29">
@@ -9537,94 +9537,94 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="C29" s="95" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="D29" s="95" t="n">
         <v>21.97</v>
       </c>
-      <c r="C29" s="95" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="D29" s="95" t="n">
+      <c r="E29" s="95" t="n">
         <v>15.42</v>
       </c>
-      <c r="E29" s="95" t="n">
+      <c r="F29" s="95" t="n">
         <v>74.7</v>
       </c>
-      <c r="F29" s="95" t="n">
+      <c r="G29" s="95" t="n">
         <v>51.35</v>
       </c>
-      <c r="G29" s="95" t="n">
+      <c r="H29" s="95" t="n">
         <v>96.66</v>
       </c>
-      <c r="H29" s="95" t="n">
+      <c r="I29" s="95" t="n">
         <v>89.75</v>
       </c>
-      <c r="I29" s="95" t="n">
+      <c r="J29" s="95" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="J29" s="95" t="n">
+      <c r="K29" s="95" t="n">
         <v>77.02</v>
       </c>
-      <c r="K29" s="95" t="n">
+      <c r="L29" s="95" t="n">
         <v>73.3</v>
       </c>
-      <c r="L29" s="95" t="n">
+      <c r="M29" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="M29" s="95" t="n">
+      <c r="N29" s="95" t="n">
         <v>42.32</v>
       </c>
-      <c r="N29" s="95" t="n">
+      <c r="O29" s="95" t="n">
         <v>70.06</v>
       </c>
-      <c r="O29" s="95" t="n">
+      <c r="P29" s="95" t="n">
         <v>61.86</v>
       </c>
-      <c r="P29" s="95" t="n">
+      <c r="Q29" s="95" t="n">
         <v>95.17</v>
       </c>
-      <c r="Q29" s="95" t="n">
+      <c r="R29" s="95" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="R29" s="95" t="n">
+      <c r="S29" s="95" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="S29" s="95" t="n">
+      <c r="T29" s="95" t="n">
         <v>65.19</v>
       </c>
-      <c r="T29" s="95" t="n">
+      <c r="U29" s="95" t="n">
         <v>44.48</v>
       </c>
-      <c r="U29" s="95" t="n">
+      <c r="V29" s="95" t="n">
         <v>6.2</v>
       </c>
-      <c r="V29" s="95" t="n">
+      <c r="W29" s="95" t="n">
         <v>27.81</v>
       </c>
-      <c r="W29" s="95" t="n">
+      <c r="X29" s="95" t="n">
         <v>12.7</v>
       </c>
-      <c r="X29" s="95" t="n">
+      <c r="Y29" s="95" t="n">
         <v>14.52</v>
-      </c>
-      <c r="Y29" s="95" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="Z29" s="95" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="AA29" s="95" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="AB29" s="95" t="n">
         <v>13.66</v>
       </c>
-      <c r="AB29" s="95" t="n">
+      <c r="AC29" s="95" t="n">
         <v>17.16</v>
       </c>
-      <c r="AC29" s="95" t="n">
+      <c r="AD29" s="95" t="n">
         <v>47.94</v>
       </c>
-      <c r="AD29" s="95" t="n">
+      <c r="AE29" s="95" t="n">
         <v>40.09</v>
-      </c>
-      <c r="AE29" s="95" t="n">
-        <v>66.23</v>
       </c>
     </row>
     <row r="30">
@@ -9638,149 +9638,149 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D30" s="93" t="inlineStr">
+      <c r="E30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E30" s="93" t="inlineStr">
+      <c r="F30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="92" t="inlineStr">
+      <c r="G30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G30" s="92" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="I30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="K30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="L30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="92" t="inlineStr">
+      <c r="M30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="93" t="inlineStr">
+      <c r="N30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="94" t="inlineStr">
+      <c r="S30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S30" s="94" t="inlineStr">
+      <c r="T30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T30" s="94" t="inlineStr">
+      <c r="U30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U30" s="94" t="inlineStr">
+      <c r="V30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V30" s="94" t="inlineStr">
+      <c r="W30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W30" s="94" t="inlineStr">
+      <c r="X30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X30" s="93" t="inlineStr">
+      <c r="Y30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y30" s="93" t="inlineStr">
+      <c r="Z30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z30" s="93" t="inlineStr">
+      <c r="AA30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA30" s="93" t="inlineStr">
+      <c r="AB30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB30" s="93" t="inlineStr">
+      <c r="AC30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC30" s="93" t="inlineStr">
+      <c r="AD30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD30" s="93" t="inlineStr">
+      <c r="AE30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -9791,94 +9791,94 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="C31" s="95" t="n">
         <v>-7.28</v>
       </c>
-      <c r="C31" s="95" t="n">
+      <c r="D31" s="95" t="n">
         <v>-7.29</v>
       </c>
-      <c r="D31" s="95" t="n">
+      <c r="E31" s="95" t="n">
         <v>-5.52</v>
       </c>
-      <c r="E31" s="95" t="n">
+      <c r="F31" s="95" t="n">
         <v>-7.32</v>
       </c>
-      <c r="F31" s="95" t="n">
+      <c r="G31" s="95" t="n">
         <v>-1.85</v>
       </c>
-      <c r="G31" s="95" t="n">
+      <c r="H31" s="95" t="n">
         <v>-2.87</v>
       </c>
-      <c r="H31" s="95" t="n">
+      <c r="I31" s="95" t="n">
         <v>-4.44</v>
       </c>
-      <c r="I31" s="95" t="n">
+      <c r="J31" s="95" t="n">
         <v>-4.15</v>
-      </c>
-      <c r="J31" s="95" t="n">
-        <v>-4.11</v>
       </c>
       <c r="K31" s="95" t="n">
         <v>-4.11</v>
       </c>
       <c r="L31" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="M31" s="95" t="n">
         <v>-6.33</v>
       </c>
-      <c r="M31" s="95" t="n">
+      <c r="N31" s="95" t="n">
         <v>-7.13</v>
       </c>
-      <c r="N31" s="95" t="n">
+      <c r="O31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="O31" s="95" t="n">
+      <c r="P31" s="95" t="n">
         <v>-5.28</v>
       </c>
-      <c r="P31" s="95" t="n">
+      <c r="Q31" s="95" t="n">
         <v>-5.31</v>
       </c>
-      <c r="Q31" s="95" t="n">
+      <c r="R31" s="95" t="n">
         <v>-4.5</v>
       </c>
-      <c r="R31" s="95" t="n">
+      <c r="S31" s="95" t="n">
         <v>-7.44</v>
       </c>
-      <c r="S31" s="95" t="n">
+      <c r="T31" s="95" t="n">
         <v>-5.1</v>
       </c>
-      <c r="T31" s="95" t="n">
+      <c r="U31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="U31" s="95" t="n">
+      <c r="V31" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="V31" s="95" t="n">
+      <c r="W31" s="95" t="n">
         <v>-5.71</v>
       </c>
-      <c r="W31" s="95" t="n">
+      <c r="X31" s="95" t="n">
         <v>-5.33</v>
       </c>
-      <c r="X31" s="95" t="n">
+      <c r="Y31" s="95" t="n">
         <v>-0.9</v>
       </c>
-      <c r="Y31" s="95" t="n">
+      <c r="Z31" s="95" t="n">
         <v>0.04</v>
       </c>
-      <c r="Z31" s="95" t="n">
+      <c r="AA31" s="95" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AA31" s="95" t="n">
+      <c r="AB31" s="95" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AB31" s="95" t="n">
+      <c r="AC31" s="95" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AC31" s="95" t="n">
+      <c r="AD31" s="95" t="n">
         <v>-1.63</v>
       </c>
-      <c r="AD31" s="95" t="n">
+      <c r="AE31" s="95" t="n">
         <v>-0.98</v>
-      </c>
-      <c r="AE31" s="95" t="n">
-        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -9888,94 +9888,94 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="C32" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="C32" s="95" t="n">
+      <c r="D32" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="D32" s="95" t="n">
+      <c r="E32" s="95" t="n">
         <v>-2.82</v>
       </c>
-      <c r="E32" s="95" t="n">
+      <c r="F32" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="F32" s="95" t="n">
+      <c r="G32" s="95" t="n">
         <v>2.15</v>
       </c>
-      <c r="G32" s="95" t="n">
+      <c r="H32" s="95" t="n">
         <v>-2.13</v>
       </c>
-      <c r="H32" s="95" t="n">
+      <c r="I32" s="95" t="n">
         <v>-4.01</v>
       </c>
-      <c r="I32" s="95" t="n">
+      <c r="J32" s="95" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="J32" s="95" t="n">
-        <v>-5.22</v>
       </c>
       <c r="K32" s="95" t="n">
         <v>-5.22</v>
       </c>
       <c r="L32" s="95" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M32" s="95" t="n">
         <v>-7.96</v>
       </c>
-      <c r="M32" s="95" t="n">
+      <c r="N32" s="95" t="n">
         <v>-9.43</v>
       </c>
-      <c r="N32" s="95" t="n">
+      <c r="O32" s="95" t="n">
         <v>-11.19</v>
       </c>
-      <c r="O32" s="95" t="n">
+      <c r="P32" s="95" t="n">
         <v>-9.5</v>
       </c>
-      <c r="P32" s="95" t="n">
+      <c r="Q32" s="95" t="n">
         <v>-9.48</v>
       </c>
-      <c r="Q32" s="95" t="n">
+      <c r="R32" s="95" t="n">
         <v>-9.92</v>
       </c>
-      <c r="R32" s="95" t="n">
+      <c r="S32" s="95" t="n">
         <v>-12.73</v>
       </c>
-      <c r="S32" s="95" t="n">
+      <c r="T32" s="95" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="T32" s="95" t="n">
+      <c r="U32" s="95" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="U32" s="95" t="n">
+      <c r="V32" s="95" t="n">
         <v>-5.98</v>
       </c>
-      <c r="V32" s="95" t="n">
+      <c r="W32" s="95" t="n">
         <v>-5.54</v>
       </c>
-      <c r="W32" s="95" t="n">
+      <c r="X32" s="95" t="n">
         <v>-4.26</v>
       </c>
-      <c r="X32" s="95" t="n">
+      <c r="Y32" s="95" t="n">
         <v>-0.29</v>
       </c>
-      <c r="Y32" s="95" t="n">
+      <c r="Z32" s="95" t="n">
         <v>-0.31</v>
       </c>
-      <c r="Z32" s="95" t="n">
+      <c r="AA32" s="95" t="n">
         <v>-2.62</v>
       </c>
-      <c r="AA32" s="95" t="n">
+      <c r="AB32" s="95" t="n">
         <v>-3.12</v>
       </c>
-      <c r="AB32" s="95" t="n">
+      <c r="AC32" s="95" t="n">
         <v>-4.29</v>
       </c>
-      <c r="AC32" s="95" t="n">
+      <c r="AD32" s="95" t="n">
         <v>-4.51</v>
       </c>
-      <c r="AD32" s="95" t="n">
+      <c r="AE32" s="95" t="n">
         <v>-4.98</v>
-      </c>
-      <c r="AE32" s="95" t="n">
-        <v>-3.88</v>
       </c>
     </row>
     <row r="33">
@@ -9985,94 +9985,94 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="C33" s="95" t="n">
         <v>56.21</v>
       </c>
-      <c r="C33" s="95" t="n">
+      <c r="D33" s="95" t="n">
         <v>50.28</v>
       </c>
-      <c r="D33" s="95" t="n">
+      <c r="E33" s="95" t="n">
         <v>58.22</v>
       </c>
-      <c r="E33" s="95" t="n">
+      <c r="F33" s="95" t="n">
         <v>52.42</v>
       </c>
-      <c r="F33" s="95" t="n">
+      <c r="G33" s="95" t="n">
         <v>77.31</v>
       </c>
-      <c r="G33" s="95" t="n">
+      <c r="H33" s="95" t="n">
         <v>71.64</v>
       </c>
-      <c r="H33" s="95" t="n">
+      <c r="I33" s="95" t="n">
         <v>61.74</v>
       </c>
-      <c r="I33" s="95" t="n">
+      <c r="J33" s="95" t="n">
         <v>63.04</v>
-      </c>
-      <c r="J33" s="95" t="n">
-        <v>60.77</v>
       </c>
       <c r="K33" s="95" t="n">
         <v>60.77</v>
       </c>
       <c r="L33" s="95" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="M33" s="95" t="n">
         <v>54.21</v>
       </c>
-      <c r="M33" s="95" t="n">
+      <c r="N33" s="95" t="n">
         <v>42.56</v>
       </c>
-      <c r="N33" s="95" t="n">
+      <c r="O33" s="95" t="n">
         <v>39.44</v>
       </c>
-      <c r="O33" s="95" t="n">
+      <c r="P33" s="95" t="n">
         <v>43.68</v>
       </c>
-      <c r="P33" s="95" t="n">
+      <c r="Q33" s="95" t="n">
         <v>43.96</v>
       </c>
-      <c r="Q33" s="95" t="n">
+      <c r="R33" s="95" t="n">
         <v>46.79</v>
       </c>
-      <c r="R33" s="95" t="n">
+      <c r="S33" s="95" t="n">
         <v>26.47</v>
       </c>
-      <c r="S33" s="95" t="n">
+      <c r="T33" s="95" t="n">
         <v>31.18</v>
       </c>
-      <c r="T33" s="95" t="n">
+      <c r="U33" s="95" t="n">
         <v>31.7</v>
       </c>
-      <c r="U33" s="95" t="n">
+      <c r="V33" s="95" t="n">
         <v>33.25</v>
       </c>
-      <c r="V33" s="95" t="n">
+      <c r="W33" s="95" t="n">
         <v>35.58</v>
       </c>
-      <c r="W33" s="95" t="n">
+      <c r="X33" s="95" t="n">
         <v>39.17</v>
       </c>
-      <c r="X33" s="95" t="n">
+      <c r="Y33" s="95" t="n">
         <v>62.79</v>
       </c>
-      <c r="Y33" s="95" t="n">
+      <c r="Z33" s="95" t="n">
         <v>63.09</v>
       </c>
-      <c r="Z33" s="95" t="n">
+      <c r="AA33" s="95" t="n">
         <v>62.51</v>
       </c>
-      <c r="AA33" s="95" t="n">
+      <c r="AB33" s="95" t="n">
         <v>59.46</v>
       </c>
-      <c r="AB33" s="95" t="n">
+      <c r="AC33" s="95" t="n">
         <v>59.6</v>
       </c>
-      <c r="AC33" s="95" t="n">
+      <c r="AD33" s="95" t="n">
         <v>58.83</v>
       </c>
-      <c r="AD33" s="95" t="n">
+      <c r="AE33" s="95" t="n">
         <v>57.26</v>
-      </c>
-      <c r="AE33" s="95" t="n">
-        <v>60.15</v>
       </c>
     </row>
     <row r="34">
@@ -10086,149 +10086,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="93" t="inlineStr">
+      <c r="C34" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D34" s="93" t="inlineStr">
+      <c r="E34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="93" t="inlineStr">
+      <c r="F34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="I34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="J34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="K34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="L34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="O34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="94" t="inlineStr">
+      <c r="P34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P34" s="94" t="inlineStr">
+      <c r="Q34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="94" t="inlineStr">
+      <c r="R34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="94" t="inlineStr">
+      <c r="S34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="94" t="inlineStr">
+      <c r="T34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="94" t="inlineStr">
+      <c r="U34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="V34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V34" s="94" t="inlineStr">
+      <c r="W34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W34" s="93" t="inlineStr">
+      <c r="X34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X34" s="93" t="inlineStr">
+      <c r="Y34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y34" s="93" t="inlineStr">
+      <c r="Z34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z34" s="93" t="inlineStr">
+      <c r="AA34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA34" s="93" t="inlineStr">
+      <c r="AB34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB34" s="93" t="inlineStr">
+      <c r="AC34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC34" s="93" t="inlineStr">
+      <c r="AD34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD34" s="93" t="inlineStr">
+      <c r="AE34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10239,73 +10239,73 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="C35" s="95" t="n">
         <v>-1.21</v>
       </c>
-      <c r="C35" s="95" t="n">
+      <c r="D35" s="95" t="n">
         <v>0.33</v>
       </c>
-      <c r="D35" s="95" t="n">
+      <c r="E35" s="95" t="n">
         <v>0.71</v>
       </c>
-      <c r="E35" s="95" t="n">
+      <c r="F35" s="95" t="n">
         <v>0.63</v>
       </c>
-      <c r="F35" s="95" t="n">
+      <c r="G35" s="95" t="n">
         <v>1.1</v>
       </c>
-      <c r="G35" s="95" t="n">
+      <c r="H35" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="H35" s="95" t="n">
+      <c r="I35" s="95" t="n">
         <v>2.62</v>
       </c>
-      <c r="I35" s="95" t="n">
+      <c r="J35" s="95" t="n">
         <v>1.79</v>
       </c>
-      <c r="J35" s="95" t="n">
+      <c r="K35" s="95" t="n">
         <v>1.86</v>
       </c>
-      <c r="K35" s="95" t="n">
+      <c r="L35" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="L35" s="95" t="n">
+      <c r="M35" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="M35" s="95" t="n">
+      <c r="N35" s="95" t="n">
         <v>0.66</v>
       </c>
-      <c r="N35" s="95" t="n">
+      <c r="O35" s="95" t="n">
         <v>0.39</v>
       </c>
-      <c r="O35" s="95" t="n">
+      <c r="P35" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="P35" s="95" t="n">
+      <c r="Q35" s="95" t="n">
         <v>-2.39</v>
       </c>
-      <c r="Q35" s="95" t="n">
+      <c r="R35" s="95" t="n">
         <v>-1.83</v>
       </c>
-      <c r="R35" s="95" t="n">
+      <c r="S35" s="95" t="n">
         <v>-2.05</v>
       </c>
-      <c r="S35" s="95" t="n">
+      <c r="T35" s="95" t="n">
         <v>-1.53</v>
       </c>
-      <c r="T35" s="95" t="n">
+      <c r="U35" s="95" t="n">
         <v>-0.95</v>
       </c>
-      <c r="U35" s="95" t="n">
+      <c r="V35" s="95" t="n">
         <v>-2.12</v>
       </c>
-      <c r="V35" s="95" t="n">
+      <c r="W35" s="95" t="n">
         <v>-2.46</v>
       </c>
-      <c r="W35" s="95" t="n">
+      <c r="X35" s="95" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="X35" s="95" t="n">
-        <v>-0.53</v>
       </c>
       <c r="Y35" s="95" t="n">
         <v>-0.53</v>
@@ -10314,19 +10314,19 @@
         <v>-0.53</v>
       </c>
       <c r="AA35" s="95" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AB35" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AB35" s="95" t="n">
+      <c r="AC35" s="95" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AC35" s="95" t="n">
+      <c r="AD35" s="95" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AD35" s="95" t="n">
+      <c r="AE35" s="95" t="n">
         <v>-0.27</v>
-      </c>
-      <c r="AE35" s="95" t="n">
-        <v>0.42</v>
       </c>
     </row>
     <row r="36">
@@ -10336,73 +10336,73 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="C36" s="95" t="n">
         <v>1.58</v>
-      </c>
-      <c r="C36" s="95" t="n">
-        <v>2.33</v>
       </c>
       <c r="D36" s="95" t="n">
         <v>2.33</v>
       </c>
       <c r="E36" s="95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F36" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="F36" s="95" t="n">
+      <c r="G36" s="95" t="n">
         <v>2.85</v>
       </c>
-      <c r="G36" s="95" t="n">
+      <c r="H36" s="95" t="n">
         <v>1.83</v>
       </c>
-      <c r="H36" s="95" t="n">
+      <c r="I36" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="I36" s="95" t="n">
+      <c r="J36" s="95" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J36" s="95" t="n">
+      <c r="K36" s="95" t="n">
         <v>-1.02</v>
       </c>
-      <c r="K36" s="95" t="n">
+      <c r="L36" s="95" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="L36" s="95" t="n">
+      <c r="M36" s="95" t="n">
         <v>-1.47</v>
       </c>
-      <c r="M36" s="95" t="n">
+      <c r="N36" s="95" t="n">
         <v>-1.42</v>
       </c>
-      <c r="N36" s="95" t="n">
+      <c r="O36" s="95" t="n">
         <v>-1.81</v>
       </c>
-      <c r="O36" s="95" t="n">
+      <c r="P36" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="P36" s="95" t="n">
+      <c r="Q36" s="95" t="n">
         <v>-2.35</v>
       </c>
-      <c r="Q36" s="95" t="n">
+      <c r="R36" s="95" t="n">
         <v>-1.57</v>
       </c>
-      <c r="R36" s="95" t="n">
+      <c r="S36" s="95" t="n">
         <v>-0.54</v>
       </c>
-      <c r="S36" s="95" t="n">
+      <c r="T36" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="T36" s="95" t="n">
+      <c r="U36" s="95" t="n">
         <v>1.94</v>
       </c>
-      <c r="U36" s="95" t="n">
+      <c r="V36" s="95" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="V36" s="95" t="n">
+      <c r="W36" s="95" t="n">
         <v>0.31</v>
       </c>
-      <c r="W36" s="95" t="n">
+      <c r="X36" s="95" t="n">
         <v>0.42</v>
-      </c>
-      <c r="X36" s="95" t="n">
-        <v>3.12</v>
       </c>
       <c r="Y36" s="95" t="n">
         <v>3.12</v>
@@ -10411,19 +10411,19 @@
         <v>3.12</v>
       </c>
       <c r="AA36" s="95" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB36" s="95" t="n">
         <v>3.72</v>
       </c>
-      <c r="AB36" s="95" t="n">
+      <c r="AC36" s="95" t="n">
         <v>2.73</v>
       </c>
-      <c r="AC36" s="95" t="n">
+      <c r="AD36" s="95" t="n">
         <v>0.95</v>
       </c>
-      <c r="AD36" s="95" t="n">
+      <c r="AE36" s="95" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AE36" s="95" t="n">
-        <v>1.21</v>
       </c>
     </row>
     <row r="37">
@@ -10433,73 +10433,73 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="C37" s="95" t="n">
         <v>23.23</v>
       </c>
-      <c r="C37" s="95" t="n">
+      <c r="D37" s="95" t="n">
         <v>50.34</v>
       </c>
-      <c r="D37" s="95" t="n">
+      <c r="E37" s="95" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="E37" s="95" t="n">
+      <c r="F37" s="95" t="n">
         <v>65.09</v>
       </c>
-      <c r="F37" s="95" t="n">
+      <c r="G37" s="95" t="n">
         <v>86.66</v>
       </c>
-      <c r="G37" s="95" t="n">
+      <c r="H37" s="95" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="H37" s="95" t="n">
+      <c r="I37" s="95" t="n">
         <v>88</v>
       </c>
-      <c r="I37" s="95" t="n">
+      <c r="J37" s="95" t="n">
         <v>77.98</v>
       </c>
-      <c r="J37" s="95" t="n">
+      <c r="K37" s="95" t="n">
         <v>59.82</v>
       </c>
-      <c r="K37" s="95" t="n">
+      <c r="L37" s="95" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="L37" s="95" t="n">
+      <c r="M37" s="95" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="M37" s="95" t="n">
+      <c r="N37" s="95" t="n">
         <v>68.98</v>
       </c>
-      <c r="N37" s="95" t="n">
+      <c r="O37" s="95" t="n">
         <v>60.96</v>
       </c>
-      <c r="O37" s="95" t="n">
+      <c r="P37" s="95" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="P37" s="95" t="n">
+      <c r="Q37" s="95" t="n">
         <v>20.58</v>
       </c>
-      <c r="Q37" s="95" t="n">
+      <c r="R37" s="95" t="n">
         <v>30.12</v>
       </c>
-      <c r="R37" s="95" t="n">
+      <c r="S37" s="95" t="n">
         <v>12.08</v>
       </c>
-      <c r="S37" s="95" t="n">
+      <c r="T37" s="95" t="n">
         <v>13.57</v>
       </c>
-      <c r="T37" s="95" t="n">
+      <c r="U37" s="95" t="n">
         <v>28.44</v>
       </c>
-      <c r="U37" s="95" t="n">
+      <c r="V37" s="95" t="n">
         <v>44.72</v>
       </c>
-      <c r="V37" s="95" t="n">
+      <c r="W37" s="95" t="n">
         <v>14.66</v>
       </c>
-      <c r="W37" s="95" t="n">
+      <c r="X37" s="95" t="n">
         <v>28.1</v>
-      </c>
-      <c r="X37" s="95" t="n">
-        <v>80.38</v>
       </c>
       <c r="Y37" s="95" t="n">
         <v>80.38</v>
@@ -10508,19 +10508,19 @@
         <v>80.38</v>
       </c>
       <c r="AA37" s="95" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="AB37" s="95" t="n">
         <v>68.92</v>
       </c>
-      <c r="AB37" s="95" t="n">
+      <c r="AC37" s="95" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="AC37" s="95" t="n">
+      <c r="AD37" s="95" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="AD37" s="95" t="n">
+      <c r="AE37" s="95" t="n">
         <v>63.9</v>
-      </c>
-      <c r="AE37" s="95" t="n">
-        <v>90.77</v>
       </c>
     </row>
     <row r="38">
@@ -10534,119 +10534,119 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="93" t="inlineStr">
+      <c r="C38" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D38" s="93" t="inlineStr">
+      <c r="E38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="93" t="inlineStr">
+      <c r="F38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="93" t="inlineStr">
+      <c r="G38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="92" t="inlineStr">
+      <c r="H38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M38" s="93" t="inlineStr">
+      <c r="N38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="92" t="inlineStr">
+      <c r="O38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O38" s="92" t="inlineStr">
+      <c r="P38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P38" s="92" t="inlineStr">
+      <c r="Q38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q38" s="92" t="inlineStr">
+      <c r="R38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R38" s="94" t="inlineStr">
+      <c r="S38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S38" s="93" t="inlineStr">
+      <c r="T38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="94" t="inlineStr">
+      <c r="U38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U38" s="94" t="inlineStr">
+      <c r="V38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V38" s="93" t="inlineStr">
+      <c r="W38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W38" s="93" t="inlineStr">
+      <c r="X38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X38" s="93" t="inlineStr">
+      <c r="Y38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Y38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="Z38" s="92" t="inlineStr">
@@ -10687,94 +10687,94 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C39" s="95" t="n">
         <v>2.67</v>
-      </c>
-      <c r="C39" s="95" t="n">
-        <v>5.39</v>
       </c>
       <c r="D39" s="95" t="n">
         <v>5.39</v>
       </c>
       <c r="E39" s="95" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="F39" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="F39" s="95" t="n">
+      <c r="G39" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="G39" s="95" t="n">
+      <c r="H39" s="95" t="n">
         <v>7.31</v>
       </c>
-      <c r="H39" s="95" t="n">
+      <c r="I39" s="95" t="n">
         <v>7.21</v>
       </c>
-      <c r="I39" s="95" t="n">
+      <c r="J39" s="95" t="n">
         <v>6.84</v>
       </c>
-      <c r="J39" s="95" t="n">
+      <c r="K39" s="95" t="n">
         <v>7.46</v>
       </c>
-      <c r="K39" s="95" t="n">
+      <c r="L39" s="95" t="n">
         <v>6.69</v>
       </c>
-      <c r="L39" s="95" t="n">
+      <c r="M39" s="95" t="n">
         <v>5.73</v>
       </c>
-      <c r="M39" s="95" t="n">
+      <c r="N39" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="N39" s="95" t="n">
+      <c r="O39" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="O39" s="95" t="n">
+      <c r="P39" s="95" t="n">
         <v>7.48</v>
       </c>
-      <c r="P39" s="95" t="n">
+      <c r="Q39" s="95" t="n">
         <v>6.99</v>
       </c>
-      <c r="Q39" s="95" t="n">
+      <c r="R39" s="95" t="n">
         <v>7.27</v>
       </c>
-      <c r="R39" s="95" t="n">
+      <c r="S39" s="95" t="n">
         <v>5.46</v>
       </c>
-      <c r="S39" s="95" t="n">
+      <c r="T39" s="95" t="n">
         <v>6.4</v>
       </c>
-      <c r="T39" s="95" t="n">
+      <c r="U39" s="95" t="n">
         <v>6.18</v>
       </c>
-      <c r="U39" s="95" t="n">
+      <c r="V39" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="V39" s="95" t="n">
+      <c r="W39" s="95" t="n">
         <v>7.51</v>
       </c>
-      <c r="W39" s="95" t="n">
+      <c r="X39" s="95" t="n">
         <v>7.66</v>
       </c>
-      <c r="X39" s="95" t="n">
+      <c r="Y39" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="Y39" s="95" t="n">
+      <c r="Z39" s="95" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="Z39" s="95" t="n">
+      <c r="AA39" s="95" t="n">
         <v>10.73</v>
       </c>
-      <c r="AA39" s="95" t="n">
+      <c r="AB39" s="95" t="n">
         <v>13.95</v>
       </c>
-      <c r="AB39" s="95" t="n">
+      <c r="AC39" s="95" t="n">
         <v>6.95</v>
       </c>
-      <c r="AC39" s="95" t="n">
+      <c r="AD39" s="95" t="n">
         <v>10.48</v>
       </c>
-      <c r="AD39" s="95" t="n">
+      <c r="AE39" s="95" t="n">
         <v>10.57</v>
-      </c>
-      <c r="AE39" s="95" t="n">
-        <v>8.84</v>
       </c>
     </row>
     <row r="40">
@@ -10784,94 +10784,94 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C40" s="95" t="n">
         <v>9.94</v>
-      </c>
-      <c r="C40" s="95" t="n">
-        <v>12.83</v>
       </c>
       <c r="D40" s="95" t="n">
         <v>12.83</v>
       </c>
       <c r="E40" s="95" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="F40" s="95" t="n">
         <v>12.79</v>
       </c>
-      <c r="F40" s="95" t="n">
+      <c r="G40" s="95" t="n">
         <v>15.25</v>
       </c>
-      <c r="G40" s="95" t="n">
+      <c r="H40" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="H40" s="95" t="n">
+      <c r="I40" s="95" t="n">
         <v>15.29</v>
       </c>
-      <c r="I40" s="95" t="n">
+      <c r="J40" s="95" t="n">
         <v>14.9</v>
       </c>
-      <c r="J40" s="95" t="n">
+      <c r="K40" s="95" t="n">
         <v>14.75</v>
       </c>
-      <c r="K40" s="95" t="n">
+      <c r="L40" s="95" t="n">
         <v>14.79</v>
       </c>
-      <c r="L40" s="95" t="n">
+      <c r="M40" s="95" t="n">
         <v>13.96</v>
       </c>
-      <c r="M40" s="95" t="n">
+      <c r="N40" s="95" t="n">
         <v>14.46</v>
       </c>
-      <c r="N40" s="95" t="n">
+      <c r="O40" s="95" t="n">
         <v>14.07</v>
       </c>
-      <c r="O40" s="95" t="n">
+      <c r="P40" s="95" t="n">
         <v>14.24</v>
       </c>
-      <c r="P40" s="95" t="n">
+      <c r="Q40" s="95" t="n">
         <v>14.96</v>
       </c>
-      <c r="Q40" s="95" t="n">
+      <c r="R40" s="95" t="n">
         <v>15.21</v>
       </c>
-      <c r="R40" s="95" t="n">
+      <c r="S40" s="95" t="n">
         <v>12.06</v>
       </c>
-      <c r="S40" s="95" t="n">
+      <c r="T40" s="95" t="n">
         <v>12.77</v>
       </c>
-      <c r="T40" s="95" t="n">
+      <c r="U40" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="U40" s="95" t="n">
+      <c r="V40" s="95" t="n">
         <v>11.57</v>
       </c>
-      <c r="V40" s="95" t="n">
+      <c r="W40" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="W40" s="95" t="n">
+      <c r="X40" s="95" t="n">
         <v>12.04</v>
       </c>
-      <c r="X40" s="95" t="n">
+      <c r="Y40" s="95" t="n">
         <v>11.38</v>
       </c>
-      <c r="Y40" s="95" t="n">
+      <c r="Z40" s="95" t="n">
         <v>11.44</v>
       </c>
-      <c r="Z40" s="95" t="n">
+      <c r="AA40" s="95" t="n">
         <v>11.79</v>
       </c>
-      <c r="AA40" s="95" t="n">
+      <c r="AB40" s="95" t="n">
         <v>11.18</v>
       </c>
-      <c r="AB40" s="95" t="n">
+      <c r="AC40" s="95" t="n">
         <v>10.81</v>
       </c>
-      <c r="AC40" s="95" t="n">
+      <c r="AD40" s="95" t="n">
         <v>10.8</v>
       </c>
-      <c r="AD40" s="95" t="n">
+      <c r="AE40" s="95" t="n">
         <v>12.69</v>
-      </c>
-      <c r="AE40" s="95" t="n">
-        <v>12.14</v>
       </c>
     </row>
     <row r="41">
@@ -10881,94 +10881,94 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="C41" s="95" t="n">
         <v>38.91</v>
-      </c>
-      <c r="C41" s="95" t="n">
-        <v>56.68</v>
       </c>
       <c r="D41" s="95" t="n">
         <v>56.68</v>
       </c>
       <c r="E41" s="95" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="F41" s="95" t="n">
         <v>57.12</v>
       </c>
-      <c r="F41" s="95" t="n">
+      <c r="G41" s="95" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="G41" s="95" t="n">
+      <c r="H41" s="95" t="n">
         <v>83.77</v>
       </c>
-      <c r="H41" s="95" t="n">
+      <c r="I41" s="95" t="n">
         <v>80.52</v>
       </c>
-      <c r="I41" s="95" t="n">
+      <c r="J41" s="95" t="n">
         <v>79.08</v>
       </c>
-      <c r="J41" s="95" t="n">
+      <c r="K41" s="95" t="n">
         <v>79.38</v>
       </c>
-      <c r="K41" s="95" t="n">
+      <c r="L41" s="95" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="L41" s="95" t="n">
+      <c r="M41" s="95" t="n">
         <v>66.75</v>
       </c>
-      <c r="M41" s="95" t="n">
+      <c r="N41" s="95" t="n">
         <v>64.14</v>
       </c>
-      <c r="N41" s="95" t="n">
+      <c r="O41" s="95" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="O41" s="95" t="n">
+      <c r="P41" s="95" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="P41" s="95" t="n">
+      <c r="Q41" s="95" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="Q41" s="95" t="n">
+      <c r="R41" s="95" t="n">
         <v>66.14</v>
       </c>
-      <c r="R41" s="95" t="n">
+      <c r="S41" s="95" t="n">
         <v>50.55</v>
       </c>
-      <c r="S41" s="95" t="n">
+      <c r="T41" s="95" t="n">
         <v>57.1</v>
       </c>
-      <c r="T41" s="95" t="n">
+      <c r="U41" s="95" t="n">
         <v>52.02</v>
       </c>
-      <c r="U41" s="95" t="n">
+      <c r="V41" s="95" t="n">
         <v>46.05</v>
       </c>
-      <c r="V41" s="95" t="n">
+      <c r="W41" s="95" t="n">
         <v>66.09</v>
       </c>
-      <c r="W41" s="95" t="n">
+      <c r="X41" s="95" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="X41" s="95" t="n">
+      <c r="Y41" s="95" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="Y41" s="95" t="n">
+      <c r="Z41" s="95" t="n">
         <v>75.97</v>
       </c>
-      <c r="Z41" s="95" t="n">
+      <c r="AA41" s="95" t="n">
         <v>74.36</v>
       </c>
-      <c r="AA41" s="95" t="n">
+      <c r="AB41" s="95" t="n">
         <v>72.38</v>
       </c>
-      <c r="AB41" s="95" t="n">
+      <c r="AC41" s="95" t="n">
         <v>69.15000000000001</v>
       </c>
-      <c r="AC41" s="95" t="n">
+      <c r="AD41" s="95" t="n">
         <v>68.44</v>
       </c>
-      <c r="AD41" s="95" t="n">
+      <c r="AE41" s="95" t="n">
         <v>68.31999999999999</v>
-      </c>
-      <c r="AE41" s="95" t="n">
-        <v>62.57</v>
       </c>
     </row>
     <row r="42">
@@ -10992,134 +10992,134 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="93" t="inlineStr">
+      <c r="E42" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F42" s="92" t="inlineStr">
+      <c r="G42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="I42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="92" t="inlineStr">
+      <c r="J42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="K42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="92" t="inlineStr">
+      <c r="M42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="92" t="inlineStr">
+      <c r="O42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="93" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="92" t="inlineStr">
+      <c r="Q42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="93" t="inlineStr">
+      <c r="R42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="94" t="inlineStr">
+      <c r="S42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S42" s="94" t="inlineStr">
+      <c r="T42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="94" t="inlineStr">
+      <c r="U42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="94" t="inlineStr">
+      <c r="V42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="94" t="inlineStr">
+      <c r="W42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="94" t="inlineStr">
+      <c r="X42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="93" t="inlineStr">
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="93" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="93" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="92" t="inlineStr">
+      <c r="AB42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE42" s="92" t="inlineStr">
@@ -11138,91 +11138,91 @@
         <v>-1.96</v>
       </c>
       <c r="C43" s="95" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="D43" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="D43" s="95" t="n">
+      <c r="E43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="E43" s="95" t="n">
+      <c r="F43" s="95" t="n">
         <v>0.11</v>
       </c>
-      <c r="F43" s="95" t="n">
+      <c r="G43" s="95" t="n">
         <v>1.51</v>
       </c>
-      <c r="G43" s="95" t="n">
+      <c r="H43" s="95" t="n">
         <v>0.6</v>
       </c>
-      <c r="H43" s="95" t="n">
+      <c r="I43" s="95" t="n">
         <v>-0.87</v>
       </c>
-      <c r="I43" s="95" t="n">
+      <c r="J43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="J43" s="95" t="n">
+      <c r="K43" s="95" t="n">
         <v>-0.7</v>
       </c>
-      <c r="K43" s="95" t="n">
+      <c r="L43" s="95" t="n">
         <v>0.28</v>
       </c>
-      <c r="L43" s="95" t="n">
+      <c r="M43" s="95" t="n">
         <v>1.12</v>
       </c>
-      <c r="M43" s="95" t="n">
+      <c r="N43" s="95" t="n">
         <v>-2.16</v>
       </c>
-      <c r="N43" s="95" t="n">
+      <c r="O43" s="95" t="n">
         <v>-2.28</v>
       </c>
-      <c r="O43" s="95" t="n">
+      <c r="P43" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="P43" s="95" t="n">
+      <c r="Q43" s="95" t="n">
         <v>-2.14</v>
       </c>
-      <c r="Q43" s="95" t="n">
+      <c r="R43" s="95" t="n">
         <v>-3.08</v>
       </c>
-      <c r="R43" s="95" t="n">
+      <c r="S43" s="95" t="n">
         <v>-2.29</v>
       </c>
-      <c r="S43" s="95" t="n">
+      <c r="T43" s="95" t="n">
         <v>-2.9</v>
       </c>
-      <c r="T43" s="95" t="n">
+      <c r="U43" s="95" t="n">
         <v>-1.93</v>
       </c>
-      <c r="U43" s="95" t="n">
+      <c r="V43" s="95" t="n">
         <v>-2.01</v>
       </c>
-      <c r="V43" s="95" t="n">
+      <c r="W43" s="95" t="n">
         <v>-3.58</v>
       </c>
-      <c r="W43" s="95" t="n">
+      <c r="X43" s="95" t="n">
         <v>-4.62</v>
       </c>
-      <c r="X43" s="95" t="n">
+      <c r="Y43" s="95" t="n">
         <v>-2.75</v>
       </c>
-      <c r="Y43" s="95" t="n">
+      <c r="Z43" s="95" t="n">
         <v>-3.14</v>
       </c>
-      <c r="Z43" s="95" t="n">
+      <c r="AA43" s="95" t="n">
         <v>-4.63</v>
       </c>
-      <c r="AA43" s="95" t="n">
+      <c r="AB43" s="95" t="n">
         <v>-4.96</v>
       </c>
-      <c r="AB43" s="95" t="n">
+      <c r="AC43" s="95" t="n">
         <v>-5.36</v>
       </c>
-      <c r="AC43" s="95" t="n">
+      <c r="AD43" s="95" t="n">
         <v>-4.69</v>
       </c>
-      <c r="AD43" s="95" t="n">
+      <c r="AE43" s="95" t="n">
         <v>-5.1</v>
-      </c>
-      <c r="AE43" s="95" t="n">
-        <v>-5.2</v>
       </c>
     </row>
     <row r="44">
@@ -11235,91 +11235,91 @@
         <v>-6.31</v>
       </c>
       <c r="C44" s="95" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="D44" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="D44" s="95" t="n">
+      <c r="E44" s="95" t="n">
         <v>-5.85</v>
       </c>
-      <c r="E44" s="95" t="n">
+      <c r="F44" s="95" t="n">
         <v>-4.68</v>
       </c>
-      <c r="F44" s="95" t="n">
+      <c r="G44" s="95" t="n">
         <v>-2.89</v>
       </c>
-      <c r="G44" s="95" t="n">
+      <c r="H44" s="95" t="n">
         <v>-3.77</v>
       </c>
-      <c r="H44" s="95" t="n">
+      <c r="I44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="I44" s="95" t="n">
+      <c r="J44" s="95" t="n">
         <v>-6.35</v>
       </c>
-      <c r="J44" s="95" t="n">
+      <c r="K44" s="95" t="n">
         <v>-6.86</v>
       </c>
-      <c r="K44" s="95" t="n">
+      <c r="L44" s="95" t="n">
         <v>-7.99</v>
       </c>
-      <c r="L44" s="95" t="n">
+      <c r="M44" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="M44" s="95" t="n">
+      <c r="N44" s="95" t="n">
         <v>-8.43</v>
       </c>
-      <c r="N44" s="95" t="n">
+      <c r="O44" s="95" t="n">
         <v>-8.75</v>
       </c>
-      <c r="O44" s="95" t="n">
+      <c r="P44" s="95" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="P44" s="95" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="Q44" s="95" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="R44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="S44" s="95" t="n">
         <v>-9.26</v>
       </c>
-      <c r="S44" s="95" t="n">
+      <c r="T44" s="95" t="n">
         <v>-9.44</v>
       </c>
-      <c r="T44" s="95" t="n">
+      <c r="U44" s="95" t="n">
         <v>-9.02</v>
       </c>
-      <c r="U44" s="95" t="n">
+      <c r="V44" s="95" t="n">
         <v>-10.35</v>
       </c>
-      <c r="V44" s="95" t="n">
+      <c r="W44" s="95" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="W44" s="95" t="n">
+      <c r="X44" s="95" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="X44" s="95" t="n">
+      <c r="Y44" s="95" t="n">
         <v>-7.18</v>
       </c>
-      <c r="Y44" s="95" t="n">
+      <c r="Z44" s="95" t="n">
         <v>-6.04</v>
       </c>
-      <c r="Z44" s="95" t="n">
+      <c r="AA44" s="95" t="n">
         <v>-5.64</v>
       </c>
-      <c r="AA44" s="95" t="n">
+      <c r="AB44" s="95" t="n">
         <v>-4.72</v>
       </c>
-      <c r="AB44" s="95" t="n">
+      <c r="AC44" s="95" t="n">
         <v>-5.61</v>
       </c>
-      <c r="AC44" s="95" t="n">
+      <c r="AD44" s="95" t="n">
         <v>-5.62</v>
       </c>
-      <c r="AD44" s="95" t="n">
+      <c r="AE44" s="95" t="n">
         <v>-4.58</v>
-      </c>
-      <c r="AE44" s="95" t="n">
-        <v>-4.48</v>
       </c>
     </row>
     <row r="45">
@@ -11332,91 +11332,91 @@
         <v>33.57</v>
       </c>
       <c r="C45" s="95" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="D45" s="95" t="n">
         <v>45.48</v>
       </c>
-      <c r="D45" s="95" t="n">
+      <c r="E45" s="95" t="n">
         <v>44.93</v>
       </c>
-      <c r="E45" s="95" t="n">
+      <c r="F45" s="95" t="n">
         <v>52.35</v>
       </c>
-      <c r="F45" s="95" t="n">
+      <c r="G45" s="95" t="n">
         <v>78.61</v>
       </c>
-      <c r="G45" s="95" t="n">
+      <c r="H45" s="95" t="n">
         <v>75.48</v>
       </c>
-      <c r="H45" s="95" t="n">
+      <c r="I45" s="95" t="n">
         <v>57.98</v>
       </c>
-      <c r="I45" s="95" t="n">
+      <c r="J45" s="95" t="n">
         <v>66.2</v>
       </c>
-      <c r="J45" s="95" t="n">
+      <c r="K45" s="95" t="n">
         <v>52.83</v>
       </c>
-      <c r="K45" s="95" t="n">
+      <c r="L45" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="L45" s="95" t="n">
+      <c r="M45" s="95" t="n">
         <v>74.97</v>
       </c>
-      <c r="M45" s="95" t="n">
+      <c r="N45" s="95" t="n">
         <v>45.92</v>
       </c>
-      <c r="N45" s="95" t="n">
+      <c r="O45" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="O45" s="95" t="n">
+      <c r="P45" s="95" t="n">
         <v>48.71</v>
       </c>
-      <c r="P45" s="95" t="n">
+      <c r="Q45" s="95" t="n">
         <v>53.61</v>
       </c>
-      <c r="Q45" s="95" t="n">
+      <c r="R45" s="95" t="n">
         <v>45.19</v>
       </c>
-      <c r="R45" s="95" t="n">
+      <c r="S45" s="95" t="n">
         <v>32.83</v>
       </c>
-      <c r="S45" s="95" t="n">
+      <c r="T45" s="95" t="n">
         <v>34.58</v>
       </c>
-      <c r="T45" s="95" t="n">
+      <c r="U45" s="95" t="n">
         <v>37.2</v>
       </c>
-      <c r="U45" s="95" t="n">
+      <c r="V45" s="95" t="n">
         <v>16.31</v>
       </c>
-      <c r="V45" s="95" t="n">
+      <c r="W45" s="95" t="n">
         <v>22.99</v>
       </c>
-      <c r="W45" s="95" t="n">
+      <c r="X45" s="95" t="n">
         <v>32.1</v>
       </c>
-      <c r="X45" s="95" t="n">
+      <c r="Y45" s="95" t="n">
         <v>48.66</v>
       </c>
-      <c r="Y45" s="95" t="n">
+      <c r="Z45" s="95" t="n">
         <v>80.73</v>
       </c>
-      <c r="Z45" s="95" t="n">
+      <c r="AA45" s="95" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="AA45" s="95" t="n">
+      <c r="AB45" s="95" t="n">
         <v>83.84</v>
       </c>
-      <c r="AB45" s="95" t="n">
+      <c r="AC45" s="95" t="n">
         <v>74.67</v>
       </c>
-      <c r="AC45" s="95" t="n">
+      <c r="AD45" s="95" t="n">
         <v>72.3</v>
       </c>
-      <c r="AD45" s="95" t="n">
+      <c r="AE45" s="95" t="n">
         <v>85.51000000000001</v>
-      </c>
-      <c r="AE45" s="95" t="n">
-        <v>84.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -11430,149 +11430,149 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C46" s="93" t="inlineStr">
+      <c r="C46" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D46" s="93" t="inlineStr">
+      <c r="E46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="93" t="inlineStr">
+      <c r="F46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="92" t="inlineStr">
+      <c r="G46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="93" t="inlineStr">
+      <c r="I46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="J46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="93" t="inlineStr">
+      <c r="L46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L46" s="92" t="inlineStr">
+      <c r="M46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M46" s="92" t="inlineStr">
+      <c r="N46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="92" t="inlineStr">
+      <c r="O46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="92" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="92" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="92" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="94" t="inlineStr">
+      <c r="S46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S46" s="94" t="inlineStr">
+      <c r="T46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T46" s="94" t="inlineStr">
+      <c r="U46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U46" s="94" t="inlineStr">
+      <c r="V46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V46" s="94" t="inlineStr">
+      <c r="W46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="94" t="inlineStr">
+      <c r="X46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X46" s="93" t="inlineStr">
+      <c r="Y46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA46" s="92" t="inlineStr">
+      <c r="AB46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB46" s="93" t="inlineStr">
+      <c r="AC46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC46" s="93" t="inlineStr">
+      <c r="AD46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD46" s="93" t="inlineStr">
+      <c r="AE46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE46" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -11586,91 +11586,91 @@
         <v>2.59</v>
       </c>
       <c r="C47" s="95" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D47" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="D47" s="95" t="n">
+      <c r="E47" s="95" t="n">
         <v>5.36</v>
       </c>
-      <c r="E47" s="95" t="n">
+      <c r="F47" s="95" t="n">
         <v>4.62</v>
       </c>
-      <c r="F47" s="95" t="n">
+      <c r="G47" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="G47" s="95" t="n">
+      <c r="H47" s="95" t="n">
         <v>4.27</v>
       </c>
-      <c r="H47" s="95" t="n">
+      <c r="I47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="I47" s="95" t="n">
+      <c r="J47" s="95" t="n">
         <v>4.58</v>
       </c>
-      <c r="J47" s="95" t="n">
+      <c r="K47" s="95" t="n">
         <v>3.04</v>
       </c>
-      <c r="K47" s="95" t="n">
+      <c r="L47" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="L47" s="95" t="n">
+      <c r="M47" s="95" t="n">
         <v>4.35</v>
       </c>
-      <c r="M47" s="95" t="n">
+      <c r="N47" s="95" t="n">
         <v>3.06</v>
       </c>
-      <c r="N47" s="95" t="n">
+      <c r="O47" s="95" t="n">
         <v>3.02</v>
       </c>
-      <c r="O47" s="95" t="n">
+      <c r="P47" s="95" t="n">
         <v>1.68</v>
       </c>
-      <c r="P47" s="95" t="n">
+      <c r="Q47" s="95" t="n">
         <v>2.95</v>
-      </c>
-      <c r="Q47" s="95" t="n">
-        <v>1.45</v>
       </c>
       <c r="R47" s="95" t="n">
         <v>1.45</v>
       </c>
       <c r="S47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T47" s="95" t="n">
         <v>0.74</v>
       </c>
-      <c r="T47" s="95" t="n">
+      <c r="U47" s="95" t="n">
         <v>2.08</v>
       </c>
-      <c r="U47" s="95" t="n">
+      <c r="V47" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="V47" s="95" t="n">
+      <c r="W47" s="95" t="n">
         <v>1.7</v>
       </c>
-      <c r="W47" s="95" t="n">
+      <c r="X47" s="95" t="n">
         <v>-0.21</v>
       </c>
-      <c r="X47" s="95" t="n">
+      <c r="Y47" s="95" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y47" s="95" t="n">
+      <c r="Z47" s="95" t="n">
         <v>2.36</v>
       </c>
-      <c r="Z47" s="95" t="n">
+      <c r="AA47" s="95" t="n">
         <v>1.88</v>
       </c>
-      <c r="AA47" s="95" t="n">
+      <c r="AB47" s="95" t="n">
         <v>1.39</v>
       </c>
-      <c r="AB47" s="95" t="n">
+      <c r="AC47" s="95" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC47" s="95" t="n">
+      <c r="AD47" s="95" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD47" s="95" t="n">
+      <c r="AE47" s="95" t="n">
         <v>0.05</v>
-      </c>
-      <c r="AE47" s="95" t="n">
-        <v>0.73</v>
       </c>
     </row>
     <row r="48">
@@ -11683,91 +11683,91 @@
         <v>7.01</v>
       </c>
       <c r="C48" s="95" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="D48" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="D48" s="95" t="n">
+      <c r="E48" s="95" t="n">
         <v>6.58</v>
       </c>
-      <c r="E48" s="95" t="n">
+      <c r="F48" s="95" t="n">
         <v>7.78</v>
       </c>
-      <c r="F48" s="95" t="n">
+      <c r="G48" s="95" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="G48" s="95" t="n">
+      <c r="H48" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="H48" s="95" t="n">
+      <c r="I48" s="95" t="n">
         <v>4.66</v>
-      </c>
-      <c r="I48" s="95" t="n">
-        <v>3.7</v>
       </c>
       <c r="J48" s="95" t="n">
         <v>3.7</v>
       </c>
       <c r="K48" s="95" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L48" s="95" t="n">
         <v>1.72</v>
       </c>
-      <c r="L48" s="95" t="n">
+      <c r="M48" s="95" t="n">
         <v>3.46</v>
       </c>
-      <c r="M48" s="95" t="n">
+      <c r="N48" s="95" t="n">
         <v>2.34</v>
       </c>
-      <c r="N48" s="95" t="n">
+      <c r="O48" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="O48" s="95" t="n">
+      <c r="P48" s="95" t="n">
         <v>0.84</v>
       </c>
-      <c r="P48" s="95" t="n">
+      <c r="Q48" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q48" s="95" t="n">
+      <c r="R48" s="95" t="n">
         <v>1.41</v>
       </c>
-      <c r="R48" s="95" t="n">
+      <c r="S48" s="95" t="n">
         <v>0.68</v>
       </c>
-      <c r="S48" s="95" t="n">
+      <c r="T48" s="95" t="n">
         <v>0.48</v>
       </c>
-      <c r="T48" s="95" t="n">
+      <c r="U48" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="U48" s="95" t="n">
+      <c r="V48" s="95" t="n">
         <v>1.75</v>
       </c>
-      <c r="V48" s="95" t="n">
+      <c r="W48" s="95" t="n">
         <v>3.59</v>
       </c>
-      <c r="W48" s="95" t="n">
+      <c r="X48" s="95" t="n">
         <v>3.65</v>
       </c>
-      <c r="X48" s="95" t="n">
+      <c r="Y48" s="95" t="n">
         <v>4.49</v>
       </c>
-      <c r="Y48" s="95" t="n">
+      <c r="Z48" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="Z48" s="95" t="n">
+      <c r="AA48" s="95" t="n">
         <v>5.24</v>
       </c>
-      <c r="AA48" s="95" t="n">
+      <c r="AB48" s="95" t="n">
         <v>6.57</v>
       </c>
-      <c r="AB48" s="95" t="n">
+      <c r="AC48" s="95" t="n">
         <v>5.43</v>
       </c>
-      <c r="AC48" s="95" t="n">
+      <c r="AD48" s="95" t="n">
         <v>4.7</v>
       </c>
-      <c r="AD48" s="95" t="n">
+      <c r="AE48" s="95" t="n">
         <v>5.08</v>
-      </c>
-      <c r="AE48" s="95" t="n">
-        <v>5.28</v>
       </c>
     </row>
     <row r="49">
@@ -11780,104 +11780,104 @@
         <v>46.86</v>
       </c>
       <c r="C49" s="95" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="D49" s="95" t="n">
         <v>56.45</v>
       </c>
-      <c r="D49" s="95" t="n">
+      <c r="E49" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="E49" s="95" t="n">
+      <c r="F49" s="95" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="F49" s="95" t="n">
+      <c r="G49" s="95" t="n">
         <v>78.38</v>
       </c>
-      <c r="G49" s="95" t="n">
+      <c r="H49" s="95" t="n">
         <v>72.42</v>
       </c>
-      <c r="H49" s="95" t="n">
+      <c r="I49" s="95" t="n">
         <v>59.91</v>
       </c>
-      <c r="I49" s="95" t="n">
+      <c r="J49" s="95" t="n">
         <v>66</v>
       </c>
-      <c r="J49" s="95" t="n">
+      <c r="K49" s="95" t="n">
         <v>59.4</v>
       </c>
-      <c r="K49" s="95" t="n">
+      <c r="L49" s="95" t="n">
         <v>52.95</v>
       </c>
-      <c r="L49" s="95" t="n">
+      <c r="M49" s="95" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="M49" s="95" t="n">
+      <c r="N49" s="95" t="n">
         <v>61.14</v>
       </c>
-      <c r="N49" s="95" t="n">
+      <c r="O49" s="95" t="n">
         <v>62.6</v>
       </c>
-      <c r="O49" s="95" t="n">
+      <c r="P49" s="95" t="n">
         <v>57.16</v>
       </c>
-      <c r="P49" s="95" t="n">
+      <c r="Q49" s="95" t="n">
         <v>62.56</v>
       </c>
-      <c r="Q49" s="95" t="n">
+      <c r="R49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="R49" s="95" t="n">
+      <c r="S49" s="95" t="n">
         <v>37.42</v>
       </c>
-      <c r="S49" s="95" t="n">
+      <c r="T49" s="95" t="n">
         <v>31.32</v>
       </c>
-      <c r="T49" s="95" t="n">
+      <c r="U49" s="95" t="n">
         <v>40.38</v>
       </c>
-      <c r="U49" s="95" t="n">
+      <c r="V49" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="V49" s="95" t="n">
+      <c r="W49" s="95" t="n">
         <v>42.54</v>
       </c>
-      <c r="W49" s="95" t="n">
+      <c r="X49" s="95" t="n">
         <v>43.82</v>
       </c>
-      <c r="X49" s="95" t="n">
+      <c r="Y49" s="95" t="n">
         <v>58.62</v>
       </c>
-      <c r="Y49" s="95" t="n">
+      <c r="Z49" s="95" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="Z49" s="95" t="n">
+      <c r="AA49" s="95" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="AA49" s="95" t="n">
+      <c r="AB49" s="95" t="n">
         <v>88.2</v>
       </c>
-      <c r="AB49" s="95" t="n">
+      <c r="AC49" s="95" t="n">
         <v>84.89</v>
       </c>
-      <c r="AC49" s="95" t="n">
+      <c r="AD49" s="95" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="AD49" s="95" t="n">
+      <c r="AE49" s="95" t="n">
         <v>79.09</v>
-      </c>
-      <c r="AE49" s="95" t="n">
-        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:15.76&lt;=22;ixic:RS2:21.97&lt;=38;vn:RS3:23.23&lt;=25;sensex:RS10:38.91&lt;=39</t>
+          <t>今日买报：us500:RS2:15.76&lt;=22;ixic:RS2:20.54&lt;=38;vn:RS3:14.32&lt;=25;sensex:RS10:35.21&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="91" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RS3:99.75&gt;=66;kc:RNG60:26.36&gt;=25;kc:RS5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RS3:99.48&gt;=93;hk50:RNG60:26.19&gt;=15;hk50:RNG120:31.41&gt;=25;hk50:RS4:85.84&gt;=73</t>
+          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RS3:99.75&gt;=66;kc:RNG60:26.36&gt;=25;kc:RS5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RS3:99.48&gt;=93;hk50:RNG60:29.75&gt;=15;hk50:RNG120:32.66&gt;=25;hk50:RS4:89.49&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>1.17</v>
+        <v>2.98</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>1.17</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>11.25</v>
+        <v>13.62</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>11.25</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>15.76</v>
+        <v>81.84</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>15.76</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>5.77</v>
+        <v>6.54</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>5.77</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>10.61</v>
+        <v>12.24</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>10.61</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>28.19</v>
+        <v>68.36</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>28.19</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>-3.91</v>
+        <v>-0.8</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>-3.91</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>10.78</v>
+        <v>14.18</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>10.78</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>20.54</v>
+        <v>85.03</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>20.54</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>2.67</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>10.4</v>
+        <v>10.03</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>9.94</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>35.21</v>
+        <v>33.56</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>38.91</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.96</v>
+        <v>-2.37</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.96</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-6.31</v>
+        <v>-6.01</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-6.31</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>33.57</v>
+        <v>45.03</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>33.57</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.59</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>7.01</v>
+        <v>7.2</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>7.01</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>46.86</v>
+        <v>53.55</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>46.86</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:15.76&lt;=22;ixic:RS2:20.54&lt;=38;vn:RS3:14.32&lt;=25;sensex:RS10:35.21&lt;=39</t>
+          <t>今日买报：vn:RS3:14.32&lt;=25;sensex:RS10:33.56&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>241007</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>241004</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>241003</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>241002</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>241001</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>240930</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>240927</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>240926</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>240925</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>240924</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>240923</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>240920</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>240919</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>240918</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>240917</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>240916</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>240913</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>240912</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>240911</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>240910</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>240909</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>240906</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>240905</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>240904</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>240903</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>240902</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>240830</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>240829</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>240828</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>240827</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>240826</t>
         </is>
       </c>
     </row>
@@ -6542,109 +6542,109 @@
           <t>red</t>
         </is>
       </c>
-      <c r="K2" s="93" t="inlineStr">
+      <c r="K2" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="93" t="inlineStr">
+      <c r="M2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="93" t="inlineStr">
+      <c r="N2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="93" t="inlineStr">
+      <c r="O2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="94" t="inlineStr">
+      <c r="P2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="94" t="inlineStr">
+      <c r="Q2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="94" t="inlineStr">
+      <c r="R2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R2" s="94" t="inlineStr">
+      <c r="S2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="94" t="inlineStr">
+      <c r="T2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="94" t="inlineStr">
+      <c r="U2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="94" t="inlineStr">
+      <c r="V2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="94" t="inlineStr">
+      <c r="W2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="94" t="inlineStr">
+      <c r="X2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="94" t="inlineStr">
+      <c r="Y2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="94" t="inlineStr">
+      <c r="Z2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="94" t="inlineStr">
+      <c r="AA2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA2" s="93" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB2" s="94" t="inlineStr">
+      <c r="AC2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC2" s="94" t="inlineStr">
+      <c r="AD2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD2" s="94" t="inlineStr">
+      <c r="AE2" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -6670,31 +6670,31 @@
         <v>12.81</v>
       </c>
       <c r="G3" s="95" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="H3" s="95" t="n">
         <v>3.53</v>
       </c>
-      <c r="H3" s="95" t="n">
+      <c r="I3" s="95" t="n">
         <v>0.13</v>
       </c>
-      <c r="I3" s="95" t="n">
+      <c r="J3" s="95" t="n">
         <v>-3.29</v>
       </c>
-      <c r="J3" s="95" t="n">
+      <c r="K3" s="95" t="n">
         <v>-3.51</v>
       </c>
-      <c r="K3" s="95" t="n">
+      <c r="L3" s="95" t="n">
         <v>-6.68</v>
       </c>
-      <c r="L3" s="95" t="n">
+      <c r="M3" s="95" t="n">
         <v>-7.93</v>
       </c>
-      <c r="M3" s="95" t="n">
+      <c r="N3" s="95" t="n">
         <v>-7.25</v>
       </c>
-      <c r="N3" s="95" t="n">
+      <c r="O3" s="95" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="O3" s="95" t="n">
-        <v>-9.81</v>
       </c>
       <c r="P3" s="95" t="n">
         <v>-9.81</v>
@@ -6703,46 +6703,46 @@
         <v>-9.81</v>
       </c>
       <c r="R3" s="95" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="S3" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="S3" s="95" t="n">
+      <c r="T3" s="95" t="n">
         <v>-9.82</v>
       </c>
-      <c r="T3" s="95" t="n">
+      <c r="U3" s="95" t="n">
         <v>-9.44</v>
       </c>
-      <c r="U3" s="95" t="n">
+      <c r="V3" s="95" t="n">
         <v>-9.26</v>
       </c>
-      <c r="V3" s="95" t="n">
+      <c r="W3" s="95" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="W3" s="95" t="n">
+      <c r="X3" s="95" t="n">
         <v>-7.94</v>
       </c>
-      <c r="X3" s="95" t="n">
+      <c r="Y3" s="95" t="n">
         <v>-8.34</v>
       </c>
-      <c r="Y3" s="95" t="n">
+      <c r="Z3" s="95" t="n">
         <v>-7.43</v>
       </c>
-      <c r="Z3" s="95" t="n">
+      <c r="AA3" s="95" t="n">
         <v>-7.87</v>
       </c>
-      <c r="AA3" s="95" t="n">
+      <c r="AB3" s="95" t="n">
         <v>-6.78</v>
       </c>
-      <c r="AB3" s="95" t="n">
+      <c r="AC3" s="95" t="n">
         <v>-7.9</v>
       </c>
-      <c r="AC3" s="95" t="n">
+      <c r="AD3" s="95" t="n">
         <v>-8.210000000000001</v>
       </c>
-      <c r="AD3" s="95" t="n">
+      <c r="AE3" s="95" t="n">
         <v>-7.46</v>
-      </c>
-      <c r="AE3" s="95" t="n">
-        <v>-7.49</v>
       </c>
     </row>
     <row r="4">
@@ -6767,31 +6767,31 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G4" s="95" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H4" s="95" t="n">
         <v>0.41</v>
       </c>
-      <c r="H4" s="95" t="n">
+      <c r="I4" s="95" t="n">
         <v>-2.48</v>
       </c>
-      <c r="I4" s="95" t="n">
+      <c r="J4" s="95" t="n">
         <v>-4.76</v>
       </c>
-      <c r="J4" s="95" t="n">
+      <c r="K4" s="95" t="n">
         <v>-4.9</v>
       </c>
-      <c r="K4" s="95" t="n">
+      <c r="L4" s="95" t="n">
         <v>-8.16</v>
       </c>
-      <c r="L4" s="95" t="n">
+      <c r="M4" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="M4" s="95" t="n">
+      <c r="N4" s="95" t="n">
         <v>-9.59</v>
       </c>
-      <c r="N4" s="95" t="n">
+      <c r="O4" s="95" t="n">
         <v>-10.85</v>
-      </c>
-      <c r="O4" s="95" t="n">
-        <v>-12.12</v>
       </c>
       <c r="P4" s="95" t="n">
         <v>-12.12</v>
@@ -6800,46 +6800,46 @@
         <v>-12.12</v>
       </c>
       <c r="R4" s="95" t="n">
+        <v>-12.12</v>
+      </c>
+      <c r="S4" s="95" t="n">
         <v>-11.77</v>
       </c>
-      <c r="S4" s="95" t="n">
+      <c r="T4" s="95" t="n">
         <v>-11.13</v>
       </c>
-      <c r="T4" s="95" t="n">
+      <c r="U4" s="95" t="n">
         <v>-11.05</v>
       </c>
-      <c r="U4" s="95" t="n">
+      <c r="V4" s="95" t="n">
         <v>-10.42</v>
       </c>
-      <c r="V4" s="95" t="n">
+      <c r="W4" s="95" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="W4" s="95" t="n">
+      <c r="X4" s="95" t="n">
         <v>-8.390000000000001</v>
       </c>
-      <c r="X4" s="95" t="n">
+      <c r="Y4" s="95" t="n">
         <v>-8.890000000000001</v>
       </c>
-      <c r="Y4" s="95" t="n">
+      <c r="Z4" s="95" t="n">
         <v>-8.65</v>
       </c>
-      <c r="Z4" s="95" t="n">
+      <c r="AA4" s="95" t="n">
         <v>-7.71</v>
       </c>
-      <c r="AA4" s="95" t="n">
+      <c r="AB4" s="95" t="n">
         <v>-6.12</v>
       </c>
-      <c r="AB4" s="95" t="n">
+      <c r="AC4" s="95" t="n">
         <v>-7.13</v>
       </c>
-      <c r="AC4" s="95" t="n">
+      <c r="AD4" s="95" t="n">
         <v>-6.9</v>
       </c>
-      <c r="AD4" s="95" t="n">
+      <c r="AE4" s="95" t="n">
         <v>-6.27</v>
-      </c>
-      <c r="AE4" s="95" t="n">
-        <v>-5.67</v>
       </c>
     </row>
     <row r="5">
@@ -6864,31 +6864,31 @@
         <v>99.75</v>
       </c>
       <c r="G5" s="95" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="H5" s="95" t="n">
         <v>99.31</v>
       </c>
-      <c r="H5" s="95" t="n">
+      <c r="I5" s="95" t="n">
         <v>98.83</v>
       </c>
-      <c r="I5" s="95" t="n">
+      <c r="J5" s="95" t="n">
         <v>97.34999999999999</v>
       </c>
-      <c r="J5" s="95" t="n">
+      <c r="K5" s="95" t="n">
         <v>96.38</v>
       </c>
-      <c r="K5" s="95" t="n">
+      <c r="L5" s="95" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="L5" s="95" t="n">
+      <c r="M5" s="95" t="n">
         <v>64.38</v>
       </c>
-      <c r="M5" s="95" t="n">
+      <c r="N5" s="95" t="n">
         <v>63.45</v>
       </c>
-      <c r="N5" s="95" t="n">
+      <c r="O5" s="95" t="n">
         <v>37.85</v>
-      </c>
-      <c r="O5" s="95" t="n">
-        <v>7.42</v>
       </c>
       <c r="P5" s="95" t="n">
         <v>7.42</v>
@@ -6897,46 +6897,46 @@
         <v>7.42</v>
       </c>
       <c r="R5" s="95" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="S5" s="95" t="n">
         <v>10.95</v>
       </c>
-      <c r="S5" s="95" t="n">
+      <c r="T5" s="95" t="n">
         <v>12.36</v>
       </c>
-      <c r="T5" s="95" t="n">
+      <c r="U5" s="95" t="n">
         <v>20.95</v>
       </c>
-      <c r="U5" s="95" t="n">
+      <c r="V5" s="95" t="n">
         <v>5.95</v>
       </c>
-      <c r="V5" s="95" t="n">
+      <c r="W5" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="W5" s="95" t="n">
+      <c r="X5" s="95" t="n">
         <v>21.9</v>
       </c>
-      <c r="X5" s="95" t="n">
+      <c r="Y5" s="95" t="n">
         <v>12.41</v>
       </c>
-      <c r="Y5" s="95" t="n">
+      <c r="Z5" s="95" t="n">
         <v>19.88</v>
       </c>
-      <c r="Z5" s="95" t="n">
+      <c r="AA5" s="95" t="n">
         <v>24.04</v>
       </c>
-      <c r="AA5" s="95" t="n">
+      <c r="AB5" s="95" t="n">
         <v>52.18</v>
       </c>
-      <c r="AB5" s="95" t="n">
+      <c r="AC5" s="95" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="AC5" s="95" t="n">
+      <c r="AD5" s="95" t="n">
         <v>15.44</v>
       </c>
-      <c r="AD5" s="95" t="n">
+      <c r="AE5" s="95" t="n">
         <v>27.78</v>
-      </c>
-      <c r="AE5" s="95" t="n">
-        <v>40.86</v>
       </c>
     </row>
     <row r="6">
@@ -6990,99 +6990,99 @@
           <t>red</t>
         </is>
       </c>
-      <c r="K6" s="94" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="M6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="N6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N6" s="94" t="inlineStr">
+      <c r="O6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" s="93" t="inlineStr">
+      <c r="P6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="93" t="inlineStr">
+      <c r="Q6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="93" t="inlineStr">
+      <c r="R6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="93" t="inlineStr">
+      <c r="S6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="93" t="inlineStr">
+      <c r="T6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="93" t="inlineStr">
+      <c r="U6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="94" t="inlineStr">
+      <c r="V6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V6" s="94" t="inlineStr">
+      <c r="W6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="X6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="Y6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Z6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z6" s="94" t="inlineStr">
+      <c r="AA6" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA6" s="92" t="inlineStr">
+      <c r="AB6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB6" s="93" t="inlineStr">
+      <c r="AC6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AC6" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AD6" s="94" t="inlineStr">
@@ -7118,31 +7118,31 @@
         <v>26.36</v>
       </c>
       <c r="G7" s="95" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="H7" s="95" t="n">
         <v>5.45</v>
       </c>
-      <c r="H7" s="95" t="n">
+      <c r="I7" s="95" t="n">
         <v>-0.85</v>
       </c>
-      <c r="I7" s="95" t="n">
+      <c r="J7" s="95" t="n">
         <v>-5.96</v>
       </c>
-      <c r="J7" s="95" t="n">
+      <c r="K7" s="95" t="n">
         <v>-6.32</v>
       </c>
-      <c r="K7" s="95" t="n">
+      <c r="L7" s="95" t="n">
         <v>-10.11</v>
       </c>
-      <c r="L7" s="95" t="n">
+      <c r="M7" s="95" t="n">
         <v>-11.14</v>
       </c>
-      <c r="M7" s="95" t="n">
+      <c r="N7" s="95" t="n">
         <v>-9.23</v>
       </c>
-      <c r="N7" s="95" t="n">
+      <c r="O7" s="95" t="n">
         <v>-12.41</v>
-      </c>
-      <c r="O7" s="95" t="n">
-        <v>-13.62</v>
       </c>
       <c r="P7" s="95" t="n">
         <v>-13.62</v>
@@ -7151,46 +7151,46 @@
         <v>-13.62</v>
       </c>
       <c r="R7" s="95" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="S7" s="95" t="n">
         <v>-12.75</v>
       </c>
-      <c r="S7" s="95" t="n">
+      <c r="T7" s="95" t="n">
         <v>-11.62</v>
       </c>
-      <c r="T7" s="95" t="n">
+      <c r="U7" s="95" t="n">
         <v>-12.8</v>
       </c>
-      <c r="U7" s="95" t="n">
+      <c r="V7" s="95" t="n">
         <v>-13.49</v>
       </c>
-      <c r="V7" s="95" t="n">
+      <c r="W7" s="95" t="n">
         <v>-12.19</v>
       </c>
-      <c r="W7" s="95" t="n">
+      <c r="X7" s="95" t="n">
         <v>-11.56</v>
       </c>
-      <c r="X7" s="95" t="n">
+      <c r="Y7" s="95" t="n">
         <v>-10.95</v>
       </c>
-      <c r="Y7" s="95" t="n">
+      <c r="Z7" s="95" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Z7" s="95" t="n">
+      <c r="AA7" s="95" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="AA7" s="95" t="n">
+      <c r="AB7" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="AB7" s="95" t="n">
+      <c r="AC7" s="95" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="AC7" s="95" t="n">
+      <c r="AD7" s="95" t="n">
         <v>-10.94</v>
       </c>
-      <c r="AD7" s="95" t="n">
+      <c r="AE7" s="95" t="n">
         <v>-10.14</v>
-      </c>
-      <c r="AE7" s="95" t="n">
-        <v>-8.17</v>
       </c>
     </row>
     <row r="8">
@@ -7215,31 +7215,31 @@
         <v>15.28</v>
       </c>
       <c r="G8" s="95" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H8" s="95" t="n">
         <v>-3.74</v>
       </c>
-      <c r="H8" s="95" t="n">
+      <c r="I8" s="95" t="n">
         <v>-10.62</v>
       </c>
-      <c r="I8" s="95" t="n">
+      <c r="J8" s="95" t="n">
         <v>-12.51</v>
       </c>
-      <c r="J8" s="95" t="n">
+      <c r="K8" s="95" t="n">
         <v>-12.61</v>
       </c>
-      <c r="K8" s="95" t="n">
+      <c r="L8" s="95" t="n">
         <v>-14.58</v>
       </c>
-      <c r="L8" s="95" t="n">
+      <c r="M8" s="95" t="n">
         <v>-16.03</v>
       </c>
-      <c r="M8" s="95" t="n">
+      <c r="N8" s="95" t="n">
         <v>-16.65</v>
       </c>
-      <c r="N8" s="95" t="n">
+      <c r="O8" s="95" t="n">
         <v>-18.48</v>
-      </c>
-      <c r="O8" s="95" t="n">
-        <v>-18.74</v>
       </c>
       <c r="P8" s="95" t="n">
         <v>-18.74</v>
@@ -7248,46 +7248,46 @@
         <v>-18.74</v>
       </c>
       <c r="R8" s="95" t="n">
+        <v>-18.74</v>
+      </c>
+      <c r="S8" s="95" t="n">
         <v>-19.06</v>
       </c>
-      <c r="S8" s="95" t="n">
+      <c r="T8" s="95" t="n">
         <v>-18.16</v>
       </c>
-      <c r="T8" s="95" t="n">
+      <c r="U8" s="95" t="n">
         <v>-20.04</v>
       </c>
-      <c r="U8" s="95" t="n">
+      <c r="V8" s="95" t="n">
         <v>-19.01</v>
       </c>
-      <c r="V8" s="95" t="n">
+      <c r="W8" s="95" t="n">
         <v>-17.71</v>
       </c>
-      <c r="W8" s="95" t="n">
+      <c r="X8" s="95" t="n">
         <v>-17.63</v>
       </c>
-      <c r="X8" s="95" t="n">
+      <c r="Y8" s="95" t="n">
         <v>-17.79</v>
       </c>
-      <c r="Y8" s="95" t="n">
+      <c r="Z8" s="95" t="n">
         <v>-17.53</v>
       </c>
-      <c r="Z8" s="95" t="n">
+      <c r="AA8" s="95" t="n">
         <v>-16.58</v>
       </c>
-      <c r="AA8" s="95" t="n">
+      <c r="AB8" s="95" t="n">
         <v>-12.6</v>
       </c>
-      <c r="AB8" s="95" t="n">
+      <c r="AC8" s="95" t="n">
         <v>-16.3</v>
       </c>
-      <c r="AC8" s="95" t="n">
+      <c r="AD8" s="95" t="n">
         <v>-17.92</v>
       </c>
-      <c r="AD8" s="95" t="n">
+      <c r="AE8" s="95" t="n">
         <v>-17.61</v>
-      </c>
-      <c r="AE8" s="95" t="n">
-        <v>-16.31</v>
       </c>
     </row>
     <row r="9">
@@ -7312,31 +7312,31 @@
         <v>96.84</v>
       </c>
       <c r="G9" s="95" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="H9" s="95" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="H9" s="95" t="n">
+      <c r="I9" s="95" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="I9" s="95" t="n">
+      <c r="J9" s="95" t="n">
         <v>64.94</v>
       </c>
-      <c r="J9" s="95" t="n">
+      <c r="K9" s="95" t="n">
         <v>64.66</v>
       </c>
-      <c r="K9" s="95" t="n">
+      <c r="L9" s="95" t="n">
         <v>23.69</v>
       </c>
-      <c r="L9" s="95" t="n">
+      <c r="M9" s="95" t="n">
         <v>29.81</v>
       </c>
-      <c r="M9" s="95" t="n">
+      <c r="N9" s="95" t="n">
         <v>33.91</v>
       </c>
-      <c r="N9" s="95" t="n">
+      <c r="O9" s="95" t="n">
         <v>22.82</v>
-      </c>
-      <c r="O9" s="95" t="n">
-        <v>30.54</v>
       </c>
       <c r="P9" s="95" t="n">
         <v>30.54</v>
@@ -7345,46 +7345,46 @@
         <v>30.54</v>
       </c>
       <c r="R9" s="95" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="S9" s="95" t="n">
         <v>35.28</v>
       </c>
-      <c r="S9" s="95" t="n">
+      <c r="T9" s="95" t="n">
         <v>42.99</v>
       </c>
-      <c r="T9" s="95" t="n">
+      <c r="U9" s="95" t="n">
         <v>33.88</v>
       </c>
-      <c r="U9" s="95" t="n">
+      <c r="V9" s="95" t="n">
         <v>22.22</v>
       </c>
-      <c r="V9" s="95" t="n">
+      <c r="W9" s="95" t="n">
         <v>27.98</v>
       </c>
-      <c r="W9" s="95" t="n">
+      <c r="X9" s="95" t="n">
         <v>37.32</v>
       </c>
-      <c r="X9" s="95" t="n">
+      <c r="Y9" s="95" t="n">
         <v>38.49</v>
       </c>
-      <c r="Y9" s="95" t="n">
+      <c r="Z9" s="95" t="n">
         <v>41.22</v>
       </c>
-      <c r="Z9" s="95" t="n">
+      <c r="AA9" s="95" t="n">
         <v>34.35</v>
       </c>
-      <c r="AA9" s="95" t="n">
+      <c r="AB9" s="95" t="n">
         <v>63.18</v>
       </c>
-      <c r="AB9" s="95" t="n">
+      <c r="AC9" s="95" t="n">
         <v>38.1</v>
       </c>
-      <c r="AC9" s="95" t="n">
+      <c r="AD9" s="95" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AD9" s="95" t="n">
+      <c r="AE9" s="95" t="n">
         <v>11.44</v>
-      </c>
-      <c r="AE9" s="95" t="n">
-        <v>17.04</v>
       </c>
     </row>
     <row r="10">
@@ -7438,109 +7438,109 @@
           <t>red</t>
         </is>
       </c>
-      <c r="K10" s="94" t="inlineStr">
+      <c r="K10" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="L10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L10" s="94" t="inlineStr">
+      <c r="M10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M10" s="93" t="inlineStr">
+      <c r="N10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N10" s="94" t="inlineStr">
+      <c r="O10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O10" s="94" t="inlineStr">
+      <c r="P10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P10" s="94" t="inlineStr">
+      <c r="Q10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q10" s="94" t="inlineStr">
+      <c r="R10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R10" s="93" t="inlineStr">
+      <c r="S10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T10" s="94" t="inlineStr">
+      <c r="U10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U10" s="94" t="inlineStr">
+      <c r="V10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V10" s="94" t="inlineStr">
+      <c r="W10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W10" s="92" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z10" s="94" t="inlineStr">
+      <c r="AA10" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA10" s="92" t="inlineStr">
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB10" s="93" t="inlineStr">
+      <c r="AC10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC10" s="93" t="inlineStr">
+      <c r="AD10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD10" s="94" t="inlineStr">
+      <c r="AE10" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -7566,31 +7566,31 @@
         <v>32.05</v>
       </c>
       <c r="G11" s="95" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="H11" s="95" t="n">
         <v>13.58</v>
       </c>
-      <c r="H11" s="95" t="n">
+      <c r="I11" s="95" t="n">
         <v>2.95</v>
       </c>
-      <c r="I11" s="95" t="n">
+      <c r="J11" s="95" t="n">
         <v>-2.45</v>
       </c>
-      <c r="J11" s="95" t="n">
+      <c r="K11" s="95" t="n">
         <v>-4.05</v>
       </c>
-      <c r="K11" s="95" t="n">
+      <c r="L11" s="95" t="n">
         <v>-10.14</v>
       </c>
-      <c r="L11" s="95" t="n">
+      <c r="M11" s="95" t="n">
         <v>-11.21</v>
       </c>
-      <c r="M11" s="95" t="n">
+      <c r="N11" s="95" t="n">
         <v>-9.029999999999999</v>
       </c>
-      <c r="N11" s="95" t="n">
+      <c r="O11" s="95" t="n">
         <v>-11.44</v>
-      </c>
-      <c r="O11" s="95" t="n">
-        <v>-12.57</v>
       </c>
       <c r="P11" s="95" t="n">
         <v>-12.57</v>
@@ -7599,46 +7599,46 @@
         <v>-12.57</v>
       </c>
       <c r="R11" s="95" t="n">
+        <v>-12.57</v>
+      </c>
+      <c r="S11" s="95" t="n">
         <v>-11.96</v>
       </c>
-      <c r="S11" s="95" t="n">
+      <c r="T11" s="95" t="n">
         <v>-12.87</v>
       </c>
-      <c r="T11" s="95" t="n">
+      <c r="U11" s="95" t="n">
         <v>-14.98</v>
       </c>
-      <c r="U11" s="95" t="n">
+      <c r="V11" s="95" t="n">
         <v>-14.79</v>
       </c>
-      <c r="V11" s="95" t="n">
+      <c r="W11" s="95" t="n">
         <v>-14.14</v>
       </c>
-      <c r="W11" s="95" t="n">
+      <c r="X11" s="95" t="n">
         <v>-11.99</v>
       </c>
-      <c r="X11" s="95" t="n">
+      <c r="Y11" s="95" t="n">
         <v>-12.63</v>
       </c>
-      <c r="Y11" s="95" t="n">
+      <c r="Z11" s="95" t="n">
         <v>-12.92</v>
       </c>
-      <c r="Z11" s="95" t="n">
+      <c r="AA11" s="95" t="n">
         <v>-13.71</v>
       </c>
-      <c r="AA11" s="95" t="n">
+      <c r="AB11" s="95" t="n">
         <v>-13.18</v>
       </c>
-      <c r="AB11" s="95" t="n">
+      <c r="AC11" s="95" t="n">
         <v>-15.93</v>
       </c>
-      <c r="AC11" s="95" t="n">
+      <c r="AD11" s="95" t="n">
         <v>-16.93</v>
       </c>
-      <c r="AD11" s="95" t="n">
+      <c r="AE11" s="95" t="n">
         <v>-15.87</v>
-      </c>
-      <c r="AE11" s="95" t="n">
-        <v>-14.39</v>
       </c>
     </row>
     <row r="12">
@@ -7663,31 +7663,31 @@
         <v>18.19</v>
       </c>
       <c r="G12" s="95" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="H12" s="95" t="n">
         <v>1.34</v>
       </c>
-      <c r="H12" s="95" t="n">
+      <c r="I12" s="95" t="n">
         <v>-8.44</v>
       </c>
-      <c r="I12" s="95" t="n">
+      <c r="J12" s="95" t="n">
         <v>-9.720000000000001</v>
       </c>
-      <c r="J12" s="95" t="n">
+      <c r="K12" s="95" t="n">
         <v>-10.6</v>
       </c>
-      <c r="K12" s="95" t="n">
+      <c r="L12" s="95" t="n">
         <v>-14.49</v>
       </c>
-      <c r="L12" s="95" t="n">
+      <c r="M12" s="95" t="n">
         <v>-16.56</v>
       </c>
-      <c r="M12" s="95" t="n">
+      <c r="N12" s="95" t="n">
         <v>-15.65</v>
       </c>
-      <c r="N12" s="95" t="n">
+      <c r="O12" s="95" t="n">
         <v>-17.96</v>
-      </c>
-      <c r="O12" s="95" t="n">
-        <v>-19.08</v>
       </c>
       <c r="P12" s="95" t="n">
         <v>-19.08</v>
@@ -7696,46 +7696,46 @@
         <v>-19.08</v>
       </c>
       <c r="R12" s="95" t="n">
+        <v>-19.08</v>
+      </c>
+      <c r="S12" s="95" t="n">
         <v>-18.72</v>
       </c>
-      <c r="S12" s="95" t="n">
+      <c r="T12" s="95" t="n">
         <v>-18.28</v>
       </c>
-      <c r="T12" s="95" t="n">
+      <c r="U12" s="95" t="n">
         <v>-20.06</v>
       </c>
-      <c r="U12" s="95" t="n">
+      <c r="V12" s="95" t="n">
         <v>-18.31</v>
       </c>
-      <c r="V12" s="95" t="n">
+      <c r="W12" s="95" t="n">
         <v>-18.32</v>
       </c>
-      <c r="W12" s="95" t="n">
+      <c r="X12" s="95" t="n">
         <v>-17.44</v>
       </c>
-      <c r="X12" s="95" t="n">
+      <c r="Y12" s="95" t="n">
         <v>-18.44</v>
       </c>
-      <c r="Y12" s="95" t="n">
+      <c r="Z12" s="95" t="n">
         <v>-17.67</v>
       </c>
-      <c r="Z12" s="95" t="n">
+      <c r="AA12" s="95" t="n">
         <v>-14.96</v>
       </c>
-      <c r="AA12" s="95" t="n">
+      <c r="AB12" s="95" t="n">
         <v>-11.7</v>
       </c>
-      <c r="AB12" s="95" t="n">
+      <c r="AC12" s="95" t="n">
         <v>-15.89</v>
       </c>
-      <c r="AC12" s="95" t="n">
+      <c r="AD12" s="95" t="n">
         <v>-16.48</v>
       </c>
-      <c r="AD12" s="95" t="n">
+      <c r="AE12" s="95" t="n">
         <v>-16.57</v>
-      </c>
-      <c r="AE12" s="95" t="n">
-        <v>-15.28</v>
       </c>
     </row>
     <row r="13">
@@ -7760,31 +7760,31 @@
         <v>99.48</v>
       </c>
       <c r="G13" s="95" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="H13" s="95" t="n">
         <v>98.62</v>
       </c>
-      <c r="H13" s="95" t="n">
+      <c r="I13" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="I13" s="95" t="n">
+      <c r="J13" s="95" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="J13" s="95" t="n">
+      <c r="K13" s="95" t="n">
         <v>88.09</v>
       </c>
-      <c r="K13" s="95" t="n">
+      <c r="L13" s="95" t="n">
         <v>30.34</v>
       </c>
-      <c r="L13" s="95" t="n">
+      <c r="M13" s="95" t="n">
         <v>39.51</v>
       </c>
-      <c r="M13" s="95" t="n">
+      <c r="N13" s="95" t="n">
         <v>58.67</v>
       </c>
-      <c r="N13" s="95" t="n">
+      <c r="O13" s="95" t="n">
         <v>28.04</v>
-      </c>
-      <c r="O13" s="95" t="n">
-        <v>29.98</v>
       </c>
       <c r="P13" s="95" t="n">
         <v>29.98</v>
@@ -7793,46 +7793,46 @@
         <v>29.98</v>
       </c>
       <c r="R13" s="95" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="S13" s="95" t="n">
         <v>54.57</v>
       </c>
-      <c r="S13" s="95" t="n">
+      <c r="T13" s="95" t="n">
         <v>69.45</v>
       </c>
-      <c r="T13" s="95" t="n">
+      <c r="U13" s="95" t="n">
         <v>37.43</v>
       </c>
-      <c r="U13" s="95" t="n">
+      <c r="V13" s="95" t="n">
         <v>35.11</v>
       </c>
-      <c r="V13" s="95" t="n">
+      <c r="W13" s="95" t="n">
         <v>33.41</v>
       </c>
-      <c r="W13" s="95" t="n">
+      <c r="X13" s="95" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="X13" s="95" t="n">
+      <c r="Y13" s="95" t="n">
         <v>53.41</v>
       </c>
-      <c r="Y13" s="95" t="n">
+      <c r="Z13" s="95" t="n">
         <v>55.28</v>
       </c>
-      <c r="Z13" s="95" t="n">
+      <c r="AA13" s="95" t="n">
         <v>38.88</v>
       </c>
-      <c r="AA13" s="95" t="n">
+      <c r="AB13" s="95" t="n">
         <v>86.18000000000001</v>
       </c>
-      <c r="AB13" s="95" t="n">
+      <c r="AC13" s="95" t="n">
         <v>49.2</v>
       </c>
-      <c r="AC13" s="95" t="n">
+      <c r="AD13" s="95" t="n">
         <v>6.86</v>
       </c>
-      <c r="AD13" s="95" t="n">
+      <c r="AE13" s="95" t="n">
         <v>3.02</v>
-      </c>
-      <c r="AE13" s="95" t="n">
-        <v>6.93</v>
       </c>
     </row>
     <row r="14">
@@ -7916,74 +7916,74 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="Q14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R14" s="93" t="inlineStr">
+      <c r="S14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S14" s="94" t="inlineStr">
+      <c r="T14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T14" s="94" t="inlineStr">
+      <c r="U14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U14" s="94" t="inlineStr">
+      <c r="V14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V14" s="94" t="inlineStr">
+      <c r="W14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="94" t="inlineStr">
+      <c r="X14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X14" s="94" t="inlineStr">
+      <c r="Y14" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Z14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="AA14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA14" s="92" t="inlineStr">
+      <c r="AB14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="93" t="inlineStr">
+      <c r="AC14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC14" s="93" t="inlineStr">
+      <c r="AD14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD14" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AE14" s="92" t="inlineStr">
@@ -7999,94 +7999,94 @@
         </is>
       </c>
       <c r="B15" s="95" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="C15" s="95" t="n">
         <v>29.75</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="D15" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="D15" s="95" t="n">
+      <c r="E15" s="95" t="n">
         <v>26.09</v>
-      </c>
-      <c r="E15" s="95" t="n">
-        <v>17.23</v>
       </c>
       <c r="F15" s="95" t="n">
         <v>17.23</v>
       </c>
       <c r="G15" s="95" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="H15" s="95" t="n">
         <v>14.76</v>
       </c>
-      <c r="H15" s="95" t="n">
+      <c r="I15" s="95" t="n">
         <v>12.13</v>
       </c>
-      <c r="I15" s="95" t="n">
+      <c r="J15" s="95" t="n">
         <v>7.96</v>
       </c>
-      <c r="J15" s="95" t="n">
+      <c r="K15" s="95" t="n">
         <v>7.25</v>
       </c>
-      <c r="K15" s="95" t="n">
+      <c r="L15" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="L15" s="95" t="n">
+      <c r="M15" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="M15" s="95" t="n">
+      <c r="N15" s="95" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="N15" s="95" t="n">
-        <v>-2.04</v>
       </c>
       <c r="O15" s="95" t="n">
         <v>-2.04</v>
       </c>
       <c r="P15" s="95" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="Q15" s="95" t="n">
         <v>-4.98</v>
       </c>
-      <c r="Q15" s="95" t="n">
+      <c r="R15" s="95" t="n">
         <v>-5.76</v>
       </c>
-      <c r="R15" s="95" t="n">
+      <c r="S15" s="95" t="n">
         <v>-3.77</v>
       </c>
-      <c r="S15" s="95" t="n">
+      <c r="T15" s="95" t="n">
         <v>-4.61</v>
       </c>
-      <c r="T15" s="95" t="n">
+      <c r="U15" s="95" t="n">
         <v>-3.94</v>
       </c>
-      <c r="U15" s="95" t="n">
+      <c r="V15" s="95" t="n">
         <v>-5.06</v>
-      </c>
-      <c r="V15" s="95" t="n">
-        <v>-2.75</v>
       </c>
       <c r="W15" s="95" t="n">
         <v>-2.75</v>
       </c>
       <c r="X15" s="95" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="Y15" s="95" t="n">
         <v>-3.96</v>
       </c>
-      <c r="Y15" s="95" t="n">
+      <c r="Z15" s="95" t="n">
         <v>-3.9</v>
       </c>
-      <c r="Z15" s="95" t="n">
+      <c r="AA15" s="95" t="n">
         <v>-4.25</v>
       </c>
-      <c r="AA15" s="95" t="n">
+      <c r="AB15" s="95" t="n">
         <v>-2.37</v>
       </c>
-      <c r="AB15" s="95" t="n">
+      <c r="AC15" s="95" t="n">
         <v>-3.57</v>
       </c>
-      <c r="AC15" s="95" t="n">
+      <c r="AD15" s="95" t="n">
         <v>-3.86</v>
       </c>
-      <c r="AD15" s="95" t="n">
+      <c r="AE15" s="95" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="AE15" s="95" t="n">
-        <v>-2.37</v>
       </c>
     </row>
     <row r="16">
@@ -8096,94 +8096,94 @@
         </is>
       </c>
       <c r="B16" s="95" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="C16" s="95" t="n">
         <v>32.66</v>
       </c>
-      <c r="C16" s="95" t="n">
+      <c r="D16" s="95" t="n">
         <v>31.41</v>
       </c>
-      <c r="D16" s="95" t="n">
+      <c r="E16" s="95" t="n">
         <v>34.13</v>
-      </c>
-      <c r="E16" s="95" t="n">
-        <v>26.37</v>
       </c>
       <c r="F16" s="95" t="n">
         <v>26.37</v>
       </c>
       <c r="G16" s="95" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="H16" s="95" t="n">
         <v>23.36</v>
       </c>
-      <c r="H16" s="95" t="n">
+      <c r="I16" s="95" t="n">
         <v>17.68</v>
       </c>
-      <c r="I16" s="95" t="n">
+      <c r="J16" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="J16" s="95" t="n">
+      <c r="K16" s="95" t="n">
         <v>15.91</v>
       </c>
-      <c r="K16" s="95" t="n">
+      <c r="L16" s="95" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="L16" s="95" t="n">
+      <c r="M16" s="95" t="n">
         <v>10.84</v>
       </c>
-      <c r="M16" s="95" t="n">
+      <c r="N16" s="95" t="n">
         <v>9.17</v>
-      </c>
-      <c r="N16" s="95" t="n">
-        <v>4.73</v>
       </c>
       <c r="O16" s="95" t="n">
         <v>4.73</v>
       </c>
       <c r="P16" s="95" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="Q16" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="Q16" s="95" t="n">
+      <c r="R16" s="95" t="n">
         <v>5.08</v>
       </c>
-      <c r="R16" s="95" t="n">
+      <c r="S16" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="S16" s="95" t="n">
+      <c r="T16" s="95" t="n">
         <v>2.32</v>
       </c>
-      <c r="T16" s="95" t="n">
+      <c r="U16" s="95" t="n">
         <v>1.61</v>
       </c>
-      <c r="U16" s="95" t="n">
+      <c r="V16" s="95" t="n">
         <v>0.67</v>
-      </c>
-      <c r="V16" s="95" t="n">
-        <v>2.05</v>
       </c>
       <c r="W16" s="95" t="n">
         <v>2.05</v>
       </c>
       <c r="X16" s="95" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y16" s="95" t="n">
         <v>5.24</v>
       </c>
-      <c r="Y16" s="95" t="n">
+      <c r="Z16" s="95" t="n">
         <v>7.94</v>
       </c>
-      <c r="Z16" s="95" t="n">
+      <c r="AA16" s="95" t="n">
         <v>9.01</v>
       </c>
-      <c r="AA16" s="95" t="n">
+      <c r="AB16" s="95" t="n">
         <v>9.44</v>
       </c>
-      <c r="AB16" s="95" t="n">
+      <c r="AC16" s="95" t="n">
         <v>10.05</v>
       </c>
-      <c r="AC16" s="95" t="n">
+      <c r="AD16" s="95" t="n">
         <v>6.61</v>
       </c>
-      <c r="AD16" s="95" t="n">
+      <c r="AE16" s="95" t="n">
         <v>7.75</v>
-      </c>
-      <c r="AE16" s="95" t="n">
-        <v>7.8</v>
       </c>
     </row>
     <row r="17">
@@ -8193,94 +8193,94 @@
         </is>
       </c>
       <c r="B17" s="95" t="n">
+        <v>91.23999999999999</v>
+      </c>
+      <c r="C17" s="95" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="C17" s="95" t="n">
+      <c r="D17" s="95" t="n">
         <v>85.84</v>
       </c>
-      <c r="D17" s="95" t="n">
+      <c r="E17" s="95" t="n">
         <v>99.56999999999999</v>
-      </c>
-      <c r="E17" s="95" t="n">
-        <v>99.18000000000001</v>
       </c>
       <c r="F17" s="95" t="n">
         <v>99.18000000000001</v>
       </c>
       <c r="G17" s="95" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H17" s="95" t="n">
         <v>98.89</v>
       </c>
-      <c r="H17" s="95" t="n">
+      <c r="I17" s="95" t="n">
         <v>98.23</v>
       </c>
-      <c r="I17" s="95" t="n">
+      <c r="J17" s="95" t="n">
         <v>96.44</v>
       </c>
-      <c r="J17" s="95" t="n">
+      <c r="K17" s="95" t="n">
         <v>95.94</v>
       </c>
-      <c r="K17" s="95" t="n">
+      <c r="L17" s="95" t="n">
         <v>89.48</v>
       </c>
-      <c r="L17" s="95" t="n">
+      <c r="M17" s="95" t="n">
         <v>91.13</v>
       </c>
-      <c r="M17" s="95" t="n">
+      <c r="N17" s="95" t="n">
         <v>87.39</v>
-      </c>
-      <c r="N17" s="95" t="n">
-        <v>76.86</v>
       </c>
       <c r="O17" s="95" t="n">
         <v>76.86</v>
       </c>
       <c r="P17" s="95" t="n">
+        <v>76.86</v>
+      </c>
+      <c r="Q17" s="95" t="n">
         <v>59.96</v>
       </c>
-      <c r="Q17" s="95" t="n">
+      <c r="R17" s="95" t="n">
         <v>54.39</v>
       </c>
-      <c r="R17" s="95" t="n">
+      <c r="S17" s="95" t="n">
         <v>38.93</v>
       </c>
-      <c r="S17" s="95" t="n">
+      <c r="T17" s="95" t="n">
         <v>17.46</v>
       </c>
-      <c r="T17" s="95" t="n">
+      <c r="U17" s="95" t="n">
         <v>23.32</v>
       </c>
-      <c r="U17" s="95" t="n">
+      <c r="V17" s="95" t="n">
         <v>17.15</v>
-      </c>
-      <c r="V17" s="95" t="n">
-        <v>28.67</v>
       </c>
       <c r="W17" s="95" t="n">
         <v>28.67</v>
       </c>
       <c r="X17" s="95" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="Y17" s="95" t="n">
         <v>29.45</v>
       </c>
-      <c r="Y17" s="95" t="n">
+      <c r="Z17" s="95" t="n">
         <v>42.37</v>
       </c>
-      <c r="Z17" s="95" t="n">
+      <c r="AA17" s="95" t="n">
         <v>45.49</v>
       </c>
-      <c r="AA17" s="95" t="n">
+      <c r="AB17" s="95" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="AB17" s="95" t="n">
+      <c r="AC17" s="95" t="n">
         <v>63.9</v>
       </c>
-      <c r="AC17" s="95" t="n">
+      <c r="AD17" s="95" t="n">
         <v>55.65</v>
       </c>
-      <c r="AD17" s="95" t="n">
+      <c r="AE17" s="95" t="n">
         <v>83.40000000000001</v>
-      </c>
-      <c r="AE17" s="95" t="n">
-        <v>80.33</v>
       </c>
     </row>
     <row r="18">
@@ -8294,124 +8294,124 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C18" s="93" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D18" s="93" t="inlineStr">
+      <c r="E18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E18" s="93" t="inlineStr">
+      <c r="F18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F18" s="93" t="inlineStr">
+      <c r="G18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G18" s="93" t="inlineStr">
+      <c r="H18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H18" s="93" t="inlineStr">
+      <c r="I18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I18" s="93" t="inlineStr">
+      <c r="J18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J18" s="92" t="inlineStr">
+      <c r="K18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
+      <c r="L18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L18" s="92" t="inlineStr">
+      <c r="M18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M18" s="92" t="inlineStr">
+      <c r="N18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="93" t="inlineStr">
+      <c r="O18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O18" s="92" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P18" s="92" t="inlineStr">
+      <c r="Q18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="92" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R18" s="92" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T18" s="93" t="inlineStr">
+      <c r="U18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U18" s="94" t="inlineStr">
+      <c r="V18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V18" s="94" t="inlineStr">
+      <c r="W18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W18" s="94" t="inlineStr">
+      <c r="X18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X18" s="94" t="inlineStr">
+      <c r="Y18" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y18" s="94" t="inlineStr">
+      <c r="Z18" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA18" s="93" t="inlineStr">
@@ -8450,91 +8450,91 @@
         <v>2.98</v>
       </c>
       <c r="C19" s="95" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D19" s="95" t="n">
         <v>1.17</v>
       </c>
-      <c r="D19" s="95" t="n">
+      <c r="E19" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="E19" s="95" t="n">
+      <c r="F19" s="95" t="n">
         <v>2.44</v>
       </c>
-      <c r="F19" s="95" t="n">
+      <c r="G19" s="95" t="n">
         <v>3.51</v>
       </c>
-      <c r="G19" s="95" t="n">
+      <c r="H19" s="95" t="n">
         <v>3.63</v>
       </c>
-      <c r="H19" s="95" t="n">
+      <c r="I19" s="95" t="n">
         <v>4.29</v>
       </c>
-      <c r="I19" s="95" t="n">
+      <c r="J19" s="95" t="n">
         <v>4.51</v>
       </c>
-      <c r="J19" s="95" t="n">
+      <c r="K19" s="95" t="n">
         <v>4.99</v>
       </c>
-      <c r="K19" s="95" t="n">
+      <c r="L19" s="95" t="n">
         <v>4.3</v>
       </c>
-      <c r="L19" s="95" t="n">
+      <c r="M19" s="95" t="n">
         <v>4.1</v>
       </c>
-      <c r="M19" s="95" t="n">
+      <c r="N19" s="95" t="n">
         <v>4.47</v>
       </c>
-      <c r="N19" s="95" t="n">
+      <c r="O19" s="95" t="n">
         <v>3.13</v>
       </c>
-      <c r="O19" s="95" t="n">
+      <c r="P19" s="95" t="n">
         <v>3.11</v>
       </c>
-      <c r="P19" s="95" t="n">
+      <c r="Q19" s="95" t="n">
         <v>2.92</v>
       </c>
-      <c r="Q19" s="95" t="n">
+      <c r="R19" s="95" t="n">
         <v>2.53</v>
       </c>
-      <c r="R19" s="95" t="n">
+      <c r="S19" s="95" t="n">
         <v>2.24</v>
       </c>
-      <c r="S19" s="95" t="n">
+      <c r="T19" s="95" t="n">
         <v>2.26</v>
       </c>
-      <c r="T19" s="95" t="n">
+      <c r="U19" s="95" t="n">
         <v>1.14</v>
       </c>
-      <c r="U19" s="95" t="n">
+      <c r="V19" s="95" t="n">
         <v>0.92</v>
       </c>
-      <c r="V19" s="95" t="n">
+      <c r="W19" s="95" t="n">
         <v>0.62</v>
       </c>
-      <c r="W19" s="95" t="n">
+      <c r="X19" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="X19" s="95" t="n">
+      <c r="Y19" s="95" t="n">
         <v>3.24</v>
       </c>
-      <c r="Y19" s="95" t="n">
+      <c r="Z19" s="95" t="n">
         <v>3.29</v>
-      </c>
-      <c r="Z19" s="95" t="n">
-        <v>5.5</v>
       </c>
       <c r="AA19" s="95" t="n">
         <v>5.5</v>
       </c>
       <c r="AB19" s="95" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC19" s="95" t="n">
         <v>5.68</v>
       </c>
-      <c r="AC19" s="95" t="n">
+      <c r="AD19" s="95" t="n">
         <v>5.84</v>
       </c>
-      <c r="AD19" s="95" t="n">
+      <c r="AE19" s="95" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AE19" s="95" t="n">
-        <v>7.28</v>
       </c>
     </row>
     <row r="20">
@@ -8547,91 +8547,91 @@
         <v>13.62</v>
       </c>
       <c r="C20" s="95" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="D20" s="95" t="n">
         <v>11.25</v>
       </c>
-      <c r="D20" s="95" t="n">
+      <c r="E20" s="95" t="n">
         <v>9.82</v>
       </c>
-      <c r="E20" s="95" t="n">
+      <c r="F20" s="95" t="n">
         <v>10.62</v>
       </c>
-      <c r="F20" s="95" t="n">
+      <c r="G20" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="G20" s="95" t="n">
+      <c r="H20" s="95" t="n">
         <v>10.3</v>
       </c>
-      <c r="H20" s="95" t="n">
+      <c r="I20" s="95" t="n">
         <v>10.4</v>
       </c>
-      <c r="I20" s="95" t="n">
+      <c r="J20" s="95" t="n">
         <v>11.17</v>
       </c>
-      <c r="J20" s="95" t="n">
+      <c r="K20" s="95" t="n">
         <v>10.01</v>
       </c>
-      <c r="K20" s="95" t="n">
+      <c r="L20" s="95" t="n">
         <v>9.85</v>
       </c>
-      <c r="L20" s="95" t="n">
+      <c r="M20" s="95" t="n">
         <v>8.75</v>
       </c>
-      <c r="M20" s="95" t="n">
+      <c r="N20" s="95" t="n">
         <v>8.74</v>
       </c>
-      <c r="N20" s="95" t="n">
+      <c r="O20" s="95" t="n">
         <v>7.05</v>
       </c>
-      <c r="O20" s="95" t="n">
+      <c r="P20" s="95" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="P20" s="95" t="n">
+      <c r="Q20" s="95" t="n">
         <v>7.95</v>
       </c>
-      <c r="Q20" s="95" t="n">
+      <c r="R20" s="95" t="n">
         <v>7.49</v>
       </c>
-      <c r="R20" s="95" t="n">
+      <c r="S20" s="95" t="n">
         <v>6.76</v>
       </c>
-      <c r="S20" s="95" t="n">
+      <c r="T20" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="T20" s="95" t="n">
+      <c r="U20" s="95" t="n">
         <v>6.12</v>
       </c>
-      <c r="U20" s="95" t="n">
+      <c r="V20" s="95" t="n">
         <v>6.25</v>
       </c>
-      <c r="V20" s="95" t="n">
+      <c r="W20" s="95" t="n">
         <v>5.69</v>
       </c>
-      <c r="W20" s="95" t="n">
+      <c r="X20" s="95" t="n">
         <v>6.85</v>
       </c>
-      <c r="X20" s="95" t="n">
+      <c r="Y20" s="95" t="n">
         <v>6.87</v>
       </c>
-      <c r="Y20" s="95" t="n">
+      <c r="Z20" s="95" t="n">
         <v>6.83</v>
-      </c>
-      <c r="Z20" s="95" t="n">
-        <v>10.36</v>
       </c>
       <c r="AA20" s="95" t="n">
         <v>10.36</v>
       </c>
       <c r="AB20" s="95" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AC20" s="95" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="AC20" s="95" t="n">
+      <c r="AD20" s="95" t="n">
         <v>8.43</v>
       </c>
-      <c r="AD20" s="95" t="n">
+      <c r="AE20" s="95" t="n">
         <v>10.21</v>
-      </c>
-      <c r="AE20" s="95" t="n">
-        <v>10.6</v>
       </c>
     </row>
     <row r="21">
@@ -8644,91 +8644,91 @@
         <v>81.84</v>
       </c>
       <c r="C21" s="95" t="n">
+        <v>81.84</v>
+      </c>
+      <c r="D21" s="95" t="n">
         <v>15.76</v>
       </c>
-      <c r="D21" s="95" t="n">
+      <c r="E21" s="95" t="n">
         <v>23.93</v>
       </c>
-      <c r="E21" s="95" t="n">
+      <c r="F21" s="95" t="n">
         <v>22.27</v>
       </c>
-      <c r="F21" s="95" t="n">
+      <c r="G21" s="95" t="n">
         <v>86.19</v>
       </c>
-      <c r="G21" s="95" t="n">
+      <c r="H21" s="95" t="n">
         <v>60.63</v>
       </c>
-      <c r="H21" s="95" t="n">
+      <c r="I21" s="95" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="I21" s="95" t="n">
+      <c r="J21" s="95" t="n">
         <v>58.19</v>
       </c>
-      <c r="J21" s="95" t="n">
+      <c r="K21" s="95" t="n">
         <v>90.16</v>
       </c>
-      <c r="K21" s="95" t="n">
+      <c r="L21" s="95" t="n">
         <v>84.39</v>
       </c>
-      <c r="L21" s="95" t="n">
+      <c r="M21" s="95" t="n">
         <v>76.79000000000001</v>
       </c>
-      <c r="M21" s="95" t="n">
+      <c r="N21" s="95" t="n">
         <v>92.34</v>
       </c>
-      <c r="N21" s="95" t="n">
+      <c r="O21" s="95" t="n">
         <v>40.89</v>
       </c>
-      <c r="O21" s="95" t="n">
+      <c r="P21" s="95" t="n">
         <v>96.09</v>
       </c>
-      <c r="P21" s="95" t="n">
+      <c r="Q21" s="95" t="n">
         <v>95.83</v>
       </c>
-      <c r="Q21" s="95" t="n">
+      <c r="R21" s="95" t="n">
         <v>95.06</v>
       </c>
-      <c r="R21" s="95" t="n">
+      <c r="S21" s="95" t="n">
         <v>91.83</v>
       </c>
-      <c r="S21" s="95" t="n">
+      <c r="T21" s="95" t="n">
         <v>85.17</v>
       </c>
-      <c r="T21" s="95" t="n">
+      <c r="U21" s="95" t="n">
         <v>65.2</v>
       </c>
-      <c r="U21" s="95" t="n">
+      <c r="V21" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="V21" s="95" t="n">
+      <c r="W21" s="95" t="n">
         <v>3</v>
       </c>
-      <c r="W21" s="95" t="n">
+      <c r="X21" s="95" t="n">
         <v>12.54</v>
       </c>
-      <c r="X21" s="95" t="n">
+      <c r="Y21" s="95" t="n">
         <v>17.38</v>
       </c>
-      <c r="Y21" s="95" t="n">
+      <c r="Z21" s="95" t="n">
         <v>19.37</v>
-      </c>
-      <c r="Z21" s="95" t="n">
-        <v>85.14</v>
       </c>
       <c r="AA21" s="95" t="n">
         <v>85.14</v>
       </c>
       <c r="AB21" s="95" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="AC21" s="95" t="n">
         <v>24.99</v>
       </c>
-      <c r="AC21" s="95" t="n">
+      <c r="AD21" s="95" t="n">
         <v>25.19</v>
       </c>
-      <c r="AD21" s="95" t="n">
+      <c r="AE21" s="95" t="n">
         <v>64.23</v>
-      </c>
-      <c r="AE21" s="95" t="n">
-        <v>54.92</v>
       </c>
     </row>
     <row r="22">
@@ -8742,149 +8742,149 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C22" s="93" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D22" s="93" t="inlineStr">
+      <c r="E22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E22" s="93" t="inlineStr">
+      <c r="F22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F22" s="93" t="inlineStr">
+      <c r="G22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G22" s="93" t="inlineStr">
+      <c r="H22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="93" t="inlineStr">
+      <c r="I22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="93" t="inlineStr">
+      <c r="J22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="92" t="inlineStr">
+      <c r="K22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="L22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
+      <c r="M22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="92" t="inlineStr">
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="92" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="92" t="inlineStr">
+      <c r="P22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="92" t="inlineStr">
+      <c r="Q22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="92" t="inlineStr">
+      <c r="R22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R22" s="92" t="inlineStr">
+      <c r="S22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S22" s="92" t="inlineStr">
+      <c r="T22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T22" s="94" t="inlineStr">
+      <c r="U22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="93" t="inlineStr">
+      <c r="V22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="94" t="inlineStr">
+      <c r="W22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="94" t="inlineStr">
+      <c r="X22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X22" s="93" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="93" t="inlineStr">
+      <c r="Z22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="92" t="inlineStr">
+      <c r="AA22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA22" s="92" t="inlineStr">
+      <c r="AB22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB22" s="93" t="inlineStr">
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="93" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="93" t="inlineStr">
+      <c r="AE22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8898,91 +8898,91 @@
         <v>6.54</v>
       </c>
       <c r="C23" s="95" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D23" s="95" t="n">
         <v>5.77</v>
       </c>
-      <c r="D23" s="95" t="n">
+      <c r="E23" s="95" t="n">
         <v>7.39</v>
       </c>
-      <c r="E23" s="95" t="n">
+      <c r="F23" s="95" t="n">
         <v>7.15</v>
       </c>
-      <c r="F23" s="95" t="n">
+      <c r="G23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="G23" s="95" t="n">
+      <c r="H23" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="H23" s="95" t="n">
+      <c r="I23" s="95" t="n">
         <v>7.23</v>
       </c>
-      <c r="I23" s="95" t="n">
+      <c r="J23" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="J23" s="95" t="n">
+      <c r="K23" s="95" t="n">
         <v>7.9</v>
       </c>
-      <c r="K23" s="95" t="n">
+      <c r="L23" s="95" t="n">
         <v>7.56</v>
       </c>
-      <c r="L23" s="95" t="n">
+      <c r="M23" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="M23" s="95" t="n">
+      <c r="N23" s="95" t="n">
         <v>7.45</v>
       </c>
-      <c r="N23" s="95" t="n">
+      <c r="O23" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="O23" s="95" t="n">
+      <c r="P23" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="P23" s="95" t="n">
+      <c r="Q23" s="95" t="n">
         <v>6.36</v>
       </c>
-      <c r="Q23" s="95" t="n">
+      <c r="R23" s="95" t="n">
         <v>6.59</v>
       </c>
-      <c r="R23" s="95" t="n">
+      <c r="S23" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="S23" s="95" t="n">
+      <c r="T23" s="95" t="n">
         <v>5.89</v>
       </c>
-      <c r="T23" s="95" t="n">
+      <c r="U23" s="95" t="n">
         <v>5.41</v>
       </c>
-      <c r="U23" s="95" t="n">
+      <c r="V23" s="95" t="n">
         <v>5.47</v>
       </c>
-      <c r="V23" s="95" t="n">
+      <c r="W23" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="W23" s="95" t="n">
+      <c r="X23" s="95" t="n">
         <v>4.86</v>
       </c>
-      <c r="X23" s="95" t="n">
+      <c r="Y23" s="95" t="n">
         <v>5.61</v>
       </c>
-      <c r="Y23" s="95" t="n">
+      <c r="Z23" s="95" t="n">
         <v>5.27</v>
-      </c>
-      <c r="Z23" s="95" t="n">
-        <v>7.1</v>
       </c>
       <c r="AA23" s="95" t="n">
         <v>7.1</v>
       </c>
       <c r="AB23" s="95" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AC23" s="95" t="n">
         <v>6.78</v>
       </c>
-      <c r="AC23" s="95" t="n">
+      <c r="AD23" s="95" t="n">
         <v>6.53</v>
       </c>
-      <c r="AD23" s="95" t="n">
+      <c r="AE23" s="95" t="n">
         <v>6.63</v>
-      </c>
-      <c r="AE23" s="95" t="n">
-        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -8995,91 +8995,91 @@
         <v>12.24</v>
       </c>
       <c r="C24" s="95" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="D24" s="95" t="n">
         <v>10.61</v>
       </c>
-      <c r="D24" s="95" t="n">
+      <c r="E24" s="95" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="E24" s="95" t="n">
+      <c r="F24" s="95" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="F24" s="95" t="n">
+      <c r="G24" s="95" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="G24" s="95" t="n">
+      <c r="H24" s="95" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="H24" s="95" t="n">
+      <c r="I24" s="95" t="n">
         <v>8.41</v>
       </c>
-      <c r="I24" s="95" t="n">
+      <c r="J24" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="J24" s="95" t="n">
+      <c r="K24" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="K24" s="95" t="n">
+      <c r="L24" s="95" t="n">
         <v>7.54</v>
       </c>
-      <c r="L24" s="95" t="n">
+      <c r="M24" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="M24" s="95" t="n">
+      <c r="N24" s="95" t="n">
         <v>5.57</v>
       </c>
-      <c r="N24" s="95" t="n">
+      <c r="O24" s="95" t="n">
         <v>4.38</v>
       </c>
-      <c r="O24" s="95" t="n">
+      <c r="P24" s="95" t="n">
         <v>5.92</v>
       </c>
-      <c r="P24" s="95" t="n">
+      <c r="Q24" s="95" t="n">
         <v>5.87</v>
       </c>
-      <c r="Q24" s="95" t="n">
+      <c r="R24" s="95" t="n">
         <v>4.86</v>
       </c>
-      <c r="R24" s="95" t="n">
+      <c r="S24" s="95" t="n">
         <v>3.31</v>
       </c>
-      <c r="S24" s="95" t="n">
+      <c r="T24" s="95" t="n">
         <v>3.42</v>
       </c>
-      <c r="T24" s="95" t="n">
+      <c r="U24" s="95" t="n">
         <v>4.16</v>
       </c>
-      <c r="U24" s="95" t="n">
+      <c r="V24" s="95" t="n">
         <v>5.26</v>
       </c>
-      <c r="V24" s="95" t="n">
+      <c r="W24" s="95" t="n">
         <v>4.21</v>
       </c>
-      <c r="W24" s="95" t="n">
+      <c r="X24" s="95" t="n">
         <v>4.76</v>
-      </c>
-      <c r="X24" s="95" t="n">
-        <v>4.95</v>
       </c>
       <c r="Y24" s="95" t="n">
         <v>4.95</v>
       </c>
       <c r="Z24" s="95" t="n">
-        <v>7.21</v>
+        <v>4.95</v>
       </c>
       <c r="AA24" s="95" t="n">
         <v>7.21</v>
       </c>
       <c r="AB24" s="95" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AC24" s="95" t="n">
         <v>6.75</v>
       </c>
-      <c r="AC24" s="95" t="n">
+      <c r="AD24" s="95" t="n">
         <v>5.93</v>
       </c>
-      <c r="AD24" s="95" t="n">
+      <c r="AE24" s="95" t="n">
         <v>6.7</v>
-      </c>
-      <c r="AE24" s="95" t="n">
-        <v>6.88</v>
       </c>
     </row>
     <row r="25">
@@ -9092,91 +9092,91 @@
         <v>68.36</v>
       </c>
       <c r="C25" s="95" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="D25" s="95" t="n">
         <v>28.19</v>
       </c>
-      <c r="D25" s="95" t="n">
+      <c r="E25" s="95" t="n">
         <v>52.09</v>
       </c>
-      <c r="E25" s="95" t="n">
+      <c r="F25" s="95" t="n">
         <v>45.5</v>
       </c>
-      <c r="F25" s="95" t="n">
+      <c r="G25" s="95" t="n">
         <v>76.02</v>
       </c>
-      <c r="G25" s="95" t="n">
+      <c r="H25" s="95" t="n">
         <v>74.91</v>
       </c>
-      <c r="H25" s="95" t="n">
+      <c r="I25" s="95" t="n">
         <v>66.62</v>
       </c>
-      <c r="I25" s="95" t="n">
+      <c r="J25" s="95" t="n">
         <v>42.84</v>
       </c>
-      <c r="J25" s="95" t="n">
+      <c r="K25" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="K25" s="95" t="n">
+      <c r="L25" s="95" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="L25" s="95" t="n">
+      <c r="M25" s="95" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="M25" s="95" t="n">
+      <c r="N25" s="95" t="n">
         <v>87.58</v>
       </c>
-      <c r="N25" s="95" t="n">
+      <c r="O25" s="95" t="n">
         <v>65.31</v>
       </c>
-      <c r="O25" s="95" t="n">
+      <c r="P25" s="95" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="P25" s="95" t="n">
+      <c r="Q25" s="95" t="n">
         <v>88.3</v>
       </c>
-      <c r="Q25" s="95" t="n">
+      <c r="R25" s="95" t="n">
         <v>82.94</v>
       </c>
-      <c r="R25" s="95" t="n">
+      <c r="S25" s="95" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="S25" s="95" t="n">
+      <c r="T25" s="95" t="n">
         <v>56.57</v>
       </c>
-      <c r="T25" s="95" t="n">
+      <c r="U25" s="95" t="n">
         <v>46.45</v>
       </c>
-      <c r="U25" s="95" t="n">
+      <c r="V25" s="95" t="n">
         <v>52.5</v>
       </c>
-      <c r="V25" s="95" t="n">
+      <c r="W25" s="95" t="n">
         <v>13.02</v>
       </c>
-      <c r="W25" s="95" t="n">
+      <c r="X25" s="95" t="n">
         <v>24.55</v>
       </c>
-      <c r="X25" s="95" t="n">
+      <c r="Y25" s="95" t="n">
         <v>35.87</v>
       </c>
-      <c r="Y25" s="95" t="n">
+      <c r="Z25" s="95" t="n">
         <v>32.25</v>
-      </c>
-      <c r="Z25" s="95" t="n">
-        <v>84.45999999999999</v>
       </c>
       <c r="AA25" s="95" t="n">
         <v>84.45999999999999</v>
       </c>
       <c r="AB25" s="95" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="AC25" s="95" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="AC25" s="95" t="n">
+      <c r="AD25" s="95" t="n">
         <v>52.49</v>
       </c>
-      <c r="AD25" s="95" t="n">
+      <c r="AE25" s="95" t="n">
         <v>83.64</v>
-      </c>
-      <c r="AE25" s="95" t="n">
-        <v>83.23</v>
       </c>
     </row>
     <row r="26">
@@ -9190,144 +9190,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D26" s="93" t="inlineStr">
+      <c r="E26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E26" s="93" t="inlineStr">
+      <c r="F26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F26" s="93" t="inlineStr">
+      <c r="G26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G26" s="93" t="inlineStr">
+      <c r="H26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="93" t="inlineStr">
+      <c r="J26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J26" s="92" t="inlineStr">
+      <c r="K26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K26" s="92" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="92" t="inlineStr">
+      <c r="M26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="92" t="inlineStr">
+      <c r="N26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="93" t="inlineStr">
+      <c r="O26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O26" s="92" t="inlineStr">
+      <c r="P26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P26" s="92" t="inlineStr">
+      <c r="Q26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q26" s="92" t="inlineStr">
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R26" s="92" t="inlineStr">
+      <c r="S26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S26" s="92" t="inlineStr">
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="U26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U26" s="94" t="inlineStr">
+      <c r="V26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V26" s="94" t="inlineStr">
+      <c r="W26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W26" s="94" t="inlineStr">
+      <c r="X26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X26" s="94" t="inlineStr">
+      <c r="Y26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="94" t="inlineStr">
+      <c r="Z26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="AA26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA26" s="93" t="inlineStr">
+      <c r="AB26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB26" s="94" t="inlineStr">
+      <c r="AC26" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC26" s="94" t="inlineStr">
+      <c r="AD26" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AD26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE26" s="93" t="inlineStr">
@@ -9346,91 +9346,91 @@
         <v>-0.8</v>
       </c>
       <c r="C27" s="95" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D27" s="95" t="n">
         <v>-3.91</v>
       </c>
-      <c r="D27" s="95" t="n">
+      <c r="E27" s="95" t="n">
         <v>-2.74</v>
       </c>
-      <c r="E27" s="95" t="n">
+      <c r="F27" s="95" t="n">
         <v>-2.68</v>
       </c>
-      <c r="F27" s="95" t="n">
+      <c r="G27" s="95" t="n">
         <v>-0.89</v>
       </c>
-      <c r="G27" s="95" t="n">
+      <c r="H27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="H27" s="95" t="n">
+      <c r="I27" s="95" t="n">
         <v>0.9</v>
       </c>
-      <c r="I27" s="95" t="n">
+      <c r="J27" s="95" t="n">
         <v>1.13</v>
       </c>
-      <c r="J27" s="95" t="n">
+      <c r="K27" s="95" t="n">
         <v>1.93</v>
       </c>
-      <c r="K27" s="95" t="n">
+      <c r="L27" s="95" t="n">
         <v>0.65</v>
       </c>
-      <c r="L27" s="95" t="n">
+      <c r="M27" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="M27" s="95" t="n">
+      <c r="N27" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="N27" s="95" t="n">
+      <c r="O27" s="95" t="n">
         <v>0.44</v>
       </c>
-      <c r="O27" s="95" t="n">
+      <c r="P27" s="95" t="n">
         <v>-0.35</v>
       </c>
-      <c r="P27" s="95" t="n">
+      <c r="Q27" s="95" t="n">
         <v>-0.73</v>
       </c>
-      <c r="Q27" s="95" t="n">
+      <c r="R27" s="95" t="n">
         <v>-1</v>
       </c>
-      <c r="R27" s="95" t="n">
+      <c r="S27" s="95" t="n">
         <v>-1.61</v>
       </c>
-      <c r="S27" s="95" t="n">
+      <c r="T27" s="95" t="n">
         <v>-1.66</v>
       </c>
-      <c r="T27" s="95" t="n">
+      <c r="U27" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="U27" s="95" t="n">
+      <c r="V27" s="95" t="n">
         <v>-4.11</v>
       </c>
-      <c r="V27" s="95" t="n">
+      <c r="W27" s="95" t="n">
         <v>-3.76</v>
       </c>
-      <c r="W27" s="95" t="n">
+      <c r="X27" s="95" t="n">
         <v>-0.38</v>
       </c>
-      <c r="X27" s="95" t="n">
+      <c r="Y27" s="95" t="n">
         <v>-0.28</v>
       </c>
-      <c r="Y27" s="95" t="n">
+      <c r="Z27" s="95" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="Z27" s="95" t="n">
-        <v>3.06</v>
       </c>
       <c r="AA27" s="95" t="n">
         <v>3.06</v>
       </c>
       <c r="AB27" s="95" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AC27" s="95" t="n">
         <v>3.91</v>
       </c>
-      <c r="AC27" s="95" t="n">
+      <c r="AD27" s="95" t="n">
         <v>4.32</v>
       </c>
-      <c r="AD27" s="95" t="n">
+      <c r="AE27" s="95" t="n">
         <v>6.09</v>
-      </c>
-      <c r="AE27" s="95" t="n">
-        <v>5.91</v>
       </c>
     </row>
     <row r="28">
@@ -9443,91 +9443,91 @@
         <v>14.18</v>
       </c>
       <c r="C28" s="95" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="D28" s="95" t="n">
         <v>10.78</v>
       </c>
-      <c r="D28" s="95" t="n">
+      <c r="E28" s="95" t="n">
         <v>9.02</v>
       </c>
-      <c r="E28" s="95" t="n">
+      <c r="F28" s="95" t="n">
         <v>10.76</v>
       </c>
-      <c r="F28" s="95" t="n">
+      <c r="G28" s="95" t="n">
         <v>11.54</v>
       </c>
-      <c r="G28" s="95" t="n">
+      <c r="H28" s="95" t="n">
         <v>11.48</v>
       </c>
-      <c r="H28" s="95" t="n">
+      <c r="I28" s="95" t="n">
         <v>11.95</v>
       </c>
-      <c r="I28" s="95" t="n">
+      <c r="J28" s="95" t="n">
         <v>12.67</v>
       </c>
-      <c r="J28" s="95" t="n">
+      <c r="K28" s="95" t="n">
         <v>11.04</v>
       </c>
-      <c r="K28" s="95" t="n">
+      <c r="L28" s="95" t="n">
         <v>10.68</v>
       </c>
-      <c r="L28" s="95" t="n">
+      <c r="M28" s="95" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="M28" s="95" t="n">
+      <c r="N28" s="95" t="n">
         <v>9.98</v>
       </c>
-      <c r="N28" s="95" t="n">
+      <c r="O28" s="95" t="n">
         <v>7.16</v>
       </c>
-      <c r="O28" s="95" t="n">
+      <c r="P28" s="95" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="P28" s="95" t="n">
+      <c r="Q28" s="95" t="n">
         <v>7.37</v>
       </c>
-      <c r="Q28" s="95" t="n">
+      <c r="R28" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="R28" s="95" t="n">
+      <c r="S28" s="95" t="n">
         <v>7.12</v>
       </c>
-      <c r="S28" s="95" t="n">
+      <c r="T28" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="T28" s="95" t="n">
+      <c r="U28" s="95" t="n">
         <v>5.31</v>
       </c>
-      <c r="U28" s="95" t="n">
+      <c r="V28" s="95" t="n">
         <v>4.85</v>
       </c>
-      <c r="V28" s="95" t="n">
+      <c r="W28" s="95" t="n">
         <v>4.49</v>
       </c>
-      <c r="W28" s="95" t="n">
+      <c r="X28" s="95" t="n">
         <v>6.19</v>
       </c>
-      <c r="X28" s="95" t="n">
+      <c r="Y28" s="95" t="n">
         <v>5.6</v>
       </c>
-      <c r="Y28" s="95" t="n">
+      <c r="Z28" s="95" t="n">
         <v>5.35</v>
-      </c>
-      <c r="Z28" s="95" t="n">
-        <v>10.58</v>
       </c>
       <c r="AA28" s="95" t="n">
         <v>10.58</v>
       </c>
       <c r="AB28" s="95" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="AC28" s="95" t="n">
         <v>8.9</v>
       </c>
-      <c r="AC28" s="95" t="n">
+      <c r="AD28" s="95" t="n">
         <v>7.88</v>
       </c>
-      <c r="AD28" s="95" t="n">
+      <c r="AE28" s="95" t="n">
         <v>10.75</v>
-      </c>
-      <c r="AE28" s="95" t="n">
-        <v>11.21</v>
       </c>
     </row>
     <row r="29">
@@ -9540,91 +9540,91 @@
         <v>85.03</v>
       </c>
       <c r="C29" s="95" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="D29" s="95" t="n">
         <v>20.54</v>
       </c>
-      <c r="D29" s="95" t="n">
+      <c r="E29" s="95" t="n">
         <v>21.97</v>
       </c>
-      <c r="E29" s="95" t="n">
+      <c r="F29" s="95" t="n">
         <v>15.42</v>
       </c>
-      <c r="F29" s="95" t="n">
+      <c r="G29" s="95" t="n">
         <v>74.7</v>
       </c>
-      <c r="G29" s="95" t="n">
+      <c r="H29" s="95" t="n">
         <v>51.35</v>
       </c>
-      <c r="H29" s="95" t="n">
+      <c r="I29" s="95" t="n">
         <v>96.66</v>
       </c>
-      <c r="I29" s="95" t="n">
+      <c r="J29" s="95" t="n">
         <v>89.75</v>
       </c>
-      <c r="J29" s="95" t="n">
+      <c r="K29" s="95" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="K29" s="95" t="n">
+      <c r="L29" s="95" t="n">
         <v>77.02</v>
       </c>
-      <c r="L29" s="95" t="n">
+      <c r="M29" s="95" t="n">
         <v>73.3</v>
       </c>
-      <c r="M29" s="95" t="n">
+      <c r="N29" s="95" t="n">
         <v>92.18000000000001</v>
       </c>
-      <c r="N29" s="95" t="n">
+      <c r="O29" s="95" t="n">
         <v>42.32</v>
       </c>
-      <c r="O29" s="95" t="n">
+      <c r="P29" s="95" t="n">
         <v>70.06</v>
       </c>
-      <c r="P29" s="95" t="n">
+      <c r="Q29" s="95" t="n">
         <v>61.86</v>
       </c>
-      <c r="Q29" s="95" t="n">
+      <c r="R29" s="95" t="n">
         <v>95.17</v>
       </c>
-      <c r="R29" s="95" t="n">
+      <c r="S29" s="95" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="S29" s="95" t="n">
+      <c r="T29" s="95" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="T29" s="95" t="n">
+      <c r="U29" s="95" t="n">
         <v>65.19</v>
       </c>
-      <c r="U29" s="95" t="n">
+      <c r="V29" s="95" t="n">
         <v>44.48</v>
       </c>
-      <c r="V29" s="95" t="n">
+      <c r="W29" s="95" t="n">
         <v>6.2</v>
       </c>
-      <c r="W29" s="95" t="n">
+      <c r="X29" s="95" t="n">
         <v>27.81</v>
       </c>
-      <c r="X29" s="95" t="n">
+      <c r="Y29" s="95" t="n">
         <v>12.7</v>
       </c>
-      <c r="Y29" s="95" t="n">
+      <c r="Z29" s="95" t="n">
         <v>14.52</v>
-      </c>
-      <c r="Z29" s="95" t="n">
-        <v>71.48999999999999</v>
       </c>
       <c r="AA29" s="95" t="n">
         <v>71.48999999999999</v>
       </c>
       <c r="AB29" s="95" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="AC29" s="95" t="n">
         <v>13.66</v>
       </c>
-      <c r="AC29" s="95" t="n">
+      <c r="AD29" s="95" t="n">
         <v>17.16</v>
       </c>
-      <c r="AD29" s="95" t="n">
+      <c r="AE29" s="95" t="n">
         <v>47.94</v>
-      </c>
-      <c r="AE29" s="95" t="n">
-        <v>40.09</v>
       </c>
     </row>
     <row r="30">
@@ -9633,124 +9633,124 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C30" s="93" t="inlineStr">
+      <c r="D30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D30" s="94" t="inlineStr">
+      <c r="E30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E30" s="93" t="inlineStr">
+      <c r="F30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F30" s="93" t="inlineStr">
+      <c r="G30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G30" s="92" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="I30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="92" t="inlineStr">
+      <c r="K30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K30" s="92" t="inlineStr">
+      <c r="L30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L30" s="92" t="inlineStr">
+      <c r="M30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M30" s="92" t="inlineStr">
+      <c r="N30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="93" t="inlineStr">
+      <c r="S30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S30" s="94" t="inlineStr">
+      <c r="T30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T30" s="94" t="inlineStr">
+      <c r="U30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U30" s="94" t="inlineStr">
+      <c r="V30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V30" s="94" t="inlineStr">
+      <c r="W30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W30" s="94" t="inlineStr">
+      <c r="X30" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X30" s="94" t="inlineStr">
+      <c r="Y30" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Y30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="Z30" s="93" t="inlineStr">
@@ -9791,94 +9791,94 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="C31" s="95" t="n">
         <v>-7.64</v>
       </c>
-      <c r="C31" s="95" t="n">
+      <c r="D31" s="95" t="n">
         <v>-7.28</v>
       </c>
-      <c r="D31" s="95" t="n">
+      <c r="E31" s="95" t="n">
         <v>-7.29</v>
       </c>
-      <c r="E31" s="95" t="n">
+      <c r="F31" s="95" t="n">
         <v>-5.52</v>
       </c>
-      <c r="F31" s="95" t="n">
+      <c r="G31" s="95" t="n">
         <v>-7.32</v>
       </c>
-      <c r="G31" s="95" t="n">
+      <c r="H31" s="95" t="n">
         <v>-1.85</v>
       </c>
-      <c r="H31" s="95" t="n">
+      <c r="I31" s="95" t="n">
         <v>-2.87</v>
       </c>
-      <c r="I31" s="95" t="n">
+      <c r="J31" s="95" t="n">
         <v>-4.44</v>
       </c>
-      <c r="J31" s="95" t="n">
+      <c r="K31" s="95" t="n">
         <v>-4.15</v>
-      </c>
-      <c r="K31" s="95" t="n">
-        <v>-4.11</v>
       </c>
       <c r="L31" s="95" t="n">
         <v>-4.11</v>
       </c>
       <c r="M31" s="95" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="N31" s="95" t="n">
         <v>-6.33</v>
       </c>
-      <c r="N31" s="95" t="n">
+      <c r="O31" s="95" t="n">
         <v>-7.13</v>
       </c>
-      <c r="O31" s="95" t="n">
+      <c r="P31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="P31" s="95" t="n">
+      <c r="Q31" s="95" t="n">
         <v>-5.28</v>
       </c>
-      <c r="Q31" s="95" t="n">
+      <c r="R31" s="95" t="n">
         <v>-5.31</v>
       </c>
-      <c r="R31" s="95" t="n">
+      <c r="S31" s="95" t="n">
         <v>-4.5</v>
       </c>
-      <c r="S31" s="95" t="n">
+      <c r="T31" s="95" t="n">
         <v>-7.44</v>
       </c>
-      <c r="T31" s="95" t="n">
+      <c r="U31" s="95" t="n">
         <v>-5.1</v>
       </c>
-      <c r="U31" s="95" t="n">
+      <c r="V31" s="95" t="n">
         <v>-6.7</v>
       </c>
-      <c r="V31" s="95" t="n">
+      <c r="W31" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="W31" s="95" t="n">
+      <c r="X31" s="95" t="n">
         <v>-5.71</v>
       </c>
-      <c r="X31" s="95" t="n">
+      <c r="Y31" s="95" t="n">
         <v>-5.33</v>
       </c>
-      <c r="Y31" s="95" t="n">
+      <c r="Z31" s="95" t="n">
         <v>-0.9</v>
       </c>
-      <c r="Z31" s="95" t="n">
+      <c r="AA31" s="95" t="n">
         <v>0.04</v>
       </c>
-      <c r="AA31" s="95" t="n">
+      <c r="AB31" s="95" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AB31" s="95" t="n">
+      <c r="AC31" s="95" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AC31" s="95" t="n">
+      <c r="AD31" s="95" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AD31" s="95" t="n">
+      <c r="AE31" s="95" t="n">
         <v>-1.63</v>
-      </c>
-      <c r="AE31" s="95" t="n">
-        <v>-0.98</v>
       </c>
     </row>
     <row r="32">
@@ -9888,94 +9888,94 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C32" s="95" t="n">
         <v>-2.25</v>
       </c>
-      <c r="C32" s="95" t="n">
+      <c r="D32" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="D32" s="95" t="n">
+      <c r="E32" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="E32" s="95" t="n">
+      <c r="F32" s="95" t="n">
         <v>-2.82</v>
       </c>
-      <c r="F32" s="95" t="n">
+      <c r="G32" s="95" t="n">
         <v>-3.63</v>
       </c>
-      <c r="G32" s="95" t="n">
+      <c r="H32" s="95" t="n">
         <v>2.15</v>
       </c>
-      <c r="H32" s="95" t="n">
+      <c r="I32" s="95" t="n">
         <v>-2.13</v>
       </c>
-      <c r="I32" s="95" t="n">
+      <c r="J32" s="95" t="n">
         <v>-4.01</v>
       </c>
-      <c r="J32" s="95" t="n">
+      <c r="K32" s="95" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="K32" s="95" t="n">
-        <v>-5.22</v>
       </c>
       <c r="L32" s="95" t="n">
         <v>-5.22</v>
       </c>
       <c r="M32" s="95" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="N32" s="95" t="n">
         <v>-7.96</v>
       </c>
-      <c r="N32" s="95" t="n">
+      <c r="O32" s="95" t="n">
         <v>-9.43</v>
       </c>
-      <c r="O32" s="95" t="n">
+      <c r="P32" s="95" t="n">
         <v>-11.19</v>
       </c>
-      <c r="P32" s="95" t="n">
+      <c r="Q32" s="95" t="n">
         <v>-9.5</v>
       </c>
-      <c r="Q32" s="95" t="n">
+      <c r="R32" s="95" t="n">
         <v>-9.48</v>
       </c>
-      <c r="R32" s="95" t="n">
+      <c r="S32" s="95" t="n">
         <v>-9.92</v>
       </c>
-      <c r="S32" s="95" t="n">
+      <c r="T32" s="95" t="n">
         <v>-12.73</v>
       </c>
-      <c r="T32" s="95" t="n">
+      <c r="U32" s="95" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="U32" s="95" t="n">
+      <c r="V32" s="95" t="n">
         <v>-8.869999999999999</v>
       </c>
-      <c r="V32" s="95" t="n">
+      <c r="W32" s="95" t="n">
         <v>-5.98</v>
       </c>
-      <c r="W32" s="95" t="n">
+      <c r="X32" s="95" t="n">
         <v>-5.54</v>
       </c>
-      <c r="X32" s="95" t="n">
+      <c r="Y32" s="95" t="n">
         <v>-4.26</v>
       </c>
-      <c r="Y32" s="95" t="n">
+      <c r="Z32" s="95" t="n">
         <v>-0.29</v>
       </c>
-      <c r="Z32" s="95" t="n">
+      <c r="AA32" s="95" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AA32" s="95" t="n">
+      <c r="AB32" s="95" t="n">
         <v>-2.62</v>
       </c>
-      <c r="AB32" s="95" t="n">
+      <c r="AC32" s="95" t="n">
         <v>-3.12</v>
       </c>
-      <c r="AC32" s="95" t="n">
+      <c r="AD32" s="95" t="n">
         <v>-4.29</v>
       </c>
-      <c r="AD32" s="95" t="n">
+      <c r="AE32" s="95" t="n">
         <v>-4.51</v>
-      </c>
-      <c r="AE32" s="95" t="n">
-        <v>-4.98</v>
       </c>
     </row>
     <row r="33">
@@ -9985,94 +9985,94 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="C33" s="95" t="n">
         <v>56.86</v>
       </c>
-      <c r="C33" s="95" t="n">
+      <c r="D33" s="95" t="n">
         <v>56.21</v>
       </c>
-      <c r="D33" s="95" t="n">
+      <c r="E33" s="95" t="n">
         <v>50.28</v>
       </c>
-      <c r="E33" s="95" t="n">
+      <c r="F33" s="95" t="n">
         <v>58.22</v>
       </c>
-      <c r="F33" s="95" t="n">
+      <c r="G33" s="95" t="n">
         <v>52.42</v>
       </c>
-      <c r="G33" s="95" t="n">
+      <c r="H33" s="95" t="n">
         <v>77.31</v>
       </c>
-      <c r="H33" s="95" t="n">
+      <c r="I33" s="95" t="n">
         <v>71.64</v>
       </c>
-      <c r="I33" s="95" t="n">
+      <c r="J33" s="95" t="n">
         <v>61.74</v>
       </c>
-      <c r="J33" s="95" t="n">
+      <c r="K33" s="95" t="n">
         <v>63.04</v>
-      </c>
-      <c r="K33" s="95" t="n">
-        <v>60.77</v>
       </c>
       <c r="L33" s="95" t="n">
         <v>60.77</v>
       </c>
       <c r="M33" s="95" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="N33" s="95" t="n">
         <v>54.21</v>
       </c>
-      <c r="N33" s="95" t="n">
+      <c r="O33" s="95" t="n">
         <v>42.56</v>
       </c>
-      <c r="O33" s="95" t="n">
+      <c r="P33" s="95" t="n">
         <v>39.44</v>
       </c>
-      <c r="P33" s="95" t="n">
+      <c r="Q33" s="95" t="n">
         <v>43.68</v>
       </c>
-      <c r="Q33" s="95" t="n">
+      <c r="R33" s="95" t="n">
         <v>43.96</v>
       </c>
-      <c r="R33" s="95" t="n">
+      <c r="S33" s="95" t="n">
         <v>46.79</v>
       </c>
-      <c r="S33" s="95" t="n">
+      <c r="T33" s="95" t="n">
         <v>26.47</v>
       </c>
-      <c r="T33" s="95" t="n">
+      <c r="U33" s="95" t="n">
         <v>31.18</v>
       </c>
-      <c r="U33" s="95" t="n">
+      <c r="V33" s="95" t="n">
         <v>31.7</v>
       </c>
-      <c r="V33" s="95" t="n">
+      <c r="W33" s="95" t="n">
         <v>33.25</v>
       </c>
-      <c r="W33" s="95" t="n">
+      <c r="X33" s="95" t="n">
         <v>35.58</v>
       </c>
-      <c r="X33" s="95" t="n">
+      <c r="Y33" s="95" t="n">
         <v>39.17</v>
       </c>
-      <c r="Y33" s="95" t="n">
+      <c r="Z33" s="95" t="n">
         <v>62.79</v>
       </c>
-      <c r="Z33" s="95" t="n">
+      <c r="AA33" s="95" t="n">
         <v>63.09</v>
       </c>
-      <c r="AA33" s="95" t="n">
+      <c r="AB33" s="95" t="n">
         <v>62.51</v>
       </c>
-      <c r="AB33" s="95" t="n">
+      <c r="AC33" s="95" t="n">
         <v>59.46</v>
       </c>
-      <c r="AC33" s="95" t="n">
+      <c r="AD33" s="95" t="n">
         <v>59.6</v>
       </c>
-      <c r="AD33" s="95" t="n">
+      <c r="AE33" s="95" t="n">
         <v>58.83</v>
-      </c>
-      <c r="AE33" s="95" t="n">
-        <v>57.26</v>
       </c>
     </row>
     <row r="34">
@@ -10091,109 +10091,109 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D34" s="93" t="inlineStr">
+      <c r="D34" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="93" t="inlineStr">
+      <c r="F34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F34" s="93" t="inlineStr">
+      <c r="G34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="92" t="inlineStr">
+      <c r="I34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I34" s="92" t="inlineStr">
+      <c r="J34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J34" s="92" t="inlineStr">
+      <c r="K34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="L34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L34" s="92" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M34" s="92" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="92" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="P34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P34" s="94" t="inlineStr">
+      <c r="Q34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="94" t="inlineStr">
+      <c r="R34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R34" s="94" t="inlineStr">
+      <c r="S34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S34" s="94" t="inlineStr">
+      <c r="T34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T34" s="94" t="inlineStr">
+      <c r="U34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U34" s="94" t="inlineStr">
+      <c r="V34" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="W34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W34" s="94" t="inlineStr">
+      <c r="X34" s="94" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="X34" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="Y34" s="93" t="inlineStr">
@@ -10239,76 +10239,76 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="C35" s="95" t="n">
         <v>-1.19</v>
       </c>
-      <c r="C35" s="95" t="n">
+      <c r="D35" s="95" t="n">
         <v>-1.21</v>
       </c>
-      <c r="D35" s="95" t="n">
+      <c r="E35" s="95" t="n">
         <v>0.33</v>
       </c>
-      <c r="E35" s="95" t="n">
+      <c r="F35" s="95" t="n">
         <v>0.71</v>
       </c>
-      <c r="F35" s="95" t="n">
+      <c r="G35" s="95" t="n">
         <v>0.63</v>
       </c>
-      <c r="G35" s="95" t="n">
+      <c r="H35" s="95" t="n">
         <v>1.1</v>
       </c>
-      <c r="H35" s="95" t="n">
+      <c r="I35" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="I35" s="95" t="n">
+      <c r="J35" s="95" t="n">
         <v>2.62</v>
       </c>
-      <c r="J35" s="95" t="n">
+      <c r="K35" s="95" t="n">
         <v>1.79</v>
       </c>
-      <c r="K35" s="95" t="n">
+      <c r="L35" s="95" t="n">
         <v>1.86</v>
       </c>
-      <c r="L35" s="95" t="n">
+      <c r="M35" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="M35" s="95" t="n">
+      <c r="N35" s="95" t="n">
         <v>0.8</v>
       </c>
-      <c r="N35" s="95" t="n">
+      <c r="O35" s="95" t="n">
         <v>0.66</v>
       </c>
-      <c r="O35" s="95" t="n">
+      <c r="P35" s="95" t="n">
         <v>0.39</v>
       </c>
-      <c r="P35" s="95" t="n">
+      <c r="Q35" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="Q35" s="95" t="n">
+      <c r="R35" s="95" t="n">
         <v>-2.39</v>
       </c>
-      <c r="R35" s="95" t="n">
+      <c r="S35" s="95" t="n">
         <v>-1.83</v>
       </c>
-      <c r="S35" s="95" t="n">
+      <c r="T35" s="95" t="n">
         <v>-2.05</v>
       </c>
-      <c r="T35" s="95" t="n">
+      <c r="U35" s="95" t="n">
         <v>-1.53</v>
       </c>
-      <c r="U35" s="95" t="n">
+      <c r="V35" s="95" t="n">
         <v>-0.95</v>
       </c>
-      <c r="V35" s="95" t="n">
+      <c r="W35" s="95" t="n">
         <v>-2.12</v>
       </c>
-      <c r="W35" s="95" t="n">
+      <c r="X35" s="95" t="n">
         <v>-2.46</v>
       </c>
-      <c r="X35" s="95" t="n">
+      <c r="Y35" s="95" t="n">
         <v>-0.67</v>
-      </c>
-      <c r="Y35" s="95" t="n">
-        <v>-0.53</v>
       </c>
       <c r="Z35" s="95" t="n">
         <v>-0.53</v>
@@ -10317,16 +10317,16 @@
         <v>-0.53</v>
       </c>
       <c r="AB35" s="95" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AC35" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AC35" s="95" t="n">
+      <c r="AD35" s="95" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AD35" s="95" t="n">
+      <c r="AE35" s="95" t="n">
         <v>-0.3</v>
-      </c>
-      <c r="AE35" s="95" t="n">
-        <v>-0.27</v>
       </c>
     </row>
     <row r="36">
@@ -10336,76 +10336,76 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C36" s="95" t="n">
         <v>-0.47</v>
       </c>
-      <c r="C36" s="95" t="n">
+      <c r="D36" s="95" t="n">
         <v>1.58</v>
-      </c>
-      <c r="D36" s="95" t="n">
-        <v>2.33</v>
       </c>
       <c r="E36" s="95" t="n">
         <v>2.33</v>
       </c>
       <c r="F36" s="95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G36" s="95" t="n">
         <v>3.01</v>
       </c>
-      <c r="G36" s="95" t="n">
+      <c r="H36" s="95" t="n">
         <v>2.85</v>
       </c>
-      <c r="H36" s="95" t="n">
+      <c r="I36" s="95" t="n">
         <v>1.83</v>
       </c>
-      <c r="I36" s="95" t="n">
+      <c r="J36" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="J36" s="95" t="n">
+      <c r="K36" s="95" t="n">
         <v>-0.78</v>
       </c>
-      <c r="K36" s="95" t="n">
+      <c r="L36" s="95" t="n">
         <v>-1.02</v>
       </c>
-      <c r="L36" s="95" t="n">
+      <c r="M36" s="95" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="M36" s="95" t="n">
+      <c r="N36" s="95" t="n">
         <v>-1.47</v>
       </c>
-      <c r="N36" s="95" t="n">
+      <c r="O36" s="95" t="n">
         <v>-1.42</v>
       </c>
-      <c r="O36" s="95" t="n">
+      <c r="P36" s="95" t="n">
         <v>-1.81</v>
       </c>
-      <c r="P36" s="95" t="n">
+      <c r="Q36" s="95" t="n">
         <v>-2.26</v>
       </c>
-      <c r="Q36" s="95" t="n">
+      <c r="R36" s="95" t="n">
         <v>-2.35</v>
       </c>
-      <c r="R36" s="95" t="n">
+      <c r="S36" s="95" t="n">
         <v>-1.57</v>
       </c>
-      <c r="S36" s="95" t="n">
+      <c r="T36" s="95" t="n">
         <v>-0.54</v>
       </c>
-      <c r="T36" s="95" t="n">
+      <c r="U36" s="95" t="n">
         <v>1.03</v>
       </c>
-      <c r="U36" s="95" t="n">
+      <c r="V36" s="95" t="n">
         <v>1.94</v>
       </c>
-      <c r="V36" s="95" t="n">
+      <c r="W36" s="95" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="W36" s="95" t="n">
+      <c r="X36" s="95" t="n">
         <v>0.31</v>
       </c>
-      <c r="X36" s="95" t="n">
+      <c r="Y36" s="95" t="n">
         <v>0.42</v>
-      </c>
-      <c r="Y36" s="95" t="n">
-        <v>3.12</v>
       </c>
       <c r="Z36" s="95" t="n">
         <v>3.12</v>
@@ -10414,95 +10414,95 @@
         <v>3.12</v>
       </c>
       <c r="AB36" s="95" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AC36" s="95" t="n">
         <v>3.72</v>
       </c>
-      <c r="AC36" s="95" t="n">
+      <c r="AD36" s="95" t="n">
         <v>2.73</v>
       </c>
-      <c r="AD36" s="95" t="n">
+      <c r="AE36" s="95" t="n">
         <v>0.95</v>
       </c>
-      <c r="AE36" s="95" t="n">
-        <v>1.37</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="95" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="C37" s="95" t="n">
         <v>14.32</v>
       </c>
-      <c r="C37" s="95" t="n">
+      <c r="D37" s="95" t="n">
         <v>23.23</v>
       </c>
-      <c r="D37" s="95" t="n">
+      <c r="E37" s="95" t="n">
         <v>50.34</v>
       </c>
-      <c r="E37" s="95" t="n">
+      <c r="F37" s="95" t="n">
         <v>77.23999999999999</v>
       </c>
-      <c r="F37" s="95" t="n">
+      <c r="G37" s="95" t="n">
         <v>65.09</v>
       </c>
-      <c r="G37" s="95" t="n">
+      <c r="H37" s="95" t="n">
         <v>86.66</v>
       </c>
-      <c r="H37" s="95" t="n">
+      <c r="I37" s="95" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="I37" s="95" t="n">
+      <c r="J37" s="95" t="n">
         <v>88</v>
       </c>
-      <c r="J37" s="95" t="n">
+      <c r="K37" s="95" t="n">
         <v>77.98</v>
       </c>
-      <c r="K37" s="95" t="n">
+      <c r="L37" s="95" t="n">
         <v>59.82</v>
       </c>
-      <c r="L37" s="95" t="n">
+      <c r="M37" s="95" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="M37" s="95" t="n">
+      <c r="N37" s="95" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="N37" s="95" t="n">
+      <c r="O37" s="95" t="n">
         <v>68.98</v>
       </c>
-      <c r="O37" s="95" t="n">
+      <c r="P37" s="95" t="n">
         <v>60.96</v>
       </c>
-      <c r="P37" s="95" t="n">
+      <c r="Q37" s="95" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="Q37" s="95" t="n">
+      <c r="R37" s="95" t="n">
         <v>20.58</v>
       </c>
-      <c r="R37" s="95" t="n">
+      <c r="S37" s="95" t="n">
         <v>30.12</v>
       </c>
-      <c r="S37" s="95" t="n">
+      <c r="T37" s="95" t="n">
         <v>12.08</v>
       </c>
-      <c r="T37" s="95" t="n">
+      <c r="U37" s="95" t="n">
         <v>13.57</v>
       </c>
-      <c r="U37" s="95" t="n">
+      <c r="V37" s="95" t="n">
         <v>28.44</v>
       </c>
-      <c r="V37" s="95" t="n">
+      <c r="W37" s="95" t="n">
         <v>44.72</v>
       </c>
-      <c r="W37" s="95" t="n">
+      <c r="X37" s="95" t="n">
         <v>14.66</v>
       </c>
-      <c r="X37" s="95" t="n">
+      <c r="Y37" s="95" t="n">
         <v>28.1</v>
-      </c>
-      <c r="Y37" s="95" t="n">
-        <v>80.38</v>
       </c>
       <c r="Z37" s="95" t="n">
         <v>80.38</v>
@@ -10511,16 +10511,16 @@
         <v>80.38</v>
       </c>
       <c r="AB37" s="95" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="AC37" s="95" t="n">
         <v>68.92</v>
       </c>
-      <c r="AC37" s="95" t="n">
+      <c r="AD37" s="95" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="AD37" s="95" t="n">
+      <c r="AE37" s="95" t="n">
         <v>65.45999999999999</v>
-      </c>
-      <c r="AE37" s="95" t="n">
-        <v>63.9</v>
       </c>
     </row>
     <row r="38">
@@ -10539,119 +10539,119 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D38" s="93" t="inlineStr">
+      <c r="D38" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="93" t="inlineStr">
+      <c r="F38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="93" t="inlineStr">
+      <c r="G38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="H38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H38" s="92" t="inlineStr">
+      <c r="I38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="J38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J38" s="92" t="inlineStr">
+      <c r="K38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K38" s="92" t="inlineStr">
+      <c r="L38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="M38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="N38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N38" s="93" t="inlineStr">
+      <c r="O38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O38" s="92" t="inlineStr">
+      <c r="P38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P38" s="92" t="inlineStr">
+      <c r="Q38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q38" s="92" t="inlineStr">
+      <c r="R38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R38" s="92" t="inlineStr">
+      <c r="S38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S38" s="94" t="inlineStr">
+      <c r="T38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="94" t="inlineStr">
+      <c r="V38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V38" s="94" t="inlineStr">
+      <c r="W38" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W38" s="93" t="inlineStr">
+      <c r="X38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X38" s="93" t="inlineStr">
+      <c r="Y38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y38" s="93" t="inlineStr">
+      <c r="Z38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Z38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AA38" s="92" t="inlineStr">
@@ -10687,94 +10687,94 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C39" s="95" t="n">
         <v>2.21</v>
       </c>
-      <c r="C39" s="95" t="n">
+      <c r="D39" s="95" t="n">
         <v>2.67</v>
-      </c>
-      <c r="D39" s="95" t="n">
-        <v>5.39</v>
       </c>
       <c r="E39" s="95" t="n">
         <v>5.39</v>
       </c>
       <c r="F39" s="95" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="G39" s="95" t="n">
         <v>5.38</v>
       </c>
-      <c r="G39" s="95" t="n">
+      <c r="H39" s="95" t="n">
         <v>6.9</v>
       </c>
-      <c r="H39" s="95" t="n">
+      <c r="I39" s="95" t="n">
         <v>7.31</v>
       </c>
-      <c r="I39" s="95" t="n">
+      <c r="J39" s="95" t="n">
         <v>7.21</v>
       </c>
-      <c r="J39" s="95" t="n">
+      <c r="K39" s="95" t="n">
         <v>6.84</v>
       </c>
-      <c r="K39" s="95" t="n">
+      <c r="L39" s="95" t="n">
         <v>7.46</v>
       </c>
-      <c r="L39" s="95" t="n">
+      <c r="M39" s="95" t="n">
         <v>6.69</v>
       </c>
-      <c r="M39" s="95" t="n">
+      <c r="N39" s="95" t="n">
         <v>5.73</v>
       </c>
-      <c r="N39" s="95" t="n">
+      <c r="O39" s="95" t="n">
         <v>6.27</v>
       </c>
-      <c r="O39" s="95" t="n">
+      <c r="P39" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="P39" s="95" t="n">
+      <c r="Q39" s="95" t="n">
         <v>7.48</v>
       </c>
-      <c r="Q39" s="95" t="n">
+      <c r="R39" s="95" t="n">
         <v>6.99</v>
       </c>
-      <c r="R39" s="95" t="n">
+      <c r="S39" s="95" t="n">
         <v>7.27</v>
       </c>
-      <c r="S39" s="95" t="n">
+      <c r="T39" s="95" t="n">
         <v>5.46</v>
       </c>
-      <c r="T39" s="95" t="n">
+      <c r="U39" s="95" t="n">
         <v>6.4</v>
       </c>
-      <c r="U39" s="95" t="n">
+      <c r="V39" s="95" t="n">
         <v>6.18</v>
       </c>
-      <c r="V39" s="95" t="n">
+      <c r="W39" s="95" t="n">
         <v>5.98</v>
       </c>
-      <c r="W39" s="95" t="n">
+      <c r="X39" s="95" t="n">
         <v>7.51</v>
       </c>
-      <c r="X39" s="95" t="n">
+      <c r="Y39" s="95" t="n">
         <v>7.66</v>
       </c>
-      <c r="Y39" s="95" t="n">
+      <c r="Z39" s="95" t="n">
         <v>7.64</v>
       </c>
-      <c r="Z39" s="95" t="n">
+      <c r="AA39" s="95" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="AA39" s="95" t="n">
+      <c r="AB39" s="95" t="n">
         <v>10.73</v>
       </c>
-      <c r="AB39" s="95" t="n">
+      <c r="AC39" s="95" t="n">
         <v>13.95</v>
       </c>
-      <c r="AC39" s="95" t="n">
+      <c r="AD39" s="95" t="n">
         <v>6.95</v>
       </c>
-      <c r="AD39" s="95" t="n">
+      <c r="AE39" s="95" t="n">
         <v>10.48</v>
-      </c>
-      <c r="AE39" s="95" t="n">
-        <v>10.57</v>
       </c>
     </row>
     <row r="40">
@@ -10784,94 +10784,94 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="C40" s="95" t="n">
         <v>10.03</v>
       </c>
-      <c r="C40" s="95" t="n">
+      <c r="D40" s="95" t="n">
         <v>9.94</v>
-      </c>
-      <c r="D40" s="95" t="n">
-        <v>12.83</v>
       </c>
       <c r="E40" s="95" t="n">
         <v>12.83</v>
       </c>
       <c r="F40" s="95" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="G40" s="95" t="n">
         <v>12.79</v>
       </c>
-      <c r="G40" s="95" t="n">
+      <c r="H40" s="95" t="n">
         <v>15.25</v>
       </c>
-      <c r="H40" s="95" t="n">
+      <c r="I40" s="95" t="n">
         <v>15.64</v>
       </c>
-      <c r="I40" s="95" t="n">
+      <c r="J40" s="95" t="n">
         <v>15.29</v>
       </c>
-      <c r="J40" s="95" t="n">
+      <c r="K40" s="95" t="n">
         <v>14.9</v>
       </c>
-      <c r="K40" s="95" t="n">
+      <c r="L40" s="95" t="n">
         <v>14.75</v>
       </c>
-      <c r="L40" s="95" t="n">
+      <c r="M40" s="95" t="n">
         <v>14.79</v>
       </c>
-      <c r="M40" s="95" t="n">
+      <c r="N40" s="95" t="n">
         <v>13.96</v>
       </c>
-      <c r="N40" s="95" t="n">
+      <c r="O40" s="95" t="n">
         <v>14.46</v>
       </c>
-      <c r="O40" s="95" t="n">
+      <c r="P40" s="95" t="n">
         <v>14.07</v>
       </c>
-      <c r="P40" s="95" t="n">
+      <c r="Q40" s="95" t="n">
         <v>14.24</v>
       </c>
-      <c r="Q40" s="95" t="n">
+      <c r="R40" s="95" t="n">
         <v>14.96</v>
       </c>
-      <c r="R40" s="95" t="n">
+      <c r="S40" s="95" t="n">
         <v>15.21</v>
       </c>
-      <c r="S40" s="95" t="n">
+      <c r="T40" s="95" t="n">
         <v>12.06</v>
       </c>
-      <c r="T40" s="95" t="n">
+      <c r="U40" s="95" t="n">
         <v>12.77</v>
       </c>
-      <c r="U40" s="95" t="n">
+      <c r="V40" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="V40" s="95" t="n">
+      <c r="W40" s="95" t="n">
         <v>11.57</v>
       </c>
-      <c r="W40" s="95" t="n">
+      <c r="X40" s="95" t="n">
         <v>11.58</v>
       </c>
-      <c r="X40" s="95" t="n">
+      <c r="Y40" s="95" t="n">
         <v>12.04</v>
       </c>
-      <c r="Y40" s="95" t="n">
+      <c r="Z40" s="95" t="n">
         <v>11.38</v>
       </c>
-      <c r="Z40" s="95" t="n">
+      <c r="AA40" s="95" t="n">
         <v>11.44</v>
       </c>
-      <c r="AA40" s="95" t="n">
+      <c r="AB40" s="95" t="n">
         <v>11.79</v>
       </c>
-      <c r="AB40" s="95" t="n">
+      <c r="AC40" s="95" t="n">
         <v>11.18</v>
       </c>
-      <c r="AC40" s="95" t="n">
+      <c r="AD40" s="95" t="n">
         <v>10.81</v>
       </c>
-      <c r="AD40" s="95" t="n">
+      <c r="AE40" s="95" t="n">
         <v>10.8</v>
-      </c>
-      <c r="AE40" s="95" t="n">
-        <v>12.69</v>
       </c>
     </row>
     <row r="41">
@@ -10881,94 +10881,94 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C41" s="95" t="n">
         <v>33.56</v>
       </c>
-      <c r="C41" s="95" t="n">
+      <c r="D41" s="95" t="n">
         <v>38.91</v>
-      </c>
-      <c r="D41" s="95" t="n">
-        <v>56.68</v>
       </c>
       <c r="E41" s="95" t="n">
         <v>56.68</v>
       </c>
       <c r="F41" s="95" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="G41" s="95" t="n">
         <v>57.12</v>
       </c>
-      <c r="G41" s="95" t="n">
+      <c r="H41" s="95" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="H41" s="95" t="n">
+      <c r="I41" s="95" t="n">
         <v>83.77</v>
       </c>
-      <c r="I41" s="95" t="n">
+      <c r="J41" s="95" t="n">
         <v>80.52</v>
       </c>
-      <c r="J41" s="95" t="n">
+      <c r="K41" s="95" t="n">
         <v>79.08</v>
       </c>
-      <c r="K41" s="95" t="n">
+      <c r="L41" s="95" t="n">
         <v>79.38</v>
       </c>
-      <c r="L41" s="95" t="n">
+      <c r="M41" s="95" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="M41" s="95" t="n">
+      <c r="N41" s="95" t="n">
         <v>66.75</v>
       </c>
-      <c r="N41" s="95" t="n">
+      <c r="O41" s="95" t="n">
         <v>64.14</v>
       </c>
-      <c r="O41" s="95" t="n">
+      <c r="P41" s="95" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="P41" s="95" t="n">
+      <c r="Q41" s="95" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="Q41" s="95" t="n">
+      <c r="R41" s="95" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="R41" s="95" t="n">
+      <c r="S41" s="95" t="n">
         <v>66.14</v>
       </c>
-      <c r="S41" s="95" t="n">
+      <c r="T41" s="95" t="n">
         <v>50.55</v>
       </c>
-      <c r="T41" s="95" t="n">
+      <c r="U41" s="95" t="n">
         <v>57.1</v>
       </c>
-      <c r="U41" s="95" t="n">
+      <c r="V41" s="95" t="n">
         <v>52.02</v>
       </c>
-      <c r="V41" s="95" t="n">
+      <c r="W41" s="95" t="n">
         <v>46.05</v>
       </c>
-      <c r="W41" s="95" t="n">
+      <c r="X41" s="95" t="n">
         <v>66.09</v>
       </c>
-      <c r="X41" s="95" t="n">
+      <c r="Y41" s="95" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="Y41" s="95" t="n">
+      <c r="Z41" s="95" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="Z41" s="95" t="n">
+      <c r="AA41" s="95" t="n">
         <v>75.97</v>
       </c>
-      <c r="AA41" s="95" t="n">
+      <c r="AB41" s="95" t="n">
         <v>74.36</v>
       </c>
-      <c r="AB41" s="95" t="n">
+      <c r="AC41" s="95" t="n">
         <v>72.38</v>
       </c>
-      <c r="AC41" s="95" t="n">
+      <c r="AD41" s="95" t="n">
         <v>69.15000000000001</v>
       </c>
-      <c r="AD41" s="95" t="n">
+      <c r="AE41" s="95" t="n">
         <v>68.44</v>
-      </c>
-      <c r="AE41" s="95" t="n">
-        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -10997,134 +10997,134 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="93" t="inlineStr">
+      <c r="F42" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G42" s="92" t="inlineStr">
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="I42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I42" s="92" t="inlineStr">
+      <c r="J42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="92" t="inlineStr">
+      <c r="K42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="93" t="inlineStr">
+      <c r="M42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="92" t="inlineStr">
+      <c r="N42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="92" t="inlineStr">
+      <c r="P42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="93" t="inlineStr">
+      <c r="Q42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="92" t="inlineStr">
+      <c r="R42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="93" t="inlineStr">
+      <c r="S42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="94" t="inlineStr">
+      <c r="T42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="94" t="inlineStr">
+      <c r="U42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="94" t="inlineStr">
+      <c r="V42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="94" t="inlineStr">
+      <c r="W42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W42" s="94" t="inlineStr">
+      <c r="X42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X42" s="94" t="inlineStr">
+      <c r="Y42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y42" s="93" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="93" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="92" t="inlineStr">
+      <c r="AC42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD42" s="93" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -11138,91 +11138,91 @@
         <v>-2.37</v>
       </c>
       <c r="C43" s="95" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="D43" s="95" t="n">
         <v>-1.96</v>
       </c>
-      <c r="D43" s="95" t="n">
+      <c r="E43" s="95" t="n">
         <v>0.05</v>
       </c>
-      <c r="E43" s="95" t="n">
+      <c r="F43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="F43" s="95" t="n">
+      <c r="G43" s="95" t="n">
         <v>0.11</v>
       </c>
-      <c r="G43" s="95" t="n">
+      <c r="H43" s="95" t="n">
         <v>1.51</v>
       </c>
-      <c r="H43" s="95" t="n">
+      <c r="I43" s="95" t="n">
         <v>0.6</v>
       </c>
-      <c r="I43" s="95" t="n">
+      <c r="J43" s="95" t="n">
         <v>-0.87</v>
       </c>
-      <c r="J43" s="95" t="n">
+      <c r="K43" s="95" t="n">
         <v>0.87</v>
       </c>
-      <c r="K43" s="95" t="n">
+      <c r="L43" s="95" t="n">
         <v>-0.7</v>
       </c>
-      <c r="L43" s="95" t="n">
+      <c r="M43" s="95" t="n">
         <v>0.28</v>
       </c>
-      <c r="M43" s="95" t="n">
+      <c r="N43" s="95" t="n">
         <v>1.12</v>
       </c>
-      <c r="N43" s="95" t="n">
+      <c r="O43" s="95" t="n">
         <v>-2.16</v>
       </c>
-      <c r="O43" s="95" t="n">
+      <c r="P43" s="95" t="n">
         <v>-2.28</v>
       </c>
-      <c r="P43" s="95" t="n">
+      <c r="Q43" s="95" t="n">
         <v>-3.34</v>
       </c>
-      <c r="Q43" s="95" t="n">
+      <c r="R43" s="95" t="n">
         <v>-2.14</v>
       </c>
-      <c r="R43" s="95" t="n">
+      <c r="S43" s="95" t="n">
         <v>-3.08</v>
       </c>
-      <c r="S43" s="95" t="n">
+      <c r="T43" s="95" t="n">
         <v>-2.29</v>
       </c>
-      <c r="T43" s="95" t="n">
+      <c r="U43" s="95" t="n">
         <v>-2.9</v>
       </c>
-      <c r="U43" s="95" t="n">
+      <c r="V43" s="95" t="n">
         <v>-1.93</v>
       </c>
-      <c r="V43" s="95" t="n">
+      <c r="W43" s="95" t="n">
         <v>-2.01</v>
       </c>
-      <c r="W43" s="95" t="n">
+      <c r="X43" s="95" t="n">
         <v>-3.58</v>
       </c>
-      <c r="X43" s="95" t="n">
+      <c r="Y43" s="95" t="n">
         <v>-4.62</v>
       </c>
-      <c r="Y43" s="95" t="n">
+      <c r="Z43" s="95" t="n">
         <v>-2.75</v>
       </c>
-      <c r="Z43" s="95" t="n">
+      <c r="AA43" s="95" t="n">
         <v>-3.14</v>
       </c>
-      <c r="AA43" s="95" t="n">
+      <c r="AB43" s="95" t="n">
         <v>-4.63</v>
       </c>
-      <c r="AB43" s="95" t="n">
+      <c r="AC43" s="95" t="n">
         <v>-4.96</v>
       </c>
-      <c r="AC43" s="95" t="n">
+      <c r="AD43" s="95" t="n">
         <v>-5.36</v>
       </c>
-      <c r="AD43" s="95" t="n">
+      <c r="AE43" s="95" t="n">
         <v>-4.69</v>
-      </c>
-      <c r="AE43" s="95" t="n">
-        <v>-5.1</v>
       </c>
     </row>
     <row r="44">
@@ -11235,91 +11235,91 @@
         <v>-6.01</v>
       </c>
       <c r="C44" s="95" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="D44" s="95" t="n">
         <v>-6.31</v>
       </c>
-      <c r="D44" s="95" t="n">
+      <c r="E44" s="95" t="n">
         <v>-4.48</v>
       </c>
-      <c r="E44" s="95" t="n">
+      <c r="F44" s="95" t="n">
         <v>-5.85</v>
       </c>
-      <c r="F44" s="95" t="n">
+      <c r="G44" s="95" t="n">
         <v>-4.68</v>
       </c>
-      <c r="G44" s="95" t="n">
+      <c r="H44" s="95" t="n">
         <v>-2.89</v>
       </c>
-      <c r="H44" s="95" t="n">
+      <c r="I44" s="95" t="n">
         <v>-3.77</v>
       </c>
-      <c r="I44" s="95" t="n">
+      <c r="J44" s="95" t="n">
         <v>-6.01</v>
       </c>
-      <c r="J44" s="95" t="n">
+      <c r="K44" s="95" t="n">
         <v>-6.35</v>
       </c>
-      <c r="K44" s="95" t="n">
+      <c r="L44" s="95" t="n">
         <v>-6.86</v>
       </c>
-      <c r="L44" s="95" t="n">
+      <c r="M44" s="95" t="n">
         <v>-7.99</v>
       </c>
-      <c r="M44" s="95" t="n">
+      <c r="N44" s="95" t="n">
         <v>-6.6</v>
       </c>
-      <c r="N44" s="95" t="n">
+      <c r="O44" s="95" t="n">
         <v>-8.43</v>
       </c>
-      <c r="O44" s="95" t="n">
+      <c r="P44" s="95" t="n">
         <v>-8.75</v>
       </c>
-      <c r="P44" s="95" t="n">
+      <c r="Q44" s="95" t="n">
         <v>-9.210000000000001</v>
-      </c>
-      <c r="Q44" s="95" t="n">
-        <v>-8.789999999999999</v>
       </c>
       <c r="R44" s="95" t="n">
         <v>-8.789999999999999</v>
       </c>
       <c r="S44" s="95" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="T44" s="95" t="n">
         <v>-9.26</v>
       </c>
-      <c r="T44" s="95" t="n">
+      <c r="U44" s="95" t="n">
         <v>-9.44</v>
       </c>
-      <c r="U44" s="95" t="n">
+      <c r="V44" s="95" t="n">
         <v>-9.02</v>
       </c>
-      <c r="V44" s="95" t="n">
+      <c r="W44" s="95" t="n">
         <v>-10.35</v>
       </c>
-      <c r="W44" s="95" t="n">
+      <c r="X44" s="95" t="n">
         <v>-8.789999999999999</v>
       </c>
-      <c r="X44" s="95" t="n">
+      <c r="Y44" s="95" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="Y44" s="95" t="n">
+      <c r="Z44" s="95" t="n">
         <v>-7.18</v>
       </c>
-      <c r="Z44" s="95" t="n">
+      <c r="AA44" s="95" t="n">
         <v>-6.04</v>
       </c>
-      <c r="AA44" s="95" t="n">
+      <c r="AB44" s="95" t="n">
         <v>-5.64</v>
       </c>
-      <c r="AB44" s="95" t="n">
+      <c r="AC44" s="95" t="n">
         <v>-4.72</v>
       </c>
-      <c r="AC44" s="95" t="n">
+      <c r="AD44" s="95" t="n">
         <v>-5.61</v>
       </c>
-      <c r="AD44" s="95" t="n">
+      <c r="AE44" s="95" t="n">
         <v>-5.62</v>
-      </c>
-      <c r="AE44" s="95" t="n">
-        <v>-4.58</v>
       </c>
     </row>
     <row r="45">
@@ -11332,91 +11332,91 @@
         <v>45.03</v>
       </c>
       <c r="C45" s="95" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="D45" s="95" t="n">
         <v>33.57</v>
       </c>
-      <c r="D45" s="95" t="n">
+      <c r="E45" s="95" t="n">
         <v>45.48</v>
       </c>
-      <c r="E45" s="95" t="n">
+      <c r="F45" s="95" t="n">
         <v>44.93</v>
       </c>
-      <c r="F45" s="95" t="n">
+      <c r="G45" s="95" t="n">
         <v>52.35</v>
       </c>
-      <c r="G45" s="95" t="n">
+      <c r="H45" s="95" t="n">
         <v>78.61</v>
       </c>
-      <c r="H45" s="95" t="n">
+      <c r="I45" s="95" t="n">
         <v>75.48</v>
       </c>
-      <c r="I45" s="95" t="n">
+      <c r="J45" s="95" t="n">
         <v>57.98</v>
       </c>
-      <c r="J45" s="95" t="n">
+      <c r="K45" s="95" t="n">
         <v>66.2</v>
       </c>
-      <c r="K45" s="95" t="n">
+      <c r="L45" s="95" t="n">
         <v>52.83</v>
       </c>
-      <c r="L45" s="95" t="n">
+      <c r="M45" s="95" t="n">
         <v>51.58</v>
       </c>
-      <c r="M45" s="95" t="n">
+      <c r="N45" s="95" t="n">
         <v>74.97</v>
       </c>
-      <c r="N45" s="95" t="n">
+      <c r="O45" s="95" t="n">
         <v>45.92</v>
       </c>
-      <c r="O45" s="95" t="n">
+      <c r="P45" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="P45" s="95" t="n">
+      <c r="Q45" s="95" t="n">
         <v>48.71</v>
       </c>
-      <c r="Q45" s="95" t="n">
+      <c r="R45" s="95" t="n">
         <v>53.61</v>
       </c>
-      <c r="R45" s="95" t="n">
+      <c r="S45" s="95" t="n">
         <v>45.19</v>
       </c>
-      <c r="S45" s="95" t="n">
+      <c r="T45" s="95" t="n">
         <v>32.83</v>
       </c>
-      <c r="T45" s="95" t="n">
+      <c r="U45" s="95" t="n">
         <v>34.58</v>
       </c>
-      <c r="U45" s="95" t="n">
+      <c r="V45" s="95" t="n">
         <v>37.2</v>
       </c>
-      <c r="V45" s="95" t="n">
+      <c r="W45" s="95" t="n">
         <v>16.31</v>
       </c>
-      <c r="W45" s="95" t="n">
+      <c r="X45" s="95" t="n">
         <v>22.99</v>
       </c>
-      <c r="X45" s="95" t="n">
+      <c r="Y45" s="95" t="n">
         <v>32.1</v>
       </c>
-      <c r="Y45" s="95" t="n">
+      <c r="Z45" s="95" t="n">
         <v>48.66</v>
       </c>
-      <c r="Z45" s="95" t="n">
+      <c r="AA45" s="95" t="n">
         <v>80.73</v>
       </c>
-      <c r="AA45" s="95" t="n">
+      <c r="AB45" s="95" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="AB45" s="95" t="n">
+      <c r="AC45" s="95" t="n">
         <v>83.84</v>
       </c>
-      <c r="AC45" s="95" t="n">
+      <c r="AD45" s="95" t="n">
         <v>74.67</v>
       </c>
-      <c r="AD45" s="95" t="n">
+      <c r="AE45" s="95" t="n">
         <v>72.3</v>
-      </c>
-      <c r="AE45" s="95" t="n">
-        <v>85.51000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -11430,139 +11430,139 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C46" s="94" t="inlineStr">
+      <c r="C46" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D46" s="93" t="inlineStr">
+      <c r="E46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E46" s="93" t="inlineStr">
+      <c r="F46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="93" t="inlineStr">
+      <c r="G46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="I46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I46" s="93" t="inlineStr">
+      <c r="J46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J46" s="92" t="inlineStr">
+      <c r="K46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="L46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L46" s="93" t="inlineStr">
+      <c r="M46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M46" s="92" t="inlineStr">
+      <c r="N46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="92" t="inlineStr">
+      <c r="O46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="92" t="inlineStr">
+      <c r="P46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="92" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q46" s="92" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="92" t="inlineStr">
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="94" t="inlineStr">
+      <c r="T46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T46" s="94" t="inlineStr">
+      <c r="U46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U46" s="94" t="inlineStr">
+      <c r="V46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V46" s="94" t="inlineStr">
+      <c r="W46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W46" s="94" t="inlineStr">
+      <c r="X46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X46" s="94" t="inlineStr">
+      <c r="Y46" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y46" s="93" t="inlineStr">
+      <c r="Z46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z46" s="93" t="inlineStr">
+      <c r="AA46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA46" s="93" t="inlineStr">
+      <c r="AB46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB46" s="92" t="inlineStr">
+      <c r="AC46" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AC46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AD46" s="93" t="inlineStr">
@@ -11586,91 +11586,91 @@
         <v>1.99</v>
       </c>
       <c r="C47" s="95" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D47" s="95" t="n">
         <v>2.59</v>
       </c>
-      <c r="D47" s="95" t="n">
+      <c r="E47" s="95" t="n">
         <v>4.12</v>
       </c>
-      <c r="E47" s="95" t="n">
+      <c r="F47" s="95" t="n">
         <v>5.36</v>
       </c>
-      <c r="F47" s="95" t="n">
+      <c r="G47" s="95" t="n">
         <v>4.62</v>
       </c>
-      <c r="G47" s="95" t="n">
+      <c r="H47" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="H47" s="95" t="n">
+      <c r="I47" s="95" t="n">
         <v>4.27</v>
       </c>
-      <c r="I47" s="95" t="n">
+      <c r="J47" s="95" t="n">
         <v>2.96</v>
       </c>
-      <c r="J47" s="95" t="n">
+      <c r="K47" s="95" t="n">
         <v>4.58</v>
       </c>
-      <c r="K47" s="95" t="n">
+      <c r="L47" s="95" t="n">
         <v>3.04</v>
       </c>
-      <c r="L47" s="95" t="n">
+      <c r="M47" s="95" t="n">
         <v>2.66</v>
       </c>
-      <c r="M47" s="95" t="n">
+      <c r="N47" s="95" t="n">
         <v>4.35</v>
       </c>
-      <c r="N47" s="95" t="n">
+      <c r="O47" s="95" t="n">
         <v>3.06</v>
       </c>
-      <c r="O47" s="95" t="n">
+      <c r="P47" s="95" t="n">
         <v>3.02</v>
       </c>
-      <c r="P47" s="95" t="n">
+      <c r="Q47" s="95" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q47" s="95" t="n">
+      <c r="R47" s="95" t="n">
         <v>2.95</v>
-      </c>
-      <c r="R47" s="95" t="n">
-        <v>1.45</v>
       </c>
       <c r="S47" s="95" t="n">
         <v>1.45</v>
       </c>
       <c r="T47" s="95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U47" s="95" t="n">
         <v>0.74</v>
       </c>
-      <c r="U47" s="95" t="n">
+      <c r="V47" s="95" t="n">
         <v>2.08</v>
       </c>
-      <c r="V47" s="95" t="n">
+      <c r="W47" s="95" t="n">
         <v>1.67</v>
       </c>
-      <c r="W47" s="95" t="n">
+      <c r="X47" s="95" t="n">
         <v>1.7</v>
       </c>
-      <c r="X47" s="95" t="n">
+      <c r="Y47" s="95" t="n">
         <v>-0.21</v>
       </c>
-      <c r="Y47" s="95" t="n">
+      <c r="Z47" s="95" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z47" s="95" t="n">
+      <c r="AA47" s="95" t="n">
         <v>2.36</v>
       </c>
-      <c r="AA47" s="95" t="n">
+      <c r="AB47" s="95" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB47" s="95" t="n">
+      <c r="AC47" s="95" t="n">
         <v>1.39</v>
       </c>
-      <c r="AC47" s="95" t="n">
+      <c r="AD47" s="95" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD47" s="95" t="n">
+      <c r="AE47" s="95" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE47" s="95" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="48">
@@ -11683,91 +11683,91 @@
         <v>7.2</v>
       </c>
       <c r="C48" s="95" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D48" s="95" t="n">
         <v>7.01</v>
       </c>
-      <c r="D48" s="95" t="n">
+      <c r="E48" s="95" t="n">
         <v>7.87</v>
       </c>
-      <c r="E48" s="95" t="n">
+      <c r="F48" s="95" t="n">
         <v>6.58</v>
       </c>
-      <c r="F48" s="95" t="n">
+      <c r="G48" s="95" t="n">
         <v>7.78</v>
       </c>
-      <c r="G48" s="95" t="n">
+      <c r="H48" s="95" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="H48" s="95" t="n">
+      <c r="I48" s="95" t="n">
         <v>6.31</v>
       </c>
-      <c r="I48" s="95" t="n">
+      <c r="J48" s="95" t="n">
         <v>4.66</v>
-      </c>
-      <c r="J48" s="95" t="n">
-        <v>3.7</v>
       </c>
       <c r="K48" s="95" t="n">
         <v>3.7</v>
       </c>
       <c r="L48" s="95" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M48" s="95" t="n">
         <v>1.72</v>
       </c>
-      <c r="M48" s="95" t="n">
+      <c r="N48" s="95" t="n">
         <v>3.46</v>
       </c>
-      <c r="N48" s="95" t="n">
+      <c r="O48" s="95" t="n">
         <v>2.34</v>
       </c>
-      <c r="O48" s="95" t="n">
+      <c r="P48" s="95" t="n">
         <v>1.26</v>
       </c>
-      <c r="P48" s="95" t="n">
+      <c r="Q48" s="95" t="n">
         <v>0.84</v>
       </c>
-      <c r="Q48" s="95" t="n">
+      <c r="R48" s="95" t="n">
         <v>1.71</v>
       </c>
-      <c r="R48" s="95" t="n">
+      <c r="S48" s="95" t="n">
         <v>1.41</v>
       </c>
-      <c r="S48" s="95" t="n">
+      <c r="T48" s="95" t="n">
         <v>0.68</v>
       </c>
-      <c r="T48" s="95" t="n">
+      <c r="U48" s="95" t="n">
         <v>0.48</v>
       </c>
-      <c r="U48" s="95" t="n">
+      <c r="V48" s="95" t="n">
         <v>2.38</v>
       </c>
-      <c r="V48" s="95" t="n">
+      <c r="W48" s="95" t="n">
         <v>1.75</v>
       </c>
-      <c r="W48" s="95" t="n">
+      <c r="X48" s="95" t="n">
         <v>3.59</v>
       </c>
-      <c r="X48" s="95" t="n">
+      <c r="Y48" s="95" t="n">
         <v>3.65</v>
       </c>
-      <c r="Y48" s="95" t="n">
+      <c r="Z48" s="95" t="n">
         <v>4.49</v>
       </c>
-      <c r="Z48" s="95" t="n">
+      <c r="AA48" s="95" t="n">
         <v>5.4</v>
       </c>
-      <c r="AA48" s="95" t="n">
+      <c r="AB48" s="95" t="n">
         <v>5.24</v>
       </c>
-      <c r="AB48" s="95" t="n">
+      <c r="AC48" s="95" t="n">
         <v>6.57</v>
       </c>
-      <c r="AC48" s="95" t="n">
+      <c r="AD48" s="95" t="n">
         <v>5.43</v>
       </c>
-      <c r="AD48" s="95" t="n">
+      <c r="AE48" s="95" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AE48" s="95" t="n">
-        <v>5.08</v>
       </c>
     </row>
     <row r="49">
@@ -11780,104 +11780,104 @@
         <v>53.55</v>
       </c>
       <c r="C49" s="95" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="D49" s="95" t="n">
         <v>46.86</v>
       </c>
-      <c r="D49" s="95" t="n">
+      <c r="E49" s="95" t="n">
         <v>56.45</v>
       </c>
-      <c r="E49" s="95" t="n">
+      <c r="F49" s="95" t="n">
         <v>59.76</v>
       </c>
-      <c r="F49" s="95" t="n">
+      <c r="G49" s="95" t="n">
         <v>67.34999999999999</v>
       </c>
-      <c r="G49" s="95" t="n">
+      <c r="H49" s="95" t="n">
         <v>78.38</v>
       </c>
-      <c r="H49" s="95" t="n">
+      <c r="I49" s="95" t="n">
         <v>72.42</v>
       </c>
-      <c r="I49" s="95" t="n">
+      <c r="J49" s="95" t="n">
         <v>59.91</v>
       </c>
-      <c r="J49" s="95" t="n">
+      <c r="K49" s="95" t="n">
         <v>66</v>
       </c>
-      <c r="K49" s="95" t="n">
+      <c r="L49" s="95" t="n">
         <v>59.4</v>
       </c>
-      <c r="L49" s="95" t="n">
+      <c r="M49" s="95" t="n">
         <v>52.95</v>
       </c>
-      <c r="M49" s="95" t="n">
+      <c r="N49" s="95" t="n">
         <v>75.06999999999999</v>
       </c>
-      <c r="N49" s="95" t="n">
+      <c r="O49" s="95" t="n">
         <v>61.14</v>
       </c>
-      <c r="O49" s="95" t="n">
+      <c r="P49" s="95" t="n">
         <v>62.6</v>
       </c>
-      <c r="P49" s="95" t="n">
+      <c r="Q49" s="95" t="n">
         <v>57.16</v>
       </c>
-      <c r="Q49" s="95" t="n">
+      <c r="R49" s="95" t="n">
         <v>62.56</v>
       </c>
-      <c r="R49" s="95" t="n">
+      <c r="S49" s="95" t="n">
         <v>52.29</v>
       </c>
-      <c r="S49" s="95" t="n">
+      <c r="T49" s="95" t="n">
         <v>37.42</v>
       </c>
-      <c r="T49" s="95" t="n">
+      <c r="U49" s="95" t="n">
         <v>31.32</v>
       </c>
-      <c r="U49" s="95" t="n">
+      <c r="V49" s="95" t="n">
         <v>40.38</v>
       </c>
-      <c r="V49" s="95" t="n">
+      <c r="W49" s="95" t="n">
         <v>26.19</v>
       </c>
-      <c r="W49" s="95" t="n">
+      <c r="X49" s="95" t="n">
         <v>42.54</v>
       </c>
-      <c r="X49" s="95" t="n">
+      <c r="Y49" s="95" t="n">
         <v>43.82</v>
       </c>
-      <c r="Y49" s="95" t="n">
+      <c r="Z49" s="95" t="n">
         <v>58.62</v>
       </c>
-      <c r="Z49" s="95" t="n">
+      <c r="AA49" s="95" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="AA49" s="95" t="n">
+      <c r="AB49" s="95" t="n">
         <v>87.20999999999999</v>
       </c>
-      <c r="AB49" s="95" t="n">
+      <c r="AC49" s="95" t="n">
         <v>88.2</v>
       </c>
-      <c r="AC49" s="95" t="n">
+      <c r="AD49" s="95" t="n">
         <v>84.89</v>
       </c>
-      <c r="AD49" s="95" t="n">
+      <c r="AE49" s="95" t="n">
         <v>81.56999999999999</v>
-      </c>
-      <c r="AE49" s="95" t="n">
-        <v>79.09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：vn:RS3:14.32&lt;=25;sensex:RS10:33.56&lt;=39</t>
+          <t>今日买报：sensex:RS10:29.6&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="91" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RS3:99.75&gt;=66;kc:RNG60:26.36&gt;=25;kc:RS5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RS3:99.48&gt;=93;hk50:RNG60:29.75&gt;=15;hk50:RNG120:32.66&gt;=25;hk50:RS4:89.49&gt;=73</t>
+          <t>今日卖报：sh:RNG60:12.81&gt;=10;sh:RS3:99.75&gt;=66;kc:RNG60:26.36&gt;=25;kc:RS5:96.84&gt;=65;cy:RNG60:32.05&gt;=25;cy:RS3:99.48&gt;=93;hk50:RNG60:32.21&gt;=15;hk50:RNG120:35.13&gt;=25;hk50:RS4:91.24&gt;=73</t>
         </is>
       </c>
     </row>

--- a/report_2409.xlsx
+++ b/report_2409.xlsx
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>2.98</v>
+        <v>1.44</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>2.98</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>13.62</v>
+        <v>12.76</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>13.62</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>81.84</v>
+        <v>30.41</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>81.84</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>6.54</v>
+        <v>4.88</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>6.54</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.24</v>
+        <v>10.99</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.24</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>68.36</v>
+        <v>34.52</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>68.36</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>-0.8</v>
+        <v>-2.58</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>-0.8</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>14.18</v>
+        <v>12.98</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>14.18</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>85.03</v>
+        <v>32.92</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>85.03</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-0.73</v>
+        <v>-1.08</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-1.19</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>4.75</v>
+        <v>4.38</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-0.47</v>
@@ -10427,13 +10427,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="76" t="inlineStr">
+      <c r="A37" s="96" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>33.58</v>
+        <v>13.62</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>14.32</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>2.21</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>10.03</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>29.6</v>
+        <v>29.96</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>33.56</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="94" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.37</v>
+        <v>-0.74</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.37</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-6.01</v>
+        <v>-5.56</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-6.01</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>45.03</v>
+        <v>50.81</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>45.03</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>1.99</v>
+        <v>2.76</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>1.99</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>7.2</v>
+        <v>7.71</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>7.2</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>53.55</v>
+        <v>52.29</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>53.55</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:29.6&lt;=39</t>
+          <t>今日买报：ixic:RS2:32.92&lt;=38;vn:RS3:13.62&lt;=25;sensex:RS10:29.96&lt;=39</t>
         </is>
       </c>
     </row>
